--- a/docs/resultados_convocatorias.xlsx
+++ b/docs/resultados_convocatorias.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Recursos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$210</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,13 +84,13 @@
     <font>
       <name val="Leelawadee UI"/>
       <b val="1"/>
-      <color rgb="00DC2626"/>
+      <color rgb="00065F46"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Leelawadee UI"/>
       <b val="1"/>
-      <color rgb="00065F46"/>
+      <color rgb="00DC2626"/>
       <sz val="10"/>
     </font>
     <font>
@@ -166,17 +166,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00065F46"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -268,11 +268,11 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -312,8 +312,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -679,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M210"/>
+  <dimension ref="A1:M209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -707,7 +707,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 12/09/2026 09:42 - 203 convocatorias - 11 nuevas</t>
+          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 13/09/2026 10:44 - 202 convocatorias - 11 nuevas</t>
         </is>
       </c>
     </row>
@@ -9802,11 +9802,7 @@
           <t>PERSONAS JURÍDICAS QUE NO DESARROLLAN ACTIVIDAD ECONÓMICA. . Regiones: ES211 - Araba/Álava</t>
         </is>
       </c>
-      <c r="L197" s="15" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+      <c r="L197" s="6" t="inlineStr"/>
       <c r="M197" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -9814,21 +9810,21 @@
       </c>
     </row>
     <row r="198" ht="28" customHeight="1">
-      <c r="A198" s="16" t="inlineStr">
+      <c r="A198" s="15" t="inlineStr">
         <is>
           <t>🟢 Euskadi</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
-      <c r="A199" s="17" t="inlineStr">
+      <c r="A199" s="16" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>EUS-47015</t>
+          <t>EUS-71187</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
@@ -9864,7 +9860,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L199" s="15" t="inlineStr">
+      <c r="L199" s="17" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9876,14 +9872,14 @@
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
-      <c r="A200" s="17" t="inlineStr">
+      <c r="A200" s="16" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>EUS-18875</t>
+          <t>EUS-18280</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
@@ -9919,7 +9915,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L200" s="15" t="inlineStr">
+      <c r="L200" s="17" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9931,14 +9927,14 @@
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
-      <c r="A201" s="17" t="inlineStr">
+      <c r="A201" s="16" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>EUS-03901</t>
+          <t>EUS-83528</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -9974,7 +9970,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L201" s="15" t="inlineStr">
+      <c r="L201" s="17" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9986,14 +9982,14 @@
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
-      <c r="A202" s="17" t="inlineStr">
+      <c r="A202" s="16" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>EUS-17248</t>
+          <t>EUS-58263</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
@@ -10029,7 +10025,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L202" s="15" t="inlineStr">
+      <c r="L202" s="17" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -10041,14 +10037,14 @@
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
-      <c r="A203" s="17" t="inlineStr">
+      <c r="A203" s="16" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>EUS-36047</t>
+          <t>EUS-37780</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
@@ -10084,7 +10080,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L203" s="15" t="inlineStr">
+      <c r="L203" s="17" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -10096,19 +10092,19 @@
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
-      <c r="A204" s="17" t="inlineStr">
+      <c r="A204" s="16" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>EUS-38592</t>
+          <t>EUS-87782</t>
         </is>
       </c>
       <c r="C204" s="6" t="inlineStr">
         <is>
-          <t>O. (pto 21036009); ; suministro de bancos ,modelo neobarcino 1800 natural,para mobiliario urbano. (pto 21036009)</t>
+          <t>Servicio de limpieza a prestar en las instalaciones del CENTRO DE DESARROLLO EMPRESARIAL DE LA MARGEN IZQUIERDA, S.A. (BIC BIZKAIA EZKERRALDEA) sitas en 48901 Barakaldo (Bizkaia), Avda. Altos Hornos d</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
@@ -10139,7 +10135,11 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L204" s="6" t="inlineStr"/>
+      <c r="L204" s="17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
       <c r="M204" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -10147,19 +10147,19 @@
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
-      <c r="A205" s="17" t="inlineStr">
+      <c r="A205" s="16" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>EUS-51365</t>
+          <t>EUS-48229</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>Servicio de alquiler de proyector digital para el Zornotza Aretoa</t>
+          <t>Servicio de mantenimiento integral del edificio e instalaciones de Azkuna Zentroa</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
@@ -10190,7 +10190,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L205" s="15" t="inlineStr">
+      <c r="L205" s="17" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -10202,19 +10202,19 @@
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
-      <c r="A206" s="17" t="inlineStr">
+      <c r="A206" s="16" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>EUS-28575</t>
+          <t>EUS-84876</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>Suministro, colocación, integración y puesta en marcha de equipos de los sistemas de seguridad del edificio Koldo Mitxelena.</t>
+          <t>O. (pto 21036009); ; suministro de bancos ,modelo neobarcino 1800 natural,para mobiliario urbano. (pto 21036009)</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
@@ -10245,7 +10245,11 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L206" s="6" t="inlineStr"/>
+      <c r="L206" s="17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
       <c r="M206" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -10253,19 +10257,19 @@
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
-      <c r="A207" s="17" t="inlineStr">
+      <c r="A207" s="16" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>EUS-74130</t>
+          <t>EUS-51515</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>Levantamiento Topográfico de la Red de saneamiento y pluviales, así como inventario de arquetas del conjunto edificado del Hospital Universitario Donostia</t>
+          <t>Servicio de alquiler de proyector digital para el Zornotza Aretoa</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
@@ -10296,7 +10300,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L207" s="15" t="inlineStr">
+      <c r="L207" s="17" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -10308,19 +10312,19 @@
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
-      <c r="A208" s="17" t="inlineStr">
+      <c r="A208" s="16" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>EUS-74639</t>
+          <t>EUS-20770</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>Obras de adecuación a la protección contra incendios en el Edificio Anexo del Hospital de Leza</t>
+          <t>Suministro, colocación, integración y puesta en marcha de equipos de los sistemas de seguridad del edificio Koldo Mitxelena.</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
@@ -10351,7 +10355,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L208" s="15" t="inlineStr">
+      <c r="L208" s="17" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -10363,19 +10367,19 @@
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
-      <c r="A209" s="17" t="inlineStr">
+      <c r="A209" s="16" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>EUS-61809</t>
+          <t>EUS-12021</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>Transporte adaptado alumna.</t>
+          <t>Levantamiento Topográfico de la Red de saneamiento y pluviales, así como inventario de arquetas del conjunto edificado del Hospital Universitario Donostia</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
@@ -10406,7 +10410,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L209" s="15" t="inlineStr">
+      <c r="L209" s="17" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -10417,63 +10421,8 @@
         </is>
       </c>
     </row>
-    <row r="210" ht="40" customHeight="1">
-      <c r="A210" s="17" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="B210" s="6" t="inlineStr">
-        <is>
-          <t>EUS-93696</t>
-        </is>
-      </c>
-      <c r="C210" s="6" t="inlineStr">
-        <is>
-          <t>Instalación paneles solares 10% instalación legalización</t>
-        </is>
-      </c>
-      <c r="D210" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="E210" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F210" s="6" t="inlineStr"/>
-      <c r="G210" s="6" t="inlineStr"/>
-      <c r="H210" s="6" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="I210" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="J210" s="6" t="inlineStr"/>
-      <c r="K210" s="6" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="L210" s="15" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="M210" s="9" t="inlineStr">
-        <is>
-          <t>Ver</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:M210"/>
+  <autoFilter ref="A4:M209"/>
   <mergeCells count="5">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
@@ -10684,7 +10633,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M210" r:id="rId203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10696,7 +10644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3044"/>
+  <dimension ref="A1:F3029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -49814,7 +49762,7 @@
     <row r="2866" ht="30" customHeight="1">
       <c r="A2866" s="18" t="inlineStr">
         <is>
-          <t>FICHA 192: EUS-47015</t>
+          <t>FICHA 192: EUS-71187</t>
         </is>
       </c>
       <c r="B2866" s="19" t="n"/>
@@ -49863,7 +49811,7 @@
       </c>
       <c r="B2869" s="21" t="inlineStr">
         <is>
-          <t>EUS-47015</t>
+          <t>EUS-71187</t>
         </is>
       </c>
       <c r="C2869" s="22" t="n"/>
@@ -50026,7 +49974,7 @@
     <row r="2881" ht="30" customHeight="1">
       <c r="A2881" s="18" t="inlineStr">
         <is>
-          <t>FICHA 193: EUS-18875</t>
+          <t>FICHA 193: EUS-18280</t>
         </is>
       </c>
       <c r="B2881" s="19" t="n"/>
@@ -50075,7 +50023,7 @@
       </c>
       <c r="B2884" s="21" t="inlineStr">
         <is>
-          <t>EUS-18875</t>
+          <t>EUS-18280</t>
         </is>
       </c>
       <c r="C2884" s="22" t="n"/>
@@ -50238,7 +50186,7 @@
     <row r="2896" ht="30" customHeight="1">
       <c r="A2896" s="18" t="inlineStr">
         <is>
-          <t>FICHA 194: EUS-03901</t>
+          <t>FICHA 194: EUS-83528</t>
         </is>
       </c>
       <c r="B2896" s="19" t="n"/>
@@ -50287,7 +50235,7 @@
       </c>
       <c r="B2899" s="21" t="inlineStr">
         <is>
-          <t>EUS-03901</t>
+          <t>EUS-83528</t>
         </is>
       </c>
       <c r="C2899" s="22" t="n"/>
@@ -50450,7 +50398,7 @@
     <row r="2911" ht="30" customHeight="1">
       <c r="A2911" s="18" t="inlineStr">
         <is>
-          <t>FICHA 195: EUS-17248</t>
+          <t>FICHA 195: EUS-58263</t>
         </is>
       </c>
       <c r="B2911" s="19" t="n"/>
@@ -50499,7 +50447,7 @@
       </c>
       <c r="B2914" s="21" t="inlineStr">
         <is>
-          <t>EUS-17248</t>
+          <t>EUS-58263</t>
         </is>
       </c>
       <c r="C2914" s="22" t="n"/>
@@ -50662,7 +50610,7 @@
     <row r="2926" ht="30" customHeight="1">
       <c r="A2926" s="18" t="inlineStr">
         <is>
-          <t>FICHA 196: EUS-36047</t>
+          <t>FICHA 196: EUS-37780</t>
         </is>
       </c>
       <c r="B2926" s="19" t="n"/>
@@ -50711,7 +50659,7 @@
       </c>
       <c r="B2929" s="21" t="inlineStr">
         <is>
-          <t>EUS-36047</t>
+          <t>EUS-37780</t>
         </is>
       </c>
       <c r="C2929" s="22" t="n"/>
@@ -50874,7 +50822,7 @@
     <row r="2941" ht="30" customHeight="1">
       <c r="A2941" s="18" t="inlineStr">
         <is>
-          <t>FICHA 197: EUS-38592</t>
+          <t>FICHA 197: EUS-87782</t>
         </is>
       </c>
       <c r="B2941" s="19" t="n"/>
@@ -50907,7 +50855,7 @@
       </c>
       <c r="B2943" s="21" t="inlineStr">
         <is>
-          <t>O. (pto 21036009); ; suministro de bancos ,modelo neobarcino 1800 natural,para mobiliario urbano. (pto 21036009)</t>
+          <t>Servicio de limpieza a prestar en las instalaciones del CENTRO DE DESARROLLO EMPRESARIAL DE LA MARGEN IZQUIERDA, S.A. (BIC BIZKAIA EZKERRALDEA) sitas en 48901 Barakaldo (Bizkaia), Avda. Altos Hornos d</t>
         </is>
       </c>
       <c r="C2943" s="22" t="n"/>
@@ -50923,7 +50871,7 @@
       </c>
       <c r="B2944" s="21" t="inlineStr">
         <is>
-          <t>EUS-38592</t>
+          <t>EUS-87782</t>
         </is>
       </c>
       <c r="C2944" s="22" t="n"/>
@@ -51075,7 +51023,7 @@
       </c>
       <c r="B2954" s="24" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/o-pto-21036009-suministro-bancos-modelo-neobarcino-1800-natural-mobiliario-urbano-pto-21036009/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-limpieza-prestar-instalaciones-del-centro-desarrollo-empresarial-margen-izquierda-s-bic-bizkaia-ezkerraldea-sitas-48901-barakaldo-bizkaia-avda-altos-hornos-vizcaya-33/expjaso740813/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2954" s="22" t="n"/>
@@ -51086,7 +51034,7 @@
     <row r="2956" ht="30" customHeight="1">
       <c r="A2956" s="18" t="inlineStr">
         <is>
-          <t>FICHA 198: EUS-51365</t>
+          <t>FICHA 198: EUS-48229</t>
         </is>
       </c>
       <c r="B2956" s="19" t="n"/>
@@ -51111,7 +51059,7 @@
       <c r="E2957" s="22" t="n"/>
       <c r="F2957" s="22" t="n"/>
     </row>
-    <row r="2958" ht="20" customHeight="1">
+    <row r="2958" ht="45" customHeight="1">
       <c r="A2958" s="20" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -51119,7 +51067,7 @@
       </c>
       <c r="B2958" s="21" t="inlineStr">
         <is>
-          <t>Servicio de alquiler de proyector digital para el Zornotza Aretoa</t>
+          <t>Servicio de mantenimiento integral del edificio e instalaciones de Azkuna Zentroa</t>
         </is>
       </c>
       <c r="C2958" s="22" t="n"/>
@@ -51135,7 +51083,7 @@
       </c>
       <c r="B2959" s="21" t="inlineStr">
         <is>
-          <t>EUS-51365</t>
+          <t>EUS-48229</t>
         </is>
       </c>
       <c r="C2959" s="22" t="n"/>
@@ -51287,7 +51235,7 @@
       </c>
       <c r="B2969" s="24" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-alquiler-proyector-digital-zornotza-aretoa/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-mantenimiento-integral-del-edificio-e-instalaciones-azkuna-zentroa/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2969" s="22" t="n"/>
@@ -51298,7 +51246,7 @@
     <row r="2971" ht="30" customHeight="1">
       <c r="A2971" s="18" t="inlineStr">
         <is>
-          <t>FICHA 199: EUS-28575</t>
+          <t>FICHA 199: EUS-84876</t>
         </is>
       </c>
       <c r="B2971" s="19" t="n"/>
@@ -51331,7 +51279,7 @@
       </c>
       <c r="B2973" s="21" t="inlineStr">
         <is>
-          <t>Suministro, colocación, integración y puesta en marcha de equipos de los sistemas de seguridad del edificio Koldo Mitxelena.</t>
+          <t>O. (pto 21036009); ; suministro de bancos ,modelo neobarcino 1800 natural,para mobiliario urbano. (pto 21036009)</t>
         </is>
       </c>
       <c r="C2973" s="22" t="n"/>
@@ -51347,7 +51295,7 @@
       </c>
       <c r="B2974" s="21" t="inlineStr">
         <is>
-          <t>EUS-28575</t>
+          <t>EUS-84876</t>
         </is>
       </c>
       <c r="C2974" s="22" t="n"/>
@@ -51499,7 +51447,7 @@
       </c>
       <c r="B2984" s="24" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-colocacion-integracion-y-puesta-marcha-equipos-sistemas-seguridad-del-edificio-koldo-mitxelena/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/o-pto-21036009-suministro-bancos-modelo-neobarcino-1800-natural-mobiliario-urbano-pto-21036009/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2984" s="22" t="n"/>
@@ -51510,7 +51458,7 @@
     <row r="2986" ht="30" customHeight="1">
       <c r="A2986" s="18" t="inlineStr">
         <is>
-          <t>FICHA 200: EUS-74130</t>
+          <t>FICHA 200: EUS-51515</t>
         </is>
       </c>
       <c r="B2986" s="19" t="n"/>
@@ -51535,7 +51483,7 @@
       <c r="E2987" s="22" t="n"/>
       <c r="F2987" s="22" t="n"/>
     </row>
-    <row r="2988" ht="45" customHeight="1">
+    <row r="2988" ht="20" customHeight="1">
       <c r="A2988" s="20" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -51543,7 +51491,7 @@
       </c>
       <c r="B2988" s="21" t="inlineStr">
         <is>
-          <t>Levantamiento Topográfico de la Red de saneamiento y pluviales, así como inventario de arquetas del conjunto edificado del Hospital Universitario Donostia</t>
+          <t>Servicio de alquiler de proyector digital para el Zornotza Aretoa</t>
         </is>
       </c>
       <c r="C2988" s="22" t="n"/>
@@ -51559,7 +51507,7 @@
       </c>
       <c r="B2989" s="21" t="inlineStr">
         <is>
-          <t>EUS-74130</t>
+          <t>EUS-51515</t>
         </is>
       </c>
       <c r="C2989" s="22" t="n"/>
@@ -51711,7 +51659,7 @@
       </c>
       <c r="B2999" s="24" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/levantamiento-topografico-red-saneamiento-y-pluviales-asi-como-inventario-arquetas-del-conjunto-edificado-del-hospital-universitario-donostia/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-alquiler-proyector-digital-zornotza-aretoa/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2999" s="22" t="n"/>
@@ -51722,7 +51670,7 @@
     <row r="3001" ht="30" customHeight="1">
       <c r="A3001" s="18" t="inlineStr">
         <is>
-          <t>FICHA 201: EUS-74639</t>
+          <t>FICHA 201: EUS-20770</t>
         </is>
       </c>
       <c r="B3001" s="19" t="n"/>
@@ -51755,7 +51703,7 @@
       </c>
       <c r="B3003" s="21" t="inlineStr">
         <is>
-          <t>Obras de adecuación a la protección contra incendios en el Edificio Anexo del Hospital de Leza</t>
+          <t>Suministro, colocación, integración y puesta en marcha de equipos de los sistemas de seguridad del edificio Koldo Mitxelena.</t>
         </is>
       </c>
       <c r="C3003" s="22" t="n"/>
@@ -51771,7 +51719,7 @@
       </c>
       <c r="B3004" s="21" t="inlineStr">
         <is>
-          <t>EUS-74639</t>
+          <t>EUS-20770</t>
         </is>
       </c>
       <c r="C3004" s="22" t="n"/>
@@ -51923,7 +51871,7 @@
       </c>
       <c r="B3014" s="24" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/obras-adecuacion-proteccion-incendios-edificio-anexo-del-hospital-leza/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-colocacion-integracion-y-puesta-marcha-equipos-sistemas-seguridad-del-edificio-koldo-mitxelena/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3014" s="22" t="n"/>
@@ -51934,7 +51882,7 @@
     <row r="3016" ht="30" customHeight="1">
       <c r="A3016" s="18" t="inlineStr">
         <is>
-          <t>FICHA 202: EUS-61809</t>
+          <t>FICHA 202: EUS-12021</t>
         </is>
       </c>
       <c r="B3016" s="19" t="n"/>
@@ -51959,7 +51907,7 @@
       <c r="E3017" s="22" t="n"/>
       <c r="F3017" s="22" t="n"/>
     </row>
-    <row r="3018" ht="20" customHeight="1">
+    <row r="3018" ht="45" customHeight="1">
       <c r="A3018" s="20" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -51967,7 +51915,7 @@
       </c>
       <c r="B3018" s="21" t="inlineStr">
         <is>
-          <t>Transporte adaptado alumna.</t>
+          <t>Levantamiento Topográfico de la Red de saneamiento y pluviales, así como inventario de arquetas del conjunto edificado del Hospital Universitario Donostia</t>
         </is>
       </c>
       <c r="C3018" s="22" t="n"/>
@@ -51983,7 +51931,7 @@
       </c>
       <c r="B3019" s="21" t="inlineStr">
         <is>
-          <t>EUS-61809</t>
+          <t>EUS-12021</t>
         </is>
       </c>
       <c r="C3019" s="22" t="n"/>
@@ -52135,7 +52083,7 @@
       </c>
       <c r="B3029" s="24" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/transporte-adaptado-alumna/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/levantamiento-topografico-red-saneamiento-y-pluviales-asi-como-inventario-arquetas-del-conjunto-edificado-del-hospital-universitario-donostia/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3029" s="22" t="n"/>
@@ -52143,220 +52091,8 @@
       <c r="E3029" s="22" t="n"/>
       <c r="F3029" s="22" t="n"/>
     </row>
-    <row r="3031" ht="30" customHeight="1">
-      <c r="A3031" s="18" t="inlineStr">
-        <is>
-          <t>FICHA 203: EUS-93696</t>
-        </is>
-      </c>
-      <c r="B3031" s="19" t="n"/>
-      <c r="C3031" s="19" t="n"/>
-      <c r="D3031" s="19" t="n"/>
-      <c r="E3031" s="19" t="n"/>
-      <c r="F3031" s="19" t="n"/>
-    </row>
-    <row r="3032" ht="20" customHeight="1">
-      <c r="A3032" s="20" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B3032" s="21" t="inlineStr">
-        <is>
-          <t>🟢 Euskadi</t>
-        </is>
-      </c>
-      <c r="C3032" s="22" t="n"/>
-      <c r="D3032" s="22" t="n"/>
-      <c r="E3032" s="22" t="n"/>
-      <c r="F3032" s="22" t="n"/>
-    </row>
-    <row r="3033" ht="20" customHeight="1">
-      <c r="A3033" s="20" t="inlineStr">
-        <is>
-          <t>Titulo</t>
-        </is>
-      </c>
-      <c r="B3033" s="21" t="inlineStr">
-        <is>
-          <t>Instalación paneles solares 10% instalación legalización</t>
-        </is>
-      </c>
-      <c r="C3033" s="22" t="n"/>
-      <c r="D3033" s="22" t="n"/>
-      <c r="E3033" s="22" t="n"/>
-      <c r="F3033" s="22" t="n"/>
-    </row>
-    <row r="3034" ht="20" customHeight="1">
-      <c r="A3034" s="20" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3034" s="21" t="inlineStr">
-        <is>
-          <t>EUS-93696</t>
-        </is>
-      </c>
-      <c r="C3034" s="22" t="n"/>
-      <c r="D3034" s="22" t="n"/>
-      <c r="E3034" s="22" t="n"/>
-      <c r="F3034" s="22" t="n"/>
-    </row>
-    <row r="3035" ht="20" customHeight="1">
-      <c r="A3035" s="20" t="inlineStr">
-        <is>
-          <t>Programa</t>
-        </is>
-      </c>
-      <c r="B3035" s="21" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="C3035" s="22" t="n"/>
-      <c r="D3035" s="22" t="n"/>
-      <c r="E3035" s="22" t="n"/>
-      <c r="F3035" s="22" t="n"/>
-    </row>
-    <row r="3036" ht="20" customHeight="1">
-      <c r="A3036" s="20" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B3036" s="21" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C3036" s="22" t="n"/>
-      <c r="D3036" s="22" t="n"/>
-      <c r="E3036" s="22" t="n"/>
-      <c r="F3036" s="22" t="n"/>
-    </row>
-    <row r="3037" ht="20" customHeight="1">
-      <c r="A3037" s="20" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="B3037" s="21" t="inlineStr"/>
-      <c r="C3037" s="22" t="n"/>
-      <c r="D3037" s="22" t="n"/>
-      <c r="E3037" s="22" t="n"/>
-      <c r="F3037" s="22" t="n"/>
-    </row>
-    <row r="3038" ht="20" customHeight="1">
-      <c r="A3038" s="20" t="inlineStr">
-        <is>
-          <t>Presupuesto (EUR)</t>
-        </is>
-      </c>
-      <c r="B3038" s="21" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="C3038" s="22" t="n"/>
-      <c r="D3038" s="22" t="n"/>
-      <c r="E3038" s="22" t="n"/>
-      <c r="F3038" s="22" t="n"/>
-    </row>
-    <row r="3039" ht="20" customHeight="1">
-      <c r="A3039" s="20" t="inlineStr">
-        <is>
-          <t>Tipo de Accion</t>
-        </is>
-      </c>
-      <c r="B3039" s="21" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="C3039" s="22" t="n"/>
-      <c r="D3039" s="22" t="n"/>
-      <c r="E3039" s="22" t="n"/>
-      <c r="F3039" s="22" t="n"/>
-    </row>
-    <row r="3040" ht="20" customHeight="1">
-      <c r="A3040" s="20" t="inlineStr">
-        <is>
-          <t>Call ID</t>
-        </is>
-      </c>
-      <c r="B3040" s="21" t="inlineStr"/>
-      <c r="C3040" s="22" t="n"/>
-      <c r="D3040" s="22" t="n"/>
-      <c r="E3040" s="22" t="n"/>
-      <c r="F3040" s="22" t="n"/>
-    </row>
-    <row r="3041" ht="20" customHeight="1">
-      <c r="A3041" s="20" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="B3041" s="21" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="C3041" s="22" t="n"/>
-      <c r="D3041" s="22" t="n"/>
-      <c r="E3041" s="22" t="n"/>
-      <c r="F3041" s="22" t="n"/>
-    </row>
-    <row r="3042" ht="20" customHeight="1">
-      <c r="A3042" s="20" t="inlineStr">
-        <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="B3042" s="21" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C3042" s="22" t="n"/>
-      <c r="D3042" s="22" t="n"/>
-      <c r="E3042" s="22" t="n"/>
-      <c r="F3042" s="22" t="n"/>
-    </row>
-    <row r="3043" ht="20" customHeight="1">
-      <c r="A3043" s="20" t="inlineStr">
-        <is>
-          <t>Relevancia Bilbao</t>
-        </is>
-      </c>
-      <c r="B3043" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
-        </is>
-      </c>
-      <c r="C3043" s="22" t="n"/>
-      <c r="D3043" s="22" t="n"/>
-      <c r="E3043" s="22" t="n"/>
-      <c r="F3043" s="22" t="n"/>
-    </row>
-    <row r="3044" ht="45" customHeight="1">
-      <c r="A3044" s="20" t="inlineStr">
-        <is>
-          <t>Enlace al portal</t>
-        </is>
-      </c>
-      <c r="B3044" s="24" t="inlineStr">
-        <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/instalacion-paneles-solares-10-instalacion-legalizacion/web01-tramite/es/</t>
-        </is>
-      </c>
-      <c r="C3044" s="22" t="n"/>
-      <c r="D3044" s="22" t="n"/>
-      <c r="E3044" s="22" t="n"/>
-      <c r="F3044" s="22" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="2842">
+  <mergeCells count="2828">
     <mergeCell ref="B679:F679"/>
     <mergeCell ref="B2192:F2192"/>
     <mergeCell ref="B1765:F1765"/>
@@ -52817,9 +52553,7 @@
     <mergeCell ref="B921:F921"/>
     <mergeCell ref="B606:F606"/>
     <mergeCell ref="B2741:F2741"/>
-    <mergeCell ref="B3039:F3039"/>
     <mergeCell ref="B2007:F2007"/>
-    <mergeCell ref="B3033:F3033"/>
     <mergeCell ref="B2436:F2436"/>
     <mergeCell ref="A1276:F1276"/>
     <mergeCell ref="B2770:F2770"/>
@@ -53018,7 +52752,6 @@
     <mergeCell ref="A2731:F2731"/>
     <mergeCell ref="B2246:F2246"/>
     <mergeCell ref="A946:F946"/>
-    <mergeCell ref="A3031:F3031"/>
     <mergeCell ref="A631:F631"/>
     <mergeCell ref="B117:F117"/>
     <mergeCell ref="B1783:F1783"/>
@@ -53096,7 +52829,6 @@
     <mergeCell ref="B2155:F2155"/>
     <mergeCell ref="B1123:F1123"/>
     <mergeCell ref="B368:F368"/>
-    <mergeCell ref="B3041:F3041"/>
     <mergeCell ref="B1254:F1254"/>
     <mergeCell ref="B1430:F1430"/>
     <mergeCell ref="B1552:F1552"/>
@@ -53279,7 +53011,6 @@
     <mergeCell ref="B1304:F1304"/>
     <mergeCell ref="B1608:F1608"/>
     <mergeCell ref="B2695:F2695"/>
-    <mergeCell ref="B3037:F3037"/>
     <mergeCell ref="B1967:F1967"/>
     <mergeCell ref="B908:F908"/>
     <mergeCell ref="B883:F883"/>
@@ -53728,7 +53459,6 @@
     <mergeCell ref="A2491:F2491"/>
     <mergeCell ref="A406:F406"/>
     <mergeCell ref="B951:F951"/>
-    <mergeCell ref="B3036:F3036"/>
     <mergeCell ref="B1249:F1249"/>
     <mergeCell ref="B524:F524"/>
     <mergeCell ref="B1854:F1854"/>
@@ -53736,7 +53466,6 @@
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B2012:F2012"/>
     <mergeCell ref="B953:F953"/>
-    <mergeCell ref="B3038:F3038"/>
     <mergeCell ref="B1251:F1251"/>
     <mergeCell ref="B1549:F1549"/>
     <mergeCell ref="B1856:F1856"/>
@@ -53822,7 +53551,6 @@
     <mergeCell ref="B891:F891"/>
     <mergeCell ref="B3009:F3009"/>
     <mergeCell ref="B1191:F1191"/>
-    <mergeCell ref="B3034:F3034"/>
     <mergeCell ref="B609:F609"/>
     <mergeCell ref="B1247:F1247"/>
     <mergeCell ref="B1977:F1977"/>
@@ -53840,7 +53568,6 @@
     <mergeCell ref="B1547:F1547"/>
     <mergeCell ref="B1207:F1207"/>
     <mergeCell ref="B490:F490"/>
-    <mergeCell ref="B3035:F3035"/>
     <mergeCell ref="B1338:F1338"/>
     <mergeCell ref="B3029:F3029"/>
     <mergeCell ref="B604:F604"/>
@@ -54443,7 +54170,6 @@
     <mergeCell ref="B1315:F1315"/>
     <mergeCell ref="B283:F283"/>
     <mergeCell ref="B2377:F2377"/>
-    <mergeCell ref="B3042:F3042"/>
     <mergeCell ref="B1649:F1649"/>
     <mergeCell ref="B590:F590"/>
     <mergeCell ref="B888:F888"/>
@@ -54467,7 +54193,6 @@
     <mergeCell ref="B512:F512"/>
     <mergeCell ref="B2734:F2734"/>
     <mergeCell ref="B2728:F2728"/>
-    <mergeCell ref="B3032:F3032"/>
     <mergeCell ref="B2000:F2000"/>
     <mergeCell ref="B303:F303"/>
     <mergeCell ref="B941:F941"/>
@@ -54907,7 +54632,6 @@
     <mergeCell ref="B318:F318"/>
     <mergeCell ref="A1741:F1741"/>
     <mergeCell ref="B1098:F1098"/>
-    <mergeCell ref="B3043:F3043"/>
     <mergeCell ref="B958:F958"/>
     <mergeCell ref="B1134:F1134"/>
     <mergeCell ref="B1256:F1256"/>
@@ -54927,7 +54651,6 @@
     <mergeCell ref="B1562:F1562"/>
     <mergeCell ref="B2317:F2317"/>
     <mergeCell ref="B1556:F1556"/>
-    <mergeCell ref="B3044:F3044"/>
     <mergeCell ref="A856:F856"/>
     <mergeCell ref="B1129:F1129"/>
     <mergeCell ref="B374:F374"/>
@@ -55027,7 +54750,6 @@
     <mergeCell ref="B197:F197"/>
     <mergeCell ref="B2104:F2104"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B3040:F3040"/>
     <mergeCell ref="B1343:F1343"/>
     <mergeCell ref="B1641:F1641"/>
     <mergeCell ref="B2315:F2315"/>
@@ -55403,7 +55125,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2999" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3014" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3029" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3044" r:id="rId203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55415,7 +55136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J204"/>
+  <dimension ref="A1:J203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -61633,7 +61354,7 @@
     <row r="193" ht="28" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>EUS-47015</t>
+          <t>EUS-71187</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
@@ -61669,7 +61390,7 @@
     <row r="194" ht="28" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>EUS-18875</t>
+          <t>EUS-18280</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
@@ -61705,7 +61426,7 @@
     <row r="195" ht="28" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>EUS-03901</t>
+          <t>EUS-83528</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
@@ -61741,7 +61462,7 @@
     <row r="196" ht="28" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>EUS-17248</t>
+          <t>EUS-58263</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
@@ -61777,7 +61498,7 @@
     <row r="197" ht="28" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>EUS-36047</t>
+          <t>EUS-37780</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
@@ -61813,12 +61534,12 @@
     <row r="198" ht="28" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>EUS-38592</t>
+          <t>EUS-87782</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>O. (pto 21036009); ; suministro de bancos ,modelo neobarcino</t>
+          <t>Servicio de limpieza a prestar en las instalaciones del CENT</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
@@ -61849,12 +61570,12 @@
     <row r="199" ht="28" customHeight="1">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>EUS-51365</t>
+          <t>EUS-48229</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>Servicio de alquiler de proyector digital para el Zornotza A</t>
+          <t>Servicio de mantenimiento integral del edificio e instalacio</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
@@ -61885,12 +61606,12 @@
     <row r="200" ht="28" customHeight="1">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>EUS-28575</t>
+          <t>EUS-84876</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Suministro, colocación, integración y puesta en marcha de eq</t>
+          <t>O. (pto 21036009); ; suministro de bancos ,modelo neobarcino</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
@@ -61921,12 +61642,12 @@
     <row r="201" ht="28" customHeight="1">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>EUS-74130</t>
+          <t>EUS-51515</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>Levantamiento Topográfico de la Red de saneamiento y pluvial</t>
+          <t>Servicio de alquiler de proyector digital para el Zornotza A</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -61957,12 +61678,12 @@
     <row r="202" ht="28" customHeight="1">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>EUS-74639</t>
+          <t>EUS-20770</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Obras de adecuación a la protección contra incendios en el E</t>
+          <t>Suministro, colocación, integración y puesta en marcha de eq</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
@@ -61993,12 +61714,12 @@
     <row r="203" ht="28" customHeight="1">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>EUS-61809</t>
+          <t>EUS-12021</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>Transporte adaptado alumna.</t>
+          <t>Levantamiento Topográfico de la Red de saneamiento y pluvial</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
@@ -62026,44 +61747,8 @@
       <c r="I203" s="6" t="inlineStr"/>
       <c r="J203" s="6" t="inlineStr"/>
     </row>
-    <row r="204" ht="28" customHeight="1">
-      <c r="A204" s="6" t="inlineStr">
-        <is>
-          <t>EUS-93696</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
-        <is>
-          <t>Instalación paneles solares 10% instalación legalización</t>
-        </is>
-      </c>
-      <c r="C204" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="D204" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E204" s="6" t="inlineStr"/>
-      <c r="F204" s="27" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="G204" s="6" t="inlineStr"/>
-      <c r="H204" s="6" t="inlineStr">
-        <is>
-          <t>Por revisar</t>
-        </is>
-      </c>
-      <c r="I204" s="6" t="inlineStr"/>
-      <c r="J204" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J204"/>
+  <autoFilter ref="A1:J203"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/resultados_convocatorias.xlsx
+++ b/docs/resultados_convocatorias.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Recursos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$208</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$204</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M208"/>
+  <dimension ref="A1:M209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -685,7 +685,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 19/09/2026 09:51 - 202 convocatorias - 11 nuevas</t>
+          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 20/09/2026 10:12 - 203 convocatorias - 12 nuevas</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>31127</t>
+          <t>410806ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
+          <t>Hydrogen cities</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr"/>
@@ -4524,12 +4524,12 @@
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>Aplicable a rehabilitación de edificios municipales.</t>
+          <t>Corredor Vasco del Hidrógeno. Petronor y Puerto de Bilbao involucrados.</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
+          <t>Hydrogen cities</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4547,12 +4547,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>96629</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
+          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background</t>
+          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr"/>
@@ -4594,19 +4594,15 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>INNOVFUND</t>
+          <t>96629</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>Innovation Fund</t>
-        </is>
-      </c>
+          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr"/>
       <c r="E87" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4627,7 +4623,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
+          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4645,15 +4641,19 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>INNOVFUND</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr"/>
+          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Innovation Fund</t>
+        </is>
+      </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarb</t>
+          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr"/>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>96375</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
+          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr"/>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>Margen izquierda con pasado industrial. Potencial reconversión.</t>
+          <t>Aplicable a rehabilitación de edificios municipales.</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
+          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarb</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>52786</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>Roadmap for updating Territorial just transition plans</t>
+          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr"/>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>Roadmap for updating Territorial just transition plans Promoting individual projects within planned concentrating activities has a small effect on economic reactivation and population fixing. Innovati</t>
+          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr"/>
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>ESF</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>A Social City Fund to foster just transition in the City of Leuven</t>
+          <t>Roadmap for updating Territorial just transition plans</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>A Social City Fund to foster just transition in the City of Leuven</t>
+          <t>Roadmap for updating Territorial just transition plans Promoting individual projects within planned concentrating activities has a small effect on economic reactivation and population fixing. Innovati</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -4833,12 +4833,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>IMREG</t>
+          <t>ESF</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
+          <t>A Social City Fund to foster just transition in the City of Leuven</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr"/>
@@ -4857,12 +4857,12 @@
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>País Vasco es región en transición. Fondos FEDER disponibles.</t>
+          <t>Margen izquierda con pasado industrial. Potencial reconversión.</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
+          <t>A Social City Fund to foster just transition in the City of Leuven</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr"/>
@@ -4880,12 +4880,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>897315282</t>
+          <t>IMREG</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Social Innovation Fund</t>
+          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr"/>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>Aplicable a Petronor/Repsol (Muskiz) y Puerto de Bilbao.</t>
+          <t>País Vasco es región en transición. Fondos FEDER disponibles.</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>Social Innovation Fund</t>
+          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -4927,19 +4927,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>897315282</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Social Innovation Fund</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr"/>
       <c r="E94" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4948,19 +4944,19 @@
       <c r="F94" s="6" t="inlineStr"/>
       <c r="G94" s="6" t="inlineStr"/>
       <c r="H94" s="6" t="inlineStr"/>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>INFO</t>
+      <c r="I94" s="12" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>Revisar relevancia para el Ayuntamiento de Bilbao.</t>
+          <t>Aplicable a Petronor/Repsol (Muskiz) y Puerto de Bilbao.</t>
         </is>
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Social Innovation Fund</t>
         </is>
       </c>
       <c r="L94" s="6" t="inlineStr"/>
@@ -4978,15 +4974,19 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5025,12 +5025,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr"/>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cove</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr"/>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr"/>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cove</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5119,19 +5119,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr"/>
       <c r="E98" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -5152,7 +5148,7 @@
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr"/>
@@ -5170,15 +5166,19 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr"/>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr"/>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr"/>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr"/>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5311,12 +5311,12 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr"/>
@@ -5358,12 +5358,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr"/>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5405,12 +5405,12 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr"/>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L104" s="6" t="inlineStr"/>
@@ -5452,12 +5452,12 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr"/>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr"/>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="L106" s="6" t="inlineStr"/>
@@ -5546,12 +5546,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5593,12 +5593,12 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="L108" s="6" t="inlineStr"/>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -5687,12 +5687,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="L110" s="6" t="inlineStr"/>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr"/>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr"/>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="L112" s="6" t="inlineStr"/>
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr"/>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -5875,12 +5875,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr"/>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="L114" s="6" t="inlineStr"/>
@@ -5922,12 +5922,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr"/>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr"/>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="L116" s="6" t="inlineStr"/>
@@ -6016,12 +6016,12 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr"/>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6063,12 +6063,12 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr"/>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through th</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr"/>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr"/>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on </t>
+          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through th</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6157,12 +6157,12 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr"/>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t xml:space="preserve">Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on </t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr"/>
@@ -6204,12 +6204,12 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr"/>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6251,12 +6251,12 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr"/>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="L122" s="6" t="inlineStr"/>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr"/>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="L124" s="6" t="inlineStr"/>
@@ -6392,12 +6392,12 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr"/>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="L126" s="6" t="inlineStr"/>
@@ -6486,12 +6486,12 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr"/>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Respon</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr"/>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Respon</t>
         </is>
       </c>
       <c r="L128" s="6" t="inlineStr"/>
@@ -6580,12 +6580,12 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr"/>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6627,12 +6627,12 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr"/>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered </t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="L130" s="6" t="inlineStr"/>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr"/>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage propo</t>
+          <t xml:space="preserve">The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered </t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -6721,12 +6721,12 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr"/>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in th</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage propo</t>
         </is>
       </c>
       <c r="L132" s="6" t="inlineStr"/>
@@ -6768,12 +6768,12 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>PPPA2027</t>
+          <t>31176</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr"/>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in th</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -6909,12 +6909,12 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>PPPA2027</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr"/>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="L136" s="6" t="inlineStr"/>
@@ -6956,12 +6956,12 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>886623263</t>
+          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr"/>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7003,12 +7003,12 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>877314852</t>
+          <t>886623263</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr"/>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr"/>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>884174595</t>
+          <t>877314852</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7097,12 +7097,12 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>900546740</t>
+          <t>884174595</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr"/>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr"/>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>941945952</t>
+          <t>900546740</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7191,12 +7191,12 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>941945952</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr"/>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="K142" s="6" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="L142" s="6" t="inlineStr"/>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>ERDFTA</t>
+          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr"/>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7285,12 +7285,12 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>ERDFTA</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr"/>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K144" s="6" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="L144" s="6" t="inlineStr"/>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>877067502</t>
+          <t>90488</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>INSTITUTIA PUBLICA CENTRUL MUNICIPAL PENTRU DEZVOLTAREA ANTREPRENORIATULUI</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>INSTITUTIA PUBLICA CENTRUL MUNICIPAL PENTRU DEZVOLTAREA ANTREPRENORIATULUI</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>EUS-27253</t>
+          <t>EUS-77406</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>EUS-76571</t>
+          <t>EUS-37002</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
@@ -9846,12 +9846,12 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>EUS-30498</t>
+          <t>EUS-85357</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>Servicio del mantenimiento preventivo del sistema de climatización RITTAL BLUE E+</t>
+          <t>Suministro y montaje de mobiliario medioambientalmente sostenible para la nueva sede de EITB en Vitoria</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
@@ -9882,7 +9882,11 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L199" s="6" t="inlineStr"/>
+      <c r="L199" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
       <c r="M199" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -9897,12 +9901,12 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>EUS-86571</t>
+          <t>EUS-32616</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>Dirección de Obra y servicio de Coordinación de Seguridad y Salud de las obras comprendidas en el Proyecto de Ejecución de Climatización y obra civil auxiliar del bar cafetería restaurante del edifici</t>
+          <t>Servicio del mantenimiento preventivo del sistema de climatización RITTAL BLUE E+</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
@@ -9952,12 +9956,12 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>EUS-99941</t>
+          <t>EUS-67929</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>Subvenciones para la organización, digitalización y difusión de archivos no públicos (2026)</t>
+          <t>Dirección de Obra y servicio de Coordinación de Seguridad y Salud de las obras comprendidas en el Proyecto de Ejecución de Climatización y obra civil auxiliar del bar cafetería restaurante del edifici</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
@@ -9974,12 +9978,12 @@
       <c r="G201" s="6" t="inlineStr"/>
       <c r="H201" s="6" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
-        </is>
-      </c>
-      <c r="I201" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I201" s="8" t="inlineStr">
+        <is>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J201" s="6" t="inlineStr"/>
@@ -10007,12 +10011,12 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>EUS-26323</t>
+          <t>EUS-13306</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>Subvenciones para la ejecución de trabajos orientados al ámbito de la salvaguarda del patrimonio cultural inmaterial 2026-2027</t>
+          <t>Subvenciones para la organización, digitalización y difusión de archivos no públicos (2026)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
@@ -10062,12 +10066,12 @@
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>EUS-50523</t>
+          <t>EUS-58268</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado una Alianza para las Cadenas de Valor Industriales Marítimas, que contempla la soberanía tecnológica y de suministros, la defensa, la compe</t>
+          <t>Subvenciones para la ejecución de trabajos orientados al ámbito de la salvaguarda del patrimonio cultural inmaterial 2026-2027</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
@@ -10117,12 +10121,12 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>EUS-38684</t>
+          <t>EUS-21314</t>
         </is>
       </c>
       <c r="C204" s="6" t="inlineStr">
         <is>
-          <t>Contrato de Servicios de Limpieza del edificio Hedy Lamarr, en el Campus Donostia de Parque Tecnológico de Euskadi</t>
+          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado una Alianza para las Cadenas de Valor Industriales Marítimas, que contempla la soberanía tecnológica y de suministros, la defensa, la compe</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
@@ -10139,7 +10143,7 @@
       <c r="G204" s="6" t="inlineStr"/>
       <c r="H204" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="I204" s="12" t="inlineStr">
@@ -10172,12 +10176,12 @@
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>EUS-54405</t>
+          <t>EUS-60761</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>Acuerdo marco para la contratación del servicio de logística para el Palacio Foral y edificios de la Diputación Foral de Gipuzkoa.</t>
+          <t>Contrato de Servicios de Limpieza del edificio Hedy Lamarr, en el Campus Donostia de Parque Tecnológico de Euskadi</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
@@ -10227,12 +10231,12 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>EUS-34834</t>
+          <t>EUS-31896</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>Acuerdo marco para la contratación, a través de la Central de Contratación Foral de Gipuzkoa, del servicio de vigilancia y seguridad de edificios de la Diputación Foral de Gipuzkoa, Juntas Generales d</t>
+          <t>Acuerdo marco para la contratación del servicio de logística para el Palacio Foral y edificios de la Diputación Foral de Gipuzkoa.</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
@@ -10282,12 +10286,12 @@
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>EUS-29338</t>
+          <t>EUS-64779</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>Servicio de instalación de infraestructuras audiovisuales y ambientación para la retransmisión de la final del Mundial de Fútbol.</t>
+          <t>Acuerdo marco para la contratación, a través de la Central de Contratación Foral de Gipuzkoa, del servicio de vigilancia y seguridad de edificios de la Diputación Foral de Gipuzkoa, Juntas Generales d</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
@@ -10318,11 +10322,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L207" s="15" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+      <c r="L207" s="6" t="inlineStr"/>
       <c r="M207" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -10337,12 +10337,12 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>EUS-60451</t>
+          <t>EUS-27350</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>Servicio de reparación de deshumectadora de la zona de piscinas cubiertas del muelle Churruca</t>
+          <t>Servicio de instalación de infraestructuras audiovisuales y ambientación para la retransmisión de la final del Mundial de Fútbol.</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
@@ -10384,8 +10384,63 @@
         </is>
       </c>
     </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>EUS-38278</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>Servicio de reparación de deshumectadora de la zona de piscinas cubiertas del muelle Churruca</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="inlineStr"/>
+      <c r="G209" s="6" t="inlineStr"/>
+      <c r="H209" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I209" s="12" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="J209" s="6" t="inlineStr"/>
+      <c r="K209" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L209" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M209" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:M208"/>
+  <autoFilter ref="A4:M209"/>
   <mergeCells count="4">
     <mergeCell ref="A196:M196"/>
     <mergeCell ref="A2:M2"/>
@@ -10595,6 +10650,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10606,7 +10662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3029"/>
+  <dimension ref="A1:F3044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26792,7 +26848,7 @@
     <row r="1186" ht="30" customHeight="1">
       <c r="A1186" s="16" t="inlineStr">
         <is>
-          <t>FICHA 80: 31127</t>
+          <t>FICHA 80: 410806ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B1186" s="17" t="n"/>
@@ -26817,7 +26873,7 @@
       <c r="E1187" s="20" t="n"/>
       <c r="F1187" s="20" t="n"/>
     </row>
-    <row r="1188" ht="45" customHeight="1">
+    <row r="1188" ht="20" customHeight="1">
       <c r="A1188" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -26825,7 +26881,7 @@
       </c>
       <c r="B1188" s="19" t="inlineStr">
         <is>
-          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
+          <t>Hydrogen cities</t>
         </is>
       </c>
       <c r="C1188" s="20" t="n"/>
@@ -26841,7 +26897,7 @@
       </c>
       <c r="B1189" s="19" t="inlineStr">
         <is>
-          <t>31127</t>
+          <t>410806ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C1189" s="20" t="n"/>
@@ -26933,7 +26989,7 @@
       <c r="E1195" s="20" t="n"/>
       <c r="F1195" s="20" t="n"/>
     </row>
-    <row r="1196" ht="45" customHeight="1">
+    <row r="1196" ht="20" customHeight="1">
       <c r="A1196" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -26941,7 +26997,7 @@
       </c>
       <c r="B1196" s="19" t="inlineStr">
         <is>
-          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
+          <t>Hydrogen cities</t>
         </is>
       </c>
       <c r="C1196" s="20" t="n"/>
@@ -26969,7 +27025,7 @@
       </c>
       <c r="B1198" s="19" t="inlineStr">
         <is>
-          <t>MEDIA — Aplicable a rehabilitación de edificios municipales.</t>
+          <t>MEDIA — Corredor Vasco del Hidrógeno. Petronor y Puerto de Bilbao involucrados.</t>
         </is>
       </c>
       <c r="C1198" s="20" t="n"/>
@@ -26985,7 +27041,7 @@
       </c>
       <c r="B1199" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31127</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/410806ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C1199" s="20" t="n"/>
@@ -26996,7 +27052,7 @@
     <row r="1201" ht="30" customHeight="1">
       <c r="A1201" s="16" t="inlineStr">
         <is>
-          <t>FICHA 81: 96629</t>
+          <t>FICHA 81: 31127</t>
         </is>
       </c>
       <c r="B1201" s="17" t="n"/>
@@ -27029,7 +27085,7 @@
       </c>
       <c r="B1203" s="19" t="inlineStr">
         <is>
-          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
+          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
         </is>
       </c>
       <c r="C1203" s="20" t="n"/>
@@ -27045,7 +27101,7 @@
       </c>
       <c r="B1204" s="19" t="inlineStr">
         <is>
-          <t>96629</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="C1204" s="20" t="n"/>
@@ -27145,7 +27201,7 @@
       </c>
       <c r="B1211" s="19" t="inlineStr">
         <is>
-          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
+          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
         </is>
       </c>
       <c r="C1211" s="20" t="n"/>
@@ -27189,7 +27245,7 @@
       </c>
       <c r="B1214" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/96629</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31127</t>
         </is>
       </c>
       <c r="C1214" s="20" t="n"/>
@@ -27200,7 +27256,7 @@
     <row r="1216" ht="30" customHeight="1">
       <c r="A1216" s="16" t="inlineStr">
         <is>
-          <t>FICHA 82: INNOVFUND</t>
+          <t>FICHA 82: 96629</t>
         </is>
       </c>
       <c r="B1216" s="17" t="n"/>
@@ -27233,7 +27289,7 @@
       </c>
       <c r="B1218" s="19" t="inlineStr">
         <is>
-          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
+          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
         </is>
       </c>
       <c r="C1218" s="20" t="n"/>
@@ -27249,7 +27305,7 @@
       </c>
       <c r="B1219" s="19" t="inlineStr">
         <is>
-          <t>INNOVFUND</t>
+          <t>96629</t>
         </is>
       </c>
       <c r="C1219" s="20" t="n"/>
@@ -27263,11 +27319,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1220" s="19" t="inlineStr">
-        <is>
-          <t>Innovation Fund</t>
-        </is>
-      </c>
+      <c r="B1220" s="19" t="inlineStr"/>
       <c r="C1220" s="20" t="n"/>
       <c r="D1220" s="20" t="n"/>
       <c r="E1220" s="20" t="n"/>
@@ -27339,11 +27391,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1225" s="19" t="inlineStr">
-        <is>
-          <t>InnovFund-2024-NZT</t>
-        </is>
-      </c>
+      <c r="B1225" s="19" t="inlineStr"/>
       <c r="C1225" s="20" t="n"/>
       <c r="D1225" s="20" t="n"/>
       <c r="E1225" s="20" t="n"/>
@@ -27357,7 +27405,7 @@
       </c>
       <c r="B1226" s="19" t="inlineStr">
         <is>
-          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
+          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
         </is>
       </c>
       <c r="C1226" s="20" t="n"/>
@@ -27401,7 +27449,7 @@
       </c>
       <c r="B1229" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/INNOVFUND</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/96629</t>
         </is>
       </c>
       <c r="C1229" s="20" t="n"/>
@@ -27412,7 +27460,7 @@
     <row r="1231" ht="30" customHeight="1">
       <c r="A1231" s="16" t="inlineStr">
         <is>
-          <t>FICHA 83: 96375</t>
+          <t>FICHA 83: INNOVFUND</t>
         </is>
       </c>
       <c r="B1231" s="17" t="n"/>
@@ -27445,7 +27493,7 @@
       </c>
       <c r="B1233" s="19" t="inlineStr">
         <is>
-          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
+          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
         </is>
       </c>
       <c r="C1233" s="20" t="n"/>
@@ -27461,7 +27509,7 @@
       </c>
       <c r="B1234" s="19" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>INNOVFUND</t>
         </is>
       </c>
       <c r="C1234" s="20" t="n"/>
@@ -27475,7 +27523,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1235" s="19" t="inlineStr"/>
+      <c r="B1235" s="19" t="inlineStr">
+        <is>
+          <t>Innovation Fund</t>
+        </is>
+      </c>
       <c r="C1235" s="20" t="n"/>
       <c r="D1235" s="20" t="n"/>
       <c r="E1235" s="20" t="n"/>
@@ -27547,7 +27599,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1240" s="19" t="inlineStr"/>
+      <c r="B1240" s="19" t="inlineStr">
+        <is>
+          <t>InnovFund-2024-NZT</t>
+        </is>
+      </c>
       <c r="C1240" s="20" t="n"/>
       <c r="D1240" s="20" t="n"/>
       <c r="E1240" s="20" t="n"/>
@@ -27561,7 +27617,7 @@
       </c>
       <c r="B1241" s="19" t="inlineStr">
         <is>
-          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
+          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
         </is>
       </c>
       <c r="C1241" s="20" t="n"/>
@@ -27605,7 +27661,7 @@
       </c>
       <c r="B1244" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/96375</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/INNOVFUND</t>
         </is>
       </c>
       <c r="C1244" s="20" t="n"/>
@@ -27616,7 +27672,7 @@
     <row r="1246" ht="30" customHeight="1">
       <c r="A1246" s="16" t="inlineStr">
         <is>
-          <t>FICHA 84: 52786</t>
+          <t>FICHA 84: 96375</t>
         </is>
       </c>
       <c r="B1246" s="17" t="n"/>
@@ -27649,7 +27705,7 @@
       </c>
       <c r="B1248" s="19" t="inlineStr">
         <is>
-          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
+          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
         </is>
       </c>
       <c r="C1248" s="20" t="n"/>
@@ -27665,7 +27721,7 @@
       </c>
       <c r="B1249" s="19" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>96375</t>
         </is>
       </c>
       <c r="C1249" s="20" t="n"/>
@@ -27765,7 +27821,7 @@
       </c>
       <c r="B1256" s="19" t="inlineStr">
         <is>
-          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
+          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
         </is>
       </c>
       <c r="C1256" s="20" t="n"/>
@@ -27793,7 +27849,7 @@
       </c>
       <c r="B1258" s="19" t="inlineStr">
         <is>
-          <t>MEDIA — Margen izquierda con pasado industrial. Potencial reconversión.</t>
+          <t>MEDIA — Aplicable a rehabilitación de edificios municipales.</t>
         </is>
       </c>
       <c r="C1258" s="20" t="n"/>
@@ -27809,7 +27865,7 @@
       </c>
       <c r="B1259" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/52786</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/96375</t>
         </is>
       </c>
       <c r="C1259" s="20" t="n"/>
@@ -27820,7 +27876,7 @@
     <row r="1261" ht="30" customHeight="1">
       <c r="A1261" s="16" t="inlineStr">
         <is>
-          <t>FICHA 85: 62137</t>
+          <t>FICHA 85: 52786</t>
         </is>
       </c>
       <c r="B1261" s="17" t="n"/>
@@ -27845,7 +27901,7 @@
       <c r="E1262" s="20" t="n"/>
       <c r="F1262" s="20" t="n"/>
     </row>
-    <row r="1263" ht="20" customHeight="1">
+    <row r="1263" ht="45" customHeight="1">
       <c r="A1263" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -27853,7 +27909,7 @@
       </c>
       <c r="B1263" s="19" t="inlineStr">
         <is>
-          <t>Roadmap for updating Territorial just transition plans</t>
+          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
         </is>
       </c>
       <c r="C1263" s="20" t="n"/>
@@ -27869,7 +27925,7 @@
       </c>
       <c r="B1264" s="19" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>52786</t>
         </is>
       </c>
       <c r="C1264" s="20" t="n"/>
@@ -27969,7 +28025,7 @@
       </c>
       <c r="B1271" s="19" t="inlineStr">
         <is>
-          <t>Roadmap for updating Territorial just transition plans Promoting individual projects within planned concentrating activities has a small effect on economic reactivation and population fixing. Innovation poles have a higher contribution to economic reactivation and population fixing than individual projects, due to the synergies they can achieve</t>
+          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
         </is>
       </c>
       <c r="C1271" s="20" t="n"/>
@@ -28013,7 +28069,7 @@
       </c>
       <c r="B1274" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/62137</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/52786</t>
         </is>
       </c>
       <c r="C1274" s="20" t="n"/>
@@ -28024,7 +28080,7 @@
     <row r="1276" ht="30" customHeight="1">
       <c r="A1276" s="16" t="inlineStr">
         <is>
-          <t>FICHA 86: ESF</t>
+          <t>FICHA 86: 62137</t>
         </is>
       </c>
       <c r="B1276" s="17" t="n"/>
@@ -28057,7 +28113,7 @@
       </c>
       <c r="B1278" s="19" t="inlineStr">
         <is>
-          <t>A Social City Fund to foster just transition in the City of Leuven</t>
+          <t>Roadmap for updating Territorial just transition plans</t>
         </is>
       </c>
       <c r="C1278" s="20" t="n"/>
@@ -28073,7 +28129,7 @@
       </c>
       <c r="B1279" s="19" t="inlineStr">
         <is>
-          <t>ESF</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="C1279" s="20" t="n"/>
@@ -28159,17 +28215,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1285" s="19" t="inlineStr">
-        <is>
-          <t>ESF-2023-SUPPLY-DEMAND</t>
-        </is>
-      </c>
+      <c r="B1285" s="19" t="inlineStr"/>
       <c r="C1285" s="20" t="n"/>
       <c r="D1285" s="20" t="n"/>
       <c r="E1285" s="20" t="n"/>
       <c r="F1285" s="20" t="n"/>
     </row>
-    <row r="1286" ht="20" customHeight="1">
+    <row r="1286" ht="45" customHeight="1">
       <c r="A1286" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -28177,7 +28229,7 @@
       </c>
       <c r="B1286" s="19" t="inlineStr">
         <is>
-          <t>A Social City Fund to foster just transition in the City of Leuven</t>
+          <t>Roadmap for updating Territorial just transition plans Promoting individual projects within planned concentrating activities has a small effect on economic reactivation and population fixing. Innovation poles have a higher contribution to economic reactivation and population fixing than individual projects, due to the synergies they can achieve</t>
         </is>
       </c>
       <c r="C1286" s="20" t="n"/>
@@ -28221,7 +28273,7 @@
       </c>
       <c r="B1289" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ESF</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/62137</t>
         </is>
       </c>
       <c r="C1289" s="20" t="n"/>
@@ -28232,7 +28284,7 @@
     <row r="1291" ht="30" customHeight="1">
       <c r="A1291" s="16" t="inlineStr">
         <is>
-          <t>FICHA 87: IMREG</t>
+          <t>FICHA 87: ESF</t>
         </is>
       </c>
       <c r="B1291" s="17" t="n"/>
@@ -28257,7 +28309,7 @@
       <c r="E1292" s="20" t="n"/>
       <c r="F1292" s="20" t="n"/>
     </row>
-    <row r="1293" ht="45" customHeight="1">
+    <row r="1293" ht="20" customHeight="1">
       <c r="A1293" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -28265,7 +28317,7 @@
       </c>
       <c r="B1293" s="19" t="inlineStr">
         <is>
-          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
+          <t>A Social City Fund to foster just transition in the City of Leuven</t>
         </is>
       </c>
       <c r="C1293" s="20" t="n"/>
@@ -28281,7 +28333,7 @@
       </c>
       <c r="B1294" s="19" t="inlineStr">
         <is>
-          <t>IMREG</t>
+          <t>ESF</t>
         </is>
       </c>
       <c r="C1294" s="20" t="n"/>
@@ -28369,7 +28421,7 @@
       </c>
       <c r="B1300" s="19" t="inlineStr">
         <is>
-          <t>IMREG-2022-INFOME</t>
+          <t>ESF-2023-SUPPLY-DEMAND</t>
         </is>
       </c>
       <c r="C1300" s="20" t="n"/>
@@ -28377,7 +28429,7 @@
       <c r="E1300" s="20" t="n"/>
       <c r="F1300" s="20" t="n"/>
     </row>
-    <row r="1301" ht="45" customHeight="1">
+    <row r="1301" ht="20" customHeight="1">
       <c r="A1301" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -28385,7 +28437,7 @@
       </c>
       <c r="B1301" s="19" t="inlineStr">
         <is>
-          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
+          <t>A Social City Fund to foster just transition in the City of Leuven</t>
         </is>
       </c>
       <c r="C1301" s="20" t="n"/>
@@ -28413,7 +28465,7 @@
       </c>
       <c r="B1303" s="19" t="inlineStr">
         <is>
-          <t>MEDIA — País Vasco es región en transición. Fondos FEDER disponibles.</t>
+          <t>MEDIA — Margen izquierda con pasado industrial. Potencial reconversión.</t>
         </is>
       </c>
       <c r="C1303" s="20" t="n"/>
@@ -28429,7 +28481,7 @@
       </c>
       <c r="B1304" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/IMREG</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ESF</t>
         </is>
       </c>
       <c r="C1304" s="20" t="n"/>
@@ -28440,7 +28492,7 @@
     <row r="1306" ht="30" customHeight="1">
       <c r="A1306" s="16" t="inlineStr">
         <is>
-          <t>FICHA 88: 897315282</t>
+          <t>FICHA 88: IMREG</t>
         </is>
       </c>
       <c r="B1306" s="17" t="n"/>
@@ -28465,7 +28517,7 @@
       <c r="E1307" s="20" t="n"/>
       <c r="F1307" s="20" t="n"/>
     </row>
-    <row r="1308" ht="20" customHeight="1">
+    <row r="1308" ht="45" customHeight="1">
       <c r="A1308" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -28473,7 +28525,7 @@
       </c>
       <c r="B1308" s="19" t="inlineStr">
         <is>
-          <t>Social Innovation Fund</t>
+          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
         </is>
       </c>
       <c r="C1308" s="20" t="n"/>
@@ -28489,7 +28541,7 @@
       </c>
       <c r="B1309" s="19" t="inlineStr">
         <is>
-          <t>897315282</t>
+          <t>IMREG</t>
         </is>
       </c>
       <c r="C1309" s="20" t="n"/>
@@ -28575,13 +28627,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1315" s="19" t="inlineStr"/>
+      <c r="B1315" s="19" t="inlineStr">
+        <is>
+          <t>IMREG-2022-INFOME</t>
+        </is>
+      </c>
       <c r="C1315" s="20" t="n"/>
       <c r="D1315" s="20" t="n"/>
       <c r="E1315" s="20" t="n"/>
       <c r="F1315" s="20" t="n"/>
     </row>
-    <row r="1316" ht="20" customHeight="1">
+    <row r="1316" ht="45" customHeight="1">
       <c r="A1316" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -28589,7 +28645,7 @@
       </c>
       <c r="B1316" s="19" t="inlineStr">
         <is>
-          <t>Social Innovation Fund</t>
+          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
         </is>
       </c>
       <c r="C1316" s="20" t="n"/>
@@ -28617,7 +28673,7 @@
       </c>
       <c r="B1318" s="19" t="inlineStr">
         <is>
-          <t>MEDIA — Aplicable a Petronor/Repsol (Muskiz) y Puerto de Bilbao.</t>
+          <t>MEDIA — País Vasco es región en transición. Fondos FEDER disponibles.</t>
         </is>
       </c>
       <c r="C1318" s="20" t="n"/>
@@ -28633,7 +28689,7 @@
       </c>
       <c r="B1319" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/897315282</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/IMREG</t>
         </is>
       </c>
       <c r="C1319" s="20" t="n"/>
@@ -28644,7 +28700,7 @@
     <row r="1321" ht="30" customHeight="1">
       <c r="A1321" s="16" t="inlineStr">
         <is>
-          <t>FICHA 89: HORIZON</t>
+          <t>FICHA 89: 897315282</t>
         </is>
       </c>
       <c r="B1321" s="17" t="n"/>
@@ -28677,7 +28733,7 @@
       </c>
       <c r="B1323" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Social Innovation Fund</t>
         </is>
       </c>
       <c r="C1323" s="20" t="n"/>
@@ -28693,7 +28749,7 @@
       </c>
       <c r="B1324" s="19" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>897315282</t>
         </is>
       </c>
       <c r="C1324" s="20" t="n"/>
@@ -28707,11 +28763,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1325" s="19" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+      <c r="B1325" s="19" t="inlineStr"/>
       <c r="C1325" s="20" t="n"/>
       <c r="D1325" s="20" t="n"/>
       <c r="E1325" s="20" t="n"/>
@@ -28783,11 +28835,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1330" s="19" t="inlineStr">
-        <is>
-          <t>HORIZON-MISS-2021-CIT-02</t>
-        </is>
-      </c>
+      <c r="B1330" s="19" t="inlineStr"/>
       <c r="C1330" s="20" t="n"/>
       <c r="D1330" s="20" t="n"/>
       <c r="E1330" s="20" t="n"/>
@@ -28801,7 +28849,7 @@
       </c>
       <c r="B1331" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Social Innovation Fund</t>
         </is>
       </c>
       <c r="C1331" s="20" t="n"/>
@@ -28829,7 +28877,7 @@
       </c>
       <c r="B1333" s="19" t="inlineStr">
         <is>
-          <t>INFO — Revisar relevancia para el Ayuntamiento de Bilbao.</t>
+          <t>MEDIA — Aplicable a Petronor/Repsol (Muskiz) y Puerto de Bilbao.</t>
         </is>
       </c>
       <c r="C1333" s="20" t="n"/>
@@ -28845,7 +28893,7 @@
       </c>
       <c r="B1334" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/897315282</t>
         </is>
       </c>
       <c r="C1334" s="20" t="n"/>
@@ -28856,7 +28904,7 @@
     <row r="1336" ht="30" customHeight="1">
       <c r="A1336" s="16" t="inlineStr">
         <is>
-          <t>FICHA 90: ERASMUS2027</t>
+          <t>FICHA 90: HORIZON</t>
         </is>
       </c>
       <c r="B1336" s="17" t="n"/>
@@ -28889,7 +28937,7 @@
       </c>
       <c r="B1338" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C1338" s="20" t="n"/>
@@ -28905,7 +28953,7 @@
       </c>
       <c r="B1339" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C1339" s="20" t="n"/>
@@ -28919,7 +28967,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1340" s="19" t="inlineStr"/>
+      <c r="B1340" s="19" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="C1340" s="20" t="n"/>
       <c r="D1340" s="20" t="n"/>
       <c r="E1340" s="20" t="n"/>
@@ -28993,7 +29045,7 @@
       </c>
       <c r="B1345" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
+          <t>HORIZON-MISS-2021-CIT-02</t>
         </is>
       </c>
       <c r="C1345" s="20" t="n"/>
@@ -29009,7 +29061,7 @@
       </c>
       <c r="B1346" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C1346" s="20" t="n"/>
@@ -29053,7 +29105,7 @@
       </c>
       <c r="B1349" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
         </is>
       </c>
       <c r="C1349" s="20" t="n"/>
@@ -29064,7 +29116,7 @@
     <row r="1351" ht="30" customHeight="1">
       <c r="A1351" s="16" t="inlineStr">
         <is>
-          <t>FICHA 91: 13349</t>
+          <t>FICHA 91: ERASMUS2027</t>
         </is>
       </c>
       <c r="B1351" s="17" t="n"/>
@@ -29089,7 +29141,7 @@
       <c r="E1352" s="20" t="n"/>
       <c r="F1352" s="20" t="n"/>
     </row>
-    <row r="1353" ht="45" customHeight="1">
+    <row r="1353" ht="20" customHeight="1">
       <c r="A1353" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -29097,7 +29149,7 @@
       </c>
       <c r="B1353" s="19" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C1353" s="20" t="n"/>
@@ -29113,7 +29165,7 @@
       </c>
       <c r="B1354" s="19" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C1354" s="20" t="n"/>
@@ -29199,13 +29251,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1360" s="19" t="inlineStr"/>
+      <c r="B1360" s="19" t="inlineStr">
+        <is>
+          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
+        </is>
+      </c>
       <c r="C1360" s="20" t="n"/>
       <c r="D1360" s="20" t="n"/>
       <c r="E1360" s="20" t="n"/>
       <c r="F1360" s="20" t="n"/>
     </row>
-    <row r="1361" ht="45" customHeight="1">
+    <row r="1361" ht="20" customHeight="1">
       <c r="A1361" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -29213,7 +29269,7 @@
       </c>
       <c r="B1361" s="19" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C1361" s="20" t="n"/>
@@ -29257,7 +29313,7 @@
       </c>
       <c r="B1364" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13349</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
         </is>
       </c>
       <c r="C1364" s="20" t="n"/>
@@ -29268,7 +29324,7 @@
     <row r="1366" ht="30" customHeight="1">
       <c r="A1366" s="16" t="inlineStr">
         <is>
-          <t>FICHA 92: 11301</t>
+          <t>FICHA 92: 13349</t>
         </is>
       </c>
       <c r="B1366" s="17" t="n"/>
@@ -29301,7 +29357,7 @@
       </c>
       <c r="B1368" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
         </is>
       </c>
       <c r="C1368" s="20" t="n"/>
@@ -29317,7 +29373,7 @@
       </c>
       <c r="B1369" s="19" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="C1369" s="20" t="n"/>
@@ -29417,7 +29473,7 @@
       </c>
       <c r="B1376" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
         </is>
       </c>
       <c r="C1376" s="20" t="n"/>
@@ -29461,7 +29517,7 @@
       </c>
       <c r="B1379" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/11301</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13349</t>
         </is>
       </c>
       <c r="C1379" s="20" t="n"/>
@@ -29472,7 +29528,7 @@
     <row r="1381" ht="30" customHeight="1">
       <c r="A1381" s="16" t="inlineStr">
         <is>
-          <t>FICHA 93: CEF2027</t>
+          <t>FICHA 93: 11301</t>
         </is>
       </c>
       <c r="B1381" s="17" t="n"/>
@@ -29497,7 +29553,7 @@
       <c r="E1382" s="20" t="n"/>
       <c r="F1382" s="20" t="n"/>
     </row>
-    <row r="1383" ht="20" customHeight="1">
+    <row r="1383" ht="45" customHeight="1">
       <c r="A1383" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -29505,7 +29561,7 @@
       </c>
       <c r="B1383" s="19" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
         </is>
       </c>
       <c r="C1383" s="20" t="n"/>
@@ -29521,7 +29577,7 @@
       </c>
       <c r="B1384" s="19" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="C1384" s="20" t="n"/>
@@ -29535,11 +29591,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1385" s="19" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+      <c r="B1385" s="19" t="inlineStr"/>
       <c r="C1385" s="20" t="n"/>
       <c r="D1385" s="20" t="n"/>
       <c r="E1385" s="20" t="n"/>
@@ -29611,17 +29663,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1390" s="19" t="inlineStr">
-        <is>
-          <t>CEF-T-2024-AFIFGEN</t>
-        </is>
-      </c>
+      <c r="B1390" s="19" t="inlineStr"/>
       <c r="C1390" s="20" t="n"/>
       <c r="D1390" s="20" t="n"/>
       <c r="E1390" s="20" t="n"/>
       <c r="F1390" s="20" t="n"/>
     </row>
-    <row r="1391" ht="20" customHeight="1">
+    <row r="1391" ht="45" customHeight="1">
       <c r="A1391" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -29629,7 +29677,7 @@
       </c>
       <c r="B1391" s="19" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
         </is>
       </c>
       <c r="C1391" s="20" t="n"/>
@@ -29673,7 +29721,7 @@
       </c>
       <c r="B1394" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/11301</t>
         </is>
       </c>
       <c r="C1394" s="20" t="n"/>
@@ -29684,7 +29732,7 @@
     <row r="1396" ht="30" customHeight="1">
       <c r="A1396" s="16" t="inlineStr">
         <is>
-          <t>FICHA 94: 19484</t>
+          <t>FICHA 94: CEF2027</t>
         </is>
       </c>
       <c r="B1396" s="17" t="n"/>
@@ -29709,7 +29757,7 @@
       <c r="E1397" s="20" t="n"/>
       <c r="F1397" s="20" t="n"/>
     </row>
-    <row r="1398" ht="45" customHeight="1">
+    <row r="1398" ht="20" customHeight="1">
       <c r="A1398" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -29717,7 +29765,7 @@
       </c>
       <c r="B1398" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="C1398" s="20" t="n"/>
@@ -29733,7 +29781,7 @@
       </c>
       <c r="B1399" s="19" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="C1399" s="20" t="n"/>
@@ -29747,7 +29795,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1400" s="19" t="inlineStr"/>
+      <c r="B1400" s="19" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="C1400" s="20" t="n"/>
       <c r="D1400" s="20" t="n"/>
       <c r="E1400" s="20" t="n"/>
@@ -29819,13 +29871,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1405" s="19" t="inlineStr"/>
+      <c r="B1405" s="19" t="inlineStr">
+        <is>
+          <t>CEF-T-2024-AFIFGEN</t>
+        </is>
+      </c>
       <c r="C1405" s="20" t="n"/>
       <c r="D1405" s="20" t="n"/>
       <c r="E1405" s="20" t="n"/>
       <c r="F1405" s="20" t="n"/>
     </row>
-    <row r="1406" ht="45" customHeight="1">
+    <row r="1406" ht="20" customHeight="1">
       <c r="A1406" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -29833,7 +29889,7 @@
       </c>
       <c r="B1406" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="C1406" s="20" t="n"/>
@@ -29877,7 +29933,7 @@
       </c>
       <c r="B1409" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19484</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF2027</t>
         </is>
       </c>
       <c r="C1409" s="20" t="n"/>
@@ -29888,7 +29944,7 @@
     <row r="1411" ht="30" customHeight="1">
       <c r="A1411" s="16" t="inlineStr">
         <is>
-          <t>FICHA 95: 915513452</t>
+          <t>FICHA 95: 19484</t>
         </is>
       </c>
       <c r="B1411" s="17" t="n"/>
@@ -29913,7 +29969,7 @@
       <c r="E1412" s="20" t="n"/>
       <c r="F1412" s="20" t="n"/>
     </row>
-    <row r="1413" ht="20" customHeight="1">
+    <row r="1413" ht="45" customHeight="1">
       <c r="A1413" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -29921,7 +29977,7 @@
       </c>
       <c r="B1413" s="19" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
         </is>
       </c>
       <c r="C1413" s="20" t="n"/>
@@ -29937,7 +29993,7 @@
       </c>
       <c r="B1414" s="19" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="C1414" s="20" t="n"/>
@@ -30029,7 +30085,7 @@
       <c r="E1420" s="20" t="n"/>
       <c r="F1420" s="20" t="n"/>
     </row>
-    <row r="1421" ht="20" customHeight="1">
+    <row r="1421" ht="45" customHeight="1">
       <c r="A1421" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -30037,7 +30093,7 @@
       </c>
       <c r="B1421" s="19" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
         </is>
       </c>
       <c r="C1421" s="20" t="n"/>
@@ -30081,7 +30137,7 @@
       </c>
       <c r="B1424" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/915513452</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19484</t>
         </is>
       </c>
       <c r="C1424" s="20" t="n"/>
@@ -30092,7 +30148,7 @@
     <row r="1426" ht="30" customHeight="1">
       <c r="A1426" s="16" t="inlineStr">
         <is>
-          <t>FICHA 96: 40556</t>
+          <t>FICHA 96: 915513452</t>
         </is>
       </c>
       <c r="B1426" s="17" t="n"/>
@@ -30117,7 +30173,7 @@
       <c r="E1427" s="20" t="n"/>
       <c r="F1427" s="20" t="n"/>
     </row>
-    <row r="1428" ht="45" customHeight="1">
+    <row r="1428" ht="20" customHeight="1">
       <c r="A1428" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -30125,7 +30181,7 @@
       </c>
       <c r="B1428" s="19" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C1428" s="20" t="n"/>
@@ -30141,7 +30197,7 @@
       </c>
       <c r="B1429" s="19" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="C1429" s="20" t="n"/>
@@ -30233,7 +30289,7 @@
       <c r="E1435" s="20" t="n"/>
       <c r="F1435" s="20" t="n"/>
     </row>
-    <row r="1436" ht="45" customHeight="1">
+    <row r="1436" ht="20" customHeight="1">
       <c r="A1436" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -30241,7 +30297,7 @@
       </c>
       <c r="B1436" s="19" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C1436" s="20" t="n"/>
@@ -30285,7 +30341,7 @@
       </c>
       <c r="B1439" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/40556</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/915513452</t>
         </is>
       </c>
       <c r="C1439" s="20" t="n"/>
@@ -30296,7 +30352,7 @@
     <row r="1441" ht="30" customHeight="1">
       <c r="A1441" s="16" t="inlineStr">
         <is>
-          <t>FICHA 97: 917671508</t>
+          <t>FICHA 97: 40556</t>
         </is>
       </c>
       <c r="B1441" s="17" t="n"/>
@@ -30321,7 +30377,7 @@
       <c r="E1442" s="20" t="n"/>
       <c r="F1442" s="20" t="n"/>
     </row>
-    <row r="1443" ht="20" customHeight="1">
+    <row r="1443" ht="45" customHeight="1">
       <c r="A1443" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -30329,7 +30385,7 @@
       </c>
       <c r="B1443" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="C1443" s="20" t="n"/>
@@ -30345,7 +30401,7 @@
       </c>
       <c r="B1444" s="19" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="C1444" s="20" t="n"/>
@@ -30437,7 +30493,7 @@
       <c r="E1450" s="20" t="n"/>
       <c r="F1450" s="20" t="n"/>
     </row>
-    <row r="1451" ht="20" customHeight="1">
+    <row r="1451" ht="45" customHeight="1">
       <c r="A1451" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -30445,7 +30501,7 @@
       </c>
       <c r="B1451" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="C1451" s="20" t="n"/>
@@ -30489,7 +30545,7 @@
       </c>
       <c r="B1454" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/40556</t>
         </is>
       </c>
       <c r="C1454" s="20" t="n"/>
@@ -30500,7 +30556,7 @@
     <row r="1456" ht="30" customHeight="1">
       <c r="A1456" s="16" t="inlineStr">
         <is>
-          <t>FICHA 98: 917721754</t>
+          <t>FICHA 98: 917671508</t>
         </is>
       </c>
       <c r="B1456" s="17" t="n"/>
@@ -30533,7 +30589,7 @@
       </c>
       <c r="B1458" s="19" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1458" s="20" t="n"/>
@@ -30549,7 +30605,7 @@
       </c>
       <c r="B1459" s="19" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C1459" s="20" t="n"/>
@@ -30649,7 +30705,7 @@
       </c>
       <c r="B1466" s="19" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1466" s="20" t="n"/>
@@ -30693,7 +30749,7 @@
       </c>
       <c r="B1469" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917721754</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
         </is>
       </c>
       <c r="C1469" s="20" t="n"/>
@@ -30704,7 +30760,7 @@
     <row r="1471" ht="30" customHeight="1">
       <c r="A1471" s="16" t="inlineStr">
         <is>
-          <t>FICHA 99: 919892711</t>
+          <t>FICHA 99: 917721754</t>
         </is>
       </c>
       <c r="B1471" s="17" t="n"/>
@@ -30737,7 +30793,7 @@
       </c>
       <c r="B1473" s="19" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1473" s="20" t="n"/>
@@ -30753,7 +30809,7 @@
       </c>
       <c r="B1474" s="19" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="C1474" s="20" t="n"/>
@@ -30853,7 +30909,7 @@
       </c>
       <c r="B1481" s="19" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1481" s="20" t="n"/>
@@ -30897,7 +30953,7 @@
       </c>
       <c r="B1484" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919892711</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917721754</t>
         </is>
       </c>
       <c r="C1484" s="20" t="n"/>
@@ -30908,7 +30964,7 @@
     <row r="1486" ht="30" customHeight="1">
       <c r="A1486" s="16" t="inlineStr">
         <is>
-          <t>FICHA 100: 939945909</t>
+          <t>FICHA 100: 919892711</t>
         </is>
       </c>
       <c r="B1486" s="17" t="n"/>
@@ -30941,7 +30997,7 @@
       </c>
       <c r="B1488" s="19" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="C1488" s="20" t="n"/>
@@ -30957,7 +31013,7 @@
       </c>
       <c r="B1489" s="19" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="C1489" s="20" t="n"/>
@@ -31057,7 +31113,7 @@
       </c>
       <c r="B1496" s="19" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="C1496" s="20" t="n"/>
@@ -31101,7 +31157,7 @@
       </c>
       <c r="B1499" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939945909</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919892711</t>
         </is>
       </c>
       <c r="C1499" s="20" t="n"/>
@@ -31112,7 +31168,7 @@
     <row r="1501" ht="30" customHeight="1">
       <c r="A1501" s="16" t="inlineStr">
         <is>
-          <t>FICHA 101: 917779760</t>
+          <t>FICHA 101: 939945909</t>
         </is>
       </c>
       <c r="B1501" s="17" t="n"/>
@@ -31145,7 +31201,7 @@
       </c>
       <c r="B1503" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C1503" s="20" t="n"/>
@@ -31161,7 +31217,7 @@
       </c>
       <c r="B1504" s="19" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="C1504" s="20" t="n"/>
@@ -31261,7 +31317,7 @@
       </c>
       <c r="B1511" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C1511" s="20" t="n"/>
@@ -31305,7 +31361,7 @@
       </c>
       <c r="B1514" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939945909</t>
         </is>
       </c>
       <c r="C1514" s="20" t="n"/>
@@ -31316,7 +31372,7 @@
     <row r="1516" ht="30" customHeight="1">
       <c r="A1516" s="16" t="inlineStr">
         <is>
-          <t>FICHA 102: 920115617</t>
+          <t>FICHA 102: 917779760</t>
         </is>
       </c>
       <c r="B1516" s="17" t="n"/>
@@ -31349,7 +31405,7 @@
       </c>
       <c r="B1518" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1518" s="20" t="n"/>
@@ -31365,7 +31421,7 @@
       </c>
       <c r="B1519" s="19" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C1519" s="20" t="n"/>
@@ -31465,7 +31521,7 @@
       </c>
       <c r="B1526" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1526" s="20" t="n"/>
@@ -31509,7 +31565,7 @@
       </c>
       <c r="B1529" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
         </is>
       </c>
       <c r="C1529" s="20" t="n"/>
@@ -31520,7 +31576,7 @@
     <row r="1531" ht="30" customHeight="1">
       <c r="A1531" s="16" t="inlineStr">
         <is>
-          <t>FICHA 103: 928447529</t>
+          <t>FICHA 103: 920115617</t>
         </is>
       </c>
       <c r="B1531" s="17" t="n"/>
@@ -31553,7 +31609,7 @@
       </c>
       <c r="B1533" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1533" s="20" t="n"/>
@@ -31569,7 +31625,7 @@
       </c>
       <c r="B1534" s="19" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C1534" s="20" t="n"/>
@@ -31669,7 +31725,7 @@
       </c>
       <c r="B1541" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1541" s="20" t="n"/>
@@ -31713,7 +31769,7 @@
       </c>
       <c r="B1544" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
         </is>
       </c>
       <c r="C1544" s="20" t="n"/>
@@ -31724,7 +31780,7 @@
     <row r="1546" ht="30" customHeight="1">
       <c r="A1546" s="16" t="inlineStr">
         <is>
-          <t>FICHA 104: 14272</t>
+          <t>FICHA 104: 928447529</t>
         </is>
       </c>
       <c r="B1546" s="17" t="n"/>
@@ -31749,7 +31805,7 @@
       <c r="E1547" s="20" t="n"/>
       <c r="F1547" s="20" t="n"/>
     </row>
-    <row r="1548" ht="45" customHeight="1">
+    <row r="1548" ht="20" customHeight="1">
       <c r="A1548" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -31757,7 +31813,7 @@
       </c>
       <c r="B1548" s="19" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1548" s="20" t="n"/>
@@ -31773,7 +31829,7 @@
       </c>
       <c r="B1549" s="19" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C1549" s="20" t="n"/>
@@ -31865,7 +31921,7 @@
       <c r="E1555" s="20" t="n"/>
       <c r="F1555" s="20" t="n"/>
     </row>
-    <row r="1556" ht="45" customHeight="1">
+    <row r="1556" ht="20" customHeight="1">
       <c r="A1556" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -31873,7 +31929,7 @@
       </c>
       <c r="B1556" s="19" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1556" s="20" t="n"/>
@@ -31917,7 +31973,7 @@
       </c>
       <c r="B1559" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14272</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
         </is>
       </c>
       <c r="C1559" s="20" t="n"/>
@@ -31928,7 +31984,7 @@
     <row r="1561" ht="30" customHeight="1">
       <c r="A1561" s="16" t="inlineStr">
         <is>
-          <t>FICHA 105: 996889759</t>
+          <t>FICHA 105: 14272</t>
         </is>
       </c>
       <c r="B1561" s="17" t="n"/>
@@ -31953,7 +32009,7 @@
       <c r="E1562" s="20" t="n"/>
       <c r="F1562" s="20" t="n"/>
     </row>
-    <row r="1563" ht="20" customHeight="1">
+    <row r="1563" ht="45" customHeight="1">
       <c r="A1563" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -31961,7 +32017,7 @@
       </c>
       <c r="B1563" s="19" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="C1563" s="20" t="n"/>
@@ -31977,7 +32033,7 @@
       </c>
       <c r="B1564" s="19" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="C1564" s="20" t="n"/>
@@ -32069,7 +32125,7 @@
       <c r="E1570" s="20" t="n"/>
       <c r="F1570" s="20" t="n"/>
     </row>
-    <row r="1571" ht="20" customHeight="1">
+    <row r="1571" ht="45" customHeight="1">
       <c r="A1571" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -32077,7 +32133,7 @@
       </c>
       <c r="B1571" s="19" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="C1571" s="20" t="n"/>
@@ -32121,7 +32177,7 @@
       </c>
       <c r="B1574" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/996889759</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14272</t>
         </is>
       </c>
       <c r="C1574" s="20" t="n"/>
@@ -32132,7 +32188,7 @@
     <row r="1576" ht="30" customHeight="1">
       <c r="A1576" s="16" t="inlineStr">
         <is>
-          <t>FICHA 106: 922165518</t>
+          <t>FICHA 106: 996889759</t>
         </is>
       </c>
       <c r="B1576" s="17" t="n"/>
@@ -32165,7 +32221,7 @@
       </c>
       <c r="B1578" s="19" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C1578" s="20" t="n"/>
@@ -32181,7 +32237,7 @@
       </c>
       <c r="B1579" s="19" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="C1579" s="20" t="n"/>
@@ -32281,7 +32337,7 @@
       </c>
       <c r="B1586" s="19" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C1586" s="20" t="n"/>
@@ -32325,7 +32381,7 @@
       </c>
       <c r="B1589" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/922165518</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/996889759</t>
         </is>
       </c>
       <c r="C1589" s="20" t="n"/>
@@ -32336,7 +32392,7 @@
     <row r="1591" ht="30" customHeight="1">
       <c r="A1591" s="16" t="inlineStr">
         <is>
-          <t>FICHA 107: 919917446</t>
+          <t>FICHA 107: 922165518</t>
         </is>
       </c>
       <c r="B1591" s="17" t="n"/>
@@ -32369,7 +32425,7 @@
       </c>
       <c r="B1593" s="19" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C1593" s="20" t="n"/>
@@ -32385,7 +32441,7 @@
       </c>
       <c r="B1594" s="19" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="C1594" s="20" t="n"/>
@@ -32485,7 +32541,7 @@
       </c>
       <c r="B1601" s="19" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C1601" s="20" t="n"/>
@@ -32529,7 +32585,7 @@
       </c>
       <c r="B1604" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919917446</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/922165518</t>
         </is>
       </c>
       <c r="C1604" s="20" t="n"/>
@@ -32540,7 +32596,7 @@
     <row r="1606" ht="30" customHeight="1">
       <c r="A1606" s="16" t="inlineStr">
         <is>
-          <t>FICHA 108: 917155468</t>
+          <t>FICHA 108: 919917446</t>
         </is>
       </c>
       <c r="B1606" s="17" t="n"/>
@@ -32573,7 +32629,7 @@
       </c>
       <c r="B1608" s="19" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C1608" s="20" t="n"/>
@@ -32589,7 +32645,7 @@
       </c>
       <c r="B1609" s="19" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="C1609" s="20" t="n"/>
@@ -32689,7 +32745,7 @@
       </c>
       <c r="B1616" s="19" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C1616" s="20" t="n"/>
@@ -32733,7 +32789,7 @@
       </c>
       <c r="B1619" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917155468</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919917446</t>
         </is>
       </c>
       <c r="C1619" s="20" t="n"/>
@@ -32744,7 +32800,7 @@
     <row r="1621" ht="30" customHeight="1">
       <c r="A1621" s="16" t="inlineStr">
         <is>
-          <t>FICHA 109: 95942</t>
+          <t>FICHA 109: 917155468</t>
         </is>
       </c>
       <c r="B1621" s="17" t="n"/>
@@ -32769,7 +32825,7 @@
       <c r="E1622" s="20" t="n"/>
       <c r="F1622" s="20" t="n"/>
     </row>
-    <row r="1623" ht="45" customHeight="1">
+    <row r="1623" ht="20" customHeight="1">
       <c r="A1623" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -32777,7 +32833,7 @@
       </c>
       <c r="B1623" s="19" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C1623" s="20" t="n"/>
@@ -32793,7 +32849,7 @@
       </c>
       <c r="B1624" s="19" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="C1624" s="20" t="n"/>
@@ -32885,7 +32941,7 @@
       <c r="E1630" s="20" t="n"/>
       <c r="F1630" s="20" t="n"/>
     </row>
-    <row r="1631" ht="45" customHeight="1">
+    <row r="1631" ht="20" customHeight="1">
       <c r="A1631" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -32893,7 +32949,7 @@
       </c>
       <c r="B1631" s="19" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C1631" s="20" t="n"/>
@@ -32937,7 +32993,7 @@
       </c>
       <c r="B1634" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95942</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917155468</t>
         </is>
       </c>
       <c r="C1634" s="20" t="n"/>
@@ -32948,7 +33004,7 @@
     <row r="1636" ht="30" customHeight="1">
       <c r="A1636" s="16" t="inlineStr">
         <is>
-          <t>FICHA 110: 898575215</t>
+          <t>FICHA 110: 95942</t>
         </is>
       </c>
       <c r="B1636" s="17" t="n"/>
@@ -32973,7 +33029,7 @@
       <c r="E1637" s="20" t="n"/>
       <c r="F1637" s="20" t="n"/>
     </row>
-    <row r="1638" ht="20" customHeight="1">
+    <row r="1638" ht="45" customHeight="1">
       <c r="A1638" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -32981,7 +33037,7 @@
       </c>
       <c r="B1638" s="19" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="C1638" s="20" t="n"/>
@@ -32997,7 +33053,7 @@
       </c>
       <c r="B1639" s="19" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="C1639" s="20" t="n"/>
@@ -33089,7 +33145,7 @@
       <c r="E1645" s="20" t="n"/>
       <c r="F1645" s="20" t="n"/>
     </row>
-    <row r="1646" ht="20" customHeight="1">
+    <row r="1646" ht="45" customHeight="1">
       <c r="A1646" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -33097,7 +33153,7 @@
       </c>
       <c r="B1646" s="19" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="C1646" s="20" t="n"/>
@@ -33141,7 +33197,7 @@
       </c>
       <c r="B1649" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/898575215</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95942</t>
         </is>
       </c>
       <c r="C1649" s="20" t="n"/>
@@ -33152,7 +33208,7 @@
     <row r="1651" ht="30" customHeight="1">
       <c r="A1651" s="16" t="inlineStr">
         <is>
-          <t>FICHA 111: 97556</t>
+          <t>FICHA 111: 898575215</t>
         </is>
       </c>
       <c r="B1651" s="17" t="n"/>
@@ -33177,7 +33233,7 @@
       <c r="E1652" s="20" t="n"/>
       <c r="F1652" s="20" t="n"/>
     </row>
-    <row r="1653" ht="45" customHeight="1">
+    <row r="1653" ht="20" customHeight="1">
       <c r="A1653" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33185,7 +33241,7 @@
       </c>
       <c r="B1653" s="19" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C1653" s="20" t="n"/>
@@ -33201,7 +33257,7 @@
       </c>
       <c r="B1654" s="19" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="C1654" s="20" t="n"/>
@@ -33293,7 +33349,7 @@
       <c r="E1660" s="20" t="n"/>
       <c r="F1660" s="20" t="n"/>
     </row>
-    <row r="1661" ht="45" customHeight="1">
+    <row r="1661" ht="20" customHeight="1">
       <c r="A1661" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -33301,7 +33357,7 @@
       </c>
       <c r="B1661" s="19" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C1661" s="20" t="n"/>
@@ -33345,7 +33401,7 @@
       </c>
       <c r="B1664" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/97556</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/898575215</t>
         </is>
       </c>
       <c r="C1664" s="20" t="n"/>
@@ -33356,7 +33412,7 @@
     <row r="1666" ht="30" customHeight="1">
       <c r="A1666" s="16" t="inlineStr">
         <is>
-          <t>FICHA 112: 73618</t>
+          <t>FICHA 112: 97556</t>
         </is>
       </c>
       <c r="B1666" s="17" t="n"/>
@@ -33389,7 +33445,7 @@
       </c>
       <c r="B1668" s="19" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="C1668" s="20" t="n"/>
@@ -33405,7 +33461,7 @@
       </c>
       <c r="B1669" s="19" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="C1669" s="20" t="n"/>
@@ -33505,7 +33561,7 @@
       </c>
       <c r="B1676" s="19" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="C1676" s="20" t="n"/>
@@ -33549,7 +33605,7 @@
       </c>
       <c r="B1679" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/73618</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/97556</t>
         </is>
       </c>
       <c r="C1679" s="20" t="n"/>
@@ -33560,7 +33616,7 @@
     <row r="1681" ht="30" customHeight="1">
       <c r="A1681" s="16" t="inlineStr">
         <is>
-          <t>FICHA 113: 83951</t>
+          <t>FICHA 113: 73618</t>
         </is>
       </c>
       <c r="B1681" s="17" t="n"/>
@@ -33585,7 +33641,7 @@
       <c r="E1682" s="20" t="n"/>
       <c r="F1682" s="20" t="n"/>
     </row>
-    <row r="1683" ht="20" customHeight="1">
+    <row r="1683" ht="45" customHeight="1">
       <c r="A1683" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33593,7 +33649,7 @@
       </c>
       <c r="B1683" s="19" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="C1683" s="20" t="n"/>
@@ -33609,7 +33665,7 @@
       </c>
       <c r="B1684" s="19" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="C1684" s="20" t="n"/>
@@ -33709,7 +33765,7 @@
       </c>
       <c r="B1691" s="19" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through the literature reviews, questionnaires, surveys and expert opinions in order to provide key recommendations on how EIT Food can make a distinctive a</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="C1691" s="20" t="n"/>
@@ -33753,7 +33809,7 @@
       </c>
       <c r="B1694" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/83951</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/73618</t>
         </is>
       </c>
       <c r="C1694" s="20" t="n"/>
@@ -33764,7 +33820,7 @@
     <row r="1696" ht="30" customHeight="1">
       <c r="A1696" s="16" t="inlineStr">
         <is>
-          <t>FICHA 114: 54353</t>
+          <t>FICHA 114: 83951</t>
         </is>
       </c>
       <c r="B1696" s="17" t="n"/>
@@ -33789,7 +33845,7 @@
       <c r="E1697" s="20" t="n"/>
       <c r="F1697" s="20" t="n"/>
     </row>
-    <row r="1698" ht="45" customHeight="1">
+    <row r="1698" ht="20" customHeight="1">
       <c r="A1698" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33797,7 +33853,7 @@
       </c>
       <c r="B1698" s="19" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="C1698" s="20" t="n"/>
@@ -33813,7 +33869,7 @@
       </c>
       <c r="B1699" s="19" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="C1699" s="20" t="n"/>
@@ -33913,7 +33969,7 @@
       </c>
       <c r="B1706" s="19" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through the literature reviews, questionnaires, surveys and expert opinions in order to provide key recommendations on how EIT Food can make a distinctive a</t>
         </is>
       </c>
       <c r="C1706" s="20" t="n"/>
@@ -33957,7 +34013,7 @@
       </c>
       <c r="B1709" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/54353</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/83951</t>
         </is>
       </c>
       <c r="C1709" s="20" t="n"/>
@@ -33968,7 +34024,7 @@
     <row r="1711" ht="30" customHeight="1">
       <c r="A1711" s="16" t="inlineStr">
         <is>
-          <t>FICHA 115: 880954583</t>
+          <t>FICHA 115: 54353</t>
         </is>
       </c>
       <c r="B1711" s="17" t="n"/>
@@ -33993,7 +34049,7 @@
       <c r="E1712" s="20" t="n"/>
       <c r="F1712" s="20" t="n"/>
     </row>
-    <row r="1713" ht="20" customHeight="1">
+    <row r="1713" ht="45" customHeight="1">
       <c r="A1713" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -34001,7 +34057,7 @@
       </c>
       <c r="B1713" s="19" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="C1713" s="20" t="n"/>
@@ -34017,7 +34073,7 @@
       </c>
       <c r="B1714" s="19" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="C1714" s="20" t="n"/>
@@ -34109,7 +34165,7 @@
       <c r="E1720" s="20" t="n"/>
       <c r="F1720" s="20" t="n"/>
     </row>
-    <row r="1721" ht="20" customHeight="1">
+    <row r="1721" ht="45" customHeight="1">
       <c r="A1721" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -34117,7 +34173,7 @@
       </c>
       <c r="B1721" s="19" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="C1721" s="20" t="n"/>
@@ -34161,7 +34217,7 @@
       </c>
       <c r="B1724" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880954583</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/54353</t>
         </is>
       </c>
       <c r="C1724" s="20" t="n"/>
@@ -34172,7 +34228,7 @@
     <row r="1726" ht="30" customHeight="1">
       <c r="A1726" s="16" t="inlineStr">
         <is>
-          <t>FICHA 116: c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>FICHA 116: 880954583</t>
         </is>
       </c>
       <c r="B1726" s="17" t="n"/>
@@ -34197,7 +34253,7 @@
       <c r="E1727" s="20" t="n"/>
       <c r="F1727" s="20" t="n"/>
     </row>
-    <row r="1728" ht="45" customHeight="1">
+    <row r="1728" ht="20" customHeight="1">
       <c r="A1728" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -34205,7 +34261,7 @@
       </c>
       <c r="B1728" s="19" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C1728" s="20" t="n"/>
@@ -34221,7 +34277,7 @@
       </c>
       <c r="B1729" s="19" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="C1729" s="20" t="n"/>
@@ -34307,17 +34363,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1735" s="19" t="inlineStr">
-        <is>
-          <t>CINEA/2026/OP/0011-PIN</t>
-        </is>
-      </c>
+      <c r="B1735" s="19" t="inlineStr"/>
       <c r="C1735" s="20" t="n"/>
       <c r="D1735" s="20" t="n"/>
       <c r="E1735" s="20" t="n"/>
       <c r="F1735" s="20" t="n"/>
     </row>
-    <row r="1736" ht="45" customHeight="1">
+    <row r="1736" ht="20" customHeight="1">
       <c r="A1736" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -34325,7 +34377,7 @@
       </c>
       <c r="B1736" s="19" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C1736" s="20" t="n"/>
@@ -34369,7 +34421,7 @@
       </c>
       <c r="B1739" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880954583</t>
         </is>
       </c>
       <c r="C1739" s="20" t="n"/>
@@ -34380,7 +34432,7 @@
     <row r="1741" ht="30" customHeight="1">
       <c r="A1741" s="16" t="inlineStr">
         <is>
-          <t>FICHA 117: 30901</t>
+          <t>FICHA 117: c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="B1741" s="17" t="n"/>
@@ -34413,7 +34465,7 @@
       </c>
       <c r="B1743" s="19" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="C1743" s="20" t="n"/>
@@ -34429,7 +34481,7 @@
       </c>
       <c r="B1744" s="19" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C1744" s="20" t="n"/>
@@ -34515,7 +34567,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1750" s="19" t="inlineStr"/>
+      <c r="B1750" s="19" t="inlineStr">
+        <is>
+          <t>CINEA/2026/OP/0011-PIN</t>
+        </is>
+      </c>
       <c r="C1750" s="20" t="n"/>
       <c r="D1750" s="20" t="n"/>
       <c r="E1750" s="20" t="n"/>
@@ -34529,7 +34585,7 @@
       </c>
       <c r="B1751" s="19" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="C1751" s="20" t="n"/>
@@ -34573,7 +34629,7 @@
       </c>
       <c r="B1754" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/30901</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C1754" s="20" t="n"/>
@@ -34584,7 +34640,7 @@
     <row r="1756" ht="30" customHeight="1">
       <c r="A1756" s="16" t="inlineStr">
         <is>
-          <t>FICHA 118: 893516374</t>
+          <t>FICHA 118: 30901</t>
         </is>
       </c>
       <c r="B1756" s="17" t="n"/>
@@ -34609,7 +34665,7 @@
       <c r="E1757" s="20" t="n"/>
       <c r="F1757" s="20" t="n"/>
     </row>
-    <row r="1758" ht="20" customHeight="1">
+    <row r="1758" ht="45" customHeight="1">
       <c r="A1758" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -34617,7 +34673,7 @@
       </c>
       <c r="B1758" s="19" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="C1758" s="20" t="n"/>
@@ -34633,7 +34689,7 @@
       </c>
       <c r="B1759" s="19" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="C1759" s="20" t="n"/>
@@ -34725,7 +34781,7 @@
       <c r="E1765" s="20" t="n"/>
       <c r="F1765" s="20" t="n"/>
     </row>
-    <row r="1766" ht="20" customHeight="1">
+    <row r="1766" ht="45" customHeight="1">
       <c r="A1766" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -34733,7 +34789,7 @@
       </c>
       <c r="B1766" s="19" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="C1766" s="20" t="n"/>
@@ -34777,7 +34833,7 @@
       </c>
       <c r="B1769" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/893516374</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/30901</t>
         </is>
       </c>
       <c r="C1769" s="20" t="n"/>
@@ -34788,7 +34844,7 @@
     <row r="1771" ht="30" customHeight="1">
       <c r="A1771" s="16" t="inlineStr">
         <is>
-          <t>FICHA 119: 894079362</t>
+          <t>FICHA 119: 893516374</t>
         </is>
       </c>
       <c r="B1771" s="17" t="n"/>
@@ -34821,7 +34877,7 @@
       </c>
       <c r="B1773" s="19" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C1773" s="20" t="n"/>
@@ -34837,7 +34893,7 @@
       </c>
       <c r="B1774" s="19" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="C1774" s="20" t="n"/>
@@ -34937,7 +34993,7 @@
       </c>
       <c r="B1781" s="19" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C1781" s="20" t="n"/>
@@ -34981,7 +35037,7 @@
       </c>
       <c r="B1784" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/894079362</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/893516374</t>
         </is>
       </c>
       <c r="C1784" s="20" t="n"/>
@@ -34992,7 +35048,7 @@
     <row r="1786" ht="30" customHeight="1">
       <c r="A1786" s="16" t="inlineStr">
         <is>
-          <t>FICHA 120: 867619605</t>
+          <t>FICHA 120: 894079362</t>
         </is>
       </c>
       <c r="B1786" s="17" t="n"/>
@@ -35025,7 +35081,7 @@
       </c>
       <c r="B1788" s="19" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C1788" s="20" t="n"/>
@@ -35041,7 +35097,7 @@
       </c>
       <c r="B1789" s="19" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="C1789" s="20" t="n"/>
@@ -35141,7 +35197,7 @@
       </c>
       <c r="B1796" s="19" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C1796" s="20" t="n"/>
@@ -35185,7 +35241,7 @@
       </c>
       <c r="B1799" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/867619605</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/894079362</t>
         </is>
       </c>
       <c r="C1799" s="20" t="n"/>
@@ -35196,7 +35252,7 @@
     <row r="1801" ht="30" customHeight="1">
       <c r="A1801" s="16" t="inlineStr">
         <is>
-          <t>FICHA 121: ncaviale</t>
+          <t>FICHA 121: 867619605</t>
         </is>
       </c>
       <c r="B1801" s="17" t="n"/>
@@ -35229,7 +35285,7 @@
       </c>
       <c r="B1803" s="19" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C1803" s="20" t="n"/>
@@ -35245,7 +35301,7 @@
       </c>
       <c r="B1804" s="19" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="C1804" s="20" t="n"/>
@@ -35345,7 +35401,7 @@
       </c>
       <c r="B1811" s="19" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C1811" s="20" t="n"/>
@@ -35389,7 +35445,7 @@
       </c>
       <c r="B1814" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ncaviale</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/867619605</t>
         </is>
       </c>
       <c r="C1814" s="20" t="n"/>
@@ -35400,7 +35456,7 @@
     <row r="1816" ht="30" customHeight="1">
       <c r="A1816" s="16" t="inlineStr">
         <is>
-          <t>FICHA 122: 34537</t>
+          <t>FICHA 122: ncaviale</t>
         </is>
       </c>
       <c r="B1816" s="17" t="n"/>
@@ -35425,7 +35481,7 @@
       <c r="E1817" s="20" t="n"/>
       <c r="F1817" s="20" t="n"/>
     </row>
-    <row r="1818" ht="45" customHeight="1">
+    <row r="1818" ht="20" customHeight="1">
       <c r="A1818" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -35433,7 +35489,7 @@
       </c>
       <c r="B1818" s="19" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C1818" s="20" t="n"/>
@@ -35449,7 +35505,7 @@
       </c>
       <c r="B1819" s="19" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="C1819" s="20" t="n"/>
@@ -35541,7 +35597,7 @@
       <c r="E1825" s="20" t="n"/>
       <c r="F1825" s="20" t="n"/>
     </row>
-    <row r="1826" ht="45" customHeight="1">
+    <row r="1826" ht="20" customHeight="1">
       <c r="A1826" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -35549,7 +35605,7 @@
       </c>
       <c r="B1826" s="19" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C1826" s="20" t="n"/>
@@ -35593,7 +35649,7 @@
       </c>
       <c r="B1829" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/34537</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ncaviale</t>
         </is>
       </c>
       <c r="C1829" s="20" t="n"/>
@@ -35604,7 +35660,7 @@
     <row r="1831" ht="30" customHeight="1">
       <c r="A1831" s="16" t="inlineStr">
         <is>
-          <t>FICHA 123: 906456368</t>
+          <t>FICHA 123: 34537</t>
         </is>
       </c>
       <c r="B1831" s="17" t="n"/>
@@ -35629,7 +35685,7 @@
       <c r="E1832" s="20" t="n"/>
       <c r="F1832" s="20" t="n"/>
     </row>
-    <row r="1833" ht="20" customHeight="1">
+    <row r="1833" ht="45" customHeight="1">
       <c r="A1833" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -35637,7 +35693,7 @@
       </c>
       <c r="B1833" s="19" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="C1833" s="20" t="n"/>
@@ -35653,7 +35709,7 @@
       </c>
       <c r="B1834" s="19" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="C1834" s="20" t="n"/>
@@ -35745,7 +35801,7 @@
       <c r="E1840" s="20" t="n"/>
       <c r="F1840" s="20" t="n"/>
     </row>
-    <row r="1841" ht="20" customHeight="1">
+    <row r="1841" ht="45" customHeight="1">
       <c r="A1841" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -35753,7 +35809,7 @@
       </c>
       <c r="B1841" s="19" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="C1841" s="20" t="n"/>
@@ -35797,7 +35853,7 @@
       </c>
       <c r="B1844" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/906456368</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/34537</t>
         </is>
       </c>
       <c r="C1844" s="20" t="n"/>
@@ -35808,7 +35864,7 @@
     <row r="1846" ht="30" customHeight="1">
       <c r="A1846" s="16" t="inlineStr">
         <is>
-          <t>FICHA 124: 939595836</t>
+          <t>FICHA 124: 906456368</t>
         </is>
       </c>
       <c r="B1846" s="17" t="n"/>
@@ -35841,7 +35897,7 @@
       </c>
       <c r="B1848" s="19" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C1848" s="20" t="n"/>
@@ -35857,7 +35913,7 @@
       </c>
       <c r="B1849" s="19" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="C1849" s="20" t="n"/>
@@ -35957,7 +36013,7 @@
       </c>
       <c r="B1856" s="19" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C1856" s="20" t="n"/>
@@ -36001,7 +36057,7 @@
       </c>
       <c r="B1859" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939595836</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/906456368</t>
         </is>
       </c>
       <c r="C1859" s="20" t="n"/>
@@ -36012,7 +36068,7 @@
     <row r="1861" ht="30" customHeight="1">
       <c r="A1861" s="16" t="inlineStr">
         <is>
-          <t>FICHA 125: 46407</t>
+          <t>FICHA 125: 939595836</t>
         </is>
       </c>
       <c r="B1861" s="17" t="n"/>
@@ -36037,7 +36093,7 @@
       <c r="E1862" s="20" t="n"/>
       <c r="F1862" s="20" t="n"/>
     </row>
-    <row r="1863" ht="45" customHeight="1">
+    <row r="1863" ht="20" customHeight="1">
       <c r="A1863" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -36045,7 +36101,7 @@
       </c>
       <c r="B1863" s="19" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C1863" s="20" t="n"/>
@@ -36061,7 +36117,7 @@
       </c>
       <c r="B1864" s="19" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="C1864" s="20" t="n"/>
@@ -36153,7 +36209,7 @@
       <c r="E1870" s="20" t="n"/>
       <c r="F1870" s="20" t="n"/>
     </row>
-    <row r="1871" ht="45" customHeight="1">
+    <row r="1871" ht="20" customHeight="1">
       <c r="A1871" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -36161,7 +36217,7 @@
       </c>
       <c r="B1871" s="19" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C1871" s="20" t="n"/>
@@ -36205,7 +36261,7 @@
       </c>
       <c r="B1874" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/46407</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939595836</t>
         </is>
       </c>
       <c r="C1874" s="20" t="n"/>
@@ -36216,7 +36272,7 @@
     <row r="1876" ht="30" customHeight="1">
       <c r="A1876" s="16" t="inlineStr">
         <is>
-          <t>FICHA 126: 71899</t>
+          <t>FICHA 126: 46407</t>
         </is>
       </c>
       <c r="B1876" s="17" t="n"/>
@@ -36249,7 +36305,7 @@
       </c>
       <c r="B1878" s="19" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="C1878" s="20" t="n"/>
@@ -36265,7 +36321,7 @@
       </c>
       <c r="B1879" s="19" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="C1879" s="20" t="n"/>
@@ -36365,7 +36421,7 @@
       </c>
       <c r="B1886" s="19" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="C1886" s="20" t="n"/>
@@ -36409,7 +36465,7 @@
       </c>
       <c r="B1889" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71899</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/46407</t>
         </is>
       </c>
       <c r="C1889" s="20" t="n"/>
@@ -36420,7 +36476,7 @@
     <row r="1891" ht="30" customHeight="1">
       <c r="A1891" s="16" t="inlineStr">
         <is>
-          <t>FICHA 127: 31176</t>
+          <t>FICHA 127: 71899</t>
         </is>
       </c>
       <c r="B1891" s="17" t="n"/>
@@ -36453,7 +36509,7 @@
       </c>
       <c r="B1893" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="C1893" s="20" t="n"/>
@@ -36469,7 +36525,7 @@
       </c>
       <c r="B1894" s="19" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="C1894" s="20" t="n"/>
@@ -36569,7 +36625,7 @@
       </c>
       <c r="B1901" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="C1901" s="20" t="n"/>
@@ -36613,7 +36669,7 @@
       </c>
       <c r="B1904" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31176</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71899</t>
         </is>
       </c>
       <c r="C1904" s="20" t="n"/>
@@ -36624,7 +36680,7 @@
     <row r="1906" ht="30" customHeight="1">
       <c r="A1906" s="16" t="inlineStr">
         <is>
-          <t>FICHA 128: PPPA2027</t>
+          <t>FICHA 128: 31176</t>
         </is>
       </c>
       <c r="B1906" s="17" t="n"/>
@@ -36657,7 +36713,7 @@
       </c>
       <c r="B1908" s="19" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
         </is>
       </c>
       <c r="C1908" s="20" t="n"/>
@@ -36673,7 +36729,7 @@
       </c>
       <c r="B1909" s="19" t="inlineStr">
         <is>
-          <t>PPPA2027</t>
+          <t>31176</t>
         </is>
       </c>
       <c r="C1909" s="20" t="n"/>
@@ -36759,11 +36815,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1915" s="19" t="inlineStr">
-        <is>
-          <t>PPPA-2025-IGF-IBA</t>
-        </is>
-      </c>
+      <c r="B1915" s="19" t="inlineStr"/>
       <c r="C1915" s="20" t="n"/>
       <c r="D1915" s="20" t="n"/>
       <c r="E1915" s="20" t="n"/>
@@ -36777,7 +36829,7 @@
       </c>
       <c r="B1916" s="19" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
         </is>
       </c>
       <c r="C1916" s="20" t="n"/>
@@ -36821,7 +36873,7 @@
       </c>
       <c r="B1919" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31176</t>
         </is>
       </c>
       <c r="C1919" s="20" t="n"/>
@@ -37248,7 +37300,7 @@
     <row r="1951" ht="30" customHeight="1">
       <c r="A1951" s="16" t="inlineStr">
         <is>
-          <t>FICHA 131: 8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>FICHA 131: PPPA2027</t>
         </is>
       </c>
       <c r="B1951" s="17" t="n"/>
@@ -37281,7 +37333,7 @@
       </c>
       <c r="B1953" s="19" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="C1953" s="20" t="n"/>
@@ -37297,7 +37349,7 @@
       </c>
       <c r="B1954" s="19" t="inlineStr">
         <is>
-          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>PPPA2027</t>
         </is>
       </c>
       <c r="C1954" s="20" t="n"/>
@@ -37385,7 +37437,7 @@
       </c>
       <c r="B1960" s="19" t="inlineStr">
         <is>
-          <t>EC-REGIO/2024/MVP/0031-EXA</t>
+          <t>PPPA-2025-IGF-IBA</t>
         </is>
       </c>
       <c r="C1960" s="20" t="n"/>
@@ -37401,7 +37453,7 @@
       </c>
       <c r="B1961" s="19" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="C1961" s="20" t="n"/>
@@ -37445,7 +37497,7 @@
       </c>
       <c r="B1964" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA2027</t>
         </is>
       </c>
       <c r="C1964" s="20" t="n"/>
@@ -37456,7 +37508,7 @@
     <row r="1966" ht="30" customHeight="1">
       <c r="A1966" s="16" t="inlineStr">
         <is>
-          <t>FICHA 132: 886623263</t>
+          <t>FICHA 132: 8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="B1966" s="17" t="n"/>
@@ -37481,7 +37533,7 @@
       <c r="E1967" s="20" t="n"/>
       <c r="F1967" s="20" t="n"/>
     </row>
-    <row r="1968" ht="20" customHeight="1">
+    <row r="1968" ht="45" customHeight="1">
       <c r="A1968" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -37489,7 +37541,7 @@
       </c>
       <c r="B1968" s="19" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="C1968" s="20" t="n"/>
@@ -37505,7 +37557,7 @@
       </c>
       <c r="B1969" s="19" t="inlineStr">
         <is>
-          <t>886623263</t>
+          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="C1969" s="20" t="n"/>
@@ -37591,13 +37643,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1975" s="19" t="inlineStr"/>
+      <c r="B1975" s="19" t="inlineStr">
+        <is>
+          <t>EC-REGIO/2024/MVP/0031-EXA</t>
+        </is>
+      </c>
       <c r="C1975" s="20" t="n"/>
       <c r="D1975" s="20" t="n"/>
       <c r="E1975" s="20" t="n"/>
       <c r="F1975" s="20" t="n"/>
     </row>
-    <row r="1976" ht="20" customHeight="1">
+    <row r="1976" ht="45" customHeight="1">
       <c r="A1976" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -37605,7 +37661,7 @@
       </c>
       <c r="B1976" s="19" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="C1976" s="20" t="n"/>
@@ -37649,7 +37705,7 @@
       </c>
       <c r="B1979" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/886623263</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="C1979" s="20" t="n"/>
@@ -37660,7 +37716,7 @@
     <row r="1981" ht="30" customHeight="1">
       <c r="A1981" s="16" t="inlineStr">
         <is>
-          <t>FICHA 133: 877314852</t>
+          <t>FICHA 133: 886623263</t>
         </is>
       </c>
       <c r="B1981" s="17" t="n"/>
@@ -37693,7 +37749,7 @@
       </c>
       <c r="B1983" s="19" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="C1983" s="20" t="n"/>
@@ -37709,7 +37765,7 @@
       </c>
       <c r="B1984" s="19" t="inlineStr">
         <is>
-          <t>877314852</t>
+          <t>886623263</t>
         </is>
       </c>
       <c r="C1984" s="20" t="n"/>
@@ -37809,7 +37865,7 @@
       </c>
       <c r="B1991" s="19" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="C1991" s="20" t="n"/>
@@ -37853,7 +37909,7 @@
       </c>
       <c r="B1994" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/877314852</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/886623263</t>
         </is>
       </c>
       <c r="C1994" s="20" t="n"/>
@@ -37864,7 +37920,7 @@
     <row r="1996" ht="30" customHeight="1">
       <c r="A1996" s="16" t="inlineStr">
         <is>
-          <t>FICHA 134: 884174595</t>
+          <t>FICHA 134: 877314852</t>
         </is>
       </c>
       <c r="B1996" s="17" t="n"/>
@@ -37897,7 +37953,7 @@
       </c>
       <c r="B1998" s="19" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="C1998" s="20" t="n"/>
@@ -37913,7 +37969,7 @@
       </c>
       <c r="B1999" s="19" t="inlineStr">
         <is>
-          <t>884174595</t>
+          <t>877314852</t>
         </is>
       </c>
       <c r="C1999" s="20" t="n"/>
@@ -38013,7 +38069,7 @@
       </c>
       <c r="B2006" s="19" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="C2006" s="20" t="n"/>
@@ -38057,7 +38113,7 @@
       </c>
       <c r="B2009" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/884174595</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/877314852</t>
         </is>
       </c>
       <c r="C2009" s="20" t="n"/>
@@ -38068,7 +38124,7 @@
     <row r="2011" ht="30" customHeight="1">
       <c r="A2011" s="16" t="inlineStr">
         <is>
-          <t>FICHA 135: 900546740</t>
+          <t>FICHA 135: 884174595</t>
         </is>
       </c>
       <c r="B2011" s="17" t="n"/>
@@ -38093,7 +38149,7 @@
       <c r="E2012" s="20" t="n"/>
       <c r="F2012" s="20" t="n"/>
     </row>
-    <row r="2013" ht="45" customHeight="1">
+    <row r="2013" ht="20" customHeight="1">
       <c r="A2013" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -38101,7 +38157,7 @@
       </c>
       <c r="B2013" s="19" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="C2013" s="20" t="n"/>
@@ -38117,7 +38173,7 @@
       </c>
       <c r="B2014" s="19" t="inlineStr">
         <is>
-          <t>900546740</t>
+          <t>884174595</t>
         </is>
       </c>
       <c r="C2014" s="20" t="n"/>
@@ -38209,7 +38265,7 @@
       <c r="E2020" s="20" t="n"/>
       <c r="F2020" s="20" t="n"/>
     </row>
-    <row r="2021" ht="45" customHeight="1">
+    <row r="2021" ht="20" customHeight="1">
       <c r="A2021" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -38217,7 +38273,7 @@
       </c>
       <c r="B2021" s="19" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="C2021" s="20" t="n"/>
@@ -38261,7 +38317,7 @@
       </c>
       <c r="B2024" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/900546740</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/884174595</t>
         </is>
       </c>
       <c r="C2024" s="20" t="n"/>
@@ -38272,7 +38328,7 @@
     <row r="2026" ht="30" customHeight="1">
       <c r="A2026" s="16" t="inlineStr">
         <is>
-          <t>FICHA 136: 941945952</t>
+          <t>FICHA 136: 900546740</t>
         </is>
       </c>
       <c r="B2026" s="17" t="n"/>
@@ -38297,7 +38353,7 @@
       <c r="E2027" s="20" t="n"/>
       <c r="F2027" s="20" t="n"/>
     </row>
-    <row r="2028" ht="20" customHeight="1">
+    <row r="2028" ht="45" customHeight="1">
       <c r="A2028" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -38305,7 +38361,7 @@
       </c>
       <c r="B2028" s="19" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="C2028" s="20" t="n"/>
@@ -38321,7 +38377,7 @@
       </c>
       <c r="B2029" s="19" t="inlineStr">
         <is>
-          <t>941945952</t>
+          <t>900546740</t>
         </is>
       </c>
       <c r="C2029" s="20" t="n"/>
@@ -38413,7 +38469,7 @@
       <c r="E2035" s="20" t="n"/>
       <c r="F2035" s="20" t="n"/>
     </row>
-    <row r="2036" ht="20" customHeight="1">
+    <row r="2036" ht="45" customHeight="1">
       <c r="A2036" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -38421,7 +38477,7 @@
       </c>
       <c r="B2036" s="19" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="C2036" s="20" t="n"/>
@@ -38465,7 +38521,7 @@
       </c>
       <c r="B2039" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/941945952</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/900546740</t>
         </is>
       </c>
       <c r="C2039" s="20" t="n"/>
@@ -38476,7 +38532,7 @@
     <row r="2041" ht="30" customHeight="1">
       <c r="A2041" s="16" t="inlineStr">
         <is>
-          <t>FICHA 137: 91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>FICHA 137: 941945952</t>
         </is>
       </c>
       <c r="B2041" s="17" t="n"/>
@@ -38509,7 +38565,7 @@
       </c>
       <c r="B2043" s="19" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="C2043" s="20" t="n"/>
@@ -38525,7 +38581,7 @@
       </c>
       <c r="B2044" s="19" t="inlineStr">
         <is>
-          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>941945952</t>
         </is>
       </c>
       <c r="C2044" s="20" t="n"/>
@@ -38611,11 +38667,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2050" s="19" t="inlineStr">
-        <is>
-          <t>EC-REGIO/2026/MVP/0069-EXA</t>
-        </is>
-      </c>
+      <c r="B2050" s="19" t="inlineStr"/>
       <c r="C2050" s="20" t="n"/>
       <c r="D2050" s="20" t="n"/>
       <c r="E2050" s="20" t="n"/>
@@ -38629,7 +38681,7 @@
       </c>
       <c r="B2051" s="19" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="C2051" s="20" t="n"/>
@@ -38673,7 +38725,7 @@
       </c>
       <c r="B2054" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/941945952</t>
         </is>
       </c>
       <c r="C2054" s="20" t="n"/>
@@ -38684,7 +38736,7 @@
     <row r="2056" ht="30" customHeight="1">
       <c r="A2056" s="16" t="inlineStr">
         <is>
-          <t>FICHA 138: ERDFTA</t>
+          <t>FICHA 138: 91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="B2056" s="17" t="n"/>
@@ -38717,7 +38769,7 @@
       </c>
       <c r="B2058" s="19" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="C2058" s="20" t="n"/>
@@ -38733,7 +38785,7 @@
       </c>
       <c r="B2059" s="19" t="inlineStr">
         <is>
-          <t>ERDFTA</t>
+          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="C2059" s="20" t="n"/>
@@ -38821,7 +38873,7 @@
       </c>
       <c r="B2065" s="19" t="inlineStr">
         <is>
-          <t>ERDFTA-2024-IVY-IBA</t>
+          <t>EC-REGIO/2026/MVP/0069-EXA</t>
         </is>
       </c>
       <c r="C2065" s="20" t="n"/>
@@ -38837,7 +38889,7 @@
       </c>
       <c r="B2066" s="19" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="C2066" s="20" t="n"/>
@@ -38881,7 +38933,7 @@
       </c>
       <c r="B2069" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="C2069" s="20" t="n"/>
@@ -38892,7 +38944,7 @@
     <row r="2071" ht="30" customHeight="1">
       <c r="A2071" s="16" t="inlineStr">
         <is>
-          <t>FICHA 139: 90488</t>
+          <t>FICHA 139: ERDFTA</t>
         </is>
       </c>
       <c r="B2071" s="17" t="n"/>
@@ -38917,7 +38969,7 @@
       <c r="E2072" s="20" t="n"/>
       <c r="F2072" s="20" t="n"/>
     </row>
-    <row r="2073" ht="45" customHeight="1">
+    <row r="2073" ht="20" customHeight="1">
       <c r="A2073" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -38925,7 +38977,7 @@
       </c>
       <c r="B2073" s="19" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="C2073" s="20" t="n"/>
@@ -38941,7 +38993,7 @@
       </c>
       <c r="B2074" s="19" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>ERDFTA</t>
         </is>
       </c>
       <c r="C2074" s="20" t="n"/>
@@ -39027,13 +39079,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2080" s="19" t="inlineStr"/>
+      <c r="B2080" s="19" t="inlineStr">
+        <is>
+          <t>ERDFTA-2024-IVY-IBA</t>
+        </is>
+      </c>
       <c r="C2080" s="20" t="n"/>
       <c r="D2080" s="20" t="n"/>
       <c r="E2080" s="20" t="n"/>
       <c r="F2080" s="20" t="n"/>
     </row>
-    <row r="2081" ht="45" customHeight="1">
+    <row r="2081" ht="20" customHeight="1">
       <c r="A2081" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -39041,7 +39097,7 @@
       </c>
       <c r="B2081" s="19" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="C2081" s="20" t="n"/>
@@ -39085,7 +39141,7 @@
       </c>
       <c r="B2084" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/90488</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA</t>
         </is>
       </c>
       <c r="C2084" s="20" t="n"/>
@@ -39096,7 +39152,7 @@
     <row r="2086" ht="30" customHeight="1">
       <c r="A2086" s="16" t="inlineStr">
         <is>
-          <t>FICHA 140: 877067502</t>
+          <t>FICHA 140: 90488</t>
         </is>
       </c>
       <c r="B2086" s="17" t="n"/>
@@ -39121,7 +39177,7 @@
       <c r="E2087" s="20" t="n"/>
       <c r="F2087" s="20" t="n"/>
     </row>
-    <row r="2088" ht="20" customHeight="1">
+    <row r="2088" ht="45" customHeight="1">
       <c r="A2088" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -39129,7 +39185,7 @@
       </c>
       <c r="B2088" s="19" t="inlineStr">
         <is>
-          <t>INSTITUTIA PUBLICA CENTRUL MUNICIPAL PENTRU DEZVOLTAREA ANTREPRENORIATULUI</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
         </is>
       </c>
       <c r="C2088" s="20" t="n"/>
@@ -39145,7 +39201,7 @@
       </c>
       <c r="B2089" s="19" t="inlineStr">
         <is>
-          <t>877067502</t>
+          <t>90488</t>
         </is>
       </c>
       <c r="C2089" s="20" t="n"/>
@@ -39237,7 +39293,7 @@
       <c r="E2095" s="20" t="n"/>
       <c r="F2095" s="20" t="n"/>
     </row>
-    <row r="2096" ht="20" customHeight="1">
+    <row r="2096" ht="45" customHeight="1">
       <c r="A2096" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -39245,7 +39301,7 @@
       </c>
       <c r="B2096" s="19" t="inlineStr">
         <is>
-          <t>INSTITUTIA PUBLICA CENTRUL MUNICIPAL PENTRU DEZVOLTAREA ANTREPRENORIATULUI</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
         </is>
       </c>
       <c r="C2096" s="20" t="n"/>
@@ -39289,7 +39345,7 @@
       </c>
       <c r="B2099" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/877067502</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/90488</t>
         </is>
       </c>
       <c r="C2099" s="20" t="n"/>
@@ -49508,7 +49564,7 @@
     <row r="2851" ht="30" customHeight="1">
       <c r="A2851" s="16" t="inlineStr">
         <is>
-          <t>FICHA 191: EUS-27253</t>
+          <t>FICHA 191: EUS-77406</t>
         </is>
       </c>
       <c r="B2851" s="17" t="n"/>
@@ -49557,7 +49613,7 @@
       </c>
       <c r="B2854" s="19" t="inlineStr">
         <is>
-          <t>EUS-27253</t>
+          <t>EUS-77406</t>
         </is>
       </c>
       <c r="C2854" s="20" t="n"/>
@@ -49720,7 +49776,7 @@
     <row r="2866" ht="30" customHeight="1">
       <c r="A2866" s="16" t="inlineStr">
         <is>
-          <t>FICHA 192: EUS-76571</t>
+          <t>FICHA 192: EUS-37002</t>
         </is>
       </c>
       <c r="B2866" s="17" t="n"/>
@@ -49769,7 +49825,7 @@
       </c>
       <c r="B2869" s="19" t="inlineStr">
         <is>
-          <t>EUS-76571</t>
+          <t>EUS-37002</t>
         </is>
       </c>
       <c r="C2869" s="20" t="n"/>
@@ -49932,7 +49988,7 @@
     <row r="2881" ht="30" customHeight="1">
       <c r="A2881" s="16" t="inlineStr">
         <is>
-          <t>FICHA 193: EUS-30498</t>
+          <t>FICHA 193: EUS-85357</t>
         </is>
       </c>
       <c r="B2881" s="17" t="n"/>
@@ -49965,7 +50021,7 @@
       </c>
       <c r="B2883" s="19" t="inlineStr">
         <is>
-          <t>Servicio del mantenimiento preventivo del sistema de climatización RITTAL BLUE E+</t>
+          <t>Suministro y montaje de mobiliario medioambientalmente sostenible para la nueva sede de EITB en Vitoria</t>
         </is>
       </c>
       <c r="C2883" s="20" t="n"/>
@@ -49981,7 +50037,7 @@
       </c>
       <c r="B2884" s="19" t="inlineStr">
         <is>
-          <t>EUS-30498</t>
+          <t>EUS-85357</t>
         </is>
       </c>
       <c r="C2884" s="20" t="n"/>
@@ -50133,7 +50189,7 @@
       </c>
       <c r="B2894" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-del-mantenimiento-preventivo-del-sistema-climatizacion-rittal-blue-e+/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-y-montaje-mobiliario-medioambientalmente-sostenible-nueva-sede-eitb-vitoria/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2894" s="20" t="n"/>
@@ -50144,7 +50200,7 @@
     <row r="2896" ht="30" customHeight="1">
       <c r="A2896" s="16" t="inlineStr">
         <is>
-          <t>FICHA 194: EUS-86571</t>
+          <t>FICHA 194: EUS-32616</t>
         </is>
       </c>
       <c r="B2896" s="17" t="n"/>
@@ -50177,7 +50233,7 @@
       </c>
       <c r="B2898" s="19" t="inlineStr">
         <is>
-          <t>Dirección de Obra y servicio de Coordinación de Seguridad y Salud de las obras comprendidas en el Proyecto de Ejecución de Climatización y obra civil auxiliar del bar cafetería restaurante del edifici</t>
+          <t>Servicio del mantenimiento preventivo del sistema de climatización RITTAL BLUE E+</t>
         </is>
       </c>
       <c r="C2898" s="20" t="n"/>
@@ -50193,7 +50249,7 @@
       </c>
       <c r="B2899" s="19" t="inlineStr">
         <is>
-          <t>EUS-86571</t>
+          <t>EUS-32616</t>
         </is>
       </c>
       <c r="C2899" s="20" t="n"/>
@@ -50345,7 +50401,7 @@
       </c>
       <c r="B2909" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/direccion-obra-y-servicio-coordinacion-seguridad-y-salud-obras-comprendidas-proyecto-ejecucion-climatizacion-y-obra-civil-auxiliar-del-bar-cafeteria-restaurante-del-edificio-piscinas-municipales-del-muelle-churruca-portugalete-bizkaia/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-del-mantenimiento-preventivo-del-sistema-climatizacion-rittal-blue-e+/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2909" s="20" t="n"/>
@@ -50356,7 +50412,7 @@
     <row r="2911" ht="30" customHeight="1">
       <c r="A2911" s="16" t="inlineStr">
         <is>
-          <t>FICHA 195: EUS-99941</t>
+          <t>FICHA 195: EUS-67929</t>
         </is>
       </c>
       <c r="B2911" s="17" t="n"/>
@@ -50389,7 +50445,7 @@
       </c>
       <c r="B2913" s="19" t="inlineStr">
         <is>
-          <t>Subvenciones para la organización, digitalización y difusión de archivos no públicos (2026)</t>
+          <t>Dirección de Obra y servicio de Coordinación de Seguridad y Salud de las obras comprendidas en el Proyecto de Ejecución de Climatización y obra civil auxiliar del bar cafetería restaurante del edifici</t>
         </is>
       </c>
       <c r="C2913" s="20" t="n"/>
@@ -50405,7 +50461,7 @@
       </c>
       <c r="B2914" s="19" t="inlineStr">
         <is>
-          <t>EUS-99941</t>
+          <t>EUS-67929</t>
         </is>
       </c>
       <c r="C2914" s="20" t="n"/>
@@ -50481,7 +50537,7 @@
       </c>
       <c r="B2919" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2919" s="20" t="n"/>
@@ -50539,9 +50595,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2923" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
+      <c r="B2923" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTA — </t>
         </is>
       </c>
       <c r="C2923" s="20" t="n"/>
@@ -50549,7 +50605,7 @@
       <c r="E2923" s="20" t="n"/>
       <c r="F2923" s="20" t="n"/>
     </row>
-    <row r="2924" ht="20" customHeight="1">
+    <row r="2924" ht="45" customHeight="1">
       <c r="A2924" s="18" t="inlineStr">
         <is>
           <t>Enlace al portal</t>
@@ -50557,7 +50613,7 @@
       </c>
       <c r="B2924" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/apri/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/direccion-obra-y-servicio-coordinacion-seguridad-y-salud-obras-comprendidas-proyecto-ejecucion-climatizacion-y-obra-civil-auxiliar-del-bar-cafeteria-restaurante-del-edificio-piscinas-municipales-del-muelle-churruca-portugalete-bizkaia/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2924" s="20" t="n"/>
@@ -50568,7 +50624,7 @@
     <row r="2926" ht="30" customHeight="1">
       <c r="A2926" s="16" t="inlineStr">
         <is>
-          <t>FICHA 196: EUS-26323</t>
+          <t>FICHA 196: EUS-13306</t>
         </is>
       </c>
       <c r="B2926" s="17" t="n"/>
@@ -50601,7 +50657,7 @@
       </c>
       <c r="B2928" s="19" t="inlineStr">
         <is>
-          <t>Subvenciones para la ejecución de trabajos orientados al ámbito de la salvaguarda del patrimonio cultural inmaterial 2026-2027</t>
+          <t>Subvenciones para la organización, digitalización y difusión de archivos no públicos (2026)</t>
         </is>
       </c>
       <c r="C2928" s="20" t="n"/>
@@ -50617,7 +50673,7 @@
       </c>
       <c r="B2929" s="19" t="inlineStr">
         <is>
-          <t>EUS-26323</t>
+          <t>EUS-13306</t>
         </is>
       </c>
       <c r="C2929" s="20" t="n"/>
@@ -50761,7 +50817,7 @@
       <c r="E2938" s="20" t="n"/>
       <c r="F2938" s="20" t="n"/>
     </row>
-    <row r="2939" ht="45" customHeight="1">
+    <row r="2939" ht="20" customHeight="1">
       <c r="A2939" s="18" t="inlineStr">
         <is>
           <t>Enlace al portal</t>
@@ -50769,7 +50825,7 @@
       </c>
       <c r="B2939" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/subvenciones-para-la-ejecucion-de-trabajos-orientados-al-ambito-de-la-salvaguarda-del-patrimonio-cultural-inmaterial-2026-2027/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/apri/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2939" s="20" t="n"/>
@@ -50780,7 +50836,7 @@
     <row r="2941" ht="30" customHeight="1">
       <c r="A2941" s="16" t="inlineStr">
         <is>
-          <t>FICHA 197: EUS-50523</t>
+          <t>FICHA 197: EUS-58268</t>
         </is>
       </c>
       <c r="B2941" s="17" t="n"/>
@@ -50813,7 +50869,7 @@
       </c>
       <c r="B2943" s="19" t="inlineStr">
         <is>
-          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado una Alianza para las Cadenas de Valor Industriales Marítimas, que contempla la soberanía tecnológica y de suministros, la defensa, la compe</t>
+          <t>Subvenciones para la ejecución de trabajos orientados al ámbito de la salvaguarda del patrimonio cultural inmaterial 2026-2027</t>
         </is>
       </c>
       <c r="C2943" s="20" t="n"/>
@@ -50829,7 +50885,7 @@
       </c>
       <c r="B2944" s="19" t="inlineStr">
         <is>
-          <t>EUS-50523</t>
+          <t>EUS-58268</t>
         </is>
       </c>
       <c r="C2944" s="20" t="n"/>
@@ -50981,7 +51037,7 @@
       </c>
       <c r="B2954" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/itsasindustriarakolankide/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/subvenciones-para-la-ejecucion-de-trabajos-orientados-al-ambito-de-la-salvaguarda-del-patrimonio-cultural-inmaterial-2026-2027/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2954" s="20" t="n"/>
@@ -50992,7 +51048,7 @@
     <row r="2956" ht="30" customHeight="1">
       <c r="A2956" s="16" t="inlineStr">
         <is>
-          <t>FICHA 198: EUS-38684</t>
+          <t>FICHA 198: EUS-21314</t>
         </is>
       </c>
       <c r="B2956" s="17" t="n"/>
@@ -51025,7 +51081,7 @@
       </c>
       <c r="B2958" s="19" t="inlineStr">
         <is>
-          <t>Contrato de Servicios de Limpieza del edificio Hedy Lamarr, en el Campus Donostia de Parque Tecnológico de Euskadi</t>
+          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado una Alianza para las Cadenas de Valor Industriales Marítimas, que contempla la soberanía tecnológica y de suministros, la defensa, la compe</t>
         </is>
       </c>
       <c r="C2958" s="20" t="n"/>
@@ -51041,7 +51097,7 @@
       </c>
       <c r="B2959" s="19" t="inlineStr">
         <is>
-          <t>EUS-38684</t>
+          <t>EUS-21314</t>
         </is>
       </c>
       <c r="C2959" s="20" t="n"/>
@@ -51117,7 +51173,7 @@
       </c>
       <c r="B2964" s="19" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="C2964" s="20" t="n"/>
@@ -51193,7 +51249,7 @@
       </c>
       <c r="B2969" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/contrato-servicios-limpieza-del-edificio-hedy-lamarr-campus-donostia-parque-tecnologico-euskadi/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/itsasindustriarakolankide/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2969" s="20" t="n"/>
@@ -51204,7 +51260,7 @@
     <row r="2971" ht="30" customHeight="1">
       <c r="A2971" s="16" t="inlineStr">
         <is>
-          <t>FICHA 199: EUS-54405</t>
+          <t>FICHA 199: EUS-60761</t>
         </is>
       </c>
       <c r="B2971" s="17" t="n"/>
@@ -51237,7 +51293,7 @@
       </c>
       <c r="B2973" s="19" t="inlineStr">
         <is>
-          <t>Acuerdo marco para la contratación del servicio de logística para el Palacio Foral y edificios de la Diputación Foral de Gipuzkoa.</t>
+          <t>Contrato de Servicios de Limpieza del edificio Hedy Lamarr, en el Campus Donostia de Parque Tecnológico de Euskadi</t>
         </is>
       </c>
       <c r="C2973" s="20" t="n"/>
@@ -51253,7 +51309,7 @@
       </c>
       <c r="B2974" s="19" t="inlineStr">
         <is>
-          <t>EUS-54405</t>
+          <t>EUS-60761</t>
         </is>
       </c>
       <c r="C2974" s="20" t="n"/>
@@ -51405,7 +51461,7 @@
       </c>
       <c r="B2984" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/acuerdo-marco-contratacion-del-servicio-logistica-palacio-foral-y-edificios-diputacion-foral-gipuzkoa/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/contrato-servicios-limpieza-del-edificio-hedy-lamarr-campus-donostia-parque-tecnologico-euskadi/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2984" s="20" t="n"/>
@@ -51416,7 +51472,7 @@
     <row r="2986" ht="30" customHeight="1">
       <c r="A2986" s="16" t="inlineStr">
         <is>
-          <t>FICHA 200: EUS-34834</t>
+          <t>FICHA 200: EUS-31896</t>
         </is>
       </c>
       <c r="B2986" s="17" t="n"/>
@@ -51449,7 +51505,7 @@
       </c>
       <c r="B2988" s="19" t="inlineStr">
         <is>
-          <t>Acuerdo marco para la contratación, a través de la Central de Contratación Foral de Gipuzkoa, del servicio de vigilancia y seguridad de edificios de la Diputación Foral de Gipuzkoa, Juntas Generales d</t>
+          <t>Acuerdo marco para la contratación del servicio de logística para el Palacio Foral y edificios de la Diputación Foral de Gipuzkoa.</t>
         </is>
       </c>
       <c r="C2988" s="20" t="n"/>
@@ -51465,7 +51521,7 @@
       </c>
       <c r="B2989" s="19" t="inlineStr">
         <is>
-          <t>EUS-34834</t>
+          <t>EUS-31896</t>
         </is>
       </c>
       <c r="C2989" s="20" t="n"/>
@@ -51617,7 +51673,7 @@
       </c>
       <c r="B2999" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/acuerdo-marco-contratacion-traves-central-contratacion-foral-gipuzkoa-del-servicio-vigilancia-y-seguridad-edificios-diputacion-foral-gipuzkoa-juntas-generales-gipuzkoa-e-izfe-s-a/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/acuerdo-marco-contratacion-del-servicio-logistica-palacio-foral-y-edificios-diputacion-foral-gipuzkoa/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2999" s="20" t="n"/>
@@ -51628,7 +51684,7 @@
     <row r="3001" ht="30" customHeight="1">
       <c r="A3001" s="16" t="inlineStr">
         <is>
-          <t>FICHA 201: EUS-29338</t>
+          <t>FICHA 201: EUS-64779</t>
         </is>
       </c>
       <c r="B3001" s="17" t="n"/>
@@ -51661,7 +51717,7 @@
       </c>
       <c r="B3003" s="19" t="inlineStr">
         <is>
-          <t>Servicio de instalación de infraestructuras audiovisuales y ambientación para la retransmisión de la final del Mundial de Fútbol.</t>
+          <t>Acuerdo marco para la contratación, a través de la Central de Contratación Foral de Gipuzkoa, del servicio de vigilancia y seguridad de edificios de la Diputación Foral de Gipuzkoa, Juntas Generales d</t>
         </is>
       </c>
       <c r="C3003" s="20" t="n"/>
@@ -51677,7 +51733,7 @@
       </c>
       <c r="B3004" s="19" t="inlineStr">
         <is>
-          <t>EUS-29338</t>
+          <t>EUS-64779</t>
         </is>
       </c>
       <c r="C3004" s="20" t="n"/>
@@ -51829,7 +51885,7 @@
       </c>
       <c r="B3014" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-instalacion-infraestructuras-audiovisuales-y-ambientacion-retransmision-final-del-mundial-futbol/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/acuerdo-marco-contratacion-traves-central-contratacion-foral-gipuzkoa-del-servicio-vigilancia-y-seguridad-edificios-diputacion-foral-gipuzkoa-juntas-generales-gipuzkoa-e-izfe-s-a/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3014" s="20" t="n"/>
@@ -51840,7 +51896,7 @@
     <row r="3016" ht="30" customHeight="1">
       <c r="A3016" s="16" t="inlineStr">
         <is>
-          <t>FICHA 202: EUS-60451</t>
+          <t>FICHA 202: EUS-27350</t>
         </is>
       </c>
       <c r="B3016" s="17" t="n"/>
@@ -51873,7 +51929,7 @@
       </c>
       <c r="B3018" s="19" t="inlineStr">
         <is>
-          <t>Servicio de reparación de deshumectadora de la zona de piscinas cubiertas del muelle Churruca</t>
+          <t>Servicio de instalación de infraestructuras audiovisuales y ambientación para la retransmisión de la final del Mundial de Fútbol.</t>
         </is>
       </c>
       <c r="C3018" s="20" t="n"/>
@@ -51889,7 +51945,7 @@
       </c>
       <c r="B3019" s="19" t="inlineStr">
         <is>
-          <t>EUS-60451</t>
+          <t>EUS-27350</t>
         </is>
       </c>
       <c r="C3019" s="20" t="n"/>
@@ -52041,7 +52097,7 @@
       </c>
       <c r="B3029" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-reparacion-deshumectadora-zona-piscinas-cubiertas-del-muelle-churruca/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-instalacion-infraestructuras-audiovisuales-y-ambientacion-retransmision-final-del-mundial-futbol/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3029" s="20" t="n"/>
@@ -52049,8 +52105,220 @@
       <c r="E3029" s="20" t="n"/>
       <c r="F3029" s="20" t="n"/>
     </row>
+    <row r="3031" ht="30" customHeight="1">
+      <c r="A3031" s="16" t="inlineStr">
+        <is>
+          <t>FICHA 203: EUS-38278</t>
+        </is>
+      </c>
+      <c r="B3031" s="17" t="n"/>
+      <c r="C3031" s="17" t="n"/>
+      <c r="D3031" s="17" t="n"/>
+      <c r="E3031" s="17" t="n"/>
+      <c r="F3031" s="17" t="n"/>
+    </row>
+    <row r="3032" ht="20" customHeight="1">
+      <c r="A3032" s="18" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B3032" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+      <c r="C3032" s="20" t="n"/>
+      <c r="D3032" s="20" t="n"/>
+      <c r="E3032" s="20" t="n"/>
+      <c r="F3032" s="20" t="n"/>
+    </row>
+    <row r="3033" ht="45" customHeight="1">
+      <c r="A3033" s="18" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B3033" s="19" t="inlineStr">
+        <is>
+          <t>Servicio de reparación de deshumectadora de la zona de piscinas cubiertas del muelle Churruca</t>
+        </is>
+      </c>
+      <c r="C3033" s="20" t="n"/>
+      <c r="D3033" s="20" t="n"/>
+      <c r="E3033" s="20" t="n"/>
+      <c r="F3033" s="20" t="n"/>
+    </row>
+    <row r="3034" ht="20" customHeight="1">
+      <c r="A3034" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3034" s="19" t="inlineStr">
+        <is>
+          <t>EUS-38278</t>
+        </is>
+      </c>
+      <c r="C3034" s="20" t="n"/>
+      <c r="D3034" s="20" t="n"/>
+      <c r="E3034" s="20" t="n"/>
+      <c r="F3034" s="20" t="n"/>
+    </row>
+    <row r="3035" ht="20" customHeight="1">
+      <c r="A3035" s="18" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B3035" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="C3035" s="20" t="n"/>
+      <c r="D3035" s="20" t="n"/>
+      <c r="E3035" s="20" t="n"/>
+      <c r="F3035" s="20" t="n"/>
+    </row>
+    <row r="3036" ht="20" customHeight="1">
+      <c r="A3036" s="18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B3036" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C3036" s="20" t="n"/>
+      <c r="D3036" s="20" t="n"/>
+      <c r="E3036" s="20" t="n"/>
+      <c r="F3036" s="20" t="n"/>
+    </row>
+    <row r="3037" ht="20" customHeight="1">
+      <c r="A3037" s="18" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B3037" s="19" t="inlineStr"/>
+      <c r="C3037" s="20" t="n"/>
+      <c r="D3037" s="20" t="n"/>
+      <c r="E3037" s="20" t="n"/>
+      <c r="F3037" s="20" t="n"/>
+    </row>
+    <row r="3038" ht="20" customHeight="1">
+      <c r="A3038" s="18" t="inlineStr">
+        <is>
+          <t>Presupuesto (EUR)</t>
+        </is>
+      </c>
+      <c r="B3038" s="19" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="C3038" s="20" t="n"/>
+      <c r="D3038" s="20" t="n"/>
+      <c r="E3038" s="20" t="n"/>
+      <c r="F3038" s="20" t="n"/>
+    </row>
+    <row r="3039" ht="20" customHeight="1">
+      <c r="A3039" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de Accion</t>
+        </is>
+      </c>
+      <c r="B3039" s="19" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="C3039" s="20" t="n"/>
+      <c r="D3039" s="20" t="n"/>
+      <c r="E3039" s="20" t="n"/>
+      <c r="F3039" s="20" t="n"/>
+    </row>
+    <row r="3040" ht="20" customHeight="1">
+      <c r="A3040" s="18" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B3040" s="19" t="inlineStr"/>
+      <c r="C3040" s="20" t="n"/>
+      <c r="D3040" s="20" t="n"/>
+      <c r="E3040" s="20" t="n"/>
+      <c r="F3040" s="20" t="n"/>
+    </row>
+    <row r="3041" ht="20" customHeight="1">
+      <c r="A3041" s="18" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="B3041" s="19" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="C3041" s="20" t="n"/>
+      <c r="D3041" s="20" t="n"/>
+      <c r="E3041" s="20" t="n"/>
+      <c r="F3041" s="20" t="n"/>
+    </row>
+    <row r="3042" ht="20" customHeight="1">
+      <c r="A3042" s="18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B3042" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="C3042" s="20" t="n"/>
+      <c r="D3042" s="20" t="n"/>
+      <c r="E3042" s="20" t="n"/>
+      <c r="F3042" s="20" t="n"/>
+    </row>
+    <row r="3043" ht="20" customHeight="1">
+      <c r="A3043" s="18" t="inlineStr">
+        <is>
+          <t>Relevancia Bilbao</t>
+        </is>
+      </c>
+      <c r="B3043" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
+        </is>
+      </c>
+      <c r="C3043" s="20" t="n"/>
+      <c r="D3043" s="20" t="n"/>
+      <c r="E3043" s="20" t="n"/>
+      <c r="F3043" s="20" t="n"/>
+    </row>
+    <row r="3044" ht="45" customHeight="1">
+      <c r="A3044" s="18" t="inlineStr">
+        <is>
+          <t>Enlace al portal</t>
+        </is>
+      </c>
+      <c r="B3044" s="22" t="inlineStr">
+        <is>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-reparacion-deshumectadora-zona-piscinas-cubiertas-del-muelle-churruca/web01-tramite/es/</t>
+        </is>
+      </c>
+      <c r="C3044" s="20" t="n"/>
+      <c r="D3044" s="20" t="n"/>
+      <c r="E3044" s="20" t="n"/>
+      <c r="F3044" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2828">
+  <mergeCells count="2842">
     <mergeCell ref="B679:F679"/>
     <mergeCell ref="B2192:F2192"/>
     <mergeCell ref="B1765:F1765"/>
@@ -52511,7 +52779,9 @@
     <mergeCell ref="B921:F921"/>
     <mergeCell ref="B606:F606"/>
     <mergeCell ref="B2741:F2741"/>
+    <mergeCell ref="B3039:F3039"/>
     <mergeCell ref="B2007:F2007"/>
+    <mergeCell ref="B3033:F3033"/>
     <mergeCell ref="B2436:F2436"/>
     <mergeCell ref="A1276:F1276"/>
     <mergeCell ref="B2770:F2770"/>
@@ -52710,6 +52980,7 @@
     <mergeCell ref="A2731:F2731"/>
     <mergeCell ref="B2246:F2246"/>
     <mergeCell ref="A946:F946"/>
+    <mergeCell ref="A3031:F3031"/>
     <mergeCell ref="A631:F631"/>
     <mergeCell ref="B117:F117"/>
     <mergeCell ref="B1783:F1783"/>
@@ -52787,6 +53058,7 @@
     <mergeCell ref="B2155:F2155"/>
     <mergeCell ref="B1123:F1123"/>
     <mergeCell ref="B368:F368"/>
+    <mergeCell ref="B3041:F3041"/>
     <mergeCell ref="B1254:F1254"/>
     <mergeCell ref="B1430:F1430"/>
     <mergeCell ref="B1552:F1552"/>
@@ -52969,6 +53241,7 @@
     <mergeCell ref="B1304:F1304"/>
     <mergeCell ref="B1608:F1608"/>
     <mergeCell ref="B2695:F2695"/>
+    <mergeCell ref="B3037:F3037"/>
     <mergeCell ref="B1967:F1967"/>
     <mergeCell ref="B908:F908"/>
     <mergeCell ref="B883:F883"/>
@@ -53417,6 +53690,7 @@
     <mergeCell ref="A2491:F2491"/>
     <mergeCell ref="A406:F406"/>
     <mergeCell ref="B951:F951"/>
+    <mergeCell ref="B3036:F3036"/>
     <mergeCell ref="B1249:F1249"/>
     <mergeCell ref="B524:F524"/>
     <mergeCell ref="B1854:F1854"/>
@@ -53424,6 +53698,7 @@
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B2012:F2012"/>
     <mergeCell ref="B953:F953"/>
+    <mergeCell ref="B3038:F3038"/>
     <mergeCell ref="B1251:F1251"/>
     <mergeCell ref="B1549:F1549"/>
     <mergeCell ref="B1856:F1856"/>
@@ -53509,6 +53784,7 @@
     <mergeCell ref="B891:F891"/>
     <mergeCell ref="B3009:F3009"/>
     <mergeCell ref="B1191:F1191"/>
+    <mergeCell ref="B3034:F3034"/>
     <mergeCell ref="B609:F609"/>
     <mergeCell ref="B1247:F1247"/>
     <mergeCell ref="B1977:F1977"/>
@@ -53526,6 +53802,7 @@
     <mergeCell ref="B1547:F1547"/>
     <mergeCell ref="B1207:F1207"/>
     <mergeCell ref="B490:F490"/>
+    <mergeCell ref="B3035:F3035"/>
     <mergeCell ref="B1338:F1338"/>
     <mergeCell ref="B3029:F3029"/>
     <mergeCell ref="B604:F604"/>
@@ -54128,6 +54405,7 @@
     <mergeCell ref="B1315:F1315"/>
     <mergeCell ref="B283:F283"/>
     <mergeCell ref="B2377:F2377"/>
+    <mergeCell ref="B3042:F3042"/>
     <mergeCell ref="B1649:F1649"/>
     <mergeCell ref="B590:F590"/>
     <mergeCell ref="B888:F888"/>
@@ -54151,6 +54429,7 @@
     <mergeCell ref="B512:F512"/>
     <mergeCell ref="B2734:F2734"/>
     <mergeCell ref="B2728:F2728"/>
+    <mergeCell ref="B3032:F3032"/>
     <mergeCell ref="B2000:F2000"/>
     <mergeCell ref="B303:F303"/>
     <mergeCell ref="B941:F941"/>
@@ -54590,6 +54869,7 @@
     <mergeCell ref="B318:F318"/>
     <mergeCell ref="A1741:F1741"/>
     <mergeCell ref="B1098:F1098"/>
+    <mergeCell ref="B3043:F3043"/>
     <mergeCell ref="B958:F958"/>
     <mergeCell ref="B1134:F1134"/>
     <mergeCell ref="B1256:F1256"/>
@@ -54609,6 +54889,7 @@
     <mergeCell ref="B1562:F1562"/>
     <mergeCell ref="B2317:F2317"/>
     <mergeCell ref="B1556:F1556"/>
+    <mergeCell ref="B3044:F3044"/>
     <mergeCell ref="A856:F856"/>
     <mergeCell ref="B1129:F1129"/>
     <mergeCell ref="B374:F374"/>
@@ -54708,6 +54989,7 @@
     <mergeCell ref="B197:F197"/>
     <mergeCell ref="B2104:F2104"/>
     <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B3040:F3040"/>
     <mergeCell ref="B1343:F1343"/>
     <mergeCell ref="B1641:F1641"/>
     <mergeCell ref="B2315:F2315"/>
@@ -55083,6 +55365,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2999" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3014" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3029" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3044" r:id="rId203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55094,7 +55377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J203"/>
+  <dimension ref="A1:J204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -57708,12 +57991,12 @@
     <row r="81" ht="28" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>31127</t>
+          <t>410806ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/</t>
+          <t>Hydrogen cities</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr"/>
@@ -57740,12 +58023,12 @@
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>96629</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>The intended technological “The intended technological scope</t>
+          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr"/>
@@ -57772,19 +58055,15 @@
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>INNOVFUND</t>
+          <t>96629</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Absorption Heat Pump for waste steam from a WtE plant to pre</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>Innovation Fund</t>
-        </is>
-      </c>
+          <t>The intended technological “The intended technological scope</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr"/>
       <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -57808,15 +58087,19 @@
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>INNOVFUND</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>The intended technological scope of Tasks 2 and 3 is unclear</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr"/>
+          <t>Absorption Heat Pump for waste steam from a WtE plant to pre</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Innovation Fund</t>
+        </is>
+      </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -57840,12 +58123,12 @@
     <row r="85" ht="28" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>96375</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover</t>
+          <t>The intended technological scope of Tasks 2 and 3 is unclear</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr"/>
@@ -57872,12 +58155,12 @@
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>52786</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Roadmap for updating Territorial just transition plans</t>
+          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr"/>
@@ -57904,12 +58187,12 @@
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>ESF</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Social City Fund to foster just transition in the City of </t>
+          <t>Roadmap for updating Territorial just transition plans</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr"/>
@@ -57936,12 +58219,12 @@
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>IMREG</t>
+          <t>ESF</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>HOTSTOP-Young people discover the Cohesion Policy and act ag</t>
+          <t xml:space="preserve">A Social City Fund to foster just transition in the City of </t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr"/>
@@ -57968,12 +58251,12 @@
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>897315282</t>
+          <t>IMREG</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Social Innovation Fund</t>
+          <t>HOTSTOP-Young people discover the Cohesion Policy and act ag</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr"/>
@@ -58000,19 +58283,15 @@
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>897315282</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Social Innovation Fund</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr"/>
       <c r="D90" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -58021,7 +58300,7 @@
       <c r="E90" s="6" t="inlineStr"/>
       <c r="F90" s="25" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr"/>
@@ -58036,15 +58315,19 @@
     <row r="91" ht="28" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neu</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -58068,12 +58351,12 @@
     <row r="92" ht="28" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficien</t>
+          <t>Circular design for bio-based innovation towards climate-neu</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr"/>
@@ -58100,12 +58383,12 @@
     <row r="93" ht="28" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should </t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficien</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr"/>
@@ -58132,19 +58415,15 @@
     <row r="94" ht="28" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should </t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr"/>
       <c r="D94" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -58168,15 +58447,19 @@
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from severa</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr"/>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -58200,12 +58483,12 @@
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from severa</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr"/>
@@ -58232,12 +58515,12 @@
     <row r="97" ht="28" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission tr</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr"/>
@@ -58264,12 +58547,12 @@
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission tr</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr"/>
@@ -58296,12 +58579,12 @@
     <row r="99" ht="28" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr"/>
@@ -58328,12 +58611,12 @@
     <row r="100" ht="28" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKT</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr"/>
@@ -58360,12 +58643,12 @@
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKT</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr"/>
@@ -58392,12 +58675,12 @@
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr"/>
@@ -58424,12 +58707,12 @@
     <row r="103" ht="28" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr"/>
@@ -58456,12 +58739,12 @@
     <row r="104" ht="28" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr"/>
@@ -58488,12 +58771,12 @@
     <row r="105" ht="28" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic L</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr"/>
@@ -58520,12 +58803,12 @@
     <row r="106" ht="28" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic L</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr"/>
@@ -58552,12 +58835,12 @@
     <row r="107" ht="28" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr"/>
@@ -58584,12 +58867,12 @@
     <row r="108" ht="28" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr"/>
@@ -58616,12 +58899,12 @@
     <row r="109" ht="28" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr"/>
@@ -58648,12 +58931,12 @@
     <row r="110" ht="28" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restorati</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr"/>
@@ -58680,12 +58963,12 @@
     <row r="111" ht="28" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Considering the increasing importance of ecosystem restorati</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr"/>
@@ -58712,12 +58995,12 @@
     <row r="112" ht="28" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaam</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr"/>
@@ -58744,12 +59027,12 @@
     <row r="113" ht="28" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be on</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaam</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr"/>
@@ -58776,12 +59059,12 @@
     <row r="114" ht="28" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Should the selected port related to the Cities Mission be on</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr"/>
@@ -58808,12 +59091,12 @@
     <row r="115" ht="28" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submi</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr"/>
@@ -58840,12 +59123,12 @@
     <row r="116" ht="28" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submi</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr"/>
@@ -58872,12 +59155,12 @@
     <row r="117" ht="28" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr"/>
@@ -58904,12 +59187,12 @@
     <row r="118" ht="28" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do loca</t>
+          <t>Inter-institutional single framework contract to support the</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr"/>
@@ -58936,12 +59219,12 @@
     <row r="119" ht="28" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do loca</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr"/>
@@ -58968,12 +59251,12 @@
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr"/>
@@ -59000,12 +59283,12 @@
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr"/>
@@ -59032,12 +59315,12 @@
     <row r="122" ht="28" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr"/>
@@ -59064,12 +59347,12 @@
     <row r="123" ht="28" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by F</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr"/>
@@ -59096,12 +59379,12 @@
     <row r="124" ht="28" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by F</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr"/>
@@ -59128,12 +59411,12 @@
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr"/>
@@ -59160,12 +59443,12 @@
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr"/>
@@ -59192,12 +59475,12 @@
     <row r="127" ht="28" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint action</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr"/>
@@ -59224,12 +59507,12 @@
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total bud</t>
+          <t>The topic requires to "include a draft plan for joint action</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr"/>
@@ -59256,12 +59539,12 @@
     <row r="129" ht="28" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>PPPA2027</t>
+          <t>31176</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interreg Governance Facility initiative to support Interreg </t>
+          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total bud</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr"/>
@@ -59352,12 +59635,12 @@
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>PPPA2027</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and</t>
+          <t xml:space="preserve">Interreg Governance Facility initiative to support Interreg </t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr"/>
@@ -59384,12 +59667,12 @@
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>886623263</t>
+          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr"/>
@@ -59416,12 +59699,12 @@
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>877314852</t>
+          <t>886623263</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr"/>
@@ -59448,12 +59731,12 @@
     <row r="135" ht="28" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>884174595</t>
+          <t>877314852</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr"/>
@@ -59480,12 +59763,12 @@
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>900546740</t>
+          <t>884174595</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integra</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr"/>
@@ -59512,12 +59795,12 @@
     <row r="137" ht="28" customHeight="1">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>941945952</t>
+          <t>900546740</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Department of International Cooperation and European Integra</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr"/>
@@ -59544,12 +59827,12 @@
     <row r="138" ht="28" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>941945952</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160A</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr"/>
@@ -59576,12 +59859,12 @@
     <row r="139" ht="28" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>ERDFTA</t>
+          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160A</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr"/>
@@ -59608,12 +59891,12 @@
     <row r="140" ht="28" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>ERDFTA</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr"/>
@@ -59640,12 +59923,12 @@
     <row r="141" ht="28" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>877067502</t>
+          <t>90488</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>INSTITUTIA PUBLICA CENTRUL MUNICIPAL PENTRU DEZVOLTAREA ANTR</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr"/>
@@ -61272,7 +61555,7 @@
     <row r="192" ht="28" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>EUS-27253</t>
+          <t>EUS-77406</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
@@ -61308,7 +61591,7 @@
     <row r="193" ht="28" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>EUS-76571</t>
+          <t>EUS-37002</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
@@ -61344,12 +61627,12 @@
     <row r="194" ht="28" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>EUS-30498</t>
+          <t>EUS-85357</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Servicio del mantenimiento preventivo del sistema de climati</t>
+          <t>Suministro y montaje de mobiliario medioambientalmente soste</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
@@ -61380,12 +61663,12 @@
     <row r="195" ht="28" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>EUS-86571</t>
+          <t>EUS-32616</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dirección de Obra y servicio de Coordinación de Seguridad y </t>
+          <t>Servicio del mantenimiento preventivo del sistema de climati</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -61416,12 +61699,12 @@
     <row r="196" ht="28" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>EUS-99941</t>
+          <t>EUS-67929</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Subvenciones para la organización, digitalización y difusión</t>
+          <t xml:space="preserve">Dirección de Obra y servicio de Coordinación de Seguridad y </t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -61437,7 +61720,7 @@
       <c r="E196" s="6" t="inlineStr"/>
       <c r="F196" s="25" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr"/>
@@ -61452,12 +61735,12 @@
     <row r="197" ht="28" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>EUS-26323</t>
+          <t>EUS-13306</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>Subvenciones para la ejecución de trabajos orientados al ámb</t>
+          <t>Subvenciones para la organización, digitalización y difusión</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -61488,12 +61771,12 @@
     <row r="198" ht="28" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>EUS-50523</t>
+          <t>EUS-58268</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado</t>
+          <t>Subvenciones para la ejecución de trabajos orientados al ámb</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
@@ -61524,12 +61807,12 @@
     <row r="199" ht="28" customHeight="1">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>EUS-38684</t>
+          <t>EUS-21314</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contrato de Servicios de Limpieza del edificio Hedy Lamarr, </t>
+          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
@@ -61560,12 +61843,12 @@
     <row r="200" ht="28" customHeight="1">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>EUS-54405</t>
+          <t>EUS-60761</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Acuerdo marco para la contratación del servicio de logística</t>
+          <t xml:space="preserve">Contrato de Servicios de Limpieza del edificio Hedy Lamarr, </t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
@@ -61596,12 +61879,12 @@
     <row r="201" ht="28" customHeight="1">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>EUS-34834</t>
+          <t>EUS-31896</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>Acuerdo marco para la contratación, a través de la Central d</t>
+          <t>Acuerdo marco para la contratación del servicio de logística</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -61632,12 +61915,12 @@
     <row r="202" ht="28" customHeight="1">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>EUS-29338</t>
+          <t>EUS-64779</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de instalación de infraestructuras audiovisuales y </t>
+          <t>Acuerdo marco para la contratación, a través de la Central d</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
@@ -61668,12 +61951,12 @@
     <row r="203" ht="28" customHeight="1">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>EUS-60451</t>
+          <t>EUS-27350</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>Servicio de reparación de deshumectadora de la zona de pisci</t>
+          <t xml:space="preserve">Servicio de instalación de infraestructuras audiovisuales y </t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
@@ -61701,8 +61984,44 @@
       <c r="I203" s="6" t="inlineStr"/>
       <c r="J203" s="6" t="inlineStr"/>
     </row>
+    <row r="204" ht="28" customHeight="1">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>EUS-38278</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>Servicio de reparación de deshumectadora de la zona de pisci</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="inlineStr"/>
+      <c r="F204" s="25" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr"/>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>Por revisar</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="inlineStr"/>
+      <c r="J204" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J203"/>
+  <autoFilter ref="A1:J204"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/resultados_convocatorias.xlsx
+++ b/docs/resultados_convocatorias.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Recursos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$204</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M204"/>
+  <dimension ref="A1:M203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -685,7 +685,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 21/09/2026 11:14 - 198 convocatorias - 9 nuevas</t>
+          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 22/09/2026 10:27 - 197 convocatorias - 9 nuevas</t>
         </is>
       </c>
     </row>
@@ -4453,12 +4453,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>31127</t>
+          <t>411234ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
+          <t>Hydrogen cities</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr"/>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>Aplicable a rehabilitación de edificios municipales.</t>
+          <t>Corredor Vasco del Hidrógeno. Petronor y Puerto de Bilbao involucrados.</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
+          <t>Hydrogen cities</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr"/>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>96629</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
+          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr"/>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background</t>
+          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4547,19 +4547,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>INNOVFUND</t>
+          <t>96629</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>Innovation Fund</t>
-        </is>
-      </c>
+          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr"/>
       <c r="E86" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4580,7 +4576,7 @@
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
+          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr"/>
@@ -4598,15 +4594,19 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>INNOVFUND</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr"/>
+          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Innovation Fund</t>
+        </is>
+      </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarb</t>
+          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4645,12 +4645,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>96375</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
+          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr"/>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>Margen izquierda con pasado industrial. Potencial reconversión.</t>
+          <t>Aplicable a rehabilitación de edificios municipales.</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
+          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarb</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr"/>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>52786</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Roadmap for updating Territorial just transition plans</t>
+          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr"/>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>Roadmap for updating Territorial just transition plans Promoting individual projects within planned concentrating activities has a small effect on economic reactivation and population fixing. Innovati</t>
+          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>ESF</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>A Social City Fund to foster just transition in the City of Leuven</t>
+          <t>Roadmap for updating Territorial just transition plans</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr"/>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>A Social City Fund to foster just transition in the City of Leuven</t>
+          <t>Roadmap for updating Territorial just transition plans Promoting individual projects within planned concentrating activities has a small effect on economic reactivation and population fixing. Innovati</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr"/>
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>IMREG</t>
+          <t>ESF</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
+          <t>A Social City Fund to foster just transition in the City of Leuven</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr"/>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>País Vasco es región en transición. Fondos FEDER disponibles.</t>
+          <t>Margen izquierda con pasado industrial. Potencial reconversión.</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
+          <t>A Social City Fund to foster just transition in the City of Leuven</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -4833,12 +4833,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>897315282</t>
+          <t>IMREG</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>Social Innovation Fund</t>
+          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr"/>
@@ -4857,12 +4857,12 @@
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>Aplicable a Petronor/Repsol (Muskiz) y Puerto de Bilbao.</t>
+          <t>País Vasco es región en transición. Fondos FEDER disponibles.</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>Social Innovation Fund</t>
+          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr"/>
@@ -4880,19 +4880,15 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>897315282</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Social Innovation Fund</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr"/>
       <c r="E93" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4901,19 +4897,19 @@
       <c r="F93" s="6" t="inlineStr"/>
       <c r="G93" s="6" t="inlineStr"/>
       <c r="H93" s="6" t="inlineStr"/>
-      <c r="I93" s="10" t="inlineStr">
-        <is>
-          <t>INFO</t>
+      <c r="I93" s="12" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>Revisar relevancia para el Ayuntamiento de Bilbao.</t>
+          <t>Aplicable a Petronor/Repsol (Muskiz) y Puerto de Bilbao.</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Social Innovation Fund</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -4931,15 +4927,19 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="L94" s="6" t="inlineStr"/>
@@ -4978,12 +4978,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr"/>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cove</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5025,12 +5025,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr"/>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cove</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr"/>
@@ -5072,19 +5072,15 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr"/>
       <c r="E97" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -5105,7 +5101,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5123,15 +5119,19 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr"/>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr"/>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr"/>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr"/>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr"/>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr"/>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5311,12 +5311,12 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr"/>
@@ -5358,12 +5358,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr"/>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5405,12 +5405,12 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr"/>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="L104" s="6" t="inlineStr"/>
@@ -5452,12 +5452,12 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr"/>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr"/>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L106" s="6" t="inlineStr"/>
@@ -5546,12 +5546,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5593,12 +5593,12 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="L108" s="6" t="inlineStr"/>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -5687,12 +5687,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="L110" s="6" t="inlineStr"/>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr"/>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr"/>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="L112" s="6" t="inlineStr"/>
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr"/>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -5875,12 +5875,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr"/>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the</t>
         </is>
       </c>
       <c r="L114" s="6" t="inlineStr"/>
@@ -5922,12 +5922,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr"/>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr"/>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the</t>
         </is>
       </c>
       <c r="L116" s="6" t="inlineStr"/>
@@ -6016,12 +6016,12 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr"/>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through th</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6063,12 +6063,12 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr"/>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on </t>
+          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through th</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr"/>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr"/>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t xml:space="preserve">Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on </t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6157,12 +6157,12 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr"/>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr"/>
@@ -6204,12 +6204,12 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr"/>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6251,12 +6251,12 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr"/>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="L122" s="6" t="inlineStr"/>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr"/>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="L124" s="6" t="inlineStr"/>
@@ -6392,12 +6392,12 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr"/>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Respon</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="L126" s="6" t="inlineStr"/>
@@ -6486,12 +6486,12 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr"/>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Respon</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr"/>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="L128" s="6" t="inlineStr"/>
@@ -6580,12 +6580,12 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr"/>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered </t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6627,12 +6627,12 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr"/>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage propo</t>
+          <t xml:space="preserve">The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered </t>
         </is>
       </c>
       <c r="L130" s="6" t="inlineStr"/>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr"/>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in th</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage propo</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7520,12 +7520,12 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>937468917</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>937468917</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="K150" s="6" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a sing</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="L150" s="6" t="inlineStr"/>
@@ -7614,12 +7614,12 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>n002cet5</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a sing</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -7661,12 +7661,12 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>n002cet5</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr"/>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="K152" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="L152" s="6" t="inlineStr"/>
@@ -7708,12 +7708,12 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>885233544</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr"/>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -7755,12 +7755,12 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>885233544</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr"/>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="K154" s="6" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="L154" s="6" t="inlineStr"/>
@@ -7802,12 +7802,12 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr"/>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr"/>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="K156" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we si</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="L156" s="6" t="inlineStr"/>
@@ -7896,12 +7896,12 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr"/>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technolog</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we si</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -7943,12 +7943,12 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr"/>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="K158" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technolog</t>
         </is>
       </c>
       <c r="L158" s="6" t="inlineStr"/>
@@ -7990,12 +7990,12 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr"/>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr"/>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="K160" s="6" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="L160" s="6" t="inlineStr"/>
@@ -8084,12 +8084,12 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>956926438</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr"/>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8131,12 +8131,12 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>953677035</t>
+          <t>956926438</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr"/>
@@ -8160,7 +8160,7 @@
       </c>
       <c r="K162" s="6" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="L162" s="6" t="inlineStr"/>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>953552487</t>
+          <t>953677035</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr"/>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8225,12 +8225,12 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>953552487</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="L164" s="6" t="inlineStr"/>
@@ -8272,12 +8272,12 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8319,12 +8319,12 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>876983694</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr"/>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="K166" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="L166" s="6" t="inlineStr"/>
@@ -8366,12 +8366,12 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>876983694</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr"/>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infra</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8413,12 +8413,12 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>935134321</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr"/>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="K168" s="6" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infra</t>
         </is>
       </c>
       <c r="L168" s="6" t="inlineStr"/>
@@ -8460,12 +8460,12 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>883154834</t>
+          <t>935134321</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8507,12 +8507,12 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>883154834</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr"/>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="K170" s="6" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="L170" s="6" t="inlineStr"/>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr"/>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>Climate resilience of European coastal cities and settlements</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K172" s="6" t="inlineStr">
         <is>
-          <t>Climate resilience of European coastal cities and settlements</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="L172" s="6" t="inlineStr"/>
@@ -9642,12 +9642,12 @@
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>EUS-16189</t>
+          <t>EUS-71228</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>Servicio de asistencia técnica para la redacción de un Plan de Clima y Energía en el Ayuntamiento de Basauri.</t>
+          <t>Servicio de conservación y mantenimiento de las zonas verdes municipales (arbustos y setos, jardineras, siega de caminos, arbolado y taludes) del municipio de Basauri.</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>EUS-65237</t>
+          <t>EUS-36680</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>EUS-01883</t>
+          <t>EUS-57715</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>Renovación del sistema de climatización del centro de formación en consumo de Donostia (Zarategi 82-84)</t>
+          <t>Servicio de implementación de un programa de incentivos a la movilidad sostenible mediante la plataforma de Ciclogreen</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
@@ -9788,7 +9788,11 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L197" s="6" t="inlineStr"/>
+      <c r="L197" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
       <c r="M197" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -9803,12 +9807,12 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>EUS-30957</t>
+          <t>EUS-03003</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>vinilado coches funicular tras rehabilitacion</t>
+          <t>Subvenciones para la organización, digitalización y difusión de archivos no públicos (2026)</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
@@ -9825,12 +9829,12 @@
       <c r="G198" s="6" t="inlineStr"/>
       <c r="H198" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="I198" s="8" t="inlineStr">
-        <is>
-          <t>ALTA</t>
+          <t>Ayuda/Subvencion Euskadi</t>
+        </is>
+      </c>
+      <c r="I198" s="12" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="J198" s="6" t="inlineStr"/>
@@ -9858,12 +9862,12 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>EUS-19215</t>
+          <t>EUS-89928</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>Subvenciones para la organización, digitalización y difusión de archivos no públicos (2026)</t>
+          <t>Subvenciones para la ejecución de trabajos orientados al ámbito de la salvaguarda del patrimonio cultural inmaterial 2026-2027</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
@@ -9913,12 +9917,12 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>EUS-95140</t>
+          <t>EUS-14280</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>Subvenciones para la ejecución de trabajos orientados al ámbito de la salvaguarda del patrimonio cultural inmaterial 2026-2027</t>
+          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado una Alianza para las Cadenas de Valor Industriales Marítimas, que contempla la soberanía tecnológica y de suministros, la defensa, la compe</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
@@ -9968,12 +9972,12 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>EUS-60062</t>
+          <t>EUS-05836</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado una Alianza para las Cadenas de Valor Industriales Marítimas, que contempla la soberanía tecnológica y de suministros, la defensa, la compe</t>
+          <t>Dirección facultativa de las obras de reverdecimiento del Cantón de Anorbin en el marco del Proyecto LIFE I P URBAN KLIMA 2050 (life18 IPC/ES/000001)</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
@@ -9990,7 +9994,7 @@
       <c r="G201" s="6" t="inlineStr"/>
       <c r="H201" s="6" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="I201" s="12" t="inlineStr">
@@ -10023,12 +10027,12 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>EUS-30850</t>
+          <t>EUS-20008</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>Contratación del suministro de un total de 590 contenedores de polietileno inyectado de alta densidad, de nueva fabricación, para renovación del parque de contenedores de carga trasera de la Cuadrilla</t>
+          <t>Suministro de equipamiento e instalación de Parque Infantil en Bedia</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
@@ -10078,12 +10082,12 @@
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>EUS-00649</t>
+          <t>EUS-26417</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>Contratación de la ejecución de cubierta del centro de visitantes ?El Torco? del Valle Salado, Salinas de Añana, Álava.</t>
+          <t>Recogida, grabación y tratamiento básico de la información de la operación continua ?Encuesta de población en relación con la actividad (PRA)? y sus módulos ?Encuesta sobre la sociedad de la informaci</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
@@ -10125,63 +10129,8 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="40" customHeight="1">
-      <c r="A204" s="14" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
-        <is>
-          <t>EUS-60669</t>
-        </is>
-      </c>
-      <c r="C204" s="6" t="inlineStr">
-        <is>
-          <t>pegatinas en impresion digital a color</t>
-        </is>
-      </c>
-      <c r="D204" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="E204" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F204" s="6" t="inlineStr"/>
-      <c r="G204" s="6" t="inlineStr"/>
-      <c r="H204" s="6" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="I204" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="J204" s="6" t="inlineStr"/>
-      <c r="K204" s="6" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="L204" s="15" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="M204" s="9" t="inlineStr">
-        <is>
-          <t>Ver</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:M204"/>
+  <autoFilter ref="A4:M203"/>
   <mergeCells count="4">
     <mergeCell ref="A194:M194"/>
     <mergeCell ref="A2:M2"/>
@@ -10386,7 +10335,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId198"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10398,7 +10346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2969"/>
+  <dimension ref="A1:F2954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26380,7 +26328,7 @@
     <row r="1171" ht="30" customHeight="1">
       <c r="A1171" s="16" t="inlineStr">
         <is>
-          <t>FICHA 79: 31127</t>
+          <t>FICHA 79: 411234ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B1171" s="17" t="n"/>
@@ -26405,7 +26353,7 @@
       <c r="E1172" s="20" t="n"/>
       <c r="F1172" s="20" t="n"/>
     </row>
-    <row r="1173" ht="45" customHeight="1">
+    <row r="1173" ht="20" customHeight="1">
       <c r="A1173" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -26413,7 +26361,7 @@
       </c>
       <c r="B1173" s="19" t="inlineStr">
         <is>
-          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
+          <t>Hydrogen cities</t>
         </is>
       </c>
       <c r="C1173" s="20" t="n"/>
@@ -26429,7 +26377,7 @@
       </c>
       <c r="B1174" s="19" t="inlineStr">
         <is>
-          <t>31127</t>
+          <t>411234ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C1174" s="20" t="n"/>
@@ -26521,7 +26469,7 @@
       <c r="E1180" s="20" t="n"/>
       <c r="F1180" s="20" t="n"/>
     </row>
-    <row r="1181" ht="45" customHeight="1">
+    <row r="1181" ht="20" customHeight="1">
       <c r="A1181" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -26529,7 +26477,7 @@
       </c>
       <c r="B1181" s="19" t="inlineStr">
         <is>
-          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
+          <t>Hydrogen cities</t>
         </is>
       </c>
       <c r="C1181" s="20" t="n"/>
@@ -26557,7 +26505,7 @@
       </c>
       <c r="B1183" s="19" t="inlineStr">
         <is>
-          <t>MEDIA — Aplicable a rehabilitación de edificios municipales.</t>
+          <t>MEDIA — Corredor Vasco del Hidrógeno. Petronor y Puerto de Bilbao involucrados.</t>
         </is>
       </c>
       <c r="C1183" s="20" t="n"/>
@@ -26573,7 +26521,7 @@
       </c>
       <c r="B1184" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31127</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/411234ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C1184" s="20" t="n"/>
@@ -26584,7 +26532,7 @@
     <row r="1186" ht="30" customHeight="1">
       <c r="A1186" s="16" t="inlineStr">
         <is>
-          <t>FICHA 80: 96629</t>
+          <t>FICHA 80: 31127</t>
         </is>
       </c>
       <c r="B1186" s="17" t="n"/>
@@ -26617,7 +26565,7 @@
       </c>
       <c r="B1188" s="19" t="inlineStr">
         <is>
-          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
+          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
         </is>
       </c>
       <c r="C1188" s="20" t="n"/>
@@ -26633,7 +26581,7 @@
       </c>
       <c r="B1189" s="19" t="inlineStr">
         <is>
-          <t>96629</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="C1189" s="20" t="n"/>
@@ -26733,7 +26681,7 @@
       </c>
       <c r="B1196" s="19" t="inlineStr">
         <is>
-          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
+          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/or delivery models involving individual heat pumps connected via a district heating network be considered within scope A of the topic?</t>
         </is>
       </c>
       <c r="C1196" s="20" t="n"/>
@@ -26777,7 +26725,7 @@
       </c>
       <c r="B1199" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/96629</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31127</t>
         </is>
       </c>
       <c r="C1199" s="20" t="n"/>
@@ -26788,7 +26736,7 @@
     <row r="1201" ht="30" customHeight="1">
       <c r="A1201" s="16" t="inlineStr">
         <is>
-          <t>FICHA 81: INNOVFUND</t>
+          <t>FICHA 81: 96629</t>
         </is>
       </c>
       <c r="B1201" s="17" t="n"/>
@@ -26821,7 +26769,7 @@
       </c>
       <c r="B1203" s="19" t="inlineStr">
         <is>
-          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
+          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
         </is>
       </c>
       <c r="C1203" s="20" t="n"/>
@@ -26837,7 +26785,7 @@
       </c>
       <c r="B1204" s="19" t="inlineStr">
         <is>
-          <t>INNOVFUND</t>
+          <t>96629</t>
         </is>
       </c>
       <c r="C1204" s="20" t="n"/>
@@ -26851,11 +26799,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1205" s="19" t="inlineStr">
-        <is>
-          <t>Innovation Fund</t>
-        </is>
-      </c>
+      <c r="B1205" s="19" t="inlineStr"/>
       <c r="C1205" s="20" t="n"/>
       <c r="D1205" s="20" t="n"/>
       <c r="E1205" s="20" t="n"/>
@@ -26927,11 +26871,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1210" s="19" t="inlineStr">
-        <is>
-          <t>InnovFund-2024-NZT</t>
-        </is>
-      </c>
+      <c r="B1210" s="19" t="inlineStr"/>
       <c r="C1210" s="20" t="n"/>
       <c r="D1210" s="20" t="n"/>
       <c r="E1210" s="20" t="n"/>
@@ -26945,7 +26885,7 @@
       </c>
       <c r="B1211" s="19" t="inlineStr">
         <is>
-          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
+          <t>The intended technological “The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other</t>
         </is>
       </c>
       <c r="C1211" s="20" t="n"/>
@@ -26989,7 +26929,7 @@
       </c>
       <c r="B1214" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/INNOVFUND</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/96629</t>
         </is>
       </c>
       <c r="C1214" s="20" t="n"/>
@@ -27000,7 +26940,7 @@
     <row r="1216" ht="30" customHeight="1">
       <c r="A1216" s="16" t="inlineStr">
         <is>
-          <t>FICHA 82: 96375</t>
+          <t>FICHA 82: INNOVFUND</t>
         </is>
       </c>
       <c r="B1216" s="17" t="n"/>
@@ -27033,7 +26973,7 @@
       </c>
       <c r="B1218" s="19" t="inlineStr">
         <is>
-          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
+          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
         </is>
       </c>
       <c r="C1218" s="20" t="n"/>
@@ -27049,7 +26989,7 @@
       </c>
       <c r="B1219" s="19" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>INNOVFUND</t>
         </is>
       </c>
       <c r="C1219" s="20" t="n"/>
@@ -27063,7 +27003,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1220" s="19" t="inlineStr"/>
+      <c r="B1220" s="19" t="inlineStr">
+        <is>
+          <t>Innovation Fund</t>
+        </is>
+      </c>
       <c r="C1220" s="20" t="n"/>
       <c r="D1220" s="20" t="n"/>
       <c r="E1220" s="20" t="n"/>
@@ -27135,7 +27079,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1225" s="19" t="inlineStr"/>
+      <c r="B1225" s="19" t="inlineStr">
+        <is>
+          <t>InnovFund-2024-NZT</t>
+        </is>
+      </c>
       <c r="C1225" s="20" t="n"/>
       <c r="D1225" s="20" t="n"/>
       <c r="E1225" s="20" t="n"/>
@@ -27149,7 +27097,7 @@
       </c>
       <c r="B1226" s="19" t="inlineStr">
         <is>
-          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
+          <t>Absorption Heat Pump for waste steam from a WtE plant to pre-heat district heating</t>
         </is>
       </c>
       <c r="C1226" s="20" t="n"/>
@@ -27193,7 +27141,7 @@
       </c>
       <c r="B1229" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/96375</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/INNOVFUND</t>
         </is>
       </c>
       <c r="C1229" s="20" t="n"/>
@@ -27204,7 +27152,7 @@
     <row r="1231" ht="30" customHeight="1">
       <c r="A1231" s="16" t="inlineStr">
         <is>
-          <t>FICHA 83: 52786</t>
+          <t>FICHA 83: 96375</t>
         </is>
       </c>
       <c r="B1231" s="17" t="n"/>
@@ -27237,7 +27185,7 @@
       </c>
       <c r="B1233" s="19" t="inlineStr">
         <is>
-          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
+          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
         </is>
       </c>
       <c r="C1233" s="20" t="n"/>
@@ -27253,7 +27201,7 @@
       </c>
       <c r="B1234" s="19" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>96375</t>
         </is>
       </c>
       <c r="C1234" s="20" t="n"/>
@@ -27353,7 +27301,7 @@
       </c>
       <c r="B1241" s="19" t="inlineStr">
         <is>
-          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
+          <t>The intended technological scope of Tasks 2 and 3 is unclear, particularly regarding the inclusion of heat pumps and electrification, which are identified in the Background section as promising decarbonisation technologies. Could you confirm our understanding that heat pumps are included where they use ambient or other renewable heat sources, wher</t>
         </is>
       </c>
       <c r="C1241" s="20" t="n"/>
@@ -27381,7 +27329,7 @@
       </c>
       <c r="B1243" s="19" t="inlineStr">
         <is>
-          <t>MEDIA — Margen izquierda con pasado industrial. Potencial reconversión.</t>
+          <t>MEDIA — Aplicable a rehabilitación de edificios municipales.</t>
         </is>
       </c>
       <c r="C1243" s="20" t="n"/>
@@ -27397,7 +27345,7 @@
       </c>
       <c r="B1244" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/52786</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/96375</t>
         </is>
       </c>
       <c r="C1244" s="20" t="n"/>
@@ -27408,7 +27356,7 @@
     <row r="1246" ht="30" customHeight="1">
       <c r="A1246" s="16" t="inlineStr">
         <is>
-          <t>FICHA 84: 62137</t>
+          <t>FICHA 84: 52786</t>
         </is>
       </c>
       <c r="B1246" s="17" t="n"/>
@@ -27433,7 +27381,7 @@
       <c r="E1247" s="20" t="n"/>
       <c r="F1247" s="20" t="n"/>
     </row>
-    <row r="1248" ht="20" customHeight="1">
+    <row r="1248" ht="45" customHeight="1">
       <c r="A1248" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -27441,7 +27389,7 @@
       </c>
       <c r="B1248" s="19" t="inlineStr">
         <is>
-          <t>Roadmap for updating Territorial just transition plans</t>
+          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
         </is>
       </c>
       <c r="C1248" s="20" t="n"/>
@@ -27457,7 +27405,7 @@
       </c>
       <c r="B1249" s="19" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>52786</t>
         </is>
       </c>
       <c r="C1249" s="20" t="n"/>
@@ -27557,7 +27505,7 @@
       </c>
       <c r="B1256" s="19" t="inlineStr">
         <is>
-          <t>Roadmap for updating Territorial just transition plans Promoting individual projects within planned concentrating activities has a small effect on economic reactivation and population fixing. Innovation poles have a higher contribution to economic reactivation and population fixing than individual projects, due to the synergies they can achieve</t>
+          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover the Just Transition Fund, Technical Support Instrument, and other funds referenced under the call objectives?</t>
         </is>
       </c>
       <c r="C1256" s="20" t="n"/>
@@ -27601,7 +27549,7 @@
       </c>
       <c r="B1259" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/62137</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/52786</t>
         </is>
       </c>
       <c r="C1259" s="20" t="n"/>
@@ -27612,7 +27560,7 @@
     <row r="1261" ht="30" customHeight="1">
       <c r="A1261" s="16" t="inlineStr">
         <is>
-          <t>FICHA 85: ESF</t>
+          <t>FICHA 85: 62137</t>
         </is>
       </c>
       <c r="B1261" s="17" t="n"/>
@@ -27645,7 +27593,7 @@
       </c>
       <c r="B1263" s="19" t="inlineStr">
         <is>
-          <t>A Social City Fund to foster just transition in the City of Leuven</t>
+          <t>Roadmap for updating Territorial just transition plans</t>
         </is>
       </c>
       <c r="C1263" s="20" t="n"/>
@@ -27661,7 +27609,7 @@
       </c>
       <c r="B1264" s="19" t="inlineStr">
         <is>
-          <t>ESF</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="C1264" s="20" t="n"/>
@@ -27747,17 +27695,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1270" s="19" t="inlineStr">
-        <is>
-          <t>ESF-2023-SUPPLY-DEMAND</t>
-        </is>
-      </c>
+      <c r="B1270" s="19" t="inlineStr"/>
       <c r="C1270" s="20" t="n"/>
       <c r="D1270" s="20" t="n"/>
       <c r="E1270" s="20" t="n"/>
       <c r="F1270" s="20" t="n"/>
     </row>
-    <row r="1271" ht="20" customHeight="1">
+    <row r="1271" ht="45" customHeight="1">
       <c r="A1271" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -27765,7 +27709,7 @@
       </c>
       <c r="B1271" s="19" t="inlineStr">
         <is>
-          <t>A Social City Fund to foster just transition in the City of Leuven</t>
+          <t>Roadmap for updating Territorial just transition plans Promoting individual projects within planned concentrating activities has a small effect on economic reactivation and population fixing. Innovation poles have a higher contribution to economic reactivation and population fixing than individual projects, due to the synergies they can achieve</t>
         </is>
       </c>
       <c r="C1271" s="20" t="n"/>
@@ -27809,7 +27753,7 @@
       </c>
       <c r="B1274" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ESF</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/62137</t>
         </is>
       </c>
       <c r="C1274" s="20" t="n"/>
@@ -27820,7 +27764,7 @@
     <row r="1276" ht="30" customHeight="1">
       <c r="A1276" s="16" t="inlineStr">
         <is>
-          <t>FICHA 86: IMREG</t>
+          <t>FICHA 86: ESF</t>
         </is>
       </c>
       <c r="B1276" s="17" t="n"/>
@@ -27845,7 +27789,7 @@
       <c r="E1277" s="20" t="n"/>
       <c r="F1277" s="20" t="n"/>
     </row>
-    <row r="1278" ht="45" customHeight="1">
+    <row r="1278" ht="20" customHeight="1">
       <c r="A1278" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -27853,7 +27797,7 @@
       </c>
       <c r="B1278" s="19" t="inlineStr">
         <is>
-          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
+          <t>A Social City Fund to foster just transition in the City of Leuven</t>
         </is>
       </c>
       <c r="C1278" s="20" t="n"/>
@@ -27869,7 +27813,7 @@
       </c>
       <c r="B1279" s="19" t="inlineStr">
         <is>
-          <t>IMREG</t>
+          <t>ESF</t>
         </is>
       </c>
       <c r="C1279" s="20" t="n"/>
@@ -27957,7 +27901,7 @@
       </c>
       <c r="B1285" s="19" t="inlineStr">
         <is>
-          <t>IMREG-2022-INFOME</t>
+          <t>ESF-2023-SUPPLY-DEMAND</t>
         </is>
       </c>
       <c r="C1285" s="20" t="n"/>
@@ -27965,7 +27909,7 @@
       <c r="E1285" s="20" t="n"/>
       <c r="F1285" s="20" t="n"/>
     </row>
-    <row r="1286" ht="45" customHeight="1">
+    <row r="1286" ht="20" customHeight="1">
       <c r="A1286" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -27973,7 +27917,7 @@
       </c>
       <c r="B1286" s="19" t="inlineStr">
         <is>
-          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
+          <t>A Social City Fund to foster just transition in the City of Leuven</t>
         </is>
       </c>
       <c r="C1286" s="20" t="n"/>
@@ -28001,7 +27945,7 @@
       </c>
       <c r="B1288" s="19" t="inlineStr">
         <is>
-          <t>MEDIA — País Vasco es región en transición. Fondos FEDER disponibles.</t>
+          <t>MEDIA — Margen izquierda con pasado industrial. Potencial reconversión.</t>
         </is>
       </c>
       <c r="C1288" s="20" t="n"/>
@@ -28017,7 +27961,7 @@
       </c>
       <c r="B1289" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/IMREG</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ESF</t>
         </is>
       </c>
       <c r="C1289" s="20" t="n"/>
@@ -28028,7 +27972,7 @@
     <row r="1291" ht="30" customHeight="1">
       <c r="A1291" s="16" t="inlineStr">
         <is>
-          <t>FICHA 87: 897315282</t>
+          <t>FICHA 87: IMREG</t>
         </is>
       </c>
       <c r="B1291" s="17" t="n"/>
@@ -28053,7 +27997,7 @@
       <c r="E1292" s="20" t="n"/>
       <c r="F1292" s="20" t="n"/>
     </row>
-    <row r="1293" ht="20" customHeight="1">
+    <row r="1293" ht="45" customHeight="1">
       <c r="A1293" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -28061,7 +28005,7 @@
       </c>
       <c r="B1293" s="19" t="inlineStr">
         <is>
-          <t>Social Innovation Fund</t>
+          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
         </is>
       </c>
       <c r="C1293" s="20" t="n"/>
@@ -28077,7 +28021,7 @@
       </c>
       <c r="B1294" s="19" t="inlineStr">
         <is>
-          <t>897315282</t>
+          <t>IMREG</t>
         </is>
       </c>
       <c r="C1294" s="20" t="n"/>
@@ -28163,13 +28107,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1300" s="19" t="inlineStr"/>
+      <c r="B1300" s="19" t="inlineStr">
+        <is>
+          <t>IMREG-2022-INFOME</t>
+        </is>
+      </c>
       <c r="C1300" s="20" t="n"/>
       <c r="D1300" s="20" t="n"/>
       <c r="E1300" s="20" t="n"/>
       <c r="F1300" s="20" t="n"/>
     </row>
-    <row r="1301" ht="20" customHeight="1">
+    <row r="1301" ht="45" customHeight="1">
       <c r="A1301" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -28177,7 +28125,7 @@
       </c>
       <c r="B1301" s="19" t="inlineStr">
         <is>
-          <t>Social Innovation Fund</t>
+          <t>HOTSTOP-Young people discover the Cohesion Policy and act against climate change</t>
         </is>
       </c>
       <c r="C1301" s="20" t="n"/>
@@ -28205,7 +28153,7 @@
       </c>
       <c r="B1303" s="19" t="inlineStr">
         <is>
-          <t>MEDIA — Aplicable a Petronor/Repsol (Muskiz) y Puerto de Bilbao.</t>
+          <t>MEDIA — País Vasco es región en transición. Fondos FEDER disponibles.</t>
         </is>
       </c>
       <c r="C1303" s="20" t="n"/>
@@ -28221,7 +28169,7 @@
       </c>
       <c r="B1304" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/897315282</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/IMREG</t>
         </is>
       </c>
       <c r="C1304" s="20" t="n"/>
@@ -28232,7 +28180,7 @@
     <row r="1306" ht="30" customHeight="1">
       <c r="A1306" s="16" t="inlineStr">
         <is>
-          <t>FICHA 88: HORIZON</t>
+          <t>FICHA 88: 897315282</t>
         </is>
       </c>
       <c r="B1306" s="17" t="n"/>
@@ -28265,7 +28213,7 @@
       </c>
       <c r="B1308" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Social Innovation Fund</t>
         </is>
       </c>
       <c r="C1308" s="20" t="n"/>
@@ -28281,7 +28229,7 @@
       </c>
       <c r="B1309" s="19" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>897315282</t>
         </is>
       </c>
       <c r="C1309" s="20" t="n"/>
@@ -28295,11 +28243,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1310" s="19" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+      <c r="B1310" s="19" t="inlineStr"/>
       <c r="C1310" s="20" t="n"/>
       <c r="D1310" s="20" t="n"/>
       <c r="E1310" s="20" t="n"/>
@@ -28371,11 +28315,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1315" s="19" t="inlineStr">
-        <is>
-          <t>HORIZON-MISS-2021-CIT-02</t>
-        </is>
-      </c>
+      <c r="B1315" s="19" t="inlineStr"/>
       <c r="C1315" s="20" t="n"/>
       <c r="D1315" s="20" t="n"/>
       <c r="E1315" s="20" t="n"/>
@@ -28389,7 +28329,7 @@
       </c>
       <c r="B1316" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Social Innovation Fund</t>
         </is>
       </c>
       <c r="C1316" s="20" t="n"/>
@@ -28417,7 +28357,7 @@
       </c>
       <c r="B1318" s="19" t="inlineStr">
         <is>
-          <t>INFO — Revisar relevancia para el Ayuntamiento de Bilbao.</t>
+          <t>MEDIA — Aplicable a Petronor/Repsol (Muskiz) y Puerto de Bilbao.</t>
         </is>
       </c>
       <c r="C1318" s="20" t="n"/>
@@ -28433,7 +28373,7 @@
       </c>
       <c r="B1319" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/897315282</t>
         </is>
       </c>
       <c r="C1319" s="20" t="n"/>
@@ -28444,7 +28384,7 @@
     <row r="1321" ht="30" customHeight="1">
       <c r="A1321" s="16" t="inlineStr">
         <is>
-          <t>FICHA 89: ERASMUS2027</t>
+          <t>FICHA 89: HORIZON</t>
         </is>
       </c>
       <c r="B1321" s="17" t="n"/>
@@ -28477,7 +28417,7 @@
       </c>
       <c r="B1323" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C1323" s="20" t="n"/>
@@ -28493,7 +28433,7 @@
       </c>
       <c r="B1324" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C1324" s="20" t="n"/>
@@ -28507,7 +28447,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1325" s="19" t="inlineStr"/>
+      <c r="B1325" s="19" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="C1325" s="20" t="n"/>
       <c r="D1325" s="20" t="n"/>
       <c r="E1325" s="20" t="n"/>
@@ -28581,7 +28525,7 @@
       </c>
       <c r="B1330" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
+          <t>HORIZON-MISS-2021-CIT-02</t>
         </is>
       </c>
       <c r="C1330" s="20" t="n"/>
@@ -28597,7 +28541,7 @@
       </c>
       <c r="B1331" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C1331" s="20" t="n"/>
@@ -28641,7 +28585,7 @@
       </c>
       <c r="B1334" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
         </is>
       </c>
       <c r="C1334" s="20" t="n"/>
@@ -28652,7 +28596,7 @@
     <row r="1336" ht="30" customHeight="1">
       <c r="A1336" s="16" t="inlineStr">
         <is>
-          <t>FICHA 90: 13349</t>
+          <t>FICHA 90: ERASMUS2027</t>
         </is>
       </c>
       <c r="B1336" s="17" t="n"/>
@@ -28677,7 +28621,7 @@
       <c r="E1337" s="20" t="n"/>
       <c r="F1337" s="20" t="n"/>
     </row>
-    <row r="1338" ht="45" customHeight="1">
+    <row r="1338" ht="20" customHeight="1">
       <c r="A1338" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -28685,7 +28629,7 @@
       </c>
       <c r="B1338" s="19" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C1338" s="20" t="n"/>
@@ -28701,7 +28645,7 @@
       </c>
       <c r="B1339" s="19" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C1339" s="20" t="n"/>
@@ -28787,13 +28731,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1345" s="19" t="inlineStr"/>
+      <c r="B1345" s="19" t="inlineStr">
+        <is>
+          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
+        </is>
+      </c>
       <c r="C1345" s="20" t="n"/>
       <c r="D1345" s="20" t="n"/>
       <c r="E1345" s="20" t="n"/>
       <c r="F1345" s="20" t="n"/>
     </row>
-    <row r="1346" ht="45" customHeight="1">
+    <row r="1346" ht="20" customHeight="1">
       <c r="A1346" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -28801,7 +28749,7 @@
       </c>
       <c r="B1346" s="19" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C1346" s="20" t="n"/>
@@ -28845,7 +28793,7 @@
       </c>
       <c r="B1349" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13349</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
         </is>
       </c>
       <c r="C1349" s="20" t="n"/>
@@ -28856,7 +28804,7 @@
     <row r="1351" ht="30" customHeight="1">
       <c r="A1351" s="16" t="inlineStr">
         <is>
-          <t>FICHA 91: 11301</t>
+          <t>FICHA 91: 13349</t>
         </is>
       </c>
       <c r="B1351" s="17" t="n"/>
@@ -28889,7 +28837,7 @@
       </c>
       <c r="B1353" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
         </is>
       </c>
       <c r="C1353" s="20" t="n"/>
@@ -28905,7 +28853,7 @@
       </c>
       <c r="B1354" s="19" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="C1354" s="20" t="n"/>
@@ -29005,7 +28953,7 @@
       </c>
       <c r="B1361" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
         </is>
       </c>
       <c r="C1361" s="20" t="n"/>
@@ -29049,7 +28997,7 @@
       </c>
       <c r="B1364" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/11301</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13349</t>
         </is>
       </c>
       <c r="C1364" s="20" t="n"/>
@@ -29060,7 +29008,7 @@
     <row r="1366" ht="30" customHeight="1">
       <c r="A1366" s="16" t="inlineStr">
         <is>
-          <t>FICHA 92: CEF2027</t>
+          <t>FICHA 92: 11301</t>
         </is>
       </c>
       <c r="B1366" s="17" t="n"/>
@@ -29085,7 +29033,7 @@
       <c r="E1367" s="20" t="n"/>
       <c r="F1367" s="20" t="n"/>
     </row>
-    <row r="1368" ht="20" customHeight="1">
+    <row r="1368" ht="45" customHeight="1">
       <c r="A1368" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -29093,7 +29041,7 @@
       </c>
       <c r="B1368" s="19" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
         </is>
       </c>
       <c r="C1368" s="20" t="n"/>
@@ -29109,7 +29057,7 @@
       </c>
       <c r="B1369" s="19" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="C1369" s="20" t="n"/>
@@ -29123,11 +29071,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1370" s="19" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+      <c r="B1370" s="19" t="inlineStr"/>
       <c r="C1370" s="20" t="n"/>
       <c r="D1370" s="20" t="n"/>
       <c r="E1370" s="20" t="n"/>
@@ -29199,17 +29143,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1375" s="19" t="inlineStr">
-        <is>
-          <t>CEF-T-2024-AFIFGEN</t>
-        </is>
-      </c>
+      <c r="B1375" s="19" t="inlineStr"/>
       <c r="C1375" s="20" t="n"/>
       <c r="D1375" s="20" t="n"/>
       <c r="E1375" s="20" t="n"/>
       <c r="F1375" s="20" t="n"/>
     </row>
-    <row r="1376" ht="20" customHeight="1">
+    <row r="1376" ht="45" customHeight="1">
       <c r="A1376" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -29217,7 +29157,7 @@
       </c>
       <c r="B1376" s="19" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
         </is>
       </c>
       <c r="C1376" s="20" t="n"/>
@@ -29261,7 +29201,7 @@
       </c>
       <c r="B1379" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/11301</t>
         </is>
       </c>
       <c r="C1379" s="20" t="n"/>
@@ -29272,7 +29212,7 @@
     <row r="1381" ht="30" customHeight="1">
       <c r="A1381" s="16" t="inlineStr">
         <is>
-          <t>FICHA 93: 19484</t>
+          <t>FICHA 93: CEF2027</t>
         </is>
       </c>
       <c r="B1381" s="17" t="n"/>
@@ -29297,7 +29237,7 @@
       <c r="E1382" s="20" t="n"/>
       <c r="F1382" s="20" t="n"/>
     </row>
-    <row r="1383" ht="45" customHeight="1">
+    <row r="1383" ht="20" customHeight="1">
       <c r="A1383" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -29305,7 +29245,7 @@
       </c>
       <c r="B1383" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="C1383" s="20" t="n"/>
@@ -29321,7 +29261,7 @@
       </c>
       <c r="B1384" s="19" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="C1384" s="20" t="n"/>
@@ -29335,7 +29275,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1385" s="19" t="inlineStr"/>
+      <c r="B1385" s="19" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="C1385" s="20" t="n"/>
       <c r="D1385" s="20" t="n"/>
       <c r="E1385" s="20" t="n"/>
@@ -29407,13 +29351,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1390" s="19" t="inlineStr"/>
+      <c r="B1390" s="19" t="inlineStr">
+        <is>
+          <t>CEF-T-2024-AFIFGEN</t>
+        </is>
+      </c>
       <c r="C1390" s="20" t="n"/>
       <c r="D1390" s="20" t="n"/>
       <c r="E1390" s="20" t="n"/>
       <c r="F1390" s="20" t="n"/>
     </row>
-    <row r="1391" ht="45" customHeight="1">
+    <row r="1391" ht="20" customHeight="1">
       <c r="A1391" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -29421,7 +29369,7 @@
       </c>
       <c r="B1391" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="C1391" s="20" t="n"/>
@@ -29465,7 +29413,7 @@
       </c>
       <c r="B1394" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19484</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF2027</t>
         </is>
       </c>
       <c r="C1394" s="20" t="n"/>
@@ -29476,7 +29424,7 @@
     <row r="1396" ht="30" customHeight="1">
       <c r="A1396" s="16" t="inlineStr">
         <is>
-          <t>FICHA 94: 915513452</t>
+          <t>FICHA 94: 19484</t>
         </is>
       </c>
       <c r="B1396" s="17" t="n"/>
@@ -29501,7 +29449,7 @@
       <c r="E1397" s="20" t="n"/>
       <c r="F1397" s="20" t="n"/>
     </row>
-    <row r="1398" ht="20" customHeight="1">
+    <row r="1398" ht="45" customHeight="1">
       <c r="A1398" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -29509,7 +29457,7 @@
       </c>
       <c r="B1398" s="19" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
         </is>
       </c>
       <c r="C1398" s="20" t="n"/>
@@ -29525,7 +29473,7 @@
       </c>
       <c r="B1399" s="19" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="C1399" s="20" t="n"/>
@@ -29617,7 +29565,7 @@
       <c r="E1405" s="20" t="n"/>
       <c r="F1405" s="20" t="n"/>
     </row>
-    <row r="1406" ht="20" customHeight="1">
+    <row r="1406" ht="45" customHeight="1">
       <c r="A1406" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -29625,7 +29573,7 @@
       </c>
       <c r="B1406" s="19" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
         </is>
       </c>
       <c r="C1406" s="20" t="n"/>
@@ -29669,7 +29617,7 @@
       </c>
       <c r="B1409" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/915513452</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19484</t>
         </is>
       </c>
       <c r="C1409" s="20" t="n"/>
@@ -29680,7 +29628,7 @@
     <row r="1411" ht="30" customHeight="1">
       <c r="A1411" s="16" t="inlineStr">
         <is>
-          <t>FICHA 95: 40556</t>
+          <t>FICHA 95: 915513452</t>
         </is>
       </c>
       <c r="B1411" s="17" t="n"/>
@@ -29705,7 +29653,7 @@
       <c r="E1412" s="20" t="n"/>
       <c r="F1412" s="20" t="n"/>
     </row>
-    <row r="1413" ht="45" customHeight="1">
+    <row r="1413" ht="20" customHeight="1">
       <c r="A1413" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -29713,7 +29661,7 @@
       </c>
       <c r="B1413" s="19" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C1413" s="20" t="n"/>
@@ -29729,7 +29677,7 @@
       </c>
       <c r="B1414" s="19" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="C1414" s="20" t="n"/>
@@ -29821,7 +29769,7 @@
       <c r="E1420" s="20" t="n"/>
       <c r="F1420" s="20" t="n"/>
     </row>
-    <row r="1421" ht="45" customHeight="1">
+    <row r="1421" ht="20" customHeight="1">
       <c r="A1421" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -29829,7 +29777,7 @@
       </c>
       <c r="B1421" s="19" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C1421" s="20" t="n"/>
@@ -29873,7 +29821,7 @@
       </c>
       <c r="B1424" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/40556</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/915513452</t>
         </is>
       </c>
       <c r="C1424" s="20" t="n"/>
@@ -29884,7 +29832,7 @@
     <row r="1426" ht="30" customHeight="1">
       <c r="A1426" s="16" t="inlineStr">
         <is>
-          <t>FICHA 96: 917671508</t>
+          <t>FICHA 96: 40556</t>
         </is>
       </c>
       <c r="B1426" s="17" t="n"/>
@@ -29909,7 +29857,7 @@
       <c r="E1427" s="20" t="n"/>
       <c r="F1427" s="20" t="n"/>
     </row>
-    <row r="1428" ht="20" customHeight="1">
+    <row r="1428" ht="45" customHeight="1">
       <c r="A1428" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -29917,7 +29865,7 @@
       </c>
       <c r="B1428" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="C1428" s="20" t="n"/>
@@ -29933,7 +29881,7 @@
       </c>
       <c r="B1429" s="19" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="C1429" s="20" t="n"/>
@@ -30025,7 +29973,7 @@
       <c r="E1435" s="20" t="n"/>
       <c r="F1435" s="20" t="n"/>
     </row>
-    <row r="1436" ht="20" customHeight="1">
+    <row r="1436" ht="45" customHeight="1">
       <c r="A1436" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -30033,7 +29981,7 @@
       </c>
       <c r="B1436" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="C1436" s="20" t="n"/>
@@ -30077,7 +30025,7 @@
       </c>
       <c r="B1439" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/40556</t>
         </is>
       </c>
       <c r="C1439" s="20" t="n"/>
@@ -30088,7 +30036,7 @@
     <row r="1441" ht="30" customHeight="1">
       <c r="A1441" s="16" t="inlineStr">
         <is>
-          <t>FICHA 97: 917721754</t>
+          <t>FICHA 97: 917671508</t>
         </is>
       </c>
       <c r="B1441" s="17" t="n"/>
@@ -30121,7 +30069,7 @@
       </c>
       <c r="B1443" s="19" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1443" s="20" t="n"/>
@@ -30137,7 +30085,7 @@
       </c>
       <c r="B1444" s="19" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C1444" s="20" t="n"/>
@@ -30237,7 +30185,7 @@
       </c>
       <c r="B1451" s="19" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1451" s="20" t="n"/>
@@ -30281,7 +30229,7 @@
       </c>
       <c r="B1454" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917721754</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
         </is>
       </c>
       <c r="C1454" s="20" t="n"/>
@@ -30292,7 +30240,7 @@
     <row r="1456" ht="30" customHeight="1">
       <c r="A1456" s="16" t="inlineStr">
         <is>
-          <t>FICHA 98: 919892711</t>
+          <t>FICHA 98: 917721754</t>
         </is>
       </c>
       <c r="B1456" s="17" t="n"/>
@@ -30325,7 +30273,7 @@
       </c>
       <c r="B1458" s="19" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1458" s="20" t="n"/>
@@ -30341,7 +30289,7 @@
       </c>
       <c r="B1459" s="19" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="C1459" s="20" t="n"/>
@@ -30441,7 +30389,7 @@
       </c>
       <c r="B1466" s="19" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1466" s="20" t="n"/>
@@ -30485,7 +30433,7 @@
       </c>
       <c r="B1469" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919892711</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917721754</t>
         </is>
       </c>
       <c r="C1469" s="20" t="n"/>
@@ -30496,7 +30444,7 @@
     <row r="1471" ht="30" customHeight="1">
       <c r="A1471" s="16" t="inlineStr">
         <is>
-          <t>FICHA 99: 939945909</t>
+          <t>FICHA 99: 919892711</t>
         </is>
       </c>
       <c r="B1471" s="17" t="n"/>
@@ -30529,7 +30477,7 @@
       </c>
       <c r="B1473" s="19" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="C1473" s="20" t="n"/>
@@ -30545,7 +30493,7 @@
       </c>
       <c r="B1474" s="19" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="C1474" s="20" t="n"/>
@@ -30645,7 +30593,7 @@
       </c>
       <c r="B1481" s="19" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="C1481" s="20" t="n"/>
@@ -30689,7 +30637,7 @@
       </c>
       <c r="B1484" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939945909</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919892711</t>
         </is>
       </c>
       <c r="C1484" s="20" t="n"/>
@@ -30700,7 +30648,7 @@
     <row r="1486" ht="30" customHeight="1">
       <c r="A1486" s="16" t="inlineStr">
         <is>
-          <t>FICHA 100: 917779760</t>
+          <t>FICHA 100: 939945909</t>
         </is>
       </c>
       <c r="B1486" s="17" t="n"/>
@@ -30733,7 +30681,7 @@
       </c>
       <c r="B1488" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C1488" s="20" t="n"/>
@@ -30749,7 +30697,7 @@
       </c>
       <c r="B1489" s="19" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="C1489" s="20" t="n"/>
@@ -30849,7 +30797,7 @@
       </c>
       <c r="B1496" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C1496" s="20" t="n"/>
@@ -30893,7 +30841,7 @@
       </c>
       <c r="B1499" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939945909</t>
         </is>
       </c>
       <c r="C1499" s="20" t="n"/>
@@ -30904,7 +30852,7 @@
     <row r="1501" ht="30" customHeight="1">
       <c r="A1501" s="16" t="inlineStr">
         <is>
-          <t>FICHA 101: 920115617</t>
+          <t>FICHA 101: 917779760</t>
         </is>
       </c>
       <c r="B1501" s="17" t="n"/>
@@ -30937,7 +30885,7 @@
       </c>
       <c r="B1503" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1503" s="20" t="n"/>
@@ -30953,7 +30901,7 @@
       </c>
       <c r="B1504" s="19" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C1504" s="20" t="n"/>
@@ -31053,7 +31001,7 @@
       </c>
       <c r="B1511" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1511" s="20" t="n"/>
@@ -31097,7 +31045,7 @@
       </c>
       <c r="B1514" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
         </is>
       </c>
       <c r="C1514" s="20" t="n"/>
@@ -31108,7 +31056,7 @@
     <row r="1516" ht="30" customHeight="1">
       <c r="A1516" s="16" t="inlineStr">
         <is>
-          <t>FICHA 102: 928447529</t>
+          <t>FICHA 102: 920115617</t>
         </is>
       </c>
       <c r="B1516" s="17" t="n"/>
@@ -31141,7 +31089,7 @@
       </c>
       <c r="B1518" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1518" s="20" t="n"/>
@@ -31157,7 +31105,7 @@
       </c>
       <c r="B1519" s="19" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C1519" s="20" t="n"/>
@@ -31257,7 +31205,7 @@
       </c>
       <c r="B1526" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1526" s="20" t="n"/>
@@ -31301,7 +31249,7 @@
       </c>
       <c r="B1529" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
         </is>
       </c>
       <c r="C1529" s="20" t="n"/>
@@ -31312,7 +31260,7 @@
     <row r="1531" ht="30" customHeight="1">
       <c r="A1531" s="16" t="inlineStr">
         <is>
-          <t>FICHA 103: 14272</t>
+          <t>FICHA 103: 928447529</t>
         </is>
       </c>
       <c r="B1531" s="17" t="n"/>
@@ -31337,7 +31285,7 @@
       <c r="E1532" s="20" t="n"/>
       <c r="F1532" s="20" t="n"/>
     </row>
-    <row r="1533" ht="45" customHeight="1">
+    <row r="1533" ht="20" customHeight="1">
       <c r="A1533" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -31345,7 +31293,7 @@
       </c>
       <c r="B1533" s="19" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1533" s="20" t="n"/>
@@ -31361,7 +31309,7 @@
       </c>
       <c r="B1534" s="19" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C1534" s="20" t="n"/>
@@ -31453,7 +31401,7 @@
       <c r="E1540" s="20" t="n"/>
       <c r="F1540" s="20" t="n"/>
     </row>
-    <row r="1541" ht="45" customHeight="1">
+    <row r="1541" ht="20" customHeight="1">
       <c r="A1541" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -31461,7 +31409,7 @@
       </c>
       <c r="B1541" s="19" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1541" s="20" t="n"/>
@@ -31505,7 +31453,7 @@
       </c>
       <c r="B1544" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14272</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
         </is>
       </c>
       <c r="C1544" s="20" t="n"/>
@@ -31516,7 +31464,7 @@
     <row r="1546" ht="30" customHeight="1">
       <c r="A1546" s="16" t="inlineStr">
         <is>
-          <t>FICHA 104: 996889759</t>
+          <t>FICHA 104: 14272</t>
         </is>
       </c>
       <c r="B1546" s="17" t="n"/>
@@ -31541,7 +31489,7 @@
       <c r="E1547" s="20" t="n"/>
       <c r="F1547" s="20" t="n"/>
     </row>
-    <row r="1548" ht="20" customHeight="1">
+    <row r="1548" ht="45" customHeight="1">
       <c r="A1548" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -31549,7 +31497,7 @@
       </c>
       <c r="B1548" s="19" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="C1548" s="20" t="n"/>
@@ -31565,7 +31513,7 @@
       </c>
       <c r="B1549" s="19" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="C1549" s="20" t="n"/>
@@ -31657,7 +31605,7 @@
       <c r="E1555" s="20" t="n"/>
       <c r="F1555" s="20" t="n"/>
     </row>
-    <row r="1556" ht="20" customHeight="1">
+    <row r="1556" ht="45" customHeight="1">
       <c r="A1556" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -31665,7 +31613,7 @@
       </c>
       <c r="B1556" s="19" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="C1556" s="20" t="n"/>
@@ -31709,7 +31657,7 @@
       </c>
       <c r="B1559" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/996889759</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14272</t>
         </is>
       </c>
       <c r="C1559" s="20" t="n"/>
@@ -31720,7 +31668,7 @@
     <row r="1561" ht="30" customHeight="1">
       <c r="A1561" s="16" t="inlineStr">
         <is>
-          <t>FICHA 105: 922165518</t>
+          <t>FICHA 105: 996889759</t>
         </is>
       </c>
       <c r="B1561" s="17" t="n"/>
@@ -31753,7 +31701,7 @@
       </c>
       <c r="B1563" s="19" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C1563" s="20" t="n"/>
@@ -31769,7 +31717,7 @@
       </c>
       <c r="B1564" s="19" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="C1564" s="20" t="n"/>
@@ -31869,7 +31817,7 @@
       </c>
       <c r="B1571" s="19" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C1571" s="20" t="n"/>
@@ -31913,7 +31861,7 @@
       </c>
       <c r="B1574" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/922165518</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/996889759</t>
         </is>
       </c>
       <c r="C1574" s="20" t="n"/>
@@ -31924,7 +31872,7 @@
     <row r="1576" ht="30" customHeight="1">
       <c r="A1576" s="16" t="inlineStr">
         <is>
-          <t>FICHA 106: 919917446</t>
+          <t>FICHA 106: 922165518</t>
         </is>
       </c>
       <c r="B1576" s="17" t="n"/>
@@ -31957,7 +31905,7 @@
       </c>
       <c r="B1578" s="19" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C1578" s="20" t="n"/>
@@ -31973,7 +31921,7 @@
       </c>
       <c r="B1579" s="19" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="C1579" s="20" t="n"/>
@@ -32073,7 +32021,7 @@
       </c>
       <c r="B1586" s="19" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C1586" s="20" t="n"/>
@@ -32117,7 +32065,7 @@
       </c>
       <c r="B1589" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919917446</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/922165518</t>
         </is>
       </c>
       <c r="C1589" s="20" t="n"/>
@@ -32128,7 +32076,7 @@
     <row r="1591" ht="30" customHeight="1">
       <c r="A1591" s="16" t="inlineStr">
         <is>
-          <t>FICHA 107: 917155468</t>
+          <t>FICHA 107: 919917446</t>
         </is>
       </c>
       <c r="B1591" s="17" t="n"/>
@@ -32161,7 +32109,7 @@
       </c>
       <c r="B1593" s="19" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C1593" s="20" t="n"/>
@@ -32177,7 +32125,7 @@
       </c>
       <c r="B1594" s="19" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="C1594" s="20" t="n"/>
@@ -32277,7 +32225,7 @@
       </c>
       <c r="B1601" s="19" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C1601" s="20" t="n"/>
@@ -32321,7 +32269,7 @@
       </c>
       <c r="B1604" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917155468</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919917446</t>
         </is>
       </c>
       <c r="C1604" s="20" t="n"/>
@@ -32332,7 +32280,7 @@
     <row r="1606" ht="30" customHeight="1">
       <c r="A1606" s="16" t="inlineStr">
         <is>
-          <t>FICHA 108: 95942</t>
+          <t>FICHA 108: 917155468</t>
         </is>
       </c>
       <c r="B1606" s="17" t="n"/>
@@ -32357,7 +32305,7 @@
       <c r="E1607" s="20" t="n"/>
       <c r="F1607" s="20" t="n"/>
     </row>
-    <row r="1608" ht="45" customHeight="1">
+    <row r="1608" ht="20" customHeight="1">
       <c r="A1608" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -32365,7 +32313,7 @@
       </c>
       <c r="B1608" s="19" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C1608" s="20" t="n"/>
@@ -32381,7 +32329,7 @@
       </c>
       <c r="B1609" s="19" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="C1609" s="20" t="n"/>
@@ -32473,7 +32421,7 @@
       <c r="E1615" s="20" t="n"/>
       <c r="F1615" s="20" t="n"/>
     </row>
-    <row r="1616" ht="45" customHeight="1">
+    <row r="1616" ht="20" customHeight="1">
       <c r="A1616" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -32481,7 +32429,7 @@
       </c>
       <c r="B1616" s="19" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C1616" s="20" t="n"/>
@@ -32525,7 +32473,7 @@
       </c>
       <c r="B1619" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95942</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917155468</t>
         </is>
       </c>
       <c r="C1619" s="20" t="n"/>
@@ -32536,7 +32484,7 @@
     <row r="1621" ht="30" customHeight="1">
       <c r="A1621" s="16" t="inlineStr">
         <is>
-          <t>FICHA 109: 898575215</t>
+          <t>FICHA 109: 95942</t>
         </is>
       </c>
       <c r="B1621" s="17" t="n"/>
@@ -32561,7 +32509,7 @@
       <c r="E1622" s="20" t="n"/>
       <c r="F1622" s="20" t="n"/>
     </row>
-    <row r="1623" ht="20" customHeight="1">
+    <row r="1623" ht="45" customHeight="1">
       <c r="A1623" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -32569,7 +32517,7 @@
       </c>
       <c r="B1623" s="19" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="C1623" s="20" t="n"/>
@@ -32585,7 +32533,7 @@
       </c>
       <c r="B1624" s="19" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="C1624" s="20" t="n"/>
@@ -32677,7 +32625,7 @@
       <c r="E1630" s="20" t="n"/>
       <c r="F1630" s="20" t="n"/>
     </row>
-    <row r="1631" ht="20" customHeight="1">
+    <row r="1631" ht="45" customHeight="1">
       <c r="A1631" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -32685,7 +32633,7 @@
       </c>
       <c r="B1631" s="19" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="C1631" s="20" t="n"/>
@@ -32729,7 +32677,7 @@
       </c>
       <c r="B1634" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/898575215</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95942</t>
         </is>
       </c>
       <c r="C1634" s="20" t="n"/>
@@ -32740,7 +32688,7 @@
     <row r="1636" ht="30" customHeight="1">
       <c r="A1636" s="16" t="inlineStr">
         <is>
-          <t>FICHA 110: 97556</t>
+          <t>FICHA 110: 898575215</t>
         </is>
       </c>
       <c r="B1636" s="17" t="n"/>
@@ -32765,7 +32713,7 @@
       <c r="E1637" s="20" t="n"/>
       <c r="F1637" s="20" t="n"/>
     </row>
-    <row r="1638" ht="45" customHeight="1">
+    <row r="1638" ht="20" customHeight="1">
       <c r="A1638" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -32773,7 +32721,7 @@
       </c>
       <c r="B1638" s="19" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C1638" s="20" t="n"/>
@@ -32789,7 +32737,7 @@
       </c>
       <c r="B1639" s="19" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="C1639" s="20" t="n"/>
@@ -32881,7 +32829,7 @@
       <c r="E1645" s="20" t="n"/>
       <c r="F1645" s="20" t="n"/>
     </row>
-    <row r="1646" ht="45" customHeight="1">
+    <row r="1646" ht="20" customHeight="1">
       <c r="A1646" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -32889,7 +32837,7 @@
       </c>
       <c r="B1646" s="19" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C1646" s="20" t="n"/>
@@ -32933,7 +32881,7 @@
       </c>
       <c r="B1649" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/97556</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/898575215</t>
         </is>
       </c>
       <c r="C1649" s="20" t="n"/>
@@ -32944,7 +32892,7 @@
     <row r="1651" ht="30" customHeight="1">
       <c r="A1651" s="16" t="inlineStr">
         <is>
-          <t>FICHA 111: 73618</t>
+          <t>FICHA 111: 97556</t>
         </is>
       </c>
       <c r="B1651" s="17" t="n"/>
@@ -32977,7 +32925,7 @@
       </c>
       <c r="B1653" s="19" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="C1653" s="20" t="n"/>
@@ -32993,7 +32941,7 @@
       </c>
       <c r="B1654" s="19" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="C1654" s="20" t="n"/>
@@ -33093,7 +33041,7 @@
       </c>
       <c r="B1661" s="19" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="C1661" s="20" t="n"/>
@@ -33137,7 +33085,7 @@
       </c>
       <c r="B1664" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/73618</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/97556</t>
         </is>
       </c>
       <c r="C1664" s="20" t="n"/>
@@ -33148,7 +33096,7 @@
     <row r="1666" ht="30" customHeight="1">
       <c r="A1666" s="16" t="inlineStr">
         <is>
-          <t>FICHA 112: 83951</t>
+          <t>FICHA 112: 73618</t>
         </is>
       </c>
       <c r="B1666" s="17" t="n"/>
@@ -33173,7 +33121,7 @@
       <c r="E1667" s="20" t="n"/>
       <c r="F1667" s="20" t="n"/>
     </row>
-    <row r="1668" ht="20" customHeight="1">
+    <row r="1668" ht="45" customHeight="1">
       <c r="A1668" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33181,7 +33129,7 @@
       </c>
       <c r="B1668" s="19" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="C1668" s="20" t="n"/>
@@ -33197,7 +33145,7 @@
       </c>
       <c r="B1669" s="19" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="C1669" s="20" t="n"/>
@@ -33297,7 +33245,7 @@
       </c>
       <c r="B1676" s="19" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through the literature reviews, questionnaires, surveys and expert opinions in order to provide key recommendations on how EIT Food can make a distinctive a</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="C1676" s="20" t="n"/>
@@ -33341,7 +33289,7 @@
       </c>
       <c r="B1679" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/83951</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/73618</t>
         </is>
       </c>
       <c r="C1679" s="20" t="n"/>
@@ -33352,7 +33300,7 @@
     <row r="1681" ht="30" customHeight="1">
       <c r="A1681" s="16" t="inlineStr">
         <is>
-          <t>FICHA 113: 54353</t>
+          <t>FICHA 113: 83951</t>
         </is>
       </c>
       <c r="B1681" s="17" t="n"/>
@@ -33377,7 +33325,7 @@
       <c r="E1682" s="20" t="n"/>
       <c r="F1682" s="20" t="n"/>
     </row>
-    <row r="1683" ht="45" customHeight="1">
+    <row r="1683" ht="20" customHeight="1">
       <c r="A1683" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33385,7 +33333,7 @@
       </c>
       <c r="B1683" s="19" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="C1683" s="20" t="n"/>
@@ -33401,7 +33349,7 @@
       </c>
       <c r="B1684" s="19" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="C1684" s="20" t="n"/>
@@ -33501,7 +33449,7 @@
       </c>
       <c r="B1691" s="19" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through the literature reviews, questionnaires, surveys and expert opinions in order to provide key recommendations on how EIT Food can make a distinctive a</t>
         </is>
       </c>
       <c r="C1691" s="20" t="n"/>
@@ -33545,7 +33493,7 @@
       </c>
       <c r="B1694" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/54353</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/83951</t>
         </is>
       </c>
       <c r="C1694" s="20" t="n"/>
@@ -33556,7 +33504,7 @@
     <row r="1696" ht="30" customHeight="1">
       <c r="A1696" s="16" t="inlineStr">
         <is>
-          <t>FICHA 114: 880954583</t>
+          <t>FICHA 114: 54353</t>
         </is>
       </c>
       <c r="B1696" s="17" t="n"/>
@@ -33581,7 +33529,7 @@
       <c r="E1697" s="20" t="n"/>
       <c r="F1697" s="20" t="n"/>
     </row>
-    <row r="1698" ht="20" customHeight="1">
+    <row r="1698" ht="45" customHeight="1">
       <c r="A1698" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33589,7 +33537,7 @@
       </c>
       <c r="B1698" s="19" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="C1698" s="20" t="n"/>
@@ -33605,7 +33553,7 @@
       </c>
       <c r="B1699" s="19" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="C1699" s="20" t="n"/>
@@ -33697,7 +33645,7 @@
       <c r="E1705" s="20" t="n"/>
       <c r="F1705" s="20" t="n"/>
     </row>
-    <row r="1706" ht="20" customHeight="1">
+    <row r="1706" ht="45" customHeight="1">
       <c r="A1706" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -33705,7 +33653,7 @@
       </c>
       <c r="B1706" s="19" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="C1706" s="20" t="n"/>
@@ -33749,7 +33697,7 @@
       </c>
       <c r="B1709" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880954583</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/54353</t>
         </is>
       </c>
       <c r="C1709" s="20" t="n"/>
@@ -33760,7 +33708,7 @@
     <row r="1711" ht="30" customHeight="1">
       <c r="A1711" s="16" t="inlineStr">
         <is>
-          <t>FICHA 115: c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>FICHA 115: 880954583</t>
         </is>
       </c>
       <c r="B1711" s="17" t="n"/>
@@ -33785,7 +33733,7 @@
       <c r="E1712" s="20" t="n"/>
       <c r="F1712" s="20" t="n"/>
     </row>
-    <row r="1713" ht="45" customHeight="1">
+    <row r="1713" ht="20" customHeight="1">
       <c r="A1713" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33793,7 +33741,7 @@
       </c>
       <c r="B1713" s="19" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C1713" s="20" t="n"/>
@@ -33809,7 +33757,7 @@
       </c>
       <c r="B1714" s="19" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="C1714" s="20" t="n"/>
@@ -33895,17 +33843,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1720" s="19" t="inlineStr">
-        <is>
-          <t>CINEA/2026/OP/0011-PIN</t>
-        </is>
-      </c>
+      <c r="B1720" s="19" t="inlineStr"/>
       <c r="C1720" s="20" t="n"/>
       <c r="D1720" s="20" t="n"/>
       <c r="E1720" s="20" t="n"/>
       <c r="F1720" s="20" t="n"/>
     </row>
-    <row r="1721" ht="45" customHeight="1">
+    <row r="1721" ht="20" customHeight="1">
       <c r="A1721" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -33913,7 +33857,7 @@
       </c>
       <c r="B1721" s="19" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C1721" s="20" t="n"/>
@@ -33957,7 +33901,7 @@
       </c>
       <c r="B1724" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880954583</t>
         </is>
       </c>
       <c r="C1724" s="20" t="n"/>
@@ -33968,7 +33912,7 @@
     <row r="1726" ht="30" customHeight="1">
       <c r="A1726" s="16" t="inlineStr">
         <is>
-          <t>FICHA 116: 30901</t>
+          <t>FICHA 116: c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="B1726" s="17" t="n"/>
@@ -34001,7 +33945,7 @@
       </c>
       <c r="B1728" s="19" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="C1728" s="20" t="n"/>
@@ -34017,7 +33961,7 @@
       </c>
       <c r="B1729" s="19" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C1729" s="20" t="n"/>
@@ -34103,7 +34047,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1735" s="19" t="inlineStr"/>
+      <c r="B1735" s="19" t="inlineStr">
+        <is>
+          <t>CINEA/2026/OP/0011-PIN</t>
+        </is>
+      </c>
       <c r="C1735" s="20" t="n"/>
       <c r="D1735" s="20" t="n"/>
       <c r="E1735" s="20" t="n"/>
@@ -34117,7 +34065,7 @@
       </c>
       <c r="B1736" s="19" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="C1736" s="20" t="n"/>
@@ -34161,7 +34109,7 @@
       </c>
       <c r="B1739" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/30901</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C1739" s="20" t="n"/>
@@ -34172,7 +34120,7 @@
     <row r="1741" ht="30" customHeight="1">
       <c r="A1741" s="16" t="inlineStr">
         <is>
-          <t>FICHA 117: 893516374</t>
+          <t>FICHA 117: 30901</t>
         </is>
       </c>
       <c r="B1741" s="17" t="n"/>
@@ -34197,7 +34145,7 @@
       <c r="E1742" s="20" t="n"/>
       <c r="F1742" s="20" t="n"/>
     </row>
-    <row r="1743" ht="20" customHeight="1">
+    <row r="1743" ht="45" customHeight="1">
       <c r="A1743" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -34205,7 +34153,7 @@
       </c>
       <c r="B1743" s="19" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="C1743" s="20" t="n"/>
@@ -34221,7 +34169,7 @@
       </c>
       <c r="B1744" s="19" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="C1744" s="20" t="n"/>
@@ -34313,7 +34261,7 @@
       <c r="E1750" s="20" t="n"/>
       <c r="F1750" s="20" t="n"/>
     </row>
-    <row r="1751" ht="20" customHeight="1">
+    <row r="1751" ht="45" customHeight="1">
       <c r="A1751" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -34321,7 +34269,7 @@
       </c>
       <c r="B1751" s="19" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="C1751" s="20" t="n"/>
@@ -34365,7 +34313,7 @@
       </c>
       <c r="B1754" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/893516374</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/30901</t>
         </is>
       </c>
       <c r="C1754" s="20" t="n"/>
@@ -34376,7 +34324,7 @@
     <row r="1756" ht="30" customHeight="1">
       <c r="A1756" s="16" t="inlineStr">
         <is>
-          <t>FICHA 118: 894079362</t>
+          <t>FICHA 118: 893516374</t>
         </is>
       </c>
       <c r="B1756" s="17" t="n"/>
@@ -34409,7 +34357,7 @@
       </c>
       <c r="B1758" s="19" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C1758" s="20" t="n"/>
@@ -34425,7 +34373,7 @@
       </c>
       <c r="B1759" s="19" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="C1759" s="20" t="n"/>
@@ -34525,7 +34473,7 @@
       </c>
       <c r="B1766" s="19" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C1766" s="20" t="n"/>
@@ -34569,7 +34517,7 @@
       </c>
       <c r="B1769" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/894079362</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/893516374</t>
         </is>
       </c>
       <c r="C1769" s="20" t="n"/>
@@ -34580,7 +34528,7 @@
     <row r="1771" ht="30" customHeight="1">
       <c r="A1771" s="16" t="inlineStr">
         <is>
-          <t>FICHA 119: 867619605</t>
+          <t>FICHA 119: 894079362</t>
         </is>
       </c>
       <c r="B1771" s="17" t="n"/>
@@ -34613,7 +34561,7 @@
       </c>
       <c r="B1773" s="19" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C1773" s="20" t="n"/>
@@ -34629,7 +34577,7 @@
       </c>
       <c r="B1774" s="19" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="C1774" s="20" t="n"/>
@@ -34729,7 +34677,7 @@
       </c>
       <c r="B1781" s="19" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C1781" s="20" t="n"/>
@@ -34773,7 +34721,7 @@
       </c>
       <c r="B1784" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/867619605</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/894079362</t>
         </is>
       </c>
       <c r="C1784" s="20" t="n"/>
@@ -34784,7 +34732,7 @@
     <row r="1786" ht="30" customHeight="1">
       <c r="A1786" s="16" t="inlineStr">
         <is>
-          <t>FICHA 120: ncaviale</t>
+          <t>FICHA 120: 867619605</t>
         </is>
       </c>
       <c r="B1786" s="17" t="n"/>
@@ -34817,7 +34765,7 @@
       </c>
       <c r="B1788" s="19" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C1788" s="20" t="n"/>
@@ -34833,7 +34781,7 @@
       </c>
       <c r="B1789" s="19" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="C1789" s="20" t="n"/>
@@ -34933,7 +34881,7 @@
       </c>
       <c r="B1796" s="19" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C1796" s="20" t="n"/>
@@ -34977,7 +34925,7 @@
       </c>
       <c r="B1799" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ncaviale</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/867619605</t>
         </is>
       </c>
       <c r="C1799" s="20" t="n"/>
@@ -34988,7 +34936,7 @@
     <row r="1801" ht="30" customHeight="1">
       <c r="A1801" s="16" t="inlineStr">
         <is>
-          <t>FICHA 121: 34537</t>
+          <t>FICHA 121: ncaviale</t>
         </is>
       </c>
       <c r="B1801" s="17" t="n"/>
@@ -35013,7 +34961,7 @@
       <c r="E1802" s="20" t="n"/>
       <c r="F1802" s="20" t="n"/>
     </row>
-    <row r="1803" ht="45" customHeight="1">
+    <row r="1803" ht="20" customHeight="1">
       <c r="A1803" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -35021,7 +34969,7 @@
       </c>
       <c r="B1803" s="19" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C1803" s="20" t="n"/>
@@ -35037,7 +34985,7 @@
       </c>
       <c r="B1804" s="19" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="C1804" s="20" t="n"/>
@@ -35129,7 +35077,7 @@
       <c r="E1810" s="20" t="n"/>
       <c r="F1810" s="20" t="n"/>
     </row>
-    <row r="1811" ht="45" customHeight="1">
+    <row r="1811" ht="20" customHeight="1">
       <c r="A1811" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -35137,7 +35085,7 @@
       </c>
       <c r="B1811" s="19" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C1811" s="20" t="n"/>
@@ -35181,7 +35129,7 @@
       </c>
       <c r="B1814" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/34537</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ncaviale</t>
         </is>
       </c>
       <c r="C1814" s="20" t="n"/>
@@ -35192,7 +35140,7 @@
     <row r="1816" ht="30" customHeight="1">
       <c r="A1816" s="16" t="inlineStr">
         <is>
-          <t>FICHA 122: 906456368</t>
+          <t>FICHA 122: 34537</t>
         </is>
       </c>
       <c r="B1816" s="17" t="n"/>
@@ -35217,7 +35165,7 @@
       <c r="E1817" s="20" t="n"/>
       <c r="F1817" s="20" t="n"/>
     </row>
-    <row r="1818" ht="20" customHeight="1">
+    <row r="1818" ht="45" customHeight="1">
       <c r="A1818" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -35225,7 +35173,7 @@
       </c>
       <c r="B1818" s="19" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="C1818" s="20" t="n"/>
@@ -35241,7 +35189,7 @@
       </c>
       <c r="B1819" s="19" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="C1819" s="20" t="n"/>
@@ -35333,7 +35281,7 @@
       <c r="E1825" s="20" t="n"/>
       <c r="F1825" s="20" t="n"/>
     </row>
-    <row r="1826" ht="20" customHeight="1">
+    <row r="1826" ht="45" customHeight="1">
       <c r="A1826" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -35341,7 +35289,7 @@
       </c>
       <c r="B1826" s="19" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="C1826" s="20" t="n"/>
@@ -35385,7 +35333,7 @@
       </c>
       <c r="B1829" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/906456368</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/34537</t>
         </is>
       </c>
       <c r="C1829" s="20" t="n"/>
@@ -35396,7 +35344,7 @@
     <row r="1831" ht="30" customHeight="1">
       <c r="A1831" s="16" t="inlineStr">
         <is>
-          <t>FICHA 123: 939595836</t>
+          <t>FICHA 123: 906456368</t>
         </is>
       </c>
       <c r="B1831" s="17" t="n"/>
@@ -35429,7 +35377,7 @@
       </c>
       <c r="B1833" s="19" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C1833" s="20" t="n"/>
@@ -35445,7 +35393,7 @@
       </c>
       <c r="B1834" s="19" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="C1834" s="20" t="n"/>
@@ -35545,7 +35493,7 @@
       </c>
       <c r="B1841" s="19" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C1841" s="20" t="n"/>
@@ -35589,7 +35537,7 @@
       </c>
       <c r="B1844" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939595836</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/906456368</t>
         </is>
       </c>
       <c r="C1844" s="20" t="n"/>
@@ -35600,7 +35548,7 @@
     <row r="1846" ht="30" customHeight="1">
       <c r="A1846" s="16" t="inlineStr">
         <is>
-          <t>FICHA 124: 46407</t>
+          <t>FICHA 124: 939595836</t>
         </is>
       </c>
       <c r="B1846" s="17" t="n"/>
@@ -35625,7 +35573,7 @@
       <c r="E1847" s="20" t="n"/>
       <c r="F1847" s="20" t="n"/>
     </row>
-    <row r="1848" ht="45" customHeight="1">
+    <row r="1848" ht="20" customHeight="1">
       <c r="A1848" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -35633,7 +35581,7 @@
       </c>
       <c r="B1848" s="19" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C1848" s="20" t="n"/>
@@ -35649,7 +35597,7 @@
       </c>
       <c r="B1849" s="19" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="C1849" s="20" t="n"/>
@@ -35741,7 +35689,7 @@
       <c r="E1855" s="20" t="n"/>
       <c r="F1855" s="20" t="n"/>
     </row>
-    <row r="1856" ht="45" customHeight="1">
+    <row r="1856" ht="20" customHeight="1">
       <c r="A1856" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -35749,7 +35697,7 @@
       </c>
       <c r="B1856" s="19" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C1856" s="20" t="n"/>
@@ -35793,7 +35741,7 @@
       </c>
       <c r="B1859" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/46407</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939595836</t>
         </is>
       </c>
       <c r="C1859" s="20" t="n"/>
@@ -35804,7 +35752,7 @@
     <row r="1861" ht="30" customHeight="1">
       <c r="A1861" s="16" t="inlineStr">
         <is>
-          <t>FICHA 125: 71899</t>
+          <t>FICHA 125: 46407</t>
         </is>
       </c>
       <c r="B1861" s="17" t="n"/>
@@ -35837,7 +35785,7 @@
       </c>
       <c r="B1863" s="19" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="C1863" s="20" t="n"/>
@@ -35853,7 +35801,7 @@
       </c>
       <c r="B1864" s="19" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="C1864" s="20" t="n"/>
@@ -35953,7 +35901,7 @@
       </c>
       <c r="B1871" s="19" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="C1871" s="20" t="n"/>
@@ -35997,7 +35945,7 @@
       </c>
       <c r="B1874" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71899</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/46407</t>
         </is>
       </c>
       <c r="C1874" s="20" t="n"/>
@@ -36008,7 +35956,7 @@
     <row r="1876" ht="30" customHeight="1">
       <c r="A1876" s="16" t="inlineStr">
         <is>
-          <t>FICHA 126: 31176</t>
+          <t>FICHA 126: 71899</t>
         </is>
       </c>
       <c r="B1876" s="17" t="n"/>
@@ -36041,7 +35989,7 @@
       </c>
       <c r="B1878" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="C1878" s="20" t="n"/>
@@ -36057,7 +36005,7 @@
       </c>
       <c r="B1879" s="19" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="C1879" s="20" t="n"/>
@@ -36157,7 +36105,7 @@
       </c>
       <c r="B1886" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="C1886" s="20" t="n"/>
@@ -36201,7 +36149,7 @@
       </c>
       <c r="B1889" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31176</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71899</t>
         </is>
       </c>
       <c r="C1889" s="20" t="n"/>
@@ -39704,7 +39652,7 @@
     <row r="2146" ht="30" customHeight="1">
       <c r="A2146" s="16" t="inlineStr">
         <is>
-          <t>FICHA 144: 937468917</t>
+          <t>FICHA 144: NA</t>
         </is>
       </c>
       <c r="B2146" s="17" t="n"/>
@@ -39729,7 +39677,7 @@
       <c r="E2147" s="20" t="n"/>
       <c r="F2147" s="20" t="n"/>
     </row>
-    <row r="2148" ht="45" customHeight="1">
+    <row r="2148" ht="20" customHeight="1">
       <c r="A2148" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -39737,7 +39685,7 @@
       </c>
       <c r="B2148" s="19" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="C2148" s="20" t="n"/>
@@ -39753,7 +39701,7 @@
       </c>
       <c r="B2149" s="19" t="inlineStr">
         <is>
-          <t>937468917</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="C2149" s="20" t="n"/>
@@ -39845,7 +39793,7 @@
       <c r="E2155" s="20" t="n"/>
       <c r="F2155" s="20" t="n"/>
     </row>
-    <row r="2156" ht="45" customHeight="1">
+    <row r="2156" ht="20" customHeight="1">
       <c r="A2156" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -39853,7 +39801,7 @@
       </c>
       <c r="B2156" s="19" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="C2156" s="20" t="n"/>
@@ -39897,7 +39845,7 @@
       </c>
       <c r="B2159" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/937468917</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NA</t>
         </is>
       </c>
       <c r="C2159" s="20" t="n"/>
@@ -39908,7 +39856,7 @@
     <row r="2161" ht="30" customHeight="1">
       <c r="A2161" s="16" t="inlineStr">
         <is>
-          <t>FICHA 145: 48508</t>
+          <t>FICHA 145: 937468917</t>
         </is>
       </c>
       <c r="B2161" s="17" t="n"/>
@@ -39941,7 +39889,7 @@
       </c>
       <c r="B2163" s="19" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="C2163" s="20" t="n"/>
@@ -39957,7 +39905,7 @@
       </c>
       <c r="B2164" s="19" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>937468917</t>
         </is>
       </c>
       <c r="C2164" s="20" t="n"/>
@@ -40057,7 +40005,7 @@
       </c>
       <c r="B2171" s="19" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="C2171" s="20" t="n"/>
@@ -40101,7 +40049,7 @@
       </c>
       <c r="B2174" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/48508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/937468917</t>
         </is>
       </c>
       <c r="C2174" s="20" t="n"/>
@@ -40112,7 +40060,7 @@
     <row r="2176" ht="30" customHeight="1">
       <c r="A2176" s="16" t="inlineStr">
         <is>
-          <t>FICHA 146: n002cet5</t>
+          <t>FICHA 146: 48508</t>
         </is>
       </c>
       <c r="B2176" s="17" t="n"/>
@@ -40137,7 +40085,7 @@
       <c r="E2177" s="20" t="n"/>
       <c r="F2177" s="20" t="n"/>
     </row>
-    <row r="2178" ht="20" customHeight="1">
+    <row r="2178" ht="45" customHeight="1">
       <c r="A2178" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -40145,7 +40093,7 @@
       </c>
       <c r="B2178" s="19" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="C2178" s="20" t="n"/>
@@ -40161,7 +40109,7 @@
       </c>
       <c r="B2179" s="19" t="inlineStr">
         <is>
-          <t>n002cet5</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="C2179" s="20" t="n"/>
@@ -40253,7 +40201,7 @@
       <c r="E2185" s="20" t="n"/>
       <c r="F2185" s="20" t="n"/>
     </row>
-    <row r="2186" ht="20" customHeight="1">
+    <row r="2186" ht="45" customHeight="1">
       <c r="A2186" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -40261,7 +40209,7 @@
       </c>
       <c r="B2186" s="19" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="C2186" s="20" t="n"/>
@@ -40305,7 +40253,7 @@
       </c>
       <c r="B2189" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n002cet5</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/48508</t>
         </is>
       </c>
       <c r="C2189" s="20" t="n"/>
@@ -40316,7 +40264,7 @@
     <row r="2191" ht="30" customHeight="1">
       <c r="A2191" s="16" t="inlineStr">
         <is>
-          <t>FICHA 147: 16545</t>
+          <t>FICHA 147: n002cet5</t>
         </is>
       </c>
       <c r="B2191" s="17" t="n"/>
@@ -40341,7 +40289,7 @@
       <c r="E2192" s="20" t="n"/>
       <c r="F2192" s="20" t="n"/>
     </row>
-    <row r="2193" ht="45" customHeight="1">
+    <row r="2193" ht="20" customHeight="1">
       <c r="A2193" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -40349,7 +40297,7 @@
       </c>
       <c r="B2193" s="19" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="C2193" s="20" t="n"/>
@@ -40365,7 +40313,7 @@
       </c>
       <c r="B2194" s="19" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>n002cet5</t>
         </is>
       </c>
       <c r="C2194" s="20" t="n"/>
@@ -40457,7 +40405,7 @@
       <c r="E2200" s="20" t="n"/>
       <c r="F2200" s="20" t="n"/>
     </row>
-    <row r="2201" ht="45" customHeight="1">
+    <row r="2201" ht="20" customHeight="1">
       <c r="A2201" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -40465,7 +40413,7 @@
       </c>
       <c r="B2201" s="19" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="C2201" s="20" t="n"/>
@@ -40509,7 +40457,7 @@
       </c>
       <c r="B2204" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16545</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n002cet5</t>
         </is>
       </c>
       <c r="C2204" s="20" t="n"/>
@@ -40520,7 +40468,7 @@
     <row r="2206" ht="30" customHeight="1">
       <c r="A2206" s="16" t="inlineStr">
         <is>
-          <t>FICHA 148: 885233544</t>
+          <t>FICHA 148: 16545</t>
         </is>
       </c>
       <c r="B2206" s="17" t="n"/>
@@ -40545,7 +40493,7 @@
       <c r="E2207" s="20" t="n"/>
       <c r="F2207" s="20" t="n"/>
     </row>
-    <row r="2208" ht="20" customHeight="1">
+    <row r="2208" ht="45" customHeight="1">
       <c r="A2208" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -40553,7 +40501,7 @@
       </c>
       <c r="B2208" s="19" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="C2208" s="20" t="n"/>
@@ -40569,7 +40517,7 @@
       </c>
       <c r="B2209" s="19" t="inlineStr">
         <is>
-          <t>885233544</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C2209" s="20" t="n"/>
@@ -40661,7 +40609,7 @@
       <c r="E2215" s="20" t="n"/>
       <c r="F2215" s="20" t="n"/>
     </row>
-    <row r="2216" ht="20" customHeight="1">
+    <row r="2216" ht="45" customHeight="1">
       <c r="A2216" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -40669,7 +40617,7 @@
       </c>
       <c r="B2216" s="19" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="C2216" s="20" t="n"/>
@@ -40713,7 +40661,7 @@
       </c>
       <c r="B2219" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/885233544</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16545</t>
         </is>
       </c>
       <c r="C2219" s="20" t="n"/>
@@ -40724,7 +40672,7 @@
     <row r="2221" ht="30" customHeight="1">
       <c r="A2221" s="16" t="inlineStr">
         <is>
-          <t>FICHA 149: 18804</t>
+          <t>FICHA 149: 885233544</t>
         </is>
       </c>
       <c r="B2221" s="17" t="n"/>
@@ -40749,7 +40697,7 @@
       <c r="E2222" s="20" t="n"/>
       <c r="F2222" s="20" t="n"/>
     </row>
-    <row r="2223" ht="45" customHeight="1">
+    <row r="2223" ht="20" customHeight="1">
       <c r="A2223" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -40757,7 +40705,7 @@
       </c>
       <c r="B2223" s="19" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="C2223" s="20" t="n"/>
@@ -40773,7 +40721,7 @@
       </c>
       <c r="B2224" s="19" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>885233544</t>
         </is>
       </c>
       <c r="C2224" s="20" t="n"/>
@@ -40865,7 +40813,7 @@
       <c r="E2230" s="20" t="n"/>
       <c r="F2230" s="20" t="n"/>
     </row>
-    <row r="2231" ht="45" customHeight="1">
+    <row r="2231" ht="20" customHeight="1">
       <c r="A2231" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -40873,7 +40821,7 @@
       </c>
       <c r="B2231" s="19" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="C2231" s="20" t="n"/>
@@ -40917,7 +40865,7 @@
       </c>
       <c r="B2234" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18804</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/885233544</t>
         </is>
       </c>
       <c r="C2234" s="20" t="n"/>
@@ -40928,7 +40876,7 @@
     <row r="2236" ht="30" customHeight="1">
       <c r="A2236" s="16" t="inlineStr">
         <is>
-          <t>FICHA 150: 18749</t>
+          <t>FICHA 150: 18804</t>
         </is>
       </c>
       <c r="B2236" s="17" t="n"/>
@@ -40961,7 +40909,7 @@
       </c>
       <c r="B2238" s="19" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="C2238" s="20" t="n"/>
@@ -40977,7 +40925,7 @@
       </c>
       <c r="B2239" s="19" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="C2239" s="20" t="n"/>
@@ -41077,7 +41025,7 @@
       </c>
       <c r="B2246" s="19" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="C2246" s="20" t="n"/>
@@ -41121,7 +41069,7 @@
       </c>
       <c r="B2249" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18749</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18804</t>
         </is>
       </c>
       <c r="C2249" s="20" t="n"/>
@@ -41132,7 +41080,7 @@
     <row r="2251" ht="30" customHeight="1">
       <c r="A2251" s="16" t="inlineStr">
         <is>
-          <t>FICHA 151: 31728</t>
+          <t>FICHA 151: 18749</t>
         </is>
       </c>
       <c r="B2251" s="17" t="n"/>
@@ -41165,7 +41113,7 @@
       </c>
       <c r="B2253" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="C2253" s="20" t="n"/>
@@ -41181,7 +41129,7 @@
       </c>
       <c r="B2254" s="19" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="C2254" s="20" t="n"/>
@@ -41281,7 +41229,7 @@
       </c>
       <c r="B2261" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="C2261" s="20" t="n"/>
@@ -41325,7 +41273,7 @@
       </c>
       <c r="B2264" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31728</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18749</t>
         </is>
       </c>
       <c r="C2264" s="20" t="n"/>
@@ -41336,7 +41284,7 @@
     <row r="2266" ht="30" customHeight="1">
       <c r="A2266" s="16" t="inlineStr">
         <is>
-          <t>FICHA 152: 13660</t>
+          <t>FICHA 152: 31728</t>
         </is>
       </c>
       <c r="B2266" s="17" t="n"/>
@@ -41361,7 +41309,7 @@
       <c r="E2267" s="20" t="n"/>
       <c r="F2267" s="20" t="n"/>
     </row>
-    <row r="2268" ht="20" customHeight="1">
+    <row r="2268" ht="45" customHeight="1">
       <c r="A2268" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -41369,7 +41317,7 @@
       </c>
       <c r="B2268" s="19" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="C2268" s="20" t="n"/>
@@ -41385,7 +41333,7 @@
       </c>
       <c r="B2269" s="19" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="C2269" s="20" t="n"/>
@@ -41485,7 +41433,7 @@
       </c>
       <c r="B2276" s="19" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technology in the heating and cooling sector. This is in line with the Paris Agreement and approaches a nearly zero carbon energy system.- By</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="C2276" s="20" t="n"/>
@@ -41529,7 +41477,7 @@
       </c>
       <c r="B2279" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13660</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31728</t>
         </is>
       </c>
       <c r="C2279" s="20" t="n"/>
@@ -41540,7 +41488,7 @@
     <row r="2281" ht="30" customHeight="1">
       <c r="A2281" s="16" t="inlineStr">
         <is>
-          <t>FICHA 153: 6484</t>
+          <t>FICHA 153: 13660</t>
         </is>
       </c>
       <c r="B2281" s="17" t="n"/>
@@ -41565,7 +41513,7 @@
       <c r="E2282" s="20" t="n"/>
       <c r="F2282" s="20" t="n"/>
     </row>
-    <row r="2283" ht="45" customHeight="1">
+    <row r="2283" ht="20" customHeight="1">
       <c r="A2283" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -41573,7 +41521,7 @@
       </c>
       <c r="B2283" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
         </is>
       </c>
       <c r="C2283" s="20" t="n"/>
@@ -41589,7 +41537,7 @@
       </c>
       <c r="B2284" s="19" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="C2284" s="20" t="n"/>
@@ -41689,7 +41637,7 @@
       </c>
       <c r="B2291" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technology in the heating and cooling sector. This is in line with the Paris Agreement and approaches a nearly zero carbon energy system.- By</t>
         </is>
       </c>
       <c r="C2291" s="20" t="n"/>
@@ -41733,7 +41681,7 @@
       </c>
       <c r="B2294" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/6484</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13660</t>
         </is>
       </c>
       <c r="C2294" s="20" t="n"/>
@@ -41744,7 +41692,7 @@
     <row r="2296" ht="30" customHeight="1">
       <c r="A2296" s="16" t="inlineStr">
         <is>
-          <t>FICHA 154: 16367</t>
+          <t>FICHA 154: 6484</t>
         </is>
       </c>
       <c r="B2296" s="17" t="n"/>
@@ -41777,7 +41725,7 @@
       </c>
       <c r="B2298" s="19" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="C2298" s="20" t="n"/>
@@ -41793,7 +41741,7 @@
       </c>
       <c r="B2299" s="19" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="C2299" s="20" t="n"/>
@@ -41893,7 +41841,7 @@
       </c>
       <c r="B2306" s="19" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="C2306" s="20" t="n"/>
@@ -41937,7 +41885,7 @@
       </c>
       <c r="B2309" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16367</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/6484</t>
         </is>
       </c>
       <c r="C2309" s="20" t="n"/>
@@ -41948,7 +41896,7 @@
     <row r="2311" ht="30" customHeight="1">
       <c r="A2311" s="16" t="inlineStr">
         <is>
-          <t>FICHA 155: 71691</t>
+          <t>FICHA 155: 16367</t>
         </is>
       </c>
       <c r="B2311" s="17" t="n"/>
@@ -41981,7 +41929,7 @@
       </c>
       <c r="B2313" s="19" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="C2313" s="20" t="n"/>
@@ -41997,7 +41945,7 @@
       </c>
       <c r="B2314" s="19" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="C2314" s="20" t="n"/>
@@ -42097,7 +42045,7 @@
       </c>
       <c r="B2321" s="19" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="C2321" s="20" t="n"/>
@@ -42141,7 +42089,7 @@
       </c>
       <c r="B2324" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71691</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16367</t>
         </is>
       </c>
       <c r="C2324" s="20" t="n"/>
@@ -42152,7 +42100,7 @@
     <row r="2326" ht="30" customHeight="1">
       <c r="A2326" s="16" t="inlineStr">
         <is>
-          <t>FICHA 156: 956926438</t>
+          <t>FICHA 156: 71691</t>
         </is>
       </c>
       <c r="B2326" s="17" t="n"/>
@@ -42177,7 +42125,7 @@
       <c r="E2327" s="20" t="n"/>
       <c r="F2327" s="20" t="n"/>
     </row>
-    <row r="2328" ht="20" customHeight="1">
+    <row r="2328" ht="45" customHeight="1">
       <c r="A2328" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -42185,7 +42133,7 @@
       </c>
       <c r="B2328" s="19" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="C2328" s="20" t="n"/>
@@ -42201,7 +42149,7 @@
       </c>
       <c r="B2329" s="19" t="inlineStr">
         <is>
-          <t>956926438</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="C2329" s="20" t="n"/>
@@ -42293,7 +42241,7 @@
       <c r="E2335" s="20" t="n"/>
       <c r="F2335" s="20" t="n"/>
     </row>
-    <row r="2336" ht="20" customHeight="1">
+    <row r="2336" ht="45" customHeight="1">
       <c r="A2336" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -42301,7 +42249,7 @@
       </c>
       <c r="B2336" s="19" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="C2336" s="20" t="n"/>
@@ -42345,7 +42293,7 @@
       </c>
       <c r="B2339" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/956926438</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71691</t>
         </is>
       </c>
       <c r="C2339" s="20" t="n"/>
@@ -42356,7 +42304,7 @@
     <row r="2341" ht="30" customHeight="1">
       <c r="A2341" s="16" t="inlineStr">
         <is>
-          <t>FICHA 157: 953677035</t>
+          <t>FICHA 157: 956926438</t>
         </is>
       </c>
       <c r="B2341" s="17" t="n"/>
@@ -42389,7 +42337,7 @@
       </c>
       <c r="B2343" s="19" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="C2343" s="20" t="n"/>
@@ -42405,7 +42353,7 @@
       </c>
       <c r="B2344" s="19" t="inlineStr">
         <is>
-          <t>953677035</t>
+          <t>956926438</t>
         </is>
       </c>
       <c r="C2344" s="20" t="n"/>
@@ -42505,7 +42453,7 @@
       </c>
       <c r="B2351" s="19" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="C2351" s="20" t="n"/>
@@ -42549,7 +42497,7 @@
       </c>
       <c r="B2354" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953677035</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/956926438</t>
         </is>
       </c>
       <c r="C2354" s="20" t="n"/>
@@ -42560,7 +42508,7 @@
     <row r="2356" ht="30" customHeight="1">
       <c r="A2356" s="16" t="inlineStr">
         <is>
-          <t>FICHA 158: 953552487</t>
+          <t>FICHA 158: 953677035</t>
         </is>
       </c>
       <c r="B2356" s="17" t="n"/>
@@ -42593,7 +42541,7 @@
       </c>
       <c r="B2358" s="19" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="C2358" s="20" t="n"/>
@@ -42609,7 +42557,7 @@
       </c>
       <c r="B2359" s="19" t="inlineStr">
         <is>
-          <t>953552487</t>
+          <t>953677035</t>
         </is>
       </c>
       <c r="C2359" s="20" t="n"/>
@@ -42709,7 +42657,7 @@
       </c>
       <c r="B2366" s="19" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="C2366" s="20" t="n"/>
@@ -42753,7 +42701,7 @@
       </c>
       <c r="B2369" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953552487</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953677035</t>
         </is>
       </c>
       <c r="C2369" s="20" t="n"/>
@@ -42764,7 +42712,7 @@
     <row r="2371" ht="30" customHeight="1">
       <c r="A2371" s="16" t="inlineStr">
         <is>
-          <t>FICHA 159: 925388828</t>
+          <t>FICHA 159: 953552487</t>
         </is>
       </c>
       <c r="B2371" s="17" t="n"/>
@@ -42797,7 +42745,7 @@
       </c>
       <c r="B2373" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="C2373" s="20" t="n"/>
@@ -42813,7 +42761,7 @@
       </c>
       <c r="B2374" s="19" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>953552487</t>
         </is>
       </c>
       <c r="C2374" s="20" t="n"/>
@@ -42913,7 +42861,7 @@
       </c>
       <c r="B2381" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="C2381" s="20" t="n"/>
@@ -42957,7 +42905,7 @@
       </c>
       <c r="B2384" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953552487</t>
         </is>
       </c>
       <c r="C2384" s="20" t="n"/>
@@ -42968,7 +42916,7 @@
     <row r="2386" ht="30" customHeight="1">
       <c r="A2386" s="16" t="inlineStr">
         <is>
-          <t>FICHA 160: 934294980</t>
+          <t>FICHA 160: 925388828</t>
         </is>
       </c>
       <c r="B2386" s="17" t="n"/>
@@ -43001,7 +42949,7 @@
       </c>
       <c r="B2388" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C2388" s="20" t="n"/>
@@ -43017,7 +42965,7 @@
       </c>
       <c r="B2389" s="19" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C2389" s="20" t="n"/>
@@ -43117,7 +43065,7 @@
       </c>
       <c r="B2396" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C2396" s="20" t="n"/>
@@ -43161,7 +43109,7 @@
       </c>
       <c r="B2399" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
         </is>
       </c>
       <c r="C2399" s="20" t="n"/>
@@ -43172,7 +43120,7 @@
     <row r="2401" ht="30" customHeight="1">
       <c r="A2401" s="16" t="inlineStr">
         <is>
-          <t>FICHA 161: 876983694</t>
+          <t>FICHA 161: 934294980</t>
         </is>
       </c>
       <c r="B2401" s="17" t="n"/>
@@ -43205,7 +43153,7 @@
       </c>
       <c r="B2403" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C2403" s="20" t="n"/>
@@ -43221,7 +43169,7 @@
       </c>
       <c r="B2404" s="19" t="inlineStr">
         <is>
-          <t>876983694</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C2404" s="20" t="n"/>
@@ -43321,7 +43269,7 @@
       </c>
       <c r="B2411" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C2411" s="20" t="n"/>
@@ -43365,7 +43313,7 @@
       </c>
       <c r="B2414" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/876983694</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
         </is>
       </c>
       <c r="C2414" s="20" t="n"/>
@@ -43376,7 +43324,7 @@
     <row r="2416" ht="30" customHeight="1">
       <c r="A2416" s="16" t="inlineStr">
         <is>
-          <t>FICHA 162: 17917</t>
+          <t>FICHA 162: 876983694</t>
         </is>
       </c>
       <c r="B2416" s="17" t="n"/>
@@ -43401,7 +43349,7 @@
       <c r="E2417" s="20" t="n"/>
       <c r="F2417" s="20" t="n"/>
     </row>
-    <row r="2418" ht="45" customHeight="1">
+    <row r="2418" ht="20" customHeight="1">
       <c r="A2418" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -43409,7 +43357,7 @@
       </c>
       <c r="B2418" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="C2418" s="20" t="n"/>
@@ -43425,7 +43373,7 @@
       </c>
       <c r="B2419" s="19" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>876983694</t>
         </is>
       </c>
       <c r="C2419" s="20" t="n"/>
@@ -43517,7 +43465,7 @@
       <c r="E2425" s="20" t="n"/>
       <c r="F2425" s="20" t="n"/>
     </row>
-    <row r="2426" ht="45" customHeight="1">
+    <row r="2426" ht="20" customHeight="1">
       <c r="A2426" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -43525,7 +43473,7 @@
       </c>
       <c r="B2426" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="C2426" s="20" t="n"/>
@@ -43569,7 +43517,7 @@
       </c>
       <c r="B2429" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17917</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/876983694</t>
         </is>
       </c>
       <c r="C2429" s="20" t="n"/>
@@ -43580,7 +43528,7 @@
     <row r="2431" ht="30" customHeight="1">
       <c r="A2431" s="16" t="inlineStr">
         <is>
-          <t>FICHA 163: 935134321</t>
+          <t>FICHA 163: 17917</t>
         </is>
       </c>
       <c r="B2431" s="17" t="n"/>
@@ -43605,7 +43553,7 @@
       <c r="E2432" s="20" t="n"/>
       <c r="F2432" s="20" t="n"/>
     </row>
-    <row r="2433" ht="20" customHeight="1">
+    <row r="2433" ht="45" customHeight="1">
       <c r="A2433" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -43613,7 +43561,7 @@
       </c>
       <c r="B2433" s="19" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="C2433" s="20" t="n"/>
@@ -43629,7 +43577,7 @@
       </c>
       <c r="B2434" s="19" t="inlineStr">
         <is>
-          <t>935134321</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="C2434" s="20" t="n"/>
@@ -43721,7 +43669,7 @@
       <c r="E2440" s="20" t="n"/>
       <c r="F2440" s="20" t="n"/>
     </row>
-    <row r="2441" ht="20" customHeight="1">
+    <row r="2441" ht="45" customHeight="1">
       <c r="A2441" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -43729,7 +43677,7 @@
       </c>
       <c r="B2441" s="19" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="C2441" s="20" t="n"/>
@@ -43773,7 +43721,7 @@
       </c>
       <c r="B2444" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/935134321</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17917</t>
         </is>
       </c>
       <c r="C2444" s="20" t="n"/>
@@ -43784,7 +43732,7 @@
     <row r="2446" ht="30" customHeight="1">
       <c r="A2446" s="16" t="inlineStr">
         <is>
-          <t>FICHA 164: 883154834</t>
+          <t>FICHA 164: 935134321</t>
         </is>
       </c>
       <c r="B2446" s="17" t="n"/>
@@ -43817,7 +43765,7 @@
       </c>
       <c r="B2448" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="C2448" s="20" t="n"/>
@@ -43833,7 +43781,7 @@
       </c>
       <c r="B2449" s="19" t="inlineStr">
         <is>
-          <t>883154834</t>
+          <t>935134321</t>
         </is>
       </c>
       <c r="C2449" s="20" t="n"/>
@@ -43933,7 +43881,7 @@
       </c>
       <c r="B2456" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="C2456" s="20" t="n"/>
@@ -43977,7 +43925,7 @@
       </c>
       <c r="B2459" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/883154834</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/935134321</t>
         </is>
       </c>
       <c r="C2459" s="20" t="n"/>
@@ -43988,7 +43936,7 @@
     <row r="2461" ht="30" customHeight="1">
       <c r="A2461" s="16" t="inlineStr">
         <is>
-          <t>FICHA 165: 93508</t>
+          <t>FICHA 165: 883154834</t>
         </is>
       </c>
       <c r="B2461" s="17" t="n"/>
@@ -44013,7 +43961,7 @@
       <c r="E2462" s="20" t="n"/>
       <c r="F2462" s="20" t="n"/>
     </row>
-    <row r="2463" ht="45" customHeight="1">
+    <row r="2463" ht="20" customHeight="1">
       <c r="A2463" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -44021,7 +43969,7 @@
       </c>
       <c r="B2463" s="19" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="C2463" s="20" t="n"/>
@@ -44037,7 +43985,7 @@
       </c>
       <c r="B2464" s="19" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>883154834</t>
         </is>
       </c>
       <c r="C2464" s="20" t="n"/>
@@ -44129,7 +44077,7 @@
       <c r="E2470" s="20" t="n"/>
       <c r="F2470" s="20" t="n"/>
     </row>
-    <row r="2471" ht="45" customHeight="1">
+    <row r="2471" ht="20" customHeight="1">
       <c r="A2471" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -44137,7 +44085,7 @@
       </c>
       <c r="B2471" s="19" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="C2471" s="20" t="n"/>
@@ -44181,7 +44129,7 @@
       </c>
       <c r="B2474" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/93508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/883154834</t>
         </is>
       </c>
       <c r="C2474" s="20" t="n"/>
@@ -44192,7 +44140,7 @@
     <row r="2476" ht="30" customHeight="1">
       <c r="A2476" s="16" t="inlineStr">
         <is>
-          <t>FICHA 166: 50912</t>
+          <t>FICHA 166: 93508</t>
         </is>
       </c>
       <c r="B2476" s="17" t="n"/>
@@ -44225,7 +44173,7 @@
       </c>
       <c r="B2478" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="C2478" s="20" t="n"/>
@@ -44241,7 +44189,7 @@
       </c>
       <c r="B2479" s="19" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="C2479" s="20" t="n"/>
@@ -44341,7 +44289,7 @@
       </c>
       <c r="B2486" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="C2486" s="20" t="n"/>
@@ -44385,7 +44333,7 @@
       </c>
       <c r="B2489" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/50912</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/93508</t>
         </is>
       </c>
       <c r="C2489" s="20" t="n"/>
@@ -44396,7 +44344,7 @@
     <row r="2491" ht="30" customHeight="1">
       <c r="A2491" s="16" t="inlineStr">
         <is>
-          <t>FICHA 167: NA</t>
+          <t>FICHA 167: 50912</t>
         </is>
       </c>
       <c r="B2491" s="17" t="n"/>
@@ -44421,7 +44369,7 @@
       <c r="E2492" s="20" t="n"/>
       <c r="F2492" s="20" t="n"/>
     </row>
-    <row r="2493" ht="20" customHeight="1">
+    <row r="2493" ht="45" customHeight="1">
       <c r="A2493" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -44429,7 +44377,7 @@
       </c>
       <c r="B2493" s="19" t="inlineStr">
         <is>
-          <t>Climate resilience of European coastal cities and settlements</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="C2493" s="20" t="n"/>
@@ -44445,7 +44393,7 @@
       </c>
       <c r="B2494" s="19" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="C2494" s="20" t="n"/>
@@ -44537,7 +44485,7 @@
       <c r="E2500" s="20" t="n"/>
       <c r="F2500" s="20" t="n"/>
     </row>
-    <row r="2501" ht="20" customHeight="1">
+    <row r="2501" ht="45" customHeight="1">
       <c r="A2501" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -44545,7 +44493,7 @@
       </c>
       <c r="B2501" s="19" t="inlineStr">
         <is>
-          <t>Climate resilience of European coastal cities and settlements</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="C2501" s="20" t="n"/>
@@ -44589,7 +44537,7 @@
       </c>
       <c r="B2504" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/50912</t>
         </is>
       </c>
       <c r="C2504" s="20" t="n"/>
@@ -48892,7 +48840,7 @@
     <row r="2821" ht="30" customHeight="1">
       <c r="A2821" s="16" t="inlineStr">
         <is>
-          <t>FICHA 189: EUS-16189</t>
+          <t>FICHA 189: EUS-71228</t>
         </is>
       </c>
       <c r="B2821" s="17" t="n"/>
@@ -48925,7 +48873,7 @@
       </c>
       <c r="B2823" s="19" t="inlineStr">
         <is>
-          <t>Servicio de asistencia técnica para la redacción de un Plan de Clima y Energía en el Ayuntamiento de Basauri.</t>
+          <t>Servicio de conservación y mantenimiento de las zonas verdes municipales (arbustos y setos, jardineras, siega de caminos, arbolado y taludes) del municipio de Basauri.</t>
         </is>
       </c>
       <c r="C2823" s="20" t="n"/>
@@ -48941,7 +48889,7 @@
       </c>
       <c r="B2824" s="19" t="inlineStr">
         <is>
-          <t>EUS-16189</t>
+          <t>EUS-71228</t>
         </is>
       </c>
       <c r="C2824" s="20" t="n"/>
@@ -49093,7 +49041,7 @@
       </c>
       <c r="B2834" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-asistencia-tecnica-redaccion-plan-clima-y-energia-ayuntamiento-basauri/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-conservacion-y-mantenimiento-zonas-verdes-municipales-arbustos-y-setos-jardineras-siega-caminos-arbolado-y-taludes-del-municipio-basauri/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2834" s="20" t="n"/>
@@ -49104,7 +49052,7 @@
     <row r="2836" ht="30" customHeight="1">
       <c r="A2836" s="16" t="inlineStr">
         <is>
-          <t>FICHA 190: EUS-65237</t>
+          <t>FICHA 190: EUS-36680</t>
         </is>
       </c>
       <c r="B2836" s="17" t="n"/>
@@ -49153,7 +49101,7 @@
       </c>
       <c r="B2839" s="19" t="inlineStr">
         <is>
-          <t>EUS-65237</t>
+          <t>EUS-36680</t>
         </is>
       </c>
       <c r="C2839" s="20" t="n"/>
@@ -49316,7 +49264,7 @@
     <row r="2851" ht="30" customHeight="1">
       <c r="A2851" s="16" t="inlineStr">
         <is>
-          <t>FICHA 191: EUS-01883</t>
+          <t>FICHA 191: EUS-57715</t>
         </is>
       </c>
       <c r="B2851" s="17" t="n"/>
@@ -49349,7 +49297,7 @@
       </c>
       <c r="B2853" s="19" t="inlineStr">
         <is>
-          <t>Renovación del sistema de climatización del centro de formación en consumo de Donostia (Zarategi 82-84)</t>
+          <t>Servicio de implementación de un programa de incentivos a la movilidad sostenible mediante la plataforma de Ciclogreen</t>
         </is>
       </c>
       <c r="C2853" s="20" t="n"/>
@@ -49365,7 +49313,7 @@
       </c>
       <c r="B2854" s="19" t="inlineStr">
         <is>
-          <t>EUS-01883</t>
+          <t>EUS-57715</t>
         </is>
       </c>
       <c r="C2854" s="20" t="n"/>
@@ -49517,7 +49465,7 @@
       </c>
       <c r="B2864" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/renovacion-del-sistema-climatizacion-del-centro-formacion-consumo-donostia-zarategi-82-84/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-implementacion-programa-incentivos-movilidad-sostenible-mediante-plataforma-ciclogreen/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2864" s="20" t="n"/>
@@ -49528,7 +49476,7 @@
     <row r="2866" ht="30" customHeight="1">
       <c r="A2866" s="16" t="inlineStr">
         <is>
-          <t>FICHA 192: EUS-30957</t>
+          <t>FICHA 192: EUS-03003</t>
         </is>
       </c>
       <c r="B2866" s="17" t="n"/>
@@ -49553,7 +49501,7 @@
       <c r="E2867" s="20" t="n"/>
       <c r="F2867" s="20" t="n"/>
     </row>
-    <row r="2868" ht="20" customHeight="1">
+    <row r="2868" ht="45" customHeight="1">
       <c r="A2868" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -49561,7 +49509,7 @@
       </c>
       <c r="B2868" s="19" t="inlineStr">
         <is>
-          <t>vinilado coches funicular tras rehabilitacion</t>
+          <t>Subvenciones para la organización, digitalización y difusión de archivos no públicos (2026)</t>
         </is>
       </c>
       <c r="C2868" s="20" t="n"/>
@@ -49577,7 +49525,7 @@
       </c>
       <c r="B2869" s="19" t="inlineStr">
         <is>
-          <t>EUS-30957</t>
+          <t>EUS-03003</t>
         </is>
       </c>
       <c r="C2869" s="20" t="n"/>
@@ -49653,7 +49601,7 @@
       </c>
       <c r="B2874" s="19" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="C2874" s="20" t="n"/>
@@ -49711,9 +49659,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2878" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALTA — </t>
+      <c r="B2878" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
         </is>
       </c>
       <c r="C2878" s="20" t="n"/>
@@ -49721,7 +49669,7 @@
       <c r="E2878" s="20" t="n"/>
       <c r="F2878" s="20" t="n"/>
     </row>
-    <row r="2879" ht="45" customHeight="1">
+    <row r="2879" ht="20" customHeight="1">
       <c r="A2879" s="18" t="inlineStr">
         <is>
           <t>Enlace al portal</t>
@@ -49729,7 +49677,7 @@
       </c>
       <c r="B2879" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/vinilado-coches-funicular-rehabilitacion/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/apri/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2879" s="20" t="n"/>
@@ -49740,7 +49688,7 @@
     <row r="2881" ht="30" customHeight="1">
       <c r="A2881" s="16" t="inlineStr">
         <is>
-          <t>FICHA 193: EUS-19215</t>
+          <t>FICHA 193: EUS-89928</t>
         </is>
       </c>
       <c r="B2881" s="17" t="n"/>
@@ -49773,7 +49721,7 @@
       </c>
       <c r="B2883" s="19" t="inlineStr">
         <is>
-          <t>Subvenciones para la organización, digitalización y difusión de archivos no públicos (2026)</t>
+          <t>Subvenciones para la ejecución de trabajos orientados al ámbito de la salvaguarda del patrimonio cultural inmaterial 2026-2027</t>
         </is>
       </c>
       <c r="C2883" s="20" t="n"/>
@@ -49789,7 +49737,7 @@
       </c>
       <c r="B2884" s="19" t="inlineStr">
         <is>
-          <t>EUS-19215</t>
+          <t>EUS-89928</t>
         </is>
       </c>
       <c r="C2884" s="20" t="n"/>
@@ -49933,7 +49881,7 @@
       <c r="E2893" s="20" t="n"/>
       <c r="F2893" s="20" t="n"/>
     </row>
-    <row r="2894" ht="20" customHeight="1">
+    <row r="2894" ht="45" customHeight="1">
       <c r="A2894" s="18" t="inlineStr">
         <is>
           <t>Enlace al portal</t>
@@ -49941,7 +49889,7 @@
       </c>
       <c r="B2894" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/apri/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/subvenciones-para-la-ejecucion-de-trabajos-orientados-al-ambito-de-la-salvaguarda-del-patrimonio-cultural-inmaterial-2026-2027/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2894" s="20" t="n"/>
@@ -49952,7 +49900,7 @@
     <row r="2896" ht="30" customHeight="1">
       <c r="A2896" s="16" t="inlineStr">
         <is>
-          <t>FICHA 194: EUS-95140</t>
+          <t>FICHA 194: EUS-14280</t>
         </is>
       </c>
       <c r="B2896" s="17" t="n"/>
@@ -49985,7 +49933,7 @@
       </c>
       <c r="B2898" s="19" t="inlineStr">
         <is>
-          <t>Subvenciones para la ejecución de trabajos orientados al ámbito de la salvaguarda del patrimonio cultural inmaterial 2026-2027</t>
+          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado una Alianza para las Cadenas de Valor Industriales Marítimas, que contempla la soberanía tecnológica y de suministros, la defensa, la compe</t>
         </is>
       </c>
       <c r="C2898" s="20" t="n"/>
@@ -50001,7 +49949,7 @@
       </c>
       <c r="B2899" s="19" t="inlineStr">
         <is>
-          <t>EUS-95140</t>
+          <t>EUS-14280</t>
         </is>
       </c>
       <c r="C2899" s="20" t="n"/>
@@ -50153,7 +50101,7 @@
       </c>
       <c r="B2909" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/subvenciones-para-la-ejecucion-de-trabajos-orientados-al-ambito-de-la-salvaguarda-del-patrimonio-cultural-inmaterial-2026-2027/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/itsasindustriarakolankide/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2909" s="20" t="n"/>
@@ -50164,7 +50112,7 @@
     <row r="2911" ht="30" customHeight="1">
       <c r="A2911" s="16" t="inlineStr">
         <is>
-          <t>FICHA 195: EUS-60062</t>
+          <t>FICHA 195: EUS-05836</t>
         </is>
       </c>
       <c r="B2911" s="17" t="n"/>
@@ -50197,7 +50145,7 @@
       </c>
       <c r="B2913" s="19" t="inlineStr">
         <is>
-          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado una Alianza para las Cadenas de Valor Industriales Marítimas, que contempla la soberanía tecnológica y de suministros, la defensa, la compe</t>
+          <t>Dirección facultativa de las obras de reverdecimiento del Cantón de Anorbin en el marco del Proyecto LIFE I P URBAN KLIMA 2050 (life18 IPC/ES/000001)</t>
         </is>
       </c>
       <c r="C2913" s="20" t="n"/>
@@ -50213,7 +50161,7 @@
       </c>
       <c r="B2914" s="19" t="inlineStr">
         <is>
-          <t>EUS-60062</t>
+          <t>EUS-05836</t>
         </is>
       </c>
       <c r="C2914" s="20" t="n"/>
@@ -50289,7 +50237,7 @@
       </c>
       <c r="B2919" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2919" s="20" t="n"/>
@@ -50365,7 +50313,7 @@
       </c>
       <c r="B2924" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/itsasindustriarakolankide/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/direccion-facultativa-obras-reverdecimiento-del-canton-anorbin-marco-del-proyecto-life-i-p-urban-klima-2050-life18-ipc-es-000001/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2924" s="20" t="n"/>
@@ -50376,7 +50324,7 @@
     <row r="2926" ht="30" customHeight="1">
       <c r="A2926" s="16" t="inlineStr">
         <is>
-          <t>FICHA 196: EUS-30850</t>
+          <t>FICHA 196: EUS-20008</t>
         </is>
       </c>
       <c r="B2926" s="17" t="n"/>
@@ -50401,7 +50349,7 @@
       <c r="E2927" s="20" t="n"/>
       <c r="F2927" s="20" t="n"/>
     </row>
-    <row r="2928" ht="45" customHeight="1">
+    <row r="2928" ht="20" customHeight="1">
       <c r="A2928" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -50409,7 +50357,7 @@
       </c>
       <c r="B2928" s="19" t="inlineStr">
         <is>
-          <t>Contratación del suministro de un total de 590 contenedores de polietileno inyectado de alta densidad, de nueva fabricación, para renovación del parque de contenedores de carga trasera de la Cuadrilla</t>
+          <t>Suministro de equipamiento e instalación de Parque Infantil en Bedia</t>
         </is>
       </c>
       <c r="C2928" s="20" t="n"/>
@@ -50425,7 +50373,7 @@
       </c>
       <c r="B2929" s="19" t="inlineStr">
         <is>
-          <t>EUS-30850</t>
+          <t>EUS-20008</t>
         </is>
       </c>
       <c r="C2929" s="20" t="n"/>
@@ -50577,7 +50525,7 @@
       </c>
       <c r="B2939" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/contratacion-del-suministro-total-590-contenedores-polietileno-inyectado-alta-densidad-nueva-fabricacion-renovacion-del-parque-contenedores-carga-trasera-cuadrilla-anana/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-equipamiento-e-instalacion-parque-infantil-bedia/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2939" s="20" t="n"/>
@@ -50588,7 +50536,7 @@
     <row r="2941" ht="30" customHeight="1">
       <c r="A2941" s="16" t="inlineStr">
         <is>
-          <t>FICHA 197: EUS-00649</t>
+          <t>FICHA 197: EUS-26417</t>
         </is>
       </c>
       <c r="B2941" s="17" t="n"/>
@@ -50621,7 +50569,7 @@
       </c>
       <c r="B2943" s="19" t="inlineStr">
         <is>
-          <t>Contratación de la ejecución de cubierta del centro de visitantes ?El Torco? del Valle Salado, Salinas de Añana, Álava.</t>
+          <t>Recogida, grabación y tratamiento básico de la información de la operación continua ?Encuesta de población en relación con la actividad (PRA)? y sus módulos ?Encuesta sobre la sociedad de la informaci</t>
         </is>
       </c>
       <c r="C2943" s="20" t="n"/>
@@ -50637,7 +50585,7 @@
       </c>
       <c r="B2944" s="19" t="inlineStr">
         <is>
-          <t>EUS-00649</t>
+          <t>EUS-26417</t>
         </is>
       </c>
       <c r="C2944" s="20" t="n"/>
@@ -50789,7 +50737,7 @@
       </c>
       <c r="B2954" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/contratacion-ejecucion-cubierta-del-centro-visitantes-torco-del-valle-salado-salinas-anana-alava/expjaso743156/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/recogida-grabacion-y-tratamiento-basico-informacion-operacion-continua-encuesta-poblacion-relacion-actividad-pra-y-sus-modulos-encuesta-sociedad-informacion-familias-esif-y-encuesta-conciliacion-vida-laboral-familiar-y-personal-cvl-2027-2028/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2954" s="20" t="n"/>
@@ -50797,220 +50745,8 @@
       <c r="E2954" s="20" t="n"/>
       <c r="F2954" s="20" t="n"/>
     </row>
-    <row r="2956" ht="30" customHeight="1">
-      <c r="A2956" s="16" t="inlineStr">
-        <is>
-          <t>FICHA 198: EUS-60669</t>
-        </is>
-      </c>
-      <c r="B2956" s="17" t="n"/>
-      <c r="C2956" s="17" t="n"/>
-      <c r="D2956" s="17" t="n"/>
-      <c r="E2956" s="17" t="n"/>
-      <c r="F2956" s="17" t="n"/>
-    </row>
-    <row r="2957" ht="20" customHeight="1">
-      <c r="A2957" s="18" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B2957" s="19" t="inlineStr">
-        <is>
-          <t>🟢 Euskadi</t>
-        </is>
-      </c>
-      <c r="C2957" s="20" t="n"/>
-      <c r="D2957" s="20" t="n"/>
-      <c r="E2957" s="20" t="n"/>
-      <c r="F2957" s="20" t="n"/>
-    </row>
-    <row r="2958" ht="20" customHeight="1">
-      <c r="A2958" s="18" t="inlineStr">
-        <is>
-          <t>Titulo</t>
-        </is>
-      </c>
-      <c r="B2958" s="19" t="inlineStr">
-        <is>
-          <t>pegatinas en impresion digital a color</t>
-        </is>
-      </c>
-      <c r="C2958" s="20" t="n"/>
-      <c r="D2958" s="20" t="n"/>
-      <c r="E2958" s="20" t="n"/>
-      <c r="F2958" s="20" t="n"/>
-    </row>
-    <row r="2959" ht="20" customHeight="1">
-      <c r="A2959" s="18" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2959" s="19" t="inlineStr">
-        <is>
-          <t>EUS-60669</t>
-        </is>
-      </c>
-      <c r="C2959" s="20" t="n"/>
-      <c r="D2959" s="20" t="n"/>
-      <c r="E2959" s="20" t="n"/>
-      <c r="F2959" s="20" t="n"/>
-    </row>
-    <row r="2960" ht="20" customHeight="1">
-      <c r="A2960" s="18" t="inlineStr">
-        <is>
-          <t>Programa</t>
-        </is>
-      </c>
-      <c r="B2960" s="19" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="C2960" s="20" t="n"/>
-      <c r="D2960" s="20" t="n"/>
-      <c r="E2960" s="20" t="n"/>
-      <c r="F2960" s="20" t="n"/>
-    </row>
-    <row r="2961" ht="20" customHeight="1">
-      <c r="A2961" s="18" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B2961" s="19" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C2961" s="20" t="n"/>
-      <c r="D2961" s="20" t="n"/>
-      <c r="E2961" s="20" t="n"/>
-      <c r="F2961" s="20" t="n"/>
-    </row>
-    <row r="2962" ht="20" customHeight="1">
-      <c r="A2962" s="18" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="B2962" s="19" t="inlineStr"/>
-      <c r="C2962" s="20" t="n"/>
-      <c r="D2962" s="20" t="n"/>
-      <c r="E2962" s="20" t="n"/>
-      <c r="F2962" s="20" t="n"/>
-    </row>
-    <row r="2963" ht="20" customHeight="1">
-      <c r="A2963" s="18" t="inlineStr">
-        <is>
-          <t>Presupuesto (EUR)</t>
-        </is>
-      </c>
-      <c r="B2963" s="19" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="C2963" s="20" t="n"/>
-      <c r="D2963" s="20" t="n"/>
-      <c r="E2963" s="20" t="n"/>
-      <c r="F2963" s="20" t="n"/>
-    </row>
-    <row r="2964" ht="20" customHeight="1">
-      <c r="A2964" s="18" t="inlineStr">
-        <is>
-          <t>Tipo de Accion</t>
-        </is>
-      </c>
-      <c r="B2964" s="19" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="C2964" s="20" t="n"/>
-      <c r="D2964" s="20" t="n"/>
-      <c r="E2964" s="20" t="n"/>
-      <c r="F2964" s="20" t="n"/>
-    </row>
-    <row r="2965" ht="20" customHeight="1">
-      <c r="A2965" s="18" t="inlineStr">
-        <is>
-          <t>Call ID</t>
-        </is>
-      </c>
-      <c r="B2965" s="19" t="inlineStr"/>
-      <c r="C2965" s="20" t="n"/>
-      <c r="D2965" s="20" t="n"/>
-      <c r="E2965" s="20" t="n"/>
-      <c r="F2965" s="20" t="n"/>
-    </row>
-    <row r="2966" ht="20" customHeight="1">
-      <c r="A2966" s="18" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="B2966" s="19" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="C2966" s="20" t="n"/>
-      <c r="D2966" s="20" t="n"/>
-      <c r="E2966" s="20" t="n"/>
-      <c r="F2966" s="20" t="n"/>
-    </row>
-    <row r="2967" ht="20" customHeight="1">
-      <c r="A2967" s="18" t="inlineStr">
-        <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="B2967" s="19" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C2967" s="20" t="n"/>
-      <c r="D2967" s="20" t="n"/>
-      <c r="E2967" s="20" t="n"/>
-      <c r="F2967" s="20" t="n"/>
-    </row>
-    <row r="2968" ht="20" customHeight="1">
-      <c r="A2968" s="18" t="inlineStr">
-        <is>
-          <t>Relevancia Bilbao</t>
-        </is>
-      </c>
-      <c r="B2968" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
-        </is>
-      </c>
-      <c r="C2968" s="20" t="n"/>
-      <c r="D2968" s="20" t="n"/>
-      <c r="E2968" s="20" t="n"/>
-      <c r="F2968" s="20" t="n"/>
-    </row>
-    <row r="2969" ht="45" customHeight="1">
-      <c r="A2969" s="18" t="inlineStr">
-        <is>
-          <t>Enlace al portal</t>
-        </is>
-      </c>
-      <c r="B2969" s="22" t="inlineStr">
-        <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/pegatinas-impresion-digital-color/web01-tramite/es/</t>
-        </is>
-      </c>
-      <c r="C2969" s="20" t="n"/>
-      <c r="D2969" s="20" t="n"/>
-      <c r="E2969" s="20" t="n"/>
-      <c r="F2969" s="20" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="2772">
+  <mergeCells count="2758">
     <mergeCell ref="B679:F679"/>
     <mergeCell ref="B2192:F2192"/>
     <mergeCell ref="B1765:F1765"/>
@@ -51152,7 +50888,6 @@
     <mergeCell ref="B1444:F1444"/>
     <mergeCell ref="B385:F385"/>
     <mergeCell ref="B689:F689"/>
-    <mergeCell ref="B2957:F2957"/>
     <mergeCell ref="B1873:F1873"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="B262:F262"/>
@@ -51282,7 +51017,6 @@
     <mergeCell ref="B1161:F1161"/>
     <mergeCell ref="B2529:F2529"/>
     <mergeCell ref="B2345:F2345"/>
-    <mergeCell ref="B2958:F2958"/>
     <mergeCell ref="B2643:F2643"/>
     <mergeCell ref="B1584:F1584"/>
     <mergeCell ref="B1926:F1926"/>
@@ -51391,7 +51125,6 @@
     <mergeCell ref="B2029:F2029"/>
     <mergeCell ref="B1912:F1912"/>
     <mergeCell ref="B2667:F2667"/>
-    <mergeCell ref="B2965:F2965"/>
     <mergeCell ref="B242:F242"/>
     <mergeCell ref="B880:F880"/>
     <mergeCell ref="B2458:F2458"/>
@@ -51407,7 +51140,6 @@
     <mergeCell ref="B2756:F2756"/>
     <mergeCell ref="B1941:F1941"/>
     <mergeCell ref="B882:F882"/>
-    <mergeCell ref="B2967:F2967"/>
     <mergeCell ref="B2239:F2239"/>
     <mergeCell ref="B1180:F1180"/>
     <mergeCell ref="A151:F151"/>
@@ -51768,7 +51500,6 @@
     <mergeCell ref="B2201:F2201"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="B383:F383"/>
-    <mergeCell ref="B2966:F2966"/>
     <mergeCell ref="B1355:F1355"/>
     <mergeCell ref="B2230:F2230"/>
     <mergeCell ref="B1784:F1784"/>
@@ -52022,7 +51753,6 @@
     <mergeCell ref="A2926:F2926"/>
     <mergeCell ref="B1774:F1774"/>
     <mergeCell ref="B1019:F1019"/>
-    <mergeCell ref="B2964:F2964"/>
     <mergeCell ref="B2501:F2501"/>
     <mergeCell ref="B294:F294"/>
     <mergeCell ref="B592:F592"/>
@@ -52382,7 +52112,6 @@
     <mergeCell ref="A2116:F2116"/>
     <mergeCell ref="B964:F964"/>
     <mergeCell ref="B209:F209"/>
-    <mergeCell ref="B2968:F2968"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B2234:F2234"/>
     <mergeCell ref="B537:F537"/>
@@ -52394,13 +52123,11 @@
     <mergeCell ref="B509:F509"/>
     <mergeCell ref="B1264:F1264"/>
     <mergeCell ref="B1902:F1902"/>
-    <mergeCell ref="B2961:F2961"/>
     <mergeCell ref="B1183:F1183"/>
     <mergeCell ref="B2534:F2534"/>
     <mergeCell ref="B1475:F1475"/>
     <mergeCell ref="B2665:F2665"/>
     <mergeCell ref="B1595:F1595"/>
-    <mergeCell ref="B2963:F2963"/>
     <mergeCell ref="B2648:F2648"/>
     <mergeCell ref="B538:F538"/>
     <mergeCell ref="B1176:F1176"/>
@@ -52466,7 +52193,6 @@
     <mergeCell ref="B635:F635"/>
     <mergeCell ref="A2506:F2506"/>
     <mergeCell ref="B935:F935"/>
-    <mergeCell ref="A2956:F2956"/>
     <mergeCell ref="B2749:F2749"/>
     <mergeCell ref="B2021:F2021"/>
     <mergeCell ref="B962:F962"/>
@@ -52482,7 +52208,6 @@
     <mergeCell ref="B2661:F2661"/>
     <mergeCell ref="B2321:F2321"/>
     <mergeCell ref="B1262:F1262"/>
-    <mergeCell ref="B2959:F2959"/>
     <mergeCell ref="B2619:F2619"/>
     <mergeCell ref="B534:F534"/>
     <mergeCell ref="B805:F805"/>
@@ -53014,11 +52739,9 @@
     <mergeCell ref="B1173:F1173"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B1934:F1934"/>
-    <mergeCell ref="B2960:F2960"/>
     <mergeCell ref="B2357:F2357"/>
     <mergeCell ref="B1602:F1602"/>
     <mergeCell ref="B203:F203"/>
-    <mergeCell ref="B2962:F2962"/>
     <mergeCell ref="B1930:F1930"/>
     <mergeCell ref="B1175:F1175"/>
     <mergeCell ref="B860:F860"/>
@@ -53173,7 +52896,6 @@
     <mergeCell ref="B726:F726"/>
     <mergeCell ref="B2094:F2094"/>
     <mergeCell ref="B2811:F2811"/>
-    <mergeCell ref="B2969:F2969"/>
     <mergeCell ref="B1060:F1060"/>
     <mergeCell ref="B299:F299"/>
     <mergeCell ref="B274:F274"/>
@@ -53982,7 +53704,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2924" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2939" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2954" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2969" r:id="rId198"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53994,7 +53715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J199"/>
+  <dimension ref="A1:J198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -56576,12 +56297,12 @@
     <row r="80" ht="28" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>31127</t>
+          <t>411234ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/</t>
+          <t>Hydrogen cities</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr"/>
@@ -56608,12 +56329,12 @@
     <row r="81" ht="28" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>96629</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>The intended technological “The intended technological scope</t>
+          <t>Under LIFE-2023-CET-HEATPUMPS, can alternative business and/</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr"/>
@@ -56640,19 +56361,15 @@
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>INNOVFUND</t>
+          <t>96629</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Absorption Heat Pump for waste steam from a WtE plant to pre</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Innovation Fund</t>
-        </is>
-      </c>
+          <t>The intended technological “The intended technological scope</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr"/>
       <c r="D82" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -56676,15 +56393,19 @@
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>INNOVFUND</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>The intended technological scope of Tasks 2 and 3 is unclear</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr"/>
+          <t>Absorption Heat Pump for waste steam from a WtE plant to pre</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Innovation Fund</t>
+        </is>
+      </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -56708,12 +56429,12 @@
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>96375</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover</t>
+          <t>The intended technological scope of Tasks 2 and 3 is unclear</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr"/>
@@ -56740,12 +56461,12 @@
     <row r="85" ht="28" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>52786</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Roadmap for updating Territorial just transition plans</t>
+          <t>Under call IMREG-2024-INFOME, are proposals obliged to cover</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr"/>
@@ -56772,12 +56493,12 @@
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>ESF</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Social City Fund to foster just transition in the City of </t>
+          <t>Roadmap for updating Territorial just transition plans</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr"/>
@@ -56804,12 +56525,12 @@
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>IMREG</t>
+          <t>ESF</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>HOTSTOP-Young people discover the Cohesion Policy and act ag</t>
+          <t xml:space="preserve">A Social City Fund to foster just transition in the City of </t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr"/>
@@ -56836,12 +56557,12 @@
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>897315282</t>
+          <t>IMREG</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Social Innovation Fund</t>
+          <t>HOTSTOP-Young people discover the Cohesion Policy and act ag</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr"/>
@@ -56868,19 +56589,15 @@
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>897315282</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Social Innovation Fund</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr"/>
       <c r="D89" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -56889,7 +56606,7 @@
       <c r="E89" s="6" t="inlineStr"/>
       <c r="F89" s="25" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr"/>
@@ -56904,15 +56621,19 @@
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neu</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -56936,12 +56657,12 @@
     <row r="91" ht="28" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficien</t>
+          <t>Circular design for bio-based innovation towards climate-neu</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr"/>
@@ -56968,12 +56689,12 @@
     <row r="92" ht="28" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should </t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficien</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr"/>
@@ -57000,19 +56721,15 @@
     <row r="93" ht="28" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should </t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr"/>
       <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -57036,15 +56753,19 @@
     <row r="94" ht="28" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from severa</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr"/>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -57068,12 +56789,12 @@
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from severa</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr"/>
@@ -57100,12 +56821,12 @@
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission tr</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr"/>
@@ -57132,12 +56853,12 @@
     <row r="97" ht="28" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission tr</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr"/>
@@ -57164,12 +56885,12 @@
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr"/>
@@ -57196,12 +56917,12 @@
     <row r="99" ht="28" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKT</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr"/>
@@ -57228,12 +56949,12 @@
     <row r="100" ht="28" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKT</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr"/>
@@ -57260,12 +56981,12 @@
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr"/>
@@ -57292,12 +57013,12 @@
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr"/>
@@ -57324,12 +57045,12 @@
     <row r="103" ht="28" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr"/>
@@ -57356,12 +57077,12 @@
     <row r="104" ht="28" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic L</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr"/>
@@ -57388,12 +57109,12 @@
     <row r="105" ht="28" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic L</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr"/>
@@ -57420,12 +57141,12 @@
     <row r="106" ht="28" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr"/>
@@ -57452,12 +57173,12 @@
     <row r="107" ht="28" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr"/>
@@ -57484,12 +57205,12 @@
     <row r="108" ht="28" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr"/>
@@ -57516,12 +57237,12 @@
     <row r="109" ht="28" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restorati</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr"/>
@@ -57548,12 +57269,12 @@
     <row r="110" ht="28" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Considering the increasing importance of ecosystem restorati</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr"/>
@@ -57580,12 +57301,12 @@
     <row r="111" ht="28" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaam</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr"/>
@@ -57612,12 +57333,12 @@
     <row r="112" ht="28" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be on</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaam</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr"/>
@@ -57644,12 +57365,12 @@
     <row r="113" ht="28" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Should the selected port related to the Cities Mission be on</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr"/>
@@ -57676,12 +57397,12 @@
     <row r="114" ht="28" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submi</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr"/>
@@ -57708,12 +57429,12 @@
     <row r="115" ht="28" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submi</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr"/>
@@ -57740,12 +57461,12 @@
     <row r="116" ht="28" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr"/>
@@ -57772,12 +57493,12 @@
     <row r="117" ht="28" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do loca</t>
+          <t>Inter-institutional single framework contract to support the</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr"/>
@@ -57804,12 +57525,12 @@
     <row r="118" ht="28" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do loca</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr"/>
@@ -57836,12 +57557,12 @@
     <row r="119" ht="28" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr"/>
@@ -57868,12 +57589,12 @@
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr"/>
@@ -57900,12 +57621,12 @@
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr"/>
@@ -57932,12 +57653,12 @@
     <row r="122" ht="28" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by F</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr"/>
@@ -57964,12 +57685,12 @@
     <row r="123" ht="28" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by F</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr"/>
@@ -57996,12 +57717,12 @@
     <row r="124" ht="28" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr"/>
@@ -58028,12 +57749,12 @@
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr"/>
@@ -58060,12 +57781,12 @@
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint action</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr"/>
@@ -58092,12 +57813,12 @@
     <row r="127" ht="28" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total bud</t>
+          <t>The topic requires to "include a draft plan for joint action</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr"/>
@@ -58668,12 +58389,12 @@
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>937468917</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUT</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr"/>
@@ -58700,12 +58421,12 @@
     <row r="146" ht="28" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>937468917</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under L</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUT</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr"/>
@@ -58732,12 +58453,12 @@
     <row r="147" ht="28" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>n002cet5</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under L</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr"/>
@@ -58764,12 +58485,12 @@
     <row r="148" ht="28" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>n002cet5</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third count</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr"/>
@@ -58796,12 +58517,12 @@
     <row r="149" ht="28" customHeight="1">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>885233544</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third count</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr"/>
@@ -58828,12 +58549,12 @@
     <row r="150" ht="28" customHeight="1">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>885233544</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, w</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr"/>
@@ -58860,12 +58581,12 @@
     <row r="151" ht="28" customHeight="1">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMAR</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, w</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr"/>
@@ -58892,12 +58613,12 @@
     <row r="152" ht="28" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMAR</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr"/>
@@ -58924,12 +58645,12 @@
     <row r="153" ht="28" customHeight="1">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cool</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr"/>
@@ -58956,12 +58677,12 @@
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a propo</t>
+          <t>Strategies and tools for decarbonising EU's heating and cool</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr"/>
@@ -58988,12 +58709,12 @@
     <row r="155" ht="28" customHeight="1">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a propo</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr"/>
@@ -59020,12 +58741,12 @@
     <row r="156" ht="28" customHeight="1">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is the</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr"/>
@@ -59052,12 +58773,12 @@
     <row r="157" ht="28" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>956926438</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is the</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr"/>
@@ -59084,12 +58805,12 @@
     <row r="158" ht="28" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>953677035</t>
+          <t>956926438</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr"/>
@@ -59116,12 +58837,12 @@
     <row r="159" ht="28" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>953552487</t>
+          <t>953677035</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr"/>
@@ -59148,12 +58869,12 @@
     <row r="160" ht="28" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>953552487</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr"/>
@@ -59180,12 +58901,12 @@
     <row r="161" ht="28" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr"/>
@@ -59212,12 +58933,12 @@
     <row r="162" ht="28" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>876983694</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr"/>
@@ -59244,12 +58965,12 @@
     <row r="163" ht="28" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>876983694</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr"/>
@@ -59276,12 +58997,12 @@
     <row r="164" ht="28" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>935134321</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS S</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr"/>
@@ -59308,12 +59029,12 @@
     <row r="165" ht="28" customHeight="1">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>883154834</t>
+          <t>935134321</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS S</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr"/>
@@ -59340,12 +59061,12 @@
     <row r="166" ht="28" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>883154834</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Could the Contracting Authority clarify the scope of the </t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr"/>
@@ -59372,12 +59093,12 @@
     <row r="167" ht="28" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics u</t>
+          <t xml:space="preserve">1. Could the Contracting Authority clarify the scope of the </t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr"/>
@@ -59404,12 +59125,12 @@
     <row r="168" ht="28" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>Climate resilience of European coastal cities and settlement</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics u</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr"/>
@@ -60108,12 +59829,12 @@
     <row r="190" ht="28" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>EUS-16189</t>
+          <t>EUS-71228</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Servicio de asistencia técnica para la redacción de un Plan </t>
+          <t>Servicio de conservación y mantenimiento de las zonas verdes</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
@@ -60144,7 +59865,7 @@
     <row r="191" ht="28" customHeight="1">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>EUS-65237</t>
+          <t>EUS-36680</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
@@ -60180,12 +59901,12 @@
     <row r="192" ht="28" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>EUS-01883</t>
+          <t>EUS-57715</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Renovación del sistema de climatización del centro de formac</t>
+          <t>Servicio de implementación de un programa de incentivos a la</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
@@ -60216,12 +59937,12 @@
     <row r="193" ht="28" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>EUS-30957</t>
+          <t>EUS-03003</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>vinilado coches funicular tras rehabilitacion</t>
+          <t>Subvenciones para la organización, digitalización y difusión</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
@@ -60237,7 +59958,7 @@
       <c r="E193" s="6" t="inlineStr"/>
       <c r="F193" s="25" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="G193" s="6" t="inlineStr"/>
@@ -60252,12 +59973,12 @@
     <row r="194" ht="28" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>EUS-19215</t>
+          <t>EUS-89928</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Subvenciones para la organización, digitalización y difusión</t>
+          <t>Subvenciones para la ejecución de trabajos orientados al ámb</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
@@ -60288,12 +60009,12 @@
     <row r="195" ht="28" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>EUS-95140</t>
+          <t>EUS-14280</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>Subvenciones para la ejecución de trabajos orientados al ámb</t>
+          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -60324,12 +60045,12 @@
     <row r="196" ht="28" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>EUS-60062</t>
+          <t>EUS-05836</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado</t>
+          <t>Dirección facultativa de las obras de reverdecimiento del Ca</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -60360,12 +60081,12 @@
     <row r="197" ht="28" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>EUS-30850</t>
+          <t>EUS-20008</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratación del suministro de un total de 590 contenedores </t>
+          <t xml:space="preserve">Suministro de equipamiento e instalación de Parque Infantil </t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -60396,12 +60117,12 @@
     <row r="198" ht="28" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>EUS-00649</t>
+          <t>EUS-26417</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Contratación de la ejecución de cubierta del centro de visit</t>
+          <t>Recogida, grabación y tratamiento básico de la información d</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
@@ -60429,44 +60150,8 @@
       <c r="I198" s="6" t="inlineStr"/>
       <c r="J198" s="6" t="inlineStr"/>
     </row>
-    <row r="199" ht="28" customHeight="1">
-      <c r="A199" s="6" t="inlineStr">
-        <is>
-          <t>EUS-60669</t>
-        </is>
-      </c>
-      <c r="B199" s="6" t="inlineStr">
-        <is>
-          <t>pegatinas en impresion digital a color</t>
-        </is>
-      </c>
-      <c r="C199" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="D199" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E199" s="6" t="inlineStr"/>
-      <c r="F199" s="25" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="G199" s="6" t="inlineStr"/>
-      <c r="H199" s="6" t="inlineStr">
-        <is>
-          <t>Por revisar</t>
-        </is>
-      </c>
-      <c r="I199" s="6" t="inlineStr"/>
-      <c r="J199" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J199"/>
+  <autoFilter ref="A1:J198"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/resultados_convocatorias.xlsx
+++ b/docs/resultados_convocatorias.xlsx
@@ -685,7 +685,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 22/09/2026 10:27 - 197 convocatorias - 9 nuevas</t>
+          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 23/09/2026 10:23 - 197 convocatorias - 10 nuevas</t>
         </is>
       </c>
     </row>
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr"/>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -5875,12 +5875,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr"/>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="L114" s="6" t="inlineStr"/>
@@ -5922,12 +5922,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr"/>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr"/>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="L116" s="6" t="inlineStr"/>
@@ -6016,12 +6016,12 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr"/>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through th</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6063,12 +6063,12 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr"/>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through th</t>
+          <t xml:space="preserve">Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on </t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr"/>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr"/>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on </t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6157,12 +6157,12 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr"/>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr"/>
@@ -6204,12 +6204,12 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr"/>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6251,12 +6251,12 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr"/>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="L122" s="6" t="inlineStr"/>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr"/>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="L124" s="6" t="inlineStr"/>
@@ -6392,12 +6392,12 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr"/>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Respon</t>
         </is>
       </c>
       <c r="L126" s="6" t="inlineStr"/>
@@ -6486,12 +6486,12 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr"/>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Respon</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr"/>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="L128" s="6" t="inlineStr"/>
@@ -6580,12 +6580,12 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr"/>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t xml:space="preserve">The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered </t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6627,12 +6627,12 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr"/>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered </t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage propo</t>
         </is>
       </c>
       <c r="L130" s="6" t="inlineStr"/>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>PPPA2027</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr"/>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage propo</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -6721,12 +6721,12 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>PPPA2027</t>
+          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>Border regions Peer exchange on solving border obstacles</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr"/>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>Border regions Peer exchange on solving border obstacles</t>
         </is>
       </c>
       <c r="L132" s="6" t="inlineStr"/>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
+          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
+          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Border regions Peer exchange on solving border obstacles</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr"/>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>Border regions Peer exchange on solving border obstacles</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="L134" s="6" t="inlineStr"/>
@@ -6862,12 +6862,12 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>886623263</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr"/>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -6909,12 +6909,12 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>886623263</t>
+          <t>877314852</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr"/>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="L136" s="6" t="inlineStr"/>
@@ -6956,12 +6956,12 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>877314852</t>
+          <t>884174595</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr"/>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7003,12 +7003,12 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>884174595</t>
+          <t>900546740</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr"/>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr"/>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>900546740</t>
+          <t>941945952</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7097,12 +7097,12 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>941945952</t>
+          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr"/>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr"/>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>ERDFTA</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7191,12 +7191,12 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>ERDFTA</t>
+          <t>90488</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr"/>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="K142" s="6" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)</t>
         </is>
       </c>
       <c r="L142" s="6" t="inlineStr"/>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
+          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr"/>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)</t>
+          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7285,12 +7285,12 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
+          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr"/>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K144" s="6" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
+          <t xml:space="preserve">A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance </t>
         </is>
       </c>
       <c r="L144" s="6" t="inlineStr"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>n00brugy</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
+          <t>Joana SANTIAGO</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr"/>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="K146" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance </t>
+          <t>Joana SANTIAGO</t>
         </is>
       </c>
       <c r="L146" s="6" t="inlineStr"/>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>n00brugy</t>
+          <t>n00kmonh</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Joana SANTIAGO</t>
+          <t>Mrs LARA MARIA CERDAN AZNAR</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr"/>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>Joana SANTIAGO</t>
+          <t>Mrs LARA MARIA CERDAN AZNAR</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>n00kmonh</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>Mrs LARA MARIA CERDAN AZNAR</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr"/>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="K148" s="6" t="inlineStr">
         <is>
-          <t>Mrs LARA MARIA CERDAN AZNAR</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="L148" s="6" t="inlineStr"/>
@@ -7520,12 +7520,12 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>937468917</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>MS Elena Jauregui Baldassini</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>MS Elena Jauregui Baldassini</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>937468917</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="K150" s="6" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a sing</t>
         </is>
       </c>
       <c r="L150" s="6" t="inlineStr"/>
@@ -7614,12 +7614,12 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>n002cet5</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a sing</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -7661,12 +7661,12 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>n002cet5</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr"/>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="K152" s="6" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="L152" s="6" t="inlineStr"/>
@@ -7708,12 +7708,12 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>885233544</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr"/>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -7755,12 +7755,12 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>885233544</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr"/>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="K154" s="6" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="L154" s="6" t="inlineStr"/>
@@ -7802,12 +7802,12 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr"/>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr"/>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="K156" s="6" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we si</t>
         </is>
       </c>
       <c r="L156" s="6" t="inlineStr"/>
@@ -7896,12 +7896,12 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr"/>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we si</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technolog</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -7943,12 +7943,12 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr"/>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="K158" s="6" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technolog</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="L158" s="6" t="inlineStr"/>
@@ -7990,12 +7990,12 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr"/>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr"/>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="K160" s="6" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="L160" s="6" t="inlineStr"/>
@@ -8084,12 +8084,12 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>956926438</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr"/>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8131,12 +8131,12 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>956926438</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr"/>
@@ -8160,7 +8160,7 @@
       </c>
       <c r="K162" s="6" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="L162" s="6" t="inlineStr"/>
@@ -8225,12 +8225,12 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>953552487</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="L164" s="6" t="inlineStr"/>
@@ -8272,12 +8272,12 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8319,12 +8319,12 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>876983694</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr"/>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="K166" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="L166" s="6" t="inlineStr"/>
@@ -8366,12 +8366,12 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>876983694</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr"/>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infra</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8413,12 +8413,12 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>935134321</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr"/>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="K168" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infra</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="L168" s="6" t="inlineStr"/>
@@ -8460,12 +8460,12 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>935134321</t>
+          <t>883154834</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8507,12 +8507,12 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>883154834</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr"/>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="K170" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and</t>
         </is>
       </c>
       <c r="L170" s="6" t="inlineStr"/>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr"/>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>91523</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>In relation to the selection criteria concerning experience in “Global Gateway related projects: sustainable investment, energy transition, communication and visibility, digitalization”, we kindly request clarification regarding the interpretation of the term “sustainable investment”. Could you please clarify which typologies of projects/reference</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K172" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>In relation to the selection criteria concerning experience in “Global Gateway related projects: sustainable investment, energy transition, communication and visibility, digitalization”, we kindly req</t>
         </is>
       </c>
       <c r="L172" s="6" t="inlineStr"/>
@@ -8648,12 +8648,12 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>91523</t>
+          <t>71674</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>In relation to the selection criteria concerning experience in “Global Gateway related projects: sustainable investment, energy transition, communication and visibility, digitalization”, we kindly request clarification regarding the interpretation of the term “sustainable investment”. Could you please clarify which typologies of projects/reference</t>
+          <t>Can funding from the European Regional Development Fund (ERDF) be used as co-financing?</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr"/>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>In relation to the selection criteria concerning experience in “Global Gateway related projects: sustainable investment, energy transition, communication and visibility, digitalization”, we kindly req</t>
+          <t>Can funding from the European Regional Development Fund (ERDF) be used as co-financing?</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>71674</t>
+          <t>60394</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>60394</t>
+          <t>885683915</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>Can funding from the European Regional Development Fund (ERDF) be used as co-financing?</t>
+          <t>SOCIAL FINANCE ASSOCIATION - ASOCIATIA PENTRU FINANTARE SOCIALA</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr"/>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>Can funding from the European Regional Development Fund (ERDF) be used as co-financing?</t>
+          <t>SOCIAL FINANCE ASSOCIATION - ASOCIATIA PENTRU FINANTARE SOCIALA</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>885683915</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>SOCIAL FINANCE ASSOCIATION - ASOCIATIA PENTRU FINANTARE SOCIALA</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr"/>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>SOCIAL FINANCE ASSOCIATION - ASOCIATIA PENTRU FINANTARE SOCIALA</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
         </is>
       </c>
       <c r="L176" s="6" t="inlineStr"/>
@@ -8836,12 +8836,12 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>41082</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
+          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr"/>
@@ -8865,7 +8865,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
+          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -8883,12 +8883,12 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>85779</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr"/>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="K178" s="6" t="inlineStr">
         <is>
-          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="L178" s="6" t="inlineStr"/>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>85779</t>
+          <t>85495</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -8977,12 +8977,12 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>85495</t>
+          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr"/>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="K180" s="6" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
         </is>
       </c>
       <c r="L180" s="6" t="inlineStr"/>
@@ -9024,12 +9024,12 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
+          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr"/>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
+          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9071,12 +9071,12 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>104241</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
+          <t>HuMUS Soil Stewards training programme</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr"/>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="K182" s="6" t="inlineStr">
         <is>
-          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
+          <t>HuMUS Soil Stewards training programme The HuMUS Soil Steward Training Programme is an online capacity-building course designed to strengthen knowledge and practical skills related to soil health, par</t>
         </is>
       </c>
       <c r="L182" s="6" t="inlineStr"/>
@@ -9118,12 +9118,12 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>913756976</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>HuMUS Soil Stewards training programme</t>
+          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>HuMUS Soil Stewards training programme The HuMUS Soil Steward Training Programme is an online capacity-building course designed to strengthen knowledge and practical skills related to soil health, par</t>
+          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>913756976</t>
+          <t>880759128</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
+          <t>AYUNTAMIENTO DE FORUA</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr"/>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="K184" s="6" t="inlineStr">
         <is>
-          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
+          <t>AYUNTAMIENTO DE FORUA</t>
         </is>
       </c>
       <c r="L184" s="6" t="inlineStr"/>
@@ -9212,12 +9212,12 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>880759128</t>
+          <t>76912</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE FORUA</t>
+          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr"/>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE FORUA</t>
+          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9259,12 +9259,12 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>76912</t>
+          <t>77665</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
+          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr"/>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="K186" s="6" t="inlineStr">
         <is>
-          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
+          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or</t>
         </is>
       </c>
       <c r="L186" s="6" t="inlineStr"/>
@@ -9306,12 +9306,12 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>77665</t>
+          <t>886088211</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
+          <t>Non Architecture s.r.l.</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or</t>
+          <t>Non Architecture s.r.l.</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9353,12 +9353,12 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>886088211</t>
+          <t>871698261</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>Non Architecture s.r.l.</t>
+          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr"/>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="K188" s="6" t="inlineStr">
         <is>
-          <t>Non Architecture s.r.l.</t>
+          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
         </is>
       </c>
       <c r="L188" s="6" t="inlineStr"/>
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>871698261</t>
+          <t>918605133</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
+          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr"/>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
+          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9447,12 +9447,12 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>918605133</t>
+          <t>485</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
+          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr"/>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="K190" s="6" t="inlineStr">
         <is>
-          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
+          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
         </is>
       </c>
       <c r="L190" s="6" t="inlineStr"/>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>892931076</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr"/>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9541,12 +9541,12 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>892931076</t>
+          <t>936518123</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr"/>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="K192" s="6" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="L192" s="6" t="inlineStr"/>
@@ -9580,57 +9580,65 @@
         </is>
       </c>
     </row>
-    <row r="193" ht="40" customHeight="1">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="B193" s="6" t="inlineStr">
-        <is>
-          <t>936518123</t>
-        </is>
-      </c>
-      <c r="C193" s="6" t="inlineStr">
-        <is>
-          <t>Urban Initiative</t>
-        </is>
-      </c>
-      <c r="D193" s="6" t="inlineStr"/>
-      <c r="E193" s="10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F193" s="6" t="inlineStr"/>
-      <c r="G193" s="6" t="inlineStr"/>
-      <c r="H193" s="6" t="inlineStr"/>
-      <c r="I193" s="10" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="J193" s="6" t="inlineStr">
-        <is>
-          <t>Revisar relevancia para el Ayuntamiento de Bilbao.</t>
-        </is>
-      </c>
-      <c r="K193" s="6" t="inlineStr">
-        <is>
-          <t>Urban Initiative</t>
-        </is>
-      </c>
-      <c r="L193" s="6" t="inlineStr"/>
-      <c r="M193" s="9" t="inlineStr">
+    <row r="193" ht="28" customHeight="1">
+      <c r="A193" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>EUS-79710</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>Mantenimiento y soporte de la infraestructura hardware y software de los sistemas IBM del Ayuntamiento de Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr"/>
+      <c r="G194" s="6" t="inlineStr"/>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I194" s="11" t="inlineStr">
+        <is>
+          <t>MUY ALTA</t>
+        </is>
+      </c>
+      <c r="J194" s="6" t="inlineStr"/>
+      <c r="K194" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L194" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M194" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="28" customHeight="1">
-      <c r="A194" s="13" t="inlineStr">
-        <is>
-          <t>🟢 Euskadi</t>
         </is>
       </c>
     </row>
@@ -9642,12 +9650,12 @@
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>EUS-71228</t>
+          <t>EUS-98457</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>Servicio de conservación y mantenimiento de las zonas verdes municipales (arbustos y setos, jardineras, siega de caminos, arbolado y taludes) del municipio de Basauri.</t>
+          <t>Suministro de licencias de uso de una plataforma digital para la aplicación, corrección y generación de informes automatizados de test psicotécnicos, orientados a los procesos de selección de personal</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
@@ -9697,12 +9705,12 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>EUS-36680</t>
+          <t>EUS-10114</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfronterizos de energía renovable. Se prevé una nueva convocatoria para noviembre de 2026.</t>
+          <t>Servicio de recogida y gestión de ropa usada, otros textiles y objetos reutilizables de pequeño tamaño en los municipios de Urola Kosta. Contratación reservada (Disposición Adicional 4ª LCSP)</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
@@ -9719,12 +9727,12 @@
       <c r="G196" s="6" t="inlineStr"/>
       <c r="H196" s="6" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
-        </is>
-      </c>
-      <c r="I196" s="8" t="inlineStr">
-        <is>
-          <t>ALTA</t>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I196" s="11" t="inlineStr">
+        <is>
+          <t>MUY ALTA</t>
         </is>
       </c>
       <c r="J196" s="6" t="inlineStr"/>
@@ -9752,12 +9760,12 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>EUS-57715</t>
+          <t>EUS-47702</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>Servicio de implementación de un programa de incentivos a la movilidad sostenible mediante la plataforma de Ciclogreen</t>
+          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfronterizos de energía renovable. Se prevé una nueva convocatoria para noviembre de 2026.</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
@@ -9774,7 +9782,7 @@
       <c r="G197" s="6" t="inlineStr"/>
       <c r="H197" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="I197" s="8" t="inlineStr">
@@ -9807,7 +9815,7 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>EUS-03003</t>
+          <t>EUS-35735</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
@@ -9862,7 +9870,7 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>EUS-89928</t>
+          <t>EUS-91770</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
@@ -9917,12 +9925,12 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>EUS-14280</t>
+          <t>EUS-78388</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado una Alianza para las Cadenas de Valor Industriales Marítimas, que contempla la soberanía tecnológica y de suministros, la defensa, la compe</t>
+          <t>Renovación del alumbrado</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
@@ -9939,7 +9947,7 @@
       <c r="G200" s="6" t="inlineStr"/>
       <c r="H200" s="6" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="I200" s="12" t="inlineStr">
@@ -9972,12 +9980,12 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>EUS-05836</t>
+          <t>EUS-89916</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>Dirección facultativa de las obras de reverdecimiento del Cantón de Anorbin en el marco del Proyecto LIFE I P URBAN KLIMA 2050 (life18 IPC/ES/000001)</t>
+          <t>Arrendamiento de la vivienda municipal sita en INtxaurtxueta 26-2º derecha</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
@@ -10027,12 +10035,12 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>EUS-20008</t>
+          <t>EUS-00652</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>Suministro de equipamiento e instalación de Parque Infantil en Bedia</t>
+          <t>Obras de reverdecimiento del casco medieval de Vitoria-Gasteiz. Proyecto LIFE I P Urban Klima 2050 (LIFE18 IPC/ES/000001) - Proyecto de ejecución cantón Anorbin.</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
@@ -10082,12 +10090,12 @@
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>EUS-26417</t>
+          <t>EUS-83587</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>Recogida, grabación y tratamiento básico de la información de la operación continua ?Encuesta de población en relación con la actividad (PRA)? y sus módulos ?Encuesta sobre la sociedad de la informaci</t>
+          <t>Material de construcción para prácticas de 1º de mantenimiento de viviendas del imfpb de eibar.</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
@@ -10132,7 +10140,7 @@
   </sheetData>
   <autoFilter ref="A4:M203"/>
   <mergeCells count="4">
-    <mergeCell ref="A194:M194"/>
+    <mergeCell ref="A193:M193"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
@@ -10325,7 +10333,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId191"/>
@@ -32280,7 +32288,7 @@
     <row r="1606" ht="30" customHeight="1">
       <c r="A1606" s="16" t="inlineStr">
         <is>
-          <t>FICHA 108: 917155468</t>
+          <t>FICHA 108: 95942</t>
         </is>
       </c>
       <c r="B1606" s="17" t="n"/>
@@ -32305,7 +32313,7 @@
       <c r="E1607" s="20" t="n"/>
       <c r="F1607" s="20" t="n"/>
     </row>
-    <row r="1608" ht="20" customHeight="1">
+    <row r="1608" ht="45" customHeight="1">
       <c r="A1608" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -32313,7 +32321,7 @@
       </c>
       <c r="B1608" s="19" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="C1608" s="20" t="n"/>
@@ -32329,7 +32337,7 @@
       </c>
       <c r="B1609" s="19" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="C1609" s="20" t="n"/>
@@ -32421,7 +32429,7 @@
       <c r="E1615" s="20" t="n"/>
       <c r="F1615" s="20" t="n"/>
     </row>
-    <row r="1616" ht="20" customHeight="1">
+    <row r="1616" ht="45" customHeight="1">
       <c r="A1616" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -32429,7 +32437,7 @@
       </c>
       <c r="B1616" s="19" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="C1616" s="20" t="n"/>
@@ -32473,7 +32481,7 @@
       </c>
       <c r="B1619" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917155468</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95942</t>
         </is>
       </c>
       <c r="C1619" s="20" t="n"/>
@@ -32484,7 +32492,7 @@
     <row r="1621" ht="30" customHeight="1">
       <c r="A1621" s="16" t="inlineStr">
         <is>
-          <t>FICHA 109: 95942</t>
+          <t>FICHA 109: 898575215</t>
         </is>
       </c>
       <c r="B1621" s="17" t="n"/>
@@ -32509,7 +32517,7 @@
       <c r="E1622" s="20" t="n"/>
       <c r="F1622" s="20" t="n"/>
     </row>
-    <row r="1623" ht="45" customHeight="1">
+    <row r="1623" ht="20" customHeight="1">
       <c r="A1623" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -32517,7 +32525,7 @@
       </c>
       <c r="B1623" s="19" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C1623" s="20" t="n"/>
@@ -32533,7 +32541,7 @@
       </c>
       <c r="B1624" s="19" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="C1624" s="20" t="n"/>
@@ -32625,7 +32633,7 @@
       <c r="E1630" s="20" t="n"/>
       <c r="F1630" s="20" t="n"/>
     </row>
-    <row r="1631" ht="45" customHeight="1">
+    <row r="1631" ht="20" customHeight="1">
       <c r="A1631" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -32633,7 +32641,7 @@
       </c>
       <c r="B1631" s="19" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C1631" s="20" t="n"/>
@@ -32677,7 +32685,7 @@
       </c>
       <c r="B1634" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95942</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/898575215</t>
         </is>
       </c>
       <c r="C1634" s="20" t="n"/>
@@ -32688,7 +32696,7 @@
     <row r="1636" ht="30" customHeight="1">
       <c r="A1636" s="16" t="inlineStr">
         <is>
-          <t>FICHA 110: 898575215</t>
+          <t>FICHA 110: 97556</t>
         </is>
       </c>
       <c r="B1636" s="17" t="n"/>
@@ -32713,7 +32721,7 @@
       <c r="E1637" s="20" t="n"/>
       <c r="F1637" s="20" t="n"/>
     </row>
-    <row r="1638" ht="20" customHeight="1">
+    <row r="1638" ht="45" customHeight="1">
       <c r="A1638" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -32721,7 +32729,7 @@
       </c>
       <c r="B1638" s="19" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="C1638" s="20" t="n"/>
@@ -32737,7 +32745,7 @@
       </c>
       <c r="B1639" s="19" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="C1639" s="20" t="n"/>
@@ -32829,7 +32837,7 @@
       <c r="E1645" s="20" t="n"/>
       <c r="F1645" s="20" t="n"/>
     </row>
-    <row r="1646" ht="20" customHeight="1">
+    <row r="1646" ht="45" customHeight="1">
       <c r="A1646" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -32837,7 +32845,7 @@
       </c>
       <c r="B1646" s="19" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="C1646" s="20" t="n"/>
@@ -32881,7 +32889,7 @@
       </c>
       <c r="B1649" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/898575215</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/97556</t>
         </is>
       </c>
       <c r="C1649" s="20" t="n"/>
@@ -32892,7 +32900,7 @@
     <row r="1651" ht="30" customHeight="1">
       <c r="A1651" s="16" t="inlineStr">
         <is>
-          <t>FICHA 111: 97556</t>
+          <t>FICHA 111: 73618</t>
         </is>
       </c>
       <c r="B1651" s="17" t="n"/>
@@ -32925,7 +32933,7 @@
       </c>
       <c r="B1653" s="19" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="C1653" s="20" t="n"/>
@@ -32941,7 +32949,7 @@
       </c>
       <c r="B1654" s="19" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="C1654" s="20" t="n"/>
@@ -33041,7 +33049,7 @@
       </c>
       <c r="B1661" s="19" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="C1661" s="20" t="n"/>
@@ -33085,7 +33093,7 @@
       </c>
       <c r="B1664" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/97556</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/73618</t>
         </is>
       </c>
       <c r="C1664" s="20" t="n"/>
@@ -33096,7 +33104,7 @@
     <row r="1666" ht="30" customHeight="1">
       <c r="A1666" s="16" t="inlineStr">
         <is>
-          <t>FICHA 112: 73618</t>
+          <t>FICHA 112: 83951</t>
         </is>
       </c>
       <c r="B1666" s="17" t="n"/>
@@ -33121,7 +33129,7 @@
       <c r="E1667" s="20" t="n"/>
       <c r="F1667" s="20" t="n"/>
     </row>
-    <row r="1668" ht="45" customHeight="1">
+    <row r="1668" ht="20" customHeight="1">
       <c r="A1668" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33129,7 +33137,7 @@
       </c>
       <c r="B1668" s="19" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="C1668" s="20" t="n"/>
@@ -33145,7 +33153,7 @@
       </c>
       <c r="B1669" s="19" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="C1669" s="20" t="n"/>
@@ -33245,7 +33253,7 @@
       </c>
       <c r="B1676" s="19" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through the literature reviews, questionnaires, surveys and expert opinions in order to provide key recommendations on how EIT Food can make a distinctive a</t>
         </is>
       </c>
       <c r="C1676" s="20" t="n"/>
@@ -33289,7 +33297,7 @@
       </c>
       <c r="B1679" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/73618</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/83951</t>
         </is>
       </c>
       <c r="C1679" s="20" t="n"/>
@@ -33300,7 +33308,7 @@
     <row r="1681" ht="30" customHeight="1">
       <c r="A1681" s="16" t="inlineStr">
         <is>
-          <t>FICHA 113: 83951</t>
+          <t>FICHA 113: 54353</t>
         </is>
       </c>
       <c r="B1681" s="17" t="n"/>
@@ -33325,7 +33333,7 @@
       <c r="E1682" s="20" t="n"/>
       <c r="F1682" s="20" t="n"/>
     </row>
-    <row r="1683" ht="20" customHeight="1">
+    <row r="1683" ht="45" customHeight="1">
       <c r="A1683" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33333,7 +33341,7 @@
       </c>
       <c r="B1683" s="19" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="C1683" s="20" t="n"/>
@@ -33349,7 +33357,7 @@
       </c>
       <c r="B1684" s="19" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="C1684" s="20" t="n"/>
@@ -33449,7 +33457,7 @@
       </c>
       <c r="B1691" s="19" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through the literature reviews, questionnaires, surveys and expert opinions in order to provide key recommendations on how EIT Food can make a distinctive a</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="C1691" s="20" t="n"/>
@@ -33493,7 +33501,7 @@
       </c>
       <c r="B1694" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/83951</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/54353</t>
         </is>
       </c>
       <c r="C1694" s="20" t="n"/>
@@ -33504,7 +33512,7 @@
     <row r="1696" ht="30" customHeight="1">
       <c r="A1696" s="16" t="inlineStr">
         <is>
-          <t>FICHA 114: 54353</t>
+          <t>FICHA 114: 880954583</t>
         </is>
       </c>
       <c r="B1696" s="17" t="n"/>
@@ -33529,7 +33537,7 @@
       <c r="E1697" s="20" t="n"/>
       <c r="F1697" s="20" t="n"/>
     </row>
-    <row r="1698" ht="45" customHeight="1">
+    <row r="1698" ht="20" customHeight="1">
       <c r="A1698" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33537,7 +33545,7 @@
       </c>
       <c r="B1698" s="19" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C1698" s="20" t="n"/>
@@ -33553,7 +33561,7 @@
       </c>
       <c r="B1699" s="19" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="C1699" s="20" t="n"/>
@@ -33645,7 +33653,7 @@
       <c r="E1705" s="20" t="n"/>
       <c r="F1705" s="20" t="n"/>
     </row>
-    <row r="1706" ht="45" customHeight="1">
+    <row r="1706" ht="20" customHeight="1">
       <c r="A1706" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -33653,7 +33661,7 @@
       </c>
       <c r="B1706" s="19" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C1706" s="20" t="n"/>
@@ -33697,7 +33705,7 @@
       </c>
       <c r="B1709" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/54353</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880954583</t>
         </is>
       </c>
       <c r="C1709" s="20" t="n"/>
@@ -33708,7 +33716,7 @@
     <row r="1711" ht="30" customHeight="1">
       <c r="A1711" s="16" t="inlineStr">
         <is>
-          <t>FICHA 115: 880954583</t>
+          <t>FICHA 115: c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="B1711" s="17" t="n"/>
@@ -33733,7 +33741,7 @@
       <c r="E1712" s="20" t="n"/>
       <c r="F1712" s="20" t="n"/>
     </row>
-    <row r="1713" ht="20" customHeight="1">
+    <row r="1713" ht="45" customHeight="1">
       <c r="A1713" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33741,7 +33749,7 @@
       </c>
       <c r="B1713" s="19" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="C1713" s="20" t="n"/>
@@ -33757,7 +33765,7 @@
       </c>
       <c r="B1714" s="19" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C1714" s="20" t="n"/>
@@ -33843,13 +33851,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1720" s="19" t="inlineStr"/>
+      <c r="B1720" s="19" t="inlineStr">
+        <is>
+          <t>CINEA/2026/OP/0011-PIN</t>
+        </is>
+      </c>
       <c r="C1720" s="20" t="n"/>
       <c r="D1720" s="20" t="n"/>
       <c r="E1720" s="20" t="n"/>
       <c r="F1720" s="20" t="n"/>
     </row>
-    <row r="1721" ht="20" customHeight="1">
+    <row r="1721" ht="45" customHeight="1">
       <c r="A1721" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -33857,7 +33869,7 @@
       </c>
       <c r="B1721" s="19" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="C1721" s="20" t="n"/>
@@ -33901,7 +33913,7 @@
       </c>
       <c r="B1724" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880954583</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C1724" s="20" t="n"/>
@@ -33912,7 +33924,7 @@
     <row r="1726" ht="30" customHeight="1">
       <c r="A1726" s="16" t="inlineStr">
         <is>
-          <t>FICHA 116: c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>FICHA 116: 30901</t>
         </is>
       </c>
       <c r="B1726" s="17" t="n"/>
@@ -33945,7 +33957,7 @@
       </c>
       <c r="B1728" s="19" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="C1728" s="20" t="n"/>
@@ -33961,7 +33973,7 @@
       </c>
       <c r="B1729" s="19" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="C1729" s="20" t="n"/>
@@ -34047,11 +34059,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1735" s="19" t="inlineStr">
-        <is>
-          <t>CINEA/2026/OP/0011-PIN</t>
-        </is>
-      </c>
+      <c r="B1735" s="19" t="inlineStr"/>
       <c r="C1735" s="20" t="n"/>
       <c r="D1735" s="20" t="n"/>
       <c r="E1735" s="20" t="n"/>
@@ -34065,7 +34073,7 @@
       </c>
       <c r="B1736" s="19" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="C1736" s="20" t="n"/>
@@ -34109,7 +34117,7 @@
       </c>
       <c r="B1739" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/30901</t>
         </is>
       </c>
       <c r="C1739" s="20" t="n"/>
@@ -34120,7 +34128,7 @@
     <row r="1741" ht="30" customHeight="1">
       <c r="A1741" s="16" t="inlineStr">
         <is>
-          <t>FICHA 117: 30901</t>
+          <t>FICHA 117: 893516374</t>
         </is>
       </c>
       <c r="B1741" s="17" t="n"/>
@@ -34145,7 +34153,7 @@
       <c r="E1742" s="20" t="n"/>
       <c r="F1742" s="20" t="n"/>
     </row>
-    <row r="1743" ht="45" customHeight="1">
+    <row r="1743" ht="20" customHeight="1">
       <c r="A1743" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -34153,7 +34161,7 @@
       </c>
       <c r="B1743" s="19" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C1743" s="20" t="n"/>
@@ -34169,7 +34177,7 @@
       </c>
       <c r="B1744" s="19" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="C1744" s="20" t="n"/>
@@ -34261,7 +34269,7 @@
       <c r="E1750" s="20" t="n"/>
       <c r="F1750" s="20" t="n"/>
     </row>
-    <row r="1751" ht="45" customHeight="1">
+    <row r="1751" ht="20" customHeight="1">
       <c r="A1751" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -34269,7 +34277,7 @@
       </c>
       <c r="B1751" s="19" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C1751" s="20" t="n"/>
@@ -34313,7 +34321,7 @@
       </c>
       <c r="B1754" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/30901</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/893516374</t>
         </is>
       </c>
       <c r="C1754" s="20" t="n"/>
@@ -34324,7 +34332,7 @@
     <row r="1756" ht="30" customHeight="1">
       <c r="A1756" s="16" t="inlineStr">
         <is>
-          <t>FICHA 118: 893516374</t>
+          <t>FICHA 118: 894079362</t>
         </is>
       </c>
       <c r="B1756" s="17" t="n"/>
@@ -34357,7 +34365,7 @@
       </c>
       <c r="B1758" s="19" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C1758" s="20" t="n"/>
@@ -34373,7 +34381,7 @@
       </c>
       <c r="B1759" s="19" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="C1759" s="20" t="n"/>
@@ -34473,7 +34481,7 @@
       </c>
       <c r="B1766" s="19" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C1766" s="20" t="n"/>
@@ -34517,7 +34525,7 @@
       </c>
       <c r="B1769" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/893516374</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/894079362</t>
         </is>
       </c>
       <c r="C1769" s="20" t="n"/>
@@ -34528,7 +34536,7 @@
     <row r="1771" ht="30" customHeight="1">
       <c r="A1771" s="16" t="inlineStr">
         <is>
-          <t>FICHA 119: 894079362</t>
+          <t>FICHA 119: 867619605</t>
         </is>
       </c>
       <c r="B1771" s="17" t="n"/>
@@ -34561,7 +34569,7 @@
       </c>
       <c r="B1773" s="19" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C1773" s="20" t="n"/>
@@ -34577,7 +34585,7 @@
       </c>
       <c r="B1774" s="19" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="C1774" s="20" t="n"/>
@@ -34677,7 +34685,7 @@
       </c>
       <c r="B1781" s="19" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C1781" s="20" t="n"/>
@@ -34721,7 +34729,7 @@
       </c>
       <c r="B1784" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/894079362</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/867619605</t>
         </is>
       </c>
       <c r="C1784" s="20" t="n"/>
@@ -34732,7 +34740,7 @@
     <row r="1786" ht="30" customHeight="1">
       <c r="A1786" s="16" t="inlineStr">
         <is>
-          <t>FICHA 120: 867619605</t>
+          <t>FICHA 120: ncaviale</t>
         </is>
       </c>
       <c r="B1786" s="17" t="n"/>
@@ -34765,7 +34773,7 @@
       </c>
       <c r="B1788" s="19" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C1788" s="20" t="n"/>
@@ -34781,7 +34789,7 @@
       </c>
       <c r="B1789" s="19" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="C1789" s="20" t="n"/>
@@ -34881,7 +34889,7 @@
       </c>
       <c r="B1796" s="19" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C1796" s="20" t="n"/>
@@ -34925,7 +34933,7 @@
       </c>
       <c r="B1799" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/867619605</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ncaviale</t>
         </is>
       </c>
       <c r="C1799" s="20" t="n"/>
@@ -34936,7 +34944,7 @@
     <row r="1801" ht="30" customHeight="1">
       <c r="A1801" s="16" t="inlineStr">
         <is>
-          <t>FICHA 121: ncaviale</t>
+          <t>FICHA 121: 34537</t>
         </is>
       </c>
       <c r="B1801" s="17" t="n"/>
@@ -34961,7 +34969,7 @@
       <c r="E1802" s="20" t="n"/>
       <c r="F1802" s="20" t="n"/>
     </row>
-    <row r="1803" ht="20" customHeight="1">
+    <row r="1803" ht="45" customHeight="1">
       <c r="A1803" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -34969,7 +34977,7 @@
       </c>
       <c r="B1803" s="19" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="C1803" s="20" t="n"/>
@@ -34985,7 +34993,7 @@
       </c>
       <c r="B1804" s="19" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="C1804" s="20" t="n"/>
@@ -35077,7 +35085,7 @@
       <c r="E1810" s="20" t="n"/>
       <c r="F1810" s="20" t="n"/>
     </row>
-    <row r="1811" ht="20" customHeight="1">
+    <row r="1811" ht="45" customHeight="1">
       <c r="A1811" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -35085,7 +35093,7 @@
       </c>
       <c r="B1811" s="19" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="C1811" s="20" t="n"/>
@@ -35129,7 +35137,7 @@
       </c>
       <c r="B1814" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ncaviale</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/34537</t>
         </is>
       </c>
       <c r="C1814" s="20" t="n"/>
@@ -35140,7 +35148,7 @@
     <row r="1816" ht="30" customHeight="1">
       <c r="A1816" s="16" t="inlineStr">
         <is>
-          <t>FICHA 122: 34537</t>
+          <t>FICHA 122: 906456368</t>
         </is>
       </c>
       <c r="B1816" s="17" t="n"/>
@@ -35165,7 +35173,7 @@
       <c r="E1817" s="20" t="n"/>
       <c r="F1817" s="20" t="n"/>
     </row>
-    <row r="1818" ht="45" customHeight="1">
+    <row r="1818" ht="20" customHeight="1">
       <c r="A1818" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -35173,7 +35181,7 @@
       </c>
       <c r="B1818" s="19" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C1818" s="20" t="n"/>
@@ -35189,7 +35197,7 @@
       </c>
       <c r="B1819" s="19" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="C1819" s="20" t="n"/>
@@ -35281,7 +35289,7 @@
       <c r="E1825" s="20" t="n"/>
       <c r="F1825" s="20" t="n"/>
     </row>
-    <row r="1826" ht="45" customHeight="1">
+    <row r="1826" ht="20" customHeight="1">
       <c r="A1826" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -35289,7 +35297,7 @@
       </c>
       <c r="B1826" s="19" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C1826" s="20" t="n"/>
@@ -35333,7 +35341,7 @@
       </c>
       <c r="B1829" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/34537</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/906456368</t>
         </is>
       </c>
       <c r="C1829" s="20" t="n"/>
@@ -35344,7 +35352,7 @@
     <row r="1831" ht="30" customHeight="1">
       <c r="A1831" s="16" t="inlineStr">
         <is>
-          <t>FICHA 123: 906456368</t>
+          <t>FICHA 123: 939595836</t>
         </is>
       </c>
       <c r="B1831" s="17" t="n"/>
@@ -35377,7 +35385,7 @@
       </c>
       <c r="B1833" s="19" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C1833" s="20" t="n"/>
@@ -35393,7 +35401,7 @@
       </c>
       <c r="B1834" s="19" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="C1834" s="20" t="n"/>
@@ -35493,7 +35501,7 @@
       </c>
       <c r="B1841" s="19" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C1841" s="20" t="n"/>
@@ -35537,7 +35545,7 @@
       </c>
       <c r="B1844" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/906456368</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939595836</t>
         </is>
       </c>
       <c r="C1844" s="20" t="n"/>
@@ -35548,7 +35556,7 @@
     <row r="1846" ht="30" customHeight="1">
       <c r="A1846" s="16" t="inlineStr">
         <is>
-          <t>FICHA 124: 939595836</t>
+          <t>FICHA 124: 46407</t>
         </is>
       </c>
       <c r="B1846" s="17" t="n"/>
@@ -35573,7 +35581,7 @@
       <c r="E1847" s="20" t="n"/>
       <c r="F1847" s="20" t="n"/>
     </row>
-    <row r="1848" ht="20" customHeight="1">
+    <row r="1848" ht="45" customHeight="1">
       <c r="A1848" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -35581,7 +35589,7 @@
       </c>
       <c r="B1848" s="19" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="C1848" s="20" t="n"/>
@@ -35597,7 +35605,7 @@
       </c>
       <c r="B1849" s="19" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="C1849" s="20" t="n"/>
@@ -35689,7 +35697,7 @@
       <c r="E1855" s="20" t="n"/>
       <c r="F1855" s="20" t="n"/>
     </row>
-    <row r="1856" ht="20" customHeight="1">
+    <row r="1856" ht="45" customHeight="1">
       <c r="A1856" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -35697,7 +35705,7 @@
       </c>
       <c r="B1856" s="19" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="C1856" s="20" t="n"/>
@@ -35741,7 +35749,7 @@
       </c>
       <c r="B1859" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939595836</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/46407</t>
         </is>
       </c>
       <c r="C1859" s="20" t="n"/>
@@ -35752,7 +35760,7 @@
     <row r="1861" ht="30" customHeight="1">
       <c r="A1861" s="16" t="inlineStr">
         <is>
-          <t>FICHA 125: 46407</t>
+          <t>FICHA 125: 71899</t>
         </is>
       </c>
       <c r="B1861" s="17" t="n"/>
@@ -35785,7 +35793,7 @@
       </c>
       <c r="B1863" s="19" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="C1863" s="20" t="n"/>
@@ -35801,7 +35809,7 @@
       </c>
       <c r="B1864" s="19" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="C1864" s="20" t="n"/>
@@ -35901,7 +35909,7 @@
       </c>
       <c r="B1871" s="19" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="C1871" s="20" t="n"/>
@@ -35945,7 +35953,7 @@
       </c>
       <c r="B1874" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/46407</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71899</t>
         </is>
       </c>
       <c r="C1874" s="20" t="n"/>
@@ -35956,7 +35964,7 @@
     <row r="1876" ht="30" customHeight="1">
       <c r="A1876" s="16" t="inlineStr">
         <is>
-          <t>FICHA 126: 71899</t>
+          <t>FICHA 126: PPPA2027</t>
         </is>
       </c>
       <c r="B1876" s="17" t="n"/>
@@ -35989,7 +35997,7 @@
       </c>
       <c r="B1878" s="19" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="C1878" s="20" t="n"/>
@@ -36005,7 +36013,7 @@
       </c>
       <c r="B1879" s="19" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>PPPA2027</t>
         </is>
       </c>
       <c r="C1879" s="20" t="n"/>
@@ -36091,7 +36099,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1885" s="19" t="inlineStr"/>
+      <c r="B1885" s="19" t="inlineStr">
+        <is>
+          <t>PPPA-2025-IGF-IBA</t>
+        </is>
+      </c>
       <c r="C1885" s="20" t="n"/>
       <c r="D1885" s="20" t="n"/>
       <c r="E1885" s="20" t="n"/>
@@ -36105,7 +36117,7 @@
       </c>
       <c r="B1886" s="19" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="C1886" s="20" t="n"/>
@@ -36149,7 +36161,7 @@
       </c>
       <c r="B1889" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71899</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA2027</t>
         </is>
       </c>
       <c r="C1889" s="20" t="n"/>
@@ -36160,7 +36172,7 @@
     <row r="1891" ht="30" customHeight="1">
       <c r="A1891" s="16" t="inlineStr">
         <is>
-          <t>FICHA 127: PPPA2027</t>
+          <t>FICHA 127: dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
         </is>
       </c>
       <c r="B1891" s="17" t="n"/>
@@ -36185,7 +36197,7 @@
       <c r="E1892" s="20" t="n"/>
       <c r="F1892" s="20" t="n"/>
     </row>
-    <row r="1893" ht="45" customHeight="1">
+    <row r="1893" ht="20" customHeight="1">
       <c r="A1893" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -36193,7 +36205,7 @@
       </c>
       <c r="B1893" s="19" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>Border regions Peer exchange on solving border obstacles</t>
         </is>
       </c>
       <c r="C1893" s="20" t="n"/>
@@ -36209,7 +36221,7 @@
       </c>
       <c r="B1894" s="19" t="inlineStr">
         <is>
-          <t>PPPA2027</t>
+          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
         </is>
       </c>
       <c r="C1894" s="20" t="n"/>
@@ -36297,7 +36309,7 @@
       </c>
       <c r="B1900" s="19" t="inlineStr">
         <is>
-          <t>PPPA-2025-IGF-IBA</t>
+          <t>EC-REGIO/2025/MVP/0023-EXA</t>
         </is>
       </c>
       <c r="C1900" s="20" t="n"/>
@@ -36305,7 +36317,7 @@
       <c r="E1900" s="20" t="n"/>
       <c r="F1900" s="20" t="n"/>
     </row>
-    <row r="1901" ht="45" customHeight="1">
+    <row r="1901" ht="20" customHeight="1">
       <c r="A1901" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -36313,7 +36325,7 @@
       </c>
       <c r="B1901" s="19" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>Border regions Peer exchange on solving border obstacles</t>
         </is>
       </c>
       <c r="C1901" s="20" t="n"/>
@@ -36357,7 +36369,7 @@
       </c>
       <c r="B1904" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
         </is>
       </c>
       <c r="C1904" s="20" t="n"/>
@@ -36368,7 +36380,7 @@
     <row r="1906" ht="30" customHeight="1">
       <c r="A1906" s="16" t="inlineStr">
         <is>
-          <t>FICHA 128: dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
+          <t>FICHA 128: 4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
         </is>
       </c>
       <c r="B1906" s="17" t="n"/>
@@ -36417,7 +36429,7 @@
       </c>
       <c r="B1909" s="19" t="inlineStr">
         <is>
-          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
+          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
         </is>
       </c>
       <c r="C1909" s="20" t="n"/>
@@ -36505,7 +36517,7 @@
       </c>
       <c r="B1915" s="19" t="inlineStr">
         <is>
-          <t>EC-REGIO/2025/MVP/0023-EXA</t>
+          <t>EC-REGIO/2025/MVP/0036-EXA</t>
         </is>
       </c>
       <c r="C1915" s="20" t="n"/>
@@ -36565,7 +36577,7 @@
       </c>
       <c r="B1919" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
         </is>
       </c>
       <c r="C1919" s="20" t="n"/>
@@ -36576,7 +36588,7 @@
     <row r="1921" ht="30" customHeight="1">
       <c r="A1921" s="16" t="inlineStr">
         <is>
-          <t>FICHA 129: 4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
+          <t>FICHA 129: 8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="B1921" s="17" t="n"/>
@@ -36601,7 +36613,7 @@
       <c r="E1922" s="20" t="n"/>
       <c r="F1922" s="20" t="n"/>
     </row>
-    <row r="1923" ht="20" customHeight="1">
+    <row r="1923" ht="45" customHeight="1">
       <c r="A1923" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -36609,7 +36621,7 @@
       </c>
       <c r="B1923" s="19" t="inlineStr">
         <is>
-          <t>Border regions Peer exchange on solving border obstacles</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="C1923" s="20" t="n"/>
@@ -36625,7 +36637,7 @@
       </c>
       <c r="B1924" s="19" t="inlineStr">
         <is>
-          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
+          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="C1924" s="20" t="n"/>
@@ -36713,7 +36725,7 @@
       </c>
       <c r="B1930" s="19" t="inlineStr">
         <is>
-          <t>EC-REGIO/2025/MVP/0036-EXA</t>
+          <t>EC-REGIO/2024/MVP/0031-EXA</t>
         </is>
       </c>
       <c r="C1930" s="20" t="n"/>
@@ -36721,7 +36733,7 @@
       <c r="E1930" s="20" t="n"/>
       <c r="F1930" s="20" t="n"/>
     </row>
-    <row r="1931" ht="20" customHeight="1">
+    <row r="1931" ht="45" customHeight="1">
       <c r="A1931" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -36729,7 +36741,7 @@
       </c>
       <c r="B1931" s="19" t="inlineStr">
         <is>
-          <t>Border regions Peer exchange on solving border obstacles</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="C1931" s="20" t="n"/>
@@ -36773,7 +36785,7 @@
       </c>
       <c r="B1934" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="C1934" s="20" t="n"/>
@@ -36784,7 +36796,7 @@
     <row r="1936" ht="30" customHeight="1">
       <c r="A1936" s="16" t="inlineStr">
         <is>
-          <t>FICHA 130: 8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>FICHA 130: 886623263</t>
         </is>
       </c>
       <c r="B1936" s="17" t="n"/>
@@ -36809,7 +36821,7 @@
       <c r="E1937" s="20" t="n"/>
       <c r="F1937" s="20" t="n"/>
     </row>
-    <row r="1938" ht="45" customHeight="1">
+    <row r="1938" ht="20" customHeight="1">
       <c r="A1938" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -36817,7 +36829,7 @@
       </c>
       <c r="B1938" s="19" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="C1938" s="20" t="n"/>
@@ -36833,7 +36845,7 @@
       </c>
       <c r="B1939" s="19" t="inlineStr">
         <is>
-          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>886623263</t>
         </is>
       </c>
       <c r="C1939" s="20" t="n"/>
@@ -36919,17 +36931,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1945" s="19" t="inlineStr">
-        <is>
-          <t>EC-REGIO/2024/MVP/0031-EXA</t>
-        </is>
-      </c>
+      <c r="B1945" s="19" t="inlineStr"/>
       <c r="C1945" s="20" t="n"/>
       <c r="D1945" s="20" t="n"/>
       <c r="E1945" s="20" t="n"/>
       <c r="F1945" s="20" t="n"/>
     </row>
-    <row r="1946" ht="45" customHeight="1">
+    <row r="1946" ht="20" customHeight="1">
       <c r="A1946" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -36937,7 +36945,7 @@
       </c>
       <c r="B1946" s="19" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="C1946" s="20" t="n"/>
@@ -36981,7 +36989,7 @@
       </c>
       <c r="B1949" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/886623263</t>
         </is>
       </c>
       <c r="C1949" s="20" t="n"/>
@@ -36992,7 +37000,7 @@
     <row r="1951" ht="30" customHeight="1">
       <c r="A1951" s="16" t="inlineStr">
         <is>
-          <t>FICHA 131: 886623263</t>
+          <t>FICHA 131: 877314852</t>
         </is>
       </c>
       <c r="B1951" s="17" t="n"/>
@@ -37025,7 +37033,7 @@
       </c>
       <c r="B1953" s="19" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="C1953" s="20" t="n"/>
@@ -37041,7 +37049,7 @@
       </c>
       <c r="B1954" s="19" t="inlineStr">
         <is>
-          <t>886623263</t>
+          <t>877314852</t>
         </is>
       </c>
       <c r="C1954" s="20" t="n"/>
@@ -37141,7 +37149,7 @@
       </c>
       <c r="B1961" s="19" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="C1961" s="20" t="n"/>
@@ -37185,7 +37193,7 @@
       </c>
       <c r="B1964" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/886623263</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/877314852</t>
         </is>
       </c>
       <c r="C1964" s="20" t="n"/>
@@ -37196,7 +37204,7 @@
     <row r="1966" ht="30" customHeight="1">
       <c r="A1966" s="16" t="inlineStr">
         <is>
-          <t>FICHA 132: 877314852</t>
+          <t>FICHA 132: 884174595</t>
         </is>
       </c>
       <c r="B1966" s="17" t="n"/>
@@ -37229,7 +37237,7 @@
       </c>
       <c r="B1968" s="19" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="C1968" s="20" t="n"/>
@@ -37245,7 +37253,7 @@
       </c>
       <c r="B1969" s="19" t="inlineStr">
         <is>
-          <t>877314852</t>
+          <t>884174595</t>
         </is>
       </c>
       <c r="C1969" s="20" t="n"/>
@@ -37345,7 +37353,7 @@
       </c>
       <c r="B1976" s="19" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="C1976" s="20" t="n"/>
@@ -37389,7 +37397,7 @@
       </c>
       <c r="B1979" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/877314852</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/884174595</t>
         </is>
       </c>
       <c r="C1979" s="20" t="n"/>
@@ -37400,7 +37408,7 @@
     <row r="1981" ht="30" customHeight="1">
       <c r="A1981" s="16" t="inlineStr">
         <is>
-          <t>FICHA 133: 884174595</t>
+          <t>FICHA 133: 900546740</t>
         </is>
       </c>
       <c r="B1981" s="17" t="n"/>
@@ -37425,7 +37433,7 @@
       <c r="E1982" s="20" t="n"/>
       <c r="F1982" s="20" t="n"/>
     </row>
-    <row r="1983" ht="20" customHeight="1">
+    <row r="1983" ht="45" customHeight="1">
       <c r="A1983" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -37433,7 +37441,7 @@
       </c>
       <c r="B1983" s="19" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="C1983" s="20" t="n"/>
@@ -37449,7 +37457,7 @@
       </c>
       <c r="B1984" s="19" t="inlineStr">
         <is>
-          <t>884174595</t>
+          <t>900546740</t>
         </is>
       </c>
       <c r="C1984" s="20" t="n"/>
@@ -37541,7 +37549,7 @@
       <c r="E1990" s="20" t="n"/>
       <c r="F1990" s="20" t="n"/>
     </row>
-    <row r="1991" ht="20" customHeight="1">
+    <row r="1991" ht="45" customHeight="1">
       <c r="A1991" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -37549,7 +37557,7 @@
       </c>
       <c r="B1991" s="19" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="C1991" s="20" t="n"/>
@@ -37593,7 +37601,7 @@
       </c>
       <c r="B1994" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/884174595</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/900546740</t>
         </is>
       </c>
       <c r="C1994" s="20" t="n"/>
@@ -37604,7 +37612,7 @@
     <row r="1996" ht="30" customHeight="1">
       <c r="A1996" s="16" t="inlineStr">
         <is>
-          <t>FICHA 134: 900546740</t>
+          <t>FICHA 134: 941945952</t>
         </is>
       </c>
       <c r="B1996" s="17" t="n"/>
@@ -37629,7 +37637,7 @@
       <c r="E1997" s="20" t="n"/>
       <c r="F1997" s="20" t="n"/>
     </row>
-    <row r="1998" ht="45" customHeight="1">
+    <row r="1998" ht="20" customHeight="1">
       <c r="A1998" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -37637,7 +37645,7 @@
       </c>
       <c r="B1998" s="19" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="C1998" s="20" t="n"/>
@@ -37653,7 +37661,7 @@
       </c>
       <c r="B1999" s="19" t="inlineStr">
         <is>
-          <t>900546740</t>
+          <t>941945952</t>
         </is>
       </c>
       <c r="C1999" s="20" t="n"/>
@@ -37745,7 +37753,7 @@
       <c r="E2005" s="20" t="n"/>
       <c r="F2005" s="20" t="n"/>
     </row>
-    <row r="2006" ht="45" customHeight="1">
+    <row r="2006" ht="20" customHeight="1">
       <c r="A2006" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -37753,7 +37761,7 @@
       </c>
       <c r="B2006" s="19" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="C2006" s="20" t="n"/>
@@ -37797,7 +37805,7 @@
       </c>
       <c r="B2009" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/900546740</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/941945952</t>
         </is>
       </c>
       <c r="C2009" s="20" t="n"/>
@@ -37808,7 +37816,7 @@
     <row r="2011" ht="30" customHeight="1">
       <c r="A2011" s="16" t="inlineStr">
         <is>
-          <t>FICHA 135: 941945952</t>
+          <t>FICHA 135: 91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="B2011" s="17" t="n"/>
@@ -37841,7 +37849,7 @@
       </c>
       <c r="B2013" s="19" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="C2013" s="20" t="n"/>
@@ -37857,7 +37865,7 @@
       </c>
       <c r="B2014" s="19" t="inlineStr">
         <is>
-          <t>941945952</t>
+          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="C2014" s="20" t="n"/>
@@ -37943,7 +37951,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2020" s="19" t="inlineStr"/>
+      <c r="B2020" s="19" t="inlineStr">
+        <is>
+          <t>EC-REGIO/2026/MVP/0069-EXA</t>
+        </is>
+      </c>
       <c r="C2020" s="20" t="n"/>
       <c r="D2020" s="20" t="n"/>
       <c r="E2020" s="20" t="n"/>
@@ -37957,7 +37969,7 @@
       </c>
       <c r="B2021" s="19" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="C2021" s="20" t="n"/>
@@ -38001,7 +38013,7 @@
       </c>
       <c r="B2024" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/941945952</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="C2024" s="20" t="n"/>
@@ -38012,7 +38024,7 @@
     <row r="2026" ht="30" customHeight="1">
       <c r="A2026" s="16" t="inlineStr">
         <is>
-          <t>FICHA 136: 91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>FICHA 136: ERDFTA</t>
         </is>
       </c>
       <c r="B2026" s="17" t="n"/>
@@ -38045,7 +38057,7 @@
       </c>
       <c r="B2028" s="19" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="C2028" s="20" t="n"/>
@@ -38061,7 +38073,7 @@
       </c>
       <c r="B2029" s="19" t="inlineStr">
         <is>
-          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>ERDFTA</t>
         </is>
       </c>
       <c r="C2029" s="20" t="n"/>
@@ -38149,7 +38161,7 @@
       </c>
       <c r="B2035" s="19" t="inlineStr">
         <is>
-          <t>EC-REGIO/2026/MVP/0069-EXA</t>
+          <t>ERDFTA-2024-IVY-IBA</t>
         </is>
       </c>
       <c r="C2035" s="20" t="n"/>
@@ -38165,7 +38177,7 @@
       </c>
       <c r="B2036" s="19" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="C2036" s="20" t="n"/>
@@ -38209,7 +38221,7 @@
       </c>
       <c r="B2039" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA</t>
         </is>
       </c>
       <c r="C2039" s="20" t="n"/>
@@ -38220,7 +38232,7 @@
     <row r="2041" ht="30" customHeight="1">
       <c r="A2041" s="16" t="inlineStr">
         <is>
-          <t>FICHA 137: ERDFTA</t>
+          <t>FICHA 137: 90488</t>
         </is>
       </c>
       <c r="B2041" s="17" t="n"/>
@@ -38245,7 +38257,7 @@
       <c r="E2042" s="20" t="n"/>
       <c r="F2042" s="20" t="n"/>
     </row>
-    <row r="2043" ht="20" customHeight="1">
+    <row r="2043" ht="45" customHeight="1">
       <c r="A2043" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -38253,7 +38265,7 @@
       </c>
       <c r="B2043" s="19" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
         </is>
       </c>
       <c r="C2043" s="20" t="n"/>
@@ -38269,7 +38281,7 @@
       </c>
       <c r="B2044" s="19" t="inlineStr">
         <is>
-          <t>ERDFTA</t>
+          <t>90488</t>
         </is>
       </c>
       <c r="C2044" s="20" t="n"/>
@@ -38355,17 +38367,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2050" s="19" t="inlineStr">
-        <is>
-          <t>ERDFTA-2024-IVY-IBA</t>
-        </is>
-      </c>
+      <c r="B2050" s="19" t="inlineStr"/>
       <c r="C2050" s="20" t="n"/>
       <c r="D2050" s="20" t="n"/>
       <c r="E2050" s="20" t="n"/>
       <c r="F2050" s="20" t="n"/>
     </row>
-    <row r="2051" ht="20" customHeight="1">
+    <row r="2051" ht="45" customHeight="1">
       <c r="A2051" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -38373,7 +38381,7 @@
       </c>
       <c r="B2051" s="19" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
         </is>
       </c>
       <c r="C2051" s="20" t="n"/>
@@ -38417,7 +38425,7 @@
       </c>
       <c r="B2054" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/90488</t>
         </is>
       </c>
       <c r="C2054" s="20" t="n"/>
@@ -38428,7 +38436,7 @@
     <row r="2056" ht="30" customHeight="1">
       <c r="A2056" s="16" t="inlineStr">
         <is>
-          <t>FICHA 138: 90488</t>
+          <t>FICHA 138: 19326</t>
         </is>
       </c>
       <c r="B2056" s="17" t="n"/>
@@ -38461,7 +38469,7 @@
       </c>
       <c r="B2058" s="19" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
+          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
         </is>
       </c>
       <c r="C2058" s="20" t="n"/>
@@ -38477,7 +38485,7 @@
       </c>
       <c r="B2059" s="19" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="C2059" s="20" t="n"/>
@@ -38577,7 +38585,7 @@
       </c>
       <c r="B2066" s="19" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
+          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
         </is>
       </c>
       <c r="C2066" s="20" t="n"/>
@@ -38621,7 +38629,7 @@
       </c>
       <c r="B2069" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/90488</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19326</t>
         </is>
       </c>
       <c r="C2069" s="20" t="n"/>
@@ -38632,7 +38640,7 @@
     <row r="2071" ht="30" customHeight="1">
       <c r="A2071" s="16" t="inlineStr">
         <is>
-          <t>FICHA 139: 19326</t>
+          <t>FICHA 139: 14587</t>
         </is>
       </c>
       <c r="B2071" s="17" t="n"/>
@@ -38665,7 +38673,7 @@
       </c>
       <c r="B2073" s="19" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
+          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
         </is>
       </c>
       <c r="C2073" s="20" t="n"/>
@@ -38681,7 +38689,7 @@
       </c>
       <c r="B2074" s="19" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="C2074" s="20" t="n"/>
@@ -38781,7 +38789,7 @@
       </c>
       <c r="B2081" s="19" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
+          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
         </is>
       </c>
       <c r="C2081" s="20" t="n"/>
@@ -38825,7 +38833,7 @@
       </c>
       <c r="B2084" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19326</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14587</t>
         </is>
       </c>
       <c r="C2084" s="20" t="n"/>
@@ -39040,7 +39048,7 @@
     <row r="2101" ht="30" customHeight="1">
       <c r="A2101" s="16" t="inlineStr">
         <is>
-          <t>FICHA 141: 14587</t>
+          <t>FICHA 141: n00brugy</t>
         </is>
       </c>
       <c r="B2101" s="17" t="n"/>
@@ -39065,7 +39073,7 @@
       <c r="E2102" s="20" t="n"/>
       <c r="F2102" s="20" t="n"/>
     </row>
-    <row r="2103" ht="45" customHeight="1">
+    <row r="2103" ht="20" customHeight="1">
       <c r="A2103" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -39073,7 +39081,7 @@
       </c>
       <c r="B2103" s="19" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
+          <t>Joana SANTIAGO</t>
         </is>
       </c>
       <c r="C2103" s="20" t="n"/>
@@ -39089,7 +39097,7 @@
       </c>
       <c r="B2104" s="19" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>n00brugy</t>
         </is>
       </c>
       <c r="C2104" s="20" t="n"/>
@@ -39181,7 +39189,7 @@
       <c r="E2110" s="20" t="n"/>
       <c r="F2110" s="20" t="n"/>
     </row>
-    <row r="2111" ht="45" customHeight="1">
+    <row r="2111" ht="20" customHeight="1">
       <c r="A2111" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -39189,7 +39197,7 @@
       </c>
       <c r="B2111" s="19" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
+          <t>Joana SANTIAGO</t>
         </is>
       </c>
       <c r="C2111" s="20" t="n"/>
@@ -39233,7 +39241,7 @@
       </c>
       <c r="B2114" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14587</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n00brugy</t>
         </is>
       </c>
       <c r="C2114" s="20" t="n"/>
@@ -39244,7 +39252,7 @@
     <row r="2116" ht="30" customHeight="1">
       <c r="A2116" s="16" t="inlineStr">
         <is>
-          <t>FICHA 142: n00brugy</t>
+          <t>FICHA 142: n00kmonh</t>
         </is>
       </c>
       <c r="B2116" s="17" t="n"/>
@@ -39277,7 +39285,7 @@
       </c>
       <c r="B2118" s="19" t="inlineStr">
         <is>
-          <t>Joana SANTIAGO</t>
+          <t>Mrs LARA MARIA CERDAN AZNAR</t>
         </is>
       </c>
       <c r="C2118" s="20" t="n"/>
@@ -39293,7 +39301,7 @@
       </c>
       <c r="B2119" s="19" t="inlineStr">
         <is>
-          <t>n00brugy</t>
+          <t>n00kmonh</t>
         </is>
       </c>
       <c r="C2119" s="20" t="n"/>
@@ -39393,7 +39401,7 @@
       </c>
       <c r="B2126" s="19" t="inlineStr">
         <is>
-          <t>Joana SANTIAGO</t>
+          <t>Mrs LARA MARIA CERDAN AZNAR</t>
         </is>
       </c>
       <c r="C2126" s="20" t="n"/>
@@ -39437,7 +39445,7 @@
       </c>
       <c r="B2129" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n00brugy</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n00kmonh</t>
         </is>
       </c>
       <c r="C2129" s="20" t="n"/>
@@ -39448,7 +39456,7 @@
     <row r="2131" ht="30" customHeight="1">
       <c r="A2131" s="16" t="inlineStr">
         <is>
-          <t>FICHA 143: n00kmonh</t>
+          <t>FICHA 143: NA</t>
         </is>
       </c>
       <c r="B2131" s="17" t="n"/>
@@ -39481,7 +39489,7 @@
       </c>
       <c r="B2133" s="19" t="inlineStr">
         <is>
-          <t>Mrs LARA MARIA CERDAN AZNAR</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="C2133" s="20" t="n"/>
@@ -39497,7 +39505,7 @@
       </c>
       <c r="B2134" s="19" t="inlineStr">
         <is>
-          <t>n00kmonh</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="C2134" s="20" t="n"/>
@@ -39597,7 +39605,7 @@
       </c>
       <c r="B2141" s="19" t="inlineStr">
         <is>
-          <t>Mrs LARA MARIA CERDAN AZNAR</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="C2141" s="20" t="n"/>
@@ -39641,7 +39649,7 @@
       </c>
       <c r="B2144" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n00kmonh</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NA</t>
         </is>
       </c>
       <c r="C2144" s="20" t="n"/>
@@ -39652,7 +39660,7 @@
     <row r="2146" ht="30" customHeight="1">
       <c r="A2146" s="16" t="inlineStr">
         <is>
-          <t>FICHA 144: NA</t>
+          <t>FICHA 144: 937468917</t>
         </is>
       </c>
       <c r="B2146" s="17" t="n"/>
@@ -39677,7 +39685,7 @@
       <c r="E2147" s="20" t="n"/>
       <c r="F2147" s="20" t="n"/>
     </row>
-    <row r="2148" ht="20" customHeight="1">
+    <row r="2148" ht="45" customHeight="1">
       <c r="A2148" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -39685,7 +39693,7 @@
       </c>
       <c r="B2148" s="19" t="inlineStr">
         <is>
-          <t>MS Elena Jauregui Baldassini</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="C2148" s="20" t="n"/>
@@ -39701,7 +39709,7 @@
       </c>
       <c r="B2149" s="19" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>937468917</t>
         </is>
       </c>
       <c r="C2149" s="20" t="n"/>
@@ -39793,7 +39801,7 @@
       <c r="E2155" s="20" t="n"/>
       <c r="F2155" s="20" t="n"/>
     </row>
-    <row r="2156" ht="20" customHeight="1">
+    <row r="2156" ht="45" customHeight="1">
       <c r="A2156" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -39801,7 +39809,7 @@
       </c>
       <c r="B2156" s="19" t="inlineStr">
         <is>
-          <t>MS Elena Jauregui Baldassini</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="C2156" s="20" t="n"/>
@@ -39845,7 +39853,7 @@
       </c>
       <c r="B2159" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/937468917</t>
         </is>
       </c>
       <c r="C2159" s="20" t="n"/>
@@ -39856,7 +39864,7 @@
     <row r="2161" ht="30" customHeight="1">
       <c r="A2161" s="16" t="inlineStr">
         <is>
-          <t>FICHA 145: 937468917</t>
+          <t>FICHA 145: 48508</t>
         </is>
       </c>
       <c r="B2161" s="17" t="n"/>
@@ -39889,7 +39897,7 @@
       </c>
       <c r="B2163" s="19" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="C2163" s="20" t="n"/>
@@ -39905,7 +39913,7 @@
       </c>
       <c r="B2164" s="19" t="inlineStr">
         <is>
-          <t>937468917</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="C2164" s="20" t="n"/>
@@ -40005,7 +40013,7 @@
       </c>
       <c r="B2171" s="19" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="C2171" s="20" t="n"/>
@@ -40049,7 +40057,7 @@
       </c>
       <c r="B2174" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/937468917</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/48508</t>
         </is>
       </c>
       <c r="C2174" s="20" t="n"/>
@@ -40060,7 +40068,7 @@
     <row r="2176" ht="30" customHeight="1">
       <c r="A2176" s="16" t="inlineStr">
         <is>
-          <t>FICHA 146: 48508</t>
+          <t>FICHA 146: n002cet5</t>
         </is>
       </c>
       <c r="B2176" s="17" t="n"/>
@@ -40085,7 +40093,7 @@
       <c r="E2177" s="20" t="n"/>
       <c r="F2177" s="20" t="n"/>
     </row>
-    <row r="2178" ht="45" customHeight="1">
+    <row r="2178" ht="20" customHeight="1">
       <c r="A2178" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -40093,7 +40101,7 @@
       </c>
       <c r="B2178" s="19" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="C2178" s="20" t="n"/>
@@ -40109,7 +40117,7 @@
       </c>
       <c r="B2179" s="19" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>n002cet5</t>
         </is>
       </c>
       <c r="C2179" s="20" t="n"/>
@@ -40201,7 +40209,7 @@
       <c r="E2185" s="20" t="n"/>
       <c r="F2185" s="20" t="n"/>
     </row>
-    <row r="2186" ht="45" customHeight="1">
+    <row r="2186" ht="20" customHeight="1">
       <c r="A2186" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -40209,7 +40217,7 @@
       </c>
       <c r="B2186" s="19" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="C2186" s="20" t="n"/>
@@ -40253,7 +40261,7 @@
       </c>
       <c r="B2189" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/48508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n002cet5</t>
         </is>
       </c>
       <c r="C2189" s="20" t="n"/>
@@ -40264,7 +40272,7 @@
     <row r="2191" ht="30" customHeight="1">
       <c r="A2191" s="16" t="inlineStr">
         <is>
-          <t>FICHA 147: n002cet5</t>
+          <t>FICHA 147: 16545</t>
         </is>
       </c>
       <c r="B2191" s="17" t="n"/>
@@ -40289,7 +40297,7 @@
       <c r="E2192" s="20" t="n"/>
       <c r="F2192" s="20" t="n"/>
     </row>
-    <row r="2193" ht="20" customHeight="1">
+    <row r="2193" ht="45" customHeight="1">
       <c r="A2193" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -40297,7 +40305,7 @@
       </c>
       <c r="B2193" s="19" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="C2193" s="20" t="n"/>
@@ -40313,7 +40321,7 @@
       </c>
       <c r="B2194" s="19" t="inlineStr">
         <is>
-          <t>n002cet5</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C2194" s="20" t="n"/>
@@ -40405,7 +40413,7 @@
       <c r="E2200" s="20" t="n"/>
       <c r="F2200" s="20" t="n"/>
     </row>
-    <row r="2201" ht="20" customHeight="1">
+    <row r="2201" ht="45" customHeight="1">
       <c r="A2201" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -40413,7 +40421,7 @@
       </c>
       <c r="B2201" s="19" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="C2201" s="20" t="n"/>
@@ -40457,7 +40465,7 @@
       </c>
       <c r="B2204" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n002cet5</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16545</t>
         </is>
       </c>
       <c r="C2204" s="20" t="n"/>
@@ -40468,7 +40476,7 @@
     <row r="2206" ht="30" customHeight="1">
       <c r="A2206" s="16" t="inlineStr">
         <is>
-          <t>FICHA 148: 16545</t>
+          <t>FICHA 148: 885233544</t>
         </is>
       </c>
       <c r="B2206" s="17" t="n"/>
@@ -40493,7 +40501,7 @@
       <c r="E2207" s="20" t="n"/>
       <c r="F2207" s="20" t="n"/>
     </row>
-    <row r="2208" ht="45" customHeight="1">
+    <row r="2208" ht="20" customHeight="1">
       <c r="A2208" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -40501,7 +40509,7 @@
       </c>
       <c r="B2208" s="19" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="C2208" s="20" t="n"/>
@@ -40517,7 +40525,7 @@
       </c>
       <c r="B2209" s="19" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>885233544</t>
         </is>
       </c>
       <c r="C2209" s="20" t="n"/>
@@ -40609,7 +40617,7 @@
       <c r="E2215" s="20" t="n"/>
       <c r="F2215" s="20" t="n"/>
     </row>
-    <row r="2216" ht="45" customHeight="1">
+    <row r="2216" ht="20" customHeight="1">
       <c r="A2216" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -40617,7 +40625,7 @@
       </c>
       <c r="B2216" s="19" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="C2216" s="20" t="n"/>
@@ -40661,7 +40669,7 @@
       </c>
       <c r="B2219" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16545</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/885233544</t>
         </is>
       </c>
       <c r="C2219" s="20" t="n"/>
@@ -40672,7 +40680,7 @@
     <row r="2221" ht="30" customHeight="1">
       <c r="A2221" s="16" t="inlineStr">
         <is>
-          <t>FICHA 149: 885233544</t>
+          <t>FICHA 149: 18804</t>
         </is>
       </c>
       <c r="B2221" s="17" t="n"/>
@@ -40697,7 +40705,7 @@
       <c r="E2222" s="20" t="n"/>
       <c r="F2222" s="20" t="n"/>
     </row>
-    <row r="2223" ht="20" customHeight="1">
+    <row r="2223" ht="45" customHeight="1">
       <c r="A2223" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -40705,7 +40713,7 @@
       </c>
       <c r="B2223" s="19" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="C2223" s="20" t="n"/>
@@ -40721,7 +40729,7 @@
       </c>
       <c r="B2224" s="19" t="inlineStr">
         <is>
-          <t>885233544</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="C2224" s="20" t="n"/>
@@ -40813,7 +40821,7 @@
       <c r="E2230" s="20" t="n"/>
       <c r="F2230" s="20" t="n"/>
     </row>
-    <row r="2231" ht="20" customHeight="1">
+    <row r="2231" ht="45" customHeight="1">
       <c r="A2231" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -40821,7 +40829,7 @@
       </c>
       <c r="B2231" s="19" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="C2231" s="20" t="n"/>
@@ -40865,7 +40873,7 @@
       </c>
       <c r="B2234" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/885233544</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18804</t>
         </is>
       </c>
       <c r="C2234" s="20" t="n"/>
@@ -40876,7 +40884,7 @@
     <row r="2236" ht="30" customHeight="1">
       <c r="A2236" s="16" t="inlineStr">
         <is>
-          <t>FICHA 150: 18804</t>
+          <t>FICHA 150: 18749</t>
         </is>
       </c>
       <c r="B2236" s="17" t="n"/>
@@ -40909,7 +40917,7 @@
       </c>
       <c r="B2238" s="19" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="C2238" s="20" t="n"/>
@@ -40925,7 +40933,7 @@
       </c>
       <c r="B2239" s="19" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="C2239" s="20" t="n"/>
@@ -41025,7 +41033,7 @@
       </c>
       <c r="B2246" s="19" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="C2246" s="20" t="n"/>
@@ -41069,7 +41077,7 @@
       </c>
       <c r="B2249" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18804</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18749</t>
         </is>
       </c>
       <c r="C2249" s="20" t="n"/>
@@ -41080,7 +41088,7 @@
     <row r="2251" ht="30" customHeight="1">
       <c r="A2251" s="16" t="inlineStr">
         <is>
-          <t>FICHA 151: 18749</t>
+          <t>FICHA 151: 31728</t>
         </is>
       </c>
       <c r="B2251" s="17" t="n"/>
@@ -41113,7 +41121,7 @@
       </c>
       <c r="B2253" s="19" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="C2253" s="20" t="n"/>
@@ -41129,7 +41137,7 @@
       </c>
       <c r="B2254" s="19" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="C2254" s="20" t="n"/>
@@ -41229,7 +41237,7 @@
       </c>
       <c r="B2261" s="19" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="C2261" s="20" t="n"/>
@@ -41273,7 +41281,7 @@
       </c>
       <c r="B2264" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18749</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31728</t>
         </is>
       </c>
       <c r="C2264" s="20" t="n"/>
@@ -41284,7 +41292,7 @@
     <row r="2266" ht="30" customHeight="1">
       <c r="A2266" s="16" t="inlineStr">
         <is>
-          <t>FICHA 152: 31728</t>
+          <t>FICHA 152: 13660</t>
         </is>
       </c>
       <c r="B2266" s="17" t="n"/>
@@ -41309,7 +41317,7 @@
       <c r="E2267" s="20" t="n"/>
       <c r="F2267" s="20" t="n"/>
     </row>
-    <row r="2268" ht="45" customHeight="1">
+    <row r="2268" ht="20" customHeight="1">
       <c r="A2268" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -41317,7 +41325,7 @@
       </c>
       <c r="B2268" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
         </is>
       </c>
       <c r="C2268" s="20" t="n"/>
@@ -41333,7 +41341,7 @@
       </c>
       <c r="B2269" s="19" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="C2269" s="20" t="n"/>
@@ -41433,7 +41441,7 @@
       </c>
       <c r="B2276" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technology in the heating and cooling sector. This is in line with the Paris Agreement and approaches a nearly zero carbon energy system.- By</t>
         </is>
       </c>
       <c r="C2276" s="20" t="n"/>
@@ -41477,7 +41485,7 @@
       </c>
       <c r="B2279" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31728</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13660</t>
         </is>
       </c>
       <c r="C2279" s="20" t="n"/>
@@ -41488,7 +41496,7 @@
     <row r="2281" ht="30" customHeight="1">
       <c r="A2281" s="16" t="inlineStr">
         <is>
-          <t>FICHA 153: 13660</t>
+          <t>FICHA 153: 6484</t>
         </is>
       </c>
       <c r="B2281" s="17" t="n"/>
@@ -41513,7 +41521,7 @@
       <c r="E2282" s="20" t="n"/>
       <c r="F2282" s="20" t="n"/>
     </row>
-    <row r="2283" ht="20" customHeight="1">
+    <row r="2283" ht="45" customHeight="1">
       <c r="A2283" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -41521,7 +41529,7 @@
       </c>
       <c r="B2283" s="19" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="C2283" s="20" t="n"/>
@@ -41537,7 +41545,7 @@
       </c>
       <c r="B2284" s="19" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="C2284" s="20" t="n"/>
@@ -41637,7 +41645,7 @@
       </c>
       <c r="B2291" s="19" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technology in the heating and cooling sector. This is in line with the Paris Agreement and approaches a nearly zero carbon energy system.- By</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="C2291" s="20" t="n"/>
@@ -41681,7 +41689,7 @@
       </c>
       <c r="B2294" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13660</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/6484</t>
         </is>
       </c>
       <c r="C2294" s="20" t="n"/>
@@ -41692,7 +41700,7 @@
     <row r="2296" ht="30" customHeight="1">
       <c r="A2296" s="16" t="inlineStr">
         <is>
-          <t>FICHA 154: 6484</t>
+          <t>FICHA 154: 16367</t>
         </is>
       </c>
       <c r="B2296" s="17" t="n"/>
@@ -41725,7 +41733,7 @@
       </c>
       <c r="B2298" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="C2298" s="20" t="n"/>
@@ -41741,7 +41749,7 @@
       </c>
       <c r="B2299" s="19" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="C2299" s="20" t="n"/>
@@ -41841,7 +41849,7 @@
       </c>
       <c r="B2306" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="C2306" s="20" t="n"/>
@@ -41885,7 +41893,7 @@
       </c>
       <c r="B2309" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/6484</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16367</t>
         </is>
       </c>
       <c r="C2309" s="20" t="n"/>
@@ -41896,7 +41904,7 @@
     <row r="2311" ht="30" customHeight="1">
       <c r="A2311" s="16" t="inlineStr">
         <is>
-          <t>FICHA 155: 16367</t>
+          <t>FICHA 155: 71691</t>
         </is>
       </c>
       <c r="B2311" s="17" t="n"/>
@@ -41929,7 +41937,7 @@
       </c>
       <c r="B2313" s="19" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="C2313" s="20" t="n"/>
@@ -41945,7 +41953,7 @@
       </c>
       <c r="B2314" s="19" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="C2314" s="20" t="n"/>
@@ -42045,7 +42053,7 @@
       </c>
       <c r="B2321" s="19" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="C2321" s="20" t="n"/>
@@ -42089,7 +42097,7 @@
       </c>
       <c r="B2324" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16367</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71691</t>
         </is>
       </c>
       <c r="C2324" s="20" t="n"/>
@@ -42100,7 +42108,7 @@
     <row r="2326" ht="30" customHeight="1">
       <c r="A2326" s="16" t="inlineStr">
         <is>
-          <t>FICHA 156: 71691</t>
+          <t>FICHA 156: 956926438</t>
         </is>
       </c>
       <c r="B2326" s="17" t="n"/>
@@ -42125,7 +42133,7 @@
       <c r="E2327" s="20" t="n"/>
       <c r="F2327" s="20" t="n"/>
     </row>
-    <row r="2328" ht="45" customHeight="1">
+    <row r="2328" ht="20" customHeight="1">
       <c r="A2328" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -42133,7 +42141,7 @@
       </c>
       <c r="B2328" s="19" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="C2328" s="20" t="n"/>
@@ -42149,7 +42157,7 @@
       </c>
       <c r="B2329" s="19" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>956926438</t>
         </is>
       </c>
       <c r="C2329" s="20" t="n"/>
@@ -42241,7 +42249,7 @@
       <c r="E2335" s="20" t="n"/>
       <c r="F2335" s="20" t="n"/>
     </row>
-    <row r="2336" ht="45" customHeight="1">
+    <row r="2336" ht="20" customHeight="1">
       <c r="A2336" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -42249,7 +42257,7 @@
       </c>
       <c r="B2336" s="19" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="C2336" s="20" t="n"/>
@@ -42293,7 +42301,7 @@
       </c>
       <c r="B2339" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71691</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/956926438</t>
         </is>
       </c>
       <c r="C2339" s="20" t="n"/>
@@ -42304,7 +42312,7 @@
     <row r="2341" ht="30" customHeight="1">
       <c r="A2341" s="16" t="inlineStr">
         <is>
-          <t>FICHA 157: 956926438</t>
+          <t>FICHA 157: 10027</t>
         </is>
       </c>
       <c r="B2341" s="17" t="n"/>
@@ -42329,7 +42337,7 @@
       <c r="E2342" s="20" t="n"/>
       <c r="F2342" s="20" t="n"/>
     </row>
-    <row r="2343" ht="20" customHeight="1">
+    <row r="2343" ht="45" customHeight="1">
       <c r="A2343" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -42337,7 +42345,7 @@
       </c>
       <c r="B2343" s="19" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="C2343" s="20" t="n"/>
@@ -42353,7 +42361,7 @@
       </c>
       <c r="B2344" s="19" t="inlineStr">
         <is>
-          <t>956926438</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="C2344" s="20" t="n"/>
@@ -42445,7 +42453,7 @@
       <c r="E2350" s="20" t="n"/>
       <c r="F2350" s="20" t="n"/>
     </row>
-    <row r="2351" ht="20" customHeight="1">
+    <row r="2351" ht="45" customHeight="1">
       <c r="A2351" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -42453,7 +42461,7 @@
       </c>
       <c r="B2351" s="19" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="C2351" s="20" t="n"/>
@@ -42497,7 +42505,7 @@
       </c>
       <c r="B2354" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/956926438</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/10027</t>
         </is>
       </c>
       <c r="C2354" s="20" t="n"/>
@@ -42712,7 +42720,7 @@
     <row r="2371" ht="30" customHeight="1">
       <c r="A2371" s="16" t="inlineStr">
         <is>
-          <t>FICHA 159: 953552487</t>
+          <t>FICHA 159: 925388828</t>
         </is>
       </c>
       <c r="B2371" s="17" t="n"/>
@@ -42745,7 +42753,7 @@
       </c>
       <c r="B2373" s="19" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C2373" s="20" t="n"/>
@@ -42761,7 +42769,7 @@
       </c>
       <c r="B2374" s="19" t="inlineStr">
         <is>
-          <t>953552487</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C2374" s="20" t="n"/>
@@ -42861,7 +42869,7 @@
       </c>
       <c r="B2381" s="19" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C2381" s="20" t="n"/>
@@ -42905,7 +42913,7 @@
       </c>
       <c r="B2384" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953552487</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
         </is>
       </c>
       <c r="C2384" s="20" t="n"/>
@@ -42916,7 +42924,7 @@
     <row r="2386" ht="30" customHeight="1">
       <c r="A2386" s="16" t="inlineStr">
         <is>
-          <t>FICHA 160: 925388828</t>
+          <t>FICHA 160: 934294980</t>
         </is>
       </c>
       <c r="B2386" s="17" t="n"/>
@@ -42949,7 +42957,7 @@
       </c>
       <c r="B2388" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C2388" s="20" t="n"/>
@@ -42965,7 +42973,7 @@
       </c>
       <c r="B2389" s="19" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C2389" s="20" t="n"/>
@@ -43065,7 +43073,7 @@
       </c>
       <c r="B2396" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C2396" s="20" t="n"/>
@@ -43109,7 +43117,7 @@
       </c>
       <c r="B2399" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
         </is>
       </c>
       <c r="C2399" s="20" t="n"/>
@@ -43120,7 +43128,7 @@
     <row r="2401" ht="30" customHeight="1">
       <c r="A2401" s="16" t="inlineStr">
         <is>
-          <t>FICHA 161: 934294980</t>
+          <t>FICHA 161: 876983694</t>
         </is>
       </c>
       <c r="B2401" s="17" t="n"/>
@@ -43153,7 +43161,7 @@
       </c>
       <c r="B2403" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="C2403" s="20" t="n"/>
@@ -43169,7 +43177,7 @@
       </c>
       <c r="B2404" s="19" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>876983694</t>
         </is>
       </c>
       <c r="C2404" s="20" t="n"/>
@@ -43269,7 +43277,7 @@
       </c>
       <c r="B2411" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="C2411" s="20" t="n"/>
@@ -43313,7 +43321,7 @@
       </c>
       <c r="B2414" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/876983694</t>
         </is>
       </c>
       <c r="C2414" s="20" t="n"/>
@@ -43324,7 +43332,7 @@
     <row r="2416" ht="30" customHeight="1">
       <c r="A2416" s="16" t="inlineStr">
         <is>
-          <t>FICHA 162: 876983694</t>
+          <t>FICHA 162: 17917</t>
         </is>
       </c>
       <c r="B2416" s="17" t="n"/>
@@ -43349,7 +43357,7 @@
       <c r="E2417" s="20" t="n"/>
       <c r="F2417" s="20" t="n"/>
     </row>
-    <row r="2418" ht="20" customHeight="1">
+    <row r="2418" ht="45" customHeight="1">
       <c r="A2418" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -43357,7 +43365,7 @@
       </c>
       <c r="B2418" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="C2418" s="20" t="n"/>
@@ -43373,7 +43381,7 @@
       </c>
       <c r="B2419" s="19" t="inlineStr">
         <is>
-          <t>876983694</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="C2419" s="20" t="n"/>
@@ -43465,7 +43473,7 @@
       <c r="E2425" s="20" t="n"/>
       <c r="F2425" s="20" t="n"/>
     </row>
-    <row r="2426" ht="20" customHeight="1">
+    <row r="2426" ht="45" customHeight="1">
       <c r="A2426" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -43473,7 +43481,7 @@
       </c>
       <c r="B2426" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="C2426" s="20" t="n"/>
@@ -43517,7 +43525,7 @@
       </c>
       <c r="B2429" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/876983694</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17917</t>
         </is>
       </c>
       <c r="C2429" s="20" t="n"/>
@@ -43528,7 +43536,7 @@
     <row r="2431" ht="30" customHeight="1">
       <c r="A2431" s="16" t="inlineStr">
         <is>
-          <t>FICHA 163: 17917</t>
+          <t>FICHA 163: 935134321</t>
         </is>
       </c>
       <c r="B2431" s="17" t="n"/>
@@ -43553,7 +43561,7 @@
       <c r="E2432" s="20" t="n"/>
       <c r="F2432" s="20" t="n"/>
     </row>
-    <row r="2433" ht="45" customHeight="1">
+    <row r="2433" ht="20" customHeight="1">
       <c r="A2433" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -43561,7 +43569,7 @@
       </c>
       <c r="B2433" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="C2433" s="20" t="n"/>
@@ -43577,7 +43585,7 @@
       </c>
       <c r="B2434" s="19" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>935134321</t>
         </is>
       </c>
       <c r="C2434" s="20" t="n"/>
@@ -43669,7 +43677,7 @@
       <c r="E2440" s="20" t="n"/>
       <c r="F2440" s="20" t="n"/>
     </row>
-    <row r="2441" ht="45" customHeight="1">
+    <row r="2441" ht="20" customHeight="1">
       <c r="A2441" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -43677,7 +43685,7 @@
       </c>
       <c r="B2441" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="C2441" s="20" t="n"/>
@@ -43721,7 +43729,7 @@
       </c>
       <c r="B2444" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17917</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/935134321</t>
         </is>
       </c>
       <c r="C2444" s="20" t="n"/>
@@ -43732,7 +43740,7 @@
     <row r="2446" ht="30" customHeight="1">
       <c r="A2446" s="16" t="inlineStr">
         <is>
-          <t>FICHA 164: 935134321</t>
+          <t>FICHA 164: 883154834</t>
         </is>
       </c>
       <c r="B2446" s="17" t="n"/>
@@ -43765,7 +43773,7 @@
       </c>
       <c r="B2448" s="19" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="C2448" s="20" t="n"/>
@@ -43781,7 +43789,7 @@
       </c>
       <c r="B2449" s="19" t="inlineStr">
         <is>
-          <t>935134321</t>
+          <t>883154834</t>
         </is>
       </c>
       <c r="C2449" s="20" t="n"/>
@@ -43881,7 +43889,7 @@
       </c>
       <c r="B2456" s="19" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="C2456" s="20" t="n"/>
@@ -43925,7 +43933,7 @@
       </c>
       <c r="B2459" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/935134321</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/883154834</t>
         </is>
       </c>
       <c r="C2459" s="20" t="n"/>
@@ -43936,7 +43944,7 @@
     <row r="2461" ht="30" customHeight="1">
       <c r="A2461" s="16" t="inlineStr">
         <is>
-          <t>FICHA 165: 883154834</t>
+          <t>FICHA 165: 93508</t>
         </is>
       </c>
       <c r="B2461" s="17" t="n"/>
@@ -43961,7 +43969,7 @@
       <c r="E2462" s="20" t="n"/>
       <c r="F2462" s="20" t="n"/>
     </row>
-    <row r="2463" ht="20" customHeight="1">
+    <row r="2463" ht="45" customHeight="1">
       <c r="A2463" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -43969,7 +43977,7 @@
       </c>
       <c r="B2463" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="C2463" s="20" t="n"/>
@@ -43985,7 +43993,7 @@
       </c>
       <c r="B2464" s="19" t="inlineStr">
         <is>
-          <t>883154834</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="C2464" s="20" t="n"/>
@@ -44077,7 +44085,7 @@
       <c r="E2470" s="20" t="n"/>
       <c r="F2470" s="20" t="n"/>
     </row>
-    <row r="2471" ht="20" customHeight="1">
+    <row r="2471" ht="45" customHeight="1">
       <c r="A2471" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -44085,7 +44093,7 @@
       </c>
       <c r="B2471" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="C2471" s="20" t="n"/>
@@ -44129,7 +44137,7 @@
       </c>
       <c r="B2474" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/883154834</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/93508</t>
         </is>
       </c>
       <c r="C2474" s="20" t="n"/>
@@ -44140,7 +44148,7 @@
     <row r="2476" ht="30" customHeight="1">
       <c r="A2476" s="16" t="inlineStr">
         <is>
-          <t>FICHA 166: 93508</t>
+          <t>FICHA 166: 50912</t>
         </is>
       </c>
       <c r="B2476" s="17" t="n"/>
@@ -44173,7 +44181,7 @@
       </c>
       <c r="B2478" s="19" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="C2478" s="20" t="n"/>
@@ -44189,7 +44197,7 @@
       </c>
       <c r="B2479" s="19" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="C2479" s="20" t="n"/>
@@ -44289,7 +44297,7 @@
       </c>
       <c r="B2486" s="19" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="C2486" s="20" t="n"/>
@@ -44333,7 +44341,7 @@
       </c>
       <c r="B2489" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/93508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/50912</t>
         </is>
       </c>
       <c r="C2489" s="20" t="n"/>
@@ -44344,7 +44352,7 @@
     <row r="2491" ht="30" customHeight="1">
       <c r="A2491" s="16" t="inlineStr">
         <is>
-          <t>FICHA 167: 50912</t>
+          <t>FICHA 167: 91523</t>
         </is>
       </c>
       <c r="B2491" s="17" t="n"/>
@@ -44377,7 +44385,7 @@
       </c>
       <c r="B2493" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>In relation to the selection criteria concerning experience in “Global Gateway related projects: sustainable investment, energy transition, communication and visibility, digitalization”, we kindly request clarification regarding the interpretation of the term “sustainable investment”. Could you please clarify which typologies of projects/reference</t>
         </is>
       </c>
       <c r="C2493" s="20" t="n"/>
@@ -44393,7 +44401,7 @@
       </c>
       <c r="B2494" s="19" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>91523</t>
         </is>
       </c>
       <c r="C2494" s="20" t="n"/>
@@ -44493,7 +44501,7 @@
       </c>
       <c r="B2501" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>In relation to the selection criteria concerning experience in “Global Gateway related projects: sustainable investment, energy transition, communication and visibility, digitalization”, we kindly request clarification regarding the interpretation of the term “sustainable investment”. Could you please clarify which typologies of projects/reference</t>
         </is>
       </c>
       <c r="C2501" s="20" t="n"/>
@@ -44537,7 +44545,7 @@
       </c>
       <c r="B2504" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/50912</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/91523</t>
         </is>
       </c>
       <c r="C2504" s="20" t="n"/>
@@ -44548,7 +44556,7 @@
     <row r="2506" ht="30" customHeight="1">
       <c r="A2506" s="16" t="inlineStr">
         <is>
-          <t>FICHA 168: 91523</t>
+          <t>FICHA 168: 71674</t>
         </is>
       </c>
       <c r="B2506" s="17" t="n"/>
@@ -44581,7 +44589,7 @@
       </c>
       <c r="B2508" s="19" t="inlineStr">
         <is>
-          <t>In relation to the selection criteria concerning experience in “Global Gateway related projects: sustainable investment, energy transition, communication and visibility, digitalization”, we kindly request clarification regarding the interpretation of the term “sustainable investment”. Could you please clarify which typologies of projects/reference</t>
+          <t>Can funding from the European Regional Development Fund (ERDF) be used as co-financing?</t>
         </is>
       </c>
       <c r="C2508" s="20" t="n"/>
@@ -44597,7 +44605,7 @@
       </c>
       <c r="B2509" s="19" t="inlineStr">
         <is>
-          <t>91523</t>
+          <t>71674</t>
         </is>
       </c>
       <c r="C2509" s="20" t="n"/>
@@ -44697,7 +44705,7 @@
       </c>
       <c r="B2516" s="19" t="inlineStr">
         <is>
-          <t>In relation to the selection criteria concerning experience in “Global Gateway related projects: sustainable investment, energy transition, communication and visibility, digitalization”, we kindly request clarification regarding the interpretation of the term “sustainable investment”. Could you please clarify which typologies of projects/reference</t>
+          <t>Can funding from the European Regional Development Fund (ERDF) be used as co-financing?</t>
         </is>
       </c>
       <c r="C2516" s="20" t="n"/>
@@ -44741,7 +44749,7 @@
       </c>
       <c r="B2519" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/91523</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71674</t>
         </is>
       </c>
       <c r="C2519" s="20" t="n"/>
@@ -44752,7 +44760,7 @@
     <row r="2521" ht="30" customHeight="1">
       <c r="A2521" s="16" t="inlineStr">
         <is>
-          <t>FICHA 169: 71674</t>
+          <t>FICHA 169: 60394</t>
         </is>
       </c>
       <c r="B2521" s="17" t="n"/>
@@ -44801,7 +44809,7 @@
       </c>
       <c r="B2524" s="19" t="inlineStr">
         <is>
-          <t>71674</t>
+          <t>60394</t>
         </is>
       </c>
       <c r="C2524" s="20" t="n"/>
@@ -44945,7 +44953,7 @@
       </c>
       <c r="B2534" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71674</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/60394</t>
         </is>
       </c>
       <c r="C2534" s="20" t="n"/>
@@ -44956,7 +44964,7 @@
     <row r="2536" ht="30" customHeight="1">
       <c r="A2536" s="16" t="inlineStr">
         <is>
-          <t>FICHA 170: 60394</t>
+          <t>FICHA 170: 885683915</t>
         </is>
       </c>
       <c r="B2536" s="17" t="n"/>
@@ -44981,7 +44989,7 @@
       <c r="E2537" s="20" t="n"/>
       <c r="F2537" s="20" t="n"/>
     </row>
-    <row r="2538" ht="45" customHeight="1">
+    <row r="2538" ht="20" customHeight="1">
       <c r="A2538" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -44989,7 +44997,7 @@
       </c>
       <c r="B2538" s="19" t="inlineStr">
         <is>
-          <t>Can funding from the European Regional Development Fund (ERDF) be used as co-financing?</t>
+          <t>SOCIAL FINANCE ASSOCIATION - ASOCIATIA PENTRU FINANTARE SOCIALA</t>
         </is>
       </c>
       <c r="C2538" s="20" t="n"/>
@@ -45005,7 +45013,7 @@
       </c>
       <c r="B2539" s="19" t="inlineStr">
         <is>
-          <t>60394</t>
+          <t>885683915</t>
         </is>
       </c>
       <c r="C2539" s="20" t="n"/>
@@ -45097,7 +45105,7 @@
       <c r="E2545" s="20" t="n"/>
       <c r="F2545" s="20" t="n"/>
     </row>
-    <row r="2546" ht="45" customHeight="1">
+    <row r="2546" ht="20" customHeight="1">
       <c r="A2546" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -45105,7 +45113,7 @@
       </c>
       <c r="B2546" s="19" t="inlineStr">
         <is>
-          <t>Can funding from the European Regional Development Fund (ERDF) be used as co-financing?</t>
+          <t>SOCIAL FINANCE ASSOCIATION - ASOCIATIA PENTRU FINANTARE SOCIALA</t>
         </is>
       </c>
       <c r="C2546" s="20" t="n"/>
@@ -45149,7 +45157,7 @@
       </c>
       <c r="B2549" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/60394</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/885683915</t>
         </is>
       </c>
       <c r="C2549" s="20" t="n"/>
@@ -45160,7 +45168,7 @@
     <row r="2551" ht="30" customHeight="1">
       <c r="A2551" s="16" t="inlineStr">
         <is>
-          <t>FICHA 171: 885683915</t>
+          <t>FICHA 171: 19429</t>
         </is>
       </c>
       <c r="B2551" s="17" t="n"/>
@@ -45185,7 +45193,7 @@
       <c r="E2552" s="20" t="n"/>
       <c r="F2552" s="20" t="n"/>
     </row>
-    <row r="2553" ht="20" customHeight="1">
+    <row r="2553" ht="45" customHeight="1">
       <c r="A2553" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -45193,7 +45201,7 @@
       </c>
       <c r="B2553" s="19" t="inlineStr">
         <is>
-          <t>SOCIAL FINANCE ASSOCIATION - ASOCIATIA PENTRU FINANTARE SOCIALA</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
         </is>
       </c>
       <c r="C2553" s="20" t="n"/>
@@ -45209,7 +45217,7 @@
       </c>
       <c r="B2554" s="19" t="inlineStr">
         <is>
-          <t>885683915</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="C2554" s="20" t="n"/>
@@ -45301,7 +45309,7 @@
       <c r="E2560" s="20" t="n"/>
       <c r="F2560" s="20" t="n"/>
     </row>
-    <row r="2561" ht="20" customHeight="1">
+    <row r="2561" ht="45" customHeight="1">
       <c r="A2561" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -45309,7 +45317,7 @@
       </c>
       <c r="B2561" s="19" t="inlineStr">
         <is>
-          <t>SOCIAL FINANCE ASSOCIATION - ASOCIATIA PENTRU FINANTARE SOCIALA</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
         </is>
       </c>
       <c r="C2561" s="20" t="n"/>
@@ -45353,7 +45361,7 @@
       </c>
       <c r="B2564" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/885683915</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19429</t>
         </is>
       </c>
       <c r="C2564" s="20" t="n"/>
@@ -45364,7 +45372,7 @@
     <row r="2566" ht="30" customHeight="1">
       <c r="A2566" s="16" t="inlineStr">
         <is>
-          <t>FICHA 172: 19429</t>
+          <t>FICHA 172: 41082</t>
         </is>
       </c>
       <c r="B2566" s="17" t="n"/>
@@ -45397,7 +45405,7 @@
       </c>
       <c r="B2568" s="19" t="inlineStr">
         <is>
-          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
+          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
         </is>
       </c>
       <c r="C2568" s="20" t="n"/>
@@ -45413,7 +45421,7 @@
       </c>
       <c r="B2569" s="19" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>41082</t>
         </is>
       </c>
       <c r="C2569" s="20" t="n"/>
@@ -45513,7 +45521,7 @@
       </c>
       <c r="B2576" s="19" t="inlineStr">
         <is>
-          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
+          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
         </is>
       </c>
       <c r="C2576" s="20" t="n"/>
@@ -45557,7 +45565,7 @@
       </c>
       <c r="B2579" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19429</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/41082</t>
         </is>
       </c>
       <c r="C2579" s="20" t="n"/>
@@ -45568,7 +45576,7 @@
     <row r="2581" ht="30" customHeight="1">
       <c r="A2581" s="16" t="inlineStr">
         <is>
-          <t>FICHA 173: 41082</t>
+          <t>FICHA 173: 85779</t>
         </is>
       </c>
       <c r="B2581" s="17" t="n"/>
@@ -45601,7 +45609,7 @@
       </c>
       <c r="B2583" s="19" t="inlineStr">
         <is>
-          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="C2583" s="20" t="n"/>
@@ -45617,7 +45625,7 @@
       </c>
       <c r="B2584" s="19" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>85779</t>
         </is>
       </c>
       <c r="C2584" s="20" t="n"/>
@@ -45717,7 +45725,7 @@
       </c>
       <c r="B2591" s="19" t="inlineStr">
         <is>
-          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="C2591" s="20" t="n"/>
@@ -45761,7 +45769,7 @@
       </c>
       <c r="B2594" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/41082</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85779</t>
         </is>
       </c>
       <c r="C2594" s="20" t="n"/>
@@ -45772,7 +45780,7 @@
     <row r="2596" ht="30" customHeight="1">
       <c r="A2596" s="16" t="inlineStr">
         <is>
-          <t>FICHA 174: 85779</t>
+          <t>FICHA 174: 85495</t>
         </is>
       </c>
       <c r="B2596" s="17" t="n"/>
@@ -45821,7 +45829,7 @@
       </c>
       <c r="B2599" s="19" t="inlineStr">
         <is>
-          <t>85779</t>
+          <t>85495</t>
         </is>
       </c>
       <c r="C2599" s="20" t="n"/>
@@ -45965,7 +45973,7 @@
       </c>
       <c r="B2609" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85779</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85495</t>
         </is>
       </c>
       <c r="C2609" s="20" t="n"/>
@@ -45976,7 +45984,7 @@
     <row r="2611" ht="30" customHeight="1">
       <c r="A2611" s="16" t="inlineStr">
         <is>
-          <t>FICHA 175: 85495</t>
+          <t>FICHA 175: d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
         </is>
       </c>
       <c r="B2611" s="17" t="n"/>
@@ -46009,7 +46017,7 @@
       </c>
       <c r="B2613" s="19" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
         </is>
       </c>
       <c r="C2613" s="20" t="n"/>
@@ -46025,7 +46033,7 @@
       </c>
       <c r="B2614" s="19" t="inlineStr">
         <is>
-          <t>85495</t>
+          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
         </is>
       </c>
       <c r="C2614" s="20" t="n"/>
@@ -46111,7 +46119,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2620" s="19" t="inlineStr"/>
+      <c r="B2620" s="19" t="inlineStr">
+        <is>
+          <t>CINEA/2026/OP/0018-PIN</t>
+        </is>
+      </c>
       <c r="C2620" s="20" t="n"/>
       <c r="D2620" s="20" t="n"/>
       <c r="E2620" s="20" t="n"/>
@@ -46125,7 +46137,7 @@
       </c>
       <c r="B2621" s="19" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
         </is>
       </c>
       <c r="C2621" s="20" t="n"/>
@@ -46169,7 +46181,7 @@
       </c>
       <c r="B2624" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85495</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
         </is>
       </c>
       <c r="C2624" s="20" t="n"/>
@@ -46180,7 +46192,7 @@
     <row r="2626" ht="30" customHeight="1">
       <c r="A2626" s="16" t="inlineStr">
         <is>
-          <t>FICHA 176: d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
+          <t>FICHA 176: 14560</t>
         </is>
       </c>
       <c r="B2626" s="17" t="n"/>
@@ -46213,7 +46225,7 @@
       </c>
       <c r="B2628" s="19" t="inlineStr">
         <is>
-          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
+          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
         </is>
       </c>
       <c r="C2628" s="20" t="n"/>
@@ -46229,7 +46241,7 @@
       </c>
       <c r="B2629" s="19" t="inlineStr">
         <is>
-          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="C2629" s="20" t="n"/>
@@ -46315,11 +46327,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2635" s="19" t="inlineStr">
-        <is>
-          <t>CINEA/2026/OP/0018-PIN</t>
-        </is>
-      </c>
+      <c r="B2635" s="19" t="inlineStr"/>
       <c r="C2635" s="20" t="n"/>
       <c r="D2635" s="20" t="n"/>
       <c r="E2635" s="20" t="n"/>
@@ -46333,7 +46341,7 @@
       </c>
       <c r="B2636" s="19" t="inlineStr">
         <is>
-          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
+          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
         </is>
       </c>
       <c r="C2636" s="20" t="n"/>
@@ -46377,7 +46385,7 @@
       </c>
       <c r="B2639" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14560</t>
         </is>
       </c>
       <c r="C2639" s="20" t="n"/>
@@ -46388,7 +46396,7 @@
     <row r="2641" ht="30" customHeight="1">
       <c r="A2641" s="16" t="inlineStr">
         <is>
-          <t>FICHA 177: 14560</t>
+          <t>FICHA 177: 104241</t>
         </is>
       </c>
       <c r="B2641" s="17" t="n"/>
@@ -46413,7 +46421,7 @@
       <c r="E2642" s="20" t="n"/>
       <c r="F2642" s="20" t="n"/>
     </row>
-    <row r="2643" ht="45" customHeight="1">
+    <row r="2643" ht="20" customHeight="1">
       <c r="A2643" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -46421,7 +46429,7 @@
       </c>
       <c r="B2643" s="19" t="inlineStr">
         <is>
-          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
+          <t>HuMUS Soil Stewards training programme</t>
         </is>
       </c>
       <c r="C2643" s="20" t="n"/>
@@ -46437,7 +46445,7 @@
       </c>
       <c r="B2644" s="19" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>104241</t>
         </is>
       </c>
       <c r="C2644" s="20" t="n"/>
@@ -46523,7 +46531,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2650" s="19" t="inlineStr"/>
+      <c r="B2650" s="19" t="inlineStr">
+        <is>
+          <t>HORIZON-MISS-2021-SOIL-02</t>
+        </is>
+      </c>
       <c r="C2650" s="20" t="n"/>
       <c r="D2650" s="20" t="n"/>
       <c r="E2650" s="20" t="n"/>
@@ -46537,7 +46549,7 @@
       </c>
       <c r="B2651" s="19" t="inlineStr">
         <is>
-          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
+          <t>HuMUS Soil Stewards training programme The HuMUS Soil Steward Training Programme is an online capacity-building course designed to strengthen knowledge and practical skills related to soil health, participatory governance and community engagement. It provides a structured syllabus, learning resources, self-assessment tools and videos showcasing</t>
         </is>
       </c>
       <c r="C2651" s="20" t="n"/>
@@ -46581,7 +46593,7 @@
       </c>
       <c r="B2654" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14560</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/104241</t>
         </is>
       </c>
       <c r="C2654" s="20" t="n"/>
@@ -46592,7 +46604,7 @@
     <row r="2656" ht="30" customHeight="1">
       <c r="A2656" s="16" t="inlineStr">
         <is>
-          <t>FICHA 178: 104241</t>
+          <t>FICHA 178: 913756976</t>
         </is>
       </c>
       <c r="B2656" s="17" t="n"/>
@@ -46625,7 +46637,7 @@
       </c>
       <c r="B2658" s="19" t="inlineStr">
         <is>
-          <t>HuMUS Soil Stewards training programme</t>
+          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
         </is>
       </c>
       <c r="C2658" s="20" t="n"/>
@@ -46641,7 +46653,7 @@
       </c>
       <c r="B2659" s="19" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>913756976</t>
         </is>
       </c>
       <c r="C2659" s="20" t="n"/>
@@ -46727,17 +46739,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2665" s="19" t="inlineStr">
-        <is>
-          <t>HORIZON-MISS-2021-SOIL-02</t>
-        </is>
-      </c>
+      <c r="B2665" s="19" t="inlineStr"/>
       <c r="C2665" s="20" t="n"/>
       <c r="D2665" s="20" t="n"/>
       <c r="E2665" s="20" t="n"/>
       <c r="F2665" s="20" t="n"/>
     </row>
-    <row r="2666" ht="45" customHeight="1">
+    <row r="2666" ht="20" customHeight="1">
       <c r="A2666" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -46745,7 +46753,7 @@
       </c>
       <c r="B2666" s="19" t="inlineStr">
         <is>
-          <t>HuMUS Soil Stewards training programme The HuMUS Soil Steward Training Programme is an online capacity-building course designed to strengthen knowledge and practical skills related to soil health, participatory governance and community engagement. It provides a structured syllabus, learning resources, self-assessment tools and videos showcasing</t>
+          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
         </is>
       </c>
       <c r="C2666" s="20" t="n"/>
@@ -46789,7 +46797,7 @@
       </c>
       <c r="B2669" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/104241</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/913756976</t>
         </is>
       </c>
       <c r="C2669" s="20" t="n"/>
@@ -46800,7 +46808,7 @@
     <row r="2671" ht="30" customHeight="1">
       <c r="A2671" s="16" t="inlineStr">
         <is>
-          <t>FICHA 179: 913756976</t>
+          <t>FICHA 179: 880759128</t>
         </is>
       </c>
       <c r="B2671" s="17" t="n"/>
@@ -46833,7 +46841,7 @@
       </c>
       <c r="B2673" s="19" t="inlineStr">
         <is>
-          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
+          <t>AYUNTAMIENTO DE FORUA</t>
         </is>
       </c>
       <c r="C2673" s="20" t="n"/>
@@ -46849,7 +46857,7 @@
       </c>
       <c r="B2674" s="19" t="inlineStr">
         <is>
-          <t>913756976</t>
+          <t>880759128</t>
         </is>
       </c>
       <c r="C2674" s="20" t="n"/>
@@ -46949,7 +46957,7 @@
       </c>
       <c r="B2681" s="19" t="inlineStr">
         <is>
-          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
+          <t>AYUNTAMIENTO DE FORUA</t>
         </is>
       </c>
       <c r="C2681" s="20" t="n"/>
@@ -46993,7 +47001,7 @@
       </c>
       <c r="B2684" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/913756976</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880759128</t>
         </is>
       </c>
       <c r="C2684" s="20" t="n"/>
@@ -47004,7 +47012,7 @@
     <row r="2686" ht="30" customHeight="1">
       <c r="A2686" s="16" t="inlineStr">
         <is>
-          <t>FICHA 180: 880759128</t>
+          <t>FICHA 180: 76912</t>
         </is>
       </c>
       <c r="B2686" s="17" t="n"/>
@@ -47029,7 +47037,7 @@
       <c r="E2687" s="20" t="n"/>
       <c r="F2687" s="20" t="n"/>
     </row>
-    <row r="2688" ht="20" customHeight="1">
+    <row r="2688" ht="45" customHeight="1">
       <c r="A2688" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -47037,7 +47045,7 @@
       </c>
       <c r="B2688" s="19" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE FORUA</t>
+          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
         </is>
       </c>
       <c r="C2688" s="20" t="n"/>
@@ -47053,7 +47061,7 @@
       </c>
       <c r="B2689" s="19" t="inlineStr">
         <is>
-          <t>880759128</t>
+          <t>76912</t>
         </is>
       </c>
       <c r="C2689" s="20" t="n"/>
@@ -47145,7 +47153,7 @@
       <c r="E2695" s="20" t="n"/>
       <c r="F2695" s="20" t="n"/>
     </row>
-    <row r="2696" ht="20" customHeight="1">
+    <row r="2696" ht="45" customHeight="1">
       <c r="A2696" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -47153,7 +47161,7 @@
       </c>
       <c r="B2696" s="19" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE FORUA</t>
+          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
         </is>
       </c>
       <c r="C2696" s="20" t="n"/>
@@ -47197,7 +47205,7 @@
       </c>
       <c r="B2699" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880759128</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/76912</t>
         </is>
       </c>
       <c r="C2699" s="20" t="n"/>
@@ -47208,7 +47216,7 @@
     <row r="2701" ht="30" customHeight="1">
       <c r="A2701" s="16" t="inlineStr">
         <is>
-          <t>FICHA 181: 76912</t>
+          <t>FICHA 181: 77665</t>
         </is>
       </c>
       <c r="B2701" s="17" t="n"/>
@@ -47241,7 +47249,7 @@
       </c>
       <c r="B2703" s="19" t="inlineStr">
         <is>
-          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
+          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
         </is>
       </c>
       <c r="C2703" s="20" t="n"/>
@@ -47257,7 +47265,7 @@
       </c>
       <c r="B2704" s="19" t="inlineStr">
         <is>
-          <t>76912</t>
+          <t>77665</t>
         </is>
       </c>
       <c r="C2704" s="20" t="n"/>
@@ -47357,7 +47365,7 @@
       </c>
       <c r="B2711" s="19" t="inlineStr">
         <is>
-          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
+          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
         </is>
       </c>
       <c r="C2711" s="20" t="n"/>
@@ -47401,7 +47409,7 @@
       </c>
       <c r="B2714" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/76912</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/77665</t>
         </is>
       </c>
       <c r="C2714" s="20" t="n"/>
@@ -47412,7 +47420,7 @@
     <row r="2716" ht="30" customHeight="1">
       <c r="A2716" s="16" t="inlineStr">
         <is>
-          <t>FICHA 182: 77665</t>
+          <t>FICHA 182: 886088211</t>
         </is>
       </c>
       <c r="B2716" s="17" t="n"/>
@@ -47437,7 +47445,7 @@
       <c r="E2717" s="20" t="n"/>
       <c r="F2717" s="20" t="n"/>
     </row>
-    <row r="2718" ht="45" customHeight="1">
+    <row r="2718" ht="20" customHeight="1">
       <c r="A2718" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -47445,7 +47453,7 @@
       </c>
       <c r="B2718" s="19" t="inlineStr">
         <is>
-          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
+          <t>Non Architecture s.r.l.</t>
         </is>
       </c>
       <c r="C2718" s="20" t="n"/>
@@ -47461,7 +47469,7 @@
       </c>
       <c r="B2719" s="19" t="inlineStr">
         <is>
-          <t>77665</t>
+          <t>886088211</t>
         </is>
       </c>
       <c r="C2719" s="20" t="n"/>
@@ -47553,7 +47561,7 @@
       <c r="E2725" s="20" t="n"/>
       <c r="F2725" s="20" t="n"/>
     </row>
-    <row r="2726" ht="45" customHeight="1">
+    <row r="2726" ht="20" customHeight="1">
       <c r="A2726" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -47561,7 +47569,7 @@
       </c>
       <c r="B2726" s="19" t="inlineStr">
         <is>
-          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
+          <t>Non Architecture s.r.l.</t>
         </is>
       </c>
       <c r="C2726" s="20" t="n"/>
@@ -47605,7 +47613,7 @@
       </c>
       <c r="B2729" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/77665</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/886088211</t>
         </is>
       </c>
       <c r="C2729" s="20" t="n"/>
@@ -47616,7 +47624,7 @@
     <row r="2731" ht="30" customHeight="1">
       <c r="A2731" s="16" t="inlineStr">
         <is>
-          <t>FICHA 183: 886088211</t>
+          <t>FICHA 183: 871698261</t>
         </is>
       </c>
       <c r="B2731" s="17" t="n"/>
@@ -47649,7 +47657,7 @@
       </c>
       <c r="B2733" s="19" t="inlineStr">
         <is>
-          <t>Non Architecture s.r.l.</t>
+          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
         </is>
       </c>
       <c r="C2733" s="20" t="n"/>
@@ -47665,7 +47673,7 @@
       </c>
       <c r="B2734" s="19" t="inlineStr">
         <is>
-          <t>886088211</t>
+          <t>871698261</t>
         </is>
       </c>
       <c r="C2734" s="20" t="n"/>
@@ -47765,7 +47773,7 @@
       </c>
       <c r="B2741" s="19" t="inlineStr">
         <is>
-          <t>Non Architecture s.r.l.</t>
+          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
         </is>
       </c>
       <c r="C2741" s="20" t="n"/>
@@ -47809,7 +47817,7 @@
       </c>
       <c r="B2744" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/886088211</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/871698261</t>
         </is>
       </c>
       <c r="C2744" s="20" t="n"/>
@@ -47820,7 +47828,7 @@
     <row r="2746" ht="30" customHeight="1">
       <c r="A2746" s="16" t="inlineStr">
         <is>
-          <t>FICHA 184: 871698261</t>
+          <t>FICHA 184: 918605133</t>
         </is>
       </c>
       <c r="B2746" s="17" t="n"/>
@@ -47853,7 +47861,7 @@
       </c>
       <c r="B2748" s="19" t="inlineStr">
         <is>
-          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
+          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
         </is>
       </c>
       <c r="C2748" s="20" t="n"/>
@@ -47869,7 +47877,7 @@
       </c>
       <c r="B2749" s="19" t="inlineStr">
         <is>
-          <t>871698261</t>
+          <t>918605133</t>
         </is>
       </c>
       <c r="C2749" s="20" t="n"/>
@@ -47969,7 +47977,7 @@
       </c>
       <c r="B2756" s="19" t="inlineStr">
         <is>
-          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
+          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
         </is>
       </c>
       <c r="C2756" s="20" t="n"/>
@@ -48013,7 +48021,7 @@
       </c>
       <c r="B2759" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/871698261</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/918605133</t>
         </is>
       </c>
       <c r="C2759" s="20" t="n"/>
@@ -48024,7 +48032,7 @@
     <row r="2761" ht="30" customHeight="1">
       <c r="A2761" s="16" t="inlineStr">
         <is>
-          <t>FICHA 185: 918605133</t>
+          <t>FICHA 185: 485</t>
         </is>
       </c>
       <c r="B2761" s="17" t="n"/>
@@ -48049,7 +48057,7 @@
       <c r="E2762" s="20" t="n"/>
       <c r="F2762" s="20" t="n"/>
     </row>
-    <row r="2763" ht="20" customHeight="1">
+    <row r="2763" ht="45" customHeight="1">
       <c r="A2763" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -48057,7 +48065,7 @@
       </c>
       <c r="B2763" s="19" t="inlineStr">
         <is>
-          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
+          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
         </is>
       </c>
       <c r="C2763" s="20" t="n"/>
@@ -48073,7 +48081,7 @@
       </c>
       <c r="B2764" s="19" t="inlineStr">
         <is>
-          <t>918605133</t>
+          <t>485</t>
         </is>
       </c>
       <c r="C2764" s="20" t="n"/>
@@ -48165,7 +48173,7 @@
       <c r="E2770" s="20" t="n"/>
       <c r="F2770" s="20" t="n"/>
     </row>
-    <row r="2771" ht="20" customHeight="1">
+    <row r="2771" ht="45" customHeight="1">
       <c r="A2771" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -48173,7 +48181,7 @@
       </c>
       <c r="B2771" s="19" t="inlineStr">
         <is>
-          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
+          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
         </is>
       </c>
       <c r="C2771" s="20" t="n"/>
@@ -48217,7 +48225,7 @@
       </c>
       <c r="B2774" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/918605133</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/485</t>
         </is>
       </c>
       <c r="C2774" s="20" t="n"/>
@@ -48228,7 +48236,7 @@
     <row r="2776" ht="30" customHeight="1">
       <c r="A2776" s="16" t="inlineStr">
         <is>
-          <t>FICHA 186: 485</t>
+          <t>FICHA 186: 892931076</t>
         </is>
       </c>
       <c r="B2776" s="17" t="n"/>
@@ -48253,7 +48261,7 @@
       <c r="E2777" s="20" t="n"/>
       <c r="F2777" s="20" t="n"/>
     </row>
-    <row r="2778" ht="45" customHeight="1">
+    <row r="2778" ht="20" customHeight="1">
       <c r="A2778" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -48261,7 +48269,7 @@
       </c>
       <c r="B2778" s="19" t="inlineStr">
         <is>
-          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="C2778" s="20" t="n"/>
@@ -48277,7 +48285,7 @@
       </c>
       <c r="B2779" s="19" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>892931076</t>
         </is>
       </c>
       <c r="C2779" s="20" t="n"/>
@@ -48369,7 +48377,7 @@
       <c r="E2785" s="20" t="n"/>
       <c r="F2785" s="20" t="n"/>
     </row>
-    <row r="2786" ht="45" customHeight="1">
+    <row r="2786" ht="20" customHeight="1">
       <c r="A2786" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -48377,7 +48385,7 @@
       </c>
       <c r="B2786" s="19" t="inlineStr">
         <is>
-          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="C2786" s="20" t="n"/>
@@ -48421,7 +48429,7 @@
       </c>
       <c r="B2789" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/485</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/892931076</t>
         </is>
       </c>
       <c r="C2789" s="20" t="n"/>
@@ -48432,7 +48440,7 @@
     <row r="2791" ht="30" customHeight="1">
       <c r="A2791" s="16" t="inlineStr">
         <is>
-          <t>FICHA 187: 892931076</t>
+          <t>FICHA 187: 936518123</t>
         </is>
       </c>
       <c r="B2791" s="17" t="n"/>
@@ -48465,7 +48473,7 @@
       </c>
       <c r="B2793" s="19" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="C2793" s="20" t="n"/>
@@ -48481,7 +48489,7 @@
       </c>
       <c r="B2794" s="19" t="inlineStr">
         <is>
-          <t>892931076</t>
+          <t>936518123</t>
         </is>
       </c>
       <c r="C2794" s="20" t="n"/>
@@ -48581,7 +48589,7 @@
       </c>
       <c r="B2801" s="19" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="C2801" s="20" t="n"/>
@@ -48625,7 +48633,7 @@
       </c>
       <c r="B2804" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/892931076</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/936518123</t>
         </is>
       </c>
       <c r="C2804" s="20" t="n"/>
@@ -48636,7 +48644,7 @@
     <row r="2806" ht="30" customHeight="1">
       <c r="A2806" s="16" t="inlineStr">
         <is>
-          <t>FICHA 188: 936518123</t>
+          <t>FICHA 188: EUS-79710</t>
         </is>
       </c>
       <c r="B2806" s="17" t="n"/>
@@ -48653,7 +48661,7 @@
       </c>
       <c r="B2807" s="19" t="inlineStr">
         <is>
-          <t>🇪🇺 Europa</t>
+          <t>🟢 Euskadi</t>
         </is>
       </c>
       <c r="C2807" s="20" t="n"/>
@@ -48661,7 +48669,7 @@
       <c r="E2807" s="20" t="n"/>
       <c r="F2807" s="20" t="n"/>
     </row>
-    <row r="2808" ht="20" customHeight="1">
+    <row r="2808" ht="45" customHeight="1">
       <c r="A2808" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -48669,7 +48677,7 @@
       </c>
       <c r="B2808" s="19" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>Mantenimiento y soporte de la infraestructura hardware y software de los sistemas IBM del Ayuntamiento de Vitoria-Gasteiz</t>
         </is>
       </c>
       <c r="C2808" s="20" t="n"/>
@@ -48685,7 +48693,7 @@
       </c>
       <c r="B2809" s="19" t="inlineStr">
         <is>
-          <t>936518123</t>
+          <t>EUS-79710</t>
         </is>
       </c>
       <c r="C2809" s="20" t="n"/>
@@ -48699,7 +48707,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B2810" s="19" t="inlineStr"/>
+      <c r="B2810" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
       <c r="C2810" s="20" t="n"/>
       <c r="D2810" s="20" t="n"/>
       <c r="E2810" s="20" t="n"/>
@@ -48713,7 +48725,7 @@
       </c>
       <c r="B2811" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="C2811" s="20" t="n"/>
@@ -48757,7 +48769,7 @@
       </c>
       <c r="B2814" s="19" t="inlineStr">
         <is>
-          <t>No disponible</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2814" s="20" t="n"/>
@@ -48785,7 +48797,7 @@
       </c>
       <c r="B2816" s="19" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
       <c r="C2816" s="20" t="n"/>
@@ -48799,7 +48811,11 @@
           <t>Tags</t>
         </is>
       </c>
-      <c r="B2817" s="19" t="inlineStr"/>
+      <c r="B2817" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
       <c r="C2817" s="20" t="n"/>
       <c r="D2817" s="20" t="n"/>
       <c r="E2817" s="20" t="n"/>
@@ -48811,9 +48827,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2818" s="19" t="inlineStr">
-        <is>
-          <t>INFO — Revisar relevancia para el Ayuntamiento de Bilbao.</t>
+      <c r="B2818" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUY ALTA — </t>
         </is>
       </c>
       <c r="C2818" s="20" t="n"/>
@@ -48829,7 +48845,7 @@
       </c>
       <c r="B2819" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/936518123</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/mantenimiento-y-soporte-infraestructura-hardware-y-software-sistemas-ibm-del-ayuntamiento-vitoria-gasteiz/expjaso743459/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2819" s="20" t="n"/>
@@ -48840,7 +48856,7 @@
     <row r="2821" ht="30" customHeight="1">
       <c r="A2821" s="16" t="inlineStr">
         <is>
-          <t>FICHA 189: EUS-71228</t>
+          <t>FICHA 189: EUS-98457</t>
         </is>
       </c>
       <c r="B2821" s="17" t="n"/>
@@ -48873,7 +48889,7 @@
       </c>
       <c r="B2823" s="19" t="inlineStr">
         <is>
-          <t>Servicio de conservación y mantenimiento de las zonas verdes municipales (arbustos y setos, jardineras, siega de caminos, arbolado y taludes) del municipio de Basauri.</t>
+          <t>Suministro de licencias de uso de una plataforma digital para la aplicación, corrección y generación de informes automatizados de test psicotécnicos, orientados a los procesos de selección de personal</t>
         </is>
       </c>
       <c r="C2823" s="20" t="n"/>
@@ -48889,7 +48905,7 @@
       </c>
       <c r="B2824" s="19" t="inlineStr">
         <is>
-          <t>EUS-71228</t>
+          <t>EUS-98457</t>
         </is>
       </c>
       <c r="C2824" s="20" t="n"/>
@@ -49041,7 +49057,7 @@
       </c>
       <c r="B2834" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-conservacion-y-mantenimiento-zonas-verdes-municipales-arbustos-y-setos-jardineras-siega-caminos-arbolado-y-taludes-del-municipio-basauri/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-licencias-uso-plataforma-digital-aplicacion-correccion-y-generacion-informes-automatizados-test-psicotecnicos-orientados-procesos-seleccion-personal-bilbaotik/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2834" s="20" t="n"/>
@@ -49052,7 +49068,7 @@
     <row r="2836" ht="30" customHeight="1">
       <c r="A2836" s="16" t="inlineStr">
         <is>
-          <t>FICHA 190: EUS-36680</t>
+          <t>FICHA 190: EUS-10114</t>
         </is>
       </c>
       <c r="B2836" s="17" t="n"/>
@@ -49085,7 +49101,7 @@
       </c>
       <c r="B2838" s="19" t="inlineStr">
         <is>
-          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfronterizos de energía renovable. Se prevé una nueva convocatoria para noviembre de 2026.</t>
+          <t>Servicio de recogida y gestión de ropa usada, otros textiles y objetos reutilizables de pequeño tamaño en los municipios de Urola Kosta. Contratación reservada (Disposición Adicional 4ª LCSP)</t>
         </is>
       </c>
       <c r="C2838" s="20" t="n"/>
@@ -49101,7 +49117,7 @@
       </c>
       <c r="B2839" s="19" t="inlineStr">
         <is>
-          <t>EUS-36680</t>
+          <t>EUS-10114</t>
         </is>
       </c>
       <c r="C2839" s="20" t="n"/>
@@ -49177,7 +49193,7 @@
       </c>
       <c r="B2844" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2844" s="20" t="n"/>
@@ -49235,9 +49251,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2848" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALTA — </t>
+      <c r="B2848" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUY ALTA — </t>
         </is>
       </c>
       <c r="C2848" s="20" t="n"/>
@@ -49253,7 +49269,7 @@
       </c>
       <c r="B2849" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/cefmugazgaindikoberriztag/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-recogida-y-gestion-ropa-usada-otros-textiles-y-objetos-reutilizables-pequeno-tamano-municipios-urola-kosta-contratacion-reservada-disposicion-adicional-4-lcsp/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2849" s="20" t="n"/>
@@ -49264,7 +49280,7 @@
     <row r="2851" ht="30" customHeight="1">
       <c r="A2851" s="16" t="inlineStr">
         <is>
-          <t>FICHA 191: EUS-57715</t>
+          <t>FICHA 191: EUS-47702</t>
         </is>
       </c>
       <c r="B2851" s="17" t="n"/>
@@ -49297,7 +49313,7 @@
       </c>
       <c r="B2853" s="19" t="inlineStr">
         <is>
-          <t>Servicio de implementación de un programa de incentivos a la movilidad sostenible mediante la plataforma de Ciclogreen</t>
+          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfronterizos de energía renovable. Se prevé una nueva convocatoria para noviembre de 2026.</t>
         </is>
       </c>
       <c r="C2853" s="20" t="n"/>
@@ -49313,7 +49329,7 @@
       </c>
       <c r="B2854" s="19" t="inlineStr">
         <is>
-          <t>EUS-57715</t>
+          <t>EUS-47702</t>
         </is>
       </c>
       <c r="C2854" s="20" t="n"/>
@@ -49389,7 +49405,7 @@
       </c>
       <c r="B2859" s="19" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="C2859" s="20" t="n"/>
@@ -49465,7 +49481,7 @@
       </c>
       <c r="B2864" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-implementacion-programa-incentivos-movilidad-sostenible-mediante-plataforma-ciclogreen/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/cefmugazgaindikoberriztag/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2864" s="20" t="n"/>
@@ -49476,7 +49492,7 @@
     <row r="2866" ht="30" customHeight="1">
       <c r="A2866" s="16" t="inlineStr">
         <is>
-          <t>FICHA 192: EUS-03003</t>
+          <t>FICHA 192: EUS-35735</t>
         </is>
       </c>
       <c r="B2866" s="17" t="n"/>
@@ -49525,7 +49541,7 @@
       </c>
       <c r="B2869" s="19" t="inlineStr">
         <is>
-          <t>EUS-03003</t>
+          <t>EUS-35735</t>
         </is>
       </c>
       <c r="C2869" s="20" t="n"/>
@@ -49688,7 +49704,7 @@
     <row r="2881" ht="30" customHeight="1">
       <c r="A2881" s="16" t="inlineStr">
         <is>
-          <t>FICHA 193: EUS-89928</t>
+          <t>FICHA 193: EUS-91770</t>
         </is>
       </c>
       <c r="B2881" s="17" t="n"/>
@@ -49737,7 +49753,7 @@
       </c>
       <c r="B2884" s="19" t="inlineStr">
         <is>
-          <t>EUS-89928</t>
+          <t>EUS-91770</t>
         </is>
       </c>
       <c r="C2884" s="20" t="n"/>
@@ -49900,7 +49916,7 @@
     <row r="2896" ht="30" customHeight="1">
       <c r="A2896" s="16" t="inlineStr">
         <is>
-          <t>FICHA 194: EUS-14280</t>
+          <t>FICHA 194: EUS-78388</t>
         </is>
       </c>
       <c r="B2896" s="17" t="n"/>
@@ -49925,7 +49941,7 @@
       <c r="E2897" s="20" t="n"/>
       <c r="F2897" s="20" t="n"/>
     </row>
-    <row r="2898" ht="45" customHeight="1">
+    <row r="2898" ht="20" customHeight="1">
       <c r="A2898" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -49933,7 +49949,7 @@
       </c>
       <c r="B2898" s="19" t="inlineStr">
         <is>
-          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado una Alianza para las Cadenas de Valor Industriales Marítimas, que contempla la soberanía tecnológica y de suministros, la defensa, la compe</t>
+          <t>Renovación del alumbrado</t>
         </is>
       </c>
       <c r="C2898" s="20" t="n"/>
@@ -49949,7 +49965,7 @@
       </c>
       <c r="B2899" s="19" t="inlineStr">
         <is>
-          <t>EUS-14280</t>
+          <t>EUS-78388</t>
         </is>
       </c>
       <c r="C2899" s="20" t="n"/>
@@ -50025,7 +50041,7 @@
       </c>
       <c r="B2904" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2904" s="20" t="n"/>
@@ -50101,7 +50117,7 @@
       </c>
       <c r="B2909" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/itsasindustriarakolankide/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/renovacion-del-alumbrado/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2909" s="20" t="n"/>
@@ -50112,7 +50128,7 @@
     <row r="2911" ht="30" customHeight="1">
       <c r="A2911" s="16" t="inlineStr">
         <is>
-          <t>FICHA 195: EUS-05836</t>
+          <t>FICHA 195: EUS-89916</t>
         </is>
       </c>
       <c r="B2911" s="17" t="n"/>
@@ -50137,7 +50153,7 @@
       <c r="E2912" s="20" t="n"/>
       <c r="F2912" s="20" t="n"/>
     </row>
-    <row r="2913" ht="45" customHeight="1">
+    <row r="2913" ht="20" customHeight="1">
       <c r="A2913" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -50145,7 +50161,7 @@
       </c>
       <c r="B2913" s="19" t="inlineStr">
         <is>
-          <t>Dirección facultativa de las obras de reverdecimiento del Cantón de Anorbin en el marco del Proyecto LIFE I P URBAN KLIMA 2050 (life18 IPC/ES/000001)</t>
+          <t>Arrendamiento de la vivienda municipal sita en INtxaurtxueta 26-2º derecha</t>
         </is>
       </c>
       <c r="C2913" s="20" t="n"/>
@@ -50161,7 +50177,7 @@
       </c>
       <c r="B2914" s="19" t="inlineStr">
         <is>
-          <t>EUS-05836</t>
+          <t>EUS-89916</t>
         </is>
       </c>
       <c r="C2914" s="20" t="n"/>
@@ -50313,7 +50329,7 @@
       </c>
       <c r="B2924" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/direccion-facultativa-obras-reverdecimiento-del-canton-anorbin-marco-del-proyecto-life-i-p-urban-klima-2050-life18-ipc-es-000001/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/arrendamiento-vivienda-municipal-sita-intxaurtxueta-26-2-derecha/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2924" s="20" t="n"/>
@@ -50324,7 +50340,7 @@
     <row r="2926" ht="30" customHeight="1">
       <c r="A2926" s="16" t="inlineStr">
         <is>
-          <t>FICHA 196: EUS-20008</t>
+          <t>FICHA 196: EUS-00652</t>
         </is>
       </c>
       <c r="B2926" s="17" t="n"/>
@@ -50349,7 +50365,7 @@
       <c r="E2927" s="20" t="n"/>
       <c r="F2927" s="20" t="n"/>
     </row>
-    <row r="2928" ht="20" customHeight="1">
+    <row r="2928" ht="45" customHeight="1">
       <c r="A2928" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -50357,7 +50373,7 @@
       </c>
       <c r="B2928" s="19" t="inlineStr">
         <is>
-          <t>Suministro de equipamiento e instalación de Parque Infantil en Bedia</t>
+          <t>Obras de reverdecimiento del casco medieval de Vitoria-Gasteiz. Proyecto LIFE I P Urban Klima 2050 (LIFE18 IPC/ES/000001) - Proyecto de ejecución cantón Anorbin.</t>
         </is>
       </c>
       <c r="C2928" s="20" t="n"/>
@@ -50373,7 +50389,7 @@
       </c>
       <c r="B2929" s="19" t="inlineStr">
         <is>
-          <t>EUS-20008</t>
+          <t>EUS-00652</t>
         </is>
       </c>
       <c r="C2929" s="20" t="n"/>
@@ -50525,7 +50541,7 @@
       </c>
       <c r="B2939" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-equipamiento-e-instalacion-parque-infantil-bedia/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/obras-reverdecimiento-del-casco-medieval-vitoria-gasteiz-proyecto-life-i-p-urban-klima-2050-life18-ipc-es-000001-proyecto-ejecucion-canton-anorbin/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2939" s="20" t="n"/>
@@ -50536,7 +50552,7 @@
     <row r="2941" ht="30" customHeight="1">
       <c r="A2941" s="16" t="inlineStr">
         <is>
-          <t>FICHA 197: EUS-26417</t>
+          <t>FICHA 197: EUS-83587</t>
         </is>
       </c>
       <c r="B2941" s="17" t="n"/>
@@ -50569,7 +50585,7 @@
       </c>
       <c r="B2943" s="19" t="inlineStr">
         <is>
-          <t>Recogida, grabación y tratamiento básico de la información de la operación continua ?Encuesta de población en relación con la actividad (PRA)? y sus módulos ?Encuesta sobre la sociedad de la informaci</t>
+          <t>Material de construcción para prácticas de 1º de mantenimiento de viviendas del imfpb de eibar.</t>
         </is>
       </c>
       <c r="C2943" s="20" t="n"/>
@@ -50585,7 +50601,7 @@
       </c>
       <c r="B2944" s="19" t="inlineStr">
         <is>
-          <t>EUS-26417</t>
+          <t>EUS-83587</t>
         </is>
       </c>
       <c r="C2944" s="20" t="n"/>
@@ -50737,7 +50753,7 @@
       </c>
       <c r="B2954" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/recogida-grabacion-y-tratamiento-basico-informacion-operacion-continua-encuesta-poblacion-relacion-actividad-pra-y-sus-modulos-encuesta-sociedad-informacion-familias-esif-y-encuesta-conciliacion-vida-laboral-familiar-y-personal-cvl-2027-2028/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/material-construccion-practicas-1-mantenimiento-viviendas-del-imfpb-eibar/expgeeibar21214/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2954" s="20" t="n"/>
@@ -57237,12 +57253,12 @@
     <row r="109" ht="28" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>Considering the increasing importance of ecosystem restorati</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr"/>
@@ -57269,12 +57285,12 @@
     <row r="110" ht="28" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restorati</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr"/>
@@ -57301,12 +57317,12 @@
     <row r="111" ht="28" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaam</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr"/>
@@ -57333,12 +57349,12 @@
     <row r="112" ht="28" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaam</t>
+          <t>Should the selected port related to the Cities Mission be on</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr"/>
@@ -57365,12 +57381,12 @@
     <row r="113" ht="28" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be on</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr"/>
@@ -57397,12 +57413,12 @@
     <row r="114" ht="28" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submi</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr"/>
@@ -57429,12 +57445,12 @@
     <row r="115" ht="28" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submi</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr"/>
@@ -57461,12 +57477,12 @@
     <row r="116" ht="28" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Inter-institutional single framework contract to support the</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr"/>
@@ -57493,12 +57509,12 @@
     <row r="117" ht="28" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do loca</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr"/>
@@ -57525,12 +57541,12 @@
     <row r="118" ht="28" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do loca</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr"/>
@@ -57557,12 +57573,12 @@
     <row r="119" ht="28" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr"/>
@@ -57589,12 +57605,12 @@
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr"/>
@@ -57621,12 +57637,12 @@
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr"/>
@@ -57653,12 +57669,12 @@
     <row r="122" ht="28" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>In the paragraphs following the sentence "Any rejection by F</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr"/>
@@ -57685,12 +57701,12 @@
     <row r="123" ht="28" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by F</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr"/>
@@ -57717,12 +57733,12 @@
     <row r="124" ht="28" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr"/>
@@ -57749,12 +57765,12 @@
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr"/>
@@ -57781,12 +57797,12 @@
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14</t>
+          <t>The topic requires to "include a draft plan for joint action</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr"/>
@@ -57813,12 +57829,12 @@
     <row r="127" ht="28" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>PPPA2027</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint action</t>
+          <t xml:space="preserve">Interreg Governance Facility initiative to support Interreg </t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr"/>
@@ -57845,12 +57861,12 @@
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>PPPA2027</t>
+          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interreg Governance Facility initiative to support Interreg </t>
+          <t>Border regions Peer exchange on solving border obstacles</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr"/>
@@ -57877,7 +57893,7 @@
     <row r="129" ht="28" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
+          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
@@ -57909,12 +57925,12 @@
     <row r="130" ht="28" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
+          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Border regions Peer exchange on solving border obstacles</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr"/>
@@ -57941,12 +57957,12 @@
     <row r="131" ht="28" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>886623263</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr"/>
@@ -57973,12 +57989,12 @@
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>886623263</t>
+          <t>877314852</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr"/>
@@ -58005,12 +58021,12 @@
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>877314852</t>
+          <t>884174595</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr"/>
@@ -58037,12 +58053,12 @@
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>884174595</t>
+          <t>900546740</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>Department of International Cooperation and European Integra</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr"/>
@@ -58069,12 +58085,12 @@
     <row r="135" ht="28" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>900546740</t>
+          <t>941945952</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integra</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr"/>
@@ -58101,12 +58117,12 @@
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>941945952</t>
+          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160A</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr"/>
@@ -58133,12 +58149,12 @@
     <row r="137" ht="28" customHeight="1">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>ERDFTA</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160A</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr"/>
@@ -58165,12 +58181,12 @@
     <row r="138" ht="28" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>ERDFTA</t>
+          <t>90488</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr"/>
@@ -58197,12 +58213,12 @@
     <row r="139" ht="28" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to</t>
+          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries conside</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr"/>
@@ -58229,12 +58245,12 @@
     <row r="140" ht="28" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries conside</t>
+          <t>A project intends to build an innovative renewable energy pr</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr"/>
@@ -58293,12 +58309,12 @@
     <row r="142" ht="28" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>n00brugy</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy pr</t>
+          <t>Joana SANTIAGO</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr"/>
@@ -58325,12 +58341,12 @@
     <row r="143" ht="28" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>n00brugy</t>
+          <t>n00kmonh</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Joana SANTIAGO</t>
+          <t>Mrs LARA MARIA CERDAN AZNAR</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr"/>
@@ -58357,12 +58373,12 @@
     <row r="144" ht="28" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>n00kmonh</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Mrs LARA MARIA CERDAN AZNAR</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr"/>
@@ -58389,12 +58405,12 @@
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>937468917</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>MS Elena Jauregui Baldassini</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUT</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr"/>
@@ -58421,12 +58437,12 @@
     <row r="146" ht="28" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>937468917</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUT</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under L</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr"/>
@@ -58453,12 +58469,12 @@
     <row r="147" ht="28" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>n002cet5</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under L</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr"/>
@@ -58485,12 +58501,12 @@
     <row r="148" ht="28" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>n002cet5</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third count</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr"/>
@@ -58517,12 +58533,12 @@
     <row r="149" ht="28" customHeight="1">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>885233544</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third count</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr"/>
@@ -58549,12 +58565,12 @@
     <row r="150" ht="28" customHeight="1">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>885233544</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, w</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr"/>
@@ -58581,12 +58597,12 @@
     <row r="151" ht="28" customHeight="1">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, w</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMAR</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr"/>
@@ -58613,12 +58629,12 @@
     <row r="152" ht="28" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMAR</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr"/>
@@ -58645,12 +58661,12 @@
     <row r="153" ht="28" customHeight="1">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project</t>
+          <t>Strategies and tools for decarbonising EU's heating and cool</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr"/>
@@ -58677,12 +58693,12 @@
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cool</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a propo</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr"/>
@@ -58709,12 +58725,12 @@
     <row r="155" ht="28" customHeight="1">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a propo</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr"/>
@@ -58741,12 +58757,12 @@
     <row r="156" ht="28" customHeight="1">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4</t>
+          <t>Which kind of network optimisation should be covered? Is the</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr"/>
@@ -58773,12 +58789,12 @@
     <row r="157" ht="28" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>956926438</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is the</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr"/>
@@ -58805,12 +58821,12 @@
     <row r="158" ht="28" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>956926438</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-20</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr"/>
@@ -58869,12 +58885,12 @@
     <row r="160" ht="28" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>953552487</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr"/>
@@ -58901,12 +58917,12 @@
     <row r="161" ht="28" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr"/>
@@ -58933,12 +58949,12 @@
     <row r="162" ht="28" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>876983694</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr"/>
@@ -58965,12 +58981,12 @@
     <row r="163" ht="28" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>876983694</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr"/>
@@ -58997,12 +59013,12 @@
     <row r="164" ht="28" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>935134321</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS S</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr"/>
@@ -59029,12 +59045,12 @@
     <row r="165" ht="28" customHeight="1">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>935134321</t>
+          <t>883154834</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS S</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr"/>
@@ -59061,12 +59077,12 @@
     <row r="166" ht="28" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>883154834</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t xml:space="preserve">1. Could the Contracting Authority clarify the scope of the </t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr"/>
@@ -59093,12 +59109,12 @@
     <row r="167" ht="28" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Could the Contracting Authority clarify the scope of the </t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics u</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr"/>
@@ -59125,12 +59141,12 @@
     <row r="168" ht="28" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>91523</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics u</t>
+          <t xml:space="preserve">In relation to the selection criteria concerning experience </t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr"/>
@@ -59157,12 +59173,12 @@
     <row r="169" ht="28" customHeight="1">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>91523</t>
+          <t>71674</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">In relation to the selection criteria concerning experience </t>
+          <t>Can funding from the European Regional Development Fund (ERD</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr"/>
@@ -59189,7 +59205,7 @@
     <row r="170" ht="28" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>71674</t>
+          <t>60394</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
@@ -59221,12 +59237,12 @@
     <row r="171" ht="28" customHeight="1">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>60394</t>
+          <t>885683915</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>Can funding from the European Regional Development Fund (ERD</t>
+          <t>SOCIAL FINANCE ASSOCIATION - ASOCIATIA PENTRU FINANTARE SOCI</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr"/>
@@ -59253,12 +59269,12 @@
     <row r="172" ht="28" customHeight="1">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>885683915</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>SOCIAL FINANCE ASSOCIATION - ASOCIATIA PENTRU FINANTARE SOCI</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, I</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr"/>
@@ -59285,12 +59301,12 @@
     <row r="173" ht="28" customHeight="1">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>41082</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, I</t>
+          <t>Is a social impact fund based in Member States or listed EEA</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr"/>
@@ -59317,12 +59333,12 @@
     <row r="174" ht="28" customHeight="1">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>85779</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>Is a social impact fund based in Member States or listed EEA</t>
+          <t>Should we focus on one type of environment, or consider ocea</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr"/>
@@ -59349,7 +59365,7 @@
     <row r="175" ht="28" customHeight="1">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>85779</t>
+          <t>85495</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
@@ -59381,12 +59397,12 @@
     <row r="176" ht="28" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>85495</t>
+          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider ocea</t>
+          <t>Services to Communities to support the achievement of the ob</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr"/>
@@ -59413,12 +59429,12 @@
     <row r="177" ht="28" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>Services to Communities to support the achievement of the ob</t>
+          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of rel</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr"/>
@@ -59445,12 +59461,12 @@
     <row r="178" ht="28" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>104241</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of rel</t>
+          <t>HuMUS Soil Stewards training programme</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr"/>
@@ -59477,12 +59493,12 @@
     <row r="179" ht="28" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>913756976</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>HuMUS Soil Stewards training programme</t>
+          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr"/>
@@ -59509,12 +59525,12 @@
     <row r="180" ht="28" customHeight="1">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>913756976</t>
+          <t>880759128</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
+          <t>AYUNTAMIENTO DE FORUA</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr"/>
@@ -59541,12 +59557,12 @@
     <row r="181" ht="28" customHeight="1">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>880759128</t>
+          <t>76912</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE FORUA</t>
+          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr"/>
@@ -59573,12 +59589,12 @@
     <row r="182" ht="28" customHeight="1">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>76912</t>
+          <t>77665</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The</t>
+          <t>The call requires to ‘Demonstrate the innovative solution(s)</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr"/>
@@ -59605,12 +59621,12 @@
     <row r="183" ht="28" customHeight="1">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>77665</t>
+          <t>886088211</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>The call requires to ‘Demonstrate the innovative solution(s)</t>
+          <t>Non Architecture s.r.l.</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr"/>
@@ -59637,12 +59653,12 @@
     <row r="184" ht="28" customHeight="1">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>886088211</t>
+          <t>871698261</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>Non Architecture s.r.l.</t>
+          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr"/>
@@ -59669,12 +59685,12 @@
     <row r="185" ht="28" customHeight="1">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>871698261</t>
+          <t>918605133</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd</t>
+          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr"/>
@@ -59701,12 +59717,12 @@
     <row r="186" ht="28" customHeight="1">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>918605133</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
+          <t>Can an International European Interest Organisation (IEIO) p</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr"/>
@@ -59733,12 +59749,12 @@
     <row r="187" ht="28" customHeight="1">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>892931076</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>Can an International European Interest Organisation (IEIO) p</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr"/>
@@ -59765,12 +59781,12 @@
     <row r="188" ht="28" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>892931076</t>
+          <t>936518123</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr"/>
@@ -59797,24 +59813,28 @@
     <row r="189" ht="28" customHeight="1">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>936518123</t>
+          <t>EUS-79710</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
-        </is>
-      </c>
-      <c r="C189" s="6" t="inlineStr"/>
+          <t>Mantenimiento y soporte de la infraestructura hardware y sof</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr"/>
       <c r="F189" s="25" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>MUY ALTA</t>
         </is>
       </c>
       <c r="G189" s="6" t="inlineStr"/>
@@ -59829,12 +59849,12 @@
     <row r="190" ht="28" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>EUS-71228</t>
+          <t>EUS-98457</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>Servicio de conservación y mantenimiento de las zonas verdes</t>
+          <t>Suministro de licencias de uso de una plataforma digital par</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
@@ -59865,12 +59885,12 @@
     <row r="191" ht="28" customHeight="1">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>EUS-36680</t>
+          <t>EUS-10114</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfront</t>
+          <t>Servicio de recogida y gestión de ropa usada, otros textiles</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
@@ -59886,7 +59906,7 @@
       <c r="E191" s="6" t="inlineStr"/>
       <c r="F191" s="25" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MUY ALTA</t>
         </is>
       </c>
       <c r="G191" s="6" t="inlineStr"/>
@@ -59901,12 +59921,12 @@
     <row r="192" ht="28" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>EUS-57715</t>
+          <t>EUS-47702</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Servicio de implementación de un programa de incentivos a la</t>
+          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfront</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
@@ -59937,7 +59957,7 @@
     <row r="193" ht="28" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>EUS-03003</t>
+          <t>EUS-35735</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
@@ -59973,7 +59993,7 @@
     <row r="194" ht="28" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>EUS-89928</t>
+          <t>EUS-91770</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
@@ -60009,12 +60029,12 @@
     <row r="195" ht="28" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>EUS-14280</t>
+          <t>EUS-78388</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>En una nueva Estrategia MARÍTIMA INDUSTRIAL, la UE ha creado</t>
+          <t>Renovación del alumbrado</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -60045,12 +60065,12 @@
     <row r="196" ht="28" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>EUS-05836</t>
+          <t>EUS-89916</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Dirección facultativa de las obras de reverdecimiento del Ca</t>
+          <t>Arrendamiento de la vivienda municipal sita en INtxaurtxueta</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -60081,12 +60101,12 @@
     <row r="197" ht="28" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>EUS-20008</t>
+          <t>EUS-00652</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro de equipamiento e instalación de Parque Infantil </t>
+          <t>Obras de reverdecimiento del casco medieval de Vitoria-Gaste</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -60117,12 +60137,12 @@
     <row r="198" ht="28" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>EUS-26417</t>
+          <t>EUS-83587</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Recogida, grabación y tratamiento básico de la información d</t>
+          <t>Material de construcción para prácticas de 1º de mantenimien</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">

--- a/docs/resultados_convocatorias.xlsx
+++ b/docs/resultados_convocatorias.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Recursos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$185</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -78,13 +78,13 @@
     <font>
       <name val="Leelawadee UI"/>
       <b val="1"/>
-      <color rgb="00DC2626"/>
+      <color rgb="00065F46"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Leelawadee UI"/>
       <b val="1"/>
-      <color rgb="00065F46"/>
+      <color rgb="00DC2626"/>
       <sz val="10"/>
     </font>
     <font>
@@ -150,17 +150,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00065F46"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -246,11 +246,11 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -290,8 +290,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -685,7 +685,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 03/10/2026 10:46 - 179 convocatorias - 18 nuevas</t>
+          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 04/10/2026 11:25 - 182 convocatorias - 8 nuevas</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Empowering SMEs through Renewable Energy Communities for a Sustainable Future</t>
+          <t>Assisting the Agrifood sector in the uptake of renewable energy communities</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Empowering SMEs through Renewable Energy Communities for a Sustainable Future</t>
+          <t>Assisting the Agrifood sector in the uptake of renewable energy communities</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr"/>
@@ -3294,19 +3294,15 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>897315282</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Social Innovation Fund</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr"/>
       <c r="E59" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -3315,19 +3311,19 @@
       <c r="F59" s="6" t="inlineStr"/>
       <c r="G59" s="6" t="inlineStr"/>
       <c r="H59" s="6" t="inlineStr"/>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>INFO</t>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Revisar relevancia para el Ayuntamiento de Bilbao.</t>
+          <t>Aplicable a Petronor/Repsol (Muskiz) y Puerto de Bilbao.</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Social Innovation Fund</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr"/>
@@ -3345,15 +3341,19 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr"/>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cove</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr"/>
@@ -3439,12 +3439,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr"/>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cove</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr"/>
@@ -3486,12 +3486,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>d875bf4d-fe32-473e-a204-dcb7ff95d772-PIN</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Operation, maintenance, improvement and promotion of the BUILD UP interactive web portal</t>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr"/>
@@ -3515,14 +3515,10 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>Operation, maintenance, improvement and promotion of the BUILD UP interactive web portal</t>
-        </is>
-      </c>
-      <c r="L63" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr"/>
       <c r="M63" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -3537,12 +3533,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
+          <t>d875bf4d-fe32-473e-a204-dcb7ff95d772-PIN</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
+          <t>Operation, maintenance, improvement and promotion of the BUILD UP interactive web portal</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr"/>
@@ -3566,14 +3562,10 @@
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
-        </is>
-      </c>
-      <c r="L64" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+          <t>Operation, maintenance, improvement and promotion of the BUILD UP interactive web portal</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr"/>
       <c r="M64" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -3968,12 +3960,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr"/>
@@ -3997,7 +3989,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4015,12 +4007,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr"/>
@@ -4044,7 +4036,7 @@
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr"/>
@@ -4062,12 +4054,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr"/>
@@ -4091,7 +4083,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4109,12 +4101,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr"/>
@@ -4138,7 +4130,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr"/>
@@ -4470,11 +4462,7 @@
           <t>Regarding the case study in Lot 2, you mention terms such as "biodiversity and nature co-benefits financial flows". Could you please provide clearer explanations on what is meant by financial flow and</t>
         </is>
       </c>
-      <c r="L83" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+      <c r="L83" s="6" t="inlineStr"/>
       <c r="M83" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -6918,11 +6906,7 @@
           <t xml:space="preserve">1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? </t>
         </is>
       </c>
-      <c r="L135" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+      <c r="L135" s="6" t="inlineStr"/>
       <c r="M135" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -6937,12 +6921,12 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr"/>
@@ -6966,7 +6950,7 @@
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="L136" s="6" t="inlineStr"/>
@@ -6984,12 +6968,12 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr"/>
@@ -7013,7 +6997,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7298,11 +7282,7 @@
           <t>CURA TERRAE WATER LIMITED</t>
         </is>
       </c>
-      <c r="L143" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+      <c r="L143" s="6" t="inlineStr"/>
       <c r="M143" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -7349,11 +7329,7 @@
           <t>VEOLIA EAU - COMPAGNIE GENERALE DES EAUX</t>
         </is>
       </c>
-      <c r="L144" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+      <c r="L144" s="6" t="inlineStr"/>
       <c r="M144" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -7556,12 +7532,12 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>928057492</t>
+          <t>928211140</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr"/>
@@ -7585,7 +7561,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7603,12 +7579,12 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>926227393</t>
+          <t>928057492</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr"/>
@@ -7632,7 +7608,7 @@
       </c>
       <c r="K150" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="L150" s="6" t="inlineStr"/>
@@ -7650,12 +7626,12 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>928211140</t>
+          <t>926227393</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr"/>
@@ -7679,7 +7655,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -7932,12 +7908,12 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>85779</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr"/>
@@ -7961,7 +7937,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -7979,12 +7955,12 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>85495</t>
+          <t>41082</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr"/>
@@ -8008,7 +7984,7 @@
       </c>
       <c r="K158" s="6" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
         </is>
       </c>
       <c r="L158" s="6" t="inlineStr"/>
@@ -8026,12 +8002,12 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
+          <t>85779</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr"/>
@@ -8055,7 +8031,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8073,12 +8049,12 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>85495</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr"/>
@@ -8102,7 +8078,7 @@
       </c>
       <c r="K160" s="6" t="inlineStr">
         <is>
-          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="L160" s="6" t="inlineStr"/>
@@ -8120,12 +8096,12 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>100106</t>
+          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Should the Mission Forum be hosted during Ocean Days if in Brussels, or is there also the possibility of hosting the Mission Forum in Brussels during another time of the year?</t>
+          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr"/>
@@ -8149,7 +8125,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>Should the Mission Forum be hosted during Ocean Days if in Brussels, or is there also the possibility of hosting the Mission Forum in Brussels during another time of the year?</t>
+          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8167,12 +8143,12 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>HuMUS Soil Stewards training programme</t>
+          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr"/>
@@ -8196,7 +8172,7 @@
       </c>
       <c r="K162" s="6" t="inlineStr">
         <is>
-          <t>HuMUS Soil Stewards training programme The HuMUS Soil Steward Training Programme is an online capacity-building course designed to strengthen knowledge and practical skills related to soil health, par</t>
+          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
         </is>
       </c>
       <c r="L162" s="6" t="inlineStr"/>
@@ -8214,12 +8190,12 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>913756976</t>
+          <t>100106</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
+          <t>Should the Mission Forum be hosted during Ocean Days if in Brussels, or is there also the possibility of hosting the Mission Forum in Brussels during another time of the year?</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr"/>
@@ -8243,7 +8219,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
+          <t>Should the Mission Forum be hosted during Ocean Days if in Brussels, or is there also the possibility of hosting the Mission Forum in Brussels during another time of the year?</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8261,12 +8237,12 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>880759128</t>
+          <t>104241</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE FORUA</t>
+          <t>HuMUS Soil Stewards training programme</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr"/>
@@ -8290,7 +8266,7 @@
       </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE FORUA</t>
+          <t>HuMUS Soil Stewards training programme The HuMUS Soil Steward Training Programme is an online capacity-building course designed to strengthen knowledge and practical skills related to soil health, par</t>
         </is>
       </c>
       <c r="L164" s="6" t="inlineStr"/>
@@ -8308,12 +8284,12 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>76912</t>
+          <t>913756976</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
+          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr"/>
@@ -8337,7 +8313,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
+          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8355,12 +8331,12 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>77665</t>
+          <t>880759128</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
+          <t>AYUNTAMIENTO DE FORUA</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr"/>
@@ -8384,7 +8360,7 @@
       </c>
       <c r="K166" s="6" t="inlineStr">
         <is>
-          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or</t>
+          <t>AYUNTAMIENTO DE FORUA</t>
         </is>
       </c>
       <c r="L166" s="6" t="inlineStr"/>
@@ -8402,12 +8378,12 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>886088211</t>
+          <t>76912</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>Non Architecture s.r.l.</t>
+          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr"/>
@@ -8431,7 +8407,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>Non Architecture s.r.l.</t>
+          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8449,12 +8425,12 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>871698261</t>
+          <t>77665</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
+          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr"/>
@@ -8478,7 +8454,7 @@
       </c>
       <c r="K168" s="6" t="inlineStr">
         <is>
-          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
+          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or</t>
         </is>
       </c>
       <c r="L168" s="6" t="inlineStr"/>
@@ -8496,12 +8472,12 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>918605133</t>
+          <t>886088211</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
+          <t>Non Architecture s.r.l.</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr"/>
@@ -8525,7 +8501,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
+          <t>Non Architecture s.r.l.</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8543,12 +8519,12 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>871698261</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
+          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr"/>
@@ -8572,7 +8548,7 @@
       </c>
       <c r="K170" s="6" t="inlineStr">
         <is>
-          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
+          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
         </is>
       </c>
       <c r="L170" s="6" t="inlineStr"/>
@@ -8590,12 +8566,12 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>892931076</t>
+          <t>918605133</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr"/>
@@ -8619,7 +8595,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -8637,12 +8613,12 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>936518123</t>
+          <t>485</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr"/>
@@ -8666,7 +8642,7 @@
       </c>
       <c r="K172" s="6" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
         </is>
       </c>
       <c r="L172" s="6" t="inlineStr"/>
@@ -8684,12 +8660,12 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>EU4H</t>
+          <t>892931076</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>European Linkage of Initiative from Science to Action in Health</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr"/>
@@ -8713,14 +8689,10 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>European Linkage of Initiative from Science to Action in Health</t>
-        </is>
-      </c>
-      <c r="L173" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+          <t>MUNICIPIO DE VILA DE REI</t>
+        </is>
+      </c>
+      <c r="L173" s="6" t="inlineStr"/>
       <c r="M173" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -8735,12 +8707,12 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>19519</t>
+          <t>936518123</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge): is it possible to present an urban innovation project that intervenes in the public space of a housing district, or does it have to be a building itself?</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr"/>
@@ -8764,14 +8736,10 @@
       </c>
       <c r="K174" s="6" t="inlineStr">
         <is>
-          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge): is it possible to present an urban innovation project that intervenes in the public space of a housing district, or does it have to be a bui</t>
-        </is>
-      </c>
-      <c r="L174" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+          <t>Urban Initiative</t>
+        </is>
+      </c>
+      <c r="L174" s="6" t="inlineStr"/>
       <c r="M174" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -8786,12 +8754,12 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>EU4H</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-ICT-2018-2020, topic ICT-03-2018-2019 it is recommended that "Actions should … develop close links with on-going European and national initiatives in order to maximize impact." Where can information on those initiatives be found?</t>
+          <t>European Linkage of Initiative from Science to Action in Health</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr"/>
@@ -8815,14 +8783,10 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under call H2020-ICT-2018-2020, topic ICT-03-2018-2019 it is recommended that "Actions should … develop close links with on-going European and national initiatives in order to maximize impact." Where </t>
-        </is>
-      </c>
-      <c r="L175" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+          <t>European Linkage of Initiative from Science to Action in Health</t>
+        </is>
+      </c>
+      <c r="L175" s="6" t="inlineStr"/>
       <c r="M175" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -8837,12 +8801,12 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>Under the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)", which secondments from and to an International European Interest Organisation (IEIO) are eligible for funding?</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge): is it possible to present an urban innovation project that intervenes in the public space of a housing district, or does it have to be a building itself?</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr"/>
@@ -8866,14 +8830,10 @@
       </c>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>Under the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)", which secondments from and to an International European Interest Organisation (IEIO) are eligible for funding?</t>
-        </is>
-      </c>
-      <c r="L176" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge): is it possible to present an urban innovation project that intervenes in the public space of a housing district, or does it have to be a bui</t>
+        </is>
+      </c>
+      <c r="L176" s="6" t="inlineStr"/>
       <c r="M176" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -8888,12 +8848,12 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>22334</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2023-EUSIC-PRIZES-04: Regarding the European Social Innovation Competition, our initiative has already received a regional award from my country and/or support from European structural funds. Does this disqualify us?</t>
+          <t>Under call H2020-ICT-2018-2020, topic ICT-03-2018-2019 it is recommended that "Actions should … develop close links with on-going European and national initiatives in order to maximize impact." Where can information on those initiatives be found?</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr"/>
@@ -8917,151 +8877,131 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2023-EUSIC-PRIZES-04: Regarding the European Social Innovation Competition, our initiative has already received a regional award from my country and/or support from European structural fun</t>
-        </is>
-      </c>
-      <c r="L177" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Under call H2020-ICT-2018-2020, topic ICT-03-2018-2019 it is recommended that "Actions should … develop close links with on-going European and national initiatives in order to maximize impact." Where </t>
+        </is>
+      </c>
+      <c r="L177" s="6" t="inlineStr"/>
       <c r="M177" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="28" customHeight="1">
-      <c r="A178" s="14" t="inlineStr">
-        <is>
-          <t>🟢 Euskadi</t>
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>Under the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)", which secondments from and to an International European Interest Organisation (IEIO) are eligible for funding?</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr"/>
+      <c r="E178" s="10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr"/>
+      <c r="G178" s="6" t="inlineStr"/>
+      <c r="H178" s="6" t="inlineStr"/>
+      <c r="I178" s="10" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J178" s="6" t="inlineStr">
+        <is>
+          <t>Revisar relevancia para el Ayuntamiento de Bilbao.</t>
+        </is>
+      </c>
+      <c r="K178" s="6" t="inlineStr">
+        <is>
+          <t>Under the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)", which secondments from and to an International European Interest Organisation (IEIO) are eligible for funding?</t>
+        </is>
+      </c>
+      <c r="L178" s="6" t="inlineStr"/>
+      <c r="M178" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
-      <c r="A179" s="15" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>Europa</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>EUS-23950</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocatorias transversales ligadas a multitud de líneas innovadoras, que atañen a inteligencia artificial y digitalización, energía y descarbonizació</t>
-        </is>
-      </c>
-      <c r="D179" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>HORIZON-EIC-2023-EUSIC-PRIZES-04: Regarding the European Social Innovation Competition, our initiative has already received a regional award from my country and/or support from European structural funds. Does this disqualify us?</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr"/>
+      <c r="E179" s="10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F179" s="6" t="inlineStr"/>
       <c r="G179" s="6" t="inlineStr"/>
-      <c r="H179" s="6" t="inlineStr">
-        <is>
-          <t>Ayuda/Subvencion Euskadi</t>
-        </is>
-      </c>
-      <c r="I179" s="8" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J179" s="6" t="inlineStr"/>
+      <c r="H179" s="6" t="inlineStr"/>
+      <c r="I179" s="10" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J179" s="6" t="inlineStr">
+        <is>
+          <t>Revisar relevancia para el Ayuntamiento de Bilbao.</t>
+        </is>
+      </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="L179" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+          <t>HORIZON-EIC-2023-EUSIC-PRIZES-04: Regarding the European Social Innovation Competition, our initiative has already received a regional award from my country and/or support from European structural fun</t>
+        </is>
+      </c>
+      <c r="L179" s="6" t="inlineStr"/>
       <c r="M179" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="40" customHeight="1">
-      <c r="A180" s="15" t="inlineStr">
+    <row r="180" ht="28" customHeight="1">
+      <c r="A180" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" s="14" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
-      <c r="B180" s="6" t="inlineStr">
-        <is>
-          <t>EUS-04778</t>
-        </is>
-      </c>
-      <c r="C180" s="6" t="inlineStr">
-        <is>
-          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfronterizos de energía renovable. Se prevé una nueva convocatoria para noviembre de 2026.</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="E180" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F180" s="6" t="inlineStr"/>
-      <c r="G180" s="6" t="inlineStr"/>
-      <c r="H180" s="6" t="inlineStr">
-        <is>
-          <t>Ayuda/Subvencion Euskadi</t>
-        </is>
-      </c>
-      <c r="I180" s="8" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J180" s="6" t="inlineStr"/>
-      <c r="K180" s="6" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="L180" s="13" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="M180" s="9" t="inlineStr">
-        <is>
-          <t>Ver</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="40" customHeight="1">
-      <c r="A181" s="15" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>EUS-19473</t>
+          <t>EUS-63611</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Suministro de más trípticos relativos a la zona de bajas emisiones</t>
+          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocatorias transversales ligadas a multitud de líneas innovadoras, que atañen a inteligencia artificial y digitalización, energía y descarbonizació</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
@@ -9078,7 +9018,7 @@
       <c r="G181" s="6" t="inlineStr"/>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="I181" s="8" t="inlineStr">
@@ -9092,7 +9032,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L181" s="13" t="inlineStr">
+      <c r="L181" s="15" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9104,19 +9044,19 @@
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
-      <c r="A182" s="15" t="inlineStr">
+      <c r="A182" s="14" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>EUS-16615</t>
+          <t>EUS-46816</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
+          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfronterizos de energía renovable. Se prevé una nueva convocatoria para noviembre de 2026.</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
@@ -9136,9 +9076,9 @@
           <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
-      <c r="I182" s="11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
+      <c r="I182" s="8" t="inlineStr">
+        <is>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J182" s="6" t="inlineStr"/>
@@ -9147,7 +9087,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L182" s="13" t="inlineStr">
+      <c r="L182" s="15" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9159,19 +9099,19 @@
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
-      <c r="A183" s="15" t="inlineStr">
+      <c r="A183" s="14" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>EUS-42934</t>
+          <t>EUS-59501</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>Reparación deficiencias eléctricas en Pabellón</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
@@ -9188,12 +9128,12 @@
       <c r="G183" s="6" t="inlineStr"/>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
-        </is>
-      </c>
-      <c r="I183" s="11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I183" s="8" t="inlineStr">
+        <is>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J183" s="6" t="inlineStr"/>
@@ -9202,7 +9142,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L183" s="13" t="inlineStr">
+      <c r="L183" s="15" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9214,19 +9154,19 @@
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
-      <c r="A184" s="15" t="inlineStr">
+      <c r="A184" s="14" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>EUS-75226</t>
+          <t>EUS-73899</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>Mobiliario (incluido de oficina), complementos mobiliario, aparatos electrodomésticos y limpieza</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
@@ -9243,7 +9183,7 @@
       <c r="G184" s="6" t="inlineStr"/>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="I184" s="11" t="inlineStr">
@@ -9257,7 +9197,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L184" s="13" t="inlineStr">
+      <c r="L184" s="15" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9269,19 +9209,19 @@
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
-      <c r="A185" s="15" t="inlineStr">
+      <c r="A185" s="14" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>EUS-74374</t>
+          <t>EUS-72308</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>Mobiliario (incluido de oficina), complementos mobiliario, aparatos electrodomésticos y limpieza</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
@@ -9298,7 +9238,7 @@
       <c r="G185" s="6" t="inlineStr"/>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="I185" s="11" t="inlineStr">
@@ -9312,7 +9252,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L185" s="13" t="inlineStr">
+      <c r="L185" s="15" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9323,11 +9263,176 @@
         </is>
       </c>
     </row>
+    <row r="186" ht="40" customHeight="1">
+      <c r="A186" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>EUS-37473</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>Renovación licencias Teslab, infraestructura docente Joseba Albizuri.</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr"/>
+      <c r="G186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I186" s="11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="J186" s="6" t="inlineStr"/>
+      <c r="K186" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L186" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M186" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>EUS-31002</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>Mantenimiento preventivo de la cámara climática del Departamento de Fisiología Vegetal de la UPV/EHU en Leioa, según presupuesto 26/PMJ150, incluyendo la revisión general del equipo, comprobación de p</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr"/>
+      <c r="G187" s="6" t="inlineStr"/>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I187" s="11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="J187" s="6" t="inlineStr"/>
+      <c r="K187" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L187" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M187" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>EUS-50049</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>Reparación de fuga de gas y sustitución de válvula de la cámara climática del Departamento de Fisiología Vegetal de la UPV/EHU en Leioa, según presupuesto 2026/244. La avería fue detectada en la revis</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr"/>
+      <c r="G188" s="6" t="inlineStr"/>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I188" s="11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="J188" s="6" t="inlineStr"/>
+      <c r="K188" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L188" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M188" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:M185"/>
+  <autoFilter ref="A4:M188"/>
   <mergeCells count="4">
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A178:M178"/>
+    <mergeCell ref="A180:M180"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
   </mergeCells>
@@ -9504,13 +9609,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId182"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9522,7 +9630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2684"/>
+  <dimension ref="A1:F2729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13069,7 +13177,7 @@
       </c>
       <c r="B258" s="19" t="inlineStr">
         <is>
-          <t>Empowering SMEs through Renewable Energy Communities for a Sustainable Future</t>
+          <t>Assisting the Agrifood sector in the uptake of renewable energy communities</t>
         </is>
       </c>
       <c r="C258" s="20" t="n"/>
@@ -13189,7 +13297,7 @@
       </c>
       <c r="B266" s="19" t="inlineStr">
         <is>
-          <t>Empowering SMEs through Renewable Energy Communities for a Sustainable Future</t>
+          <t>Assisting the Agrifood sector in the uptake of renewable energy communities</t>
         </is>
       </c>
       <c r="C266" s="20" t="n"/>
@@ -20432,7 +20540,7 @@
     <row r="796" ht="30" customHeight="1">
       <c r="A796" s="16" t="inlineStr">
         <is>
-          <t>FICHA 54: HORIZON</t>
+          <t>FICHA 54: 897315282</t>
         </is>
       </c>
       <c r="B796" s="17" t="n"/>
@@ -20465,7 +20573,7 @@
       </c>
       <c r="B798" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Social Innovation Fund</t>
         </is>
       </c>
       <c r="C798" s="20" t="n"/>
@@ -20481,7 +20589,7 @@
       </c>
       <c r="B799" s="19" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>897315282</t>
         </is>
       </c>
       <c r="C799" s="20" t="n"/>
@@ -20495,11 +20603,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B800" s="19" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+      <c r="B800" s="19" t="inlineStr"/>
       <c r="C800" s="20" t="n"/>
       <c r="D800" s="20" t="n"/>
       <c r="E800" s="20" t="n"/>
@@ -20571,11 +20675,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B805" s="19" t="inlineStr">
-        <is>
-          <t>HORIZON-MISS-2021-CIT-02</t>
-        </is>
-      </c>
+      <c r="B805" s="19" t="inlineStr"/>
       <c r="C805" s="20" t="n"/>
       <c r="D805" s="20" t="n"/>
       <c r="E805" s="20" t="n"/>
@@ -20589,7 +20689,7 @@
       </c>
       <c r="B806" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Social Innovation Fund</t>
         </is>
       </c>
       <c r="C806" s="20" t="n"/>
@@ -20617,7 +20717,7 @@
       </c>
       <c r="B808" s="19" t="inlineStr">
         <is>
-          <t>INFO — Revisar relevancia para el Ayuntamiento de Bilbao.</t>
+          <t>MEDIA — Aplicable a Petronor/Repsol (Muskiz) y Puerto de Bilbao.</t>
         </is>
       </c>
       <c r="C808" s="20" t="n"/>
@@ -20633,7 +20733,7 @@
       </c>
       <c r="B809" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/897315282</t>
         </is>
       </c>
       <c r="C809" s="20" t="n"/>
@@ -20644,7 +20744,7 @@
     <row r="811" ht="30" customHeight="1">
       <c r="A811" s="16" t="inlineStr">
         <is>
-          <t>FICHA 55: ERASMUS2027</t>
+          <t>FICHA 55: HORIZON</t>
         </is>
       </c>
       <c r="B811" s="17" t="n"/>
@@ -20677,7 +20777,7 @@
       </c>
       <c r="B813" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C813" s="20" t="n"/>
@@ -20693,7 +20793,7 @@
       </c>
       <c r="B814" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C814" s="20" t="n"/>
@@ -20707,7 +20807,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B815" s="19" t="inlineStr"/>
+      <c r="B815" s="19" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="C815" s="20" t="n"/>
       <c r="D815" s="20" t="n"/>
       <c r="E815" s="20" t="n"/>
@@ -20781,7 +20885,7 @@
       </c>
       <c r="B820" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
+          <t>HORIZON-MISS-2021-CIT-02</t>
         </is>
       </c>
       <c r="C820" s="20" t="n"/>
@@ -20797,7 +20901,7 @@
       </c>
       <c r="B821" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C821" s="20" t="n"/>
@@ -20841,7 +20945,7 @@
       </c>
       <c r="B824" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
         </is>
       </c>
       <c r="C824" s="20" t="n"/>
@@ -20852,7 +20956,7 @@
     <row r="826" ht="30" customHeight="1">
       <c r="A826" s="16" t="inlineStr">
         <is>
-          <t>FICHA 56: 13349</t>
+          <t>FICHA 56: ERASMUS2027</t>
         </is>
       </c>
       <c r="B826" s="17" t="n"/>
@@ -20877,7 +20981,7 @@
       <c r="E827" s="20" t="n"/>
       <c r="F827" s="20" t="n"/>
     </row>
-    <row r="828" ht="45" customHeight="1">
+    <row r="828" ht="20" customHeight="1">
       <c r="A828" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -20885,7 +20989,7 @@
       </c>
       <c r="B828" s="19" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C828" s="20" t="n"/>
@@ -20901,7 +21005,7 @@
       </c>
       <c r="B829" s="19" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C829" s="20" t="n"/>
@@ -20987,13 +21091,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B835" s="19" t="inlineStr"/>
+      <c r="B835" s="19" t="inlineStr">
+        <is>
+          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
+        </is>
+      </c>
       <c r="C835" s="20" t="n"/>
       <c r="D835" s="20" t="n"/>
       <c r="E835" s="20" t="n"/>
       <c r="F835" s="20" t="n"/>
     </row>
-    <row r="836" ht="45" customHeight="1">
+    <row r="836" ht="20" customHeight="1">
       <c r="A836" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -21001,7 +21109,7 @@
       </c>
       <c r="B836" s="19" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C836" s="20" t="n"/>
@@ -21045,7 +21153,7 @@
       </c>
       <c r="B839" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13349</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
         </is>
       </c>
       <c r="C839" s="20" t="n"/>
@@ -21056,7 +21164,7 @@
     <row r="841" ht="30" customHeight="1">
       <c r="A841" s="16" t="inlineStr">
         <is>
-          <t>FICHA 57: 11301</t>
+          <t>FICHA 57: 13349</t>
         </is>
       </c>
       <c r="B841" s="17" t="n"/>
@@ -21089,7 +21197,7 @@
       </c>
       <c r="B843" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
         </is>
       </c>
       <c r="C843" s="20" t="n"/>
@@ -21105,7 +21213,7 @@
       </c>
       <c r="B844" s="19" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="C844" s="20" t="n"/>
@@ -21205,7 +21313,7 @@
       </c>
       <c r="B851" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficiency investments - Smart Finance for Smart Buildings, when communicating across Europe towards potential replicators, do projects have to cover all EU Members States?</t>
         </is>
       </c>
       <c r="C851" s="20" t="n"/>
@@ -21249,7 +21357,7 @@
       </c>
       <c r="B854" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/11301</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13349</t>
         </is>
       </c>
       <c r="C854" s="20" t="n"/>
@@ -21260,7 +21368,7 @@
     <row r="856" ht="30" customHeight="1">
       <c r="A856" s="16" t="inlineStr">
         <is>
-          <t>FICHA 58: d875bf4d-fe32-473e-a204-dcb7ff95d772-PIN</t>
+          <t>FICHA 58: 11301</t>
         </is>
       </c>
       <c r="B856" s="17" t="n"/>
@@ -21293,7 +21401,7 @@
       </c>
       <c r="B858" s="19" t="inlineStr">
         <is>
-          <t>Operation, maintenance, improvement and promotion of the BUILD UP interactive web portal</t>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
         </is>
       </c>
       <c r="C858" s="20" t="n"/>
@@ -21309,7 +21417,7 @@
       </c>
       <c r="B859" s="19" t="inlineStr">
         <is>
-          <t>d875bf4d-fe32-473e-a204-dcb7ff95d772-PIN</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="C859" s="20" t="n"/>
@@ -21395,11 +21503,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B865" s="19" t="inlineStr">
-        <is>
-          <t>CINEA/2023/OP/0020-PIN</t>
-        </is>
-      </c>
+      <c r="B865" s="19" t="inlineStr"/>
       <c r="C865" s="20" t="n"/>
       <c r="D865" s="20" t="n"/>
       <c r="E865" s="20" t="n"/>
@@ -21413,7 +21517,7 @@
       </c>
       <c r="B866" s="19" t="inlineStr">
         <is>
-          <t>Operation, maintenance, improvement and promotion of the BUILD UP interactive web portal</t>
+          <t>Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should proposals focus on building comfort or building energy efficiency?</t>
         </is>
       </c>
       <c r="C866" s="20" t="n"/>
@@ -21457,7 +21561,7 @@
       </c>
       <c r="B869" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/d875bf4d-fe32-473e-a204-dcb7ff95d772-PIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/11301</t>
         </is>
       </c>
       <c r="C869" s="20" t="n"/>
@@ -21468,7 +21572,7 @@
     <row r="871" ht="30" customHeight="1">
       <c r="A871" s="16" t="inlineStr">
         <is>
-          <t>FICHA 59: 5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
+          <t>FICHA 59: d875bf4d-fe32-473e-a204-dcb7ff95d772-PIN</t>
         </is>
       </c>
       <c r="B871" s="17" t="n"/>
@@ -21493,7 +21597,7 @@
       <c r="E872" s="20" t="n"/>
       <c r="F872" s="20" t="n"/>
     </row>
-    <row r="873" ht="20" customHeight="1">
+    <row r="873" ht="45" customHeight="1">
       <c r="A873" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -21501,7 +21605,7 @@
       </c>
       <c r="B873" s="19" t="inlineStr">
         <is>
-          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
+          <t>Operation, maintenance, improvement and promotion of the BUILD UP interactive web portal</t>
         </is>
       </c>
       <c r="C873" s="20" t="n"/>
@@ -21517,7 +21621,7 @@
       </c>
       <c r="B874" s="19" t="inlineStr">
         <is>
-          <t>5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
+          <t>d875bf4d-fe32-473e-a204-dcb7ff95d772-PIN</t>
         </is>
       </c>
       <c r="C874" s="20" t="n"/>
@@ -21605,7 +21709,7 @@
       </c>
       <c r="B880" s="19" t="inlineStr">
         <is>
-          <t>NEAR/IEV/2021/EA-RP/0041</t>
+          <t>CINEA/2023/OP/0020-PIN</t>
         </is>
       </c>
       <c r="C880" s="20" t="n"/>
@@ -21613,7 +21717,7 @@
       <c r="E880" s="20" t="n"/>
       <c r="F880" s="20" t="n"/>
     </row>
-    <row r="881" ht="20" customHeight="1">
+    <row r="881" ht="45" customHeight="1">
       <c r="A881" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -21621,7 +21725,7 @@
       </c>
       <c r="B881" s="19" t="inlineStr">
         <is>
-          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
+          <t>Operation, maintenance, improvement and promotion of the BUILD UP interactive web portal</t>
         </is>
       </c>
       <c r="C881" s="20" t="n"/>
@@ -21665,7 +21769,7 @@
       </c>
       <c r="B884" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/d875bf4d-fe32-473e-a204-dcb7ff95d772-PIN</t>
         </is>
       </c>
       <c r="C884" s="20" t="n"/>
@@ -23316,7 +23420,7 @@
     <row r="1006" ht="30" customHeight="1">
       <c r="A1006" s="16" t="inlineStr">
         <is>
-          <t>FICHA 68: 928447529</t>
+          <t>FICHA 68: 917779760</t>
         </is>
       </c>
       <c r="B1006" s="17" t="n"/>
@@ -23349,7 +23453,7 @@
       </c>
       <c r="B1008" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1008" s="20" t="n"/>
@@ -23365,7 +23469,7 @@
       </c>
       <c r="B1009" s="19" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C1009" s="20" t="n"/>
@@ -23465,7 +23569,7 @@
       </c>
       <c r="B1016" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1016" s="20" t="n"/>
@@ -23509,7 +23613,7 @@
       </c>
       <c r="B1019" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
         </is>
       </c>
       <c r="C1019" s="20" t="n"/>
@@ -23520,7 +23624,7 @@
     <row r="1021" ht="30" customHeight="1">
       <c r="A1021" s="16" t="inlineStr">
         <is>
-          <t>FICHA 69: 917671508</t>
+          <t>FICHA 69: 920115617</t>
         </is>
       </c>
       <c r="B1021" s="17" t="n"/>
@@ -23553,7 +23657,7 @@
       </c>
       <c r="B1023" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1023" s="20" t="n"/>
@@ -23569,7 +23673,7 @@
       </c>
       <c r="B1024" s="19" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C1024" s="20" t="n"/>
@@ -23669,7 +23773,7 @@
       </c>
       <c r="B1031" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1031" s="20" t="n"/>
@@ -23713,7 +23817,7 @@
       </c>
       <c r="B1034" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
         </is>
       </c>
       <c r="C1034" s="20" t="n"/>
@@ -23724,7 +23828,7 @@
     <row r="1036" ht="30" customHeight="1">
       <c r="A1036" s="16" t="inlineStr">
         <is>
-          <t>FICHA 70: 917779760</t>
+          <t>FICHA 70: 917671508</t>
         </is>
       </c>
       <c r="B1036" s="17" t="n"/>
@@ -23757,7 +23861,7 @@
       </c>
       <c r="B1038" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1038" s="20" t="n"/>
@@ -23773,7 +23877,7 @@
       </c>
       <c r="B1039" s="19" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C1039" s="20" t="n"/>
@@ -23873,7 +23977,7 @@
       </c>
       <c r="B1046" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1046" s="20" t="n"/>
@@ -23917,7 +24021,7 @@
       </c>
       <c r="B1049" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
         </is>
       </c>
       <c r="C1049" s="20" t="n"/>
@@ -23928,7 +24032,7 @@
     <row r="1051" ht="30" customHeight="1">
       <c r="A1051" s="16" t="inlineStr">
         <is>
-          <t>FICHA 71: 920115617</t>
+          <t>FICHA 71: 928447529</t>
         </is>
       </c>
       <c r="B1051" s="17" t="n"/>
@@ -23961,7 +24065,7 @@
       </c>
       <c r="B1053" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1053" s="20" t="n"/>
@@ -23977,7 +24081,7 @@
       </c>
       <c r="B1054" s="19" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C1054" s="20" t="n"/>
@@ -24077,7 +24181,7 @@
       </c>
       <c r="B1061" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1061" s="20" t="n"/>
@@ -24121,7 +24225,7 @@
       </c>
       <c r="B1064" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
         </is>
       </c>
       <c r="C1064" s="20" t="n"/>
@@ -36196,7 +36300,7 @@
     <row r="1951" ht="30" customHeight="1">
       <c r="A1951" s="16" t="inlineStr">
         <is>
-          <t>FICHA 131: 925388828</t>
+          <t>FICHA 131: 934294980</t>
         </is>
       </c>
       <c r="B1951" s="17" t="n"/>
@@ -36229,7 +36333,7 @@
       </c>
       <c r="B1953" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C1953" s="20" t="n"/>
@@ -36245,7 +36349,7 @@
       </c>
       <c r="B1954" s="19" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C1954" s="20" t="n"/>
@@ -36345,7 +36449,7 @@
       </c>
       <c r="B1961" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C1961" s="20" t="n"/>
@@ -36389,7 +36493,7 @@
       </c>
       <c r="B1964" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
         </is>
       </c>
       <c r="C1964" s="20" t="n"/>
@@ -36400,7 +36504,7 @@
     <row r="1966" ht="30" customHeight="1">
       <c r="A1966" s="16" t="inlineStr">
         <is>
-          <t>FICHA 132: 934294980</t>
+          <t>FICHA 132: 925388828</t>
         </is>
       </c>
       <c r="B1966" s="17" t="n"/>
@@ -36433,7 +36537,7 @@
       </c>
       <c r="B1968" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C1968" s="20" t="n"/>
@@ -36449,7 +36553,7 @@
       </c>
       <c r="B1969" s="19" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C1969" s="20" t="n"/>
@@ -36549,7 +36653,7 @@
       </c>
       <c r="B1976" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C1976" s="20" t="n"/>
@@ -36593,7 +36697,7 @@
       </c>
       <c r="B1979" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
         </is>
       </c>
       <c r="C1979" s="20" t="n"/>
@@ -38848,7 +38952,7 @@
     <row r="2146" ht="30" customHeight="1">
       <c r="A2146" s="16" t="inlineStr">
         <is>
-          <t>FICHA 144: 928057492</t>
+          <t>FICHA 144: 928211140</t>
         </is>
       </c>
       <c r="B2146" s="17" t="n"/>
@@ -38881,7 +38985,7 @@
       </c>
       <c r="B2148" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="C2148" s="20" t="n"/>
@@ -38897,7 +39001,7 @@
       </c>
       <c r="B2149" s="19" t="inlineStr">
         <is>
-          <t>928057492</t>
+          <t>928211140</t>
         </is>
       </c>
       <c r="C2149" s="20" t="n"/>
@@ -38997,7 +39101,7 @@
       </c>
       <c r="B2156" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="C2156" s="20" t="n"/>
@@ -39041,7 +39145,7 @@
       </c>
       <c r="B2159" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928057492</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928211140</t>
         </is>
       </c>
       <c r="C2159" s="20" t="n"/>
@@ -39052,7 +39156,7 @@
     <row r="2161" ht="30" customHeight="1">
       <c r="A2161" s="16" t="inlineStr">
         <is>
-          <t>FICHA 145: 926227393</t>
+          <t>FICHA 145: 928057492</t>
         </is>
       </c>
       <c r="B2161" s="17" t="n"/>
@@ -39085,7 +39189,7 @@
       </c>
       <c r="B2163" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="C2163" s="20" t="n"/>
@@ -39101,7 +39205,7 @@
       </c>
       <c r="B2164" s="19" t="inlineStr">
         <is>
-          <t>926227393</t>
+          <t>928057492</t>
         </is>
       </c>
       <c r="C2164" s="20" t="n"/>
@@ -39201,7 +39305,7 @@
       </c>
       <c r="B2171" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="C2171" s="20" t="n"/>
@@ -39245,7 +39349,7 @@
       </c>
       <c r="B2174" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/926227393</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928057492</t>
         </is>
       </c>
       <c r="C2174" s="20" t="n"/>
@@ -39256,7 +39360,7 @@
     <row r="2176" ht="30" customHeight="1">
       <c r="A2176" s="16" t="inlineStr">
         <is>
-          <t>FICHA 146: 928211140</t>
+          <t>FICHA 146: 926227393</t>
         </is>
       </c>
       <c r="B2176" s="17" t="n"/>
@@ -39289,7 +39393,7 @@
       </c>
       <c r="B2178" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="C2178" s="20" t="n"/>
@@ -39305,7 +39409,7 @@
       </c>
       <c r="B2179" s="19" t="inlineStr">
         <is>
-          <t>928211140</t>
+          <t>926227393</t>
         </is>
       </c>
       <c r="C2179" s="20" t="n"/>
@@ -39405,7 +39509,7 @@
       </c>
       <c r="B2186" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="C2186" s="20" t="n"/>
@@ -39449,7 +39553,7 @@
       </c>
       <c r="B2189" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928211140</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/926227393</t>
         </is>
       </c>
       <c r="C2189" s="20" t="n"/>
@@ -40480,7 +40584,7 @@
     <row r="2266" ht="30" customHeight="1">
       <c r="A2266" s="16" t="inlineStr">
         <is>
-          <t>FICHA 152: 85779</t>
+          <t>FICHA 152: 19429</t>
         </is>
       </c>
       <c r="B2266" s="17" t="n"/>
@@ -40513,7 +40617,7 @@
       </c>
       <c r="B2268" s="19" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
         </is>
       </c>
       <c r="C2268" s="20" t="n"/>
@@ -40529,7 +40633,7 @@
       </c>
       <c r="B2269" s="19" t="inlineStr">
         <is>
-          <t>85779</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="C2269" s="20" t="n"/>
@@ -40629,7 +40733,7 @@
       </c>
       <c r="B2276" s="19" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, Impact), which activities can we fund with the money award?</t>
         </is>
       </c>
       <c r="C2276" s="20" t="n"/>
@@ -40673,7 +40777,7 @@
       </c>
       <c r="B2279" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85779</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19429</t>
         </is>
       </c>
       <c r="C2279" s="20" t="n"/>
@@ -40684,7 +40788,7 @@
     <row r="2281" ht="30" customHeight="1">
       <c r="A2281" s="16" t="inlineStr">
         <is>
-          <t>FICHA 153: 85495</t>
+          <t>FICHA 153: 41082</t>
         </is>
       </c>
       <c r="B2281" s="17" t="n"/>
@@ -40717,7 +40821,7 @@
       </c>
       <c r="B2283" s="19" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
         </is>
       </c>
       <c r="C2283" s="20" t="n"/>
@@ -40733,7 +40837,7 @@
       </c>
       <c r="B2284" s="19" t="inlineStr">
         <is>
-          <t>85495</t>
+          <t>41082</t>
         </is>
       </c>
       <c r="C2284" s="20" t="n"/>
@@ -40833,7 +40937,7 @@
       </c>
       <c r="B2291" s="19" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
+          <t>Is a social impact fund based in Member States or listed EEA countries but operating mainly in developing countries eligible?</t>
         </is>
       </c>
       <c r="C2291" s="20" t="n"/>
@@ -40877,7 +40981,7 @@
       </c>
       <c r="B2294" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85495</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/41082</t>
         </is>
       </c>
       <c r="C2294" s="20" t="n"/>
@@ -40888,7 +40992,7 @@
     <row r="2296" ht="30" customHeight="1">
       <c r="A2296" s="16" t="inlineStr">
         <is>
-          <t>FICHA 154: d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
+          <t>FICHA 154: 85779</t>
         </is>
       </c>
       <c r="B2296" s="17" t="n"/>
@@ -40921,7 +41025,7 @@
       </c>
       <c r="B2298" s="19" t="inlineStr">
         <is>
-          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="C2298" s="20" t="n"/>
@@ -40937,7 +41041,7 @@
       </c>
       <c r="B2299" s="19" t="inlineStr">
         <is>
-          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
+          <t>85779</t>
         </is>
       </c>
       <c r="C2299" s="20" t="n"/>
@@ -41023,11 +41127,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2305" s="19" t="inlineStr">
-        <is>
-          <t>CINEA/2026/OP/0018-PIN</t>
-        </is>
-      </c>
+      <c r="B2305" s="19" t="inlineStr"/>
       <c r="C2305" s="20" t="n"/>
       <c r="D2305" s="20" t="n"/>
       <c r="E2305" s="20" t="n"/>
@@ -41041,7 +41141,7 @@
       </c>
       <c r="B2306" s="19" t="inlineStr">
         <is>
-          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="C2306" s="20" t="n"/>
@@ -41085,7 +41185,7 @@
       </c>
       <c r="B2309" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85779</t>
         </is>
       </c>
       <c r="C2309" s="20" t="n"/>
@@ -41096,7 +41196,7 @@
     <row r="2311" ht="30" customHeight="1">
       <c r="A2311" s="16" t="inlineStr">
         <is>
-          <t>FICHA 155: 14560</t>
+          <t>FICHA 155: 85495</t>
         </is>
       </c>
       <c r="B2311" s="17" t="n"/>
@@ -41129,7 +41229,7 @@
       </c>
       <c r="B2313" s="19" t="inlineStr">
         <is>
-          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="C2313" s="20" t="n"/>
@@ -41145,7 +41245,7 @@
       </c>
       <c r="B2314" s="19" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>85495</t>
         </is>
       </c>
       <c r="C2314" s="20" t="n"/>
@@ -41245,7 +41345,7 @@
       </c>
       <c r="B2321" s="19" t="inlineStr">
         <is>
-          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
+          <t>Should we focus on one type of environment, or consider oceanic, coastal, and terrestrial environments?</t>
         </is>
       </c>
       <c r="C2321" s="20" t="n"/>
@@ -41289,7 +41389,7 @@
       </c>
       <c r="B2324" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14560</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85495</t>
         </is>
       </c>
       <c r="C2324" s="20" t="n"/>
@@ -41300,7 +41400,7 @@
     <row r="2326" ht="30" customHeight="1">
       <c r="A2326" s="16" t="inlineStr">
         <is>
-          <t>FICHA 156: 100106</t>
+          <t>FICHA 156: d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
         </is>
       </c>
       <c r="B2326" s="17" t="n"/>
@@ -41333,7 +41433,7 @@
       </c>
       <c r="B2328" s="19" t="inlineStr">
         <is>
-          <t>Should the Mission Forum be hosted during Ocean Days if in Brussels, or is there also the possibility of hosting the Mission Forum in Brussels during another time of the year?</t>
+          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
         </is>
       </c>
       <c r="C2328" s="20" t="n"/>
@@ -41349,7 +41449,7 @@
       </c>
       <c r="B2329" s="19" t="inlineStr">
         <is>
-          <t>100106</t>
+          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
         </is>
       </c>
       <c r="C2329" s="20" t="n"/>
@@ -41435,7 +41535,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2335" s="19" t="inlineStr"/>
+      <c r="B2335" s="19" t="inlineStr">
+        <is>
+          <t>CINEA/2026/OP/0018-PIN</t>
+        </is>
+      </c>
       <c r="C2335" s="20" t="n"/>
       <c r="D2335" s="20" t="n"/>
       <c r="E2335" s="20" t="n"/>
@@ -41449,7 +41553,7 @@
       </c>
       <c r="B2336" s="19" t="inlineStr">
         <is>
-          <t>Should the Mission Forum be hosted during Ocean Days if in Brussels, or is there also the possibility of hosting the Mission Forum in Brussels during another time of the year?</t>
+          <t>Services to Communities to support the achievement of the objectives of the Mission Ocean and Waters</t>
         </is>
       </c>
       <c r="C2336" s="20" t="n"/>
@@ -41493,7 +41597,7 @@
       </c>
       <c r="B2339" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/100106</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
         </is>
       </c>
       <c r="C2339" s="20" t="n"/>
@@ -41504,7 +41608,7 @@
     <row r="2341" ht="30" customHeight="1">
       <c r="A2341" s="16" t="inlineStr">
         <is>
-          <t>FICHA 157: 104241</t>
+          <t>FICHA 157: 14560</t>
         </is>
       </c>
       <c r="B2341" s="17" t="n"/>
@@ -41529,7 +41633,7 @@
       <c r="E2342" s="20" t="n"/>
       <c r="F2342" s="20" t="n"/>
     </row>
-    <row r="2343" ht="20" customHeight="1">
+    <row r="2343" ht="45" customHeight="1">
       <c r="A2343" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -41537,7 +41641,7 @@
       </c>
       <c r="B2343" s="19" t="inlineStr">
         <is>
-          <t>HuMUS Soil Stewards training programme</t>
+          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
         </is>
       </c>
       <c r="C2343" s="20" t="n"/>
@@ -41553,7 +41657,7 @@
       </c>
       <c r="B2344" s="19" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="C2344" s="20" t="n"/>
@@ -41639,11 +41743,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2350" s="19" t="inlineStr">
-        <is>
-          <t>HORIZON-MISS-2021-SOIL-02</t>
-        </is>
-      </c>
+      <c r="B2350" s="19" t="inlineStr"/>
       <c r="C2350" s="20" t="n"/>
       <c r="D2350" s="20" t="n"/>
       <c r="E2350" s="20" t="n"/>
@@ -41657,7 +41757,7 @@
       </c>
       <c r="B2351" s="19" t="inlineStr">
         <is>
-          <t>HuMUS Soil Stewards training programme The HuMUS Soil Steward Training Programme is an online capacity-building course designed to strengthen knowledge and practical skills related to soil health, participatory governance and community engagement. It provides a structured syllabus, learning resources, self-assessment tools and videos showcasing</t>
+          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of relevant areas for the blue economy, does the term "ocean and coastal activities" include the European rivers?</t>
         </is>
       </c>
       <c r="C2351" s="20" t="n"/>
@@ -41701,7 +41801,7 @@
       </c>
       <c r="B2354" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/104241</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14560</t>
         </is>
       </c>
       <c r="C2354" s="20" t="n"/>
@@ -41712,7 +41812,7 @@
     <row r="2356" ht="30" customHeight="1">
       <c r="A2356" s="16" t="inlineStr">
         <is>
-          <t>FICHA 158: 913756976</t>
+          <t>FICHA 158: 100106</t>
         </is>
       </c>
       <c r="B2356" s="17" t="n"/>
@@ -41737,7 +41837,7 @@
       <c r="E2357" s="20" t="n"/>
       <c r="F2357" s="20" t="n"/>
     </row>
-    <row r="2358" ht="20" customHeight="1">
+    <row r="2358" ht="45" customHeight="1">
       <c r="A2358" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -41745,7 +41845,7 @@
       </c>
       <c r="B2358" s="19" t="inlineStr">
         <is>
-          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
+          <t>Should the Mission Forum be hosted during Ocean Days if in Brussels, or is there also the possibility of hosting the Mission Forum in Brussels during another time of the year?</t>
         </is>
       </c>
       <c r="C2358" s="20" t="n"/>
@@ -41761,7 +41861,7 @@
       </c>
       <c r="B2359" s="19" t="inlineStr">
         <is>
-          <t>913756976</t>
+          <t>100106</t>
         </is>
       </c>
       <c r="C2359" s="20" t="n"/>
@@ -41853,7 +41953,7 @@
       <c r="E2365" s="20" t="n"/>
       <c r="F2365" s="20" t="n"/>
     </row>
-    <row r="2366" ht="20" customHeight="1">
+    <row r="2366" ht="45" customHeight="1">
       <c r="A2366" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -41861,7 +41961,7 @@
       </c>
       <c r="B2366" s="19" t="inlineStr">
         <is>
-          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
+          <t>Should the Mission Forum be hosted during Ocean Days if in Brussels, or is there also the possibility of hosting the Mission Forum in Brussels during another time of the year?</t>
         </is>
       </c>
       <c r="C2366" s="20" t="n"/>
@@ -41905,7 +42005,7 @@
       </c>
       <c r="B2369" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/913756976</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/100106</t>
         </is>
       </c>
       <c r="C2369" s="20" t="n"/>
@@ -41916,7 +42016,7 @@
     <row r="2371" ht="30" customHeight="1">
       <c r="A2371" s="16" t="inlineStr">
         <is>
-          <t>FICHA 159: 880759128</t>
+          <t>FICHA 159: 104241</t>
         </is>
       </c>
       <c r="B2371" s="17" t="n"/>
@@ -41949,7 +42049,7 @@
       </c>
       <c r="B2373" s="19" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE FORUA</t>
+          <t>HuMUS Soil Stewards training programme</t>
         </is>
       </c>
       <c r="C2373" s="20" t="n"/>
@@ -41965,7 +42065,7 @@
       </c>
       <c r="B2374" s="19" t="inlineStr">
         <is>
-          <t>880759128</t>
+          <t>104241</t>
         </is>
       </c>
       <c r="C2374" s="20" t="n"/>
@@ -42051,13 +42151,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2380" s="19" t="inlineStr"/>
+      <c r="B2380" s="19" t="inlineStr">
+        <is>
+          <t>HORIZON-MISS-2021-SOIL-02</t>
+        </is>
+      </c>
       <c r="C2380" s="20" t="n"/>
       <c r="D2380" s="20" t="n"/>
       <c r="E2380" s="20" t="n"/>
       <c r="F2380" s="20" t="n"/>
     </row>
-    <row r="2381" ht="20" customHeight="1">
+    <row r="2381" ht="45" customHeight="1">
       <c r="A2381" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -42065,7 +42169,7 @@
       </c>
       <c r="B2381" s="19" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE FORUA</t>
+          <t>HuMUS Soil Stewards training programme The HuMUS Soil Steward Training Programme is an online capacity-building course designed to strengthen knowledge and practical skills related to soil health, participatory governance and community engagement. It provides a structured syllabus, learning resources, self-assessment tools and videos showcasing</t>
         </is>
       </c>
       <c r="C2381" s="20" t="n"/>
@@ -42109,7 +42213,7 @@
       </c>
       <c r="B2384" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880759128</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/104241</t>
         </is>
       </c>
       <c r="C2384" s="20" t="n"/>
@@ -42120,7 +42224,7 @@
     <row r="2386" ht="30" customHeight="1">
       <c r="A2386" s="16" t="inlineStr">
         <is>
-          <t>FICHA 160: 76912</t>
+          <t>FICHA 160: 913756976</t>
         </is>
       </c>
       <c r="B2386" s="17" t="n"/>
@@ -42145,7 +42249,7 @@
       <c r="E2387" s="20" t="n"/>
       <c r="F2387" s="20" t="n"/>
     </row>
-    <row r="2388" ht="45" customHeight="1">
+    <row r="2388" ht="20" customHeight="1">
       <c r="A2388" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -42153,7 +42257,7 @@
       </c>
       <c r="B2388" s="19" t="inlineStr">
         <is>
-          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
+          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
         </is>
       </c>
       <c r="C2388" s="20" t="n"/>
@@ -42169,7 +42273,7 @@
       </c>
       <c r="B2389" s="19" t="inlineStr">
         <is>
-          <t>76912</t>
+          <t>913756976</t>
         </is>
       </c>
       <c r="C2389" s="20" t="n"/>
@@ -42261,7 +42365,7 @@
       <c r="E2395" s="20" t="n"/>
       <c r="F2395" s="20" t="n"/>
     </row>
-    <row r="2396" ht="45" customHeight="1">
+    <row r="2396" ht="20" customHeight="1">
       <c r="A2396" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -42269,7 +42373,7 @@
       </c>
       <c r="B2396" s="19" t="inlineStr">
         <is>
-          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
+          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
         </is>
       </c>
       <c r="C2396" s="20" t="n"/>
@@ -42313,7 +42417,7 @@
       </c>
       <c r="B2399" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/76912</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/913756976</t>
         </is>
       </c>
       <c r="C2399" s="20" t="n"/>
@@ -42324,7 +42428,7 @@
     <row r="2401" ht="30" customHeight="1">
       <c r="A2401" s="16" t="inlineStr">
         <is>
-          <t>FICHA 161: 77665</t>
+          <t>FICHA 161: 880759128</t>
         </is>
       </c>
       <c r="B2401" s="17" t="n"/>
@@ -42349,7 +42453,7 @@
       <c r="E2402" s="20" t="n"/>
       <c r="F2402" s="20" t="n"/>
     </row>
-    <row r="2403" ht="45" customHeight="1">
+    <row r="2403" ht="20" customHeight="1">
       <c r="A2403" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -42357,7 +42461,7 @@
       </c>
       <c r="B2403" s="19" t="inlineStr">
         <is>
-          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
+          <t>AYUNTAMIENTO DE FORUA</t>
         </is>
       </c>
       <c r="C2403" s="20" t="n"/>
@@ -42373,7 +42477,7 @@
       </c>
       <c r="B2404" s="19" t="inlineStr">
         <is>
-          <t>77665</t>
+          <t>880759128</t>
         </is>
       </c>
       <c r="C2404" s="20" t="n"/>
@@ -42465,7 +42569,7 @@
       <c r="E2410" s="20" t="n"/>
       <c r="F2410" s="20" t="n"/>
     </row>
-    <row r="2411" ht="45" customHeight="1">
+    <row r="2411" ht="20" customHeight="1">
       <c r="A2411" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -42473,7 +42577,7 @@
       </c>
       <c r="B2411" s="19" t="inlineStr">
         <is>
-          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
+          <t>AYUNTAMIENTO DE FORUA</t>
         </is>
       </c>
       <c r="C2411" s="20" t="n"/>
@@ -42517,7 +42621,7 @@
       </c>
       <c r="B2414" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/77665</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880759128</t>
         </is>
       </c>
       <c r="C2414" s="20" t="n"/>
@@ -42528,7 +42632,7 @@
     <row r="2416" ht="30" customHeight="1">
       <c r="A2416" s="16" t="inlineStr">
         <is>
-          <t>FICHA 162: 886088211</t>
+          <t>FICHA 162: 76912</t>
         </is>
       </c>
       <c r="B2416" s="17" t="n"/>
@@ -42553,7 +42657,7 @@
       <c r="E2417" s="20" t="n"/>
       <c r="F2417" s="20" t="n"/>
     </row>
-    <row r="2418" ht="20" customHeight="1">
+    <row r="2418" ht="45" customHeight="1">
       <c r="A2418" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -42561,7 +42665,7 @@
       </c>
       <c r="B2418" s="19" t="inlineStr">
         <is>
-          <t>Non Architecture s.r.l.</t>
+          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
         </is>
       </c>
       <c r="C2418" s="20" t="n"/>
@@ -42577,7 +42681,7 @@
       </c>
       <c r="B2419" s="19" t="inlineStr">
         <is>
-          <t>886088211</t>
+          <t>76912</t>
         </is>
       </c>
       <c r="C2419" s="20" t="n"/>
@@ -42669,7 +42773,7 @@
       <c r="E2425" s="20" t="n"/>
       <c r="F2425" s="20" t="n"/>
     </row>
-    <row r="2426" ht="20" customHeight="1">
+    <row r="2426" ht="45" customHeight="1">
       <c r="A2426" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -42677,7 +42781,7 @@
       </c>
       <c r="B2426" s="19" t="inlineStr">
         <is>
-          <t>Non Architecture s.r.l.</t>
+          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The limits of peri-urban, semi-urban are quite different across European national legislation.</t>
         </is>
       </c>
       <c r="C2426" s="20" t="n"/>
@@ -42721,7 +42825,7 @@
       </c>
       <c r="B2429" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/886088211</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/76912</t>
         </is>
       </c>
       <c r="C2429" s="20" t="n"/>
@@ -42732,7 +42836,7 @@
     <row r="2431" ht="30" customHeight="1">
       <c r="A2431" s="16" t="inlineStr">
         <is>
-          <t>FICHA 163: 871698261</t>
+          <t>FICHA 163: 77665</t>
         </is>
       </c>
       <c r="B2431" s="17" t="n"/>
@@ -42757,7 +42861,7 @@
       <c r="E2432" s="20" t="n"/>
       <c r="F2432" s="20" t="n"/>
     </row>
-    <row r="2433" ht="20" customHeight="1">
+    <row r="2433" ht="45" customHeight="1">
       <c r="A2433" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -42765,7 +42869,7 @@
       </c>
       <c r="B2433" s="19" t="inlineStr">
         <is>
-          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
+          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
         </is>
       </c>
       <c r="C2433" s="20" t="n"/>
@@ -42781,7 +42885,7 @@
       </c>
       <c r="B2434" s="19" t="inlineStr">
         <is>
-          <t>871698261</t>
+          <t>77665</t>
         </is>
       </c>
       <c r="C2434" s="20" t="n"/>
@@ -42873,7 +42977,7 @@
       <c r="E2440" s="20" t="n"/>
       <c r="F2440" s="20" t="n"/>
     </row>
-    <row r="2441" ht="20" customHeight="1">
+    <row r="2441" ht="45" customHeight="1">
       <c r="A2441" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -42881,7 +42985,7 @@
       </c>
       <c r="B2441" s="19" t="inlineStr">
         <is>
-          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
+          <t>The call requires to ‘Demonstrate the innovative solution(s) in at least three neighbourhoods from urban, peri-urban and rural areas (…)‘. Does every single demonstration need to cover the 3 areas, or at least one demonstration in each area?</t>
         </is>
       </c>
       <c r="C2441" s="20" t="n"/>
@@ -42925,7 +43029,7 @@
       </c>
       <c r="B2444" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/871698261</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/77665</t>
         </is>
       </c>
       <c r="C2444" s="20" t="n"/>
@@ -42936,7 +43040,7 @@
     <row r="2446" ht="30" customHeight="1">
       <c r="A2446" s="16" t="inlineStr">
         <is>
-          <t>FICHA 164: 918605133</t>
+          <t>FICHA 164: 886088211</t>
         </is>
       </c>
       <c r="B2446" s="17" t="n"/>
@@ -42969,7 +43073,7 @@
       </c>
       <c r="B2448" s="19" t="inlineStr">
         <is>
-          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
+          <t>Non Architecture s.r.l.</t>
         </is>
       </c>
       <c r="C2448" s="20" t="n"/>
@@ -42985,7 +43089,7 @@
       </c>
       <c r="B2449" s="19" t="inlineStr">
         <is>
-          <t>918605133</t>
+          <t>886088211</t>
         </is>
       </c>
       <c r="C2449" s="20" t="n"/>
@@ -43085,7 +43189,7 @@
       </c>
       <c r="B2456" s="19" t="inlineStr">
         <is>
-          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
+          <t>Non Architecture s.r.l.</t>
         </is>
       </c>
       <c r="C2456" s="20" t="n"/>
@@ -43129,7 +43233,7 @@
       </c>
       <c r="B2459" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/918605133</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/886088211</t>
         </is>
       </c>
       <c r="C2459" s="20" t="n"/>
@@ -43140,7 +43244,7 @@
     <row r="2461" ht="30" customHeight="1">
       <c r="A2461" s="16" t="inlineStr">
         <is>
-          <t>FICHA 165: 485</t>
+          <t>FICHA 165: 871698261</t>
         </is>
       </c>
       <c r="B2461" s="17" t="n"/>
@@ -43165,7 +43269,7 @@
       <c r="E2462" s="20" t="n"/>
       <c r="F2462" s="20" t="n"/>
     </row>
-    <row r="2463" ht="45" customHeight="1">
+    <row r="2463" ht="20" customHeight="1">
       <c r="A2463" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -43173,7 +43277,7 @@
       </c>
       <c r="B2463" s="19" t="inlineStr">
         <is>
-          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
+          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
         </is>
       </c>
       <c r="C2463" s="20" t="n"/>
@@ -43189,7 +43293,7 @@
       </c>
       <c r="B2464" s="19" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>871698261</t>
         </is>
       </c>
       <c r="C2464" s="20" t="n"/>
@@ -43281,7 +43385,7 @@
       <c r="E2470" s="20" t="n"/>
       <c r="F2470" s="20" t="n"/>
     </row>
-    <row r="2471" ht="45" customHeight="1">
+    <row r="2471" ht="20" customHeight="1">
       <c r="A2471" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -43289,7 +43393,7 @@
       </c>
       <c r="B2471" s="19" t="inlineStr">
         <is>
-          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
+          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd. Sti.</t>
         </is>
       </c>
       <c r="C2471" s="20" t="n"/>
@@ -43333,7 +43437,7 @@
       </c>
       <c r="B2474" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/485</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/871698261</t>
         </is>
       </c>
       <c r="C2474" s="20" t="n"/>
@@ -43344,7 +43448,7 @@
     <row r="2476" ht="30" customHeight="1">
       <c r="A2476" s="16" t="inlineStr">
         <is>
-          <t>FICHA 166: 892931076</t>
+          <t>FICHA 166: 918605133</t>
         </is>
       </c>
       <c r="B2476" s="17" t="n"/>
@@ -43377,7 +43481,7 @@
       </c>
       <c r="B2478" s="19" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
         </is>
       </c>
       <c r="C2478" s="20" t="n"/>
@@ -43393,7 +43497,7 @@
       </c>
       <c r="B2479" s="19" t="inlineStr">
         <is>
-          <t>892931076</t>
+          <t>918605133</t>
         </is>
       </c>
       <c r="C2479" s="20" t="n"/>
@@ -43493,7 +43597,7 @@
       </c>
       <c r="B2486" s="19" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
         </is>
       </c>
       <c r="C2486" s="20" t="n"/>
@@ -43537,7 +43641,7 @@
       </c>
       <c r="B2489" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/892931076</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/918605133</t>
         </is>
       </c>
       <c r="C2489" s="20" t="n"/>
@@ -43548,7 +43652,7 @@
     <row r="2491" ht="30" customHeight="1">
       <c r="A2491" s="16" t="inlineStr">
         <is>
-          <t>FICHA 167: 936518123</t>
+          <t>FICHA 167: 485</t>
         </is>
       </c>
       <c r="B2491" s="17" t="n"/>
@@ -43573,7 +43677,7 @@
       <c r="E2492" s="20" t="n"/>
       <c r="F2492" s="20" t="n"/>
     </row>
-    <row r="2493" ht="20" customHeight="1">
+    <row r="2493" ht="45" customHeight="1">
       <c r="A2493" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -43581,7 +43685,7 @@
       </c>
       <c r="B2493" s="19" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
         </is>
       </c>
       <c r="C2493" s="20" t="n"/>
@@ -43597,7 +43701,7 @@
       </c>
       <c r="B2494" s="19" t="inlineStr">
         <is>
-          <t>936518123</t>
+          <t>485</t>
         </is>
       </c>
       <c r="C2494" s="20" t="n"/>
@@ -43689,7 +43793,7 @@
       <c r="E2500" s="20" t="n"/>
       <c r="F2500" s="20" t="n"/>
     </row>
-    <row r="2501" ht="20" customHeight="1">
+    <row r="2501" ht="45" customHeight="1">
       <c r="A2501" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -43697,7 +43801,7 @@
       </c>
       <c r="B2501" s="19" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>Can an International European Interest Organisation (IEIO) participate in the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)"?</t>
         </is>
       </c>
       <c r="C2501" s="20" t="n"/>
@@ -43741,7 +43845,7 @@
       </c>
       <c r="B2504" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/936518123</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/485</t>
         </is>
       </c>
       <c r="C2504" s="20" t="n"/>
@@ -43752,7 +43856,7 @@
     <row r="2506" ht="30" customHeight="1">
       <c r="A2506" s="16" t="inlineStr">
         <is>
-          <t>FICHA 168: EU4H</t>
+          <t>FICHA 168: 892931076</t>
         </is>
       </c>
       <c r="B2506" s="17" t="n"/>
@@ -43785,7 +43889,7 @@
       </c>
       <c r="B2508" s="19" t="inlineStr">
         <is>
-          <t>European Linkage of Initiative from Science to Action in Health</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="C2508" s="20" t="n"/>
@@ -43801,7 +43905,7 @@
       </c>
       <c r="B2509" s="19" t="inlineStr">
         <is>
-          <t>EU4H</t>
+          <t>892931076</t>
         </is>
       </c>
       <c r="C2509" s="20" t="n"/>
@@ -43887,11 +43991,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2515" s="19" t="inlineStr">
-        <is>
-          <t>EU4H-2022-PJ-3</t>
-        </is>
-      </c>
+      <c r="B2515" s="19" t="inlineStr"/>
       <c r="C2515" s="20" t="n"/>
       <c r="D2515" s="20" t="n"/>
       <c r="E2515" s="20" t="n"/>
@@ -43905,7 +44005,7 @@
       </c>
       <c r="B2516" s="19" t="inlineStr">
         <is>
-          <t>European Linkage of Initiative from Science to Action in Health</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="C2516" s="20" t="n"/>
@@ -43949,7 +44049,7 @@
       </c>
       <c r="B2519" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EU4H</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/892931076</t>
         </is>
       </c>
       <c r="C2519" s="20" t="n"/>
@@ -43960,7 +44060,7 @@
     <row r="2521" ht="30" customHeight="1">
       <c r="A2521" s="16" t="inlineStr">
         <is>
-          <t>FICHA 169: 19519</t>
+          <t>FICHA 169: 936518123</t>
         </is>
       </c>
       <c r="B2521" s="17" t="n"/>
@@ -43985,7 +44085,7 @@
       <c r="E2522" s="20" t="n"/>
       <c r="F2522" s="20" t="n"/>
     </row>
-    <row r="2523" ht="45" customHeight="1">
+    <row r="2523" ht="20" customHeight="1">
       <c r="A2523" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -43993,7 +44093,7 @@
       </c>
       <c r="B2523" s="19" t="inlineStr">
         <is>
-          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge): is it possible to present an urban innovation project that intervenes in the public space of a housing district, or does it have to be a building itself?</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="C2523" s="20" t="n"/>
@@ -44009,7 +44109,7 @@
       </c>
       <c r="B2524" s="19" t="inlineStr">
         <is>
-          <t>19519</t>
+          <t>936518123</t>
         </is>
       </c>
       <c r="C2524" s="20" t="n"/>
@@ -44101,7 +44201,7 @@
       <c r="E2530" s="20" t="n"/>
       <c r="F2530" s="20" t="n"/>
     </row>
-    <row r="2531" ht="45" customHeight="1">
+    <row r="2531" ht="20" customHeight="1">
       <c r="A2531" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -44109,7 +44209,7 @@
       </c>
       <c r="B2531" s="19" t="inlineStr">
         <is>
-          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge): is it possible to present an urban innovation project that intervenes in the public space of a housing district, or does it have to be a building itself?</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="C2531" s="20" t="n"/>
@@ -44153,7 +44253,7 @@
       </c>
       <c r="B2534" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19519</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/936518123</t>
         </is>
       </c>
       <c r="C2534" s="20" t="n"/>
@@ -44164,7 +44264,7 @@
     <row r="2536" ht="30" customHeight="1">
       <c r="A2536" s="16" t="inlineStr">
         <is>
-          <t>FICHA 170: 9532</t>
+          <t>FICHA 170: EU4H</t>
         </is>
       </c>
       <c r="B2536" s="17" t="n"/>
@@ -44189,7 +44289,7 @@
       <c r="E2537" s="20" t="n"/>
       <c r="F2537" s="20" t="n"/>
     </row>
-    <row r="2538" ht="45" customHeight="1">
+    <row r="2538" ht="20" customHeight="1">
       <c r="A2538" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -44197,7 +44297,7 @@
       </c>
       <c r="B2538" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-ICT-2018-2020, topic ICT-03-2018-2019 it is recommended that "Actions should … develop close links with on-going European and national initiatives in order to maximize impact." Where can information on those initiatives be found?</t>
+          <t>European Linkage of Initiative from Science to Action in Health</t>
         </is>
       </c>
       <c r="C2538" s="20" t="n"/>
@@ -44213,7 +44313,7 @@
       </c>
       <c r="B2539" s="19" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>EU4H</t>
         </is>
       </c>
       <c r="C2539" s="20" t="n"/>
@@ -44299,13 +44399,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2545" s="19" t="inlineStr"/>
+      <c r="B2545" s="19" t="inlineStr">
+        <is>
+          <t>EU4H-2022-PJ-3</t>
+        </is>
+      </c>
       <c r="C2545" s="20" t="n"/>
       <c r="D2545" s="20" t="n"/>
       <c r="E2545" s="20" t="n"/>
       <c r="F2545" s="20" t="n"/>
     </row>
-    <row r="2546" ht="45" customHeight="1">
+    <row r="2546" ht="20" customHeight="1">
       <c r="A2546" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -44313,7 +44417,7 @@
       </c>
       <c r="B2546" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-ICT-2018-2020, topic ICT-03-2018-2019 it is recommended that "Actions should … develop close links with on-going European and national initiatives in order to maximize impact." Where can information on those initiatives be found?</t>
+          <t>European Linkage of Initiative from Science to Action in Health</t>
         </is>
       </c>
       <c r="C2546" s="20" t="n"/>
@@ -44357,7 +44461,7 @@
       </c>
       <c r="B2549" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/9532</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EU4H</t>
         </is>
       </c>
       <c r="C2549" s="20" t="n"/>
@@ -44368,7 +44472,7 @@
     <row r="2551" ht="30" customHeight="1">
       <c r="A2551" s="16" t="inlineStr">
         <is>
-          <t>FICHA 171: 513</t>
+          <t>FICHA 171: 19519</t>
         </is>
       </c>
       <c r="B2551" s="17" t="n"/>
@@ -44401,7 +44505,7 @@
       </c>
       <c r="B2553" s="19" t="inlineStr">
         <is>
-          <t>Under the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)", which secondments from and to an International European Interest Organisation (IEIO) are eligible for funding?</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge): is it possible to present an urban innovation project that intervenes in the public space of a housing district, or does it have to be a building itself?</t>
         </is>
       </c>
       <c r="C2553" s="20" t="n"/>
@@ -44417,7 +44521,7 @@
       </c>
       <c r="B2554" s="19" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="C2554" s="20" t="n"/>
@@ -44517,7 +44621,7 @@
       </c>
       <c r="B2561" s="19" t="inlineStr">
         <is>
-          <t>Under the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)", which secondments from and to an International European Interest Organisation (IEIO) are eligible for funding?</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge): is it possible to present an urban innovation project that intervenes in the public space of a housing district, or does it have to be a building itself?</t>
         </is>
       </c>
       <c r="C2561" s="20" t="n"/>
@@ -44561,7 +44665,7 @@
       </c>
       <c r="B2564" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/513</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19519</t>
         </is>
       </c>
       <c r="C2564" s="20" t="n"/>
@@ -44572,7 +44676,7 @@
     <row r="2566" ht="30" customHeight="1">
       <c r="A2566" s="16" t="inlineStr">
         <is>
-          <t>FICHA 172: 22334</t>
+          <t>FICHA 172: 9532</t>
         </is>
       </c>
       <c r="B2566" s="17" t="n"/>
@@ -44605,7 +44709,7 @@
       </c>
       <c r="B2568" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2023-EUSIC-PRIZES-04: Regarding the European Social Innovation Competition, our initiative has already received a regional award from my country and/or support from European structural funds. Does this disqualify us?</t>
+          <t>Under call H2020-ICT-2018-2020, topic ICT-03-2018-2019 it is recommended that "Actions should … develop close links with on-going European and national initiatives in order to maximize impact." Where can information on those initiatives be found?</t>
         </is>
       </c>
       <c r="C2568" s="20" t="n"/>
@@ -44621,7 +44725,7 @@
       </c>
       <c r="B2569" s="19" t="inlineStr">
         <is>
-          <t>22334</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="C2569" s="20" t="n"/>
@@ -44721,7 +44825,7 @@
       </c>
       <c r="B2576" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2023-EUSIC-PRIZES-04: Regarding the European Social Innovation Competition, our initiative has already received a regional award from my country and/or support from European structural funds. Does this disqualify us?</t>
+          <t>Under call H2020-ICT-2018-2020, topic ICT-03-2018-2019 it is recommended that "Actions should … develop close links with on-going European and national initiatives in order to maximize impact." Where can information on those initiatives be found?</t>
         </is>
       </c>
       <c r="C2576" s="20" t="n"/>
@@ -44765,7 +44869,7 @@
       </c>
       <c r="B2579" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/22334</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/9532</t>
         </is>
       </c>
       <c r="C2579" s="20" t="n"/>
@@ -44776,7 +44880,7 @@
     <row r="2581" ht="30" customHeight="1">
       <c r="A2581" s="16" t="inlineStr">
         <is>
-          <t>FICHA 173: EUS-23950</t>
+          <t>FICHA 173: 513</t>
         </is>
       </c>
       <c r="B2581" s="17" t="n"/>
@@ -44793,7 +44897,7 @@
       </c>
       <c r="B2582" s="19" t="inlineStr">
         <is>
-          <t>🟢 Euskadi</t>
+          <t>🇪🇺 Europa</t>
         </is>
       </c>
       <c r="C2582" s="20" t="n"/>
@@ -44809,7 +44913,7 @@
       </c>
       <c r="B2583" s="19" t="inlineStr">
         <is>
-          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocatorias transversales ligadas a multitud de líneas innovadoras, que atañen a inteligencia artificial y digitalización, energía y descarbonizació</t>
+          <t>Under the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)", which secondments from and to an International European Interest Organisation (IEIO) are eligible for funding?</t>
         </is>
       </c>
       <c r="C2583" s="20" t="n"/>
@@ -44825,7 +44929,7 @@
       </c>
       <c r="B2584" s="19" t="inlineStr">
         <is>
-          <t>EUS-23950</t>
+          <t>513</t>
         </is>
       </c>
       <c r="C2584" s="20" t="n"/>
@@ -44839,11 +44943,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B2585" s="19" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
+      <c r="B2585" s="19" t="inlineStr"/>
       <c r="C2585" s="20" t="n"/>
       <c r="D2585" s="20" t="n"/>
       <c r="E2585" s="20" t="n"/>
@@ -44857,7 +44957,7 @@
       </c>
       <c r="B2586" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C2586" s="20" t="n"/>
@@ -44901,7 +45001,7 @@
       </c>
       <c r="B2589" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>No disponible</t>
         </is>
       </c>
       <c r="C2589" s="20" t="n"/>
@@ -44921,7 +45021,7 @@
       <c r="E2590" s="20" t="n"/>
       <c r="F2590" s="20" t="n"/>
     </row>
-    <row r="2591" ht="20" customHeight="1">
+    <row r="2591" ht="45" customHeight="1">
       <c r="A2591" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -44929,7 +45029,7 @@
       </c>
       <c r="B2591" s="19" t="inlineStr">
         <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+          <t>Under the action "Marie Skłodowska-Curie Research and Innovation Staff Exchange (RISE)", which secondments from and to an International European Interest Organisation (IEIO) are eligible for funding?</t>
         </is>
       </c>
       <c r="C2591" s="20" t="n"/>
@@ -44943,11 +45043,7 @@
           <t>Tags</t>
         </is>
       </c>
-      <c r="B2592" s="19" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
+      <c r="B2592" s="19" t="inlineStr"/>
       <c r="C2592" s="20" t="n"/>
       <c r="D2592" s="20" t="n"/>
       <c r="E2592" s="20" t="n"/>
@@ -44959,9 +45055,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2593" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALTA — </t>
+      <c r="B2593" s="19" t="inlineStr">
+        <is>
+          <t>INFO — Revisar relevancia para el Ayuntamiento de Bilbao.</t>
         </is>
       </c>
       <c r="C2593" s="20" t="n"/>
@@ -44977,7 +45073,7 @@
       </c>
       <c r="B2594" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/horizonzeharkakodeialdiak/web01-tramite/es/</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/513</t>
         </is>
       </c>
       <c r="C2594" s="20" t="n"/>
@@ -44988,7 +45084,7 @@
     <row r="2596" ht="30" customHeight="1">
       <c r="A2596" s="16" t="inlineStr">
         <is>
-          <t>FICHA 174: EUS-04778</t>
+          <t>FICHA 174: 22334</t>
         </is>
       </c>
       <c r="B2596" s="17" t="n"/>
@@ -45005,7 +45101,7 @@
       </c>
       <c r="B2597" s="19" t="inlineStr">
         <is>
-          <t>🟢 Euskadi</t>
+          <t>🇪🇺 Europa</t>
         </is>
       </c>
       <c r="C2597" s="20" t="n"/>
@@ -45021,7 +45117,7 @@
       </c>
       <c r="B2598" s="19" t="inlineStr">
         <is>
-          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfronterizos de energía renovable. Se prevé una nueva convocatoria para noviembre de 2026.</t>
+          <t>HORIZON-EIC-2023-EUSIC-PRIZES-04: Regarding the European Social Innovation Competition, our initiative has already received a regional award from my country and/or support from European structural funds. Does this disqualify us?</t>
         </is>
       </c>
       <c r="C2598" s="20" t="n"/>
@@ -45037,7 +45133,7 @@
       </c>
       <c r="B2599" s="19" t="inlineStr">
         <is>
-          <t>EUS-04778</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="C2599" s="20" t="n"/>
@@ -45051,11 +45147,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B2600" s="19" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
+      <c r="B2600" s="19" t="inlineStr"/>
       <c r="C2600" s="20" t="n"/>
       <c r="D2600" s="20" t="n"/>
       <c r="E2600" s="20" t="n"/>
@@ -45069,7 +45161,7 @@
       </c>
       <c r="B2601" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C2601" s="20" t="n"/>
@@ -45113,7 +45205,7 @@
       </c>
       <c r="B2604" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>No disponible</t>
         </is>
       </c>
       <c r="C2604" s="20" t="n"/>
@@ -45133,7 +45225,7 @@
       <c r="E2605" s="20" t="n"/>
       <c r="F2605" s="20" t="n"/>
     </row>
-    <row r="2606" ht="20" customHeight="1">
+    <row r="2606" ht="45" customHeight="1">
       <c r="A2606" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -45141,7 +45233,7 @@
       </c>
       <c r="B2606" s="19" t="inlineStr">
         <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+          <t>HORIZON-EIC-2023-EUSIC-PRIZES-04: Regarding the European Social Innovation Competition, our initiative has already received a regional award from my country and/or support from European structural funds. Does this disqualify us?</t>
         </is>
       </c>
       <c r="C2606" s="20" t="n"/>
@@ -45155,11 +45247,7 @@
           <t>Tags</t>
         </is>
       </c>
-      <c r="B2607" s="19" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
+      <c r="B2607" s="19" t="inlineStr"/>
       <c r="C2607" s="20" t="n"/>
       <c r="D2607" s="20" t="n"/>
       <c r="E2607" s="20" t="n"/>
@@ -45171,9 +45259,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2608" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALTA — </t>
+      <c r="B2608" s="19" t="inlineStr">
+        <is>
+          <t>INFO — Revisar relevancia para el Ayuntamiento de Bilbao.</t>
         </is>
       </c>
       <c r="C2608" s="20" t="n"/>
@@ -45189,7 +45277,7 @@
       </c>
       <c r="B2609" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/cefmugazgaindikoberriztag/web01-tramite/es/</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/22334</t>
         </is>
       </c>
       <c r="C2609" s="20" t="n"/>
@@ -45200,7 +45288,7 @@
     <row r="2611" ht="30" customHeight="1">
       <c r="A2611" s="16" t="inlineStr">
         <is>
-          <t>FICHA 175: EUS-19473</t>
+          <t>FICHA 175: EUS-63611</t>
         </is>
       </c>
       <c r="B2611" s="17" t="n"/>
@@ -45225,7 +45313,7 @@
       <c r="E2612" s="20" t="n"/>
       <c r="F2612" s="20" t="n"/>
     </row>
-    <row r="2613" ht="20" customHeight="1">
+    <row r="2613" ht="45" customHeight="1">
       <c r="A2613" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -45233,7 +45321,7 @@
       </c>
       <c r="B2613" s="19" t="inlineStr">
         <is>
-          <t>Suministro de más trípticos relativos a la zona de bajas emisiones</t>
+          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocatorias transversales ligadas a multitud de líneas innovadoras, que atañen a inteligencia artificial y digitalización, energía y descarbonizació</t>
         </is>
       </c>
       <c r="C2613" s="20" t="n"/>
@@ -45249,7 +45337,7 @@
       </c>
       <c r="B2614" s="19" t="inlineStr">
         <is>
-          <t>EUS-19473</t>
+          <t>EUS-63611</t>
         </is>
       </c>
       <c r="C2614" s="20" t="n"/>
@@ -45325,7 +45413,7 @@
       </c>
       <c r="B2619" s="19" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="C2619" s="20" t="n"/>
@@ -45401,7 +45489,7 @@
       </c>
       <c r="B2624" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-mas-tripticos-relativos-zona-bajas-emisiones/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/horizonzeharkakodeialdiak/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2624" s="20" t="n"/>
@@ -45412,7 +45500,7 @@
     <row r="2626" ht="30" customHeight="1">
       <c r="A2626" s="16" t="inlineStr">
         <is>
-          <t>FICHA 176: EUS-16615</t>
+          <t>FICHA 176: EUS-46816</t>
         </is>
       </c>
       <c r="B2626" s="17" t="n"/>
@@ -45445,7 +45533,7 @@
       </c>
       <c r="B2628" s="19" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
+          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfronterizos de energía renovable. Se prevé una nueva convocatoria para noviembre de 2026.</t>
         </is>
       </c>
       <c r="C2628" s="20" t="n"/>
@@ -45461,7 +45549,7 @@
       </c>
       <c r="B2629" s="19" t="inlineStr">
         <is>
-          <t>EUS-16615</t>
+          <t>EUS-46816</t>
         </is>
       </c>
       <c r="C2629" s="20" t="n"/>
@@ -45595,9 +45683,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2638" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
+      <c r="B2638" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTA — </t>
         </is>
       </c>
       <c r="C2638" s="20" t="n"/>
@@ -45613,7 +45701,7 @@
       </c>
       <c r="B2639" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/bioaniztasunfundaziohirin/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/cefmugazgaindikoberriztag/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2639" s="20" t="n"/>
@@ -45624,7 +45712,7 @@
     <row r="2641" ht="30" customHeight="1">
       <c r="A2641" s="16" t="inlineStr">
         <is>
-          <t>FICHA 177: EUS-42934</t>
+          <t>FICHA 177: EUS-59501</t>
         </is>
       </c>
       <c r="B2641" s="17" t="n"/>
@@ -45657,7 +45745,7 @@
       </c>
       <c r="B2643" s="19" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>Reparación deficiencias eléctricas en Pabellón</t>
         </is>
       </c>
       <c r="C2643" s="20" t="n"/>
@@ -45673,7 +45761,7 @@
       </c>
       <c r="B2644" s="19" t="inlineStr">
         <is>
-          <t>EUS-42934</t>
+          <t>EUS-59501</t>
         </is>
       </c>
       <c r="C2644" s="20" t="n"/>
@@ -45749,7 +45837,7 @@
       </c>
       <c r="B2649" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2649" s="20" t="n"/>
@@ -45807,9 +45895,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2653" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
+      <c r="B2653" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTA — </t>
         </is>
       </c>
       <c r="C2653" s="20" t="n"/>
@@ -45825,7 +45913,7 @@
       </c>
       <c r="B2654" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/comunicacion-previs-digitalizacion-2027/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/reparacion-deficiencias-electricas-pabellon/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2654" s="20" t="n"/>
@@ -45836,7 +45924,7 @@
     <row r="2656" ht="30" customHeight="1">
       <c r="A2656" s="16" t="inlineStr">
         <is>
-          <t>FICHA 178: EUS-75226</t>
+          <t>FICHA 178: EUS-73899</t>
         </is>
       </c>
       <c r="B2656" s="17" t="n"/>
@@ -45869,7 +45957,7 @@
       </c>
       <c r="B2658" s="19" t="inlineStr">
         <is>
-          <t>Mobiliario (incluido de oficina), complementos mobiliario, aparatos electrodomésticos y limpieza</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
         </is>
       </c>
       <c r="C2658" s="20" t="n"/>
@@ -45885,7 +45973,7 @@
       </c>
       <c r="B2659" s="19" t="inlineStr">
         <is>
-          <t>EUS-75226</t>
+          <t>EUS-73899</t>
         </is>
       </c>
       <c r="C2659" s="20" t="n"/>
@@ -45961,7 +46049,7 @@
       </c>
       <c r="B2664" s="19" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="C2664" s="20" t="n"/>
@@ -46037,7 +46125,7 @@
       </c>
       <c r="B2669" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/mobiliario-incluido-oficina-complementos-mobiliario-aparatos-electrodomesticos-y-limpieza/expcm535274/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/bioaniztasunfundaziohirin/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2669" s="20" t="n"/>
@@ -46048,7 +46136,7 @@
     <row r="2671" ht="30" customHeight="1">
       <c r="A2671" s="16" t="inlineStr">
         <is>
-          <t>FICHA 179: EUS-74374</t>
+          <t>FICHA 179: EUS-72308</t>
         </is>
       </c>
       <c r="B2671" s="17" t="n"/>
@@ -46073,7 +46161,7 @@
       <c r="E2672" s="20" t="n"/>
       <c r="F2672" s="20" t="n"/>
     </row>
-    <row r="2673" ht="45" customHeight="1">
+    <row r="2673" ht="20" customHeight="1">
       <c r="A2673" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -46081,7 +46169,7 @@
       </c>
       <c r="B2673" s="19" t="inlineStr">
         <is>
-          <t>Mobiliario (incluido de oficina), complementos mobiliario, aparatos electrodomésticos y limpieza</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="C2673" s="20" t="n"/>
@@ -46097,7 +46185,7 @@
       </c>
       <c r="B2674" s="19" t="inlineStr">
         <is>
-          <t>EUS-74374</t>
+          <t>EUS-72308</t>
         </is>
       </c>
       <c r="C2674" s="20" t="n"/>
@@ -46173,7 +46261,7 @@
       </c>
       <c r="B2679" s="19" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="C2679" s="20" t="n"/>
@@ -46249,7 +46337,7 @@
       </c>
       <c r="B2684" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/mobiliario-incluido-oficina-complementos-mobiliario-aparatos-electrodomesticos-y-limpieza/expcm535265/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/comunicacion-previs-digitalizacion-2027/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2684" s="20" t="n"/>
@@ -46257,8 +46345,644 @@
       <c r="E2684" s="20" t="n"/>
       <c r="F2684" s="20" t="n"/>
     </row>
+    <row r="2686" ht="30" customHeight="1">
+      <c r="A2686" s="16" t="inlineStr">
+        <is>
+          <t>FICHA 180: EUS-37473</t>
+        </is>
+      </c>
+      <c r="B2686" s="17" t="n"/>
+      <c r="C2686" s="17" t="n"/>
+      <c r="D2686" s="17" t="n"/>
+      <c r="E2686" s="17" t="n"/>
+      <c r="F2686" s="17" t="n"/>
+    </row>
+    <row r="2687" ht="20" customHeight="1">
+      <c r="A2687" s="18" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B2687" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+      <c r="C2687" s="20" t="n"/>
+      <c r="D2687" s="20" t="n"/>
+      <c r="E2687" s="20" t="n"/>
+      <c r="F2687" s="20" t="n"/>
+    </row>
+    <row r="2688" ht="20" customHeight="1">
+      <c r="A2688" s="18" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B2688" s="19" t="inlineStr">
+        <is>
+          <t>Renovación licencias Teslab, infraestructura docente Joseba Albizuri.</t>
+        </is>
+      </c>
+      <c r="C2688" s="20" t="n"/>
+      <c r="D2688" s="20" t="n"/>
+      <c r="E2688" s="20" t="n"/>
+      <c r="F2688" s="20" t="n"/>
+    </row>
+    <row r="2689" ht="20" customHeight="1">
+      <c r="A2689" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2689" s="19" t="inlineStr">
+        <is>
+          <t>EUS-37473</t>
+        </is>
+      </c>
+      <c r="C2689" s="20" t="n"/>
+      <c r="D2689" s="20" t="n"/>
+      <c r="E2689" s="20" t="n"/>
+      <c r="F2689" s="20" t="n"/>
+    </row>
+    <row r="2690" ht="20" customHeight="1">
+      <c r="A2690" s="18" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B2690" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="C2690" s="20" t="n"/>
+      <c r="D2690" s="20" t="n"/>
+      <c r="E2690" s="20" t="n"/>
+      <c r="F2690" s="20" t="n"/>
+    </row>
+    <row r="2691" ht="20" customHeight="1">
+      <c r="A2691" s="18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B2691" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C2691" s="20" t="n"/>
+      <c r="D2691" s="20" t="n"/>
+      <c r="E2691" s="20" t="n"/>
+      <c r="F2691" s="20" t="n"/>
+    </row>
+    <row r="2692" ht="20" customHeight="1">
+      <c r="A2692" s="18" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B2692" s="19" t="inlineStr"/>
+      <c r="C2692" s="20" t="n"/>
+      <c r="D2692" s="20" t="n"/>
+      <c r="E2692" s="20" t="n"/>
+      <c r="F2692" s="20" t="n"/>
+    </row>
+    <row r="2693" ht="20" customHeight="1">
+      <c r="A2693" s="18" t="inlineStr">
+        <is>
+          <t>Presupuesto (EUR)</t>
+        </is>
+      </c>
+      <c r="B2693" s="19" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="C2693" s="20" t="n"/>
+      <c r="D2693" s="20" t="n"/>
+      <c r="E2693" s="20" t="n"/>
+      <c r="F2693" s="20" t="n"/>
+    </row>
+    <row r="2694" ht="20" customHeight="1">
+      <c r="A2694" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de Accion</t>
+        </is>
+      </c>
+      <c r="B2694" s="19" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="C2694" s="20" t="n"/>
+      <c r="D2694" s="20" t="n"/>
+      <c r="E2694" s="20" t="n"/>
+      <c r="F2694" s="20" t="n"/>
+    </row>
+    <row r="2695" ht="20" customHeight="1">
+      <c r="A2695" s="18" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B2695" s="19" t="inlineStr"/>
+      <c r="C2695" s="20" t="n"/>
+      <c r="D2695" s="20" t="n"/>
+      <c r="E2695" s="20" t="n"/>
+      <c r="F2695" s="20" t="n"/>
+    </row>
+    <row r="2696" ht="20" customHeight="1">
+      <c r="A2696" s="18" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="B2696" s="19" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="C2696" s="20" t="n"/>
+      <c r="D2696" s="20" t="n"/>
+      <c r="E2696" s="20" t="n"/>
+      <c r="F2696" s="20" t="n"/>
+    </row>
+    <row r="2697" ht="20" customHeight="1">
+      <c r="A2697" s="18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B2697" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="C2697" s="20" t="n"/>
+      <c r="D2697" s="20" t="n"/>
+      <c r="E2697" s="20" t="n"/>
+      <c r="F2697" s="20" t="n"/>
+    </row>
+    <row r="2698" ht="20" customHeight="1">
+      <c r="A2698" s="18" t="inlineStr">
+        <is>
+          <t>Relevancia Bilbao</t>
+        </is>
+      </c>
+      <c r="B2698" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
+        </is>
+      </c>
+      <c r="C2698" s="20" t="n"/>
+      <c r="D2698" s="20" t="n"/>
+      <c r="E2698" s="20" t="n"/>
+      <c r="F2698" s="20" t="n"/>
+    </row>
+    <row r="2699" ht="45" customHeight="1">
+      <c r="A2699" s="18" t="inlineStr">
+        <is>
+          <t>Enlace al portal</t>
+        </is>
+      </c>
+      <c r="B2699" s="22" t="inlineStr">
+        <is>
+          <t>https://www.euskadi.eus/anuncio_contratacion/renovacion-licencias-teslab-infraestructura-docente-joseba-albizuri/web01-tramite/es/</t>
+        </is>
+      </c>
+      <c r="C2699" s="20" t="n"/>
+      <c r="D2699" s="20" t="n"/>
+      <c r="E2699" s="20" t="n"/>
+      <c r="F2699" s="20" t="n"/>
+    </row>
+    <row r="2701" ht="30" customHeight="1">
+      <c r="A2701" s="16" t="inlineStr">
+        <is>
+          <t>FICHA 181: EUS-31002</t>
+        </is>
+      </c>
+      <c r="B2701" s="17" t="n"/>
+      <c r="C2701" s="17" t="n"/>
+      <c r="D2701" s="17" t="n"/>
+      <c r="E2701" s="17" t="n"/>
+      <c r="F2701" s="17" t="n"/>
+    </row>
+    <row r="2702" ht="20" customHeight="1">
+      <c r="A2702" s="18" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B2702" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+      <c r="C2702" s="20" t="n"/>
+      <c r="D2702" s="20" t="n"/>
+      <c r="E2702" s="20" t="n"/>
+      <c r="F2702" s="20" t="n"/>
+    </row>
+    <row r="2703" ht="45" customHeight="1">
+      <c r="A2703" s="18" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B2703" s="19" t="inlineStr">
+        <is>
+          <t>Mantenimiento preventivo de la cámara climática del Departamento de Fisiología Vegetal de la UPV/EHU en Leioa, según presupuesto 26/PMJ150, incluyendo la revisión general del equipo, comprobación de p</t>
+        </is>
+      </c>
+      <c r="C2703" s="20" t="n"/>
+      <c r="D2703" s="20" t="n"/>
+      <c r="E2703" s="20" t="n"/>
+      <c r="F2703" s="20" t="n"/>
+    </row>
+    <row r="2704" ht="20" customHeight="1">
+      <c r="A2704" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2704" s="19" t="inlineStr">
+        <is>
+          <t>EUS-31002</t>
+        </is>
+      </c>
+      <c r="C2704" s="20" t="n"/>
+      <c r="D2704" s="20" t="n"/>
+      <c r="E2704" s="20" t="n"/>
+      <c r="F2704" s="20" t="n"/>
+    </row>
+    <row r="2705" ht="20" customHeight="1">
+      <c r="A2705" s="18" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B2705" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="C2705" s="20" t="n"/>
+      <c r="D2705" s="20" t="n"/>
+      <c r="E2705" s="20" t="n"/>
+      <c r="F2705" s="20" t="n"/>
+    </row>
+    <row r="2706" ht="20" customHeight="1">
+      <c r="A2706" s="18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B2706" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C2706" s="20" t="n"/>
+      <c r="D2706" s="20" t="n"/>
+      <c r="E2706" s="20" t="n"/>
+      <c r="F2706" s="20" t="n"/>
+    </row>
+    <row r="2707" ht="20" customHeight="1">
+      <c r="A2707" s="18" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B2707" s="19" t="inlineStr"/>
+      <c r="C2707" s="20" t="n"/>
+      <c r="D2707" s="20" t="n"/>
+      <c r="E2707" s="20" t="n"/>
+      <c r="F2707" s="20" t="n"/>
+    </row>
+    <row r="2708" ht="20" customHeight="1">
+      <c r="A2708" s="18" t="inlineStr">
+        <is>
+          <t>Presupuesto (EUR)</t>
+        </is>
+      </c>
+      <c r="B2708" s="19" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="C2708" s="20" t="n"/>
+      <c r="D2708" s="20" t="n"/>
+      <c r="E2708" s="20" t="n"/>
+      <c r="F2708" s="20" t="n"/>
+    </row>
+    <row r="2709" ht="20" customHeight="1">
+      <c r="A2709" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de Accion</t>
+        </is>
+      </c>
+      <c r="B2709" s="19" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="C2709" s="20" t="n"/>
+      <c r="D2709" s="20" t="n"/>
+      <c r="E2709" s="20" t="n"/>
+      <c r="F2709" s="20" t="n"/>
+    </row>
+    <row r="2710" ht="20" customHeight="1">
+      <c r="A2710" s="18" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B2710" s="19" t="inlineStr"/>
+      <c r="C2710" s="20" t="n"/>
+      <c r="D2710" s="20" t="n"/>
+      <c r="E2710" s="20" t="n"/>
+      <c r="F2710" s="20" t="n"/>
+    </row>
+    <row r="2711" ht="20" customHeight="1">
+      <c r="A2711" s="18" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="B2711" s="19" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="C2711" s="20" t="n"/>
+      <c r="D2711" s="20" t="n"/>
+      <c r="E2711" s="20" t="n"/>
+      <c r="F2711" s="20" t="n"/>
+    </row>
+    <row r="2712" ht="20" customHeight="1">
+      <c r="A2712" s="18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B2712" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="C2712" s="20" t="n"/>
+      <c r="D2712" s="20" t="n"/>
+      <c r="E2712" s="20" t="n"/>
+      <c r="F2712" s="20" t="n"/>
+    </row>
+    <row r="2713" ht="20" customHeight="1">
+      <c r="A2713" s="18" t="inlineStr">
+        <is>
+          <t>Relevancia Bilbao</t>
+        </is>
+      </c>
+      <c r="B2713" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
+        </is>
+      </c>
+      <c r="C2713" s="20" t="n"/>
+      <c r="D2713" s="20" t="n"/>
+      <c r="E2713" s="20" t="n"/>
+      <c r="F2713" s="20" t="n"/>
+    </row>
+    <row r="2714" ht="45" customHeight="1">
+      <c r="A2714" s="18" t="inlineStr">
+        <is>
+          <t>Enlace al portal</t>
+        </is>
+      </c>
+      <c r="B2714" s="22" t="inlineStr">
+        <is>
+          <t>https://www.euskadi.eus/anuncio_contratacion/mantenimiento-preventivo-camara-climatica-del-departamento-fisiologia-vegetal-upv-ehu-leioa-presupuesto-26-pmj150-incluyendo-revision-general-del-equipo-comprobacion-parametros-funcionamiento-presiones-temperaturas-consumos-electricos-y-tensiones-verific/web01-tramite/es/</t>
+        </is>
+      </c>
+      <c r="C2714" s="20" t="n"/>
+      <c r="D2714" s="20" t="n"/>
+      <c r="E2714" s="20" t="n"/>
+      <c r="F2714" s="20" t="n"/>
+    </row>
+    <row r="2716" ht="30" customHeight="1">
+      <c r="A2716" s="16" t="inlineStr">
+        <is>
+          <t>FICHA 182: EUS-50049</t>
+        </is>
+      </c>
+      <c r="B2716" s="17" t="n"/>
+      <c r="C2716" s="17" t="n"/>
+      <c r="D2716" s="17" t="n"/>
+      <c r="E2716" s="17" t="n"/>
+      <c r="F2716" s="17" t="n"/>
+    </row>
+    <row r="2717" ht="20" customHeight="1">
+      <c r="A2717" s="18" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B2717" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+      <c r="C2717" s="20" t="n"/>
+      <c r="D2717" s="20" t="n"/>
+      <c r="E2717" s="20" t="n"/>
+      <c r="F2717" s="20" t="n"/>
+    </row>
+    <row r="2718" ht="45" customHeight="1">
+      <c r="A2718" s="18" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B2718" s="19" t="inlineStr">
+        <is>
+          <t>Reparación de fuga de gas y sustitución de válvula de la cámara climática del Departamento de Fisiología Vegetal de la UPV/EHU en Leioa, según presupuesto 2026/244. La avería fue detectada en la revis</t>
+        </is>
+      </c>
+      <c r="C2718" s="20" t="n"/>
+      <c r="D2718" s="20" t="n"/>
+      <c r="E2718" s="20" t="n"/>
+      <c r="F2718" s="20" t="n"/>
+    </row>
+    <row r="2719" ht="20" customHeight="1">
+      <c r="A2719" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2719" s="19" t="inlineStr">
+        <is>
+          <t>EUS-50049</t>
+        </is>
+      </c>
+      <c r="C2719" s="20" t="n"/>
+      <c r="D2719" s="20" t="n"/>
+      <c r="E2719" s="20" t="n"/>
+      <c r="F2719" s="20" t="n"/>
+    </row>
+    <row r="2720" ht="20" customHeight="1">
+      <c r="A2720" s="18" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B2720" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="C2720" s="20" t="n"/>
+      <c r="D2720" s="20" t="n"/>
+      <c r="E2720" s="20" t="n"/>
+      <c r="F2720" s="20" t="n"/>
+    </row>
+    <row r="2721" ht="20" customHeight="1">
+      <c r="A2721" s="18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B2721" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C2721" s="20" t="n"/>
+      <c r="D2721" s="20" t="n"/>
+      <c r="E2721" s="20" t="n"/>
+      <c r="F2721" s="20" t="n"/>
+    </row>
+    <row r="2722" ht="20" customHeight="1">
+      <c r="A2722" s="18" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B2722" s="19" t="inlineStr"/>
+      <c r="C2722" s="20" t="n"/>
+      <c r="D2722" s="20" t="n"/>
+      <c r="E2722" s="20" t="n"/>
+      <c r="F2722" s="20" t="n"/>
+    </row>
+    <row r="2723" ht="20" customHeight="1">
+      <c r="A2723" s="18" t="inlineStr">
+        <is>
+          <t>Presupuesto (EUR)</t>
+        </is>
+      </c>
+      <c r="B2723" s="19" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="C2723" s="20" t="n"/>
+      <c r="D2723" s="20" t="n"/>
+      <c r="E2723" s="20" t="n"/>
+      <c r="F2723" s="20" t="n"/>
+    </row>
+    <row r="2724" ht="20" customHeight="1">
+      <c r="A2724" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de Accion</t>
+        </is>
+      </c>
+      <c r="B2724" s="19" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="C2724" s="20" t="n"/>
+      <c r="D2724" s="20" t="n"/>
+      <c r="E2724" s="20" t="n"/>
+      <c r="F2724" s="20" t="n"/>
+    </row>
+    <row r="2725" ht="20" customHeight="1">
+      <c r="A2725" s="18" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B2725" s="19" t="inlineStr"/>
+      <c r="C2725" s="20" t="n"/>
+      <c r="D2725" s="20" t="n"/>
+      <c r="E2725" s="20" t="n"/>
+      <c r="F2725" s="20" t="n"/>
+    </row>
+    <row r="2726" ht="20" customHeight="1">
+      <c r="A2726" s="18" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="B2726" s="19" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="C2726" s="20" t="n"/>
+      <c r="D2726" s="20" t="n"/>
+      <c r="E2726" s="20" t="n"/>
+      <c r="F2726" s="20" t="n"/>
+    </row>
+    <row r="2727" ht="20" customHeight="1">
+      <c r="A2727" s="18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B2727" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="C2727" s="20" t="n"/>
+      <c r="D2727" s="20" t="n"/>
+      <c r="E2727" s="20" t="n"/>
+      <c r="F2727" s="20" t="n"/>
+    </row>
+    <row r="2728" ht="20" customHeight="1">
+      <c r="A2728" s="18" t="inlineStr">
+        <is>
+          <t>Relevancia Bilbao</t>
+        </is>
+      </c>
+      <c r="B2728" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
+        </is>
+      </c>
+      <c r="C2728" s="20" t="n"/>
+      <c r="D2728" s="20" t="n"/>
+      <c r="E2728" s="20" t="n"/>
+      <c r="F2728" s="20" t="n"/>
+    </row>
+    <row r="2729" ht="45" customHeight="1">
+      <c r="A2729" s="18" t="inlineStr">
+        <is>
+          <t>Enlace al portal</t>
+        </is>
+      </c>
+      <c r="B2729" s="22" t="inlineStr">
+        <is>
+          <t>https://www.euskadi.eus/anuncio_contratacion/reparacion-fuga-gas-y-sustitucion-valvula-camara-climatica-del-departamento-fisiologia-vegetal-upv-ehu-leioa-presupuesto-2026-244-averia-fue-detectada-revision-general-infraestructura-realizada-gailur/web01-tramite/es/</t>
+        </is>
+      </c>
+      <c r="C2729" s="20" t="n"/>
+      <c r="D2729" s="20" t="n"/>
+      <c r="E2729" s="20" t="n"/>
+      <c r="F2729" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2506">
+  <mergeCells count="2548">
     <mergeCell ref="B679:F679"/>
     <mergeCell ref="B2192:F2192"/>
     <mergeCell ref="B1765:F1765"/>
@@ -46396,6 +47120,7 @@
     <mergeCell ref="B444:F444"/>
     <mergeCell ref="B104:F104"/>
     <mergeCell ref="B742:F742"/>
+    <mergeCell ref="B2687:F2687"/>
     <mergeCell ref="B778:F778"/>
     <mergeCell ref="B2108:F2108"/>
     <mergeCell ref="B1076:F1076"/>
@@ -46433,6 +47158,7 @@
     <mergeCell ref="B2154:F2154"/>
     <mergeCell ref="B2402:F2402"/>
     <mergeCell ref="B755:F755"/>
+    <mergeCell ref="B2706:F2706"/>
     <mergeCell ref="B2488:F2488"/>
     <mergeCell ref="B791:F791"/>
     <mergeCell ref="B913:F913"/>
@@ -46523,6 +47249,7 @@
     <mergeCell ref="B1487:F1487"/>
     <mergeCell ref="B428:F428"/>
     <mergeCell ref="B2373:F2373"/>
+    <mergeCell ref="B2696:F2696"/>
     <mergeCell ref="B884:F884"/>
     <mergeCell ref="A781:F781"/>
     <mergeCell ref="B123:F123"/>
@@ -46530,12 +47257,14 @@
     <mergeCell ref="B2573:F2573"/>
     <mergeCell ref="B1184:F1184"/>
     <mergeCell ref="B2270:F2270"/>
+    <mergeCell ref="B2699:F2699"/>
     <mergeCell ref="B297:F297"/>
     <mergeCell ref="B813:F813"/>
     <mergeCell ref="A1756:F1756"/>
     <mergeCell ref="B1242:F1242"/>
     <mergeCell ref="B2301:F2301"/>
     <mergeCell ref="B902:F902"/>
+    <mergeCell ref="B2724:F2724"/>
     <mergeCell ref="B1331:F1331"/>
     <mergeCell ref="B815:F815"/>
     <mergeCell ref="B1629:F1629"/>
@@ -46734,6 +47463,7 @@
     <mergeCell ref="B1461:F1461"/>
     <mergeCell ref="B1678:F1678"/>
     <mergeCell ref="B619:F619"/>
+    <mergeCell ref="B2704:F2704"/>
     <mergeCell ref="B279:F279"/>
     <mergeCell ref="B410:F410"/>
     <mergeCell ref="B733:F733"/>
@@ -46778,6 +47508,7 @@
     <mergeCell ref="B1991:F1991"/>
     <mergeCell ref="A1291:F1291"/>
     <mergeCell ref="B1388:F1388"/>
+    <mergeCell ref="A2686:F2686"/>
     <mergeCell ref="B806:F806"/>
     <mergeCell ref="B1077:F1077"/>
     <mergeCell ref="A1591:F1591"/>
@@ -46992,6 +47723,7 @@
     <mergeCell ref="B1942:F1942"/>
     <mergeCell ref="B910:F910"/>
     <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B2697:F2697"/>
     <mergeCell ref="B149:F149"/>
     <mergeCell ref="B1855:F1855"/>
     <mergeCell ref="B2392:F2392"/>
@@ -47060,6 +47792,7 @@
     <mergeCell ref="B1309:F1309"/>
     <mergeCell ref="B581:F581"/>
     <mergeCell ref="B2395:F2395"/>
+    <mergeCell ref="B2693:F2693"/>
     <mergeCell ref="B583:F583"/>
     <mergeCell ref="B539:F539"/>
     <mergeCell ref="B577:F577"/>
@@ -47067,10 +47800,12 @@
     <mergeCell ref="B1633:F1633"/>
     <mergeCell ref="B1304:F1304"/>
     <mergeCell ref="B1608:F1608"/>
+    <mergeCell ref="B2695:F2695"/>
     <mergeCell ref="B1967:F1967"/>
     <mergeCell ref="B908:F908"/>
     <mergeCell ref="B883:F883"/>
     <mergeCell ref="B2390:F2390"/>
+    <mergeCell ref="B2694:F2694"/>
     <mergeCell ref="B1969:F1969"/>
     <mergeCell ref="B2267:F2267"/>
     <mergeCell ref="B1208:F1208"/>
@@ -47080,6 +47815,7 @@
     <mergeCell ref="B207:F207"/>
     <mergeCell ref="B1353:F1353"/>
     <mergeCell ref="B636:F636"/>
+    <mergeCell ref="B2721:F2721"/>
     <mergeCell ref="B296:F296"/>
     <mergeCell ref="B934:F934"/>
     <mergeCell ref="B1232:F1232"/>
@@ -47098,6 +47834,7 @@
     <mergeCell ref="B473:F473"/>
     <mergeCell ref="B1532:F1532"/>
     <mergeCell ref="B2424:F2424"/>
+    <mergeCell ref="B2722:F2722"/>
     <mergeCell ref="B1690:F1690"/>
     <mergeCell ref="B807:F807"/>
     <mergeCell ref="B1997:F1997"/>
@@ -47186,6 +47923,7 @@
     <mergeCell ref="B716:F716"/>
     <mergeCell ref="B2291:F2291"/>
     <mergeCell ref="B892:F892"/>
+    <mergeCell ref="B2720:F2720"/>
     <mergeCell ref="B289:F289"/>
     <mergeCell ref="B1479:F1479"/>
     <mergeCell ref="B1777:F1777"/>
@@ -47346,6 +48084,7 @@
     <mergeCell ref="B471:F471"/>
     <mergeCell ref="A1921:F1921"/>
     <mergeCell ref="B769:F769"/>
+    <mergeCell ref="B2714:F2714"/>
     <mergeCell ref="B927:F927"/>
     <mergeCell ref="B1443:F1443"/>
     <mergeCell ref="B44:F44"/>
@@ -47451,6 +48190,7 @@
     <mergeCell ref="B2284:F2284"/>
     <mergeCell ref="B1225:F1225"/>
     <mergeCell ref="B1523:F1523"/>
+    <mergeCell ref="B2713:F2713"/>
     <mergeCell ref="B1979:F1979"/>
     <mergeCell ref="A2191:F2191"/>
     <mergeCell ref="B2286:F2286"/>
@@ -47542,6 +48282,7 @@
     <mergeCell ref="B1318:F1318"/>
     <mergeCell ref="B1494:F1494"/>
     <mergeCell ref="B1792:F1792"/>
+    <mergeCell ref="B2703:F2703"/>
     <mergeCell ref="B1652:F1652"/>
     <mergeCell ref="B2678:F2678"/>
     <mergeCell ref="B891:F891"/>
@@ -47649,6 +48390,7 @@
     <mergeCell ref="A1111:F1111"/>
     <mergeCell ref="B1663:F1663"/>
     <mergeCell ref="B1961:F1961"/>
+    <mergeCell ref="B2718:F2718"/>
     <mergeCell ref="B170:F170"/>
     <mergeCell ref="B2413:F2413"/>
     <mergeCell ref="B328:F328"/>
@@ -47661,6 +48403,7 @@
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B2421:F2421"/>
     <mergeCell ref="B1389:F1389"/>
+    <mergeCell ref="B2719:F2719"/>
     <mergeCell ref="B1345:F1345"/>
     <mergeCell ref="B506:F506"/>
     <mergeCell ref="B628:F628"/>
@@ -47704,6 +48447,7 @@
     <mergeCell ref="B1702:F1702"/>
     <mergeCell ref="B1758:F1758"/>
     <mergeCell ref="B359:F359"/>
+    <mergeCell ref="A2701:F2701"/>
     <mergeCell ref="B2187:F2187"/>
     <mergeCell ref="B2485:F2485"/>
     <mergeCell ref="B788:F788"/>
@@ -47750,18 +48494,21 @@
     <mergeCell ref="B2229:F2229"/>
     <mergeCell ref="B1474:F1474"/>
     <mergeCell ref="B415:F415"/>
+    <mergeCell ref="B2709:F2709"/>
     <mergeCell ref="B1468:F1468"/>
     <mergeCell ref="B713:F713"/>
     <mergeCell ref="B2410:F2410"/>
     <mergeCell ref="B1766:F1766"/>
     <mergeCell ref="B1011:F1011"/>
     <mergeCell ref="B1897:F1897"/>
+    <mergeCell ref="B2717:F2717"/>
     <mergeCell ref="B1685:F1685"/>
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="A1381:F1381"/>
     <mergeCell ref="B1983:F1983"/>
     <mergeCell ref="B924:F924"/>
     <mergeCell ref="B2195:F2195"/>
+    <mergeCell ref="B2711:F2711"/>
     <mergeCell ref="B584:F584"/>
     <mergeCell ref="B2114:F2114"/>
     <mergeCell ref="B2412:F2412"/>
@@ -47769,6 +48516,7 @@
     <mergeCell ref="B1013:F1013"/>
     <mergeCell ref="B1985:F1985"/>
     <mergeCell ref="A1681:F1681"/>
+    <mergeCell ref="B2712:F2712"/>
     <mergeCell ref="B1799:F1799"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B731:F731"/>
@@ -47979,6 +48727,7 @@
     <mergeCell ref="B2560:F2560"/>
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B230:F230"/>
+    <mergeCell ref="B2691:F2691"/>
     <mergeCell ref="B1202:F1202"/>
     <mergeCell ref="B143:F143"/>
     <mergeCell ref="B118:F118"/>
@@ -48001,10 +48750,12 @@
     <mergeCell ref="B503:F503"/>
     <mergeCell ref="B2588:F2588"/>
     <mergeCell ref="B932:F932"/>
+    <mergeCell ref="B2702:F2702"/>
     <mergeCell ref="B617:F617"/>
     <mergeCell ref="B1222:F1222"/>
     <mergeCell ref="B1520:F1520"/>
     <mergeCell ref="B803:F803"/>
+    <mergeCell ref="B2710:F2710"/>
     <mergeCell ref="B917:F917"/>
     <mergeCell ref="B162:F162"/>
     <mergeCell ref="B2247:F2247"/>
@@ -48016,6 +48767,7 @@
     <mergeCell ref="B2276:F2276"/>
     <mergeCell ref="B1217:F1217"/>
     <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B2705:F2705"/>
     <mergeCell ref="A1891:F1891"/>
     <mergeCell ref="B485:F485"/>
     <mergeCell ref="B2189:F2189"/>
@@ -48115,6 +48867,7 @@
     <mergeCell ref="B2299:F2299"/>
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B512:F512"/>
+    <mergeCell ref="B2728:F2728"/>
     <mergeCell ref="B2000:F2000"/>
     <mergeCell ref="B303:F303"/>
     <mergeCell ref="B941:F941"/>
@@ -48125,12 +48878,14 @@
     <mergeCell ref="B732:F732"/>
     <mergeCell ref="B2605:F2605"/>
     <mergeCell ref="B1030:F1030"/>
+    <mergeCell ref="B2727:F2727"/>
     <mergeCell ref="B1328:F1328"/>
     <mergeCell ref="B812:F812"/>
     <mergeCell ref="B2002:F2002"/>
     <mergeCell ref="B2300:F2300"/>
     <mergeCell ref="B603:F603"/>
     <mergeCell ref="B1241:F1241"/>
+    <mergeCell ref="B2729:F2729"/>
     <mergeCell ref="A2626:F2626"/>
     <mergeCell ref="A541:F541"/>
     <mergeCell ref="B2302:F2302"/>
@@ -48225,6 +48980,7 @@
     <mergeCell ref="B1789:F1789"/>
     <mergeCell ref="B2087:F2087"/>
     <mergeCell ref="B1028:F1028"/>
+    <mergeCell ref="B2725:F2725"/>
     <mergeCell ref="B1055:F1055"/>
     <mergeCell ref="B1326:F1326"/>
     <mergeCell ref="B1668:F1668"/>
@@ -48361,6 +49117,7 @@
     <mergeCell ref="B1524:F1524"/>
     <mergeCell ref="B763:F763"/>
     <mergeCell ref="B738:F738"/>
+    <mergeCell ref="B2708:F2708"/>
     <mergeCell ref="B1061:F1061"/>
     <mergeCell ref="A2461:F2461"/>
     <mergeCell ref="B4:F4"/>
@@ -48414,6 +49171,7 @@
     <mergeCell ref="B777:F777"/>
     <mergeCell ref="B2504:F2504"/>
     <mergeCell ref="B1749:F1749"/>
+    <mergeCell ref="A2716:F2716"/>
     <mergeCell ref="B504:F504"/>
     <mergeCell ref="B802:F802"/>
     <mergeCell ref="B1136:F1136"/>
@@ -48473,6 +49231,7 @@
     <mergeCell ref="B2578:F2578"/>
     <mergeCell ref="A2056:F2056"/>
     <mergeCell ref="B447:F447"/>
+    <mergeCell ref="B2690:F2690"/>
     <mergeCell ref="B605:F605"/>
     <mergeCell ref="B1631:F1631"/>
     <mergeCell ref="B142:F142"/>
@@ -48483,6 +49242,7 @@
     <mergeCell ref="B1508:F1508"/>
     <mergeCell ref="B1114:F1114"/>
     <mergeCell ref="A2476:F2476"/>
+    <mergeCell ref="B2692:F2692"/>
     <mergeCell ref="B607:F607"/>
     <mergeCell ref="B1660:F1660"/>
     <mergeCell ref="B905:F905"/>
@@ -48569,6 +49329,7 @@
     <mergeCell ref="B138:F138"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="A1081:F1081"/>
+    <mergeCell ref="B2688:F2688"/>
     <mergeCell ref="B1933:F1933"/>
     <mergeCell ref="B1927:F1927"/>
     <mergeCell ref="B876:F876"/>
@@ -48587,6 +49348,7 @@
     <mergeCell ref="B1499:F1499"/>
     <mergeCell ref="B440:F440"/>
     <mergeCell ref="B2391:F2391"/>
+    <mergeCell ref="B2689:F2689"/>
     <mergeCell ref="B2683:F2683"/>
     <mergeCell ref="B598:F598"/>
     <mergeCell ref="B1928:F1928"/>
@@ -48692,14 +49454,17 @@
     <mergeCell ref="B2278:F2278"/>
     <mergeCell ref="B193:F193"/>
     <mergeCell ref="B1016:F1016"/>
+    <mergeCell ref="B2707:F2707"/>
     <mergeCell ref="B282:F282"/>
     <mergeCell ref="B920:F920"/>
     <mergeCell ref="B580:F580"/>
     <mergeCell ref="B711:F711"/>
     <mergeCell ref="B1009:F1009"/>
     <mergeCell ref="B2102:F2102"/>
+    <mergeCell ref="B2698:F2698"/>
     <mergeCell ref="B582:F582"/>
     <mergeCell ref="B2095:F2095"/>
+    <mergeCell ref="B2723:F2723"/>
     <mergeCell ref="B638:F638"/>
     <mergeCell ref="B936:F936"/>
     <mergeCell ref="B727:F727"/>
@@ -48724,6 +49489,7 @@
     <mergeCell ref="B1238:F1238"/>
     <mergeCell ref="B206:F206"/>
     <mergeCell ref="B2428:F2428"/>
+    <mergeCell ref="B2726:F2726"/>
     <mergeCell ref="B1694:F1694"/>
     <mergeCell ref="B2123:F2123"/>
     <mergeCell ref="B2457:F2457"/>
@@ -48946,6 +49712,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2654" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2669" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2684" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2699" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2714" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2729" r:id="rId182"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48957,7 +49726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J180"/>
+  <dimension ref="A1:J183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -49588,7 +50357,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Empowering SMEs through Renewable Energy Communities for a S</t>
+          <t>Assisting the Agrifood sector in the uptake of renewable ene</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr"/>
@@ -50747,19 +51516,15 @@
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>897315282</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Social Innovation Fund</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr"/>
       <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -50768,7 +51533,7 @@
       <c r="E55" s="6" t="inlineStr"/>
       <c r="F55" s="25" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr"/>
@@ -50783,15 +51548,19 @@
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neu</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -50815,12 +51584,12 @@
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficien</t>
+          <t>Circular design for bio-based innovation towards climate-neu</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr"/>
@@ -50847,12 +51616,12 @@
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should </t>
+          <t>Under topic LC-SC3-B4E-11-2020 Financing for energy efficien</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr"/>
@@ -50879,12 +51648,12 @@
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>d875bf4d-fe32-473e-a204-dcb7ff95d772-PIN</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Operation, maintenance, improvement and promotion of the BUI</t>
+          <t xml:space="preserve">Under call H2020-DT-2018-2020, topic DT-ICT-11-2019, should </t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr"/>
@@ -50911,12 +51680,12 @@
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
+          <t>d875bf4d-fe32-473e-a204-dcb7ff95d772-PIN</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
+          <t>Operation, maintenance, improvement and promotion of the BUI</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr"/>
@@ -51203,12 +51972,12 @@
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr"/>
@@ -51235,12 +52004,12 @@
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr"/>
@@ -51267,12 +52036,12 @@
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr"/>
@@ -51299,12 +52068,12 @@
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr"/>
@@ -53219,12 +53988,12 @@
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr"/>
@@ -53251,12 +54020,12 @@
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr"/>
@@ -53635,12 +54404,12 @@
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>928057492</t>
+          <t>928211140</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr"/>
@@ -53667,12 +54436,12 @@
     <row r="146" ht="28" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>926227393</t>
+          <t>928057492</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr"/>
@@ -53699,12 +54468,12 @@
     <row r="147" ht="28" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>928211140</t>
+          <t>926227393</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr"/>
@@ -53891,12 +54660,12 @@
     <row r="153" ht="28" customHeight="1">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>85779</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider ocea</t>
+          <t>Under HORIZON-EIC-2022-Social Innovation Prize (Challenge, I</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr"/>
@@ -53923,12 +54692,12 @@
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>85495</t>
+          <t>41082</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Should we focus on one type of environment, or consider ocea</t>
+          <t>Is a social impact fund based in Member States or listed EEA</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr"/>
@@ -53955,12 +54724,12 @@
     <row r="155" ht="28" customHeight="1">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
+          <t>85779</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Services to Communities to support the achievement of the ob</t>
+          <t>Should we focus on one type of environment, or consider ocea</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr"/>
@@ -53987,12 +54756,12 @@
     <row r="156" ht="28" customHeight="1">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>85495</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of rel</t>
+          <t>Should we focus on one type of environment, or consider ocea</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr"/>
@@ -54019,12 +54788,12 @@
     <row r="157" ht="28" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>100106</t>
+          <t>d22a6ed6-a62d-43a1-bd07-72ffb8a79aa9-PIN</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Should the Mission Forum be hosted during Ocean Days if in B</t>
+          <t>Services to Communities to support the achievement of the ob</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr"/>
@@ -54051,12 +54820,12 @@
     <row r="158" ht="28" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>HuMUS Soil Stewards training programme</t>
+          <t>In the EMFF-BEW-2020 call, in the non-exhaustive list of rel</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr"/>
@@ -54083,12 +54852,12 @@
     <row r="159" ht="28" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>913756976</t>
+          <t>100106</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
+          <t>Should the Mission Forum be hosted during Ocean Days if in B</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr"/>
@@ -54115,12 +54884,12 @@
     <row r="160" ht="28" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>880759128</t>
+          <t>104241</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE FORUA</t>
+          <t>HuMUS Soil Stewards training programme</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr"/>
@@ -54147,12 +54916,12 @@
     <row r="161" ht="28" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>76912</t>
+          <t>913756976</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The</t>
+          <t>FELSOBBFOKU TANULMANYOK INTEZETE</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr"/>
@@ -54179,12 +54948,12 @@
     <row r="162" ht="28" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>77665</t>
+          <t>880759128</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>The call requires to ‘Demonstrate the innovative solution(s)</t>
+          <t>AYUNTAMIENTO DE FORUA</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr"/>
@@ -54211,12 +54980,12 @@
     <row r="163" ht="28" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>886088211</t>
+          <t>76912</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>Non Architecture s.r.l.</t>
+          <t>How should we understand ‘peri-urban’ and ‘rural areas’? The</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr"/>
@@ -54243,12 +55012,12 @@
     <row r="164" ht="28" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>871698261</t>
+          <t>77665</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd</t>
+          <t>The call requires to ‘Demonstrate the innovative solution(s)</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr"/>
@@ -54275,12 +55044,12 @@
     <row r="165" ht="28" customHeight="1">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>918605133</t>
+          <t>886088211</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
+          <t>Non Architecture s.r.l.</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr"/>
@@ -54307,12 +55076,12 @@
     <row r="166" ht="28" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>871698261</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Can an International European Interest Organisation (IEIO) p</t>
+          <t>Kentsel Strateji ve Proje Gelistirme Danismanlik Ticaret Ltd</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr"/>
@@ -54339,12 +55108,12 @@
     <row r="167" ht="28" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>892931076</t>
+          <t>918605133</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>CONSEJO SUPERIOR DE COLEGIOS DE ARQUITECTOS DE ESPANA</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr"/>
@@ -54371,12 +55140,12 @@
     <row r="168" ht="28" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>936518123</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>Can an International European Interest Organisation (IEIO) p</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr"/>
@@ -54403,12 +55172,12 @@
     <row r="169" ht="28" customHeight="1">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>EU4H</t>
+          <t>892931076</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>European Linkage of Initiative from Science to Action in Hea</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr"/>
@@ -54435,12 +55204,12 @@
     <row r="170" ht="28" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>19519</t>
+          <t>936518123</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under HORIZON-EIC-2022-Social Innovation Prize (Challenge): </t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr"/>
@@ -54467,12 +55236,12 @@
     <row r="171" ht="28" customHeight="1">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>EU4H</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-ICT-2018-2020, topic ICT-03-2018-2019 it is</t>
+          <t>European Linkage of Initiative from Science to Action in Hea</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr"/>
@@ -54499,12 +55268,12 @@
     <row r="172" ht="28" customHeight="1">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Under the action "Marie Skłodowska-Curie Research and Innova</t>
+          <t xml:space="preserve">Under HORIZON-EIC-2022-Social Innovation Prize (Challenge): </t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr"/>
@@ -54531,12 +55300,12 @@
     <row r="173" ht="28" customHeight="1">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>22334</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2023-EUSIC-PRIZES-04: Regarding the European Soc</t>
+          <t>Under call H2020-ICT-2018-2020, topic ICT-03-2018-2019 it is</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr"/>
@@ -54563,28 +55332,24 @@
     <row r="174" ht="28" customHeight="1">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>EUS-23950</t>
+          <t>513</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocator</t>
-        </is>
-      </c>
-      <c r="C174" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
+          <t>Under the action "Marie Skłodowska-Curie Research and Innova</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr"/>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr"/>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr"/>
@@ -54599,28 +55364,24 @@
     <row r="175" ht="28" customHeight="1">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>EUS-04778</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfront</t>
-        </is>
-      </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
+          <t>HORIZON-EIC-2023-EUSIC-PRIZES-04: Regarding the European Soc</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr"/>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr"/>
       <c r="F175" s="25" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="G175" s="6" t="inlineStr"/>
@@ -54635,12 +55396,12 @@
     <row r="176" ht="28" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>EUS-19473</t>
+          <t>EUS-63611</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Suministro de más trípticos relativos a la zona de bajas emi</t>
+          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocator</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
@@ -54671,12 +55432,12 @@
     <row r="177" ht="28" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>EUS-16615</t>
+          <t>EUS-46816</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Euro</t>
+          <t>CEF ENERGIA. Mecanismo Conectar Europa. Proyectos transfront</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
@@ -54692,7 +55453,7 @@
       <c r="E177" s="6" t="inlineStr"/>
       <c r="F177" s="25" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="G177" s="6" t="inlineStr"/>
@@ -54707,12 +55468,12 @@
     <row r="178" ht="28" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>EUS-42934</t>
+          <t>EUS-59501</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>Reparación deficiencias eléctricas en Pabellón</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
@@ -54728,7 +55489,7 @@
       <c r="E178" s="6" t="inlineStr"/>
       <c r="F178" s="25" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr"/>
@@ -54743,12 +55504,12 @@
     <row r="179" ht="28" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>EUS-75226</t>
+          <t>EUS-73899</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>Mobiliario (incluido de oficina), complementos mobiliario, a</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Euro</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -54779,12 +55540,12 @@
     <row r="180" ht="28" customHeight="1">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>EUS-74374</t>
+          <t>EUS-72308</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Mobiliario (incluido de oficina), complementos mobiliario, a</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
@@ -54812,8 +55573,116 @@
       <c r="I180" s="6" t="inlineStr"/>
       <c r="J180" s="6" t="inlineStr"/>
     </row>
+    <row r="181" ht="28" customHeight="1">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>EUS-37473</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renovación licencias Teslab, infraestructura docente Joseba </t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr"/>
+      <c r="F181" s="25" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr"/>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>Por revisar</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="inlineStr"/>
+      <c r="J181" s="6" t="inlineStr"/>
+    </row>
+    <row r="182" ht="28" customHeight="1">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>EUS-31002</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>Mantenimiento preventivo de la cámara climática del Departam</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr"/>
+      <c r="F182" s="25" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr"/>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>Por revisar</t>
+        </is>
+      </c>
+      <c r="I182" s="6" t="inlineStr"/>
+      <c r="J182" s="6" t="inlineStr"/>
+    </row>
+    <row r="183" ht="28" customHeight="1">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>EUS-50049</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>Reparación de fuga de gas y sustitución de válvula de la cám</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="inlineStr"/>
+      <c r="F183" s="25" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr"/>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>Por revisar</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="inlineStr"/>
+      <c r="J183" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J180"/>
+  <autoFilter ref="A1:J183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/resultados_convocatorias.xlsx
+++ b/docs/resultados_convocatorias.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Recursos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$188</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M188"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -685,7 +685,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 04/10/2026 11:25 - 182 convocatorias - 8 nuevas</t>
+          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 05/10/2026 12:49 - 185 convocatorias - 11 nuevas</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr"/>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr"/>
@@ -3627,19 +3627,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr"/>
       <c r="E66" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -3660,7 +3656,7 @@
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr"/>
@@ -3678,15 +3674,19 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr"/>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr"/>
@@ -3725,12 +3725,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr"/>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr"/>
@@ -3772,12 +3772,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr"/>
@@ -3819,12 +3819,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr"/>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -3866,12 +3866,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr"/>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr"/>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr"/>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr"/>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr"/>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4007,12 +4007,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr"/>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr"/>
@@ -4101,12 +4101,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr"/>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr"/>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4195,12 +4195,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr"/>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr"/>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr"/>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4289,12 +4289,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr"/>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr"/>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr"/>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr"/>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr"/>
@@ -4430,12 +4430,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>49506</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Regarding the case study in Lot 2, you mention terms such as "biodiversity and nature co-benefits financial flows". Could you please provide clearer explanations on what is meant by financial flow and who you would define biodiversity and nature co-benefits.</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr"/>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>Regarding the case study in Lot 2, you mention terms such as "biodiversity and nature co-benefits financial flows". Could you please provide clearer explanations on what is meant by financial flow and</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Regarding the case study in Lot 2, you mention terms such as "biodiversity and nature co-benefits financial flows". Could you please provide clearer explanations on what is meant by financial flow and who you would define biodiversity and nature co-benefits.</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr"/>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Regarding the case study in Lot 2, you mention terms such as "biodiversity and nature co-benefits financial flows". Could you please provide clearer explanations on what is meant by financial flow and</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr"/>
@@ -4524,12 +4524,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr"/>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4571,12 +4571,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr"/>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr"/>
@@ -4618,12 +4618,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through th</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on </t>
+          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through th</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr"/>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t xml:space="preserve">Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on </t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -4759,12 +4759,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr"/>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr"/>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr"/>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr"/>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="L94" s="6" t="inlineStr"/>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr"/>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Respon</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr"/>
@@ -5088,12 +5088,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr"/>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Respon</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5135,12 +5135,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr"/>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr"/>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr"/>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered </t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr"/>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage propo</t>
+          <t xml:space="preserve">The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered </t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr"/>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr"/>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in th</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage propo</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5323,12 +5323,12 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>PPPA2027</t>
+          <t>31176</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr"/>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in th</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr"/>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
+          <t>PPPA2027</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Border regions Peer exchange on solving border obstacles</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr"/>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>Border regions Peer exchange on solving border obstacles</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
+          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Border regions Peer exchange on solving border obstacles</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr"/>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Border regions Peer exchange on solving border obstacles</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>886623263</t>
+          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr"/>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="L106" s="6" t="inlineStr"/>
@@ -5558,12 +5558,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>877314852</t>
+          <t>886623263</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr"/>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>900546740</t>
+          <t>877314852</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr"/>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="L108" s="6" t="inlineStr"/>
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>884174595</t>
+          <t>900546740</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr"/>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>941945952</t>
+          <t>884174595</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr"/>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="L110" s="6" t="inlineStr"/>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>941945952</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr"/>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -5793,12 +5793,12 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>ERDFTA</t>
+          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="L112" s="6" t="inlineStr"/>
@@ -5840,12 +5840,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>ERDFTA</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr"/>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -5887,12 +5887,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>90488</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr"/>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)</t>
         </is>
       </c>
       <c r="L114" s="6" t="inlineStr"/>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
+          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance </t>
+          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>njaunzdz</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Mr. Dzintars Jaunzems</t>
+          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>Mr. Dzintars Jaunzems</t>
+          <t xml:space="preserve">A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance </t>
         </is>
       </c>
       <c r="L116" s="6" t="inlineStr"/>
@@ -6028,12 +6028,12 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>n00brugy</t>
+          <t>njaunzdz</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Joana SANTIAGO</t>
+          <t>Mr. Dzintars Jaunzems</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr"/>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>Joana SANTIAGO</t>
+          <t>Mr. Dzintars Jaunzems</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>n00kmonh</t>
+          <t>n00brugy</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Mrs LARA MARIA CERDAN AZNAR</t>
+          <t>Joana SANTIAGO</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr"/>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>Mrs LARA MARIA CERDAN AZNAR</t>
+          <t>Joana SANTIAGO</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr"/>
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>937468917</t>
+          <t>n00kmonh</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>Mrs LARA MARIA CERDAN AZNAR</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr"/>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>Mrs LARA MARIA CERDAN AZNAR</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6169,12 +6169,12 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>937468917</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr"/>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a sing</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr"/>
@@ -6263,12 +6263,12 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr"/>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a sing</t>
         </is>
       </c>
       <c r="L122" s="6" t="inlineStr"/>
@@ -6310,12 +6310,12 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>885233544</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr"/>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6357,12 +6357,12 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>885233544</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr"/>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="L124" s="6" t="inlineStr"/>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr"/>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6451,12 +6451,12 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr"/>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we si</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="L126" s="6" t="inlineStr"/>
@@ -6498,12 +6498,12 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr"/>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technolog</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we si</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6545,12 +6545,12 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr"/>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technolog</t>
         </is>
       </c>
       <c r="L128" s="6" t="inlineStr"/>
@@ -6592,12 +6592,12 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr"/>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr"/>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="L130" s="6" t="inlineStr"/>
@@ -6686,12 +6686,12 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>956926438</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -6733,12 +6733,12 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>953677035</t>
+          <t>956926438</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr"/>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="L132" s="6" t="inlineStr"/>
@@ -6780,12 +6780,12 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>953552487</t>
+          <t>953677035</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr"/>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -6827,12 +6827,12 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>953552487</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr"/>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="L134" s="6" t="inlineStr"/>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>95140</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr"/>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? </t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -6921,12 +6921,12 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>95140</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t xml:space="preserve">1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? </t>
         </is>
       </c>
       <c r="L136" s="6" t="inlineStr"/>
@@ -7015,12 +7015,12 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>876983694</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr"/>
@@ -7062,12 +7062,12 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>876983694</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr"/>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infra</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>935134321</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr"/>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infra</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr"/>
@@ -7156,12 +7156,12 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>883154834</t>
+          <t>935134321</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr"/>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>883154834</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr"/>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="K142" s="6" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="L142" s="6" t="inlineStr"/>
@@ -7250,12 +7250,12 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>950910110</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>CURA TERRAE WATER LIMITED</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr"/>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>CURA TERRAE WATER LIMITED</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>954037778</t>
+          <t>950910110</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>VEOLIA EAU - COMPAGNIE GENERALE DES EAUX</t>
+          <t>CURA TERRAE WATER LIMITED</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr"/>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K144" s="6" t="inlineStr">
         <is>
-          <t>VEOLIA EAU - COMPAGNIE GENERALE DES EAUX</t>
+          <t>CURA TERRAE WATER LIMITED</t>
         </is>
       </c>
       <c r="L144" s="6" t="inlineStr"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>EUS-63611</t>
+          <t>EUS-43735</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>EUS-46816</t>
+          <t>EUS-23831</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>EUS-59501</t>
+          <t>EUS-89429</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>Reparación deficiencias eléctricas en Pabellón</t>
+          <t>Licitación, mediante procedimiento negociado sin publicidad, para la contratación de servicios de creación y edición de obra literaria y su divulgación para la Asociación BC3 Basque Centre for Climate</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>EUS-73899</t>
+          <t>EUS-69995</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>EUS-72308</t>
+          <t>EUS-59844</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>EUS-37473</t>
+          <t>EUS-33760</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>Renovación licencias Teslab, infraestructura docente Joseba Albizuri.</t>
+          <t>Aprobar la contratación de los trabajos de "Integración de levantamientos topográficos en la base topográfica urbana de Álava", como contrato menor de servicios.</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>EUS-31002</t>
+          <t>EUS-93831</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>Mantenimiento preventivo de la cámara climática del Departamento de Fisiología Vegetal de la UPV/EHU en Leioa, según presupuesto 26/PMJ150, incluyendo la revisión general del equipo, comprobación de p</t>
+          <t>Contratación del servicio de asistencia técnica y gestión de venta de los ahorros energéticos generados por la empresa de Transporte Urbano de Vitoria-Gasteiz (TUVISA)</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>EUS-50049</t>
+          <t>EUS-16126</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>Reparación de fuga de gas y sustitución de válvula de la cámara climática del Departamento de Fisiología Vegetal de la UPV/EHU en Leioa, según presupuesto 2026/244. La avería fue detectada en la revis</t>
+          <t>Obras del proyecto de construcción de itinerario peatonal paralelo a la calzada entre los PK 1,810 y 2,030 de la  GI-3131 a Goroeta en Aretxabaleta (14-SV-79/2025 2LIC)</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
@@ -9428,8 +9428,173 @@
         </is>
       </c>
     </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>EUS-08987</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>reparación y puesta en servicio de red de fecales y pluviales en el centro CEIP Cantarrana Eskola HLHI</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr"/>
+      <c r="G189" s="6" t="inlineStr"/>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I189" s="11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="J189" s="6" t="inlineStr"/>
+      <c r="K189" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L189" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M189" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>EUS-71383</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>Suministro e instalación de un portón industrial enrollable para el edificio AIC Ermua</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr"/>
+      <c r="G190" s="6" t="inlineStr"/>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I190" s="11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="J190" s="6" t="inlineStr"/>
+      <c r="K190" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L190" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M190" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>EUS-06475</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>ANS para determinadas aplicaciones implementadas por Izfe para el Departamento de Equilibrio Territorial Verde de la GFA-DFG para la gestión de la identificación, registro, saneamiento y movimiento an</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr"/>
+      <c r="G191" s="6" t="inlineStr"/>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I191" s="11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="J191" s="6" t="inlineStr"/>
+      <c r="K191" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L191" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M191" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:M188"/>
+  <autoFilter ref="A4:M191"/>
   <mergeCells count="4">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A180:M180"/>
@@ -9619,6 +9784,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9630,7 +9798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2729"/>
+  <dimension ref="A1:F2774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21780,7 +21948,7 @@
     <row r="886" ht="30" customHeight="1">
       <c r="A886" s="16" t="inlineStr">
         <is>
-          <t>FICHA 60: 50912</t>
+          <t>FICHA 60: 5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
         </is>
       </c>
       <c r="B886" s="17" t="n"/>
@@ -21805,7 +21973,7 @@
       <c r="E887" s="20" t="n"/>
       <c r="F887" s="20" t="n"/>
     </row>
-    <row r="888" ht="45" customHeight="1">
+    <row r="888" ht="20" customHeight="1">
       <c r="A888" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -21813,7 +21981,7 @@
       </c>
       <c r="B888" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
         </is>
       </c>
       <c r="C888" s="20" t="n"/>
@@ -21829,7 +21997,7 @@
       </c>
       <c r="B889" s="19" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
         </is>
       </c>
       <c r="C889" s="20" t="n"/>
@@ -21915,13 +22083,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B895" s="19" t="inlineStr"/>
+      <c r="B895" s="19" t="inlineStr">
+        <is>
+          <t>NEAR/IEV/2021/EA-RP/0041</t>
+        </is>
+      </c>
       <c r="C895" s="20" t="n"/>
       <c r="D895" s="20" t="n"/>
       <c r="E895" s="20" t="n"/>
       <c r="F895" s="20" t="n"/>
     </row>
-    <row r="896" ht="45" customHeight="1">
+    <row r="896" ht="20" customHeight="1">
       <c r="A896" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -21929,7 +22101,7 @@
       </c>
       <c r="B896" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
         </is>
       </c>
       <c r="C896" s="20" t="n"/>
@@ -21973,7 +22145,7 @@
       </c>
       <c r="B899" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/50912</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
         </is>
       </c>
       <c r="C899" s="20" t="n"/>
@@ -21984,7 +22156,7 @@
     <row r="901" ht="30" customHeight="1">
       <c r="A901" s="16" t="inlineStr">
         <is>
-          <t>FICHA 61: CEF2027</t>
+          <t>FICHA 61: 50912</t>
         </is>
       </c>
       <c r="B901" s="17" t="n"/>
@@ -22009,7 +22181,7 @@
       <c r="E902" s="20" t="n"/>
       <c r="F902" s="20" t="n"/>
     </row>
-    <row r="903" ht="20" customHeight="1">
+    <row r="903" ht="45" customHeight="1">
       <c r="A903" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -22017,7 +22189,7 @@
       </c>
       <c r="B903" s="19" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="C903" s="20" t="n"/>
@@ -22033,7 +22205,7 @@
       </c>
       <c r="B904" s="19" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="C904" s="20" t="n"/>
@@ -22047,11 +22219,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B905" s="19" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+      <c r="B905" s="19" t="inlineStr"/>
       <c r="C905" s="20" t="n"/>
       <c r="D905" s="20" t="n"/>
       <c r="E905" s="20" t="n"/>
@@ -22123,17 +22291,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B910" s="19" t="inlineStr">
-        <is>
-          <t>CEF-T-2024-AFIFGEN</t>
-        </is>
-      </c>
+      <c r="B910" s="19" t="inlineStr"/>
       <c r="C910" s="20" t="n"/>
       <c r="D910" s="20" t="n"/>
       <c r="E910" s="20" t="n"/>
       <c r="F910" s="20" t="n"/>
     </row>
-    <row r="911" ht="20" customHeight="1">
+    <row r="911" ht="45" customHeight="1">
       <c r="A911" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -22141,7 +22305,7 @@
       </c>
       <c r="B911" s="19" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="C911" s="20" t="n"/>
@@ -22185,7 +22349,7 @@
       </c>
       <c r="B914" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/50912</t>
         </is>
       </c>
       <c r="C914" s="20" t="n"/>
@@ -22196,7 +22360,7 @@
     <row r="916" ht="30" customHeight="1">
       <c r="A916" s="16" t="inlineStr">
         <is>
-          <t>FICHA 62: 19484</t>
+          <t>FICHA 62: CEF2027</t>
         </is>
       </c>
       <c r="B916" s="17" t="n"/>
@@ -22221,7 +22385,7 @@
       <c r="E917" s="20" t="n"/>
       <c r="F917" s="20" t="n"/>
     </row>
-    <row r="918" ht="45" customHeight="1">
+    <row r="918" ht="20" customHeight="1">
       <c r="A918" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -22229,7 +22393,7 @@
       </c>
       <c r="B918" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="C918" s="20" t="n"/>
@@ -22245,7 +22409,7 @@
       </c>
       <c r="B919" s="19" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="C919" s="20" t="n"/>
@@ -22259,7 +22423,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B920" s="19" t="inlineStr"/>
+      <c r="B920" s="19" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="C920" s="20" t="n"/>
       <c r="D920" s="20" t="n"/>
       <c r="E920" s="20" t="n"/>
@@ -22331,13 +22499,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B925" s="19" t="inlineStr"/>
+      <c r="B925" s="19" t="inlineStr">
+        <is>
+          <t>CEF-T-2024-AFIFGEN</t>
+        </is>
+      </c>
       <c r="C925" s="20" t="n"/>
       <c r="D925" s="20" t="n"/>
       <c r="E925" s="20" t="n"/>
       <c r="F925" s="20" t="n"/>
     </row>
-    <row r="926" ht="45" customHeight="1">
+    <row r="926" ht="20" customHeight="1">
       <c r="A926" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -22345,7 +22517,7 @@
       </c>
       <c r="B926" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="C926" s="20" t="n"/>
@@ -22389,7 +22561,7 @@
       </c>
       <c r="B929" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19484</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF2027</t>
         </is>
       </c>
       <c r="C929" s="20" t="n"/>
@@ -22400,7 +22572,7 @@
     <row r="931" ht="30" customHeight="1">
       <c r="A931" s="16" t="inlineStr">
         <is>
-          <t>FICHA 63: 915513452</t>
+          <t>FICHA 63: 19484</t>
         </is>
       </c>
       <c r="B931" s="17" t="n"/>
@@ -22425,7 +22597,7 @@
       <c r="E932" s="20" t="n"/>
       <c r="F932" s="20" t="n"/>
     </row>
-    <row r="933" ht="20" customHeight="1">
+    <row r="933" ht="45" customHeight="1">
       <c r="A933" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -22433,7 +22605,7 @@
       </c>
       <c r="B933" s="19" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
         </is>
       </c>
       <c r="C933" s="20" t="n"/>
@@ -22449,7 +22621,7 @@
       </c>
       <c r="B934" s="19" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="C934" s="20" t="n"/>
@@ -22541,7 +22713,7 @@
       <c r="E940" s="20" t="n"/>
       <c r="F940" s="20" t="n"/>
     </row>
-    <row r="941" ht="20" customHeight="1">
+    <row r="941" ht="45" customHeight="1">
       <c r="A941" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -22549,7 +22721,7 @@
       </c>
       <c r="B941" s="19" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
         </is>
       </c>
       <c r="C941" s="20" t="n"/>
@@ -22593,7 +22765,7 @@
       </c>
       <c r="B944" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/915513452</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19484</t>
         </is>
       </c>
       <c r="C944" s="20" t="n"/>
@@ -22604,7 +22776,7 @@
     <row r="946" ht="30" customHeight="1">
       <c r="A946" s="16" t="inlineStr">
         <is>
-          <t>FICHA 64: 40556</t>
+          <t>FICHA 64: 915513452</t>
         </is>
       </c>
       <c r="B946" s="17" t="n"/>
@@ -22629,7 +22801,7 @@
       <c r="E947" s="20" t="n"/>
       <c r="F947" s="20" t="n"/>
     </row>
-    <row r="948" ht="45" customHeight="1">
+    <row r="948" ht="20" customHeight="1">
       <c r="A948" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -22637,7 +22809,7 @@
       </c>
       <c r="B948" s="19" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C948" s="20" t="n"/>
@@ -22653,7 +22825,7 @@
       </c>
       <c r="B949" s="19" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="C949" s="20" t="n"/>
@@ -22745,7 +22917,7 @@
       <c r="E955" s="20" t="n"/>
       <c r="F955" s="20" t="n"/>
     </row>
-    <row r="956" ht="45" customHeight="1">
+    <row r="956" ht="20" customHeight="1">
       <c r="A956" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -22753,7 +22925,7 @@
       </c>
       <c r="B956" s="19" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C956" s="20" t="n"/>
@@ -22797,7 +22969,7 @@
       </c>
       <c r="B959" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/40556</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/915513452</t>
         </is>
       </c>
       <c r="C959" s="20" t="n"/>
@@ -22808,7 +22980,7 @@
     <row r="961" ht="30" customHeight="1">
       <c r="A961" s="16" t="inlineStr">
         <is>
-          <t>FICHA 65: 917721754</t>
+          <t>FICHA 65: 40556</t>
         </is>
       </c>
       <c r="B961" s="17" t="n"/>
@@ -22833,7 +23005,7 @@
       <c r="E962" s="20" t="n"/>
       <c r="F962" s="20" t="n"/>
     </row>
-    <row r="963" ht="20" customHeight="1">
+    <row r="963" ht="45" customHeight="1">
       <c r="A963" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -22841,7 +23013,7 @@
       </c>
       <c r="B963" s="19" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="C963" s="20" t="n"/>
@@ -22857,7 +23029,7 @@
       </c>
       <c r="B964" s="19" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="C964" s="20" t="n"/>
@@ -22949,7 +23121,7 @@
       <c r="E970" s="20" t="n"/>
       <c r="F970" s="20" t="n"/>
     </row>
-    <row r="971" ht="20" customHeight="1">
+    <row r="971" ht="45" customHeight="1">
       <c r="A971" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -22957,7 +23129,7 @@
       </c>
       <c r="B971" s="19" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="C971" s="20" t="n"/>
@@ -23001,7 +23173,7 @@
       </c>
       <c r="B974" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917721754</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/40556</t>
         </is>
       </c>
       <c r="C974" s="20" t="n"/>
@@ -23012,7 +23184,7 @@
     <row r="976" ht="30" customHeight="1">
       <c r="A976" s="16" t="inlineStr">
         <is>
-          <t>FICHA 66: 919892711</t>
+          <t>FICHA 66: 917721754</t>
         </is>
       </c>
       <c r="B976" s="17" t="n"/>
@@ -23045,7 +23217,7 @@
       </c>
       <c r="B978" s="19" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C978" s="20" t="n"/>
@@ -23061,7 +23233,7 @@
       </c>
       <c r="B979" s="19" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="C979" s="20" t="n"/>
@@ -23161,7 +23333,7 @@
       </c>
       <c r="B986" s="19" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C986" s="20" t="n"/>
@@ -23205,7 +23377,7 @@
       </c>
       <c r="B989" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919892711</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917721754</t>
         </is>
       </c>
       <c r="C989" s="20" t="n"/>
@@ -23216,7 +23388,7 @@
     <row r="991" ht="30" customHeight="1">
       <c r="A991" s="16" t="inlineStr">
         <is>
-          <t>FICHA 67: 939945909</t>
+          <t>FICHA 67: 919892711</t>
         </is>
       </c>
       <c r="B991" s="17" t="n"/>
@@ -23249,7 +23421,7 @@
       </c>
       <c r="B993" s="19" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="C993" s="20" t="n"/>
@@ -23265,7 +23437,7 @@
       </c>
       <c r="B994" s="19" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="C994" s="20" t="n"/>
@@ -23365,7 +23537,7 @@
       </c>
       <c r="B1001" s="19" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="C1001" s="20" t="n"/>
@@ -23409,7 +23581,7 @@
       </c>
       <c r="B1004" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939945909</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919892711</t>
         </is>
       </c>
       <c r="C1004" s="20" t="n"/>
@@ -23420,7 +23592,7 @@
     <row r="1006" ht="30" customHeight="1">
       <c r="A1006" s="16" t="inlineStr">
         <is>
-          <t>FICHA 68: 917779760</t>
+          <t>FICHA 68: 939945909</t>
         </is>
       </c>
       <c r="B1006" s="17" t="n"/>
@@ -23453,7 +23625,7 @@
       </c>
       <c r="B1008" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C1008" s="20" t="n"/>
@@ -23469,7 +23641,7 @@
       </c>
       <c r="B1009" s="19" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="C1009" s="20" t="n"/>
@@ -23569,7 +23741,7 @@
       </c>
       <c r="B1016" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C1016" s="20" t="n"/>
@@ -23613,7 +23785,7 @@
       </c>
       <c r="B1019" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939945909</t>
         </is>
       </c>
       <c r="C1019" s="20" t="n"/>
@@ -23624,7 +23796,7 @@
     <row r="1021" ht="30" customHeight="1">
       <c r="A1021" s="16" t="inlineStr">
         <is>
-          <t>FICHA 69: 920115617</t>
+          <t>FICHA 69: 928447529</t>
         </is>
       </c>
       <c r="B1021" s="17" t="n"/>
@@ -23657,7 +23829,7 @@
       </c>
       <c r="B1023" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1023" s="20" t="n"/>
@@ -23673,7 +23845,7 @@
       </c>
       <c r="B1024" s="19" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C1024" s="20" t="n"/>
@@ -23773,7 +23945,7 @@
       </c>
       <c r="B1031" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1031" s="20" t="n"/>
@@ -23817,7 +23989,7 @@
       </c>
       <c r="B1034" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
         </is>
       </c>
       <c r="C1034" s="20" t="n"/>
@@ -24032,7 +24204,7 @@
     <row r="1051" ht="30" customHeight="1">
       <c r="A1051" s="16" t="inlineStr">
         <is>
-          <t>FICHA 71: 928447529</t>
+          <t>FICHA 71: 917779760</t>
         </is>
       </c>
       <c r="B1051" s="17" t="n"/>
@@ -24065,7 +24237,7 @@
       </c>
       <c r="B1053" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1053" s="20" t="n"/>
@@ -24081,7 +24253,7 @@
       </c>
       <c r="B1054" s="19" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C1054" s="20" t="n"/>
@@ -24181,7 +24353,7 @@
       </c>
       <c r="B1061" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1061" s="20" t="n"/>
@@ -24225,7 +24397,7 @@
       </c>
       <c r="B1064" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
         </is>
       </c>
       <c r="C1064" s="20" t="n"/>
@@ -24236,7 +24408,7 @@
     <row r="1066" ht="30" customHeight="1">
       <c r="A1066" s="16" t="inlineStr">
         <is>
-          <t>FICHA 72: 14272</t>
+          <t>FICHA 72: 920115617</t>
         </is>
       </c>
       <c r="B1066" s="17" t="n"/>
@@ -24261,7 +24433,7 @@
       <c r="E1067" s="20" t="n"/>
       <c r="F1067" s="20" t="n"/>
     </row>
-    <row r="1068" ht="45" customHeight="1">
+    <row r="1068" ht="20" customHeight="1">
       <c r="A1068" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -24269,7 +24441,7 @@
       </c>
       <c r="B1068" s="19" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1068" s="20" t="n"/>
@@ -24285,7 +24457,7 @@
       </c>
       <c r="B1069" s="19" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C1069" s="20" t="n"/>
@@ -24377,7 +24549,7 @@
       <c r="E1075" s="20" t="n"/>
       <c r="F1075" s="20" t="n"/>
     </row>
-    <row r="1076" ht="45" customHeight="1">
+    <row r="1076" ht="20" customHeight="1">
       <c r="A1076" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -24385,7 +24557,7 @@
       </c>
       <c r="B1076" s="19" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1076" s="20" t="n"/>
@@ -24429,7 +24601,7 @@
       </c>
       <c r="B1079" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14272</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
         </is>
       </c>
       <c r="C1079" s="20" t="n"/>
@@ -24440,7 +24612,7 @@
     <row r="1081" ht="30" customHeight="1">
       <c r="A1081" s="16" t="inlineStr">
         <is>
-          <t>FICHA 73: 996889759</t>
+          <t>FICHA 73: 14272</t>
         </is>
       </c>
       <c r="B1081" s="17" t="n"/>
@@ -24465,7 +24637,7 @@
       <c r="E1082" s="20" t="n"/>
       <c r="F1082" s="20" t="n"/>
     </row>
-    <row r="1083" ht="20" customHeight="1">
+    <row r="1083" ht="45" customHeight="1">
       <c r="A1083" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -24473,7 +24645,7 @@
       </c>
       <c r="B1083" s="19" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="C1083" s="20" t="n"/>
@@ -24489,7 +24661,7 @@
       </c>
       <c r="B1084" s="19" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="C1084" s="20" t="n"/>
@@ -24581,7 +24753,7 @@
       <c r="E1090" s="20" t="n"/>
       <c r="F1090" s="20" t="n"/>
     </row>
-    <row r="1091" ht="20" customHeight="1">
+    <row r="1091" ht="45" customHeight="1">
       <c r="A1091" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -24589,7 +24761,7 @@
       </c>
       <c r="B1091" s="19" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="C1091" s="20" t="n"/>
@@ -24633,7 +24805,7 @@
       </c>
       <c r="B1094" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/996889759</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14272</t>
         </is>
       </c>
       <c r="C1094" s="20" t="n"/>
@@ -24644,7 +24816,7 @@
     <row r="1096" ht="30" customHeight="1">
       <c r="A1096" s="16" t="inlineStr">
         <is>
-          <t>FICHA 74: 922165518</t>
+          <t>FICHA 74: 996889759</t>
         </is>
       </c>
       <c r="B1096" s="17" t="n"/>
@@ -24677,7 +24849,7 @@
       </c>
       <c r="B1098" s="19" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C1098" s="20" t="n"/>
@@ -24693,7 +24865,7 @@
       </c>
       <c r="B1099" s="19" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="C1099" s="20" t="n"/>
@@ -24793,7 +24965,7 @@
       </c>
       <c r="B1106" s="19" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C1106" s="20" t="n"/>
@@ -24837,7 +25009,7 @@
       </c>
       <c r="B1109" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/922165518</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/996889759</t>
         </is>
       </c>
       <c r="C1109" s="20" t="n"/>
@@ -24848,7 +25020,7 @@
     <row r="1111" ht="30" customHeight="1">
       <c r="A1111" s="16" t="inlineStr">
         <is>
-          <t>FICHA 75: 919917446</t>
+          <t>FICHA 75: 922165518</t>
         </is>
       </c>
       <c r="B1111" s="17" t="n"/>
@@ -24881,7 +25053,7 @@
       </c>
       <c r="B1113" s="19" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C1113" s="20" t="n"/>
@@ -24897,7 +25069,7 @@
       </c>
       <c r="B1114" s="19" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="C1114" s="20" t="n"/>
@@ -24997,7 +25169,7 @@
       </c>
       <c r="B1121" s="19" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C1121" s="20" t="n"/>
@@ -25041,7 +25213,7 @@
       </c>
       <c r="B1124" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919917446</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/922165518</t>
         </is>
       </c>
       <c r="C1124" s="20" t="n"/>
@@ -25052,7 +25224,7 @@
     <row r="1126" ht="30" customHeight="1">
       <c r="A1126" s="16" t="inlineStr">
         <is>
-          <t>FICHA 76: 917155468</t>
+          <t>FICHA 76: 919917446</t>
         </is>
       </c>
       <c r="B1126" s="17" t="n"/>
@@ -25085,7 +25257,7 @@
       </c>
       <c r="B1128" s="19" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C1128" s="20" t="n"/>
@@ -25101,7 +25273,7 @@
       </c>
       <c r="B1129" s="19" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="C1129" s="20" t="n"/>
@@ -25201,7 +25373,7 @@
       </c>
       <c r="B1136" s="19" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C1136" s="20" t="n"/>
@@ -25245,7 +25417,7 @@
       </c>
       <c r="B1139" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917155468</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919917446</t>
         </is>
       </c>
       <c r="C1139" s="20" t="n"/>
@@ -25256,7 +25428,7 @@
     <row r="1141" ht="30" customHeight="1">
       <c r="A1141" s="16" t="inlineStr">
         <is>
-          <t>FICHA 77: 95942</t>
+          <t>FICHA 77: 917155468</t>
         </is>
       </c>
       <c r="B1141" s="17" t="n"/>
@@ -25281,7 +25453,7 @@
       <c r="E1142" s="20" t="n"/>
       <c r="F1142" s="20" t="n"/>
     </row>
-    <row r="1143" ht="45" customHeight="1">
+    <row r="1143" ht="20" customHeight="1">
       <c r="A1143" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -25289,7 +25461,7 @@
       </c>
       <c r="B1143" s="19" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C1143" s="20" t="n"/>
@@ -25305,7 +25477,7 @@
       </c>
       <c r="B1144" s="19" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="C1144" s="20" t="n"/>
@@ -25397,7 +25569,7 @@
       <c r="E1150" s="20" t="n"/>
       <c r="F1150" s="20" t="n"/>
     </row>
-    <row r="1151" ht="45" customHeight="1">
+    <row r="1151" ht="20" customHeight="1">
       <c r="A1151" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -25405,7 +25577,7 @@
       </c>
       <c r="B1151" s="19" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C1151" s="20" t="n"/>
@@ -25449,7 +25621,7 @@
       </c>
       <c r="B1154" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95942</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917155468</t>
         </is>
       </c>
       <c r="C1154" s="20" t="n"/>
@@ -25460,7 +25632,7 @@
     <row r="1156" ht="30" customHeight="1">
       <c r="A1156" s="16" t="inlineStr">
         <is>
-          <t>FICHA 78: 49506</t>
+          <t>FICHA 78: 95942</t>
         </is>
       </c>
       <c r="B1156" s="17" t="n"/>
@@ -25493,7 +25665,7 @@
       </c>
       <c r="B1158" s="19" t="inlineStr">
         <is>
-          <t>Regarding the case study in Lot 2, you mention terms such as "biodiversity and nature co-benefits financial flows". Could you please provide clearer explanations on what is meant by financial flow and who you would define biodiversity and nature co-benefits.</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="C1158" s="20" t="n"/>
@@ -25509,7 +25681,7 @@
       </c>
       <c r="B1159" s="19" t="inlineStr">
         <is>
-          <t>49506</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="C1159" s="20" t="n"/>
@@ -25609,7 +25781,7 @@
       </c>
       <c r="B1166" s="19" t="inlineStr">
         <is>
-          <t>Regarding the case study in Lot 2, you mention terms such as "biodiversity and nature co-benefits financial flows". Could you please provide clearer explanations on what is meant by financial flow and who you would define biodiversity and nature co-benefits.</t>
+          <t>Considering the increasing importance of ecosystem restoration and soil health for biodiversity conservation, do you expect the future Topic Centre on Biodiversity and Nature to further strengthen the integration of Soil Mission knowledge, soil-related indicators, and digital geospatial services within biodiversity monitoring, reporting and Nature</t>
         </is>
       </c>
       <c r="C1166" s="20" t="n"/>
@@ -25653,7 +25825,7 @@
       </c>
       <c r="B1169" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/49506</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95942</t>
         </is>
       </c>
       <c r="C1169" s="20" t="n"/>
@@ -25664,7 +25836,7 @@
     <row r="1171" ht="30" customHeight="1">
       <c r="A1171" s="16" t="inlineStr">
         <is>
-          <t>FICHA 79: 898575215</t>
+          <t>FICHA 79: 49506</t>
         </is>
       </c>
       <c r="B1171" s="17" t="n"/>
@@ -25689,7 +25861,7 @@
       <c r="E1172" s="20" t="n"/>
       <c r="F1172" s="20" t="n"/>
     </row>
-    <row r="1173" ht="20" customHeight="1">
+    <row r="1173" ht="45" customHeight="1">
       <c r="A1173" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -25697,7 +25869,7 @@
       </c>
       <c r="B1173" s="19" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Regarding the case study in Lot 2, you mention terms such as "biodiversity and nature co-benefits financial flows". Could you please provide clearer explanations on what is meant by financial flow and who you would define biodiversity and nature co-benefits.</t>
         </is>
       </c>
       <c r="C1173" s="20" t="n"/>
@@ -25713,7 +25885,7 @@
       </c>
       <c r="B1174" s="19" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="C1174" s="20" t="n"/>
@@ -25805,7 +25977,7 @@
       <c r="E1180" s="20" t="n"/>
       <c r="F1180" s="20" t="n"/>
     </row>
-    <row r="1181" ht="20" customHeight="1">
+    <row r="1181" ht="45" customHeight="1">
       <c r="A1181" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -25813,7 +25985,7 @@
       </c>
       <c r="B1181" s="19" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Regarding the case study in Lot 2, you mention terms such as "biodiversity and nature co-benefits financial flows". Could you please provide clearer explanations on what is meant by financial flow and who you would define biodiversity and nature co-benefits.</t>
         </is>
       </c>
       <c r="C1181" s="20" t="n"/>
@@ -25857,7 +26029,7 @@
       </c>
       <c r="B1184" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/898575215</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/49506</t>
         </is>
       </c>
       <c r="C1184" s="20" t="n"/>
@@ -25868,7 +26040,7 @@
     <row r="1186" ht="30" customHeight="1">
       <c r="A1186" s="16" t="inlineStr">
         <is>
-          <t>FICHA 80: 97556</t>
+          <t>FICHA 80: 898575215</t>
         </is>
       </c>
       <c r="B1186" s="17" t="n"/>
@@ -25893,7 +26065,7 @@
       <c r="E1187" s="20" t="n"/>
       <c r="F1187" s="20" t="n"/>
     </row>
-    <row r="1188" ht="45" customHeight="1">
+    <row r="1188" ht="20" customHeight="1">
       <c r="A1188" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -25901,7 +26073,7 @@
       </c>
       <c r="B1188" s="19" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C1188" s="20" t="n"/>
@@ -25917,7 +26089,7 @@
       </c>
       <c r="B1189" s="19" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="C1189" s="20" t="n"/>
@@ -26009,7 +26181,7 @@
       <c r="E1195" s="20" t="n"/>
       <c r="F1195" s="20" t="n"/>
     </row>
-    <row r="1196" ht="45" customHeight="1">
+    <row r="1196" ht="20" customHeight="1">
       <c r="A1196" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -26017,7 +26189,7 @@
       </c>
       <c r="B1196" s="19" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C1196" s="20" t="n"/>
@@ -26061,7 +26233,7 @@
       </c>
       <c r="B1199" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/97556</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/898575215</t>
         </is>
       </c>
       <c r="C1199" s="20" t="n"/>
@@ -26072,7 +26244,7 @@
     <row r="1201" ht="30" customHeight="1">
       <c r="A1201" s="16" t="inlineStr">
         <is>
-          <t>FICHA 81: 73618</t>
+          <t>FICHA 81: 97556</t>
         </is>
       </c>
       <c r="B1201" s="17" t="n"/>
@@ -26105,7 +26277,7 @@
       </c>
       <c r="B1203" s="19" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="C1203" s="20" t="n"/>
@@ -26121,7 +26293,7 @@
       </c>
       <c r="B1204" s="19" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="C1204" s="20" t="n"/>
@@ -26221,7 +26393,7 @@
       </c>
       <c r="B1211" s="19" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaamheid, energy neutrality, circularity) The procurement documents refer to “Net Zero” in relation to the required reference project. Could the Contracting Authority clarify how the term “Net Zero” should be interpreted for the purpose of assessing compliance with this requirement? In partic</t>
         </is>
       </c>
       <c r="C1211" s="20" t="n"/>
@@ -26265,7 +26437,7 @@
       </c>
       <c r="B1214" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/73618</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/97556</t>
         </is>
       </c>
       <c r="C1214" s="20" t="n"/>
@@ -26276,7 +26448,7 @@
     <row r="1216" ht="30" customHeight="1">
       <c r="A1216" s="16" t="inlineStr">
         <is>
-          <t>FICHA 82: 83951</t>
+          <t>FICHA 82: 73618</t>
         </is>
       </c>
       <c r="B1216" s="17" t="n"/>
@@ -26301,7 +26473,7 @@
       <c r="E1217" s="20" t="n"/>
       <c r="F1217" s="20" t="n"/>
     </row>
-    <row r="1218" ht="20" customHeight="1">
+    <row r="1218" ht="45" customHeight="1">
       <c r="A1218" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -26309,7 +26481,7 @@
       </c>
       <c r="B1218" s="19" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="C1218" s="20" t="n"/>
@@ -26325,7 +26497,7 @@
       </c>
       <c r="B1219" s="19" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="C1219" s="20" t="n"/>
@@ -26425,7 +26597,7 @@
       </c>
       <c r="B1226" s="19" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through the literature reviews, questionnaires, surveys and expert opinions in order to provide key recommendations on how EIT Food can make a distinctive a</t>
+          <t>Should the selected port related to the Cities Mission be one of the Mission Label cities, or if it is sufficient for it to be among the broader list of 112 Mission Cities?</t>
         </is>
       </c>
       <c r="C1226" s="20" t="n"/>
@@ -26469,7 +26641,7 @@
       </c>
       <c r="B1229" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/83951</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/73618</t>
         </is>
       </c>
       <c r="C1229" s="20" t="n"/>
@@ -26480,7 +26652,7 @@
     <row r="1231" ht="30" customHeight="1">
       <c r="A1231" s="16" t="inlineStr">
         <is>
-          <t>FICHA 83: 54353</t>
+          <t>FICHA 83: 83951</t>
         </is>
       </c>
       <c r="B1231" s="17" t="n"/>
@@ -26505,7 +26677,7 @@
       <c r="E1232" s="20" t="n"/>
       <c r="F1232" s="20" t="n"/>
     </row>
-    <row r="1233" ht="45" customHeight="1">
+    <row r="1233" ht="20" customHeight="1">
       <c r="A1233" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -26513,7 +26685,7 @@
       </c>
       <c r="B1233" s="19" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="C1233" s="20" t="n"/>
@@ -26529,7 +26701,7 @@
       </c>
       <c r="B1234" s="19" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="C1234" s="20" t="n"/>
@@ -26629,7 +26801,7 @@
       </c>
       <c r="B1241" s="19" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
+          <t>A Net Zero Food System - Insight Report The aim of the EIT Food Mission roadmapping exercise to A Net Zero Food System was to critically analyse and synthesise all the information collected through the literature reviews, questionnaires, surveys and expert opinions in order to provide key recommendations on how EIT Food can make a distinctive a</t>
         </is>
       </c>
       <c r="C1241" s="20" t="n"/>
@@ -26673,7 +26845,7 @@
       </c>
       <c r="B1244" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/54353</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/83951</t>
         </is>
       </c>
       <c r="C1244" s="20" t="n"/>
@@ -26684,7 +26856,7 @@
     <row r="1246" ht="30" customHeight="1">
       <c r="A1246" s="16" t="inlineStr">
         <is>
-          <t>FICHA 84: 880954583</t>
+          <t>FICHA 84: 54353</t>
         </is>
       </c>
       <c r="B1246" s="17" t="n"/>
@@ -26709,7 +26881,7 @@
       <c r="E1247" s="20" t="n"/>
       <c r="F1247" s="20" t="n"/>
     </row>
-    <row r="1248" ht="20" customHeight="1">
+    <row r="1248" ht="45" customHeight="1">
       <c r="A1248" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -26717,7 +26889,7 @@
       </c>
       <c r="B1248" s="19" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="C1248" s="20" t="n"/>
@@ -26733,7 +26905,7 @@
       </c>
       <c r="B1249" s="19" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="C1249" s="20" t="n"/>
@@ -26825,7 +26997,7 @@
       <c r="E1255" s="20" t="n"/>
       <c r="F1255" s="20" t="n"/>
     </row>
-    <row r="1256" ht="20" customHeight="1">
+    <row r="1256" ht="45" customHeight="1">
       <c r="A1256" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -26833,7 +27005,7 @@
       </c>
       <c r="B1256" s="19" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submitted under Strand 1 focus on net-zero technologies and critical raw technologies, or one of the two? If we choose net-zero technologies, on how many of them should we focus (one or more)?</t>
         </is>
       </c>
       <c r="C1256" s="20" t="n"/>
@@ -26877,7 +27049,7 @@
       </c>
       <c r="B1259" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880954583</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/54353</t>
         </is>
       </c>
       <c r="C1259" s="20" t="n"/>
@@ -26888,7 +27060,7 @@
     <row r="1261" ht="30" customHeight="1">
       <c r="A1261" s="16" t="inlineStr">
         <is>
-          <t>FICHA 85: c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>FICHA 85: 880954583</t>
         </is>
       </c>
       <c r="B1261" s="17" t="n"/>
@@ -26913,7 +27085,7 @@
       <c r="E1262" s="20" t="n"/>
       <c r="F1262" s="20" t="n"/>
     </row>
-    <row r="1263" ht="45" customHeight="1">
+    <row r="1263" ht="20" customHeight="1">
       <c r="A1263" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -26921,7 +27093,7 @@
       </c>
       <c r="B1263" s="19" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C1263" s="20" t="n"/>
@@ -26937,7 +27109,7 @@
       </c>
       <c r="B1264" s="19" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="C1264" s="20" t="n"/>
@@ -27023,17 +27195,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1270" s="19" t="inlineStr">
-        <is>
-          <t>CINEA/2026/OP/0011-PIN</t>
-        </is>
-      </c>
+      <c r="B1270" s="19" t="inlineStr"/>
       <c r="C1270" s="20" t="n"/>
       <c r="D1270" s="20" t="n"/>
       <c r="E1270" s="20" t="n"/>
       <c r="F1270" s="20" t="n"/>
     </row>
-    <row r="1271" ht="45" customHeight="1">
+    <row r="1271" ht="20" customHeight="1">
       <c r="A1271" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -27041,7 +27209,7 @@
       </c>
       <c r="B1271" s="19" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C1271" s="20" t="n"/>
@@ -27085,7 +27253,7 @@
       </c>
       <c r="B1274" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/880954583</t>
         </is>
       </c>
       <c r="C1274" s="20" t="n"/>
@@ -27096,7 +27264,7 @@
     <row r="1276" ht="30" customHeight="1">
       <c r="A1276" s="16" t="inlineStr">
         <is>
-          <t>FICHA 86: 30901</t>
+          <t>FICHA 86: c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="B1276" s="17" t="n"/>
@@ -27129,7 +27297,7 @@
       </c>
       <c r="B1278" s="19" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="C1278" s="20" t="n"/>
@@ -27145,7 +27313,7 @@
       </c>
       <c r="B1279" s="19" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C1279" s="20" t="n"/>
@@ -27231,7 +27399,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1285" s="19" t="inlineStr"/>
+      <c r="B1285" s="19" t="inlineStr">
+        <is>
+          <t>CINEA/2026/OP/0011-PIN</t>
+        </is>
+      </c>
       <c r="C1285" s="20" t="n"/>
       <c r="D1285" s="20" t="n"/>
       <c r="E1285" s="20" t="n"/>
@@ -27245,7 +27417,7 @@
       </c>
       <c r="B1286" s="19" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
+          <t>Inter-institutional single framework contract to support the monitoring of LIFE projects (action and operating grants), communication about the LIFE programme and other related activities</t>
         </is>
       </c>
       <c r="C1286" s="20" t="n"/>
@@ -27289,7 +27461,7 @@
       </c>
       <c r="B1289" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/30901</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="C1289" s="20" t="n"/>
@@ -27300,7 +27472,7 @@
     <row r="1291" ht="30" customHeight="1">
       <c r="A1291" s="16" t="inlineStr">
         <is>
-          <t>FICHA 87: 893516374</t>
+          <t>FICHA 87: 30901</t>
         </is>
       </c>
       <c r="B1291" s="17" t="n"/>
@@ -27325,7 +27497,7 @@
       <c r="E1292" s="20" t="n"/>
       <c r="F1292" s="20" t="n"/>
     </row>
-    <row r="1293" ht="20" customHeight="1">
+    <row r="1293" ht="45" customHeight="1">
       <c r="A1293" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -27333,7 +27505,7 @@
       </c>
       <c r="B1293" s="19" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="C1293" s="20" t="n"/>
@@ -27349,7 +27521,7 @@
       </c>
       <c r="B1294" s="19" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="C1294" s="20" t="n"/>
@@ -27441,7 +27613,7 @@
       <c r="E1300" s="20" t="n"/>
       <c r="F1300" s="20" t="n"/>
     </row>
-    <row r="1301" ht="20" customHeight="1">
+    <row r="1301" ht="45" customHeight="1">
       <c r="A1301" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -27449,7 +27621,7 @@
       </c>
       <c r="B1301" s="19" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do local and regional authorities need to be beneficiaries of the consortium?</t>
         </is>
       </c>
       <c r="C1301" s="20" t="n"/>
@@ -27493,7 +27665,7 @@
       </c>
       <c r="B1304" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/893516374</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/30901</t>
         </is>
       </c>
       <c r="C1304" s="20" t="n"/>
@@ -27504,7 +27676,7 @@
     <row r="1306" ht="30" customHeight="1">
       <c r="A1306" s="16" t="inlineStr">
         <is>
-          <t>FICHA 88: 894079362</t>
+          <t>FICHA 88: 893516374</t>
         </is>
       </c>
       <c r="B1306" s="17" t="n"/>
@@ -27537,7 +27709,7 @@
       </c>
       <c r="B1308" s="19" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C1308" s="20" t="n"/>
@@ -27553,7 +27725,7 @@
       </c>
       <c r="B1309" s="19" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="C1309" s="20" t="n"/>
@@ -27653,7 +27825,7 @@
       </c>
       <c r="B1316" s="19" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C1316" s="20" t="n"/>
@@ -27697,7 +27869,7 @@
       </c>
       <c r="B1319" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/894079362</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/893516374</t>
         </is>
       </c>
       <c r="C1319" s="20" t="n"/>
@@ -27708,7 +27880,7 @@
     <row r="1321" ht="30" customHeight="1">
       <c r="A1321" s="16" t="inlineStr">
         <is>
-          <t>FICHA 89: 867619605</t>
+          <t>FICHA 89: 894079362</t>
         </is>
       </c>
       <c r="B1321" s="17" t="n"/>
@@ -27741,7 +27913,7 @@
       </c>
       <c r="B1323" s="19" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C1323" s="20" t="n"/>
@@ -27757,7 +27929,7 @@
       </c>
       <c r="B1324" s="19" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="C1324" s="20" t="n"/>
@@ -27857,7 +28029,7 @@
       </c>
       <c r="B1331" s="19" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C1331" s="20" t="n"/>
@@ -27901,7 +28073,7 @@
       </c>
       <c r="B1334" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/867619605</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/894079362</t>
         </is>
       </c>
       <c r="C1334" s="20" t="n"/>
@@ -27912,7 +28084,7 @@
     <row r="1336" ht="30" customHeight="1">
       <c r="A1336" s="16" t="inlineStr">
         <is>
-          <t>FICHA 90: ncaviale</t>
+          <t>FICHA 90: 867619605</t>
         </is>
       </c>
       <c r="B1336" s="17" t="n"/>
@@ -27945,7 +28117,7 @@
       </c>
       <c r="B1338" s="19" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C1338" s="20" t="n"/>
@@ -27961,7 +28133,7 @@
       </c>
       <c r="B1339" s="19" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="C1339" s="20" t="n"/>
@@ -28061,7 +28233,7 @@
       </c>
       <c r="B1346" s="19" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C1346" s="20" t="n"/>
@@ -28105,7 +28277,7 @@
       </c>
       <c r="B1349" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ncaviale</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/867619605</t>
         </is>
       </c>
       <c r="C1349" s="20" t="n"/>
@@ -28116,7 +28288,7 @@
     <row r="1351" ht="30" customHeight="1">
       <c r="A1351" s="16" t="inlineStr">
         <is>
-          <t>FICHA 91: 34537</t>
+          <t>FICHA 91: ncaviale</t>
         </is>
       </c>
       <c r="B1351" s="17" t="n"/>
@@ -28141,7 +28313,7 @@
       <c r="E1352" s="20" t="n"/>
       <c r="F1352" s="20" t="n"/>
     </row>
-    <row r="1353" ht="45" customHeight="1">
+    <row r="1353" ht="20" customHeight="1">
       <c r="A1353" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -28149,7 +28321,7 @@
       </c>
       <c r="B1353" s="19" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C1353" s="20" t="n"/>
@@ -28165,7 +28337,7 @@
       </c>
       <c r="B1354" s="19" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="C1354" s="20" t="n"/>
@@ -28257,7 +28429,7 @@
       <c r="E1360" s="20" t="n"/>
       <c r="F1360" s="20" t="n"/>
     </row>
-    <row r="1361" ht="45" customHeight="1">
+    <row r="1361" ht="20" customHeight="1">
       <c r="A1361" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -28265,7 +28437,7 @@
       </c>
       <c r="B1361" s="19" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C1361" s="20" t="n"/>
@@ -28309,7 +28481,7 @@
       </c>
       <c r="B1364" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/34537</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ncaviale</t>
         </is>
       </c>
       <c r="C1364" s="20" t="n"/>
@@ -28320,7 +28492,7 @@
     <row r="1366" ht="30" customHeight="1">
       <c r="A1366" s="16" t="inlineStr">
         <is>
-          <t>FICHA 92: 906456368</t>
+          <t>FICHA 92: 34537</t>
         </is>
       </c>
       <c r="B1366" s="17" t="n"/>
@@ -28345,7 +28517,7 @@
       <c r="E1367" s="20" t="n"/>
       <c r="F1367" s="20" t="n"/>
     </row>
-    <row r="1368" ht="20" customHeight="1">
+    <row r="1368" ht="45" customHeight="1">
       <c r="A1368" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -28353,7 +28525,7 @@
       </c>
       <c r="B1368" s="19" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="C1368" s="20" t="n"/>
@@ -28369,7 +28541,7 @@
       </c>
       <c r="B1369" s="19" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="C1369" s="20" t="n"/>
@@ -28461,7 +28633,7 @@
       <c r="E1375" s="20" t="n"/>
       <c r="F1375" s="20" t="n"/>
     </row>
-    <row r="1376" ht="20" customHeight="1">
+    <row r="1376" ht="45" customHeight="1">
       <c r="A1376" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -28469,7 +28641,7 @@
       </c>
       <c r="B1376" s="19" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by Frontex of a single deliverable (timesheet, report on tasks, SLA provisions) should trigger an analysis and response with eventually a Response Plan action", there is a concomitant use of Response plan and Action plan in the same context. Do we understand it correctly that the referred-to</t>
         </is>
       </c>
       <c r="C1376" s="20" t="n"/>
@@ -28513,7 +28685,7 @@
       </c>
       <c r="B1379" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/906456368</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/34537</t>
         </is>
       </c>
       <c r="C1379" s="20" t="n"/>
@@ -28524,7 +28696,7 @@
     <row r="1381" ht="30" customHeight="1">
       <c r="A1381" s="16" t="inlineStr">
         <is>
-          <t>FICHA 93: 939595836</t>
+          <t>FICHA 93: 906456368</t>
         </is>
       </c>
       <c r="B1381" s="17" t="n"/>
@@ -28557,7 +28729,7 @@
       </c>
       <c r="B1383" s="19" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C1383" s="20" t="n"/>
@@ -28573,7 +28745,7 @@
       </c>
       <c r="B1384" s="19" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="C1384" s="20" t="n"/>
@@ -28673,7 +28845,7 @@
       </c>
       <c r="B1391" s="19" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C1391" s="20" t="n"/>
@@ -28717,7 +28889,7 @@
       </c>
       <c r="B1394" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939595836</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/906456368</t>
         </is>
       </c>
       <c r="C1394" s="20" t="n"/>
@@ -28728,7 +28900,7 @@
     <row r="1396" ht="30" customHeight="1">
       <c r="A1396" s="16" t="inlineStr">
         <is>
-          <t>FICHA 94: 46407</t>
+          <t>FICHA 94: 939595836</t>
         </is>
       </c>
       <c r="B1396" s="17" t="n"/>
@@ -28753,7 +28925,7 @@
       <c r="E1397" s="20" t="n"/>
       <c r="F1397" s="20" t="n"/>
     </row>
-    <row r="1398" ht="45" customHeight="1">
+    <row r="1398" ht="20" customHeight="1">
       <c r="A1398" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -28761,7 +28933,7 @@
       </c>
       <c r="B1398" s="19" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C1398" s="20" t="n"/>
@@ -28777,7 +28949,7 @@
       </c>
       <c r="B1399" s="19" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="C1399" s="20" t="n"/>
@@ -28869,7 +29041,7 @@
       <c r="E1405" s="20" t="n"/>
       <c r="F1405" s="20" t="n"/>
     </row>
-    <row r="1406" ht="45" customHeight="1">
+    <row r="1406" ht="20" customHeight="1">
       <c r="A1406" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -28877,7 +29049,7 @@
       </c>
       <c r="B1406" s="19" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C1406" s="20" t="n"/>
@@ -28921,7 +29093,7 @@
       </c>
       <c r="B1409" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/46407</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939595836</t>
         </is>
       </c>
       <c r="C1409" s="20" t="n"/>
@@ -28932,7 +29104,7 @@
     <row r="1411" ht="30" customHeight="1">
       <c r="A1411" s="16" t="inlineStr">
         <is>
-          <t>FICHA 95: 71899</t>
+          <t>FICHA 95: 46407</t>
         </is>
       </c>
       <c r="B1411" s="17" t="n"/>
@@ -28965,7 +29137,7 @@
       </c>
       <c r="B1413" s="19" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="C1413" s="20" t="n"/>
@@ -28981,7 +29153,7 @@
       </c>
       <c r="B1414" s="19" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="C1414" s="20" t="n"/>
@@ -29081,7 +29253,7 @@
       </c>
       <c r="B1421" s="19" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14 crisis specific Action Plans. What are the 14 crisis scenarios that should be covered by those documents? How many of these 14 are covered by existing CM Action plans?</t>
         </is>
       </c>
       <c r="C1421" s="20" t="n"/>
@@ -29125,7 +29297,7 @@
       </c>
       <c r="B1424" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71899</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/46407</t>
         </is>
       </c>
       <c r="C1424" s="20" t="n"/>
@@ -29136,7 +29308,7 @@
     <row r="1426" ht="30" customHeight="1">
       <c r="A1426" s="16" t="inlineStr">
         <is>
-          <t>FICHA 96: 31176</t>
+          <t>FICHA 96: 71899</t>
         </is>
       </c>
       <c r="B1426" s="17" t="n"/>
@@ -29169,7 +29341,7 @@
       </c>
       <c r="B1428" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="C1428" s="20" t="n"/>
@@ -29185,7 +29357,7 @@
       </c>
       <c r="B1429" s="19" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="C1429" s="20" t="n"/>
@@ -29285,7 +29457,7 @@
       </c>
       <c r="B1436" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
+          <t>The topic requires to "include a draft plan for joint actions, to be then adapted and agreed between all funded projects." Can this "plan for joint actions" be omitted at the 10-page first stage proposal?</t>
         </is>
       </c>
       <c r="C1436" s="20" t="n"/>
@@ -29329,7 +29501,7 @@
       </c>
       <c r="B1439" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31176</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71899</t>
         </is>
       </c>
       <c r="C1439" s="20" t="n"/>
@@ -29340,7 +29512,7 @@
     <row r="1441" ht="30" customHeight="1">
       <c r="A1441" s="16" t="inlineStr">
         <is>
-          <t>FICHA 97: PPPA2027</t>
+          <t>FICHA 97: 31176</t>
         </is>
       </c>
       <c r="B1441" s="17" t="n"/>
@@ -29373,7 +29545,7 @@
       </c>
       <c r="B1443" s="19" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
         </is>
       </c>
       <c r="C1443" s="20" t="n"/>
@@ -29389,7 +29561,7 @@
       </c>
       <c r="B1444" s="19" t="inlineStr">
         <is>
-          <t>PPPA2027</t>
+          <t>31176</t>
         </is>
       </c>
       <c r="C1444" s="20" t="n"/>
@@ -29475,11 +29647,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1450" s="19" t="inlineStr">
-        <is>
-          <t>PPPA-2025-IGF-IBA</t>
-        </is>
-      </c>
+      <c r="B1450" s="19" t="inlineStr"/>
       <c r="C1450" s="20" t="n"/>
       <c r="D1450" s="20" t="n"/>
       <c r="E1450" s="20" t="n"/>
@@ -29493,7 +29661,7 @@
       </c>
       <c r="B1451" s="19" t="inlineStr">
         <is>
-          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
+          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total budget the same as the proposal budget and, in case the two budgets are different, what elements are in the proposal budget which are not in the action plan budget?</t>
         </is>
       </c>
       <c r="C1451" s="20" t="n"/>
@@ -29537,7 +29705,7 @@
       </c>
       <c r="B1454" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31176</t>
         </is>
       </c>
       <c r="C1454" s="20" t="n"/>
@@ -29548,7 +29716,7 @@
     <row r="1456" ht="30" customHeight="1">
       <c r="A1456" s="16" t="inlineStr">
         <is>
-          <t>FICHA 98: dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
+          <t>FICHA 98: PPPA2027</t>
         </is>
       </c>
       <c r="B1456" s="17" t="n"/>
@@ -29573,7 +29741,7 @@
       <c r="E1457" s="20" t="n"/>
       <c r="F1457" s="20" t="n"/>
     </row>
-    <row r="1458" ht="20" customHeight="1">
+    <row r="1458" ht="45" customHeight="1">
       <c r="A1458" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -29581,7 +29749,7 @@
       </c>
       <c r="B1458" s="19" t="inlineStr">
         <is>
-          <t>Border regions Peer exchange on solving border obstacles</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="C1458" s="20" t="n"/>
@@ -29597,7 +29765,7 @@
       </c>
       <c r="B1459" s="19" t="inlineStr">
         <is>
-          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
+          <t>PPPA2027</t>
         </is>
       </c>
       <c r="C1459" s="20" t="n"/>
@@ -29685,7 +29853,7 @@
       </c>
       <c r="B1465" s="19" t="inlineStr">
         <is>
-          <t>EC-REGIO/2025/MVP/0023-EXA</t>
+          <t>PPPA-2025-IGF-IBA</t>
         </is>
       </c>
       <c r="C1465" s="20" t="n"/>
@@ -29693,7 +29861,7 @@
       <c r="E1465" s="20" t="n"/>
       <c r="F1465" s="20" t="n"/>
     </row>
-    <row r="1466" ht="20" customHeight="1">
+    <row r="1466" ht="45" customHeight="1">
       <c r="A1466" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -29701,7 +29869,7 @@
       </c>
       <c r="B1466" s="19" t="inlineStr">
         <is>
-          <t>Border regions Peer exchange on solving border obstacles</t>
+          <t>Interreg Governance Facility initiative to support Interreg cross-border cooperation (CBC) programmes</t>
         </is>
       </c>
       <c r="C1466" s="20" t="n"/>
@@ -29745,7 +29913,7 @@
       </c>
       <c r="B1469" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA2027</t>
         </is>
       </c>
       <c r="C1469" s="20" t="n"/>
@@ -29756,7 +29924,7 @@
     <row r="1471" ht="30" customHeight="1">
       <c r="A1471" s="16" t="inlineStr">
         <is>
-          <t>FICHA 99: 4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
+          <t>FICHA 99: dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
         </is>
       </c>
       <c r="B1471" s="17" t="n"/>
@@ -29805,7 +29973,7 @@
       </c>
       <c r="B1474" s="19" t="inlineStr">
         <is>
-          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
+          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
         </is>
       </c>
       <c r="C1474" s="20" t="n"/>
@@ -29893,7 +30061,7 @@
       </c>
       <c r="B1480" s="19" t="inlineStr">
         <is>
-          <t>EC-REGIO/2025/MVP/0036-EXA</t>
+          <t>EC-REGIO/2025/MVP/0023-EXA</t>
         </is>
       </c>
       <c r="C1480" s="20" t="n"/>
@@ -29953,7 +30121,7 @@
       </c>
       <c r="B1484" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
         </is>
       </c>
       <c r="C1484" s="20" t="n"/>
@@ -29964,7 +30132,7 @@
     <row r="1486" ht="30" customHeight="1">
       <c r="A1486" s="16" t="inlineStr">
         <is>
-          <t>FICHA 100: 8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>FICHA 100: 4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
         </is>
       </c>
       <c r="B1486" s="17" t="n"/>
@@ -29989,7 +30157,7 @@
       <c r="E1487" s="20" t="n"/>
       <c r="F1487" s="20" t="n"/>
     </row>
-    <row r="1488" ht="45" customHeight="1">
+    <row r="1488" ht="20" customHeight="1">
       <c r="A1488" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -29997,7 +30165,7 @@
       </c>
       <c r="B1488" s="19" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Border regions Peer exchange on solving border obstacles</t>
         </is>
       </c>
       <c r="C1488" s="20" t="n"/>
@@ -30013,7 +30181,7 @@
       </c>
       <c r="B1489" s="19" t="inlineStr">
         <is>
-          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
         </is>
       </c>
       <c r="C1489" s="20" t="n"/>
@@ -30101,7 +30269,7 @@
       </c>
       <c r="B1495" s="19" t="inlineStr">
         <is>
-          <t>EC-REGIO/2024/MVP/0031-EXA</t>
+          <t>EC-REGIO/2025/MVP/0036-EXA</t>
         </is>
       </c>
       <c r="C1495" s="20" t="n"/>
@@ -30109,7 +30277,7 @@
       <c r="E1495" s="20" t="n"/>
       <c r="F1495" s="20" t="n"/>
     </row>
-    <row r="1496" ht="45" customHeight="1">
+    <row r="1496" ht="20" customHeight="1">
       <c r="A1496" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -30117,7 +30285,7 @@
       </c>
       <c r="B1496" s="19" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
+          <t>Border regions Peer exchange on solving border obstacles</t>
         </is>
       </c>
       <c r="C1496" s="20" t="n"/>
@@ -30161,7 +30329,7 @@
       </c>
       <c r="B1499" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
         </is>
       </c>
       <c r="C1499" s="20" t="n"/>
@@ -30172,7 +30340,7 @@
     <row r="1501" ht="30" customHeight="1">
       <c r="A1501" s="16" t="inlineStr">
         <is>
-          <t>FICHA 101: 886623263</t>
+          <t>FICHA 101: 8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="B1501" s="17" t="n"/>
@@ -30197,7 +30365,7 @@
       <c r="E1502" s="20" t="n"/>
       <c r="F1502" s="20" t="n"/>
     </row>
-    <row r="1503" ht="20" customHeight="1">
+    <row r="1503" ht="45" customHeight="1">
       <c r="A1503" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -30205,7 +30373,7 @@
       </c>
       <c r="B1503" s="19" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="C1503" s="20" t="n"/>
@@ -30221,7 +30389,7 @@
       </c>
       <c r="B1504" s="19" t="inlineStr">
         <is>
-          <t>886623263</t>
+          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="C1504" s="20" t="n"/>
@@ -30307,13 +30475,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1510" s="19" t="inlineStr"/>
+      <c r="B1510" s="19" t="inlineStr">
+        <is>
+          <t>EC-REGIO/2024/MVP/0031-EXA</t>
+        </is>
+      </c>
       <c r="C1510" s="20" t="n"/>
       <c r="D1510" s="20" t="n"/>
       <c r="E1510" s="20" t="n"/>
       <c r="F1510" s="20" t="n"/>
     </row>
-    <row r="1511" ht="20" customHeight="1">
+    <row r="1511" ht="45" customHeight="1">
       <c r="A1511" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -30321,7 +30493,7 @@
       </c>
       <c r="B1511" s="19" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and Interreg IPA programmes’ cultural dimensions (2024CE160AT088)</t>
         </is>
       </c>
       <c r="C1511" s="20" t="n"/>
@@ -30365,7 +30537,7 @@
       </c>
       <c r="B1514" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/886623263</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="C1514" s="20" t="n"/>
@@ -30376,7 +30548,7 @@
     <row r="1516" ht="30" customHeight="1">
       <c r="A1516" s="16" t="inlineStr">
         <is>
-          <t>FICHA 102: 877314852</t>
+          <t>FICHA 102: 886623263</t>
         </is>
       </c>
       <c r="B1516" s="17" t="n"/>
@@ -30409,7 +30581,7 @@
       </c>
       <c r="B1518" s="19" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="C1518" s="20" t="n"/>
@@ -30425,7 +30597,7 @@
       </c>
       <c r="B1519" s="19" t="inlineStr">
         <is>
-          <t>877314852</t>
+          <t>886623263</t>
         </is>
       </c>
       <c r="C1519" s="20" t="n"/>
@@ -30525,7 +30697,7 @@
       </c>
       <c r="B1526" s="19" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="C1526" s="20" t="n"/>
@@ -30569,7 +30741,7 @@
       </c>
       <c r="B1529" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/877314852</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/886623263</t>
         </is>
       </c>
       <c r="C1529" s="20" t="n"/>
@@ -30580,7 +30752,7 @@
     <row r="1531" ht="30" customHeight="1">
       <c r="A1531" s="16" t="inlineStr">
         <is>
-          <t>FICHA 103: 900546740</t>
+          <t>FICHA 103: 877314852</t>
         </is>
       </c>
       <c r="B1531" s="17" t="n"/>
@@ -30605,7 +30777,7 @@
       <c r="E1532" s="20" t="n"/>
       <c r="F1532" s="20" t="n"/>
     </row>
-    <row r="1533" ht="45" customHeight="1">
+    <row r="1533" ht="20" customHeight="1">
       <c r="A1533" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -30613,7 +30785,7 @@
       </c>
       <c r="B1533" s="19" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="C1533" s="20" t="n"/>
@@ -30629,7 +30801,7 @@
       </c>
       <c r="B1534" s="19" t="inlineStr">
         <is>
-          <t>900546740</t>
+          <t>877314852</t>
         </is>
       </c>
       <c r="C1534" s="20" t="n"/>
@@ -30721,7 +30893,7 @@
       <c r="E1540" s="20" t="n"/>
       <c r="F1540" s="20" t="n"/>
     </row>
-    <row r="1541" ht="45" customHeight="1">
+    <row r="1541" ht="20" customHeight="1">
       <c r="A1541" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -30729,7 +30901,7 @@
       </c>
       <c r="B1541" s="19" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="C1541" s="20" t="n"/>
@@ -30773,7 +30945,7 @@
       </c>
       <c r="B1544" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/900546740</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/877314852</t>
         </is>
       </c>
       <c r="C1544" s="20" t="n"/>
@@ -30784,7 +30956,7 @@
     <row r="1546" ht="30" customHeight="1">
       <c r="A1546" s="16" t="inlineStr">
         <is>
-          <t>FICHA 104: 884174595</t>
+          <t>FICHA 104: 900546740</t>
         </is>
       </c>
       <c r="B1546" s="17" t="n"/>
@@ -30809,7 +30981,7 @@
       <c r="E1547" s="20" t="n"/>
       <c r="F1547" s="20" t="n"/>
     </row>
-    <row r="1548" ht="20" customHeight="1">
+    <row r="1548" ht="45" customHeight="1">
       <c r="A1548" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -30817,7 +30989,7 @@
       </c>
       <c r="B1548" s="19" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="C1548" s="20" t="n"/>
@@ -30833,7 +31005,7 @@
       </c>
       <c r="B1549" s="19" t="inlineStr">
         <is>
-          <t>884174595</t>
+          <t>900546740</t>
         </is>
       </c>
       <c r="C1549" s="20" t="n"/>
@@ -30925,7 +31097,7 @@
       <c r="E1555" s="20" t="n"/>
       <c r="F1555" s="20" t="n"/>
     </row>
-    <row r="1556" ht="20" customHeight="1">
+    <row r="1556" ht="45" customHeight="1">
       <c r="A1556" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -30933,7 +31105,7 @@
       </c>
       <c r="B1556" s="19" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>Department of International Cooperation and European Integration of the Rivne Regional State Administration</t>
         </is>
       </c>
       <c r="C1556" s="20" t="n"/>
@@ -30977,7 +31149,7 @@
       </c>
       <c r="B1559" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/884174595</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/900546740</t>
         </is>
       </c>
       <c r="C1559" s="20" t="n"/>
@@ -30988,7 +31160,7 @@
     <row r="1561" ht="30" customHeight="1">
       <c r="A1561" s="16" t="inlineStr">
         <is>
-          <t>FICHA 105: 941945952</t>
+          <t>FICHA 105: 884174595</t>
         </is>
       </c>
       <c r="B1561" s="17" t="n"/>
@@ -31021,7 +31193,7 @@
       </c>
       <c r="B1563" s="19" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="C1563" s="20" t="n"/>
@@ -31037,7 +31209,7 @@
       </c>
       <c r="B1564" s="19" t="inlineStr">
         <is>
-          <t>941945952</t>
+          <t>884174595</t>
         </is>
       </c>
       <c r="C1564" s="20" t="n"/>
@@ -31137,7 +31309,7 @@
       </c>
       <c r="B1571" s="19" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="C1571" s="20" t="n"/>
@@ -31181,7 +31353,7 @@
       </c>
       <c r="B1574" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/941945952</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/884174595</t>
         </is>
       </c>
       <c r="C1574" s="20" t="n"/>
@@ -31192,7 +31364,7 @@
     <row r="1576" ht="30" customHeight="1">
       <c r="A1576" s="16" t="inlineStr">
         <is>
-          <t>FICHA 106: 91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>FICHA 106: 941945952</t>
         </is>
       </c>
       <c r="B1576" s="17" t="n"/>
@@ -31225,7 +31397,7 @@
       </c>
       <c r="B1578" s="19" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="C1578" s="20" t="n"/>
@@ -31241,7 +31413,7 @@
       </c>
       <c r="B1579" s="19" t="inlineStr">
         <is>
-          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>941945952</t>
         </is>
       </c>
       <c r="C1579" s="20" t="n"/>
@@ -31327,11 +31499,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1585" s="19" t="inlineStr">
-        <is>
-          <t>EC-REGIO/2026/MVP/0069-EXA</t>
-        </is>
-      </c>
+      <c r="B1585" s="19" t="inlineStr"/>
       <c r="C1585" s="20" t="n"/>
       <c r="D1585" s="20" t="n"/>
       <c r="E1585" s="20" t="n"/>
@@ -31345,7 +31513,7 @@
       </c>
       <c r="B1586" s="19" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="C1586" s="20" t="n"/>
@@ -31389,7 +31557,7 @@
       </c>
       <c r="B1589" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/941945952</t>
         </is>
       </c>
       <c r="C1589" s="20" t="n"/>
@@ -31400,7 +31568,7 @@
     <row r="1591" ht="30" customHeight="1">
       <c r="A1591" s="16" t="inlineStr">
         <is>
-          <t>FICHA 107: ERDFTA</t>
+          <t>FICHA 107: 91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="B1591" s="17" t="n"/>
@@ -31433,7 +31601,7 @@
       </c>
       <c r="B1593" s="19" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="C1593" s="20" t="n"/>
@@ -31449,7 +31617,7 @@
       </c>
       <c r="B1594" s="19" t="inlineStr">
         <is>
-          <t>ERDFTA</t>
+          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="C1594" s="20" t="n"/>
@@ -31537,7 +31705,7 @@
       </c>
       <c r="B1600" s="19" t="inlineStr">
         <is>
-          <t>ERDFTA-2024-IVY-IBA</t>
+          <t>EC-REGIO/2026/MVP/0069-EXA</t>
         </is>
       </c>
       <c r="C1600" s="20" t="n"/>
@@ -31553,7 +31721,7 @@
       </c>
       <c r="B1601" s="19" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160AT102</t>
         </is>
       </c>
       <c r="C1601" s="20" t="n"/>
@@ -31597,7 +31765,7 @@
       </c>
       <c r="B1604" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="C1604" s="20" t="n"/>
@@ -31608,7 +31776,7 @@
     <row r="1606" ht="30" customHeight="1">
       <c r="A1606" s="16" t="inlineStr">
         <is>
-          <t>FICHA 108: 90488</t>
+          <t>FICHA 108: ERDFTA</t>
         </is>
       </c>
       <c r="B1606" s="17" t="n"/>
@@ -31633,7 +31801,7 @@
       <c r="E1607" s="20" t="n"/>
       <c r="F1607" s="20" t="n"/>
     </row>
-    <row r="1608" ht="45" customHeight="1">
+    <row r="1608" ht="20" customHeight="1">
       <c r="A1608" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -31641,7 +31809,7 @@
       </c>
       <c r="B1608" s="19" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="C1608" s="20" t="n"/>
@@ -31657,7 +31825,7 @@
       </c>
       <c r="B1609" s="19" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>ERDFTA</t>
         </is>
       </c>
       <c r="C1609" s="20" t="n"/>
@@ -31743,13 +31911,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B1615" s="19" t="inlineStr"/>
+      <c r="B1615" s="19" t="inlineStr">
+        <is>
+          <t>ERDFTA-2024-IVY-IBA</t>
+        </is>
+      </c>
       <c r="C1615" s="20" t="n"/>
       <c r="D1615" s="20" t="n"/>
       <c r="E1615" s="20" t="n"/>
       <c r="F1615" s="20" t="n"/>
     </row>
-    <row r="1616" ht="45" customHeight="1">
+    <row r="1616" ht="20" customHeight="1">
       <c r="A1616" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -31757,7 +31929,7 @@
       </c>
       <c r="B1616" s="19" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="C1616" s="20" t="n"/>
@@ -31801,7 +31973,7 @@
       </c>
       <c r="B1619" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/90488</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA</t>
         </is>
       </c>
       <c r="C1619" s="20" t="n"/>
@@ -31812,7 +31984,7 @@
     <row r="1621" ht="30" customHeight="1">
       <c r="A1621" s="16" t="inlineStr">
         <is>
-          <t>FICHA 109: 19326</t>
+          <t>FICHA 109: 90488</t>
         </is>
       </c>
       <c r="B1621" s="17" t="n"/>
@@ -31845,7 +32017,7 @@
       </c>
       <c r="B1623" s="19" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
         </is>
       </c>
       <c r="C1623" s="20" t="n"/>
@@ -31861,7 +32033,7 @@
       </c>
       <c r="B1624" s="19" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>90488</t>
         </is>
       </c>
       <c r="C1624" s="20" t="n"/>
@@ -31961,7 +32133,7 @@
       </c>
       <c r="B1631" s="19" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to indicate any priority examples—such as specific cross‑border protected areas or EU‑funded cross‑border cooperation projects (e.g. Interreg)—or should the selection be undertaken on the basis of a fully evidence‑based assessment?</t>
         </is>
       </c>
       <c r="C1631" s="20" t="n"/>
@@ -32005,7 +32177,7 @@
       </c>
       <c r="B1634" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19326</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/90488</t>
         </is>
       </c>
       <c r="C1634" s="20" t="n"/>
@@ -32016,7 +32188,7 @@
     <row r="1636" ht="30" customHeight="1">
       <c r="A1636" s="16" t="inlineStr">
         <is>
-          <t>FICHA 110: 14587</t>
+          <t>FICHA 110: 19326</t>
         </is>
       </c>
       <c r="B1636" s="17" t="n"/>
@@ -32049,7 +32221,7 @@
       </c>
       <c r="B1638" s="19" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
+          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
         </is>
       </c>
       <c r="C1638" s="20" t="n"/>
@@ -32065,7 +32237,7 @@
       </c>
       <c r="B1639" s="19" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="C1639" s="20" t="n"/>
@@ -32165,7 +32337,7 @@
       </c>
       <c r="B1646" s="19" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
+          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries considered to be within the scope of Innovative Energy Storage?</t>
         </is>
       </c>
       <c r="C1646" s="20" t="n"/>
@@ -32209,7 +32381,7 @@
       </c>
       <c r="B1649" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14587</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19326</t>
         </is>
       </c>
       <c r="C1649" s="20" t="n"/>
@@ -32220,7 +32392,7 @@
     <row r="1651" ht="30" customHeight="1">
       <c r="A1651" s="16" t="inlineStr">
         <is>
-          <t>FICHA 111: njaunzdz</t>
+          <t>FICHA 111: 14587</t>
         </is>
       </c>
       <c r="B1651" s="17" t="n"/>
@@ -32245,7 +32417,7 @@
       <c r="E1652" s="20" t="n"/>
       <c r="F1652" s="20" t="n"/>
     </row>
-    <row r="1653" ht="20" customHeight="1">
+    <row r="1653" ht="45" customHeight="1">
       <c r="A1653" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -32253,7 +32425,7 @@
       </c>
       <c r="B1653" s="19" t="inlineStr">
         <is>
-          <t>Mr. Dzintars Jaunzems</t>
+          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
         </is>
       </c>
       <c r="C1653" s="20" t="n"/>
@@ -32269,7 +32441,7 @@
       </c>
       <c r="B1654" s="19" t="inlineStr">
         <is>
-          <t>njaunzdz</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="C1654" s="20" t="n"/>
@@ -32361,7 +32533,7 @@
       <c r="E1660" s="20" t="n"/>
       <c r="F1660" s="20" t="n"/>
     </row>
-    <row r="1661" ht="20" customHeight="1">
+    <row r="1661" ht="45" customHeight="1">
       <c r="A1661" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -32369,7 +32541,7 @@
       </c>
       <c r="B1661" s="19" t="inlineStr">
         <is>
-          <t>Mr. Dzintars Jaunzems</t>
+          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
         </is>
       </c>
       <c r="C1661" s="20" t="n"/>
@@ -32413,7 +32585,7 @@
       </c>
       <c r="B1664" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/njaunzdz</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14587</t>
         </is>
       </c>
       <c r="C1664" s="20" t="n"/>
@@ -32424,7 +32596,7 @@
     <row r="1666" ht="30" customHeight="1">
       <c r="A1666" s="16" t="inlineStr">
         <is>
-          <t>FICHA 112: n00brugy</t>
+          <t>FICHA 112: njaunzdz</t>
         </is>
       </c>
       <c r="B1666" s="17" t="n"/>
@@ -32457,7 +32629,7 @@
       </c>
       <c r="B1668" s="19" t="inlineStr">
         <is>
-          <t>Joana SANTIAGO</t>
+          <t>Mr. Dzintars Jaunzems</t>
         </is>
       </c>
       <c r="C1668" s="20" t="n"/>
@@ -32473,7 +32645,7 @@
       </c>
       <c r="B1669" s="19" t="inlineStr">
         <is>
-          <t>n00brugy</t>
+          <t>njaunzdz</t>
         </is>
       </c>
       <c r="C1669" s="20" t="n"/>
@@ -32573,7 +32745,7 @@
       </c>
       <c r="B1676" s="19" t="inlineStr">
         <is>
-          <t>Joana SANTIAGO</t>
+          <t>Mr. Dzintars Jaunzems</t>
         </is>
       </c>
       <c r="C1676" s="20" t="n"/>
@@ -32617,7 +32789,7 @@
       </c>
       <c r="B1679" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n00brugy</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/njaunzdz</t>
         </is>
       </c>
       <c r="C1679" s="20" t="n"/>
@@ -32628,7 +32800,7 @@
     <row r="1681" ht="30" customHeight="1">
       <c r="A1681" s="16" t="inlineStr">
         <is>
-          <t>FICHA 113: n00kmonh</t>
+          <t>FICHA 113: n00brugy</t>
         </is>
       </c>
       <c r="B1681" s="17" t="n"/>
@@ -32661,7 +32833,7 @@
       </c>
       <c r="B1683" s="19" t="inlineStr">
         <is>
-          <t>Mrs LARA MARIA CERDAN AZNAR</t>
+          <t>Joana SANTIAGO</t>
         </is>
       </c>
       <c r="C1683" s="20" t="n"/>
@@ -32677,7 +32849,7 @@
       </c>
       <c r="B1684" s="19" t="inlineStr">
         <is>
-          <t>n00kmonh</t>
+          <t>n00brugy</t>
         </is>
       </c>
       <c r="C1684" s="20" t="n"/>
@@ -32777,7 +32949,7 @@
       </c>
       <c r="B1691" s="19" t="inlineStr">
         <is>
-          <t>Mrs LARA MARIA CERDAN AZNAR</t>
+          <t>Joana SANTIAGO</t>
         </is>
       </c>
       <c r="C1691" s="20" t="n"/>
@@ -32821,7 +32993,7 @@
       </c>
       <c r="B1694" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n00kmonh</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n00brugy</t>
         </is>
       </c>
       <c r="C1694" s="20" t="n"/>
@@ -32832,7 +33004,7 @@
     <row r="1696" ht="30" customHeight="1">
       <c r="A1696" s="16" t="inlineStr">
         <is>
-          <t>FICHA 114: 937468917</t>
+          <t>FICHA 114: n00kmonh</t>
         </is>
       </c>
       <c r="B1696" s="17" t="n"/>
@@ -32857,7 +33029,7 @@
       <c r="E1697" s="20" t="n"/>
       <c r="F1697" s="20" t="n"/>
     </row>
-    <row r="1698" ht="45" customHeight="1">
+    <row r="1698" ht="20" customHeight="1">
       <c r="A1698" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -32865,7 +33037,7 @@
       </c>
       <c r="B1698" s="19" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>Mrs LARA MARIA CERDAN AZNAR</t>
         </is>
       </c>
       <c r="C1698" s="20" t="n"/>
@@ -32881,7 +33053,7 @@
       </c>
       <c r="B1699" s="19" t="inlineStr">
         <is>
-          <t>937468917</t>
+          <t>n00kmonh</t>
         </is>
       </c>
       <c r="C1699" s="20" t="n"/>
@@ -32973,7 +33145,7 @@
       <c r="E1705" s="20" t="n"/>
       <c r="F1705" s="20" t="n"/>
     </row>
-    <row r="1706" ht="45" customHeight="1">
+    <row r="1706" ht="20" customHeight="1">
       <c r="A1706" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -32981,7 +33153,7 @@
       </c>
       <c r="B1706" s="19" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>Mrs LARA MARIA CERDAN AZNAR</t>
         </is>
       </c>
       <c r="C1706" s="20" t="n"/>
@@ -33025,7 +33197,7 @@
       </c>
       <c r="B1709" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/937468917</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n00kmonh</t>
         </is>
       </c>
       <c r="C1709" s="20" t="n"/>
@@ -33036,7 +33208,7 @@
     <row r="1711" ht="30" customHeight="1">
       <c r="A1711" s="16" t="inlineStr">
         <is>
-          <t>FICHA 115: 48508</t>
+          <t>FICHA 115: 937468917</t>
         </is>
       </c>
       <c r="B1711" s="17" t="n"/>
@@ -33069,7 +33241,7 @@
       </c>
       <c r="B1713" s="19" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="C1713" s="20" t="n"/>
@@ -33085,7 +33257,7 @@
       </c>
       <c r="B1714" s="19" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>937468917</t>
         </is>
       </c>
       <c r="C1714" s="20" t="n"/>
@@ -33185,7 +33357,7 @@
       </c>
       <c r="B1721" s="19" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="C1721" s="20" t="n"/>
@@ -33229,7 +33401,7 @@
       </c>
       <c r="B1724" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/48508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/937468917</t>
         </is>
       </c>
       <c r="C1724" s="20" t="n"/>
@@ -33444,7 +33616,7 @@
     <row r="1741" ht="30" customHeight="1">
       <c r="A1741" s="16" t="inlineStr">
         <is>
-          <t>FICHA 117: 16545</t>
+          <t>FICHA 117: 48508</t>
         </is>
       </c>
       <c r="B1741" s="17" t="n"/>
@@ -33477,7 +33649,7 @@
       </c>
       <c r="B1743" s="19" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="C1743" s="20" t="n"/>
@@ -33493,7 +33665,7 @@
       </c>
       <c r="B1744" s="19" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="C1744" s="20" t="n"/>
@@ -33593,7 +33765,7 @@
       </c>
       <c r="B1751" s="19" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="C1751" s="20" t="n"/>
@@ -33637,7 +33809,7 @@
       </c>
       <c r="B1754" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16545</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/48508</t>
         </is>
       </c>
       <c r="C1754" s="20" t="n"/>
@@ -33648,7 +33820,7 @@
     <row r="1756" ht="30" customHeight="1">
       <c r="A1756" s="16" t="inlineStr">
         <is>
-          <t>FICHA 118: 885233544</t>
+          <t>FICHA 118: 16545</t>
         </is>
       </c>
       <c r="B1756" s="17" t="n"/>
@@ -33673,7 +33845,7 @@
       <c r="E1757" s="20" t="n"/>
       <c r="F1757" s="20" t="n"/>
     </row>
-    <row r="1758" ht="20" customHeight="1">
+    <row r="1758" ht="45" customHeight="1">
       <c r="A1758" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33681,7 +33853,7 @@
       </c>
       <c r="B1758" s="19" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="C1758" s="20" t="n"/>
@@ -33697,7 +33869,7 @@
       </c>
       <c r="B1759" s="19" t="inlineStr">
         <is>
-          <t>885233544</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C1759" s="20" t="n"/>
@@ -33789,7 +33961,7 @@
       <c r="E1765" s="20" t="n"/>
       <c r="F1765" s="20" t="n"/>
     </row>
-    <row r="1766" ht="20" customHeight="1">
+    <row r="1766" ht="45" customHeight="1">
       <c r="A1766" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -33797,7 +33969,7 @@
       </c>
       <c r="B1766" s="19" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="C1766" s="20" t="n"/>
@@ -33841,7 +34013,7 @@
       </c>
       <c r="B1769" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/885233544</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16545</t>
         </is>
       </c>
       <c r="C1769" s="20" t="n"/>
@@ -33852,7 +34024,7 @@
     <row r="1771" ht="30" customHeight="1">
       <c r="A1771" s="16" t="inlineStr">
         <is>
-          <t>FICHA 119: 18804</t>
+          <t>FICHA 119: 885233544</t>
         </is>
       </c>
       <c r="B1771" s="17" t="n"/>
@@ -33877,7 +34049,7 @@
       <c r="E1772" s="20" t="n"/>
       <c r="F1772" s="20" t="n"/>
     </row>
-    <row r="1773" ht="45" customHeight="1">
+    <row r="1773" ht="20" customHeight="1">
       <c r="A1773" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -33885,7 +34057,7 @@
       </c>
       <c r="B1773" s="19" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="C1773" s="20" t="n"/>
@@ -33901,7 +34073,7 @@
       </c>
       <c r="B1774" s="19" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>885233544</t>
         </is>
       </c>
       <c r="C1774" s="20" t="n"/>
@@ -33993,7 +34165,7 @@
       <c r="E1780" s="20" t="n"/>
       <c r="F1780" s="20" t="n"/>
     </row>
-    <row r="1781" ht="45" customHeight="1">
+    <row r="1781" ht="20" customHeight="1">
       <c r="A1781" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -34001,7 +34173,7 @@
       </c>
       <c r="B1781" s="19" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="C1781" s="20" t="n"/>
@@ -34045,7 +34217,7 @@
       </c>
       <c r="B1784" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18804</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/885233544</t>
         </is>
       </c>
       <c r="C1784" s="20" t="n"/>
@@ -34056,7 +34228,7 @@
     <row r="1786" ht="30" customHeight="1">
       <c r="A1786" s="16" t="inlineStr">
         <is>
-          <t>FICHA 120: 18749</t>
+          <t>FICHA 120: 18804</t>
         </is>
       </c>
       <c r="B1786" s="17" t="n"/>
@@ -34089,7 +34261,7 @@
       </c>
       <c r="B1788" s="19" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="C1788" s="20" t="n"/>
@@ -34105,7 +34277,7 @@
       </c>
       <c r="B1789" s="19" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="C1789" s="20" t="n"/>
@@ -34205,7 +34377,7 @@
       </c>
       <c r="B1796" s="19" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="C1796" s="20" t="n"/>
@@ -34249,7 +34421,7 @@
       </c>
       <c r="B1799" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18749</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18804</t>
         </is>
       </c>
       <c r="C1799" s="20" t="n"/>
@@ -34260,7 +34432,7 @@
     <row r="1801" ht="30" customHeight="1">
       <c r="A1801" s="16" t="inlineStr">
         <is>
-          <t>FICHA 121: 31728</t>
+          <t>FICHA 121: 18749</t>
         </is>
       </c>
       <c r="B1801" s="17" t="n"/>
@@ -34293,7 +34465,7 @@
       </c>
       <c r="B1803" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="C1803" s="20" t="n"/>
@@ -34309,7 +34481,7 @@
       </c>
       <c r="B1804" s="19" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="C1804" s="20" t="n"/>
@@ -34409,7 +34581,7 @@
       </c>
       <c r="B1811" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="C1811" s="20" t="n"/>
@@ -34453,7 +34625,7 @@
       </c>
       <c r="B1814" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31728</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18749</t>
         </is>
       </c>
       <c r="C1814" s="20" t="n"/>
@@ -34464,7 +34636,7 @@
     <row r="1816" ht="30" customHeight="1">
       <c r="A1816" s="16" t="inlineStr">
         <is>
-          <t>FICHA 122: 13660</t>
+          <t>FICHA 122: 31728</t>
         </is>
       </c>
       <c r="B1816" s="17" t="n"/>
@@ -34489,7 +34661,7 @@
       <c r="E1817" s="20" t="n"/>
       <c r="F1817" s="20" t="n"/>
     </row>
-    <row r="1818" ht="20" customHeight="1">
+    <row r="1818" ht="45" customHeight="1">
       <c r="A1818" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -34497,7 +34669,7 @@
       </c>
       <c r="B1818" s="19" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="C1818" s="20" t="n"/>
@@ -34513,7 +34685,7 @@
       </c>
       <c r="B1819" s="19" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="C1819" s="20" t="n"/>
@@ -34613,7 +34785,7 @@
       </c>
       <c r="B1826" s="19" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technology in the heating and cooling sector. This is in line with the Paris Agreement and approaches a nearly zero carbon energy system.- By</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="C1826" s="20" t="n"/>
@@ -34657,7 +34829,7 @@
       </c>
       <c r="B1829" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13660</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31728</t>
         </is>
       </c>
       <c r="C1829" s="20" t="n"/>
@@ -34668,7 +34840,7 @@
     <row r="1831" ht="30" customHeight="1">
       <c r="A1831" s="16" t="inlineStr">
         <is>
-          <t>FICHA 123: 6484</t>
+          <t>FICHA 123: 13660</t>
         </is>
       </c>
       <c r="B1831" s="17" t="n"/>
@@ -34693,7 +34865,7 @@
       <c r="E1832" s="20" t="n"/>
       <c r="F1832" s="20" t="n"/>
     </row>
-    <row r="1833" ht="45" customHeight="1">
+    <row r="1833" ht="20" customHeight="1">
       <c r="A1833" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -34701,7 +34873,7 @@
       </c>
       <c r="B1833" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
         </is>
       </c>
       <c r="C1833" s="20" t="n"/>
@@ -34717,7 +34889,7 @@
       </c>
       <c r="B1834" s="19" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="C1834" s="20" t="n"/>
@@ -34817,7 +34989,7 @@
       </c>
       <c r="B1841" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technology in the heating and cooling sector. This is in line with the Paris Agreement and approaches a nearly zero carbon energy system.- By</t>
         </is>
       </c>
       <c r="C1841" s="20" t="n"/>
@@ -34861,7 +35033,7 @@
       </c>
       <c r="B1844" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/6484</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13660</t>
         </is>
       </c>
       <c r="C1844" s="20" t="n"/>
@@ -34872,7 +35044,7 @@
     <row r="1846" ht="30" customHeight="1">
       <c r="A1846" s="16" t="inlineStr">
         <is>
-          <t>FICHA 124: 16367</t>
+          <t>FICHA 124: 6484</t>
         </is>
       </c>
       <c r="B1846" s="17" t="n"/>
@@ -34905,7 +35077,7 @@
       </c>
       <c r="B1848" s="19" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="C1848" s="20" t="n"/>
@@ -34921,7 +35093,7 @@
       </c>
       <c r="B1849" s="19" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="C1849" s="20" t="n"/>
@@ -35021,7 +35193,7 @@
       </c>
       <c r="B1856" s="19" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="C1856" s="20" t="n"/>
@@ -35065,7 +35237,7 @@
       </c>
       <c r="B1859" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16367</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/6484</t>
         </is>
       </c>
       <c r="C1859" s="20" t="n"/>
@@ -35076,7 +35248,7 @@
     <row r="1861" ht="30" customHeight="1">
       <c r="A1861" s="16" t="inlineStr">
         <is>
-          <t>FICHA 125: 71691</t>
+          <t>FICHA 125: 16367</t>
         </is>
       </c>
       <c r="B1861" s="17" t="n"/>
@@ -35109,7 +35281,7 @@
       </c>
       <c r="B1863" s="19" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="C1863" s="20" t="n"/>
@@ -35125,7 +35297,7 @@
       </c>
       <c r="B1864" s="19" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="C1864" s="20" t="n"/>
@@ -35225,7 +35397,7 @@
       </c>
       <c r="B1871" s="19" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="C1871" s="20" t="n"/>
@@ -35269,7 +35441,7 @@
       </c>
       <c r="B1874" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71691</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16367</t>
         </is>
       </c>
       <c r="C1874" s="20" t="n"/>
@@ -35280,7 +35452,7 @@
     <row r="1876" ht="30" customHeight="1">
       <c r="A1876" s="16" t="inlineStr">
         <is>
-          <t>FICHA 126: 956926438</t>
+          <t>FICHA 126: 71691</t>
         </is>
       </c>
       <c r="B1876" s="17" t="n"/>
@@ -35305,7 +35477,7 @@
       <c r="E1877" s="20" t="n"/>
       <c r="F1877" s="20" t="n"/>
     </row>
-    <row r="1878" ht="20" customHeight="1">
+    <row r="1878" ht="45" customHeight="1">
       <c r="A1878" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -35313,7 +35485,7 @@
       </c>
       <c r="B1878" s="19" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="C1878" s="20" t="n"/>
@@ -35329,7 +35501,7 @@
       </c>
       <c r="B1879" s="19" t="inlineStr">
         <is>
-          <t>956926438</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="C1879" s="20" t="n"/>
@@ -35421,7 +35593,7 @@
       <c r="E1885" s="20" t="n"/>
       <c r="F1885" s="20" t="n"/>
     </row>
-    <row r="1886" ht="20" customHeight="1">
+    <row r="1886" ht="45" customHeight="1">
       <c r="A1886" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -35429,7 +35601,7 @@
       </c>
       <c r="B1886" s="19" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="C1886" s="20" t="n"/>
@@ -35473,7 +35645,7 @@
       </c>
       <c r="B1889" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/956926438</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71691</t>
         </is>
       </c>
       <c r="C1889" s="20" t="n"/>
@@ -35484,7 +35656,7 @@
     <row r="1891" ht="30" customHeight="1">
       <c r="A1891" s="16" t="inlineStr">
         <is>
-          <t>FICHA 127: 953677035</t>
+          <t>FICHA 127: 956926438</t>
         </is>
       </c>
       <c r="B1891" s="17" t="n"/>
@@ -35517,7 +35689,7 @@
       </c>
       <c r="B1893" s="19" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="C1893" s="20" t="n"/>
@@ -35533,7 +35705,7 @@
       </c>
       <c r="B1894" s="19" t="inlineStr">
         <is>
-          <t>953677035</t>
+          <t>956926438</t>
         </is>
       </c>
       <c r="C1894" s="20" t="n"/>
@@ -35633,7 +35805,7 @@
       </c>
       <c r="B1901" s="19" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="C1901" s="20" t="n"/>
@@ -35677,7 +35849,7 @@
       </c>
       <c r="B1904" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953677035</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/956926438</t>
         </is>
       </c>
       <c r="C1904" s="20" t="n"/>
@@ -35688,7 +35860,7 @@
     <row r="1906" ht="30" customHeight="1">
       <c r="A1906" s="16" t="inlineStr">
         <is>
-          <t>FICHA 128: 953552487</t>
+          <t>FICHA 128: 953677035</t>
         </is>
       </c>
       <c r="B1906" s="17" t="n"/>
@@ -35721,7 +35893,7 @@
       </c>
       <c r="B1908" s="19" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="C1908" s="20" t="n"/>
@@ -35737,7 +35909,7 @@
       </c>
       <c r="B1909" s="19" t="inlineStr">
         <is>
-          <t>953552487</t>
+          <t>953677035</t>
         </is>
       </c>
       <c r="C1909" s="20" t="n"/>
@@ -35837,7 +36009,7 @@
       </c>
       <c r="B1916" s="19" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="C1916" s="20" t="n"/>
@@ -35881,7 +36053,7 @@
       </c>
       <c r="B1919" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953552487</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953677035</t>
         </is>
       </c>
       <c r="C1919" s="20" t="n"/>
@@ -35892,7 +36064,7 @@
     <row r="1921" ht="30" customHeight="1">
       <c r="A1921" s="16" t="inlineStr">
         <is>
-          <t>FICHA 129: 10027</t>
+          <t>FICHA 129: 953552487</t>
         </is>
       </c>
       <c r="B1921" s="17" t="n"/>
@@ -35917,7 +36089,7 @@
       <c r="E1922" s="20" t="n"/>
       <c r="F1922" s="20" t="n"/>
     </row>
-    <row r="1923" ht="45" customHeight="1">
+    <row r="1923" ht="20" customHeight="1">
       <c r="A1923" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -35925,7 +36097,7 @@
       </c>
       <c r="B1923" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="C1923" s="20" t="n"/>
@@ -35941,7 +36113,7 @@
       </c>
       <c r="B1924" s="19" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>953552487</t>
         </is>
       </c>
       <c r="C1924" s="20" t="n"/>
@@ -36033,7 +36205,7 @@
       <c r="E1930" s="20" t="n"/>
       <c r="F1930" s="20" t="n"/>
     </row>
-    <row r="1931" ht="45" customHeight="1">
+    <row r="1931" ht="20" customHeight="1">
       <c r="A1931" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -36041,7 +36213,7 @@
       </c>
       <c r="B1931" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="C1931" s="20" t="n"/>
@@ -36085,7 +36257,7 @@
       </c>
       <c r="B1934" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/10027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953552487</t>
         </is>
       </c>
       <c r="C1934" s="20" t="n"/>
@@ -36096,7 +36268,7 @@
     <row r="1936" ht="30" customHeight="1">
       <c r="A1936" s="16" t="inlineStr">
         <is>
-          <t>FICHA 130: 95140</t>
+          <t>FICHA 130: 10027</t>
         </is>
       </c>
       <c r="B1936" s="17" t="n"/>
@@ -36129,7 +36301,7 @@
       </c>
       <c r="B1938" s="19" t="inlineStr">
         <is>
-          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="C1938" s="20" t="n"/>
@@ -36145,7 +36317,7 @@
       </c>
       <c r="B1939" s="19" t="inlineStr">
         <is>
-          <t>95140</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="C1939" s="20" t="n"/>
@@ -36245,7 +36417,7 @@
       </c>
       <c r="B1946" s="19" t="inlineStr">
         <is>
-          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="C1946" s="20" t="n"/>
@@ -36289,7 +36461,7 @@
       </c>
       <c r="B1949" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95140</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/10027</t>
         </is>
       </c>
       <c r="C1949" s="20" t="n"/>
@@ -36300,7 +36472,7 @@
     <row r="1951" ht="30" customHeight="1">
       <c r="A1951" s="16" t="inlineStr">
         <is>
-          <t>FICHA 131: 934294980</t>
+          <t>FICHA 131: 95140</t>
         </is>
       </c>
       <c r="B1951" s="17" t="n"/>
@@ -36325,7 +36497,7 @@
       <c r="E1952" s="20" t="n"/>
       <c r="F1952" s="20" t="n"/>
     </row>
-    <row r="1953" ht="20" customHeight="1">
+    <row r="1953" ht="45" customHeight="1">
       <c r="A1953" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -36333,7 +36505,7 @@
       </c>
       <c r="B1953" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
         </is>
       </c>
       <c r="C1953" s="20" t="n"/>
@@ -36349,7 +36521,7 @@
       </c>
       <c r="B1954" s="19" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>95140</t>
         </is>
       </c>
       <c r="C1954" s="20" t="n"/>
@@ -36441,7 +36613,7 @@
       <c r="E1960" s="20" t="n"/>
       <c r="F1960" s="20" t="n"/>
     </row>
-    <row r="1961" ht="20" customHeight="1">
+    <row r="1961" ht="45" customHeight="1">
       <c r="A1961" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -36449,7 +36621,7 @@
       </c>
       <c r="B1961" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
         </is>
       </c>
       <c r="C1961" s="20" t="n"/>
@@ -36493,7 +36665,7 @@
       </c>
       <c r="B1964" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95140</t>
         </is>
       </c>
       <c r="C1964" s="20" t="n"/>
@@ -36708,7 +36880,7 @@
     <row r="1981" ht="30" customHeight="1">
       <c r="A1981" s="16" t="inlineStr">
         <is>
-          <t>FICHA 133: 876983694</t>
+          <t>FICHA 133: 934294980</t>
         </is>
       </c>
       <c r="B1981" s="17" t="n"/>
@@ -36741,7 +36913,7 @@
       </c>
       <c r="B1983" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C1983" s="20" t="n"/>
@@ -36757,7 +36929,7 @@
       </c>
       <c r="B1984" s="19" t="inlineStr">
         <is>
-          <t>876983694</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C1984" s="20" t="n"/>
@@ -36857,7 +37029,7 @@
       </c>
       <c r="B1991" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C1991" s="20" t="n"/>
@@ -36901,7 +37073,7 @@
       </c>
       <c r="B1994" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/876983694</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
         </is>
       </c>
       <c r="C1994" s="20" t="n"/>
@@ -36912,7 +37084,7 @@
     <row r="1996" ht="30" customHeight="1">
       <c r="A1996" s="16" t="inlineStr">
         <is>
-          <t>FICHA 134: 17917</t>
+          <t>FICHA 134: 876983694</t>
         </is>
       </c>
       <c r="B1996" s="17" t="n"/>
@@ -36937,7 +37109,7 @@
       <c r="E1997" s="20" t="n"/>
       <c r="F1997" s="20" t="n"/>
     </row>
-    <row r="1998" ht="45" customHeight="1">
+    <row r="1998" ht="20" customHeight="1">
       <c r="A1998" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -36945,7 +37117,7 @@
       </c>
       <c r="B1998" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="C1998" s="20" t="n"/>
@@ -36961,7 +37133,7 @@
       </c>
       <c r="B1999" s="19" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>876983694</t>
         </is>
       </c>
       <c r="C1999" s="20" t="n"/>
@@ -37053,7 +37225,7 @@
       <c r="E2005" s="20" t="n"/>
       <c r="F2005" s="20" t="n"/>
     </row>
-    <row r="2006" ht="45" customHeight="1">
+    <row r="2006" ht="20" customHeight="1">
       <c r="A2006" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -37061,7 +37233,7 @@
       </c>
       <c r="B2006" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="C2006" s="20" t="n"/>
@@ -37105,7 +37277,7 @@
       </c>
       <c r="B2009" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17917</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/876983694</t>
         </is>
       </c>
       <c r="C2009" s="20" t="n"/>
@@ -37116,7 +37288,7 @@
     <row r="2011" ht="30" customHeight="1">
       <c r="A2011" s="16" t="inlineStr">
         <is>
-          <t>FICHA 135: 935134321</t>
+          <t>FICHA 135: 17917</t>
         </is>
       </c>
       <c r="B2011" s="17" t="n"/>
@@ -37141,7 +37313,7 @@
       <c r="E2012" s="20" t="n"/>
       <c r="F2012" s="20" t="n"/>
     </row>
-    <row r="2013" ht="20" customHeight="1">
+    <row r="2013" ht="45" customHeight="1">
       <c r="A2013" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -37149,7 +37321,7 @@
       </c>
       <c r="B2013" s="19" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="C2013" s="20" t="n"/>
@@ -37165,7 +37337,7 @@
       </c>
       <c r="B2014" s="19" t="inlineStr">
         <is>
-          <t>935134321</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="C2014" s="20" t="n"/>
@@ -37257,7 +37429,7 @@
       <c r="E2020" s="20" t="n"/>
       <c r="F2020" s="20" t="n"/>
     </row>
-    <row r="2021" ht="20" customHeight="1">
+    <row r="2021" ht="45" customHeight="1">
       <c r="A2021" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -37265,7 +37437,7 @@
       </c>
       <c r="B2021" s="19" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="C2021" s="20" t="n"/>
@@ -37309,7 +37481,7 @@
       </c>
       <c r="B2024" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/935134321</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17917</t>
         </is>
       </c>
       <c r="C2024" s="20" t="n"/>
@@ -37320,7 +37492,7 @@
     <row r="2026" ht="30" customHeight="1">
       <c r="A2026" s="16" t="inlineStr">
         <is>
-          <t>FICHA 136: 883154834</t>
+          <t>FICHA 136: 935134321</t>
         </is>
       </c>
       <c r="B2026" s="17" t="n"/>
@@ -37353,7 +37525,7 @@
       </c>
       <c r="B2028" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="C2028" s="20" t="n"/>
@@ -37369,7 +37541,7 @@
       </c>
       <c r="B2029" s="19" t="inlineStr">
         <is>
-          <t>883154834</t>
+          <t>935134321</t>
         </is>
       </c>
       <c r="C2029" s="20" t="n"/>
@@ -37469,7 +37641,7 @@
       </c>
       <c r="B2036" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="C2036" s="20" t="n"/>
@@ -37513,7 +37685,7 @@
       </c>
       <c r="B2039" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/883154834</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/935134321</t>
         </is>
       </c>
       <c r="C2039" s="20" t="n"/>
@@ -37524,7 +37696,7 @@
     <row r="2041" ht="30" customHeight="1">
       <c r="A2041" s="16" t="inlineStr">
         <is>
-          <t>FICHA 137: 93508</t>
+          <t>FICHA 137: 883154834</t>
         </is>
       </c>
       <c r="B2041" s="17" t="n"/>
@@ -37549,7 +37721,7 @@
       <c r="E2042" s="20" t="n"/>
       <c r="F2042" s="20" t="n"/>
     </row>
-    <row r="2043" ht="45" customHeight="1">
+    <row r="2043" ht="20" customHeight="1">
       <c r="A2043" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -37557,7 +37729,7 @@
       </c>
       <c r="B2043" s="19" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="C2043" s="20" t="n"/>
@@ -37573,7 +37745,7 @@
       </c>
       <c r="B2044" s="19" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>883154834</t>
         </is>
       </c>
       <c r="C2044" s="20" t="n"/>
@@ -37665,7 +37837,7 @@
       <c r="E2050" s="20" t="n"/>
       <c r="F2050" s="20" t="n"/>
     </row>
-    <row r="2051" ht="45" customHeight="1">
+    <row r="2051" ht="20" customHeight="1">
       <c r="A2051" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -37673,7 +37845,7 @@
       </c>
       <c r="B2051" s="19" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="C2051" s="20" t="n"/>
@@ -37717,7 +37889,7 @@
       </c>
       <c r="B2054" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/93508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/883154834</t>
         </is>
       </c>
       <c r="C2054" s="20" t="n"/>
@@ -37728,7 +37900,7 @@
     <row r="2056" ht="30" customHeight="1">
       <c r="A2056" s="16" t="inlineStr">
         <is>
-          <t>FICHA 138: 950910110</t>
+          <t>FICHA 138: 93508</t>
         </is>
       </c>
       <c r="B2056" s="17" t="n"/>
@@ -37753,7 +37925,7 @@
       <c r="E2057" s="20" t="n"/>
       <c r="F2057" s="20" t="n"/>
     </row>
-    <row r="2058" ht="20" customHeight="1">
+    <row r="2058" ht="45" customHeight="1">
       <c r="A2058" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -37761,7 +37933,7 @@
       </c>
       <c r="B2058" s="19" t="inlineStr">
         <is>
-          <t>CURA TERRAE WATER LIMITED</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="C2058" s="20" t="n"/>
@@ -37777,7 +37949,7 @@
       </c>
       <c r="B2059" s="19" t="inlineStr">
         <is>
-          <t>950910110</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="C2059" s="20" t="n"/>
@@ -37869,7 +38041,7 @@
       <c r="E2065" s="20" t="n"/>
       <c r="F2065" s="20" t="n"/>
     </row>
-    <row r="2066" ht="20" customHeight="1">
+    <row r="2066" ht="45" customHeight="1">
       <c r="A2066" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -37877,7 +38049,7 @@
       </c>
       <c r="B2066" s="19" t="inlineStr">
         <is>
-          <t>CURA TERRAE WATER LIMITED</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="C2066" s="20" t="n"/>
@@ -37921,7 +38093,7 @@
       </c>
       <c r="B2069" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/950910110</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/93508</t>
         </is>
       </c>
       <c r="C2069" s="20" t="n"/>
@@ -37932,7 +38104,7 @@
     <row r="2071" ht="30" customHeight="1">
       <c r="A2071" s="16" t="inlineStr">
         <is>
-          <t>FICHA 139: 954037778</t>
+          <t>FICHA 139: 950910110</t>
         </is>
       </c>
       <c r="B2071" s="17" t="n"/>
@@ -37965,7 +38137,7 @@
       </c>
       <c r="B2073" s="19" t="inlineStr">
         <is>
-          <t>VEOLIA EAU - COMPAGNIE GENERALE DES EAUX</t>
+          <t>CURA TERRAE WATER LIMITED</t>
         </is>
       </c>
       <c r="C2073" s="20" t="n"/>
@@ -37981,7 +38153,7 @@
       </c>
       <c r="B2074" s="19" t="inlineStr">
         <is>
-          <t>954037778</t>
+          <t>950910110</t>
         </is>
       </c>
       <c r="C2074" s="20" t="n"/>
@@ -38081,7 +38253,7 @@
       </c>
       <c r="B2081" s="19" t="inlineStr">
         <is>
-          <t>VEOLIA EAU - COMPAGNIE GENERALE DES EAUX</t>
+          <t>CURA TERRAE WATER LIMITED</t>
         </is>
       </c>
       <c r="C2081" s="20" t="n"/>
@@ -38125,7 +38297,7 @@
       </c>
       <c r="B2084" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/954037778</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/950910110</t>
         </is>
       </c>
       <c r="C2084" s="20" t="n"/>
@@ -45288,7 +45460,7 @@
     <row r="2611" ht="30" customHeight="1">
       <c r="A2611" s="16" t="inlineStr">
         <is>
-          <t>FICHA 175: EUS-63611</t>
+          <t>FICHA 175: EUS-43735</t>
         </is>
       </c>
       <c r="B2611" s="17" t="n"/>
@@ -45337,7 +45509,7 @@
       </c>
       <c r="B2614" s="19" t="inlineStr">
         <is>
-          <t>EUS-63611</t>
+          <t>EUS-43735</t>
         </is>
       </c>
       <c r="C2614" s="20" t="n"/>
@@ -45500,7 +45672,7 @@
     <row r="2626" ht="30" customHeight="1">
       <c r="A2626" s="16" t="inlineStr">
         <is>
-          <t>FICHA 176: EUS-46816</t>
+          <t>FICHA 176: EUS-23831</t>
         </is>
       </c>
       <c r="B2626" s="17" t="n"/>
@@ -45549,7 +45721,7 @@
       </c>
       <c r="B2629" s="19" t="inlineStr">
         <is>
-          <t>EUS-46816</t>
+          <t>EUS-23831</t>
         </is>
       </c>
       <c r="C2629" s="20" t="n"/>
@@ -45712,7 +45884,7 @@
     <row r="2641" ht="30" customHeight="1">
       <c r="A2641" s="16" t="inlineStr">
         <is>
-          <t>FICHA 177: EUS-59501</t>
+          <t>FICHA 177: EUS-89429</t>
         </is>
       </c>
       <c r="B2641" s="17" t="n"/>
@@ -45737,7 +45909,7 @@
       <c r="E2642" s="20" t="n"/>
       <c r="F2642" s="20" t="n"/>
     </row>
-    <row r="2643" ht="20" customHeight="1">
+    <row r="2643" ht="45" customHeight="1">
       <c r="A2643" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -45745,7 +45917,7 @@
       </c>
       <c r="B2643" s="19" t="inlineStr">
         <is>
-          <t>Reparación deficiencias eléctricas en Pabellón</t>
+          <t>Licitación, mediante procedimiento negociado sin publicidad, para la contratación de servicios de creación y edición de obra literaria y su divulgación para la Asociación BC3 Basque Centre for Climate</t>
         </is>
       </c>
       <c r="C2643" s="20" t="n"/>
@@ -45761,7 +45933,7 @@
       </c>
       <c r="B2644" s="19" t="inlineStr">
         <is>
-          <t>EUS-59501</t>
+          <t>EUS-89429</t>
         </is>
       </c>
       <c r="C2644" s="20" t="n"/>
@@ -45913,7 +46085,7 @@
       </c>
       <c r="B2654" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/reparacion-deficiencias-electricas-pabellon/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/licitacion-mediante-procedimiento-negociado-publicidad-contratacion-servicios-creacion-y-edicion-obra-literaria-y-su-divulgacion-asociacion-bc3-basque-centre-for-climate-change-klima-aldaketa-ikergai/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2654" s="20" t="n"/>
@@ -45924,7 +46096,7 @@
     <row r="2656" ht="30" customHeight="1">
       <c r="A2656" s="16" t="inlineStr">
         <is>
-          <t>FICHA 178: EUS-73899</t>
+          <t>FICHA 178: EUS-69995</t>
         </is>
       </c>
       <c r="B2656" s="17" t="n"/>
@@ -45973,7 +46145,7 @@
       </c>
       <c r="B2659" s="19" t="inlineStr">
         <is>
-          <t>EUS-73899</t>
+          <t>EUS-69995</t>
         </is>
       </c>
       <c r="C2659" s="20" t="n"/>
@@ -46136,7 +46308,7 @@
     <row r="2671" ht="30" customHeight="1">
       <c r="A2671" s="16" t="inlineStr">
         <is>
-          <t>FICHA 179: EUS-72308</t>
+          <t>FICHA 179: EUS-59844</t>
         </is>
       </c>
       <c r="B2671" s="17" t="n"/>
@@ -46185,7 +46357,7 @@
       </c>
       <c r="B2674" s="19" t="inlineStr">
         <is>
-          <t>EUS-72308</t>
+          <t>EUS-59844</t>
         </is>
       </c>
       <c r="C2674" s="20" t="n"/>
@@ -46348,7 +46520,7 @@
     <row r="2686" ht="30" customHeight="1">
       <c r="A2686" s="16" t="inlineStr">
         <is>
-          <t>FICHA 180: EUS-37473</t>
+          <t>FICHA 180: EUS-33760</t>
         </is>
       </c>
       <c r="B2686" s="17" t="n"/>
@@ -46373,7 +46545,7 @@
       <c r="E2687" s="20" t="n"/>
       <c r="F2687" s="20" t="n"/>
     </row>
-    <row r="2688" ht="20" customHeight="1">
+    <row r="2688" ht="45" customHeight="1">
       <c r="A2688" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -46381,7 +46553,7 @@
       </c>
       <c r="B2688" s="19" t="inlineStr">
         <is>
-          <t>Renovación licencias Teslab, infraestructura docente Joseba Albizuri.</t>
+          <t>Aprobar la contratación de los trabajos de "Integración de levantamientos topográficos en la base topográfica urbana de Álava", como contrato menor de servicios.</t>
         </is>
       </c>
       <c r="C2688" s="20" t="n"/>
@@ -46397,7 +46569,7 @@
       </c>
       <c r="B2689" s="19" t="inlineStr">
         <is>
-          <t>EUS-37473</t>
+          <t>EUS-33760</t>
         </is>
       </c>
       <c r="C2689" s="20" t="n"/>
@@ -46549,7 +46721,7 @@
       </c>
       <c r="B2699" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/renovacion-licencias-teslab-infraestructura-docente-joseba-albizuri/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/aprobar-contratacion-trabajos-integracion-levantamientos-topograficos-base-topografica-urbana-alava-como-contrato-menor-servicios/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2699" s="20" t="n"/>
@@ -46560,7 +46732,7 @@
     <row r="2701" ht="30" customHeight="1">
       <c r="A2701" s="16" t="inlineStr">
         <is>
-          <t>FICHA 181: EUS-31002</t>
+          <t>FICHA 181: EUS-93831</t>
         </is>
       </c>
       <c r="B2701" s="17" t="n"/>
@@ -46593,7 +46765,7 @@
       </c>
       <c r="B2703" s="19" t="inlineStr">
         <is>
-          <t>Mantenimiento preventivo de la cámara climática del Departamento de Fisiología Vegetal de la UPV/EHU en Leioa, según presupuesto 26/PMJ150, incluyendo la revisión general del equipo, comprobación de p</t>
+          <t>Contratación del servicio de asistencia técnica y gestión de venta de los ahorros energéticos generados por la empresa de Transporte Urbano de Vitoria-Gasteiz (TUVISA)</t>
         </is>
       </c>
       <c r="C2703" s="20" t="n"/>
@@ -46609,7 +46781,7 @@
       </c>
       <c r="B2704" s="19" t="inlineStr">
         <is>
-          <t>EUS-31002</t>
+          <t>EUS-93831</t>
         </is>
       </c>
       <c r="C2704" s="20" t="n"/>
@@ -46761,7 +46933,7 @@
       </c>
       <c r="B2714" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/mantenimiento-preventivo-camara-climatica-del-departamento-fisiologia-vegetal-upv-ehu-leioa-presupuesto-26-pmj150-incluyendo-revision-general-del-equipo-comprobacion-parametros-funcionamiento-presiones-temperaturas-consumos-electricos-y-tensiones-verific/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/contratacion-del-servicio-asistencia-tecnica-y-gestion-venta-ahorros-energeticos-generados-empresa-transporte-urbano-vitoria-gasteiz-tuvisa/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2714" s="20" t="n"/>
@@ -46772,7 +46944,7 @@
     <row r="2716" ht="30" customHeight="1">
       <c r="A2716" s="16" t="inlineStr">
         <is>
-          <t>FICHA 182: EUS-50049</t>
+          <t>FICHA 182: EUS-16126</t>
         </is>
       </c>
       <c r="B2716" s="17" t="n"/>
@@ -46805,7 +46977,7 @@
       </c>
       <c r="B2718" s="19" t="inlineStr">
         <is>
-          <t>Reparación de fuga de gas y sustitución de válvula de la cámara climática del Departamento de Fisiología Vegetal de la UPV/EHU en Leioa, según presupuesto 2026/244. La avería fue detectada en la revis</t>
+          <t>Obras del proyecto de construcción de itinerario peatonal paralelo a la calzada entre los PK 1,810 y 2,030 de la  GI-3131 a Goroeta en Aretxabaleta (14-SV-79/2025 2LIC)</t>
         </is>
       </c>
       <c r="C2718" s="20" t="n"/>
@@ -46821,7 +46993,7 @@
       </c>
       <c r="B2719" s="19" t="inlineStr">
         <is>
-          <t>EUS-50049</t>
+          <t>EUS-16126</t>
         </is>
       </c>
       <c r="C2719" s="20" t="n"/>
@@ -46973,7 +47145,7 @@
       </c>
       <c r="B2729" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/reparacion-fuga-gas-y-sustitucion-valvula-camara-climatica-del-departamento-fisiologia-vegetal-upv-ehu-leioa-presupuesto-2026-244-averia-fue-detectada-revision-general-infraestructura-realizada-gailur/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/obras-del-proyecto-construccion-itinerario-peatonal-paralelo-calzada-pk-1-810-y-2-030-gi-3131-goroeta-aretxabaleta-14-sv-79-2025-2lic/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2729" s="20" t="n"/>
@@ -46981,8 +47153,644 @@
       <c r="E2729" s="20" t="n"/>
       <c r="F2729" s="20" t="n"/>
     </row>
+    <row r="2731" ht="30" customHeight="1">
+      <c r="A2731" s="16" t="inlineStr">
+        <is>
+          <t>FICHA 183: EUS-08987</t>
+        </is>
+      </c>
+      <c r="B2731" s="17" t="n"/>
+      <c r="C2731" s="17" t="n"/>
+      <c r="D2731" s="17" t="n"/>
+      <c r="E2731" s="17" t="n"/>
+      <c r="F2731" s="17" t="n"/>
+    </row>
+    <row r="2732" ht="20" customHeight="1">
+      <c r="A2732" s="18" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B2732" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+      <c r="C2732" s="20" t="n"/>
+      <c r="D2732" s="20" t="n"/>
+      <c r="E2732" s="20" t="n"/>
+      <c r="F2732" s="20" t="n"/>
+    </row>
+    <row r="2733" ht="45" customHeight="1">
+      <c r="A2733" s="18" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B2733" s="19" t="inlineStr">
+        <is>
+          <t>reparación y puesta en servicio de red de fecales y pluviales en el centro CEIP Cantarrana Eskola HLHI</t>
+        </is>
+      </c>
+      <c r="C2733" s="20" t="n"/>
+      <c r="D2733" s="20" t="n"/>
+      <c r="E2733" s="20" t="n"/>
+      <c r="F2733" s="20" t="n"/>
+    </row>
+    <row r="2734" ht="20" customHeight="1">
+      <c r="A2734" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2734" s="19" t="inlineStr">
+        <is>
+          <t>EUS-08987</t>
+        </is>
+      </c>
+      <c r="C2734" s="20" t="n"/>
+      <c r="D2734" s="20" t="n"/>
+      <c r="E2734" s="20" t="n"/>
+      <c r="F2734" s="20" t="n"/>
+    </row>
+    <row r="2735" ht="20" customHeight="1">
+      <c r="A2735" s="18" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B2735" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="C2735" s="20" t="n"/>
+      <c r="D2735" s="20" t="n"/>
+      <c r="E2735" s="20" t="n"/>
+      <c r="F2735" s="20" t="n"/>
+    </row>
+    <row r="2736" ht="20" customHeight="1">
+      <c r="A2736" s="18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B2736" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C2736" s="20" t="n"/>
+      <c r="D2736" s="20" t="n"/>
+      <c r="E2736" s="20" t="n"/>
+      <c r="F2736" s="20" t="n"/>
+    </row>
+    <row r="2737" ht="20" customHeight="1">
+      <c r="A2737" s="18" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B2737" s="19" t="inlineStr"/>
+      <c r="C2737" s="20" t="n"/>
+      <c r="D2737" s="20" t="n"/>
+      <c r="E2737" s="20" t="n"/>
+      <c r="F2737" s="20" t="n"/>
+    </row>
+    <row r="2738" ht="20" customHeight="1">
+      <c r="A2738" s="18" t="inlineStr">
+        <is>
+          <t>Presupuesto (EUR)</t>
+        </is>
+      </c>
+      <c r="B2738" s="19" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="C2738" s="20" t="n"/>
+      <c r="D2738" s="20" t="n"/>
+      <c r="E2738" s="20" t="n"/>
+      <c r="F2738" s="20" t="n"/>
+    </row>
+    <row r="2739" ht="20" customHeight="1">
+      <c r="A2739" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de Accion</t>
+        </is>
+      </c>
+      <c r="B2739" s="19" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="C2739" s="20" t="n"/>
+      <c r="D2739" s="20" t="n"/>
+      <c r="E2739" s="20" t="n"/>
+      <c r="F2739" s="20" t="n"/>
+    </row>
+    <row r="2740" ht="20" customHeight="1">
+      <c r="A2740" s="18" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B2740" s="19" t="inlineStr"/>
+      <c r="C2740" s="20" t="n"/>
+      <c r="D2740" s="20" t="n"/>
+      <c r="E2740" s="20" t="n"/>
+      <c r="F2740" s="20" t="n"/>
+    </row>
+    <row r="2741" ht="20" customHeight="1">
+      <c r="A2741" s="18" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="B2741" s="19" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="C2741" s="20" t="n"/>
+      <c r="D2741" s="20" t="n"/>
+      <c r="E2741" s="20" t="n"/>
+      <c r="F2741" s="20" t="n"/>
+    </row>
+    <row r="2742" ht="20" customHeight="1">
+      <c r="A2742" s="18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B2742" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="C2742" s="20" t="n"/>
+      <c r="D2742" s="20" t="n"/>
+      <c r="E2742" s="20" t="n"/>
+      <c r="F2742" s="20" t="n"/>
+    </row>
+    <row r="2743" ht="20" customHeight="1">
+      <c r="A2743" s="18" t="inlineStr">
+        <is>
+          <t>Relevancia Bilbao</t>
+        </is>
+      </c>
+      <c r="B2743" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
+        </is>
+      </c>
+      <c r="C2743" s="20" t="n"/>
+      <c r="D2743" s="20" t="n"/>
+      <c r="E2743" s="20" t="n"/>
+      <c r="F2743" s="20" t="n"/>
+    </row>
+    <row r="2744" ht="45" customHeight="1">
+      <c r="A2744" s="18" t="inlineStr">
+        <is>
+          <t>Enlace al portal</t>
+        </is>
+      </c>
+      <c r="B2744" s="22" t="inlineStr">
+        <is>
+          <t>https://www.euskadi.eus/anuncio_contratacion/reparacion-y-puesta-servicio-red-fecales-y-pluviales-centro-ceip-cantarrana-eskola-hlhi/web01-tramite/es/</t>
+        </is>
+      </c>
+      <c r="C2744" s="20" t="n"/>
+      <c r="D2744" s="20" t="n"/>
+      <c r="E2744" s="20" t="n"/>
+      <c r="F2744" s="20" t="n"/>
+    </row>
+    <row r="2746" ht="30" customHeight="1">
+      <c r="A2746" s="16" t="inlineStr">
+        <is>
+          <t>FICHA 184: EUS-71383</t>
+        </is>
+      </c>
+      <c r="B2746" s="17" t="n"/>
+      <c r="C2746" s="17" t="n"/>
+      <c r="D2746" s="17" t="n"/>
+      <c r="E2746" s="17" t="n"/>
+      <c r="F2746" s="17" t="n"/>
+    </row>
+    <row r="2747" ht="20" customHeight="1">
+      <c r="A2747" s="18" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B2747" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+      <c r="C2747" s="20" t="n"/>
+      <c r="D2747" s="20" t="n"/>
+      <c r="E2747" s="20" t="n"/>
+      <c r="F2747" s="20" t="n"/>
+    </row>
+    <row r="2748" ht="45" customHeight="1">
+      <c r="A2748" s="18" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B2748" s="19" t="inlineStr">
+        <is>
+          <t>Suministro e instalación de un portón industrial enrollable para el edificio AIC Ermua</t>
+        </is>
+      </c>
+      <c r="C2748" s="20" t="n"/>
+      <c r="D2748" s="20" t="n"/>
+      <c r="E2748" s="20" t="n"/>
+      <c r="F2748" s="20" t="n"/>
+    </row>
+    <row r="2749" ht="20" customHeight="1">
+      <c r="A2749" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2749" s="19" t="inlineStr">
+        <is>
+          <t>EUS-71383</t>
+        </is>
+      </c>
+      <c r="C2749" s="20" t="n"/>
+      <c r="D2749" s="20" t="n"/>
+      <c r="E2749" s="20" t="n"/>
+      <c r="F2749" s="20" t="n"/>
+    </row>
+    <row r="2750" ht="20" customHeight="1">
+      <c r="A2750" s="18" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B2750" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="C2750" s="20" t="n"/>
+      <c r="D2750" s="20" t="n"/>
+      <c r="E2750" s="20" t="n"/>
+      <c r="F2750" s="20" t="n"/>
+    </row>
+    <row r="2751" ht="20" customHeight="1">
+      <c r="A2751" s="18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B2751" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C2751" s="20" t="n"/>
+      <c r="D2751" s="20" t="n"/>
+      <c r="E2751" s="20" t="n"/>
+      <c r="F2751" s="20" t="n"/>
+    </row>
+    <row r="2752" ht="20" customHeight="1">
+      <c r="A2752" s="18" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B2752" s="19" t="inlineStr"/>
+      <c r="C2752" s="20" t="n"/>
+      <c r="D2752" s="20" t="n"/>
+      <c r="E2752" s="20" t="n"/>
+      <c r="F2752" s="20" t="n"/>
+    </row>
+    <row r="2753" ht="20" customHeight="1">
+      <c r="A2753" s="18" t="inlineStr">
+        <is>
+          <t>Presupuesto (EUR)</t>
+        </is>
+      </c>
+      <c r="B2753" s="19" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="C2753" s="20" t="n"/>
+      <c r="D2753" s="20" t="n"/>
+      <c r="E2753" s="20" t="n"/>
+      <c r="F2753" s="20" t="n"/>
+    </row>
+    <row r="2754" ht="20" customHeight="1">
+      <c r="A2754" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de Accion</t>
+        </is>
+      </c>
+      <c r="B2754" s="19" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="C2754" s="20" t="n"/>
+      <c r="D2754" s="20" t="n"/>
+      <c r="E2754" s="20" t="n"/>
+      <c r="F2754" s="20" t="n"/>
+    </row>
+    <row r="2755" ht="20" customHeight="1">
+      <c r="A2755" s="18" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B2755" s="19" t="inlineStr"/>
+      <c r="C2755" s="20" t="n"/>
+      <c r="D2755" s="20" t="n"/>
+      <c r="E2755" s="20" t="n"/>
+      <c r="F2755" s="20" t="n"/>
+    </row>
+    <row r="2756" ht="20" customHeight="1">
+      <c r="A2756" s="18" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="B2756" s="19" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="C2756" s="20" t="n"/>
+      <c r="D2756" s="20" t="n"/>
+      <c r="E2756" s="20" t="n"/>
+      <c r="F2756" s="20" t="n"/>
+    </row>
+    <row r="2757" ht="20" customHeight="1">
+      <c r="A2757" s="18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B2757" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="C2757" s="20" t="n"/>
+      <c r="D2757" s="20" t="n"/>
+      <c r="E2757" s="20" t="n"/>
+      <c r="F2757" s="20" t="n"/>
+    </row>
+    <row r="2758" ht="20" customHeight="1">
+      <c r="A2758" s="18" t="inlineStr">
+        <is>
+          <t>Relevancia Bilbao</t>
+        </is>
+      </c>
+      <c r="B2758" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
+        </is>
+      </c>
+      <c r="C2758" s="20" t="n"/>
+      <c r="D2758" s="20" t="n"/>
+      <c r="E2758" s="20" t="n"/>
+      <c r="F2758" s="20" t="n"/>
+    </row>
+    <row r="2759" ht="45" customHeight="1">
+      <c r="A2759" s="18" t="inlineStr">
+        <is>
+          <t>Enlace al portal</t>
+        </is>
+      </c>
+      <c r="B2759" s="22" t="inlineStr">
+        <is>
+          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-e-instalacion-porton-industrial-enrollable-edificio-aic-ermua/expjaso747486/web01-tramite/es/</t>
+        </is>
+      </c>
+      <c r="C2759" s="20" t="n"/>
+      <c r="D2759" s="20" t="n"/>
+      <c r="E2759" s="20" t="n"/>
+      <c r="F2759" s="20" t="n"/>
+    </row>
+    <row r="2761" ht="30" customHeight="1">
+      <c r="A2761" s="16" t="inlineStr">
+        <is>
+          <t>FICHA 185: EUS-06475</t>
+        </is>
+      </c>
+      <c r="B2761" s="17" t="n"/>
+      <c r="C2761" s="17" t="n"/>
+      <c r="D2761" s="17" t="n"/>
+      <c r="E2761" s="17" t="n"/>
+      <c r="F2761" s="17" t="n"/>
+    </row>
+    <row r="2762" ht="20" customHeight="1">
+      <c r="A2762" s="18" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B2762" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+      <c r="C2762" s="20" t="n"/>
+      <c r="D2762" s="20" t="n"/>
+      <c r="E2762" s="20" t="n"/>
+      <c r="F2762" s="20" t="n"/>
+    </row>
+    <row r="2763" ht="45" customHeight="1">
+      <c r="A2763" s="18" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B2763" s="19" t="inlineStr">
+        <is>
+          <t>ANS para determinadas aplicaciones implementadas por Izfe para el Departamento de Equilibrio Territorial Verde de la GFA-DFG para la gestión de la identificación, registro, saneamiento y movimiento an</t>
+        </is>
+      </c>
+      <c r="C2763" s="20" t="n"/>
+      <c r="D2763" s="20" t="n"/>
+      <c r="E2763" s="20" t="n"/>
+      <c r="F2763" s="20" t="n"/>
+    </row>
+    <row r="2764" ht="20" customHeight="1">
+      <c r="A2764" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2764" s="19" t="inlineStr">
+        <is>
+          <t>EUS-06475</t>
+        </is>
+      </c>
+      <c r="C2764" s="20" t="n"/>
+      <c r="D2764" s="20" t="n"/>
+      <c r="E2764" s="20" t="n"/>
+      <c r="F2764" s="20" t="n"/>
+    </row>
+    <row r="2765" ht="20" customHeight="1">
+      <c r="A2765" s="18" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B2765" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="C2765" s="20" t="n"/>
+      <c r="D2765" s="20" t="n"/>
+      <c r="E2765" s="20" t="n"/>
+      <c r="F2765" s="20" t="n"/>
+    </row>
+    <row r="2766" ht="20" customHeight="1">
+      <c r="A2766" s="18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B2766" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C2766" s="20" t="n"/>
+      <c r="D2766" s="20" t="n"/>
+      <c r="E2766" s="20" t="n"/>
+      <c r="F2766" s="20" t="n"/>
+    </row>
+    <row r="2767" ht="20" customHeight="1">
+      <c r="A2767" s="18" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B2767" s="19" t="inlineStr"/>
+      <c r="C2767" s="20" t="n"/>
+      <c r="D2767" s="20" t="n"/>
+      <c r="E2767" s="20" t="n"/>
+      <c r="F2767" s="20" t="n"/>
+    </row>
+    <row r="2768" ht="20" customHeight="1">
+      <c r="A2768" s="18" t="inlineStr">
+        <is>
+          <t>Presupuesto (EUR)</t>
+        </is>
+      </c>
+      <c r="B2768" s="19" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="C2768" s="20" t="n"/>
+      <c r="D2768" s="20" t="n"/>
+      <c r="E2768" s="20" t="n"/>
+      <c r="F2768" s="20" t="n"/>
+    </row>
+    <row r="2769" ht="20" customHeight="1">
+      <c r="A2769" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de Accion</t>
+        </is>
+      </c>
+      <c r="B2769" s="19" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="C2769" s="20" t="n"/>
+      <c r="D2769" s="20" t="n"/>
+      <c r="E2769" s="20" t="n"/>
+      <c r="F2769" s="20" t="n"/>
+    </row>
+    <row r="2770" ht="20" customHeight="1">
+      <c r="A2770" s="18" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B2770" s="19" t="inlineStr"/>
+      <c r="C2770" s="20" t="n"/>
+      <c r="D2770" s="20" t="n"/>
+      <c r="E2770" s="20" t="n"/>
+      <c r="F2770" s="20" t="n"/>
+    </row>
+    <row r="2771" ht="20" customHeight="1">
+      <c r="A2771" s="18" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="B2771" s="19" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="C2771" s="20" t="n"/>
+      <c r="D2771" s="20" t="n"/>
+      <c r="E2771" s="20" t="n"/>
+      <c r="F2771" s="20" t="n"/>
+    </row>
+    <row r="2772" ht="20" customHeight="1">
+      <c r="A2772" s="18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B2772" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="C2772" s="20" t="n"/>
+      <c r="D2772" s="20" t="n"/>
+      <c r="E2772" s="20" t="n"/>
+      <c r="F2772" s="20" t="n"/>
+    </row>
+    <row r="2773" ht="20" customHeight="1">
+      <c r="A2773" s="18" t="inlineStr">
+        <is>
+          <t>Relevancia Bilbao</t>
+        </is>
+      </c>
+      <c r="B2773" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
+        </is>
+      </c>
+      <c r="C2773" s="20" t="n"/>
+      <c r="D2773" s="20" t="n"/>
+      <c r="E2773" s="20" t="n"/>
+      <c r="F2773" s="20" t="n"/>
+    </row>
+    <row r="2774" ht="45" customHeight="1">
+      <c r="A2774" s="18" t="inlineStr">
+        <is>
+          <t>Enlace al portal</t>
+        </is>
+      </c>
+      <c r="B2774" s="22" t="inlineStr">
+        <is>
+          <t>https://www.euskadi.eus/anuncio_contratacion/ans-determinadas-aplicaciones-implementadas-izfe-departamento-equilibrio-territorial-verde-gfa-dfg-gestion-identificacion-registro-saneamiento-y-movimiento-animal/expjaso739026/web01-tramite/es/</t>
+        </is>
+      </c>
+      <c r="C2774" s="20" t="n"/>
+      <c r="D2774" s="20" t="n"/>
+      <c r="E2774" s="20" t="n"/>
+      <c r="F2774" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2548">
+  <mergeCells count="2590">
     <mergeCell ref="B679:F679"/>
     <mergeCell ref="B2192:F2192"/>
     <mergeCell ref="B1765:F1765"/>
@@ -47084,6 +47892,7 @@
     <mergeCell ref="B243:F243"/>
     <mergeCell ref="B2465:F2465"/>
     <mergeCell ref="B2150:F2150"/>
+    <mergeCell ref="B2763:F2763"/>
     <mergeCell ref="B678:F678"/>
     <mergeCell ref="B363:F363"/>
     <mergeCell ref="B1731:F1731"/>
@@ -47220,6 +48029,7 @@
     <mergeCell ref="B1626:F1626"/>
     <mergeCell ref="B1582:F1582"/>
     <mergeCell ref="B1924:F1924"/>
+    <mergeCell ref="B2772:F2772"/>
     <mergeCell ref="B863:F863"/>
     <mergeCell ref="B2231:F2231"/>
     <mergeCell ref="B857:F857"/>
@@ -47275,6 +48085,7 @@
     <mergeCell ref="B1542:F1542"/>
     <mergeCell ref="B1840:F1840"/>
     <mergeCell ref="B808:F808"/>
+    <mergeCell ref="B2753:F2753"/>
     <mergeCell ref="B1237:F1237"/>
     <mergeCell ref="B897:F897"/>
     <mergeCell ref="B1413:F1413"/>
@@ -47302,6 +48113,8 @@
     <mergeCell ref="B798:F798"/>
     <mergeCell ref="B521:F521"/>
     <mergeCell ref="B1553:F1553"/>
+    <mergeCell ref="B2743:F2743"/>
+    <mergeCell ref="B2737:F2737"/>
     <mergeCell ref="B2009:F2009"/>
     <mergeCell ref="B828:F828"/>
     <mergeCell ref="B950:F950"/>
@@ -47342,6 +48155,7 @@
     <mergeCell ref="B2240:F2240"/>
     <mergeCell ref="B963:F963"/>
     <mergeCell ref="B208:F208"/>
+    <mergeCell ref="B2756:F2756"/>
     <mergeCell ref="B1941:F1941"/>
     <mergeCell ref="B882:F882"/>
     <mergeCell ref="B2239:F2239"/>
@@ -47386,16 +48200,20 @@
     <mergeCell ref="B621:F621"/>
     <mergeCell ref="B613:F613"/>
     <mergeCell ref="B911:F911"/>
+    <mergeCell ref="B2739:F2739"/>
     <mergeCell ref="B1340:F1340"/>
     <mergeCell ref="B623:F623"/>
     <mergeCell ref="B2005:F2005"/>
     <mergeCell ref="B1676:F1676"/>
     <mergeCell ref="B921:F921"/>
     <mergeCell ref="B606:F606"/>
+    <mergeCell ref="B2741:F2741"/>
     <mergeCell ref="B2007:F2007"/>
     <mergeCell ref="B2436:F2436"/>
     <mergeCell ref="A1276:F1276"/>
+    <mergeCell ref="B2770:F2770"/>
     <mergeCell ref="B2307:F2307"/>
+    <mergeCell ref="B2736:F2736"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="A1486:F1486"/>
     <mergeCell ref="B334:F334"/>
@@ -47411,9 +48229,11 @@
     <mergeCell ref="B2448:F2448"/>
     <mergeCell ref="B1720:F1720"/>
     <mergeCell ref="B965:F965"/>
+    <mergeCell ref="B2752:F2752"/>
     <mergeCell ref="B2027:F2027"/>
     <mergeCell ref="B2149:F2149"/>
     <mergeCell ref="B2447:F2447"/>
+    <mergeCell ref="B2754:F2754"/>
     <mergeCell ref="B669:F669"/>
     <mergeCell ref="B1722:F1722"/>
     <mergeCell ref="B2020:F2020"/>
@@ -47568,6 +48388,7 @@
     <mergeCell ref="B2215:F2215"/>
     <mergeCell ref="B1460:F1460"/>
     <mergeCell ref="B2486:F2486"/>
+    <mergeCell ref="A2731:F2731"/>
     <mergeCell ref="B2246:F2246"/>
     <mergeCell ref="A946:F946"/>
     <mergeCell ref="A631:F631"/>
@@ -47754,6 +48575,7 @@
     <mergeCell ref="B1263:F1263"/>
     <mergeCell ref="A2206:F2206"/>
     <mergeCell ref="B2629:F2629"/>
+    <mergeCell ref="B2751:F2751"/>
     <mergeCell ref="B842:F842"/>
     <mergeCell ref="B1868:F1868"/>
     <mergeCell ref="B836:F836"/>
@@ -47768,11 +48590,13 @@
     <mergeCell ref="B1596:F1596"/>
     <mergeCell ref="B1281:F1281"/>
     <mergeCell ref="B1579:F1579"/>
+    <mergeCell ref="B2769:F2769"/>
     <mergeCell ref="B1589:F1589"/>
     <mergeCell ref="B2342:F2342"/>
     <mergeCell ref="B1283:F1283"/>
     <mergeCell ref="B257:F257"/>
     <mergeCell ref="B2464:F2464"/>
+    <mergeCell ref="B2771:F2771"/>
     <mergeCell ref="B1124:F1124"/>
     <mergeCell ref="B1162:F1162"/>
     <mergeCell ref="B92:F92"/>
@@ -47780,6 +48604,7 @@
     <mergeCell ref="B2675:F2675"/>
     <mergeCell ref="B1282:F1282"/>
     <mergeCell ref="B2335:F2335"/>
+    <mergeCell ref="B2764:F2764"/>
     <mergeCell ref="B557:F557"/>
     <mergeCell ref="B2248:F2248"/>
     <mergeCell ref="B2223:F2223"/>
@@ -47806,6 +48631,7 @@
     <mergeCell ref="B883:F883"/>
     <mergeCell ref="B2390:F2390"/>
     <mergeCell ref="B2694:F2694"/>
+    <mergeCell ref="B2732:F2732"/>
     <mergeCell ref="B1969:F1969"/>
     <mergeCell ref="B2267:F2267"/>
     <mergeCell ref="B1208:F1208"/>
@@ -47848,6 +48674,7 @@
     <mergeCell ref="B647:F647"/>
     <mergeCell ref="B1252:F1252"/>
     <mergeCell ref="B1374:F1374"/>
+    <mergeCell ref="B2740:F2740"/>
     <mergeCell ref="B1708:F1708"/>
     <mergeCell ref="B649:F649"/>
     <mergeCell ref="A1801:F1801"/>
@@ -47865,6 +48692,7 @@
     <mergeCell ref="B949:F949"/>
     <mergeCell ref="B221:F221"/>
     <mergeCell ref="B2462:F2462"/>
+    <mergeCell ref="B2735:F2735"/>
     <mergeCell ref="B650:F650"/>
     <mergeCell ref="B2219:F2219"/>
     <mergeCell ref="B948:F948"/>
@@ -47948,13 +48776,16 @@
     <mergeCell ref="B2433:F2433"/>
     <mergeCell ref="B1401:F1401"/>
     <mergeCell ref="B2427:F2427"/>
+    <mergeCell ref="B2767:F2767"/>
     <mergeCell ref="B2006:F2006"/>
     <mergeCell ref="B2304:F2304"/>
     <mergeCell ref="B219:F219"/>
     <mergeCell ref="B460:F460"/>
     <mergeCell ref="B517:F517"/>
+    <mergeCell ref="B2733:F2733"/>
     <mergeCell ref="B1701:F1701"/>
     <mergeCell ref="B760:F760"/>
+    <mergeCell ref="B2762:F2762"/>
     <mergeCell ref="B1119:F1119"/>
     <mergeCell ref="A2026:F2026"/>
     <mergeCell ref="B333:F333"/>
@@ -48108,6 +48939,7 @@
     <mergeCell ref="B1438:F1438"/>
     <mergeCell ref="B683:F683"/>
     <mergeCell ref="B1742:F1742"/>
+    <mergeCell ref="B2768:F2768"/>
     <mergeCell ref="B1527:F1527"/>
     <mergeCell ref="B2043:F2043"/>
     <mergeCell ref="A1036:F1036"/>
@@ -48173,6 +49005,7 @@
     <mergeCell ref="B1624:F1624"/>
     <mergeCell ref="B2110:F2110"/>
     <mergeCell ref="A991:F991"/>
+    <mergeCell ref="A2761:F2761"/>
     <mergeCell ref="A676:F676"/>
     <mergeCell ref="B137:F137"/>
     <mergeCell ref="B2283:F2283"/>
@@ -48313,12 +49146,14 @@
     <mergeCell ref="B635:F635"/>
     <mergeCell ref="A2506:F2506"/>
     <mergeCell ref="B935:F935"/>
+    <mergeCell ref="B2749:F2749"/>
     <mergeCell ref="B2021:F2021"/>
     <mergeCell ref="B962:F962"/>
     <mergeCell ref="B505:F505"/>
     <mergeCell ref="B1558:F1558"/>
     <mergeCell ref="B499:F499"/>
     <mergeCell ref="B2450:F2450"/>
+    <mergeCell ref="B2748:F2748"/>
     <mergeCell ref="A1171:F1171"/>
     <mergeCell ref="B1716:F1716"/>
     <mergeCell ref="B2023:F2023"/>
@@ -48328,6 +49163,7 @@
     <mergeCell ref="B2619:F2619"/>
     <mergeCell ref="B534:F534"/>
     <mergeCell ref="B805:F805"/>
+    <mergeCell ref="B2750:F2750"/>
     <mergeCell ref="B1718:F1718"/>
     <mergeCell ref="B2016:F2016"/>
     <mergeCell ref="B957:F957"/>
@@ -48441,6 +49277,7 @@
     <mergeCell ref="B1700:F1700"/>
     <mergeCell ref="B641:F641"/>
     <mergeCell ref="B2645:F2645"/>
+    <mergeCell ref="B2759:F2759"/>
     <mergeCell ref="B1404:F1404"/>
     <mergeCell ref="B1287:F1287"/>
     <mergeCell ref="B972:F972"/>
@@ -48683,6 +49520,7 @@
     <mergeCell ref="B377:F377"/>
     <mergeCell ref="B2620:F2620"/>
     <mergeCell ref="B1277:F1277"/>
+    <mergeCell ref="B2765:F2765"/>
     <mergeCell ref="B2249:F2249"/>
     <mergeCell ref="B2547:F2547"/>
     <mergeCell ref="B850:F850"/>
@@ -48867,6 +49705,7 @@
     <mergeCell ref="B2299:F2299"/>
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B512:F512"/>
+    <mergeCell ref="B2734:F2734"/>
     <mergeCell ref="B2728:F2728"/>
     <mergeCell ref="B2000:F2000"/>
     <mergeCell ref="B303:F303"/>
@@ -48881,6 +49720,7 @@
     <mergeCell ref="B2727:F2727"/>
     <mergeCell ref="B1328:F1328"/>
     <mergeCell ref="B812:F812"/>
+    <mergeCell ref="B2757:F2757"/>
     <mergeCell ref="B2002:F2002"/>
     <mergeCell ref="B2300:F2300"/>
     <mergeCell ref="B603:F603"/>
@@ -48891,6 +49731,7 @@
     <mergeCell ref="B2302:F2302"/>
     <mergeCell ref="B2600:F2600"/>
     <mergeCell ref="B515:F515"/>
+    <mergeCell ref="B2758:F2758"/>
     <mergeCell ref="A841:F841"/>
     <mergeCell ref="B959:F959"/>
     <mergeCell ref="B1257:F1257"/>
@@ -48911,6 +49752,7 @@
     <mergeCell ref="B531:F531"/>
     <mergeCell ref="B1417:F1417"/>
     <mergeCell ref="B662:F662"/>
+    <mergeCell ref="B2747:F2747"/>
     <mergeCell ref="B1715:F1715"/>
     <mergeCell ref="B2353:F2353"/>
     <mergeCell ref="B2013:F2013"/>
@@ -48926,6 +49768,7 @@
     <mergeCell ref="B2313:F2313"/>
     <mergeCell ref="B228:F228"/>
     <mergeCell ref="B2444:F2444"/>
+    <mergeCell ref="B2742:F2742"/>
     <mergeCell ref="B657:F657"/>
     <mergeCell ref="A2251:F2251"/>
     <mergeCell ref="B672:F672"/>
@@ -49014,6 +49857,7 @@
     <mergeCell ref="B2440:F2440"/>
     <mergeCell ref="B1408:F1408"/>
     <mergeCell ref="B1383:F1383"/>
+    <mergeCell ref="B2738:F2738"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B467:F467"/>
     <mergeCell ref="B2469:F2469"/>
@@ -49041,6 +49885,7 @@
     <mergeCell ref="B2337:F2337"/>
     <mergeCell ref="B252:F252"/>
     <mergeCell ref="B2495:F2495"/>
+    <mergeCell ref="B2766:F2766"/>
     <mergeCell ref="B2451:F2451"/>
     <mergeCell ref="B366:F366"/>
     <mergeCell ref="B979:F979"/>
@@ -49083,6 +49928,7 @@
     <mergeCell ref="B1480:F1480"/>
     <mergeCell ref="B1165:F1165"/>
     <mergeCell ref="B1048:F1048"/>
+    <mergeCell ref="A2746:F2746"/>
     <mergeCell ref="B1594:F1594"/>
     <mergeCell ref="B1892:F1892"/>
     <mergeCell ref="B1167:F1167"/>
@@ -49270,9 +50116,11 @@
     <mergeCell ref="A2041:F2041"/>
     <mergeCell ref="B1432:F1432"/>
     <mergeCell ref="B1554:F1554"/>
+    <mergeCell ref="B2744:F2744"/>
     <mergeCell ref="B835:F835"/>
     <mergeCell ref="B829:F829"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B2774:F2774"/>
     <mergeCell ref="B1127:F1127"/>
     <mergeCell ref="B68:F68"/>
     <mergeCell ref="B372:F372"/>
@@ -49400,6 +50248,7 @@
     <mergeCell ref="B1267:F1267"/>
     <mergeCell ref="B1609:F1609"/>
     <mergeCell ref="A751:F751"/>
+    <mergeCell ref="B2755:F2755"/>
     <mergeCell ref="B1723:F1723"/>
     <mergeCell ref="B2328:F2328"/>
     <mergeCell ref="B1567:F1567"/>
@@ -49420,6 +50269,7 @@
     <mergeCell ref="B872:F872"/>
     <mergeCell ref="B866:F866"/>
     <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B2773:F2773"/>
     <mergeCell ref="B1301:F1301"/>
     <mergeCell ref="B986:F986"/>
     <mergeCell ref="B1024:F1024"/>
@@ -49715,6 +50565,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2699" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2714" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2729" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2744" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2759" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2774" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -49726,7 +50579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J183"/>
+  <dimension ref="A1:J186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -51712,12 +52565,12 @@
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics u</t>
+          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr"/>
@@ -51744,19 +52597,15 @@
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics u</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr"/>
       <c r="D62" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -51780,15 +52629,19 @@
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from severa</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr"/>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -51812,12 +52665,12 @@
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – Is it possible to submit a joint proposal from severa</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr"/>
@@ -51844,12 +52697,12 @@
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission tr</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr"/>
@@ -51876,12 +52729,12 @@
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>AFIF – What kind of equipment is considered zero-emission tr</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr"/>
@@ -51908,12 +52761,12 @@
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKT</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr"/>
@@ -51940,12 +52793,12 @@
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKT</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr"/>
@@ -51972,12 +52825,12 @@
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr"/>
@@ -52004,12 +52857,12 @@
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr"/>
@@ -52068,12 +52921,12 @@
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr"/>
@@ -52100,12 +52953,12 @@
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic L</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr"/>
@@ -52132,12 +52985,12 @@
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic L</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr"/>
@@ -52164,12 +53017,12 @@
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr"/>
@@ -52196,12 +53049,12 @@
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr"/>
@@ -52228,12 +53081,12 @@
     <row r="77" ht="28" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr"/>
@@ -52260,12 +53113,12 @@
     <row r="78" ht="28" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Considering the increasing importance of ecosystem restorati</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr"/>
@@ -52292,12 +53145,12 @@
     <row r="79" ht="28" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>49506</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Regarding the case study in Lot 2, you mention terms such as</t>
+          <t>Considering the increasing importance of ecosystem restorati</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr"/>
@@ -52324,12 +53177,12 @@
     <row r="80" ht="28" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>898575215</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
+          <t>Regarding the case study in Lot 2, you mention terms such as</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr"/>
@@ -52356,12 +53209,12 @@
     <row r="81" ht="28" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>898575215</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaam</t>
+          <t>FORENINGEN C40 CITIES CLIMATE LEADERSHIP DENMARK</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr"/>
@@ -52388,12 +53241,12 @@
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Should the selected port related to the Cities Mission be on</t>
+          <t>Annex I - Part 2 - Technical Specifications_V1.pdf (duurzaam</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr"/>
@@ -52420,12 +53273,12 @@
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>A Net Zero Food System - Insight Report</t>
+          <t>Should the selected port related to the Cities Mission be on</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr"/>
@@ -52452,12 +53305,12 @@
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>83951</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submi</t>
+          <t>A Net Zero Food System - Insight Report</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr"/>
@@ -52484,12 +53337,12 @@
     <row r="85" ht="28" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>880954583</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>STICHTING JONGE KLIMAATBEWEGING</t>
+          <t>Under the call SMP-COSME-2024-CLUSTER, shall proposals submi</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr"/>
@@ -52516,12 +53369,12 @@
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
+          <t>880954583</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Inter-institutional single framework contract to support the</t>
+          <t>STICHTING JONGE KLIMAATBEWEGING</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr"/>
@@ -52548,12 +53401,12 @@
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>c68aab09-64dc-4939-bab0-f1614fc69012-PIN</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do loca</t>
+          <t>Inter-institutional single framework contract to support the</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr"/>
@@ -52580,12 +53433,12 @@
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>893516374</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Foundation for Urban Resilience and Climate Sustainability</t>
+          <t>Under call LIFE-2023-CET, topic LIFE-2023-CET-LOCAL, do loca</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr"/>
@@ -52612,12 +53465,12 @@
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>894079362</t>
+          <t>893516374</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Verga Pietro Lupo</t>
+          <t>Foundation for Urban Resilience and Climate Sustainability</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr"/>
@@ -52644,12 +53497,12 @@
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>867619605</t>
+          <t>894079362</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Mancomunitat l'Horta Nord</t>
+          <t>Verga Pietro Lupo</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr"/>
@@ -52676,12 +53529,12 @@
     <row r="91" ht="28" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>ncaviale</t>
+          <t>867619605</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Prof. Alessio CAVICCHI</t>
+          <t>Mancomunitat l'Horta Nord</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr"/>
@@ -52708,12 +53561,12 @@
     <row r="92" ht="28" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>ncaviale</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>In the paragraphs following the sentence "Any rejection by F</t>
+          <t>Prof. Alessio CAVICCHI</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr"/>
@@ -52740,12 +53593,12 @@
     <row r="93" ht="28" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>906456368</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Global Action Plan</t>
+          <t>In the paragraphs following the sentence "Any rejection by F</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr"/>
@@ -52772,12 +53625,12 @@
     <row r="94" ht="28" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>939595836</t>
+          <t>906456368</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL ACTION PLAN</t>
+          <t>Global Action Plan</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr"/>
@@ -52804,12 +53657,12 @@
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>939595836</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>The deliverable for the “Crisis Management Plan” includes 14</t>
+          <t>GLOBAL ACTION PLAN</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr"/>
@@ -52836,12 +53689,12 @@
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>The topic requires to "include a draft plan for joint action</t>
+          <t>The deliverable for the “Crisis Management Plan” includes 14</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr"/>
@@ -52868,12 +53721,12 @@
     <row r="97" ht="28" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total bud</t>
+          <t>The topic requires to "include a draft plan for joint action</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr"/>
@@ -52900,12 +53753,12 @@
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>PPPA2027</t>
+          <t>31176</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interreg Governance Facility initiative to support Interreg </t>
+          <t>HORIZON-EIE-2023-CONNECT-03-01: Is the action plan total bud</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr"/>
@@ -52932,12 +53785,12 @@
     <row r="99" ht="28" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
+          <t>PPPA2027</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Border regions Peer exchange on solving border obstacles</t>
+          <t xml:space="preserve">Interreg Governance Facility initiative to support Interreg </t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr"/>
@@ -52964,7 +53817,7 @@
     <row r="100" ht="28" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
+          <t>dc0033a0-cb94-44ed-8102-0fd0a386989e-EXA</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -52996,12 +53849,12 @@
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
+          <t>4b45d249-5739-4bf7-9595-a4715b73c2f6-EXA</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and</t>
+          <t>Border regions Peer exchange on solving border obstacles</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr"/>
@@ -53028,12 +53881,12 @@
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>886623263</t>
+          <t>8ab2c92d-4494-4837-ba85-77de9b0cc7f3-EXA</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Pécs Urban Development Company</t>
+          <t>Develop the EU Adriatic-Ionian macro-regional strategy’s and</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr"/>
@@ -53060,12 +53913,12 @@
     <row r="103" ht="28" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>877314852</t>
+          <t>886623263</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>ESPRIT EDUCATIF</t>
+          <t>Pécs Urban Development Company</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr"/>
@@ -53092,12 +53945,12 @@
     <row r="104" ht="28" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>900546740</t>
+          <t>877314852</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Department of International Cooperation and European Integra</t>
+          <t>ESPRIT EDUCATIF</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr"/>
@@ -53124,12 +53977,12 @@
     <row r="105" ht="28" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>884174595</t>
+          <t>900546740</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Basse-Meuse développement</t>
+          <t>Department of International Cooperation and European Integra</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr"/>
@@ -53156,12 +54009,12 @@
     <row r="106" ht="28" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>941945952</t>
+          <t>884174595</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>JADRANSKO JONSKA EUROEGIJA</t>
+          <t>Basse-Meuse développement</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr"/>
@@ -53188,12 +54041,12 @@
     <row r="107" ht="28" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
+          <t>941945952</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160A</t>
+          <t>JADRANSKO JONSKA EUROEGIJA</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr"/>
@@ -53220,12 +54073,12 @@
     <row r="108" ht="28" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>ERDFTA</t>
+          <t>91a18e6a-ad92-4d0e-a3a6-5f0b34f67061-EXA</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Interreg Vrijwilligersjongeren (IVY)</t>
+          <t>Thematic Monographs on Cross Border Cooperation - 2026CE160A</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr"/>
@@ -53252,12 +54105,12 @@
     <row r="109" ht="28" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>ERDFTA</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>For the purposes of the case studies, would DG REGIO wish to</t>
+          <t>Interreg Vrijwilligersjongeren (IVY)</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr"/>
@@ -53284,12 +54137,12 @@
     <row r="110" ht="28" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>90488</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries conside</t>
+          <t>For the purposes of the case studies, would DG REGIO wish to</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr"/>
@@ -53316,12 +54169,12 @@
     <row r="111" ht="28" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy pr</t>
+          <t>Under topic HORIZON-CL5-2022-D5-01-02, are batteries conside</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr"/>
@@ -53348,12 +54201,12 @@
     <row r="112" ht="28" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>njaunzdz</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Mr. Dzintars Jaunzems</t>
+          <t>A project intends to build an innovative renewable energy pr</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr"/>
@@ -53380,12 +54233,12 @@
     <row r="113" ht="28" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>n00brugy</t>
+          <t>njaunzdz</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Joana SANTIAGO</t>
+          <t>Mr. Dzintars Jaunzems</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr"/>
@@ -53412,12 +54265,12 @@
     <row r="114" ht="28" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>n00kmonh</t>
+          <t>n00brugy</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Mrs LARA MARIA CERDAN AZNAR</t>
+          <t>Joana SANTIAGO</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr"/>
@@ -53444,12 +54297,12 @@
     <row r="115" ht="28" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>937468917</t>
+          <t>n00kmonh</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUT</t>
+          <t>Mrs LARA MARIA CERDAN AZNAR</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr"/>
@@ -53476,12 +54329,12 @@
     <row r="116" ht="28" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>937468917</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under L</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUT</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr"/>
@@ -53540,12 +54393,12 @@
     <row r="118" ht="28" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third count</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under L</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr"/>
@@ -53572,12 +54425,12 @@
     <row r="119" ht="28" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>885233544</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third count</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr"/>
@@ -53604,12 +54457,12 @@
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>885233544</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, w</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr"/>
@@ -53636,12 +54489,12 @@
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMAR</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, w</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr"/>
@@ -53668,12 +54521,12 @@
     <row r="122" ht="28" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMAR</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr"/>
@@ -53700,12 +54553,12 @@
     <row r="123" ht="28" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cool</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr"/>
@@ -53732,12 +54585,12 @@
     <row r="124" ht="28" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a propo</t>
+          <t>Strategies and tools for decarbonising EU's heating and cool</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr"/>
@@ -53764,12 +54617,12 @@
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a propo</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr"/>
@@ -53796,12 +54649,12 @@
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is the</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr"/>
@@ -53828,12 +54681,12 @@
     <row r="127" ht="28" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>956926438</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is the</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr"/>
@@ -53860,12 +54713,12 @@
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>953677035</t>
+          <t>956926438</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr"/>
@@ -53892,12 +54745,12 @@
     <row r="129" ht="28" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>953552487</t>
+          <t>953677035</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr"/>
@@ -53924,12 +54777,12 @@
     <row r="130" ht="28" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>953552487</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-20</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr"/>
@@ -53956,12 +54809,12 @@
     <row r="131" ht="28" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>95140</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>1. Should combustible industrial residues, like syngases, re</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-20</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr"/>
@@ -53988,12 +54841,12 @@
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>95140</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>1. Should combustible industrial residues, like syngases, re</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr"/>
@@ -54052,12 +54905,12 @@
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>876983694</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr"/>
@@ -54084,12 +54937,12 @@
     <row r="135" ht="28" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>876983694</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr"/>
@@ -54116,12 +54969,12 @@
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>935134321</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS S</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr"/>
@@ -54148,12 +55001,12 @@
     <row r="137" ht="28" customHeight="1">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>883154834</t>
+          <t>935134321</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS S</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr"/>
@@ -54180,12 +55033,12 @@
     <row r="138" ht="28" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>883154834</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Could the Contracting Authority clarify the scope of the </t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr"/>
@@ -54212,12 +55065,12 @@
     <row r="139" ht="28" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>950910110</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>CURA TERRAE WATER LIMITED</t>
+          <t xml:space="preserve">1. Could the Contracting Authority clarify the scope of the </t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr"/>
@@ -54244,12 +55097,12 @@
     <row r="140" ht="28" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>954037778</t>
+          <t>950910110</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>VEOLIA EAU - COMPAGNIE GENERALE DES EAUX</t>
+          <t>CURA TERRAE WATER LIMITED</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr"/>
@@ -55396,7 +56249,7 @@
     <row r="176" ht="28" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>EUS-63611</t>
+          <t>EUS-43735</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
@@ -55432,7 +56285,7 @@
     <row r="177" ht="28" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>EUS-46816</t>
+          <t>EUS-23831</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
@@ -55468,12 +56321,12 @@
     <row r="178" ht="28" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>EUS-59501</t>
+          <t>EUS-89429</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Reparación deficiencias eléctricas en Pabellón</t>
+          <t>Licitación, mediante procedimiento negociado sin publicidad,</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
@@ -55504,7 +56357,7 @@
     <row r="179" ht="28" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>EUS-73899</t>
+          <t>EUS-69995</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
@@ -55540,7 +56393,7 @@
     <row r="180" ht="28" customHeight="1">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>EUS-72308</t>
+          <t>EUS-59844</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
@@ -55576,12 +56429,12 @@
     <row r="181" ht="28" customHeight="1">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>EUS-37473</t>
+          <t>EUS-33760</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renovación licencias Teslab, infraestructura docente Joseba </t>
+          <t>Aprobar la contratación de los trabajos de "Integración de l</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -55612,12 +56465,12 @@
     <row r="182" ht="28" customHeight="1">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>EUS-31002</t>
+          <t>EUS-93831</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Mantenimiento preventivo de la cámara climática del Departam</t>
+          <t>Contratación del servicio de asistencia técnica y gestión de</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
@@ -55648,12 +56501,12 @@
     <row r="183" ht="28" customHeight="1">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>EUS-50049</t>
+          <t>EUS-16126</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>Reparación de fuga de gas y sustitución de válvula de la cám</t>
+          <t>Obras del proyecto de construcción de itinerario peatonal pa</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -55681,8 +56534,116 @@
       <c r="I183" s="6" t="inlineStr"/>
       <c r="J183" s="6" t="inlineStr"/>
     </row>
+    <row r="184" ht="28" customHeight="1">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>EUS-08987</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>reparación y puesta en servicio de red de fecales y pluviale</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="inlineStr"/>
+      <c r="F184" s="25" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr"/>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>Por revisar</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="inlineStr"/>
+      <c r="J184" s="6" t="inlineStr"/>
+    </row>
+    <row r="185" ht="28" customHeight="1">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>EUS-71383</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación de un portón industrial enrollable </t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr"/>
+      <c r="F185" s="25" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr"/>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>Por revisar</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr"/>
+      <c r="J185" s="6" t="inlineStr"/>
+    </row>
+    <row r="186" ht="28" customHeight="1">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>EUS-06475</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>ANS para determinadas aplicaciones implementadas por Izfe pa</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr"/>
+      <c r="F186" s="25" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>Por revisar</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="inlineStr"/>
+      <c r="J186" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J183"/>
+  <autoFilter ref="A1:J186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/resultados_convocatorias.xlsx
+++ b/docs/resultados_convocatorias.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Recursos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$191</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M191"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -685,7 +685,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 05/10/2026 12:49 - 185 convocatorias - 11 nuevas</t>
+          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 06/10/2026 12:18 - 184 convocatorias - 10 nuevas</t>
         </is>
       </c>
     </row>
@@ -3341,19 +3341,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr"/>
       <c r="E60" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -3374,7 +3370,7 @@
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr"/>
@@ -3392,15 +3388,19 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr"/>
@@ -4007,12 +4007,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr"/>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr"/>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4101,12 +4101,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr"/>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr"/>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -6968,12 +6968,12 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr"/>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7015,12 +7015,12 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>EUS-43735</t>
+          <t>EUS-47596</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>EUS-23831</t>
+          <t>EUS-51067</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>EUS-89429</t>
+          <t>EUS-92303</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>Licitación, mediante procedimiento negociado sin publicidad, para la contratación de servicios de creación y edición de obra literaria y su divulgación para la Asociación BC3 Basque Centre for Climate</t>
+          <t>Servicio de retirada, transporte y gestión de los residuos Sandach de la cámara frigorífica situada en el Garbigune de Eibar</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>EUS-69995</t>
+          <t>EUS-86597</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
+          <t>Rehabilitacion parrales del barrio San Bartolome (zona Bizezko)</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
@@ -9183,12 +9183,12 @@
       <c r="G184" s="6" t="inlineStr"/>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
-        </is>
-      </c>
-      <c r="I184" s="11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I184" s="8" t="inlineStr">
+        <is>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J184" s="6" t="inlineStr"/>
@@ -9216,12 +9216,12 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>EUS-59844</t>
+          <t>EUS-60193</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>EUS-33760</t>
+          <t>EUS-65298</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>Aprobar la contratación de los trabajos de "Integración de levantamientos topográficos en la base topográfica urbana de Álava", como contrato menor de servicios.</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
@@ -9293,7 +9293,7 @@
       <c r="G186" s="6" t="inlineStr"/>
       <c r="H186" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="I186" s="11" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>EUS-93831</t>
+          <t>EUS-77322</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>Contratación del servicio de asistencia técnica y gestión de venta de los ahorros energéticos generados por la empresa de Transporte Urbano de Vitoria-Gasteiz (TUVISA)</t>
+          <t>Redacción del proyecto y dirección de las obras de renovación de la red de distribución de agua en distintas zonas del centro de Irun</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>EUS-16126</t>
+          <t>EUS-36090</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>Obras del proyecto de construcción de itinerario peatonal paralelo a la calzada entre los PK 1,810 y 2,030 de la  GI-3131 a Goroeta en Aretxabaleta (14-SV-79/2025 2LIC)</t>
+          <t>Obras de rehabilitación del edificio del Emisario submarino de Monpas</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>EUS-08987</t>
+          <t>EUS-09001</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>reparación y puesta en servicio de red de fecales y pluviales en el centro CEIP Cantarrana Eskola HLHI</t>
+          <t>Servicio para la elaboración de un estudio medioambiental de la zona costera de Mompás y del estuario del río Oiartzun</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>EUS-71383</t>
+          <t>EUS-57679</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>Suministro e instalación de un portón industrial enrollable para el edificio AIC Ermua</t>
+          <t>Plan de comunicacion y Sistema de Portavocias de la Agencia Vasca del Agua</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
@@ -9538,63 +9538,8 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="40" customHeight="1">
-      <c r="A191" s="14" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="B191" s="6" t="inlineStr">
-        <is>
-          <t>EUS-06475</t>
-        </is>
-      </c>
-      <c r="C191" s="6" t="inlineStr">
-        <is>
-          <t>ANS para determinadas aplicaciones implementadas por Izfe para el Departamento de Equilibrio Territorial Verde de la GFA-DFG para la gestión de la identificación, registro, saneamiento y movimiento an</t>
-        </is>
-      </c>
-      <c r="D191" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="E191" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F191" s="6" t="inlineStr"/>
-      <c r="G191" s="6" t="inlineStr"/>
-      <c r="H191" s="6" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="I191" s="11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="J191" s="6" t="inlineStr"/>
-      <c r="K191" s="6" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="L191" s="15" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="M191" s="9" t="inlineStr">
-        <is>
-          <t>Ver</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:M191"/>
+  <autoFilter ref="A4:M190"/>
   <mergeCells count="4">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A180:M180"/>
@@ -9786,7 +9731,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9798,7 +9742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2774"/>
+  <dimension ref="A1:F2759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20912,7 +20856,7 @@
     <row r="811" ht="30" customHeight="1">
       <c r="A811" s="16" t="inlineStr">
         <is>
-          <t>FICHA 55: HORIZON</t>
+          <t>FICHA 55: ERASMUS2027</t>
         </is>
       </c>
       <c r="B811" s="17" t="n"/>
@@ -20945,7 +20889,7 @@
       </c>
       <c r="B813" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C813" s="20" t="n"/>
@@ -20961,7 +20905,7 @@
       </c>
       <c r="B814" s="19" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C814" s="20" t="n"/>
@@ -20975,11 +20919,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B815" s="19" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+      <c r="B815" s="19" t="inlineStr"/>
       <c r="C815" s="20" t="n"/>
       <c r="D815" s="20" t="n"/>
       <c r="E815" s="20" t="n"/>
@@ -21053,7 +20993,7 @@
       </c>
       <c r="B820" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2021-CIT-02</t>
+          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
         </is>
       </c>
       <c r="C820" s="20" t="n"/>
@@ -21069,7 +21009,7 @@
       </c>
       <c r="B821" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C821" s="20" t="n"/>
@@ -21113,7 +21053,7 @@
       </c>
       <c r="B824" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
         </is>
       </c>
       <c r="C824" s="20" t="n"/>
@@ -21124,7 +21064,7 @@
     <row r="826" ht="30" customHeight="1">
       <c r="A826" s="16" t="inlineStr">
         <is>
-          <t>FICHA 56: ERASMUS2027</t>
+          <t>FICHA 56: HORIZON</t>
         </is>
       </c>
       <c r="B826" s="17" t="n"/>
@@ -21157,7 +21097,7 @@
       </c>
       <c r="B828" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C828" s="20" t="n"/>
@@ -21173,7 +21113,7 @@
       </c>
       <c r="B829" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C829" s="20" t="n"/>
@@ -21187,7 +21127,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B830" s="19" t="inlineStr"/>
+      <c r="B830" s="19" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="C830" s="20" t="n"/>
       <c r="D830" s="20" t="n"/>
       <c r="E830" s="20" t="n"/>
@@ -21261,7 +21205,7 @@
       </c>
       <c r="B835" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
+          <t>HORIZON-MISS-2021-CIT-02</t>
         </is>
       </c>
       <c r="C835" s="20" t="n"/>
@@ -21277,7 +21221,7 @@
       </c>
       <c r="B836" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C836" s="20" t="n"/>
@@ -21321,7 +21265,7 @@
       </c>
       <c r="B839" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
         </is>
       </c>
       <c r="C839" s="20" t="n"/>
@@ -23796,7 +23740,7 @@
     <row r="1021" ht="30" customHeight="1">
       <c r="A1021" s="16" t="inlineStr">
         <is>
-          <t>FICHA 69: 928447529</t>
+          <t>FICHA 69: 917779760</t>
         </is>
       </c>
       <c r="B1021" s="17" t="n"/>
@@ -23829,7 +23773,7 @@
       </c>
       <c r="B1023" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1023" s="20" t="n"/>
@@ -23845,7 +23789,7 @@
       </c>
       <c r="B1024" s="19" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C1024" s="20" t="n"/>
@@ -23945,7 +23889,7 @@
       </c>
       <c r="B1031" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1031" s="20" t="n"/>
@@ -23989,7 +23933,7 @@
       </c>
       <c r="B1034" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
         </is>
       </c>
       <c r="C1034" s="20" t="n"/>
@@ -24000,7 +23944,7 @@
     <row r="1036" ht="30" customHeight="1">
       <c r="A1036" s="16" t="inlineStr">
         <is>
-          <t>FICHA 70: 917671508</t>
+          <t>FICHA 70: 920115617</t>
         </is>
       </c>
       <c r="B1036" s="17" t="n"/>
@@ -24033,7 +23977,7 @@
       </c>
       <c r="B1038" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1038" s="20" t="n"/>
@@ -24049,7 +23993,7 @@
       </c>
       <c r="B1039" s="19" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C1039" s="20" t="n"/>
@@ -24149,7 +24093,7 @@
       </c>
       <c r="B1046" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1046" s="20" t="n"/>
@@ -24193,7 +24137,7 @@
       </c>
       <c r="B1049" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
         </is>
       </c>
       <c r="C1049" s="20" t="n"/>
@@ -24204,7 +24148,7 @@
     <row r="1051" ht="30" customHeight="1">
       <c r="A1051" s="16" t="inlineStr">
         <is>
-          <t>FICHA 71: 917779760</t>
+          <t>FICHA 71: 917671508</t>
         </is>
       </c>
       <c r="B1051" s="17" t="n"/>
@@ -24237,7 +24181,7 @@
       </c>
       <c r="B1053" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1053" s="20" t="n"/>
@@ -24253,7 +24197,7 @@
       </c>
       <c r="B1054" s="19" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C1054" s="20" t="n"/>
@@ -24353,7 +24297,7 @@
       </c>
       <c r="B1061" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1061" s="20" t="n"/>
@@ -24397,7 +24341,7 @@
       </c>
       <c r="B1064" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
         </is>
       </c>
       <c r="C1064" s="20" t="n"/>
@@ -24408,7 +24352,7 @@
     <row r="1066" ht="30" customHeight="1">
       <c r="A1066" s="16" t="inlineStr">
         <is>
-          <t>FICHA 72: 920115617</t>
+          <t>FICHA 72: 928447529</t>
         </is>
       </c>
       <c r="B1066" s="17" t="n"/>
@@ -24441,7 +24385,7 @@
       </c>
       <c r="B1068" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1068" s="20" t="n"/>
@@ -24457,7 +24401,7 @@
       </c>
       <c r="B1069" s="19" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C1069" s="20" t="n"/>
@@ -24557,7 +24501,7 @@
       </c>
       <c r="B1076" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1076" s="20" t="n"/>
@@ -24601,7 +24545,7 @@
       </c>
       <c r="B1079" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
         </is>
       </c>
       <c r="C1079" s="20" t="n"/>
@@ -36676,7 +36620,7 @@
     <row r="1966" ht="30" customHeight="1">
       <c r="A1966" s="16" t="inlineStr">
         <is>
-          <t>FICHA 132: 925388828</t>
+          <t>FICHA 132: 934294980</t>
         </is>
       </c>
       <c r="B1966" s="17" t="n"/>
@@ -36709,7 +36653,7 @@
       </c>
       <c r="B1968" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C1968" s="20" t="n"/>
@@ -36725,7 +36669,7 @@
       </c>
       <c r="B1969" s="19" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C1969" s="20" t="n"/>
@@ -36825,7 +36769,7 @@
       </c>
       <c r="B1976" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C1976" s="20" t="n"/>
@@ -36869,7 +36813,7 @@
       </c>
       <c r="B1979" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
         </is>
       </c>
       <c r="C1979" s="20" t="n"/>
@@ -36880,7 +36824,7 @@
     <row r="1981" ht="30" customHeight="1">
       <c r="A1981" s="16" t="inlineStr">
         <is>
-          <t>FICHA 133: 934294980</t>
+          <t>FICHA 133: 925388828</t>
         </is>
       </c>
       <c r="B1981" s="17" t="n"/>
@@ -36913,7 +36857,7 @@
       </c>
       <c r="B1983" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C1983" s="20" t="n"/>
@@ -36929,7 +36873,7 @@
       </c>
       <c r="B1984" s="19" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C1984" s="20" t="n"/>
@@ -37029,7 +36973,7 @@
       </c>
       <c r="B1991" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C1991" s="20" t="n"/>
@@ -37073,7 +37017,7 @@
       </c>
       <c r="B1994" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
         </is>
       </c>
       <c r="C1994" s="20" t="n"/>
@@ -45460,7 +45404,7 @@
     <row r="2611" ht="30" customHeight="1">
       <c r="A2611" s="16" t="inlineStr">
         <is>
-          <t>FICHA 175: EUS-43735</t>
+          <t>FICHA 175: EUS-47596</t>
         </is>
       </c>
       <c r="B2611" s="17" t="n"/>
@@ -45509,7 +45453,7 @@
       </c>
       <c r="B2614" s="19" t="inlineStr">
         <is>
-          <t>EUS-43735</t>
+          <t>EUS-47596</t>
         </is>
       </c>
       <c r="C2614" s="20" t="n"/>
@@ -45672,7 +45616,7 @@
     <row r="2626" ht="30" customHeight="1">
       <c r="A2626" s="16" t="inlineStr">
         <is>
-          <t>FICHA 176: EUS-23831</t>
+          <t>FICHA 176: EUS-51067</t>
         </is>
       </c>
       <c r="B2626" s="17" t="n"/>
@@ -45721,7 +45665,7 @@
       </c>
       <c r="B2629" s="19" t="inlineStr">
         <is>
-          <t>EUS-23831</t>
+          <t>EUS-51067</t>
         </is>
       </c>
       <c r="C2629" s="20" t="n"/>
@@ -45884,7 +45828,7 @@
     <row r="2641" ht="30" customHeight="1">
       <c r="A2641" s="16" t="inlineStr">
         <is>
-          <t>FICHA 177: EUS-89429</t>
+          <t>FICHA 177: EUS-92303</t>
         </is>
       </c>
       <c r="B2641" s="17" t="n"/>
@@ -45917,7 +45861,7 @@
       </c>
       <c r="B2643" s="19" t="inlineStr">
         <is>
-          <t>Licitación, mediante procedimiento negociado sin publicidad, para la contratación de servicios de creación y edición de obra literaria y su divulgación para la Asociación BC3 Basque Centre for Climate</t>
+          <t>Servicio de retirada, transporte y gestión de los residuos Sandach de la cámara frigorífica situada en el Garbigune de Eibar</t>
         </is>
       </c>
       <c r="C2643" s="20" t="n"/>
@@ -45933,7 +45877,7 @@
       </c>
       <c r="B2644" s="19" t="inlineStr">
         <is>
-          <t>EUS-89429</t>
+          <t>EUS-92303</t>
         </is>
       </c>
       <c r="C2644" s="20" t="n"/>
@@ -46085,7 +46029,7 @@
       </c>
       <c r="B2654" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/licitacion-mediante-procedimiento-negociado-publicidad-contratacion-servicios-creacion-y-edicion-obra-literaria-y-su-divulgacion-asociacion-bc3-basque-centre-for-climate-change-klima-aldaketa-ikergai/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-retirada-transporte-y-gestion-residuos-sandach-camara-frigorifica-situada-garbigune-eibar/expjaso743728/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2654" s="20" t="n"/>
@@ -46096,7 +46040,7 @@
     <row r="2656" ht="30" customHeight="1">
       <c r="A2656" s="16" t="inlineStr">
         <is>
-          <t>FICHA 178: EUS-69995</t>
+          <t>FICHA 178: EUS-86597</t>
         </is>
       </c>
       <c r="B2656" s="17" t="n"/>
@@ -46121,7 +46065,7 @@
       <c r="E2657" s="20" t="n"/>
       <c r="F2657" s="20" t="n"/>
     </row>
-    <row r="2658" ht="45" customHeight="1">
+    <row r="2658" ht="20" customHeight="1">
       <c r="A2658" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -46129,7 +46073,7 @@
       </c>
       <c r="B2658" s="19" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
+          <t>Rehabilitacion parrales del barrio San Bartolome (zona Bizezko)</t>
         </is>
       </c>
       <c r="C2658" s="20" t="n"/>
@@ -46145,7 +46089,7 @@
       </c>
       <c r="B2659" s="19" t="inlineStr">
         <is>
-          <t>EUS-69995</t>
+          <t>EUS-86597</t>
         </is>
       </c>
       <c r="C2659" s="20" t="n"/>
@@ -46221,7 +46165,7 @@
       </c>
       <c r="B2664" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2664" s="20" t="n"/>
@@ -46279,9 +46223,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2668" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
+      <c r="B2668" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTA — </t>
         </is>
       </c>
       <c r="C2668" s="20" t="n"/>
@@ -46297,7 +46241,7 @@
       </c>
       <c r="B2669" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/bioaniztasunfundaziohirin/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/rehabilitacion-parrales-del-barrio-san-bartolome-zona-bizezko/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2669" s="20" t="n"/>
@@ -46308,7 +46252,7 @@
     <row r="2671" ht="30" customHeight="1">
       <c r="A2671" s="16" t="inlineStr">
         <is>
-          <t>FICHA 179: EUS-59844</t>
+          <t>FICHA 179: EUS-60193</t>
         </is>
       </c>
       <c r="B2671" s="17" t="n"/>
@@ -46333,7 +46277,7 @@
       <c r="E2672" s="20" t="n"/>
       <c r="F2672" s="20" t="n"/>
     </row>
-    <row r="2673" ht="20" customHeight="1">
+    <row r="2673" ht="45" customHeight="1">
       <c r="A2673" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -46341,7 +46285,7 @@
       </c>
       <c r="B2673" s="19" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
         </is>
       </c>
       <c r="C2673" s="20" t="n"/>
@@ -46357,7 +46301,7 @@
       </c>
       <c r="B2674" s="19" t="inlineStr">
         <is>
-          <t>EUS-59844</t>
+          <t>EUS-60193</t>
         </is>
       </c>
       <c r="C2674" s="20" t="n"/>
@@ -46509,7 +46453,7 @@
       </c>
       <c r="B2684" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/comunicacion-previs-digitalizacion-2027/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/bioaniztasunfundaziohirin/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2684" s="20" t="n"/>
@@ -46520,7 +46464,7 @@
     <row r="2686" ht="30" customHeight="1">
       <c r="A2686" s="16" t="inlineStr">
         <is>
-          <t>FICHA 180: EUS-33760</t>
+          <t>FICHA 180: EUS-65298</t>
         </is>
       </c>
       <c r="B2686" s="17" t="n"/>
@@ -46545,7 +46489,7 @@
       <c r="E2687" s="20" t="n"/>
       <c r="F2687" s="20" t="n"/>
     </row>
-    <row r="2688" ht="45" customHeight="1">
+    <row r="2688" ht="20" customHeight="1">
       <c r="A2688" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -46553,7 +46497,7 @@
       </c>
       <c r="B2688" s="19" t="inlineStr">
         <is>
-          <t>Aprobar la contratación de los trabajos de "Integración de levantamientos topográficos en la base topográfica urbana de Álava", como contrato menor de servicios.</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="C2688" s="20" t="n"/>
@@ -46569,7 +46513,7 @@
       </c>
       <c r="B2689" s="19" t="inlineStr">
         <is>
-          <t>EUS-33760</t>
+          <t>EUS-65298</t>
         </is>
       </c>
       <c r="C2689" s="20" t="n"/>
@@ -46645,7 +46589,7 @@
       </c>
       <c r="B2694" s="19" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="C2694" s="20" t="n"/>
@@ -46721,7 +46665,7 @@
       </c>
       <c r="B2699" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/aprobar-contratacion-trabajos-integracion-levantamientos-topograficos-base-topografica-urbana-alava-como-contrato-menor-servicios/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/comunicacion-previs-digitalizacion-2027/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2699" s="20" t="n"/>
@@ -46732,7 +46676,7 @@
     <row r="2701" ht="30" customHeight="1">
       <c r="A2701" s="16" t="inlineStr">
         <is>
-          <t>FICHA 181: EUS-93831</t>
+          <t>FICHA 181: EUS-77322</t>
         </is>
       </c>
       <c r="B2701" s="17" t="n"/>
@@ -46765,7 +46709,7 @@
       </c>
       <c r="B2703" s="19" t="inlineStr">
         <is>
-          <t>Contratación del servicio de asistencia técnica y gestión de venta de los ahorros energéticos generados por la empresa de Transporte Urbano de Vitoria-Gasteiz (TUVISA)</t>
+          <t>Redacción del proyecto y dirección de las obras de renovación de la red de distribución de agua en distintas zonas del centro de Irun</t>
         </is>
       </c>
       <c r="C2703" s="20" t="n"/>
@@ -46781,7 +46725,7 @@
       </c>
       <c r="B2704" s="19" t="inlineStr">
         <is>
-          <t>EUS-93831</t>
+          <t>EUS-77322</t>
         </is>
       </c>
       <c r="C2704" s="20" t="n"/>
@@ -46933,7 +46877,7 @@
       </c>
       <c r="B2714" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/contratacion-del-servicio-asistencia-tecnica-y-gestion-venta-ahorros-energeticos-generados-empresa-transporte-urbano-vitoria-gasteiz-tuvisa/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/redaccion-del-proyecto-y-direccion-obras-renovacion-red-distribucion-agua-distintas-zonas-del-centro-irun/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2714" s="20" t="n"/>
@@ -46944,7 +46888,7 @@
     <row r="2716" ht="30" customHeight="1">
       <c r="A2716" s="16" t="inlineStr">
         <is>
-          <t>FICHA 182: EUS-16126</t>
+          <t>FICHA 182: EUS-36090</t>
         </is>
       </c>
       <c r="B2716" s="17" t="n"/>
@@ -46969,7 +46913,7 @@
       <c r="E2717" s="20" t="n"/>
       <c r="F2717" s="20" t="n"/>
     </row>
-    <row r="2718" ht="45" customHeight="1">
+    <row r="2718" ht="20" customHeight="1">
       <c r="A2718" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -46977,7 +46921,7 @@
       </c>
       <c r="B2718" s="19" t="inlineStr">
         <is>
-          <t>Obras del proyecto de construcción de itinerario peatonal paralelo a la calzada entre los PK 1,810 y 2,030 de la  GI-3131 a Goroeta en Aretxabaleta (14-SV-79/2025 2LIC)</t>
+          <t>Obras de rehabilitación del edificio del Emisario submarino de Monpas</t>
         </is>
       </c>
       <c r="C2718" s="20" t="n"/>
@@ -46993,7 +46937,7 @@
       </c>
       <c r="B2719" s="19" t="inlineStr">
         <is>
-          <t>EUS-16126</t>
+          <t>EUS-36090</t>
         </is>
       </c>
       <c r="C2719" s="20" t="n"/>
@@ -47145,7 +47089,7 @@
       </c>
       <c r="B2729" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/obras-del-proyecto-construccion-itinerario-peatonal-paralelo-calzada-pk-1-810-y-2-030-gi-3131-goroeta-aretxabaleta-14-sv-79-2025-2lic/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/obras-rehabilitacion-del-edificio-del-emisario-submarino-monpas/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2729" s="20" t="n"/>
@@ -47156,7 +47100,7 @@
     <row r="2731" ht="30" customHeight="1">
       <c r="A2731" s="16" t="inlineStr">
         <is>
-          <t>FICHA 183: EUS-08987</t>
+          <t>FICHA 183: EUS-09001</t>
         </is>
       </c>
       <c r="B2731" s="17" t="n"/>
@@ -47189,7 +47133,7 @@
       </c>
       <c r="B2733" s="19" t="inlineStr">
         <is>
-          <t>reparación y puesta en servicio de red de fecales y pluviales en el centro CEIP Cantarrana Eskola HLHI</t>
+          <t>Servicio para la elaboración de un estudio medioambiental de la zona costera de Mompás y del estuario del río Oiartzun</t>
         </is>
       </c>
       <c r="C2733" s="20" t="n"/>
@@ -47205,7 +47149,7 @@
       </c>
       <c r="B2734" s="19" t="inlineStr">
         <is>
-          <t>EUS-08987</t>
+          <t>EUS-09001</t>
         </is>
       </c>
       <c r="C2734" s="20" t="n"/>
@@ -47357,7 +47301,7 @@
       </c>
       <c r="B2744" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/reparacion-y-puesta-servicio-red-fecales-y-pluviales-centro-ceip-cantarrana-eskola-hlhi/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-elaboracion-estudio-medioambiental-zona-costera-mompas-y-del-estuario-del-rio-oiartzun/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2744" s="20" t="n"/>
@@ -47368,7 +47312,7 @@
     <row r="2746" ht="30" customHeight="1">
       <c r="A2746" s="16" t="inlineStr">
         <is>
-          <t>FICHA 184: EUS-71383</t>
+          <t>FICHA 184: EUS-57679</t>
         </is>
       </c>
       <c r="B2746" s="17" t="n"/>
@@ -47393,7 +47337,7 @@
       <c r="E2747" s="20" t="n"/>
       <c r="F2747" s="20" t="n"/>
     </row>
-    <row r="2748" ht="45" customHeight="1">
+    <row r="2748" ht="20" customHeight="1">
       <c r="A2748" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -47401,7 +47345,7 @@
       </c>
       <c r="B2748" s="19" t="inlineStr">
         <is>
-          <t>Suministro e instalación de un portón industrial enrollable para el edificio AIC Ermua</t>
+          <t>Plan de comunicacion y Sistema de Portavocias de la Agencia Vasca del Agua</t>
         </is>
       </c>
       <c r="C2748" s="20" t="n"/>
@@ -47417,7 +47361,7 @@
       </c>
       <c r="B2749" s="19" t="inlineStr">
         <is>
-          <t>EUS-71383</t>
+          <t>EUS-57679</t>
         </is>
       </c>
       <c r="C2749" s="20" t="n"/>
@@ -47569,7 +47513,7 @@
       </c>
       <c r="B2759" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-e-instalacion-porton-industrial-enrollable-edificio-aic-ermua/expjaso747486/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/plan-comunicacion-y-sistema-portavocias-agencia-vasca-del-agua/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2759" s="20" t="n"/>
@@ -47577,220 +47521,8 @@
       <c r="E2759" s="20" t="n"/>
       <c r="F2759" s="20" t="n"/>
     </row>
-    <row r="2761" ht="30" customHeight="1">
-      <c r="A2761" s="16" t="inlineStr">
-        <is>
-          <t>FICHA 185: EUS-06475</t>
-        </is>
-      </c>
-      <c r="B2761" s="17" t="n"/>
-      <c r="C2761" s="17" t="n"/>
-      <c r="D2761" s="17" t="n"/>
-      <c r="E2761" s="17" t="n"/>
-      <c r="F2761" s="17" t="n"/>
-    </row>
-    <row r="2762" ht="20" customHeight="1">
-      <c r="A2762" s="18" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B2762" s="19" t="inlineStr">
-        <is>
-          <t>🟢 Euskadi</t>
-        </is>
-      </c>
-      <c r="C2762" s="20" t="n"/>
-      <c r="D2762" s="20" t="n"/>
-      <c r="E2762" s="20" t="n"/>
-      <c r="F2762" s="20" t="n"/>
-    </row>
-    <row r="2763" ht="45" customHeight="1">
-      <c r="A2763" s="18" t="inlineStr">
-        <is>
-          <t>Titulo</t>
-        </is>
-      </c>
-      <c r="B2763" s="19" t="inlineStr">
-        <is>
-          <t>ANS para determinadas aplicaciones implementadas por Izfe para el Departamento de Equilibrio Territorial Verde de la GFA-DFG para la gestión de la identificación, registro, saneamiento y movimiento an</t>
-        </is>
-      </c>
-      <c r="C2763" s="20" t="n"/>
-      <c r="D2763" s="20" t="n"/>
-      <c r="E2763" s="20" t="n"/>
-      <c r="F2763" s="20" t="n"/>
-    </row>
-    <row r="2764" ht="20" customHeight="1">
-      <c r="A2764" s="18" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2764" s="19" t="inlineStr">
-        <is>
-          <t>EUS-06475</t>
-        </is>
-      </c>
-      <c r="C2764" s="20" t="n"/>
-      <c r="D2764" s="20" t="n"/>
-      <c r="E2764" s="20" t="n"/>
-      <c r="F2764" s="20" t="n"/>
-    </row>
-    <row r="2765" ht="20" customHeight="1">
-      <c r="A2765" s="18" t="inlineStr">
-        <is>
-          <t>Programa</t>
-        </is>
-      </c>
-      <c r="B2765" s="19" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="C2765" s="20" t="n"/>
-      <c r="D2765" s="20" t="n"/>
-      <c r="E2765" s="20" t="n"/>
-      <c r="F2765" s="20" t="n"/>
-    </row>
-    <row r="2766" ht="20" customHeight="1">
-      <c r="A2766" s="18" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B2766" s="19" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C2766" s="20" t="n"/>
-      <c r="D2766" s="20" t="n"/>
-      <c r="E2766" s="20" t="n"/>
-      <c r="F2766" s="20" t="n"/>
-    </row>
-    <row r="2767" ht="20" customHeight="1">
-      <c r="A2767" s="18" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="B2767" s="19" t="inlineStr"/>
-      <c r="C2767" s="20" t="n"/>
-      <c r="D2767" s="20" t="n"/>
-      <c r="E2767" s="20" t="n"/>
-      <c r="F2767" s="20" t="n"/>
-    </row>
-    <row r="2768" ht="20" customHeight="1">
-      <c r="A2768" s="18" t="inlineStr">
-        <is>
-          <t>Presupuesto (EUR)</t>
-        </is>
-      </c>
-      <c r="B2768" s="19" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="C2768" s="20" t="n"/>
-      <c r="D2768" s="20" t="n"/>
-      <c r="E2768" s="20" t="n"/>
-      <c r="F2768" s="20" t="n"/>
-    </row>
-    <row r="2769" ht="20" customHeight="1">
-      <c r="A2769" s="18" t="inlineStr">
-        <is>
-          <t>Tipo de Accion</t>
-        </is>
-      </c>
-      <c r="B2769" s="19" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="C2769" s="20" t="n"/>
-      <c r="D2769" s="20" t="n"/>
-      <c r="E2769" s="20" t="n"/>
-      <c r="F2769" s="20" t="n"/>
-    </row>
-    <row r="2770" ht="20" customHeight="1">
-      <c r="A2770" s="18" t="inlineStr">
-        <is>
-          <t>Call ID</t>
-        </is>
-      </c>
-      <c r="B2770" s="19" t="inlineStr"/>
-      <c r="C2770" s="20" t="n"/>
-      <c r="D2770" s="20" t="n"/>
-      <c r="E2770" s="20" t="n"/>
-      <c r="F2770" s="20" t="n"/>
-    </row>
-    <row r="2771" ht="20" customHeight="1">
-      <c r="A2771" s="18" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="B2771" s="19" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="C2771" s="20" t="n"/>
-      <c r="D2771" s="20" t="n"/>
-      <c r="E2771" s="20" t="n"/>
-      <c r="F2771" s="20" t="n"/>
-    </row>
-    <row r="2772" ht="20" customHeight="1">
-      <c r="A2772" s="18" t="inlineStr">
-        <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="B2772" s="19" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C2772" s="20" t="n"/>
-      <c r="D2772" s="20" t="n"/>
-      <c r="E2772" s="20" t="n"/>
-      <c r="F2772" s="20" t="n"/>
-    </row>
-    <row r="2773" ht="20" customHeight="1">
-      <c r="A2773" s="18" t="inlineStr">
-        <is>
-          <t>Relevancia Bilbao</t>
-        </is>
-      </c>
-      <c r="B2773" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
-        </is>
-      </c>
-      <c r="C2773" s="20" t="n"/>
-      <c r="D2773" s="20" t="n"/>
-      <c r="E2773" s="20" t="n"/>
-      <c r="F2773" s="20" t="n"/>
-    </row>
-    <row r="2774" ht="45" customHeight="1">
-      <c r="A2774" s="18" t="inlineStr">
-        <is>
-          <t>Enlace al portal</t>
-        </is>
-      </c>
-      <c r="B2774" s="22" t="inlineStr">
-        <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/ans-determinadas-aplicaciones-implementadas-izfe-departamento-equilibrio-territorial-verde-gfa-dfg-gestion-identificacion-registro-saneamiento-y-movimiento-animal/expjaso739026/web01-tramite/es/</t>
-        </is>
-      </c>
-      <c r="C2774" s="20" t="n"/>
-      <c r="D2774" s="20" t="n"/>
-      <c r="E2774" s="20" t="n"/>
-      <c r="F2774" s="20" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="2590">
+  <mergeCells count="2576">
     <mergeCell ref="B679:F679"/>
     <mergeCell ref="B2192:F2192"/>
     <mergeCell ref="B1765:F1765"/>
@@ -47892,7 +47624,6 @@
     <mergeCell ref="B243:F243"/>
     <mergeCell ref="B2465:F2465"/>
     <mergeCell ref="B2150:F2150"/>
-    <mergeCell ref="B2763:F2763"/>
     <mergeCell ref="B678:F678"/>
     <mergeCell ref="B363:F363"/>
     <mergeCell ref="B1731:F1731"/>
@@ -48029,7 +47760,6 @@
     <mergeCell ref="B1626:F1626"/>
     <mergeCell ref="B1582:F1582"/>
     <mergeCell ref="B1924:F1924"/>
-    <mergeCell ref="B2772:F2772"/>
     <mergeCell ref="B863:F863"/>
     <mergeCell ref="B2231:F2231"/>
     <mergeCell ref="B857:F857"/>
@@ -48211,7 +47941,6 @@
     <mergeCell ref="B2007:F2007"/>
     <mergeCell ref="B2436:F2436"/>
     <mergeCell ref="A1276:F1276"/>
-    <mergeCell ref="B2770:F2770"/>
     <mergeCell ref="B2307:F2307"/>
     <mergeCell ref="B2736:F2736"/>
     <mergeCell ref="B36:F36"/>
@@ -48590,13 +48319,11 @@
     <mergeCell ref="B1596:F1596"/>
     <mergeCell ref="B1281:F1281"/>
     <mergeCell ref="B1579:F1579"/>
-    <mergeCell ref="B2769:F2769"/>
     <mergeCell ref="B1589:F1589"/>
     <mergeCell ref="B2342:F2342"/>
     <mergeCell ref="B1283:F1283"/>
     <mergeCell ref="B257:F257"/>
     <mergeCell ref="B2464:F2464"/>
-    <mergeCell ref="B2771:F2771"/>
     <mergeCell ref="B1124:F1124"/>
     <mergeCell ref="B1162:F1162"/>
     <mergeCell ref="B92:F92"/>
@@ -48604,7 +48331,6 @@
     <mergeCell ref="B2675:F2675"/>
     <mergeCell ref="B1282:F1282"/>
     <mergeCell ref="B2335:F2335"/>
-    <mergeCell ref="B2764:F2764"/>
     <mergeCell ref="B557:F557"/>
     <mergeCell ref="B2248:F2248"/>
     <mergeCell ref="B2223:F2223"/>
@@ -48776,7 +48502,6 @@
     <mergeCell ref="B2433:F2433"/>
     <mergeCell ref="B1401:F1401"/>
     <mergeCell ref="B2427:F2427"/>
-    <mergeCell ref="B2767:F2767"/>
     <mergeCell ref="B2006:F2006"/>
     <mergeCell ref="B2304:F2304"/>
     <mergeCell ref="B219:F219"/>
@@ -48785,7 +48510,6 @@
     <mergeCell ref="B2733:F2733"/>
     <mergeCell ref="B1701:F1701"/>
     <mergeCell ref="B760:F760"/>
-    <mergeCell ref="B2762:F2762"/>
     <mergeCell ref="B1119:F1119"/>
     <mergeCell ref="A2026:F2026"/>
     <mergeCell ref="B333:F333"/>
@@ -48939,7 +48663,6 @@
     <mergeCell ref="B1438:F1438"/>
     <mergeCell ref="B683:F683"/>
     <mergeCell ref="B1742:F1742"/>
-    <mergeCell ref="B2768:F2768"/>
     <mergeCell ref="B1527:F1527"/>
     <mergeCell ref="B2043:F2043"/>
     <mergeCell ref="A1036:F1036"/>
@@ -49005,7 +48728,6 @@
     <mergeCell ref="B1624:F1624"/>
     <mergeCell ref="B2110:F2110"/>
     <mergeCell ref="A991:F991"/>
-    <mergeCell ref="A2761:F2761"/>
     <mergeCell ref="A676:F676"/>
     <mergeCell ref="B137:F137"/>
     <mergeCell ref="B2283:F2283"/>
@@ -49520,7 +49242,6 @@
     <mergeCell ref="B377:F377"/>
     <mergeCell ref="B2620:F2620"/>
     <mergeCell ref="B1277:F1277"/>
-    <mergeCell ref="B2765:F2765"/>
     <mergeCell ref="B2249:F2249"/>
     <mergeCell ref="B2547:F2547"/>
     <mergeCell ref="B850:F850"/>
@@ -49885,7 +49606,6 @@
     <mergeCell ref="B2337:F2337"/>
     <mergeCell ref="B252:F252"/>
     <mergeCell ref="B2495:F2495"/>
-    <mergeCell ref="B2766:F2766"/>
     <mergeCell ref="B2451:F2451"/>
     <mergeCell ref="B366:F366"/>
     <mergeCell ref="B979:F979"/>
@@ -50120,7 +49840,6 @@
     <mergeCell ref="B835:F835"/>
     <mergeCell ref="B829:F829"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B2774:F2774"/>
     <mergeCell ref="B1127:F1127"/>
     <mergeCell ref="B68:F68"/>
     <mergeCell ref="B372:F372"/>
@@ -50269,7 +49988,6 @@
     <mergeCell ref="B872:F872"/>
     <mergeCell ref="B866:F866"/>
     <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B2773:F2773"/>
     <mergeCell ref="B1301:F1301"/>
     <mergeCell ref="B986:F986"/>
     <mergeCell ref="B1024:F1024"/>
@@ -50567,7 +50285,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2729" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2744" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2759" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2774" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50579,7 +50296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J186"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -52401,19 +52118,15 @@
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Circular design for bio-based innovation towards climate-neu</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr"/>
       <c r="D56" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -52437,15 +52150,19 @@
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neu</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -52857,12 +52574,12 @@
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr"/>
@@ -52889,12 +52606,12 @@
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr"/>
@@ -52921,12 +52638,12 @@
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr"/>
@@ -52953,12 +52670,12 @@
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr"/>
@@ -54873,12 +54590,12 @@
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr"/>
@@ -54905,12 +54622,12 @@
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr"/>
@@ -56249,7 +55966,7 @@
     <row r="176" ht="28" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>EUS-43735</t>
+          <t>EUS-47596</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
@@ -56285,7 +56002,7 @@
     <row r="177" ht="28" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>EUS-23831</t>
+          <t>EUS-51067</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
@@ -56321,12 +56038,12 @@
     <row r="178" ht="28" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>EUS-89429</t>
+          <t>EUS-92303</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Licitación, mediante procedimiento negociado sin publicidad,</t>
+          <t>Servicio de retirada, transporte y gestión de los residuos S</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
@@ -56357,12 +56074,12 @@
     <row r="179" ht="28" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>EUS-69995</t>
+          <t>EUS-86597</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Euro</t>
+          <t>Rehabilitacion parrales del barrio San Bartolome (zona Bizez</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -56378,7 +56095,7 @@
       <c r="E179" s="6" t="inlineStr"/>
       <c r="F179" s="25" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="G179" s="6" t="inlineStr"/>
@@ -56393,12 +56110,12 @@
     <row r="180" ht="28" customHeight="1">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>EUS-59844</t>
+          <t>EUS-60193</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Euro</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
@@ -56429,12 +56146,12 @@
     <row r="181" ht="28" customHeight="1">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>EUS-33760</t>
+          <t>EUS-65298</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>Aprobar la contratación de los trabajos de "Integración de l</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -56465,12 +56182,12 @@
     <row r="182" ht="28" customHeight="1">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>EUS-93831</t>
+          <t>EUS-77322</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Contratación del servicio de asistencia técnica y gestión de</t>
+          <t>Redacción del proyecto y dirección de las obras de renovació</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
@@ -56501,12 +56218,12 @@
     <row r="183" ht="28" customHeight="1">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>EUS-16126</t>
+          <t>EUS-36090</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>Obras del proyecto de construcción de itinerario peatonal pa</t>
+          <t xml:space="preserve">Obras de rehabilitación del edificio del Emisario submarino </t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -56537,12 +56254,12 @@
     <row r="184" ht="28" customHeight="1">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>EUS-08987</t>
+          <t>EUS-09001</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>reparación y puesta en servicio de red de fecales y pluviale</t>
+          <t>Servicio para la elaboración de un estudio medioambiental de</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -56573,12 +56290,12 @@
     <row r="185" ht="28" customHeight="1">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>EUS-71383</t>
+          <t>EUS-57679</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro e instalación de un portón industrial enrollable </t>
+          <t xml:space="preserve">Plan de comunicacion y Sistema de Portavocias de la Agencia </t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
@@ -56606,44 +56323,8 @@
       <c r="I185" s="6" t="inlineStr"/>
       <c r="J185" s="6" t="inlineStr"/>
     </row>
-    <row r="186" ht="28" customHeight="1">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>EUS-06475</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
-        <is>
-          <t>ANS para determinadas aplicaciones implementadas por Izfe pa</t>
-        </is>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="inlineStr"/>
-      <c r="F186" s="25" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr"/>
-      <c r="H186" s="6" t="inlineStr">
-        <is>
-          <t>Por revisar</t>
-        </is>
-      </c>
-      <c r="I186" s="6" t="inlineStr"/>
-      <c r="J186" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J186"/>
+  <autoFilter ref="A1:J185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/resultados_convocatorias.xlsx
+++ b/docs/resultados_convocatorias.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Recursos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$190</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -78,13 +78,13 @@
     <font>
       <name val="Leelawadee UI"/>
       <b val="1"/>
-      <color rgb="00065F46"/>
+      <color rgb="00DC2626"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Leelawadee UI"/>
       <b val="1"/>
-      <color rgb="00DC2626"/>
+      <color rgb="00065F46"/>
       <sz val="10"/>
     </font>
     <font>
@@ -150,17 +150,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00065F46"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -246,11 +246,11 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -290,8 +290,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -685,7 +685,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 06/10/2026 12:18 - 184 convocatorias - 10 nuevas</t>
+          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 07/10/2026 12:10 - 182 convocatorias - 9 nuevas</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>85035</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Could you kindly confirm our understanding that in order to be eligible, each reference needs to be in EU-law approximation, harmonisation or implementation related to circular economy OR waste management, with all references together necessarily covering both circular economy and waste management.</t>
+          <t>DIGITAL-2021-DEPLOY-01-TWINS-HEALTH: Does the topic also cover digital twins of healthcare organisations (e.g. a hospital)?</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
@@ -1806,15 +1806,19 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Bilbao tiene Plan de Economía Circular y proyectos en Mercabilbao.</t>
+          <t>Proyecto BIM/GIS de Bilbao. Complementa estrategia digital.</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Could you kindly confirm our understanding that in order to be eligible, each reference needs to be in EU-law approximation, harmonisation or implementation related to circular economy OR waste manage</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr"/>
+          <t>DIGITAL-2021-DEPLOY-01-TWINS-HEALTH: Does the topic also cover digital twins of healthcare organisations (e.g. a hospital)?</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -1829,12 +1833,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>85039</t>
+          <t>85035</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>With reference to Technical Criteria Point 3.3, we kindly request clarification on what is classified as “implementation” activities related to circular economy and waste management. Specifically, we would appreciate guidance on how “implementation” should be understood in the context of the following requirement: “The completed services are in th</t>
+          <t>Could you kindly confirm our understanding that in order to be eligible, each reference needs to be in EU-law approximation, harmonisation or implementation related to circular economy OR waste management, with all references together necessarily covering both circular economy and waste management.</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
@@ -1858,7 +1862,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">With reference to Technical Criteria Point 3.3, we kindly request clarification on what is classified as “implementation” activities related to circular economy and waste management. Specifically, we </t>
+          <t>Could you kindly confirm our understanding that in order to be eligible, each reference needs to be in EU-law approximation, harmonisation or implementation related to circular economy OR waste manage</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr"/>
@@ -1876,12 +1880,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>85376</t>
+          <t>85039</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Regarding Section 16, point 3 of the Contract Notice: a) Could you please clarify whether each completed contract must include both elements - EU law approximation related to the circular economy and waste management - or whether it is acceptable to demonstrate this experience through two separate contracts, one covering circular economy and the o</t>
+          <t>With reference to Technical Criteria Point 3.3, we kindly request clarification on what is classified as “implementation” activities related to circular economy and waste management. Specifically, we would appreciate guidance on how “implementation” should be understood in the context of the following requirement: “The completed services are in th</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
@@ -1905,7 +1909,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regarding Section 16, point 3 of the Contract Notice: a) Could you please clarify whether each completed contract must include both elements - EU law approximation related to the circular economy and </t>
+          <t xml:space="preserve">With reference to Technical Criteria Point 3.3, we kindly request clarification on what is classified as “implementation” activities related to circular economy and waste management. Specifically, we </t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr"/>
@@ -1923,12 +1927,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>103603</t>
+          <t>85376</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Bio4HUMAN video - developed together with Horizon Results Booster Platform</t>
+          <t>Regarding Section 16, point 3 of the Contract Notice: a) Could you please clarify whether each completed contract must include both elements - EU law approximation related to the circular economy and waste management - or whether it is acceptable to demonstrate this experience through two separate contracts, one covering circular economy and the o</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
@@ -1947,12 +1951,12 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Garbiker y gestión de residuos municipal. Plan de residuos activo.</t>
+          <t>Bilbao tiene Plan de Economía Circular y proyectos en Mercabilbao.</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Bio4HUMAN video - developed together with Horizon Results Booster Platform  The Bio4HUMAN final project video is an accessible audiovisual resource presenting the project’s approach, findings and prac</t>
+          <t xml:space="preserve">Regarding Section 16, point 3 of the Contract Notice: a) Could you please clarify whether each completed contract must include both elements - EU law approximation related to the circular economy and </t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr"/>
@@ -1970,19 +1974,15 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>103603</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Ecosystem approach to climate change adaptation and flood risk management in the East Aegean river basin of Bulgaria</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>LIFE</t>
-        </is>
-      </c>
+          <t>Bio4HUMAN video - developed together with Horizon Results Booster Platform</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Bilbao tiene historial de inundaciones (ría del Nervión). Planes activos.</t>
+          <t>Garbiker y gestión de residuos municipal. Plan de residuos activo.</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Ecosystem approach to climate change adaptation and flood risk management in the East Aegean river basin of Bulgaria</t>
+          <t>Bio4HUMAN video - developed together with Horizon Results Booster Platform  The Bio4HUMAN final project video is an accessible audiovisual resource presenting the project’s approach, findings and prac</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr"/>
@@ -2021,15 +2021,19 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>8f39fbaa-ed92-4f7a-a36e-c862147e499c-PIN</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Technical Assistance for river basin and flood risk plan</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
+          <t>Ecosystem approach to climate change adaptation and flood risk management in the East Aegean river basin of Bulgaria</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -2050,7 +2054,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Technical Assistance for river basin and flood risk plan</t>
+          <t>Ecosystem approach to climate change adaptation and flood risk management in the East Aegean river basin of Bulgaria</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr"/>
@@ -2068,12 +2072,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>c1b82527-35ef-4dd7-b67e-a57588ca2380-EXA</t>
+          <t>8f39fbaa-ed92-4f7a-a36e-c862147e499c-PIN</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>New European Bauhaus Label</t>
+          <t>Technical Assistance for river basin and flood risk plan</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
@@ -2092,12 +2096,12 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>NEB combina sostenibilidad + diseño + inclusion. Ideal para regeneracion urbana Bilbao (Zorrotzaurre, Casco Viejo).</t>
+          <t>Bilbao tiene historial de inundaciones (ría del Nervión). Planes activos.</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>New European Bauhaus Label</t>
+          <t>Technical Assistance for river basin and flood risk plan</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
@@ -2115,12 +2119,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>c1b82527-35ef-4dd7-b67e-a57588ca2380-EXA</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, are proposals expected to develop connections between the New European Bauhaus (NEB) initiative and Horizon Europe missions?</t>
+          <t>New European Bauhaus Label</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
@@ -2144,7 +2148,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, are proposals expected to develop connections between the New European Bauhaus (NEB) initiative and Horizon Europe missions?</t>
+          <t>New European Bauhaus Label</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr"/>
@@ -2162,12 +2166,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, should the lighthouse demonstrator address all three core values of the New European Bauhaus or just one?</t>
+          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, are proposals expected to develop connections between the New European Bauhaus (NEB) initiative and Horizon Europe missions?</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
@@ -2191,7 +2195,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, should the lighthouse demonstrator address all three core values of the New European Bauhaus or just one?</t>
+          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, are proposals expected to develop connections between the New European Bauhaus (NEB) initiative and Horizon Europe missions?</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
@@ -2209,12 +2213,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>102435</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Is there any practical guidance on the implementation of the requirement for proposals to allocate at least 0.8% of their budget for engaging with the Horizon Europe-funded ‘New European Bauhaus hub for results and impact’?</t>
+          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, should the lighthouse demonstrator address all three core values of the New European Bauhaus or just one?</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
@@ -2238,7 +2242,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>Is there any practical guidance on the implementation of the requirement for proposals to allocate at least 0.8% of their budget for engaging with the Horizon Europe-funded ‘New European Bauhaus hub f</t>
+          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, should the lighthouse demonstrator address all three core values of the New European Bauhaus or just one?</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr"/>
@@ -2256,12 +2260,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>102435</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-HLTH-2023-ENVHLTH-02-02, how should proposals contribute to the New European Bauhaus (NEB) initiative? How and with whom concretely should they interact, and what kind of activities are expected?</t>
+          <t>Is there any practical guidance on the implementation of the requirement for proposals to allocate at least 0.8% of their budget for engaging with the Horizon Europe-funded ‘New European Bauhaus hub for results and impact’?</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
@@ -2285,7 +2289,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-HLTH-2023-ENVHLTH-02-02, how should proposals contribute to the New European Bauhaus (NEB) initiative? How and with whom concretely should they interact, and what kind of activitie</t>
+          <t>Is there any practical guidance on the implementation of the requirement for proposals to allocate at least 0.8% of their budget for engaging with the Horizon Europe-funded ‘New European Bauhaus hub f</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr"/>
@@ -2303,12 +2307,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>c36effc6-e7b0-423c-93a5-2b74a21546c0-EXA</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>EEA/SUN/25/001- Clean tech production in Europe: implications for quality jobs and a just transition</t>
+          <t>Under topic HORIZON-HLTH-2023-ENVHLTH-02-02, how should proposals contribute to the New European Bauhaus (NEB) initiative? How and with whom concretely should they interact, and what kind of activities are expected?</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -2320,19 +2324,19 @@
       <c r="F38" s="6" t="inlineStr"/>
       <c r="G38" s="6" t="inlineStr"/>
       <c r="H38" s="6" t="inlineStr"/>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Margen izquierda con pasado industrial. Potencial reconversión.</t>
+          <t>NEB combina sostenibilidad + diseño + inclusion. Ideal para regeneracion urbana Bilbao (Zorrotzaurre, Casco Viejo).</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>EEA/SUN/25/001- Clean tech production in Europe: implications for quality jobs and a just transition</t>
+          <t>Under topic HORIZON-HLTH-2023-ENVHLTH-02-02, how should proposals contribute to the New European Bauhaus (NEB) initiative? How and with whom concretely should they interact, and what kind of activitie</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr"/>
@@ -2350,12 +2354,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>c36effc6-e7b0-423c-93a5-2b74a21546c0-EXA</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, our proposed action concerns the construction of infrastructure. It will be implemented by a private company which is not a project promoter. Can this company apply for a CEF Energy grant and still receive funding?</t>
+          <t>EEA/SUN/25/001- Clean tech production in Europe: implications for quality jobs and a just transition</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -2374,12 +2378,12 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Infraestructuras energéticas del País Vasco potencialmente elegibles.</t>
+          <t>Margen izquierda con pasado industrial. Potencial reconversión.</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, our proposed action concerns the construction of infrastructure. It will be implemented by a private company which is not a project promoter. Can this company apply for a CEF</t>
+          <t>EEA/SUN/25/001- Clean tech production in Europe: implications for quality jobs and a just transition</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr"/>
@@ -2397,12 +2401,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>326952ANNOUNCEMENTen</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Hydrogen cities</t>
+          <t>Under Call CEF-E-PCI-PMI, our proposed action concerns the construction of infrastructure. It will be implemented by a private company which is not a project promoter. Can this company apply for a CEF Energy grant and still receive funding?</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -2421,12 +2425,12 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Corredor Vasco del Hidrógeno. Petronor y Puerto de Bilbao involucrados.</t>
+          <t>Infraestructuras energéticas del País Vasco potencialmente elegibles.</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>Hydrogen cities</t>
+          <t>Under Call CEF-E-PCI-PMI, our proposed action concerns the construction of infrastructure. It will be implemented by a private company which is not a project promoter. Can this company apply for a CEF</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr"/>
@@ -2444,7 +2448,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>328464ANNOUNCEMENTen</t>
+          <t>326952ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2491,7 +2495,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>330857ANNOUNCEMENTen</t>
+          <t>328464ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2538,7 +2542,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>333297ANNOUNCEMENTen</t>
+          <t>330857ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2585,7 +2589,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>335155ANNOUNCEMENTen</t>
+          <t>333297ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -2632,7 +2636,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>338237ANNOUNCEMENTen</t>
+          <t>335155ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2679,7 +2683,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>339612ANNOUNCEMENTen</t>
+          <t>338237ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2726,7 +2730,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>343814ANNOUNCEMENTen</t>
+          <t>339612ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -2773,7 +2777,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>328462ANNOUNCEMENTen</t>
+          <t>343814ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -2820,7 +2824,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>328461ANNOUNCEMENTen</t>
+          <t>328462ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -2867,7 +2871,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>345032ANNOUNCEMENTen</t>
+          <t>328461ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -3341,15 +3345,19 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -3370,7 +3378,7 @@
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr"/>
@@ -3388,19 +3396,15 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr"/>
       <c r="E61" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -3421,7 +3425,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr"/>
@@ -3580,12 +3584,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr"/>
@@ -3609,7 +3613,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr"/>
@@ -3627,15 +3631,19 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr"/>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -3656,7 +3664,7 @@
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr"/>
@@ -3674,19 +3682,15 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr"/>
       <c r="E67" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -3707,7 +3711,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr"/>
@@ -3725,12 +3729,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr"/>
@@ -3754,7 +3758,7 @@
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr"/>
@@ -3772,12 +3776,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr"/>
@@ -3801,7 +3805,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr"/>
@@ -3819,12 +3823,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr"/>
@@ -3848,7 +3852,7 @@
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -3866,12 +3870,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr"/>
@@ -3895,7 +3899,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr"/>
@@ -3913,12 +3917,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr"/>
@@ -3942,7 +3946,7 @@
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr"/>
@@ -3960,12 +3964,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr"/>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4007,12 +4011,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr"/>
@@ -4036,7 +4040,7 @@
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr"/>
@@ -4054,12 +4058,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr"/>
@@ -4083,7 +4087,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4101,12 +4105,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr"/>
@@ -4130,7 +4134,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr"/>
@@ -4148,12 +4152,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr"/>
@@ -4177,7 +4181,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4195,12 +4199,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr"/>
@@ -4224,7 +4228,7 @@
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr"/>
@@ -4242,12 +4246,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr"/>
@@ -4271,7 +4275,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4289,12 +4293,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr"/>
@@ -4318,7 +4322,7 @@
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr"/>
@@ -4336,12 +4340,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr"/>
@@ -4365,7 +4369,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4383,12 +4387,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>938191470</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>IMS INDUSTRIE MECCANICHE SCARDELLATO SPA</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr"/>
@@ -4412,7 +4416,7 @@
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>IMS INDUSTRIE MECCANICHE SCARDELLATO SPA</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr"/>
@@ -6968,12 +6972,12 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr"/>
@@ -6997,7 +7001,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7015,12 +7019,12 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr"/>
@@ -7044,7 +7048,7 @@
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr"/>
@@ -7532,12 +7536,12 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>928211140</t>
+          <t>928057492</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr"/>
@@ -7561,7 +7565,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7579,12 +7583,12 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>928057492</t>
+          <t>926227393</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr"/>
@@ -7608,7 +7612,7 @@
       </c>
       <c r="K150" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="L150" s="6" t="inlineStr"/>
@@ -7626,12 +7630,12 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>926227393</t>
+          <t>928211140</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr"/>
@@ -7655,7 +7659,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8982,21 +8986,21 @@
       </c>
     </row>
     <row r="180" ht="28" customHeight="1">
-      <c r="A180" s="13" t="inlineStr">
+      <c r="A180" s="14" t="inlineStr">
         <is>
           <t>🟢 Euskadi</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
-      <c r="A181" s="14" t="inlineStr">
+      <c r="A181" s="15" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>EUS-47596</t>
+          <t>EUS-49083</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -9032,7 +9036,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L181" s="15" t="inlineStr">
+      <c r="L181" s="13" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9044,14 +9048,14 @@
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
-      <c r="A182" s="14" t="inlineStr">
+      <c r="A182" s="15" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>EUS-51067</t>
+          <t>EUS-36489</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
@@ -9087,7 +9091,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L182" s="15" t="inlineStr">
+      <c r="L182" s="13" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9099,19 +9103,19 @@
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
-      <c r="A183" s="14" t="inlineStr">
+      <c r="A183" s="15" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>EUS-92303</t>
+          <t>EUS-51813</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>Servicio de retirada, transporte y gestión de los residuos Sandach de la cámara frigorífica situada en el Garbigune de Eibar</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
@@ -9128,12 +9132,12 @@
       <c r="G183" s="6" t="inlineStr"/>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="I183" s="8" t="inlineStr">
-        <is>
-          <t>ALTA</t>
+          <t>Ayuda/Subvencion Euskadi</t>
+        </is>
+      </c>
+      <c r="I183" s="11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="J183" s="6" t="inlineStr"/>
@@ -9142,7 +9146,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L183" s="15" t="inlineStr">
+      <c r="L183" s="13" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9154,19 +9158,19 @@
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
-      <c r="A184" s="14" t="inlineStr">
+      <c r="A184" s="15" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>EUS-86597</t>
+          <t>EUS-95789</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>Rehabilitacion parrales del barrio San Bartolome (zona Bizezko)</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
@@ -9183,12 +9187,12 @@
       <c r="G184" s="6" t="inlineStr"/>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="I184" s="8" t="inlineStr">
-        <is>
-          <t>ALTA</t>
+          <t>Ayuda/Subvencion Euskadi</t>
+        </is>
+      </c>
+      <c r="I184" s="11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="J184" s="6" t="inlineStr"/>
@@ -9197,7 +9201,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L184" s="15" t="inlineStr">
+      <c r="L184" s="13" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9209,19 +9213,19 @@
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
-      <c r="A185" s="14" t="inlineStr">
+      <c r="A185" s="15" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>EUS-60193</t>
+          <t>EUS-26823</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
+          <t>Digitalizacion del riego</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
@@ -9238,7 +9242,7 @@
       <c r="G185" s="6" t="inlineStr"/>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="I185" s="11" t="inlineStr">
@@ -9252,7 +9256,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L185" s="15" t="inlineStr">
+      <c r="L185" s="13" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9264,19 +9268,19 @@
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
-      <c r="A186" s="14" t="inlineStr">
+      <c r="A186" s="15" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>EUS-65298</t>
+          <t>EUS-20763</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>elgoibar kirola - análisis del agua de las piscinas y legionella, julio 2026</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
@@ -9293,7 +9297,7 @@
       <c r="G186" s="6" t="inlineStr"/>
       <c r="H186" s="6" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="I186" s="11" t="inlineStr">
@@ -9307,7 +9311,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L186" s="15" t="inlineStr">
+      <c r="L186" s="13" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9319,19 +9323,19 @@
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
-      <c r="A187" s="14" t="inlineStr">
+      <c r="A187" s="15" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>EUS-77322</t>
+          <t>EUS-09315</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>Redacción del proyecto y dirección de las obras de renovación de la red de distribución de agua en distintas zonas del centro de Irun</t>
+          <t>Suministro de recipientes para el control sanitario de aguas de las piscinas Ugarteigaran de Elkargune.</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
@@ -9362,7 +9366,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L187" s="15" t="inlineStr">
+      <c r="L187" s="13" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9374,19 +9378,19 @@
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
-      <c r="A188" s="14" t="inlineStr">
+      <c r="A188" s="15" t="inlineStr">
         <is>
           <t>Euskadi</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>EUS-36090</t>
+          <t>EUS-97313</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>Obras de rehabilitación del edificio del Emisario submarino de Monpas</t>
+          <t>Servicio de Limpieza de la Sede de Emakunde-Insituto Vasco de la Mujer.</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
@@ -9417,7 +9421,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L188" s="15" t="inlineStr">
+      <c r="L188" s="13" t="inlineStr">
         <is>
           <t>NUEVA</t>
         </is>
@@ -9428,118 +9432,8 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="40" customHeight="1">
-      <c r="A189" s="14" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
-        <is>
-          <t>EUS-09001</t>
-        </is>
-      </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>Servicio para la elaboración de un estudio medioambiental de la zona costera de Mompás y del estuario del río Oiartzun</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="E189" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F189" s="6" t="inlineStr"/>
-      <c r="G189" s="6" t="inlineStr"/>
-      <c r="H189" s="6" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="I189" s="11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="J189" s="6" t="inlineStr"/>
-      <c r="K189" s="6" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="L189" s="15" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="M189" s="9" t="inlineStr">
-        <is>
-          <t>Ver</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="40" customHeight="1">
-      <c r="A190" s="14" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
-        <is>
-          <t>EUS-57679</t>
-        </is>
-      </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>Plan de comunicacion y Sistema de Portavocias de la Agencia Vasca del Agua</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="E190" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F190" s="6" t="inlineStr"/>
-      <c r="G190" s="6" t="inlineStr"/>
-      <c r="H190" s="6" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="I190" s="11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="J190" s="6" t="inlineStr"/>
-      <c r="K190" s="6" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="L190" s="15" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="M190" s="9" t="inlineStr">
-        <is>
-          <t>Ver</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:M190"/>
+  <autoFilter ref="A4:M188"/>
   <mergeCells count="4">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A180:M180"/>
@@ -9729,8 +9623,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId184"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9742,7 +9634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2759"/>
+  <dimension ref="A1:F2729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14084,7 +13976,7 @@
     <row r="316" ht="30" customHeight="1">
       <c r="A316" s="16" t="inlineStr">
         <is>
-          <t>FICHA 22: 85035</t>
+          <t>FICHA 22: 18526</t>
         </is>
       </c>
       <c r="B316" s="17" t="n"/>
@@ -14117,7 +14009,7 @@
       </c>
       <c r="B318" s="19" t="inlineStr">
         <is>
-          <t>Could you kindly confirm our understanding that in order to be eligible, each reference needs to be in EU-law approximation, harmonisation or implementation related to circular economy OR waste management, with all references together necessarily covering both circular economy and waste management.</t>
+          <t>DIGITAL-2021-DEPLOY-01-TWINS-HEALTH: Does the topic also cover digital twins of healthcare organisations (e.g. a hospital)?</t>
         </is>
       </c>
       <c r="C318" s="20" t="n"/>
@@ -14133,7 +14025,7 @@
       </c>
       <c r="B319" s="19" t="inlineStr">
         <is>
-          <t>85035</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="C319" s="20" t="n"/>
@@ -14233,7 +14125,7 @@
       </c>
       <c r="B326" s="19" t="inlineStr">
         <is>
-          <t>Could you kindly confirm our understanding that in order to be eligible, each reference needs to be in EU-law approximation, harmonisation or implementation related to circular economy OR waste management, with all references together necessarily covering both circular economy and waste management.</t>
+          <t>DIGITAL-2021-DEPLOY-01-TWINS-HEALTH: Does the topic also cover digital twins of healthcare organisations (e.g. a hospital)?</t>
         </is>
       </c>
       <c r="C326" s="20" t="n"/>
@@ -14261,7 +14153,7 @@
       </c>
       <c r="B328" s="21" t="inlineStr">
         <is>
-          <t>ALTA — Bilbao tiene Plan de Economía Circular y proyectos en Mercabilbao.</t>
+          <t>ALTA — Proyecto BIM/GIS de Bilbao. Complementa estrategia digital.</t>
         </is>
       </c>
       <c r="C328" s="20" t="n"/>
@@ -14277,7 +14169,7 @@
       </c>
       <c r="B329" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85035</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18526</t>
         </is>
       </c>
       <c r="C329" s="20" t="n"/>
@@ -14288,7 +14180,7 @@
     <row r="331" ht="30" customHeight="1">
       <c r="A331" s="16" t="inlineStr">
         <is>
-          <t>FICHA 23: 85039</t>
+          <t>FICHA 23: 85035</t>
         </is>
       </c>
       <c r="B331" s="17" t="n"/>
@@ -14321,7 +14213,7 @@
       </c>
       <c r="B333" s="19" t="inlineStr">
         <is>
-          <t>With reference to Technical Criteria Point 3.3, we kindly request clarification on what is classified as “implementation” activities related to circular economy and waste management. Specifically, we would appreciate guidance on how “implementation” should be understood in the context of the following requirement: “The completed services are in th</t>
+          <t>Could you kindly confirm our understanding that in order to be eligible, each reference needs to be in EU-law approximation, harmonisation or implementation related to circular economy OR waste management, with all references together necessarily covering both circular economy and waste management.</t>
         </is>
       </c>
       <c r="C333" s="20" t="n"/>
@@ -14337,7 +14229,7 @@
       </c>
       <c r="B334" s="19" t="inlineStr">
         <is>
-          <t>85039</t>
+          <t>85035</t>
         </is>
       </c>
       <c r="C334" s="20" t="n"/>
@@ -14437,7 +14329,7 @@
       </c>
       <c r="B341" s="19" t="inlineStr">
         <is>
-          <t>With reference to Technical Criteria Point 3.3, we kindly request clarification on what is classified as “implementation” activities related to circular economy and waste management. Specifically, we would appreciate guidance on how “implementation” should be understood in the context of the following requirement: “The completed services are in th</t>
+          <t>Could you kindly confirm our understanding that in order to be eligible, each reference needs to be in EU-law approximation, harmonisation or implementation related to circular economy OR waste management, with all references together necessarily covering both circular economy and waste management.</t>
         </is>
       </c>
       <c r="C341" s="20" t="n"/>
@@ -14481,7 +14373,7 @@
       </c>
       <c r="B344" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85039</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85035</t>
         </is>
       </c>
       <c r="C344" s="20" t="n"/>
@@ -14492,7 +14384,7 @@
     <row r="346" ht="30" customHeight="1">
       <c r="A346" s="16" t="inlineStr">
         <is>
-          <t>FICHA 24: 85376</t>
+          <t>FICHA 24: 85039</t>
         </is>
       </c>
       <c r="B346" s="17" t="n"/>
@@ -14525,7 +14417,7 @@
       </c>
       <c r="B348" s="19" t="inlineStr">
         <is>
-          <t>Regarding Section 16, point 3 of the Contract Notice: a) Could you please clarify whether each completed contract must include both elements - EU law approximation related to the circular economy and waste management - or whether it is acceptable to demonstrate this experience through two separate contracts, one covering circular economy and the o</t>
+          <t>With reference to Technical Criteria Point 3.3, we kindly request clarification on what is classified as “implementation” activities related to circular economy and waste management. Specifically, we would appreciate guidance on how “implementation” should be understood in the context of the following requirement: “The completed services are in th</t>
         </is>
       </c>
       <c r="C348" s="20" t="n"/>
@@ -14541,7 +14433,7 @@
       </c>
       <c r="B349" s="19" t="inlineStr">
         <is>
-          <t>85376</t>
+          <t>85039</t>
         </is>
       </c>
       <c r="C349" s="20" t="n"/>
@@ -14641,7 +14533,7 @@
       </c>
       <c r="B356" s="19" t="inlineStr">
         <is>
-          <t>Regarding Section 16, point 3 of the Contract Notice: a) Could you please clarify whether each completed contract must include both elements - EU law approximation related to the circular economy and waste management - or whether it is acceptable to demonstrate this experience through two separate contracts, one covering circular economy and the o</t>
+          <t>With reference to Technical Criteria Point 3.3, we kindly request clarification on what is classified as “implementation” activities related to circular economy and waste management. Specifically, we would appreciate guidance on how “implementation” should be understood in the context of the following requirement: “The completed services are in th</t>
         </is>
       </c>
       <c r="C356" s="20" t="n"/>
@@ -14685,7 +14577,7 @@
       </c>
       <c r="B359" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85376</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85039</t>
         </is>
       </c>
       <c r="C359" s="20" t="n"/>
@@ -14696,7 +14588,7 @@
     <row r="361" ht="30" customHeight="1">
       <c r="A361" s="16" t="inlineStr">
         <is>
-          <t>FICHA 25: 103603</t>
+          <t>FICHA 25: 85376</t>
         </is>
       </c>
       <c r="B361" s="17" t="n"/>
@@ -14721,7 +14613,7 @@
       <c r="E362" s="20" t="n"/>
       <c r="F362" s="20" t="n"/>
     </row>
-    <row r="363" ht="20" customHeight="1">
+    <row r="363" ht="45" customHeight="1">
       <c r="A363" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -14729,7 +14621,7 @@
       </c>
       <c r="B363" s="19" t="inlineStr">
         <is>
-          <t>Bio4HUMAN video - developed together with Horizon Results Booster Platform</t>
+          <t>Regarding Section 16, point 3 of the Contract Notice: a) Could you please clarify whether each completed contract must include both elements - EU law approximation related to the circular economy and waste management - or whether it is acceptable to demonstrate this experience through two separate contracts, one covering circular economy and the o</t>
         </is>
       </c>
       <c r="C363" s="20" t="n"/>
@@ -14745,7 +14637,7 @@
       </c>
       <c r="B364" s="19" t="inlineStr">
         <is>
-          <t>103603</t>
+          <t>85376</t>
         </is>
       </c>
       <c r="C364" s="20" t="n"/>
@@ -14831,11 +14723,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B370" s="19" t="inlineStr">
-        <is>
-          <t>HORIZON-CL6-2023-CIRCBIO-01</t>
-        </is>
-      </c>
+      <c r="B370" s="19" t="inlineStr"/>
       <c r="C370" s="20" t="n"/>
       <c r="D370" s="20" t="n"/>
       <c r="E370" s="20" t="n"/>
@@ -14849,7 +14737,7 @@
       </c>
       <c r="B371" s="19" t="inlineStr">
         <is>
-          <t>Bio4HUMAN video - developed together with Horizon Results Booster Platform  The Bio4HUMAN final project video is an accessible audiovisual resource presenting the project’s approach, findings and practical tools for improving solid waste management in humanitarian settings. Developed with support from the Horizon Results Booster, it explains ho</t>
+          <t>Regarding Section 16, point 3 of the Contract Notice: a) Could you please clarify whether each completed contract must include both elements - EU law approximation related to the circular economy and waste management - or whether it is acceptable to demonstrate this experience through two separate contracts, one covering circular economy and the o</t>
         </is>
       </c>
       <c r="C371" s="20" t="n"/>
@@ -14877,7 +14765,7 @@
       </c>
       <c r="B373" s="21" t="inlineStr">
         <is>
-          <t>ALTA — Garbiker y gestión de residuos municipal. Plan de residuos activo.</t>
+          <t>ALTA — Bilbao tiene Plan de Economía Circular y proyectos en Mercabilbao.</t>
         </is>
       </c>
       <c r="C373" s="20" t="n"/>
@@ -14893,7 +14781,7 @@
       </c>
       <c r="B374" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/103603</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/85376</t>
         </is>
       </c>
       <c r="C374" s="20" t="n"/>
@@ -14904,7 +14792,7 @@
     <row r="376" ht="30" customHeight="1">
       <c r="A376" s="16" t="inlineStr">
         <is>
-          <t>FICHA 26: LIFE</t>
+          <t>FICHA 26: 103603</t>
         </is>
       </c>
       <c r="B376" s="17" t="n"/>
@@ -14929,7 +14817,7 @@
       <c r="E377" s="20" t="n"/>
       <c r="F377" s="20" t="n"/>
     </row>
-    <row r="378" ht="45" customHeight="1">
+    <row r="378" ht="20" customHeight="1">
       <c r="A378" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -14937,7 +14825,7 @@
       </c>
       <c r="B378" s="19" t="inlineStr">
         <is>
-          <t>Ecosystem approach to climate change adaptation and flood risk management in the East Aegean river basin of Bulgaria</t>
+          <t>Bio4HUMAN video - developed together with Horizon Results Booster Platform</t>
         </is>
       </c>
       <c r="C378" s="20" t="n"/>
@@ -14953,7 +14841,7 @@
       </c>
       <c r="B379" s="19" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>103603</t>
         </is>
       </c>
       <c r="C379" s="20" t="n"/>
@@ -14967,11 +14855,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B380" s="19" t="inlineStr">
-        <is>
-          <t>LIFE</t>
-        </is>
-      </c>
+      <c r="B380" s="19" t="inlineStr"/>
       <c r="C380" s="20" t="n"/>
       <c r="D380" s="20" t="n"/>
       <c r="E380" s="20" t="n"/>
@@ -15045,7 +14929,7 @@
       </c>
       <c r="B385" s="19" t="inlineStr">
         <is>
-          <t>LIFE-TA-2020</t>
+          <t>HORIZON-CL6-2023-CIRCBIO-01</t>
         </is>
       </c>
       <c r="C385" s="20" t="n"/>
@@ -15061,7 +14945,7 @@
       </c>
       <c r="B386" s="19" t="inlineStr">
         <is>
-          <t>Ecosystem approach to climate change adaptation and flood risk management in the East Aegean river basin of Bulgaria</t>
+          <t>Bio4HUMAN video - developed together with Horizon Results Booster Platform  The Bio4HUMAN final project video is an accessible audiovisual resource presenting the project’s approach, findings and practical tools for improving solid waste management in humanitarian settings. Developed with support from the Horizon Results Booster, it explains ho</t>
         </is>
       </c>
       <c r="C386" s="20" t="n"/>
@@ -15081,7 +14965,7 @@
       <c r="E387" s="20" t="n"/>
       <c r="F387" s="20" t="n"/>
     </row>
-    <row r="388" ht="45" customHeight="1">
+    <row r="388" ht="20" customHeight="1">
       <c r="A388" s="18" t="inlineStr">
         <is>
           <t>Relevancia Bilbao</t>
@@ -15089,7 +14973,7 @@
       </c>
       <c r="B388" s="21" t="inlineStr">
         <is>
-          <t>ALTA — Bilbao tiene historial de inundaciones (ría del Nervión). Planes activos.</t>
+          <t>ALTA — Garbiker y gestión de residuos municipal. Plan de residuos activo.</t>
         </is>
       </c>
       <c r="C388" s="20" t="n"/>
@@ -15105,7 +14989,7 @@
       </c>
       <c r="B389" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/103603</t>
         </is>
       </c>
       <c r="C389" s="20" t="n"/>
@@ -15116,7 +15000,7 @@
     <row r="391" ht="30" customHeight="1">
       <c r="A391" s="16" t="inlineStr">
         <is>
-          <t>FICHA 27: 8f39fbaa-ed92-4f7a-a36e-c862147e499c-PIN</t>
+          <t>FICHA 27: LIFE</t>
         </is>
       </c>
       <c r="B391" s="17" t="n"/>
@@ -15141,7 +15025,7 @@
       <c r="E392" s="20" t="n"/>
       <c r="F392" s="20" t="n"/>
     </row>
-    <row r="393" ht="20" customHeight="1">
+    <row r="393" ht="45" customHeight="1">
       <c r="A393" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -15149,7 +15033,7 @@
       </c>
       <c r="B393" s="19" t="inlineStr">
         <is>
-          <t>Technical Assistance for river basin and flood risk plan</t>
+          <t>Ecosystem approach to climate change adaptation and flood risk management in the East Aegean river basin of Bulgaria</t>
         </is>
       </c>
       <c r="C393" s="20" t="n"/>
@@ -15165,7 +15049,7 @@
       </c>
       <c r="B394" s="19" t="inlineStr">
         <is>
-          <t>8f39fbaa-ed92-4f7a-a36e-c862147e499c-PIN</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C394" s="20" t="n"/>
@@ -15179,7 +15063,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B395" s="19" t="inlineStr"/>
+      <c r="B395" s="19" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
       <c r="C395" s="20" t="n"/>
       <c r="D395" s="20" t="n"/>
       <c r="E395" s="20" t="n"/>
@@ -15253,7 +15141,7 @@
       </c>
       <c r="B400" s="19" t="inlineStr">
         <is>
-          <t>EC-ENEST/BEG/2025/EA-RP/0052-PIN</t>
+          <t>LIFE-TA-2020</t>
         </is>
       </c>
       <c r="C400" s="20" t="n"/>
@@ -15261,7 +15149,7 @@
       <c r="E400" s="20" t="n"/>
       <c r="F400" s="20" t="n"/>
     </row>
-    <row r="401" ht="20" customHeight="1">
+    <row r="401" ht="45" customHeight="1">
       <c r="A401" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -15269,7 +15157,7 @@
       </c>
       <c r="B401" s="19" t="inlineStr">
         <is>
-          <t>Technical Assistance for river basin and flood risk plan</t>
+          <t>Ecosystem approach to climate change adaptation and flood risk management in the East Aegean river basin of Bulgaria</t>
         </is>
       </c>
       <c r="C401" s="20" t="n"/>
@@ -15313,7 +15201,7 @@
       </c>
       <c r="B404" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/8f39fbaa-ed92-4f7a-a36e-c862147e499c-PIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE</t>
         </is>
       </c>
       <c r="C404" s="20" t="n"/>
@@ -15324,7 +15212,7 @@
     <row r="406" ht="30" customHeight="1">
       <c r="A406" s="16" t="inlineStr">
         <is>
-          <t>FICHA 28: c1b82527-35ef-4dd7-b67e-a57588ca2380-EXA</t>
+          <t>FICHA 28: 8f39fbaa-ed92-4f7a-a36e-c862147e499c-PIN</t>
         </is>
       </c>
       <c r="B406" s="17" t="n"/>
@@ -15357,7 +15245,7 @@
       </c>
       <c r="B408" s="19" t="inlineStr">
         <is>
-          <t>New European Bauhaus Label</t>
+          <t>Technical Assistance for river basin and flood risk plan</t>
         </is>
       </c>
       <c r="C408" s="20" t="n"/>
@@ -15373,7 +15261,7 @@
       </c>
       <c r="B409" s="19" t="inlineStr">
         <is>
-          <t>c1b82527-35ef-4dd7-b67e-a57588ca2380-EXA</t>
+          <t>8f39fbaa-ed92-4f7a-a36e-c862147e499c-PIN</t>
         </is>
       </c>
       <c r="C409" s="20" t="n"/>
@@ -15461,7 +15349,7 @@
       </c>
       <c r="B415" s="19" t="inlineStr">
         <is>
-          <t>EC-JRC/2026/LVP/3876-EXA</t>
+          <t>EC-ENEST/BEG/2025/EA-RP/0052-PIN</t>
         </is>
       </c>
       <c r="C415" s="20" t="n"/>
@@ -15477,7 +15365,7 @@
       </c>
       <c r="B416" s="19" t="inlineStr">
         <is>
-          <t>New European Bauhaus Label</t>
+          <t>Technical Assistance for river basin and flood risk plan</t>
         </is>
       </c>
       <c r="C416" s="20" t="n"/>
@@ -15505,7 +15393,7 @@
       </c>
       <c r="B418" s="21" t="inlineStr">
         <is>
-          <t>ALTA — NEB combina sostenibilidad + diseño + inclusion. Ideal para regeneracion urbana Bilbao (Zorrotzaurre, Casco Viejo).</t>
+          <t>ALTA — Bilbao tiene historial de inundaciones (ría del Nervión). Planes activos.</t>
         </is>
       </c>
       <c r="C418" s="20" t="n"/>
@@ -15521,7 +15409,7 @@
       </c>
       <c r="B419" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c1b82527-35ef-4dd7-b67e-a57588ca2380-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/8f39fbaa-ed92-4f7a-a36e-c862147e499c-PIN</t>
         </is>
       </c>
       <c r="C419" s="20" t="n"/>
@@ -15532,7 +15420,7 @@
     <row r="421" ht="30" customHeight="1">
       <c r="A421" s="16" t="inlineStr">
         <is>
-          <t>FICHA 29: 17529</t>
+          <t>FICHA 29: c1b82527-35ef-4dd7-b67e-a57588ca2380-EXA</t>
         </is>
       </c>
       <c r="B421" s="17" t="n"/>
@@ -15557,7 +15445,7 @@
       <c r="E422" s="20" t="n"/>
       <c r="F422" s="20" t="n"/>
     </row>
-    <row r="423" ht="45" customHeight="1">
+    <row r="423" ht="20" customHeight="1">
       <c r="A423" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -15565,7 +15453,7 @@
       </c>
       <c r="B423" s="19" t="inlineStr">
         <is>
-          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, are proposals expected to develop connections between the New European Bauhaus (NEB) initiative and Horizon Europe missions?</t>
+          <t>New European Bauhaus Label</t>
         </is>
       </c>
       <c r="C423" s="20" t="n"/>
@@ -15581,7 +15469,7 @@
       </c>
       <c r="B424" s="19" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>c1b82527-35ef-4dd7-b67e-a57588ca2380-EXA</t>
         </is>
       </c>
       <c r="C424" s="20" t="n"/>
@@ -15667,13 +15555,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B430" s="19" t="inlineStr"/>
+      <c r="B430" s="19" t="inlineStr">
+        <is>
+          <t>EC-JRC/2026/LVP/3876-EXA</t>
+        </is>
+      </c>
       <c r="C430" s="20" t="n"/>
       <c r="D430" s="20" t="n"/>
       <c r="E430" s="20" t="n"/>
       <c r="F430" s="20" t="n"/>
     </row>
-    <row r="431" ht="45" customHeight="1">
+    <row r="431" ht="20" customHeight="1">
       <c r="A431" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -15681,7 +15573,7 @@
       </c>
       <c r="B431" s="19" t="inlineStr">
         <is>
-          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, are proposals expected to develop connections between the New European Bauhaus (NEB) initiative and Horizon Europe missions?</t>
+          <t>New European Bauhaus Label</t>
         </is>
       </c>
       <c r="C431" s="20" t="n"/>
@@ -15725,7 +15617,7 @@
       </c>
       <c r="B434" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17529</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c1b82527-35ef-4dd7-b67e-a57588ca2380-EXA</t>
         </is>
       </c>
       <c r="C434" s="20" t="n"/>
@@ -15736,7 +15628,7 @@
     <row r="436" ht="30" customHeight="1">
       <c r="A436" s="16" t="inlineStr">
         <is>
-          <t>FICHA 30: 17534</t>
+          <t>FICHA 30: 17529</t>
         </is>
       </c>
       <c r="B436" s="17" t="n"/>
@@ -15769,7 +15661,7 @@
       </c>
       <c r="B438" s="19" t="inlineStr">
         <is>
-          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, should the lighthouse demonstrator address all three core values of the New European Bauhaus or just one?</t>
+          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, are proposals expected to develop connections between the New European Bauhaus (NEB) initiative and Horizon Europe missions?</t>
         </is>
       </c>
       <c r="C438" s="20" t="n"/>
@@ -15785,7 +15677,7 @@
       </c>
       <c r="B439" s="19" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="C439" s="20" t="n"/>
@@ -15885,7 +15777,7 @@
       </c>
       <c r="B446" s="19" t="inlineStr">
         <is>
-          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, should the lighthouse demonstrator address all three core values of the New European Bauhaus or just one?</t>
+          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, are proposals expected to develop connections between the New European Bauhaus (NEB) initiative and Horizon Europe missions?</t>
         </is>
       </c>
       <c r="C446" s="20" t="n"/>
@@ -15929,7 +15821,7 @@
       </c>
       <c r="B449" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17534</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17529</t>
         </is>
       </c>
       <c r="C449" s="20" t="n"/>
@@ -15940,7 +15832,7 @@
     <row r="451" ht="30" customHeight="1">
       <c r="A451" s="16" t="inlineStr">
         <is>
-          <t>FICHA 31: 102435</t>
+          <t>FICHA 31: 17534</t>
         </is>
       </c>
       <c r="B451" s="17" t="n"/>
@@ -15973,7 +15865,7 @@
       </c>
       <c r="B453" s="19" t="inlineStr">
         <is>
-          <t>Is there any practical guidance on the implementation of the requirement for proposals to allocate at least 0.8% of their budget for engaging with the Horizon Europe-funded ‘New European Bauhaus hub for results and impact’?</t>
+          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, should the lighthouse demonstrator address all three core values of the New European Bauhaus or just one?</t>
         </is>
       </c>
       <c r="C453" s="20" t="n"/>
@@ -15989,7 +15881,7 @@
       </c>
       <c r="B454" s="19" t="inlineStr">
         <is>
-          <t>102435</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="C454" s="20" t="n"/>
@@ -16089,7 +15981,7 @@
       </c>
       <c r="B461" s="19" t="inlineStr">
         <is>
-          <t>Is there any practical guidance on the implementation of the requirement for proposals to allocate at least 0.8% of their budget for engaging with the Horizon Europe-funded ‘New European Bauhaus hub for results and impact’?</t>
+          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01-01, should the lighthouse demonstrator address all three core values of the New European Bauhaus or just one?</t>
         </is>
       </c>
       <c r="C461" s="20" t="n"/>
@@ -16133,7 +16025,7 @@
       </c>
       <c r="B464" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/102435</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17534</t>
         </is>
       </c>
       <c r="C464" s="20" t="n"/>
@@ -16144,7 +16036,7 @@
     <row r="466" ht="30" customHeight="1">
       <c r="A466" s="16" t="inlineStr">
         <is>
-          <t>FICHA 32: 21710</t>
+          <t>FICHA 32: 102435</t>
         </is>
       </c>
       <c r="B466" s="17" t="n"/>
@@ -16177,7 +16069,7 @@
       </c>
       <c r="B468" s="19" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-HLTH-2023-ENVHLTH-02-02, how should proposals contribute to the New European Bauhaus (NEB) initiative? How and with whom concretely should they interact, and what kind of activities are expected?</t>
+          <t>Is there any practical guidance on the implementation of the requirement for proposals to allocate at least 0.8% of their budget for engaging with the Horizon Europe-funded ‘New European Bauhaus hub for results and impact’?</t>
         </is>
       </c>
       <c r="C468" s="20" t="n"/>
@@ -16193,7 +16085,7 @@
       </c>
       <c r="B469" s="19" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>102435</t>
         </is>
       </c>
       <c r="C469" s="20" t="n"/>
@@ -16293,7 +16185,7 @@
       </c>
       <c r="B476" s="19" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-HLTH-2023-ENVHLTH-02-02, how should proposals contribute to the New European Bauhaus (NEB) initiative? How and with whom concretely should they interact, and what kind of activities are expected?</t>
+          <t>Is there any practical guidance on the implementation of the requirement for proposals to allocate at least 0.8% of their budget for engaging with the Horizon Europe-funded ‘New European Bauhaus hub for results and impact’?</t>
         </is>
       </c>
       <c r="C476" s="20" t="n"/>
@@ -16337,7 +16229,7 @@
       </c>
       <c r="B479" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/21710</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/102435</t>
         </is>
       </c>
       <c r="C479" s="20" t="n"/>
@@ -16348,7 +16240,7 @@
     <row r="481" ht="30" customHeight="1">
       <c r="A481" s="16" t="inlineStr">
         <is>
-          <t>FICHA 33: c36effc6-e7b0-423c-93a5-2b74a21546c0-EXA</t>
+          <t>FICHA 33: 21710</t>
         </is>
       </c>
       <c r="B481" s="17" t="n"/>
@@ -16381,7 +16273,7 @@
       </c>
       <c r="B483" s="19" t="inlineStr">
         <is>
-          <t>EEA/SUN/25/001- Clean tech production in Europe: implications for quality jobs and a just transition</t>
+          <t>Under topic HORIZON-HLTH-2023-ENVHLTH-02-02, how should proposals contribute to the New European Bauhaus (NEB) initiative? How and with whom concretely should they interact, and what kind of activities are expected?</t>
         </is>
       </c>
       <c r="C483" s="20" t="n"/>
@@ -16397,7 +16289,7 @@
       </c>
       <c r="B484" s="19" t="inlineStr">
         <is>
-          <t>c36effc6-e7b0-423c-93a5-2b74a21546c0-EXA</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="C484" s="20" t="n"/>
@@ -16483,11 +16375,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B490" s="19" t="inlineStr">
-        <is>
-          <t>EEA/2025/MVP/0001-EXA</t>
-        </is>
-      </c>
+      <c r="B490" s="19" t="inlineStr"/>
       <c r="C490" s="20" t="n"/>
       <c r="D490" s="20" t="n"/>
       <c r="E490" s="20" t="n"/>
@@ -16501,7 +16389,7 @@
       </c>
       <c r="B491" s="19" t="inlineStr">
         <is>
-          <t>EEA/SUN/25/001- Clean tech production in Europe: implications for quality jobs and a just transition</t>
+          <t>Under topic HORIZON-HLTH-2023-ENVHLTH-02-02, how should proposals contribute to the New European Bauhaus (NEB) initiative? How and with whom concretely should they interact, and what kind of activities are expected?</t>
         </is>
       </c>
       <c r="C491" s="20" t="n"/>
@@ -16521,15 +16409,15 @@
       <c r="E492" s="20" t="n"/>
       <c r="F492" s="20" t="n"/>
     </row>
-    <row r="493" ht="20" customHeight="1">
+    <row r="493" ht="45" customHeight="1">
       <c r="A493" s="18" t="inlineStr">
         <is>
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B493" s="19" t="inlineStr">
-        <is>
-          <t>MEDIA — Margen izquierda con pasado industrial. Potencial reconversión.</t>
+      <c r="B493" s="21" t="inlineStr">
+        <is>
+          <t>ALTA — NEB combina sostenibilidad + diseño + inclusion. Ideal para regeneracion urbana Bilbao (Zorrotzaurre, Casco Viejo).</t>
         </is>
       </c>
       <c r="C493" s="20" t="n"/>
@@ -16545,7 +16433,7 @@
       </c>
       <c r="B494" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c36effc6-e7b0-423c-93a5-2b74a21546c0-EXA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/21710</t>
         </is>
       </c>
       <c r="C494" s="20" t="n"/>
@@ -16556,7 +16444,7 @@
     <row r="496" ht="30" customHeight="1">
       <c r="A496" s="16" t="inlineStr">
         <is>
-          <t>FICHA 34: 16662</t>
+          <t>FICHA 34: c36effc6-e7b0-423c-93a5-2b74a21546c0-EXA</t>
         </is>
       </c>
       <c r="B496" s="17" t="n"/>
@@ -16589,7 +16477,7 @@
       </c>
       <c r="B498" s="19" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, our proposed action concerns the construction of infrastructure. It will be implemented by a private company which is not a project promoter. Can this company apply for a CEF Energy grant and still receive funding?</t>
+          <t>EEA/SUN/25/001- Clean tech production in Europe: implications for quality jobs and a just transition</t>
         </is>
       </c>
       <c r="C498" s="20" t="n"/>
@@ -16605,7 +16493,7 @@
       </c>
       <c r="B499" s="19" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>c36effc6-e7b0-423c-93a5-2b74a21546c0-EXA</t>
         </is>
       </c>
       <c r="C499" s="20" t="n"/>
@@ -16691,7 +16579,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B505" s="19" t="inlineStr"/>
+      <c r="B505" s="19" t="inlineStr">
+        <is>
+          <t>EEA/2025/MVP/0001-EXA</t>
+        </is>
+      </c>
       <c r="C505" s="20" t="n"/>
       <c r="D505" s="20" t="n"/>
       <c r="E505" s="20" t="n"/>
@@ -16705,7 +16597,7 @@
       </c>
       <c r="B506" s="19" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, our proposed action concerns the construction of infrastructure. It will be implemented by a private company which is not a project promoter. Can this company apply for a CEF Energy grant and still receive funding?</t>
+          <t>EEA/SUN/25/001- Clean tech production in Europe: implications for quality jobs and a just transition</t>
         </is>
       </c>
       <c r="C506" s="20" t="n"/>
@@ -16733,7 +16625,7 @@
       </c>
       <c r="B508" s="19" t="inlineStr">
         <is>
-          <t>MEDIA — Infraestructuras energéticas del País Vasco potencialmente elegibles.</t>
+          <t>MEDIA — Margen izquierda con pasado industrial. Potencial reconversión.</t>
         </is>
       </c>
       <c r="C508" s="20" t="n"/>
@@ -16749,7 +16641,7 @@
       </c>
       <c r="B509" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16662</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/c36effc6-e7b0-423c-93a5-2b74a21546c0-EXA</t>
         </is>
       </c>
       <c r="C509" s="20" t="n"/>
@@ -16760,7 +16652,7 @@
     <row r="511" ht="30" customHeight="1">
       <c r="A511" s="16" t="inlineStr">
         <is>
-          <t>FICHA 35: 326952ANNOUNCEMENTen</t>
+          <t>FICHA 35: 16662</t>
         </is>
       </c>
       <c r="B511" s="17" t="n"/>
@@ -16785,7 +16677,7 @@
       <c r="E512" s="20" t="n"/>
       <c r="F512" s="20" t="n"/>
     </row>
-    <row r="513" ht="20" customHeight="1">
+    <row r="513" ht="45" customHeight="1">
       <c r="A513" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -16793,7 +16685,7 @@
       </c>
       <c r="B513" s="19" t="inlineStr">
         <is>
-          <t>Hydrogen cities</t>
+          <t>Under Call CEF-E-PCI-PMI, our proposed action concerns the construction of infrastructure. It will be implemented by a private company which is not a project promoter. Can this company apply for a CEF Energy grant and still receive funding?</t>
         </is>
       </c>
       <c r="C513" s="20" t="n"/>
@@ -16809,7 +16701,7 @@
       </c>
       <c r="B514" s="19" t="inlineStr">
         <is>
-          <t>326952ANNOUNCEMENTen</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="C514" s="20" t="n"/>
@@ -16901,7 +16793,7 @@
       <c r="E520" s="20" t="n"/>
       <c r="F520" s="20" t="n"/>
     </row>
-    <row r="521" ht="20" customHeight="1">
+    <row r="521" ht="45" customHeight="1">
       <c r="A521" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -16909,7 +16801,7 @@
       </c>
       <c r="B521" s="19" t="inlineStr">
         <is>
-          <t>Hydrogen cities</t>
+          <t>Under Call CEF-E-PCI-PMI, our proposed action concerns the construction of infrastructure. It will be implemented by a private company which is not a project promoter. Can this company apply for a CEF Energy grant and still receive funding?</t>
         </is>
       </c>
       <c r="C521" s="20" t="n"/>
@@ -16937,7 +16829,7 @@
       </c>
       <c r="B523" s="19" t="inlineStr">
         <is>
-          <t>MEDIA — Corredor Vasco del Hidrógeno. Petronor y Puerto de Bilbao involucrados.</t>
+          <t>MEDIA — Infraestructuras energéticas del País Vasco potencialmente elegibles.</t>
         </is>
       </c>
       <c r="C523" s="20" t="n"/>
@@ -16953,7 +16845,7 @@
       </c>
       <c r="B524" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/326952ANNOUNCEMENTen</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16662</t>
         </is>
       </c>
       <c r="C524" s="20" t="n"/>
@@ -16964,7 +16856,7 @@
     <row r="526" ht="30" customHeight="1">
       <c r="A526" s="16" t="inlineStr">
         <is>
-          <t>FICHA 36: 328464ANNOUNCEMENTen</t>
+          <t>FICHA 36: 326952ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B526" s="17" t="n"/>
@@ -17013,7 +16905,7 @@
       </c>
       <c r="B529" s="19" t="inlineStr">
         <is>
-          <t>328464ANNOUNCEMENTen</t>
+          <t>326952ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C529" s="20" t="n"/>
@@ -17157,7 +17049,7 @@
       </c>
       <c r="B539" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/328464ANNOUNCEMENTen</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/326952ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C539" s="20" t="n"/>
@@ -17168,7 +17060,7 @@
     <row r="541" ht="30" customHeight="1">
       <c r="A541" s="16" t="inlineStr">
         <is>
-          <t>FICHA 37: 330857ANNOUNCEMENTen</t>
+          <t>FICHA 37: 328464ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B541" s="17" t="n"/>
@@ -17217,7 +17109,7 @@
       </c>
       <c r="B544" s="19" t="inlineStr">
         <is>
-          <t>330857ANNOUNCEMENTen</t>
+          <t>328464ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C544" s="20" t="n"/>
@@ -17361,7 +17253,7 @@
       </c>
       <c r="B554" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/330857ANNOUNCEMENTen</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/328464ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C554" s="20" t="n"/>
@@ -17372,7 +17264,7 @@
     <row r="556" ht="30" customHeight="1">
       <c r="A556" s="16" t="inlineStr">
         <is>
-          <t>FICHA 38: 333297ANNOUNCEMENTen</t>
+          <t>FICHA 38: 330857ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B556" s="17" t="n"/>
@@ -17421,7 +17313,7 @@
       </c>
       <c r="B559" s="19" t="inlineStr">
         <is>
-          <t>333297ANNOUNCEMENTen</t>
+          <t>330857ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C559" s="20" t="n"/>
@@ -17565,7 +17457,7 @@
       </c>
       <c r="B569" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/333297ANNOUNCEMENTen</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/330857ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C569" s="20" t="n"/>
@@ -17576,7 +17468,7 @@
     <row r="571" ht="30" customHeight="1">
       <c r="A571" s="16" t="inlineStr">
         <is>
-          <t>FICHA 39: 335155ANNOUNCEMENTen</t>
+          <t>FICHA 39: 333297ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B571" s="17" t="n"/>
@@ -17625,7 +17517,7 @@
       </c>
       <c r="B574" s="19" t="inlineStr">
         <is>
-          <t>335155ANNOUNCEMENTen</t>
+          <t>333297ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C574" s="20" t="n"/>
@@ -17769,7 +17661,7 @@
       </c>
       <c r="B584" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/335155ANNOUNCEMENTen</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/333297ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C584" s="20" t="n"/>
@@ -17780,7 +17672,7 @@
     <row r="586" ht="30" customHeight="1">
       <c r="A586" s="16" t="inlineStr">
         <is>
-          <t>FICHA 40: 338237ANNOUNCEMENTen</t>
+          <t>FICHA 40: 335155ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B586" s="17" t="n"/>
@@ -17829,7 +17721,7 @@
       </c>
       <c r="B589" s="19" t="inlineStr">
         <is>
-          <t>338237ANNOUNCEMENTen</t>
+          <t>335155ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C589" s="20" t="n"/>
@@ -17973,7 +17865,7 @@
       </c>
       <c r="B599" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/338237ANNOUNCEMENTen</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/335155ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C599" s="20" t="n"/>
@@ -17984,7 +17876,7 @@
     <row r="601" ht="30" customHeight="1">
       <c r="A601" s="16" t="inlineStr">
         <is>
-          <t>FICHA 41: 339612ANNOUNCEMENTen</t>
+          <t>FICHA 41: 338237ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B601" s="17" t="n"/>
@@ -18033,7 +17925,7 @@
       </c>
       <c r="B604" s="19" t="inlineStr">
         <is>
-          <t>339612ANNOUNCEMENTen</t>
+          <t>338237ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C604" s="20" t="n"/>
@@ -18177,7 +18069,7 @@
       </c>
       <c r="B614" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/339612ANNOUNCEMENTen</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/338237ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C614" s="20" t="n"/>
@@ -18188,7 +18080,7 @@
     <row r="616" ht="30" customHeight="1">
       <c r="A616" s="16" t="inlineStr">
         <is>
-          <t>FICHA 42: 343814ANNOUNCEMENTen</t>
+          <t>FICHA 42: 339612ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B616" s="17" t="n"/>
@@ -18237,7 +18129,7 @@
       </c>
       <c r="B619" s="19" t="inlineStr">
         <is>
-          <t>343814ANNOUNCEMENTen</t>
+          <t>339612ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C619" s="20" t="n"/>
@@ -18381,7 +18273,7 @@
       </c>
       <c r="B629" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/343814ANNOUNCEMENTen</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/339612ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C629" s="20" t="n"/>
@@ -18392,7 +18284,7 @@
     <row r="631" ht="30" customHeight="1">
       <c r="A631" s="16" t="inlineStr">
         <is>
-          <t>FICHA 43: 328462ANNOUNCEMENTen</t>
+          <t>FICHA 43: 343814ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B631" s="17" t="n"/>
@@ -18441,7 +18333,7 @@
       </c>
       <c r="B634" s="19" t="inlineStr">
         <is>
-          <t>328462ANNOUNCEMENTen</t>
+          <t>343814ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C634" s="20" t="n"/>
@@ -18585,7 +18477,7 @@
       </c>
       <c r="B644" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/328462ANNOUNCEMENTen</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/343814ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C644" s="20" t="n"/>
@@ -18596,7 +18488,7 @@
     <row r="646" ht="30" customHeight="1">
       <c r="A646" s="16" t="inlineStr">
         <is>
-          <t>FICHA 44: 328461ANNOUNCEMENTen</t>
+          <t>FICHA 44: 328462ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B646" s="17" t="n"/>
@@ -18645,7 +18537,7 @@
       </c>
       <c r="B649" s="19" t="inlineStr">
         <is>
-          <t>328461ANNOUNCEMENTen</t>
+          <t>328462ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C649" s="20" t="n"/>
@@ -18789,7 +18681,7 @@
       </c>
       <c r="B659" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/328461ANNOUNCEMENTen</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/328462ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C659" s="20" t="n"/>
@@ -18800,7 +18692,7 @@
     <row r="661" ht="30" customHeight="1">
       <c r="A661" s="16" t="inlineStr">
         <is>
-          <t>FICHA 45: 345032ANNOUNCEMENTen</t>
+          <t>FICHA 45: 328461ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B661" s="17" t="n"/>
@@ -18849,7 +18741,7 @@
       </c>
       <c r="B664" s="19" t="inlineStr">
         <is>
-          <t>345032ANNOUNCEMENTen</t>
+          <t>328461ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C664" s="20" t="n"/>
@@ -18993,7 +18885,7 @@
       </c>
       <c r="B674" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/345032ANNOUNCEMENTen</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/328461ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="C674" s="20" t="n"/>
@@ -20856,7 +20748,7 @@
     <row r="811" ht="30" customHeight="1">
       <c r="A811" s="16" t="inlineStr">
         <is>
-          <t>FICHA 55: ERASMUS2027</t>
+          <t>FICHA 55: HORIZON</t>
         </is>
       </c>
       <c r="B811" s="17" t="n"/>
@@ -20889,7 +20781,7 @@
       </c>
       <c r="B813" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C813" s="20" t="n"/>
@@ -20905,7 +20797,7 @@
       </c>
       <c r="B814" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C814" s="20" t="n"/>
@@ -20919,7 +20811,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B815" s="19" t="inlineStr"/>
+      <c r="B815" s="19" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="C815" s="20" t="n"/>
       <c r="D815" s="20" t="n"/>
       <c r="E815" s="20" t="n"/>
@@ -20993,7 +20889,7 @@
       </c>
       <c r="B820" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
+          <t>HORIZON-MISS-2021-CIT-02</t>
         </is>
       </c>
       <c r="C820" s="20" t="n"/>
@@ -21009,7 +20905,7 @@
       </c>
       <c r="B821" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C821" s="20" t="n"/>
@@ -21053,7 +20949,7 @@
       </c>
       <c r="B824" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
         </is>
       </c>
       <c r="C824" s="20" t="n"/>
@@ -21064,7 +20960,7 @@
     <row r="826" ht="30" customHeight="1">
       <c r="A826" s="16" t="inlineStr">
         <is>
-          <t>FICHA 56: HORIZON</t>
+          <t>FICHA 56: ERASMUS2027</t>
         </is>
       </c>
       <c r="B826" s="17" t="n"/>
@@ -21097,7 +20993,7 @@
       </c>
       <c r="B828" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C828" s="20" t="n"/>
@@ -21113,7 +21009,7 @@
       </c>
       <c r="B829" s="19" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C829" s="20" t="n"/>
@@ -21127,11 +21023,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B830" s="19" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+      <c r="B830" s="19" t="inlineStr"/>
       <c r="C830" s="20" t="n"/>
       <c r="D830" s="20" t="n"/>
       <c r="E830" s="20" t="n"/>
@@ -21205,7 +21097,7 @@
       </c>
       <c r="B835" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2021-CIT-02</t>
+          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
         </is>
       </c>
       <c r="C835" s="20" t="n"/>
@@ -21221,7 +21113,7 @@
       </c>
       <c r="B836" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C836" s="20" t="n"/>
@@ -21265,7 +21157,7 @@
       </c>
       <c r="B839" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
         </is>
       </c>
       <c r="C839" s="20" t="n"/>
@@ -21892,7 +21784,7 @@
     <row r="886" ht="30" customHeight="1">
       <c r="A886" s="16" t="inlineStr">
         <is>
-          <t>FICHA 60: 5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
+          <t>FICHA 60: 50912</t>
         </is>
       </c>
       <c r="B886" s="17" t="n"/>
@@ -21917,7 +21809,7 @@
       <c r="E887" s="20" t="n"/>
       <c r="F887" s="20" t="n"/>
     </row>
-    <row r="888" ht="20" customHeight="1">
+    <row r="888" ht="45" customHeight="1">
       <c r="A888" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -21925,7 +21817,7 @@
       </c>
       <c r="B888" s="19" t="inlineStr">
         <is>
-          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="C888" s="20" t="n"/>
@@ -21941,7 +21833,7 @@
       </c>
       <c r="B889" s="19" t="inlineStr">
         <is>
-          <t>5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="C889" s="20" t="n"/>
@@ -22027,17 +21919,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B895" s="19" t="inlineStr">
-        <is>
-          <t>NEAR/IEV/2021/EA-RP/0041</t>
-        </is>
-      </c>
+      <c r="B895" s="19" t="inlineStr"/>
       <c r="C895" s="20" t="n"/>
       <c r="D895" s="20" t="n"/>
       <c r="E895" s="20" t="n"/>
       <c r="F895" s="20" t="n"/>
     </row>
-    <row r="896" ht="20" customHeight="1">
+    <row r="896" ht="45" customHeight="1">
       <c r="A896" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -22045,7 +21933,7 @@
       </c>
       <c r="B896" s="19" t="inlineStr">
         <is>
-          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
         </is>
       </c>
       <c r="C896" s="20" t="n"/>
@@ -22089,7 +21977,7 @@
       </c>
       <c r="B899" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/50912</t>
         </is>
       </c>
       <c r="C899" s="20" t="n"/>
@@ -22100,7 +21988,7 @@
     <row r="901" ht="30" customHeight="1">
       <c r="A901" s="16" t="inlineStr">
         <is>
-          <t>FICHA 61: 50912</t>
+          <t>FICHA 61: CEF2027</t>
         </is>
       </c>
       <c r="B901" s="17" t="n"/>
@@ -22125,7 +22013,7 @@
       <c r="E902" s="20" t="n"/>
       <c r="F902" s="20" t="n"/>
     </row>
-    <row r="903" ht="45" customHeight="1">
+    <row r="903" ht="20" customHeight="1">
       <c r="A903" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -22133,7 +22021,7 @@
       </c>
       <c r="B903" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="C903" s="20" t="n"/>
@@ -22149,7 +22037,7 @@
       </c>
       <c r="B904" s="19" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="C904" s="20" t="n"/>
@@ -22163,7 +22051,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B905" s="19" t="inlineStr"/>
+      <c r="B905" s="19" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="C905" s="20" t="n"/>
       <c r="D905" s="20" t="n"/>
       <c r="E905" s="20" t="n"/>
@@ -22235,13 +22127,17 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B910" s="19" t="inlineStr"/>
+      <c r="B910" s="19" t="inlineStr">
+        <is>
+          <t>CEF-T-2024-AFIFGEN</t>
+        </is>
+      </c>
       <c r="C910" s="20" t="n"/>
       <c r="D910" s="20" t="n"/>
       <c r="E910" s="20" t="n"/>
       <c r="F910" s="20" t="n"/>
     </row>
-    <row r="911" ht="45" customHeight="1">
+    <row r="911" ht="20" customHeight="1">
       <c r="A911" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -22249,7 +22145,7 @@
       </c>
       <c r="B911" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics under “Mission: Adaptation to Climate Change” which cover climate urban stress and related extreme heat?</t>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
         </is>
       </c>
       <c r="C911" s="20" t="n"/>
@@ -22293,7 +22189,7 @@
       </c>
       <c r="B914" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/50912</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF2027</t>
         </is>
       </c>
       <c r="C914" s="20" t="n"/>
@@ -22304,7 +22200,7 @@
     <row r="916" ht="30" customHeight="1">
       <c r="A916" s="16" t="inlineStr">
         <is>
-          <t>FICHA 62: CEF2027</t>
+          <t>FICHA 62: 19484</t>
         </is>
       </c>
       <c r="B916" s="17" t="n"/>
@@ -22329,7 +22225,7 @@
       <c r="E917" s="20" t="n"/>
       <c r="F917" s="20" t="n"/>
     </row>
-    <row r="918" ht="20" customHeight="1">
+    <row r="918" ht="45" customHeight="1">
       <c r="A918" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -22337,7 +22233,7 @@
       </c>
       <c r="B918" s="19" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
         </is>
       </c>
       <c r="C918" s="20" t="n"/>
@@ -22353,7 +22249,7 @@
       </c>
       <c r="B919" s="19" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="C919" s="20" t="n"/>
@@ -22367,11 +22263,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B920" s="19" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+      <c r="B920" s="19" t="inlineStr"/>
       <c r="C920" s="20" t="n"/>
       <c r="D920" s="20" t="n"/>
       <c r="E920" s="20" t="n"/>
@@ -22443,17 +22335,13 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B925" s="19" t="inlineStr">
-        <is>
-          <t>CEF-T-2024-AFIFGEN</t>
-        </is>
-      </c>
+      <c r="B925" s="19" t="inlineStr"/>
       <c r="C925" s="20" t="n"/>
       <c r="D925" s="20" t="n"/>
       <c r="E925" s="20" t="n"/>
       <c r="F925" s="20" t="n"/>
     </row>
-    <row r="926" ht="20" customHeight="1">
+    <row r="926" ht="45" customHeight="1">
       <c r="A926" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -22461,7 +22349,7 @@
       </c>
       <c r="B926" s="19" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
         </is>
       </c>
       <c r="C926" s="20" t="n"/>
@@ -22505,7 +22393,7 @@
       </c>
       <c r="B929" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19484</t>
         </is>
       </c>
       <c r="C929" s="20" t="n"/>
@@ -22516,7 +22404,7 @@
     <row r="931" ht="30" customHeight="1">
       <c r="A931" s="16" t="inlineStr">
         <is>
-          <t>FICHA 63: 19484</t>
+          <t>FICHA 63: 915513452</t>
         </is>
       </c>
       <c r="B931" s="17" t="n"/>
@@ -22541,7 +22429,7 @@
       <c r="E932" s="20" t="n"/>
       <c r="F932" s="20" t="n"/>
     </row>
-    <row r="933" ht="45" customHeight="1">
+    <row r="933" ht="20" customHeight="1">
       <c r="A933" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -22549,7 +22437,7 @@
       </c>
       <c r="B933" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C933" s="20" t="n"/>
@@ -22565,7 +22453,7 @@
       </c>
       <c r="B934" s="19" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="C934" s="20" t="n"/>
@@ -22657,7 +22545,7 @@
       <c r="E940" s="20" t="n"/>
       <c r="F940" s="20" t="n"/>
     </row>
-    <row r="941" ht="45" customHeight="1">
+    <row r="941" ht="20" customHeight="1">
       <c r="A941" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -22665,7 +22553,7 @@
       </c>
       <c r="B941" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from several partners under the “zero emissions” topic consisting of recharging infrastructure for port vehicles and equipment, public transport in TEN-T urban nodes and airport ground operations?</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C941" s="20" t="n"/>
@@ -22709,7 +22597,7 @@
       </c>
       <c r="B944" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19484</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/915513452</t>
         </is>
       </c>
       <c r="C944" s="20" t="n"/>
@@ -22720,7 +22608,7 @@
     <row r="946" ht="30" customHeight="1">
       <c r="A946" s="16" t="inlineStr">
         <is>
-          <t>FICHA 64: 915513452</t>
+          <t>FICHA 64: 40556</t>
         </is>
       </c>
       <c r="B946" s="17" t="n"/>
@@ -22745,7 +22633,7 @@
       <c r="E947" s="20" t="n"/>
       <c r="F947" s="20" t="n"/>
     </row>
-    <row r="948" ht="20" customHeight="1">
+    <row r="948" ht="45" customHeight="1">
       <c r="A948" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -22753,7 +22641,7 @@
       </c>
       <c r="B948" s="19" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="C948" s="20" t="n"/>
@@ -22769,7 +22657,7 @@
       </c>
       <c r="B949" s="19" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="C949" s="20" t="n"/>
@@ -22861,7 +22749,7 @@
       <c r="E955" s="20" t="n"/>
       <c r="F955" s="20" t="n"/>
     </row>
-    <row r="956" ht="20" customHeight="1">
+    <row r="956" ht="45" customHeight="1">
       <c r="A956" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -22869,7 +22757,7 @@
       </c>
       <c r="B956" s="19" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
         </is>
       </c>
       <c r="C956" s="20" t="n"/>
@@ -22913,7 +22801,7 @@
       </c>
       <c r="B959" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/915513452</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/40556</t>
         </is>
       </c>
       <c r="C959" s="20" t="n"/>
@@ -22924,7 +22812,7 @@
     <row r="961" ht="30" customHeight="1">
       <c r="A961" s="16" t="inlineStr">
         <is>
-          <t>FICHA 65: 40556</t>
+          <t>FICHA 65: 917721754</t>
         </is>
       </c>
       <c r="B961" s="17" t="n"/>
@@ -22949,7 +22837,7 @@
       <c r="E962" s="20" t="n"/>
       <c r="F962" s="20" t="n"/>
     </row>
-    <row r="963" ht="45" customHeight="1">
+    <row r="963" ht="20" customHeight="1">
       <c r="A963" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -22957,7 +22845,7 @@
       </c>
       <c r="B963" s="19" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C963" s="20" t="n"/>
@@ -22973,7 +22861,7 @@
       </c>
       <c r="B964" s="19" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="C964" s="20" t="n"/>
@@ -23065,7 +22953,7 @@
       <c r="E970" s="20" t="n"/>
       <c r="F970" s="20" t="n"/>
     </row>
-    <row r="971" ht="45" customHeight="1">
+    <row r="971" ht="20" customHeight="1">
       <c r="A971" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -23073,7 +22961,7 @@
       </c>
       <c r="B971" s="19" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission transhipment equipment?</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C971" s="20" t="n"/>
@@ -23117,7 +23005,7 @@
       </c>
       <c r="B974" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/40556</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917721754</t>
         </is>
       </c>
       <c r="C974" s="20" t="n"/>
@@ -23128,7 +23016,7 @@
     <row r="976" ht="30" customHeight="1">
       <c r="A976" s="16" t="inlineStr">
         <is>
-          <t>FICHA 66: 917721754</t>
+          <t>FICHA 66: 919892711</t>
         </is>
       </c>
       <c r="B976" s="17" t="n"/>
@@ -23161,7 +23049,7 @@
       </c>
       <c r="B978" s="19" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="C978" s="20" t="n"/>
@@ -23177,7 +23065,7 @@
       </c>
       <c r="B979" s="19" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="C979" s="20" t="n"/>
@@ -23277,7 +23165,7 @@
       </c>
       <c r="B986" s="19" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
         </is>
       </c>
       <c r="C986" s="20" t="n"/>
@@ -23321,7 +23209,7 @@
       </c>
       <c r="B989" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917721754</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919892711</t>
         </is>
       </c>
       <c r="C989" s="20" t="n"/>
@@ -23332,7 +23220,7 @@
     <row r="991" ht="30" customHeight="1">
       <c r="A991" s="16" t="inlineStr">
         <is>
-          <t>FICHA 67: 919892711</t>
+          <t>FICHA 67: 939945909</t>
         </is>
       </c>
       <c r="B991" s="17" t="n"/>
@@ -23365,7 +23253,7 @@
       </c>
       <c r="B993" s="19" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C993" s="20" t="n"/>
@@ -23381,7 +23269,7 @@
       </c>
       <c r="B994" s="19" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="C994" s="20" t="n"/>
@@ -23481,7 +23369,7 @@
       </c>
       <c r="B1001" s="19" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKTER HAFTUNG</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C1001" s="20" t="n"/>
@@ -23525,7 +23413,7 @@
       </c>
       <c r="B1004" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919892711</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939945909</t>
         </is>
       </c>
       <c r="C1004" s="20" t="n"/>
@@ -23536,7 +23424,7 @@
     <row r="1006" ht="30" customHeight="1">
       <c r="A1006" s="16" t="inlineStr">
         <is>
-          <t>FICHA 68: 939945909</t>
+          <t>FICHA 68: 928447529</t>
         </is>
       </c>
       <c r="B1006" s="17" t="n"/>
@@ -23569,7 +23457,7 @@
       </c>
       <c r="B1008" s="19" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1008" s="20" t="n"/>
@@ -23585,7 +23473,7 @@
       </c>
       <c r="B1009" s="19" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C1009" s="20" t="n"/>
@@ -23685,7 +23573,7 @@
       </c>
       <c r="B1016" s="19" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1016" s="20" t="n"/>
@@ -23729,7 +23617,7 @@
       </c>
       <c r="B1019" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/939945909</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
         </is>
       </c>
       <c r="C1019" s="20" t="n"/>
@@ -23740,7 +23628,7 @@
     <row r="1021" ht="30" customHeight="1">
       <c r="A1021" s="16" t="inlineStr">
         <is>
-          <t>FICHA 69: 917779760</t>
+          <t>FICHA 69: 917671508</t>
         </is>
       </c>
       <c r="B1021" s="17" t="n"/>
@@ -23773,7 +23661,7 @@
       </c>
       <c r="B1023" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1023" s="20" t="n"/>
@@ -23789,7 +23677,7 @@
       </c>
       <c r="B1024" s="19" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C1024" s="20" t="n"/>
@@ -23889,7 +23777,7 @@
       </c>
       <c r="B1031" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1031" s="20" t="n"/>
@@ -23933,7 +23821,7 @@
       </c>
       <c r="B1034" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
         </is>
       </c>
       <c r="C1034" s="20" t="n"/>
@@ -23944,7 +23832,7 @@
     <row r="1036" ht="30" customHeight="1">
       <c r="A1036" s="16" t="inlineStr">
         <is>
-          <t>FICHA 70: 920115617</t>
+          <t>FICHA 70: 917779760</t>
         </is>
       </c>
       <c r="B1036" s="17" t="n"/>
@@ -23977,7 +23865,7 @@
       </c>
       <c r="B1038" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1038" s="20" t="n"/>
@@ -23993,7 +23881,7 @@
       </c>
       <c r="B1039" s="19" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C1039" s="20" t="n"/>
@@ -24093,7 +23981,7 @@
       </c>
       <c r="B1046" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1046" s="20" t="n"/>
@@ -24137,7 +24025,7 @@
       </c>
       <c r="B1049" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
         </is>
       </c>
       <c r="C1049" s="20" t="n"/>
@@ -24148,7 +24036,7 @@
     <row r="1051" ht="30" customHeight="1">
       <c r="A1051" s="16" t="inlineStr">
         <is>
-          <t>FICHA 71: 917671508</t>
+          <t>FICHA 71: 920115617</t>
         </is>
       </c>
       <c r="B1051" s="17" t="n"/>
@@ -24181,7 +24069,7 @@
       </c>
       <c r="B1053" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1053" s="20" t="n"/>
@@ -24197,7 +24085,7 @@
       </c>
       <c r="B1054" s="19" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C1054" s="20" t="n"/>
@@ -24297,7 +24185,7 @@
       </c>
       <c r="B1061" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1061" s="20" t="n"/>
@@ -24341,7 +24229,7 @@
       </c>
       <c r="B1064" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
         </is>
       </c>
       <c r="C1064" s="20" t="n"/>
@@ -24352,7 +24240,7 @@
     <row r="1066" ht="30" customHeight="1">
       <c r="A1066" s="16" t="inlineStr">
         <is>
-          <t>FICHA 72: 928447529</t>
+          <t>FICHA 72: 14272</t>
         </is>
       </c>
       <c r="B1066" s="17" t="n"/>
@@ -24377,7 +24265,7 @@
       <c r="E1067" s="20" t="n"/>
       <c r="F1067" s="20" t="n"/>
     </row>
-    <row r="1068" ht="20" customHeight="1">
+    <row r="1068" ht="45" customHeight="1">
       <c r="A1068" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -24385,7 +24273,7 @@
       </c>
       <c r="B1068" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="C1068" s="20" t="n"/>
@@ -24401,7 +24289,7 @@
       </c>
       <c r="B1069" s="19" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="C1069" s="20" t="n"/>
@@ -24493,7 +24381,7 @@
       <c r="E1075" s="20" t="n"/>
       <c r="F1075" s="20" t="n"/>
     </row>
-    <row r="1076" ht="20" customHeight="1">
+    <row r="1076" ht="45" customHeight="1">
       <c r="A1076" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -24501,7 +24389,7 @@
       </c>
       <c r="B1076" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
         </is>
       </c>
       <c r="C1076" s="20" t="n"/>
@@ -24545,7 +24433,7 @@
       </c>
       <c r="B1079" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14272</t>
         </is>
       </c>
       <c r="C1079" s="20" t="n"/>
@@ -24556,7 +24444,7 @@
     <row r="1081" ht="30" customHeight="1">
       <c r="A1081" s="16" t="inlineStr">
         <is>
-          <t>FICHA 73: 14272</t>
+          <t>FICHA 73: 996889759</t>
         </is>
       </c>
       <c r="B1081" s="17" t="n"/>
@@ -24581,7 +24469,7 @@
       <c r="E1082" s="20" t="n"/>
       <c r="F1082" s="20" t="n"/>
     </row>
-    <row r="1083" ht="45" customHeight="1">
+    <row r="1083" ht="20" customHeight="1">
       <c r="A1083" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -24589,7 +24477,7 @@
       </c>
       <c r="B1083" s="19" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C1083" s="20" t="n"/>
@@ -24605,7 +24493,7 @@
       </c>
       <c r="B1084" s="19" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="C1084" s="20" t="n"/>
@@ -24697,7 +24585,7 @@
       <c r="E1090" s="20" t="n"/>
       <c r="F1090" s="20" t="n"/>
     </row>
-    <row r="1091" ht="45" customHeight="1">
+    <row r="1091" ht="20" customHeight="1">
       <c r="A1091" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -24705,7 +24593,7 @@
       </c>
       <c r="B1091" s="19" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic LC-GD-4-1-2020, what is meant by ‘zero-emission/zero-pollution’?</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C1091" s="20" t="n"/>
@@ -24749,7 +24637,7 @@
       </c>
       <c r="B1094" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14272</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/996889759</t>
         </is>
       </c>
       <c r="C1094" s="20" t="n"/>
@@ -24760,7 +24648,7 @@
     <row r="1096" ht="30" customHeight="1">
       <c r="A1096" s="16" t="inlineStr">
         <is>
-          <t>FICHA 74: 996889759</t>
+          <t>FICHA 74: 922165518</t>
         </is>
       </c>
       <c r="B1096" s="17" t="n"/>
@@ -24793,7 +24681,7 @@
       </c>
       <c r="B1098" s="19" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C1098" s="20" t="n"/>
@@ -24809,7 +24697,7 @@
       </c>
       <c r="B1099" s="19" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="C1099" s="20" t="n"/>
@@ -24909,7 +24797,7 @@
       </c>
       <c r="B1106" s="19" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C1106" s="20" t="n"/>
@@ -24953,7 +24841,7 @@
       </c>
       <c r="B1109" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/996889759</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/922165518</t>
         </is>
       </c>
       <c r="C1109" s="20" t="n"/>
@@ -24964,7 +24852,7 @@
     <row r="1111" ht="30" customHeight="1">
       <c r="A1111" s="16" t="inlineStr">
         <is>
-          <t>FICHA 75: 922165518</t>
+          <t>FICHA 75: 919917446</t>
         </is>
       </c>
       <c r="B1111" s="17" t="n"/>
@@ -24997,7 +24885,7 @@
       </c>
       <c r="B1113" s="19" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C1113" s="20" t="n"/>
@@ -25013,7 +24901,7 @@
       </c>
       <c r="B1114" s="19" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="C1114" s="20" t="n"/>
@@ -25113,7 +25001,7 @@
       </c>
       <c r="B1121" s="19" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C1121" s="20" t="n"/>
@@ -25157,7 +25045,7 @@
       </c>
       <c r="B1124" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/922165518</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919917446</t>
         </is>
       </c>
       <c r="C1124" s="20" t="n"/>
@@ -25168,7 +25056,7 @@
     <row r="1126" ht="30" customHeight="1">
       <c r="A1126" s="16" t="inlineStr">
         <is>
-          <t>FICHA 76: 919917446</t>
+          <t>FICHA 76: 917155468</t>
         </is>
       </c>
       <c r="B1126" s="17" t="n"/>
@@ -25201,7 +25089,7 @@
       </c>
       <c r="B1128" s="19" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C1128" s="20" t="n"/>
@@ -25217,7 +25105,7 @@
       </c>
       <c r="B1129" s="19" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="C1129" s="20" t="n"/>
@@ -25317,7 +25205,7 @@
       </c>
       <c r="B1136" s="19" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C1136" s="20" t="n"/>
@@ -25361,7 +25249,7 @@
       </c>
       <c r="B1139" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/919917446</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917155468</t>
         </is>
       </c>
       <c r="C1139" s="20" t="n"/>
@@ -25372,7 +25260,7 @@
     <row r="1141" ht="30" customHeight="1">
       <c r="A1141" s="16" t="inlineStr">
         <is>
-          <t>FICHA 77: 917155468</t>
+          <t>FICHA 77: 938191470</t>
         </is>
       </c>
       <c r="B1141" s="17" t="n"/>
@@ -25405,7 +25293,7 @@
       </c>
       <c r="B1143" s="19" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>IMS INDUSTRIE MECCANICHE SCARDELLATO SPA</t>
         </is>
       </c>
       <c r="C1143" s="20" t="n"/>
@@ -25421,7 +25309,7 @@
       </c>
       <c r="B1144" s="19" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>938191470</t>
         </is>
       </c>
       <c r="C1144" s="20" t="n"/>
@@ -25521,7 +25409,7 @@
       </c>
       <c r="B1151" s="19" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>IMS INDUSTRIE MECCANICHE SCARDELLATO SPA</t>
         </is>
       </c>
       <c r="C1151" s="20" t="n"/>
@@ -25565,7 +25453,7 @@
       </c>
       <c r="B1154" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917155468</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/938191470</t>
         </is>
       </c>
       <c r="C1154" s="20" t="n"/>
@@ -36620,7 +36508,7 @@
     <row r="1966" ht="30" customHeight="1">
       <c r="A1966" s="16" t="inlineStr">
         <is>
-          <t>FICHA 132: 934294980</t>
+          <t>FICHA 132: 925388828</t>
         </is>
       </c>
       <c r="B1966" s="17" t="n"/>
@@ -36653,7 +36541,7 @@
       </c>
       <c r="B1968" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C1968" s="20" t="n"/>
@@ -36669,7 +36557,7 @@
       </c>
       <c r="B1969" s="19" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C1969" s="20" t="n"/>
@@ -36769,7 +36657,7 @@
       </c>
       <c r="B1976" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C1976" s="20" t="n"/>
@@ -36813,7 +36701,7 @@
       </c>
       <c r="B1979" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
         </is>
       </c>
       <c r="C1979" s="20" t="n"/>
@@ -36824,7 +36712,7 @@
     <row r="1981" ht="30" customHeight="1">
       <c r="A1981" s="16" t="inlineStr">
         <is>
-          <t>FICHA 133: 925388828</t>
+          <t>FICHA 133: 934294980</t>
         </is>
       </c>
       <c r="B1981" s="17" t="n"/>
@@ -36857,7 +36745,7 @@
       </c>
       <c r="B1983" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C1983" s="20" t="n"/>
@@ -36873,7 +36761,7 @@
       </c>
       <c r="B1984" s="19" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C1984" s="20" t="n"/>
@@ -36973,7 +36861,7 @@
       </c>
       <c r="B1991" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C1991" s="20" t="n"/>
@@ -37017,7 +36905,7 @@
       </c>
       <c r="B1994" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
         </is>
       </c>
       <c r="C1994" s="20" t="n"/>
@@ -39068,7 +38956,7 @@
     <row r="2146" ht="30" customHeight="1">
       <c r="A2146" s="16" t="inlineStr">
         <is>
-          <t>FICHA 144: 928211140</t>
+          <t>FICHA 144: 928057492</t>
         </is>
       </c>
       <c r="B2146" s="17" t="n"/>
@@ -39101,7 +38989,7 @@
       </c>
       <c r="B2148" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="C2148" s="20" t="n"/>
@@ -39117,7 +39005,7 @@
       </c>
       <c r="B2149" s="19" t="inlineStr">
         <is>
-          <t>928211140</t>
+          <t>928057492</t>
         </is>
       </c>
       <c r="C2149" s="20" t="n"/>
@@ -39217,7 +39105,7 @@
       </c>
       <c r="B2156" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="C2156" s="20" t="n"/>
@@ -39261,7 +39149,7 @@
       </c>
       <c r="B2159" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928211140</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928057492</t>
         </is>
       </c>
       <c r="C2159" s="20" t="n"/>
@@ -39272,7 +39160,7 @@
     <row r="2161" ht="30" customHeight="1">
       <c r="A2161" s="16" t="inlineStr">
         <is>
-          <t>FICHA 145: 928057492</t>
+          <t>FICHA 145: 926227393</t>
         </is>
       </c>
       <c r="B2161" s="17" t="n"/>
@@ -39305,7 +39193,7 @@
       </c>
       <c r="B2163" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="C2163" s="20" t="n"/>
@@ -39321,7 +39209,7 @@
       </c>
       <c r="B2164" s="19" t="inlineStr">
         <is>
-          <t>928057492</t>
+          <t>926227393</t>
         </is>
       </c>
       <c r="C2164" s="20" t="n"/>
@@ -39421,7 +39309,7 @@
       </c>
       <c r="B2171" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="C2171" s="20" t="n"/>
@@ -39465,7 +39353,7 @@
       </c>
       <c r="B2174" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928057492</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/926227393</t>
         </is>
       </c>
       <c r="C2174" s="20" t="n"/>
@@ -39476,7 +39364,7 @@
     <row r="2176" ht="30" customHeight="1">
       <c r="A2176" s="16" t="inlineStr">
         <is>
-          <t>FICHA 146: 926227393</t>
+          <t>FICHA 146: 928211140</t>
         </is>
       </c>
       <c r="B2176" s="17" t="n"/>
@@ -39509,7 +39397,7 @@
       </c>
       <c r="B2178" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="C2178" s="20" t="n"/>
@@ -39525,7 +39413,7 @@
       </c>
       <c r="B2179" s="19" t="inlineStr">
         <is>
-          <t>926227393</t>
+          <t>928211140</t>
         </is>
       </c>
       <c r="C2179" s="20" t="n"/>
@@ -39625,7 +39513,7 @@
       </c>
       <c r="B2186" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="C2186" s="20" t="n"/>
@@ -39669,7 +39557,7 @@
       </c>
       <c r="B2189" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/926227393</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928211140</t>
         </is>
       </c>
       <c r="C2189" s="20" t="n"/>
@@ -45404,7 +45292,7 @@
     <row r="2611" ht="30" customHeight="1">
       <c r="A2611" s="16" t="inlineStr">
         <is>
-          <t>FICHA 175: EUS-47596</t>
+          <t>FICHA 175: EUS-49083</t>
         </is>
       </c>
       <c r="B2611" s="17" t="n"/>
@@ -45453,7 +45341,7 @@
       </c>
       <c r="B2614" s="19" t="inlineStr">
         <is>
-          <t>EUS-47596</t>
+          <t>EUS-49083</t>
         </is>
       </c>
       <c r="C2614" s="20" t="n"/>
@@ -45616,7 +45504,7 @@
     <row r="2626" ht="30" customHeight="1">
       <c r="A2626" s="16" t="inlineStr">
         <is>
-          <t>FICHA 176: EUS-51067</t>
+          <t>FICHA 176: EUS-36489</t>
         </is>
       </c>
       <c r="B2626" s="17" t="n"/>
@@ -45665,7 +45553,7 @@
       </c>
       <c r="B2629" s="19" t="inlineStr">
         <is>
-          <t>EUS-51067</t>
+          <t>EUS-36489</t>
         </is>
       </c>
       <c r="C2629" s="20" t="n"/>
@@ -45828,7 +45716,7 @@
     <row r="2641" ht="30" customHeight="1">
       <c r="A2641" s="16" t="inlineStr">
         <is>
-          <t>FICHA 177: EUS-92303</t>
+          <t>FICHA 177: EUS-51813</t>
         </is>
       </c>
       <c r="B2641" s="17" t="n"/>
@@ -45861,7 +45749,7 @@
       </c>
       <c r="B2643" s="19" t="inlineStr">
         <is>
-          <t>Servicio de retirada, transporte y gestión de los residuos Sandach de la cámara frigorífica situada en el Garbigune de Eibar</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
         </is>
       </c>
       <c r="C2643" s="20" t="n"/>
@@ -45877,7 +45765,7 @@
       </c>
       <c r="B2644" s="19" t="inlineStr">
         <is>
-          <t>EUS-92303</t>
+          <t>EUS-51813</t>
         </is>
       </c>
       <c r="C2644" s="20" t="n"/>
@@ -45953,7 +45841,7 @@
       </c>
       <c r="B2649" s="19" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="C2649" s="20" t="n"/>
@@ -46011,9 +45899,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2653" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALTA — </t>
+      <c r="B2653" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
         </is>
       </c>
       <c r="C2653" s="20" t="n"/>
@@ -46029,7 +45917,7 @@
       </c>
       <c r="B2654" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-retirada-transporte-y-gestion-residuos-sandach-camara-frigorifica-situada-garbigune-eibar/expjaso743728/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/bioaniztasunfundaziohirin/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2654" s="20" t="n"/>
@@ -46040,7 +45928,7 @@
     <row r="2656" ht="30" customHeight="1">
       <c r="A2656" s="16" t="inlineStr">
         <is>
-          <t>FICHA 178: EUS-86597</t>
+          <t>FICHA 178: EUS-95789</t>
         </is>
       </c>
       <c r="B2656" s="17" t="n"/>
@@ -46073,7 +45961,7 @@
       </c>
       <c r="B2658" s="19" t="inlineStr">
         <is>
-          <t>Rehabilitacion parrales del barrio San Bartolome (zona Bizezko)</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="C2658" s="20" t="n"/>
@@ -46089,7 +45977,7 @@
       </c>
       <c r="B2659" s="19" t="inlineStr">
         <is>
-          <t>EUS-86597</t>
+          <t>EUS-95789</t>
         </is>
       </c>
       <c r="C2659" s="20" t="n"/>
@@ -46165,7 +46053,7 @@
       </c>
       <c r="B2664" s="19" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="C2664" s="20" t="n"/>
@@ -46223,9 +46111,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2668" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALTA — </t>
+      <c r="B2668" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
         </is>
       </c>
       <c r="C2668" s="20" t="n"/>
@@ -46241,7 +46129,7 @@
       </c>
       <c r="B2669" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/rehabilitacion-parrales-del-barrio-san-bartolome-zona-bizezko/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/comunicacion-previs-digitalizacion-2027/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2669" s="20" t="n"/>
@@ -46252,7 +46140,7 @@
     <row r="2671" ht="30" customHeight="1">
       <c r="A2671" s="16" t="inlineStr">
         <is>
-          <t>FICHA 179: EUS-60193</t>
+          <t>FICHA 179: EUS-26823</t>
         </is>
       </c>
       <c r="B2671" s="17" t="n"/>
@@ -46277,7 +46165,7 @@
       <c r="E2672" s="20" t="n"/>
       <c r="F2672" s="20" t="n"/>
     </row>
-    <row r="2673" ht="45" customHeight="1">
+    <row r="2673" ht="20" customHeight="1">
       <c r="A2673" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -46285,7 +46173,7 @@
       </c>
       <c r="B2673" s="19" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
+          <t>Digitalizacion del riego</t>
         </is>
       </c>
       <c r="C2673" s="20" t="n"/>
@@ -46301,7 +46189,7 @@
       </c>
       <c r="B2674" s="19" t="inlineStr">
         <is>
-          <t>EUS-60193</t>
+          <t>EUS-26823</t>
         </is>
       </c>
       <c r="C2674" s="20" t="n"/>
@@ -46377,7 +46265,7 @@
       </c>
       <c r="B2679" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2679" s="20" t="n"/>
@@ -46453,7 +46341,7 @@
       </c>
       <c r="B2684" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/bioaniztasunfundaziohirin/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/digitalizacion-del-riego/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2684" s="20" t="n"/>
@@ -46464,7 +46352,7 @@
     <row r="2686" ht="30" customHeight="1">
       <c r="A2686" s="16" t="inlineStr">
         <is>
-          <t>FICHA 180: EUS-65298</t>
+          <t>FICHA 180: EUS-20763</t>
         </is>
       </c>
       <c r="B2686" s="17" t="n"/>
@@ -46497,7 +46385,7 @@
       </c>
       <c r="B2688" s="19" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>elgoibar kirola - análisis del agua de las piscinas y legionella, julio 2026</t>
         </is>
       </c>
       <c r="C2688" s="20" t="n"/>
@@ -46513,7 +46401,7 @@
       </c>
       <c r="B2689" s="19" t="inlineStr">
         <is>
-          <t>EUS-65298</t>
+          <t>EUS-20763</t>
         </is>
       </c>
       <c r="C2689" s="20" t="n"/>
@@ -46589,7 +46477,7 @@
       </c>
       <c r="B2694" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2694" s="20" t="n"/>
@@ -46665,7 +46553,7 @@
       </c>
       <c r="B2699" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/comunicacion-previs-digitalizacion-2027/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/elgoibar-kirola-analisis-del-agua-piscinas-y-legionella-julio-2026/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2699" s="20" t="n"/>
@@ -46676,7 +46564,7 @@
     <row r="2701" ht="30" customHeight="1">
       <c r="A2701" s="16" t="inlineStr">
         <is>
-          <t>FICHA 181: EUS-77322</t>
+          <t>FICHA 181: EUS-09315</t>
         </is>
       </c>
       <c r="B2701" s="17" t="n"/>
@@ -46709,7 +46597,7 @@
       </c>
       <c r="B2703" s="19" t="inlineStr">
         <is>
-          <t>Redacción del proyecto y dirección de las obras de renovación de la red de distribución de agua en distintas zonas del centro de Irun</t>
+          <t>Suministro de recipientes para el control sanitario de aguas de las piscinas Ugarteigaran de Elkargune.</t>
         </is>
       </c>
       <c r="C2703" s="20" t="n"/>
@@ -46725,7 +46613,7 @@
       </c>
       <c r="B2704" s="19" t="inlineStr">
         <is>
-          <t>EUS-77322</t>
+          <t>EUS-09315</t>
         </is>
       </c>
       <c r="C2704" s="20" t="n"/>
@@ -46877,7 +46765,7 @@
       </c>
       <c r="B2714" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/redaccion-del-proyecto-y-direccion-obras-renovacion-red-distribucion-agua-distintas-zonas-del-centro-irun/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-recipientes-control-sanitario-aguas-piscinas-ugarteigaran-elkargune/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2714" s="20" t="n"/>
@@ -46888,7 +46776,7 @@
     <row r="2716" ht="30" customHeight="1">
       <c r="A2716" s="16" t="inlineStr">
         <is>
-          <t>FICHA 182: EUS-36090</t>
+          <t>FICHA 182: EUS-97313</t>
         </is>
       </c>
       <c r="B2716" s="17" t="n"/>
@@ -46921,7 +46809,7 @@
       </c>
       <c r="B2718" s="19" t="inlineStr">
         <is>
-          <t>Obras de rehabilitación del edificio del Emisario submarino de Monpas</t>
+          <t>Servicio de Limpieza de la Sede de Emakunde-Insituto Vasco de la Mujer.</t>
         </is>
       </c>
       <c r="C2718" s="20" t="n"/>
@@ -46937,7 +46825,7 @@
       </c>
       <c r="B2719" s="19" t="inlineStr">
         <is>
-          <t>EUS-36090</t>
+          <t>EUS-97313</t>
         </is>
       </c>
       <c r="C2719" s="20" t="n"/>
@@ -47089,7 +46977,7 @@
       </c>
       <c r="B2729" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/obras-rehabilitacion-del-edificio-del-emisario-submarino-monpas/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-limpieza-sede-emakunde-insituto-vasco-mujer/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2729" s="20" t="n"/>
@@ -47097,432 +46985,8 @@
       <c r="E2729" s="20" t="n"/>
       <c r="F2729" s="20" t="n"/>
     </row>
-    <row r="2731" ht="30" customHeight="1">
-      <c r="A2731" s="16" t="inlineStr">
-        <is>
-          <t>FICHA 183: EUS-09001</t>
-        </is>
-      </c>
-      <c r="B2731" s="17" t="n"/>
-      <c r="C2731" s="17" t="n"/>
-      <c r="D2731" s="17" t="n"/>
-      <c r="E2731" s="17" t="n"/>
-      <c r="F2731" s="17" t="n"/>
-    </row>
-    <row r="2732" ht="20" customHeight="1">
-      <c r="A2732" s="18" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B2732" s="19" t="inlineStr">
-        <is>
-          <t>🟢 Euskadi</t>
-        </is>
-      </c>
-      <c r="C2732" s="20" t="n"/>
-      <c r="D2732" s="20" t="n"/>
-      <c r="E2732" s="20" t="n"/>
-      <c r="F2732" s="20" t="n"/>
-    </row>
-    <row r="2733" ht="45" customHeight="1">
-      <c r="A2733" s="18" t="inlineStr">
-        <is>
-          <t>Titulo</t>
-        </is>
-      </c>
-      <c r="B2733" s="19" t="inlineStr">
-        <is>
-          <t>Servicio para la elaboración de un estudio medioambiental de la zona costera de Mompás y del estuario del río Oiartzun</t>
-        </is>
-      </c>
-      <c r="C2733" s="20" t="n"/>
-      <c r="D2733" s="20" t="n"/>
-      <c r="E2733" s="20" t="n"/>
-      <c r="F2733" s="20" t="n"/>
-    </row>
-    <row r="2734" ht="20" customHeight="1">
-      <c r="A2734" s="18" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2734" s="19" t="inlineStr">
-        <is>
-          <t>EUS-09001</t>
-        </is>
-      </c>
-      <c r="C2734" s="20" t="n"/>
-      <c r="D2734" s="20" t="n"/>
-      <c r="E2734" s="20" t="n"/>
-      <c r="F2734" s="20" t="n"/>
-    </row>
-    <row r="2735" ht="20" customHeight="1">
-      <c r="A2735" s="18" t="inlineStr">
-        <is>
-          <t>Programa</t>
-        </is>
-      </c>
-      <c r="B2735" s="19" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="C2735" s="20" t="n"/>
-      <c r="D2735" s="20" t="n"/>
-      <c r="E2735" s="20" t="n"/>
-      <c r="F2735" s="20" t="n"/>
-    </row>
-    <row r="2736" ht="20" customHeight="1">
-      <c r="A2736" s="18" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B2736" s="19" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C2736" s="20" t="n"/>
-      <c r="D2736" s="20" t="n"/>
-      <c r="E2736" s="20" t="n"/>
-      <c r="F2736" s="20" t="n"/>
-    </row>
-    <row r="2737" ht="20" customHeight="1">
-      <c r="A2737" s="18" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="B2737" s="19" t="inlineStr"/>
-      <c r="C2737" s="20" t="n"/>
-      <c r="D2737" s="20" t="n"/>
-      <c r="E2737" s="20" t="n"/>
-      <c r="F2737" s="20" t="n"/>
-    </row>
-    <row r="2738" ht="20" customHeight="1">
-      <c r="A2738" s="18" t="inlineStr">
-        <is>
-          <t>Presupuesto (EUR)</t>
-        </is>
-      </c>
-      <c r="B2738" s="19" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="C2738" s="20" t="n"/>
-      <c r="D2738" s="20" t="n"/>
-      <c r="E2738" s="20" t="n"/>
-      <c r="F2738" s="20" t="n"/>
-    </row>
-    <row r="2739" ht="20" customHeight="1">
-      <c r="A2739" s="18" t="inlineStr">
-        <is>
-          <t>Tipo de Accion</t>
-        </is>
-      </c>
-      <c r="B2739" s="19" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="C2739" s="20" t="n"/>
-      <c r="D2739" s="20" t="n"/>
-      <c r="E2739" s="20" t="n"/>
-      <c r="F2739" s="20" t="n"/>
-    </row>
-    <row r="2740" ht="20" customHeight="1">
-      <c r="A2740" s="18" t="inlineStr">
-        <is>
-          <t>Call ID</t>
-        </is>
-      </c>
-      <c r="B2740" s="19" t="inlineStr"/>
-      <c r="C2740" s="20" t="n"/>
-      <c r="D2740" s="20" t="n"/>
-      <c r="E2740" s="20" t="n"/>
-      <c r="F2740" s="20" t="n"/>
-    </row>
-    <row r="2741" ht="20" customHeight="1">
-      <c r="A2741" s="18" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="B2741" s="19" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="C2741" s="20" t="n"/>
-      <c r="D2741" s="20" t="n"/>
-      <c r="E2741" s="20" t="n"/>
-      <c r="F2741" s="20" t="n"/>
-    </row>
-    <row r="2742" ht="20" customHeight="1">
-      <c r="A2742" s="18" t="inlineStr">
-        <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="B2742" s="19" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C2742" s="20" t="n"/>
-      <c r="D2742" s="20" t="n"/>
-      <c r="E2742" s="20" t="n"/>
-      <c r="F2742" s="20" t="n"/>
-    </row>
-    <row r="2743" ht="20" customHeight="1">
-      <c r="A2743" s="18" t="inlineStr">
-        <is>
-          <t>Relevancia Bilbao</t>
-        </is>
-      </c>
-      <c r="B2743" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
-        </is>
-      </c>
-      <c r="C2743" s="20" t="n"/>
-      <c r="D2743" s="20" t="n"/>
-      <c r="E2743" s="20" t="n"/>
-      <c r="F2743" s="20" t="n"/>
-    </row>
-    <row r="2744" ht="45" customHeight="1">
-      <c r="A2744" s="18" t="inlineStr">
-        <is>
-          <t>Enlace al portal</t>
-        </is>
-      </c>
-      <c r="B2744" s="22" t="inlineStr">
-        <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-elaboracion-estudio-medioambiental-zona-costera-mompas-y-del-estuario-del-rio-oiartzun/web01-tramite/es/</t>
-        </is>
-      </c>
-      <c r="C2744" s="20" t="n"/>
-      <c r="D2744" s="20" t="n"/>
-      <c r="E2744" s="20" t="n"/>
-      <c r="F2744" s="20" t="n"/>
-    </row>
-    <row r="2746" ht="30" customHeight="1">
-      <c r="A2746" s="16" t="inlineStr">
-        <is>
-          <t>FICHA 184: EUS-57679</t>
-        </is>
-      </c>
-      <c r="B2746" s="17" t="n"/>
-      <c r="C2746" s="17" t="n"/>
-      <c r="D2746" s="17" t="n"/>
-      <c r="E2746" s="17" t="n"/>
-      <c r="F2746" s="17" t="n"/>
-    </row>
-    <row r="2747" ht="20" customHeight="1">
-      <c r="A2747" s="18" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B2747" s="19" t="inlineStr">
-        <is>
-          <t>🟢 Euskadi</t>
-        </is>
-      </c>
-      <c r="C2747" s="20" t="n"/>
-      <c r="D2747" s="20" t="n"/>
-      <c r="E2747" s="20" t="n"/>
-      <c r="F2747" s="20" t="n"/>
-    </row>
-    <row r="2748" ht="20" customHeight="1">
-      <c r="A2748" s="18" t="inlineStr">
-        <is>
-          <t>Titulo</t>
-        </is>
-      </c>
-      <c r="B2748" s="19" t="inlineStr">
-        <is>
-          <t>Plan de comunicacion y Sistema de Portavocias de la Agencia Vasca del Agua</t>
-        </is>
-      </c>
-      <c r="C2748" s="20" t="n"/>
-      <c r="D2748" s="20" t="n"/>
-      <c r="E2748" s="20" t="n"/>
-      <c r="F2748" s="20" t="n"/>
-    </row>
-    <row r="2749" ht="20" customHeight="1">
-      <c r="A2749" s="18" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B2749" s="19" t="inlineStr">
-        <is>
-          <t>EUS-57679</t>
-        </is>
-      </c>
-      <c r="C2749" s="20" t="n"/>
-      <c r="D2749" s="20" t="n"/>
-      <c r="E2749" s="20" t="n"/>
-      <c r="F2749" s="20" t="n"/>
-    </row>
-    <row r="2750" ht="20" customHeight="1">
-      <c r="A2750" s="18" t="inlineStr">
-        <is>
-          <t>Programa</t>
-        </is>
-      </c>
-      <c r="B2750" s="19" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="C2750" s="20" t="n"/>
-      <c r="D2750" s="20" t="n"/>
-      <c r="E2750" s="20" t="n"/>
-      <c r="F2750" s="20" t="n"/>
-    </row>
-    <row r="2751" ht="20" customHeight="1">
-      <c r="A2751" s="18" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B2751" s="19" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C2751" s="20" t="n"/>
-      <c r="D2751" s="20" t="n"/>
-      <c r="E2751" s="20" t="n"/>
-      <c r="F2751" s="20" t="n"/>
-    </row>
-    <row r="2752" ht="20" customHeight="1">
-      <c r="A2752" s="18" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="B2752" s="19" t="inlineStr"/>
-      <c r="C2752" s="20" t="n"/>
-      <c r="D2752" s="20" t="n"/>
-      <c r="E2752" s="20" t="n"/>
-      <c r="F2752" s="20" t="n"/>
-    </row>
-    <row r="2753" ht="20" customHeight="1">
-      <c r="A2753" s="18" t="inlineStr">
-        <is>
-          <t>Presupuesto (EUR)</t>
-        </is>
-      </c>
-      <c r="B2753" s="19" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="C2753" s="20" t="n"/>
-      <c r="D2753" s="20" t="n"/>
-      <c r="E2753" s="20" t="n"/>
-      <c r="F2753" s="20" t="n"/>
-    </row>
-    <row r="2754" ht="20" customHeight="1">
-      <c r="A2754" s="18" t="inlineStr">
-        <is>
-          <t>Tipo de Accion</t>
-        </is>
-      </c>
-      <c r="B2754" s="19" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="C2754" s="20" t="n"/>
-      <c r="D2754" s="20" t="n"/>
-      <c r="E2754" s="20" t="n"/>
-      <c r="F2754" s="20" t="n"/>
-    </row>
-    <row r="2755" ht="20" customHeight="1">
-      <c r="A2755" s="18" t="inlineStr">
-        <is>
-          <t>Call ID</t>
-        </is>
-      </c>
-      <c r="B2755" s="19" t="inlineStr"/>
-      <c r="C2755" s="20" t="n"/>
-      <c r="D2755" s="20" t="n"/>
-      <c r="E2755" s="20" t="n"/>
-      <c r="F2755" s="20" t="n"/>
-    </row>
-    <row r="2756" ht="20" customHeight="1">
-      <c r="A2756" s="18" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="B2756" s="19" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="C2756" s="20" t="n"/>
-      <c r="D2756" s="20" t="n"/>
-      <c r="E2756" s="20" t="n"/>
-      <c r="F2756" s="20" t="n"/>
-    </row>
-    <row r="2757" ht="20" customHeight="1">
-      <c r="A2757" s="18" t="inlineStr">
-        <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="B2757" s="19" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C2757" s="20" t="n"/>
-      <c r="D2757" s="20" t="n"/>
-      <c r="E2757" s="20" t="n"/>
-      <c r="F2757" s="20" t="n"/>
-    </row>
-    <row r="2758" ht="20" customHeight="1">
-      <c r="A2758" s="18" t="inlineStr">
-        <is>
-          <t>Relevancia Bilbao</t>
-        </is>
-      </c>
-      <c r="B2758" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
-        </is>
-      </c>
-      <c r="C2758" s="20" t="n"/>
-      <c r="D2758" s="20" t="n"/>
-      <c r="E2758" s="20" t="n"/>
-      <c r="F2758" s="20" t="n"/>
-    </row>
-    <row r="2759" ht="45" customHeight="1">
-      <c r="A2759" s="18" t="inlineStr">
-        <is>
-          <t>Enlace al portal</t>
-        </is>
-      </c>
-      <c r="B2759" s="22" t="inlineStr">
-        <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/plan-comunicacion-y-sistema-portavocias-agencia-vasca-del-agua/web01-tramite/es/</t>
-        </is>
-      </c>
-      <c r="C2759" s="20" t="n"/>
-      <c r="D2759" s="20" t="n"/>
-      <c r="E2759" s="20" t="n"/>
-      <c r="F2759" s="20" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="2576">
+  <mergeCells count="2548">
     <mergeCell ref="B679:F679"/>
     <mergeCell ref="B2192:F2192"/>
     <mergeCell ref="B1765:F1765"/>
@@ -47815,7 +47279,6 @@
     <mergeCell ref="B1542:F1542"/>
     <mergeCell ref="B1840:F1840"/>
     <mergeCell ref="B808:F808"/>
-    <mergeCell ref="B2753:F2753"/>
     <mergeCell ref="B1237:F1237"/>
     <mergeCell ref="B897:F897"/>
     <mergeCell ref="B1413:F1413"/>
@@ -47843,8 +47306,6 @@
     <mergeCell ref="B798:F798"/>
     <mergeCell ref="B521:F521"/>
     <mergeCell ref="B1553:F1553"/>
-    <mergeCell ref="B2743:F2743"/>
-    <mergeCell ref="B2737:F2737"/>
     <mergeCell ref="B2009:F2009"/>
     <mergeCell ref="B828:F828"/>
     <mergeCell ref="B950:F950"/>
@@ -47885,7 +47346,6 @@
     <mergeCell ref="B2240:F2240"/>
     <mergeCell ref="B963:F963"/>
     <mergeCell ref="B208:F208"/>
-    <mergeCell ref="B2756:F2756"/>
     <mergeCell ref="B1941:F1941"/>
     <mergeCell ref="B882:F882"/>
     <mergeCell ref="B2239:F2239"/>
@@ -47930,19 +47390,16 @@
     <mergeCell ref="B621:F621"/>
     <mergeCell ref="B613:F613"/>
     <mergeCell ref="B911:F911"/>
-    <mergeCell ref="B2739:F2739"/>
     <mergeCell ref="B1340:F1340"/>
     <mergeCell ref="B623:F623"/>
     <mergeCell ref="B2005:F2005"/>
     <mergeCell ref="B1676:F1676"/>
     <mergeCell ref="B921:F921"/>
     <mergeCell ref="B606:F606"/>
-    <mergeCell ref="B2741:F2741"/>
     <mergeCell ref="B2007:F2007"/>
     <mergeCell ref="B2436:F2436"/>
     <mergeCell ref="A1276:F1276"/>
     <mergeCell ref="B2307:F2307"/>
-    <mergeCell ref="B2736:F2736"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="A1486:F1486"/>
     <mergeCell ref="B334:F334"/>
@@ -47958,11 +47415,9 @@
     <mergeCell ref="B2448:F2448"/>
     <mergeCell ref="B1720:F1720"/>
     <mergeCell ref="B965:F965"/>
-    <mergeCell ref="B2752:F2752"/>
     <mergeCell ref="B2027:F2027"/>
     <mergeCell ref="B2149:F2149"/>
     <mergeCell ref="B2447:F2447"/>
-    <mergeCell ref="B2754:F2754"/>
     <mergeCell ref="B669:F669"/>
     <mergeCell ref="B1722:F1722"/>
     <mergeCell ref="B2020:F2020"/>
@@ -48117,7 +47572,6 @@
     <mergeCell ref="B2215:F2215"/>
     <mergeCell ref="B1460:F1460"/>
     <mergeCell ref="B2486:F2486"/>
-    <mergeCell ref="A2731:F2731"/>
     <mergeCell ref="B2246:F2246"/>
     <mergeCell ref="A946:F946"/>
     <mergeCell ref="A631:F631"/>
@@ -48304,7 +47758,6 @@
     <mergeCell ref="B1263:F1263"/>
     <mergeCell ref="A2206:F2206"/>
     <mergeCell ref="B2629:F2629"/>
-    <mergeCell ref="B2751:F2751"/>
     <mergeCell ref="B842:F842"/>
     <mergeCell ref="B1868:F1868"/>
     <mergeCell ref="B836:F836"/>
@@ -48357,7 +47810,6 @@
     <mergeCell ref="B883:F883"/>
     <mergeCell ref="B2390:F2390"/>
     <mergeCell ref="B2694:F2694"/>
-    <mergeCell ref="B2732:F2732"/>
     <mergeCell ref="B1969:F1969"/>
     <mergeCell ref="B2267:F2267"/>
     <mergeCell ref="B1208:F1208"/>
@@ -48400,7 +47852,6 @@
     <mergeCell ref="B647:F647"/>
     <mergeCell ref="B1252:F1252"/>
     <mergeCell ref="B1374:F1374"/>
-    <mergeCell ref="B2740:F2740"/>
     <mergeCell ref="B1708:F1708"/>
     <mergeCell ref="B649:F649"/>
     <mergeCell ref="A1801:F1801"/>
@@ -48418,7 +47869,6 @@
     <mergeCell ref="B949:F949"/>
     <mergeCell ref="B221:F221"/>
     <mergeCell ref="B2462:F2462"/>
-    <mergeCell ref="B2735:F2735"/>
     <mergeCell ref="B650:F650"/>
     <mergeCell ref="B2219:F2219"/>
     <mergeCell ref="B948:F948"/>
@@ -48507,7 +47957,6 @@
     <mergeCell ref="B219:F219"/>
     <mergeCell ref="B460:F460"/>
     <mergeCell ref="B517:F517"/>
-    <mergeCell ref="B2733:F2733"/>
     <mergeCell ref="B1701:F1701"/>
     <mergeCell ref="B760:F760"/>
     <mergeCell ref="B1119:F1119"/>
@@ -48868,14 +48317,12 @@
     <mergeCell ref="B635:F635"/>
     <mergeCell ref="A2506:F2506"/>
     <mergeCell ref="B935:F935"/>
-    <mergeCell ref="B2749:F2749"/>
     <mergeCell ref="B2021:F2021"/>
     <mergeCell ref="B962:F962"/>
     <mergeCell ref="B505:F505"/>
     <mergeCell ref="B1558:F1558"/>
     <mergeCell ref="B499:F499"/>
     <mergeCell ref="B2450:F2450"/>
-    <mergeCell ref="B2748:F2748"/>
     <mergeCell ref="A1171:F1171"/>
     <mergeCell ref="B1716:F1716"/>
     <mergeCell ref="B2023:F2023"/>
@@ -48885,7 +48332,6 @@
     <mergeCell ref="B2619:F2619"/>
     <mergeCell ref="B534:F534"/>
     <mergeCell ref="B805:F805"/>
-    <mergeCell ref="B2750:F2750"/>
     <mergeCell ref="B1718:F1718"/>
     <mergeCell ref="B2016:F2016"/>
     <mergeCell ref="B957:F957"/>
@@ -48999,7 +48445,6 @@
     <mergeCell ref="B1700:F1700"/>
     <mergeCell ref="B641:F641"/>
     <mergeCell ref="B2645:F2645"/>
-    <mergeCell ref="B2759:F2759"/>
     <mergeCell ref="B1404:F1404"/>
     <mergeCell ref="B1287:F1287"/>
     <mergeCell ref="B972:F972"/>
@@ -49426,7 +48871,6 @@
     <mergeCell ref="B2299:F2299"/>
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B512:F512"/>
-    <mergeCell ref="B2734:F2734"/>
     <mergeCell ref="B2728:F2728"/>
     <mergeCell ref="B2000:F2000"/>
     <mergeCell ref="B303:F303"/>
@@ -49441,7 +48885,6 @@
     <mergeCell ref="B2727:F2727"/>
     <mergeCell ref="B1328:F1328"/>
     <mergeCell ref="B812:F812"/>
-    <mergeCell ref="B2757:F2757"/>
     <mergeCell ref="B2002:F2002"/>
     <mergeCell ref="B2300:F2300"/>
     <mergeCell ref="B603:F603"/>
@@ -49452,7 +48895,6 @@
     <mergeCell ref="B2302:F2302"/>
     <mergeCell ref="B2600:F2600"/>
     <mergeCell ref="B515:F515"/>
-    <mergeCell ref="B2758:F2758"/>
     <mergeCell ref="A841:F841"/>
     <mergeCell ref="B959:F959"/>
     <mergeCell ref="B1257:F1257"/>
@@ -49473,7 +48915,6 @@
     <mergeCell ref="B531:F531"/>
     <mergeCell ref="B1417:F1417"/>
     <mergeCell ref="B662:F662"/>
-    <mergeCell ref="B2747:F2747"/>
     <mergeCell ref="B1715:F1715"/>
     <mergeCell ref="B2353:F2353"/>
     <mergeCell ref="B2013:F2013"/>
@@ -49489,7 +48930,6 @@
     <mergeCell ref="B2313:F2313"/>
     <mergeCell ref="B228:F228"/>
     <mergeCell ref="B2444:F2444"/>
-    <mergeCell ref="B2742:F2742"/>
     <mergeCell ref="B657:F657"/>
     <mergeCell ref="A2251:F2251"/>
     <mergeCell ref="B672:F672"/>
@@ -49578,7 +49018,6 @@
     <mergeCell ref="B2440:F2440"/>
     <mergeCell ref="B1408:F1408"/>
     <mergeCell ref="B1383:F1383"/>
-    <mergeCell ref="B2738:F2738"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B467:F467"/>
     <mergeCell ref="B2469:F2469"/>
@@ -49648,7 +49087,6 @@
     <mergeCell ref="B1480:F1480"/>
     <mergeCell ref="B1165:F1165"/>
     <mergeCell ref="B1048:F1048"/>
-    <mergeCell ref="A2746:F2746"/>
     <mergeCell ref="B1594:F1594"/>
     <mergeCell ref="B1892:F1892"/>
     <mergeCell ref="B1167:F1167"/>
@@ -49836,7 +49274,6 @@
     <mergeCell ref="A2041:F2041"/>
     <mergeCell ref="B1432:F1432"/>
     <mergeCell ref="B1554:F1554"/>
-    <mergeCell ref="B2744:F2744"/>
     <mergeCell ref="B835:F835"/>
     <mergeCell ref="B829:F829"/>
     <mergeCell ref="B74:F74"/>
@@ -49967,7 +49404,6 @@
     <mergeCell ref="B1267:F1267"/>
     <mergeCell ref="B1609:F1609"/>
     <mergeCell ref="A751:F751"/>
-    <mergeCell ref="B2755:F2755"/>
     <mergeCell ref="B1723:F1723"/>
     <mergeCell ref="B2328:F2328"/>
     <mergeCell ref="B1567:F1567"/>
@@ -50283,8 +49719,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2699" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2714" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2729" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2744" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2759" r:id="rId184"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50296,7 +49730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:J183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -51054,12 +50488,12 @@
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>85035</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Could you kindly confirm our understanding that in order to </t>
+          <t>DIGITAL-2021-DEPLOY-01-TWINS-HEALTH: Does the topic also cov</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr"/>
@@ -51086,12 +50520,12 @@
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>85039</t>
+          <t>85035</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>With reference to Technical Criteria Point 3.3, we kindly re</t>
+          <t xml:space="preserve">Could you kindly confirm our understanding that in order to </t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr"/>
@@ -51118,12 +50552,12 @@
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>85376</t>
+          <t>85039</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Regarding Section 16, point 3 of the Contract Notice: a) Cou</t>
+          <t>With reference to Technical Criteria Point 3.3, we kindly re</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr"/>
@@ -51150,12 +50584,12 @@
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>103603</t>
+          <t>85376</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Bio4HUMAN video - developed together with Horizon Results Bo</t>
+          <t>Regarding Section 16, point 3 of the Contract Notice: a) Cou</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr"/>
@@ -51182,19 +50616,15 @@
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>103603</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Ecosystem approach to climate change adaptation and flood ri</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>LIFE</t>
-        </is>
-      </c>
+          <t>Bio4HUMAN video - developed together with Horizon Results Bo</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -51218,15 +50648,19 @@
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>8f39fbaa-ed92-4f7a-a36e-c862147e499c-PIN</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Technical Assistance for river basin and flood risk plan</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr"/>
+          <t>Ecosystem approach to climate change adaptation and flood ri</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -51250,12 +50684,12 @@
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>c1b82527-35ef-4dd7-b67e-a57588ca2380-EXA</t>
+          <t>8f39fbaa-ed92-4f7a-a36e-c862147e499c-PIN</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>New European Bauhaus Label</t>
+          <t>Technical Assistance for river basin and flood risk plan</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr"/>
@@ -51282,12 +50716,12 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>c1b82527-35ef-4dd7-b67e-a57588ca2380-EXA</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01</t>
+          <t>New European Bauhaus Label</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr"/>
@@ -51314,7 +50748,7 @@
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -51346,12 +50780,12 @@
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>102435</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Is there any practical guidance on the implementation of the</t>
+          <t>Under Horizon Europe, mission topic HORIZON-MISS-2021-NEB-01</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr"/>
@@ -51378,12 +50812,12 @@
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>102435</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Under topic HORIZON-HLTH-2023-ENVHLTH-02-02, how should prop</t>
+          <t>Is there any practical guidance on the implementation of the</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr"/>
@@ -51410,12 +50844,12 @@
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>c36effc6-e7b0-423c-93a5-2b74a21546c0-EXA</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>EEA/SUN/25/001- Clean tech production in Europe: implication</t>
+          <t>Under topic HORIZON-HLTH-2023-ENVHLTH-02-02, how should prop</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr"/>
@@ -51427,7 +50861,7 @@
       <c r="E34" s="6" t="inlineStr"/>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr"/>
@@ -51442,12 +50876,12 @@
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>c36effc6-e7b0-423c-93a5-2b74a21546c0-EXA</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, our proposed action concerns the c</t>
+          <t>EEA/SUN/25/001- Clean tech production in Europe: implication</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr"/>
@@ -51474,12 +50908,12 @@
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>326952ANNOUNCEMENTen</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Hydrogen cities</t>
+          <t>Under Call CEF-E-PCI-PMI, our proposed action concerns the c</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr"/>
@@ -51506,7 +50940,7 @@
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>328464ANNOUNCEMENTen</t>
+          <t>326952ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -51538,7 +50972,7 @@
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>330857ANNOUNCEMENTen</t>
+          <t>328464ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -51570,7 +51004,7 @@
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>333297ANNOUNCEMENTen</t>
+          <t>330857ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -51602,7 +51036,7 @@
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>335155ANNOUNCEMENTen</t>
+          <t>333297ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -51634,7 +51068,7 @@
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>338237ANNOUNCEMENTen</t>
+          <t>335155ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -51666,7 +51100,7 @@
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>339612ANNOUNCEMENTen</t>
+          <t>338237ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -51698,7 +51132,7 @@
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>343814ANNOUNCEMENTen</t>
+          <t>339612ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -51730,7 +51164,7 @@
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>328462ANNOUNCEMENTen</t>
+          <t>343814ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -51762,7 +51196,7 @@
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>328461ANNOUNCEMENTen</t>
+          <t>328462ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -51794,7 +51228,7 @@
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>345032ANNOUNCEMENTen</t>
+          <t>328461ANNOUNCEMENTen</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -52118,15 +51552,19 @@
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neu</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -52150,19 +51588,15 @@
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Circular design for bio-based innovation towards climate-neu</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr"/>
       <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -52282,12 +51716,12 @@
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>5b272c0a-b51a-4dab-8a06-4b470a7c84b3</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Training for Energy Auditors and Technical Designers (TEAD)</t>
+          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics u</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr"/>
@@ -52314,15 +51748,19 @@
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>CEF2027</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CIT-01-02: Which are the relevant topics u</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr"/>
+          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -52346,19 +51784,15 @@
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>CEF2027</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Zero-Emission Offentlig bus Transport Urban Node Utrecht</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
+          <t>AFIF – Is it possible to submit a joint proposal from severa</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr"/>
       <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -52382,12 +51816,12 @@
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>915513452</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is it possible to submit a joint proposal from severa</t>
+          <t>SEABUBBLES</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr"/>
@@ -52414,12 +51848,12 @@
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>915513452</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>SEABUBBLES</t>
+          <t>AFIF – What kind of equipment is considered zero-emission tr</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr"/>
@@ -52446,12 +51880,12 @@
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>917721754</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>AFIF – What kind of equipment is considered zero-emission tr</t>
+          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr"/>
@@ -52478,12 +51912,12 @@
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>917721754</t>
+          <t>919892711</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>ESWE VERKEHRSGESELLSCHAFT MBH</t>
+          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKT</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr"/>
@@ -52510,12 +51944,12 @@
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>919892711</t>
+          <t>939945909</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>VERKEHRS-VERBUND MAINZ-WIESBADEN GESELLSCHAFT MIT BESCHRANKT</t>
+          <t>TRENTINO TRASPORTI SPA</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr"/>
@@ -52542,12 +51976,12 @@
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>939945909</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>TRENTINO TRASPORTI SPA</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr"/>
@@ -52574,12 +52008,12 @@
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr"/>
@@ -52606,12 +52040,12 @@
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr"/>
@@ -52638,12 +52072,12 @@
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr"/>
@@ -52670,12 +52104,12 @@
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>Under the European Green Deal call H2020-LC-GD-2020, topic L</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr"/>
@@ -52702,12 +52136,12 @@
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>996889759</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Under the European Green Deal call H2020-LC-GD-2020, topic L</t>
+          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr"/>
@@ -52734,12 +52168,12 @@
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>996889759</t>
+          <t>922165518</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>PLANET PLANUNGSGRUPPE ENERGIE UND TECHNIK GBR</t>
+          <t>DUNDEE CITY COUNCIL</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr"/>
@@ -52766,12 +52200,12 @@
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>922165518</t>
+          <t>919917446</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>DUNDEE CITY COUNCIL</t>
+          <t>REGIONALVERKEHR KOLN GMBH</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr"/>
@@ -52798,12 +52232,12 @@
     <row r="77" ht="28" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>919917446</t>
+          <t>917155468</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>REGIONALVERKEHR KOLN GMBH</t>
+          <t>REBELGROUP ADVISORY BV</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr"/>
@@ -52830,12 +52264,12 @@
     <row r="78" ht="28" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>917155468</t>
+          <t>938191470</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>REBELGROUP ADVISORY BV</t>
+          <t>IMS INDUSTRIE MECCANICHE SCARDELLATO SPA</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr"/>
@@ -54590,12 +54024,12 @@
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr"/>
@@ -54622,12 +54056,12 @@
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr"/>
@@ -54974,12 +54408,12 @@
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>928211140</t>
+          <t>928057492</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr"/>
@@ -55006,12 +54440,12 @@
     <row r="146" ht="28" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>928057492</t>
+          <t>926227393</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr"/>
@@ -55038,12 +54472,12 @@
     <row r="147" ht="28" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>926227393</t>
+          <t>928211140</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr"/>
@@ -55966,7 +55400,7 @@
     <row r="176" ht="28" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>EUS-47596</t>
+          <t>EUS-49083</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
@@ -56002,7 +55436,7 @@
     <row r="177" ht="28" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>EUS-51067</t>
+          <t>EUS-36489</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
@@ -56038,12 +55472,12 @@
     <row r="178" ht="28" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>EUS-92303</t>
+          <t>EUS-51813</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Servicio de retirada, transporte y gestión de los residuos S</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Euro</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
@@ -56059,7 +55493,7 @@
       <c r="E178" s="6" t="inlineStr"/>
       <c r="F178" s="25" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr"/>
@@ -56074,12 +55508,12 @@
     <row r="179" ht="28" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>EUS-86597</t>
+          <t>EUS-95789</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>Rehabilitacion parrales del barrio San Bartolome (zona Bizez</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -56095,7 +55529,7 @@
       <c r="E179" s="6" t="inlineStr"/>
       <c r="F179" s="25" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="G179" s="6" t="inlineStr"/>
@@ -56110,12 +55544,12 @@
     <row r="180" ht="28" customHeight="1">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>EUS-60193</t>
+          <t>EUS-26823</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Euro</t>
+          <t>Digitalizacion del riego</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
@@ -56146,12 +55580,12 @@
     <row r="181" ht="28" customHeight="1">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>EUS-65298</t>
+          <t>EUS-20763</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>elgoibar kirola - análisis del agua de las piscinas y legion</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -56182,12 +55616,12 @@
     <row r="182" ht="28" customHeight="1">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>EUS-77322</t>
+          <t>EUS-09315</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Redacción del proyecto y dirección de las obras de renovació</t>
+          <t>Suministro de recipientes para el control sanitario de aguas</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
@@ -56218,12 +55652,12 @@
     <row r="183" ht="28" customHeight="1">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>EUS-36090</t>
+          <t>EUS-97313</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obras de rehabilitación del edificio del Emisario submarino </t>
+          <t>Servicio de Limpieza de la Sede de Emakunde-Insituto Vasco d</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -56251,80 +55685,8 @@
       <c r="I183" s="6" t="inlineStr"/>
       <c r="J183" s="6" t="inlineStr"/>
     </row>
-    <row r="184" ht="28" customHeight="1">
-      <c r="A184" s="6" t="inlineStr">
-        <is>
-          <t>EUS-09001</t>
-        </is>
-      </c>
-      <c r="B184" s="6" t="inlineStr">
-        <is>
-          <t>Servicio para la elaboración de un estudio medioambiental de</t>
-        </is>
-      </c>
-      <c r="C184" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E184" s="6" t="inlineStr"/>
-      <c r="F184" s="25" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="G184" s="6" t="inlineStr"/>
-      <c r="H184" s="6" t="inlineStr">
-        <is>
-          <t>Por revisar</t>
-        </is>
-      </c>
-      <c r="I184" s="6" t="inlineStr"/>
-      <c r="J184" s="6" t="inlineStr"/>
-    </row>
-    <row r="185" ht="28" customHeight="1">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>EUS-57679</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plan de comunicacion y Sistema de Portavocias de la Agencia </t>
-        </is>
-      </c>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="D185" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E185" s="6" t="inlineStr"/>
-      <c r="F185" s="25" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="G185" s="6" t="inlineStr"/>
-      <c r="H185" s="6" t="inlineStr">
-        <is>
-          <t>Por revisar</t>
-        </is>
-      </c>
-      <c r="I185" s="6" t="inlineStr"/>
-      <c r="J185" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J185"/>
+  <autoFilter ref="A1:J183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/resultados_convocatorias.xlsx
+++ b/docs/resultados_convocatorias.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Recursos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$209</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M209"/>
+  <dimension ref="A1:M206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -685,7 +685,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 18/10/2026 10:00 - 203 convocatorias - 14 nuevas</t>
+          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 19/10/2026 11:22 - 200 convocatorias - 14 nuevas</t>
         </is>
       </c>
     </row>
@@ -6713,12 +6713,12 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>njaunzdz</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Mr. Dzintars Jaunzems</t>
+          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr"/>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>Mr. Dzintars Jaunzems</t>
+          <t xml:space="preserve">A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance </t>
         </is>
       </c>
       <c r="L132" s="6" t="inlineStr"/>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>njaunzdz</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
+          <t>Mr. Dzintars Jaunzems</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr"/>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance </t>
+          <t>Mr. Dzintars Jaunzems</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>928057492</t>
+          <t>928211140</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr"/>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8311,12 +8311,12 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>926227393</t>
+          <t>928057492</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="K166" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="L166" s="6" t="inlineStr"/>
@@ -8358,12 +8358,12 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>928211140</t>
+          <t>926227393</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>892931076</t>
+          <t>936518123</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="K190" s="6" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="L190" s="6" t="inlineStr"/>
@@ -9486,12 +9486,12 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>936518123</t>
+          <t>892931076</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr"/>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9525,57 +9525,65 @@
         </is>
       </c>
     </row>
-    <row r="192" ht="40" customHeight="1">
-      <c r="A192" s="5" t="inlineStr">
-        <is>
-          <t>Europa</t>
-        </is>
-      </c>
-      <c r="B192" s="6" t="inlineStr">
-        <is>
-          <t>EU4H</t>
-        </is>
-      </c>
-      <c r="C192" s="6" t="inlineStr">
-        <is>
-          <t>European Linkage of Initiative from Science to Action in Health</t>
-        </is>
-      </c>
-      <c r="D192" s="6" t="inlineStr"/>
-      <c r="E192" s="10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F192" s="6" t="inlineStr"/>
-      <c r="G192" s="6" t="inlineStr"/>
-      <c r="H192" s="6" t="inlineStr"/>
-      <c r="I192" s="10" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="J192" s="6" t="inlineStr">
-        <is>
-          <t>Revisar relevancia para el Ayuntamiento de Bilbao.</t>
-        </is>
-      </c>
-      <c r="K192" s="6" t="inlineStr">
-        <is>
-          <t>European Linkage of Initiative from Science to Action in Health</t>
-        </is>
-      </c>
-      <c r="L192" s="6" t="inlineStr"/>
-      <c r="M192" s="9" t="inlineStr">
+    <row r="192" ht="28" customHeight="1">
+      <c r="A192" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>EUS-45445</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>Coordinación de seguridad y salud en las obras de reparación de escudo en la fachada principal de CIPF EMILIO CAMPUZANO de Bilbao (Bizkaia</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr"/>
+      <c r="G193" s="6" t="inlineStr"/>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I193" s="11" t="inlineStr">
+        <is>
+          <t>MUY ALTA</t>
+        </is>
+      </c>
+      <c r="J193" s="6" t="inlineStr"/>
+      <c r="K193" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L193" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M193" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="28" customHeight="1">
-      <c r="A193" s="13" t="inlineStr">
-        <is>
-          <t>🟢 Euskadi</t>
         </is>
       </c>
     </row>
@@ -9587,12 +9595,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>EUS-75332</t>
+          <t>EUS-92164</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>Renovación de las licencias o suscripciones de software VMWare actualmente implantadas en la infraestructura tecnológica del Ayuntamiento de Eibar</t>
+          <t>Coordinación de
+seguridad y salud en las obras de desinfección y
+cierre de huecos en cancha cubierta en el IES
+IBARREKOLANDA de Bilbao (Bizkaia)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
@@ -9642,7 +9653,7 @@
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>EUS-52813</t>
+          <t>EUS-64887</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -9697,7 +9708,7 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>EUS-91123</t>
+          <t>EUS-78605</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -9752,12 +9763,12 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>EUS-55604</t>
+          <t>EUS-19539</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Redacción del proyecto básico, de ejecución y la dirección facultativa para la construcción de aproximadamente 32 viviendas de protección oficial en la parcela SZR-1 y 11 alojamientos dotacionales en </t>
+          <t>coordinación de seguridad y salud en la obra de renovación y mejora de la eficiencia energética del alumbrado público</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
@@ -9807,12 +9818,12 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>EUS-64978</t>
+          <t>EUS-34915</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>Ayudas para la adquisición e implantación de sistemas de nuevas tecnologías y de seguridad en el sector del transporte público 2026.</t>
+          <t>1-alquiler camión cesta- (j9/01/2025) / seguro diario / gestión de residuos y limpieza plataforma / gasoil consumido 14</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
@@ -9829,12 +9840,12 @@
       <c r="G198" s="6" t="inlineStr"/>
       <c r="H198" s="6" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
-        </is>
-      </c>
-      <c r="I198" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I198" s="8" t="inlineStr">
+        <is>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J198" s="6" t="inlineStr"/>
@@ -9862,12 +9873,12 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>EUS-61815</t>
+          <t>EUS-66515</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>9 FAROS DE INNOVACIÓN, 3 transiciones (digital, ecológica y sociosanitaria) y 2 líneas (de retos y plataformas) son los ejes de una nueva convocatoria del Gobierno Vasco que persigue colaboración de E</t>
+          <t>Ayudas para la adquisición e implantación de sistemas de nuevas tecnologías y de seguridad en el sector del transporte público 2026.</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
@@ -9898,7 +9909,11 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L199" s="6" t="inlineStr"/>
+      <c r="L199" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
       <c r="M199" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -9913,12 +9928,12 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>EUS-29689</t>
+          <t>EUS-12421</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
+          <t>9 FAROS DE INNOVACIÓN, 3 transiciones (digital, ecológica y sociosanitaria) y 2 líneas (de retos y plataformas) son los ejes de una nueva convocatoria del Gobierno Vasco que persigue colaboración de E</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
@@ -9968,12 +9983,12 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>EUS-96720</t>
+          <t>EUS-30744</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
@@ -10023,12 +10038,12 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>EUS-38676</t>
+          <t>EUS-39957</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>Servicio público de transporte urbano de viajeros en autobús de Arrasate</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
@@ -10045,7 +10060,7 @@
       <c r="G202" s="6" t="inlineStr"/>
       <c r="H202" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="I202" s="12" t="inlineStr">
@@ -10078,12 +10093,12 @@
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>EUS-18235</t>
+          <t>EUS-35301</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>Mantenimiento de la jardinería y limpieza de los parques de Monterron y Santa Barbara de Arrasate (reservado a centros especiales de empleo de iniciativa social y empresas de inserción)</t>
+          <t>transporte autobús histórico centenario funicular</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
@@ -10133,12 +10148,12 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>EUS-95301</t>
+          <t>EUS-05161</t>
         </is>
       </c>
       <c r="C204" s="6" t="inlineStr">
         <is>
-          <t>Productos de limpieza para andretxea</t>
+          <t>suministro artículos de limpieza</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
@@ -10188,12 +10203,12 @@
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>EUS-12012</t>
+          <t>EUS-89367</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>Menaje para las viviendas municipales</t>
+          <t>diorama estación kontxa ut 980 inaguación pasante</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
@@ -10243,12 +10258,12 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>EUS-26392</t>
+          <t>EUS-18525</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>Menaje de hogar para viviendas municipales</t>
+          <t>trabajos y transportes de mercancías</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
@@ -10290,171 +10305,10 @@
         </is>
       </c>
     </row>
-    <row r="207" ht="40" customHeight="1">
-      <c r="A207" s="14" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="B207" s="6" t="inlineStr">
-        <is>
-          <t>EUS-09152</t>
-        </is>
-      </c>
-      <c r="C207" s="6" t="inlineStr">
-        <is>
-          <t>Paraguas como obsequio para el día de aitites-amamas en fiestas</t>
-        </is>
-      </c>
-      <c r="D207" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="E207" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F207" s="6" t="inlineStr"/>
-      <c r="G207" s="6" t="inlineStr"/>
-      <c r="H207" s="6" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="I207" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="J207" s="6" t="inlineStr"/>
-      <c r="K207" s="6" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="L207" s="6" t="inlineStr"/>
-      <c r="M207" s="9" t="inlineStr">
-        <is>
-          <t>Ver</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="40" customHeight="1">
-      <c r="A208" s="14" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="B208" s="6" t="inlineStr">
-        <is>
-          <t>EUS-46833</t>
-        </is>
-      </c>
-      <c r="C208" s="6" t="inlineStr">
-        <is>
-          <t>Suministro e instalación de 27 farolas led de alumbrado solar autónomo</t>
-        </is>
-      </c>
-      <c r="D208" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="E208" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F208" s="6" t="inlineStr"/>
-      <c r="G208" s="6" t="inlineStr"/>
-      <c r="H208" s="6" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="I208" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="J208" s="6" t="inlineStr"/>
-      <c r="K208" s="6" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="L208" s="15" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="M208" s="9" t="inlineStr">
-        <is>
-          <t>Ver</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="40" customHeight="1">
-      <c r="A209" s="14" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="B209" s="6" t="inlineStr">
-        <is>
-          <t>EUS-10725</t>
-        </is>
-      </c>
-      <c r="C209" s="6" t="inlineStr">
-        <is>
-          <t>Suministro en régimen de alquiler de 2 contenedores y 1 caseta vestuario con 2 duchas para uso de la brigada municipal de obras</t>
-        </is>
-      </c>
-      <c r="D209" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="E209" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F209" s="6" t="inlineStr"/>
-      <c r="G209" s="6" t="inlineStr"/>
-      <c r="H209" s="6" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="I209" s="12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="J209" s="6" t="inlineStr"/>
-      <c r="K209" s="6" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="L209" s="15" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="M209" s="9" t="inlineStr">
-        <is>
-          <t>Ver</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:M209"/>
+  <autoFilter ref="A4:M206"/>
   <mergeCells count="4">
-    <mergeCell ref="A193:M193"/>
+    <mergeCell ref="A192:M192"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
@@ -10646,7 +10500,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId190"/>
@@ -10660,9 +10514,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10674,7 +10525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3044"/>
+  <dimension ref="A1:F2999"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -36500,7 +36351,7 @@
     <row r="1891" ht="30" customHeight="1">
       <c r="A1891" s="16" t="inlineStr">
         <is>
-          <t>FICHA 127: njaunzdz</t>
+          <t>FICHA 127: 14587</t>
         </is>
       </c>
       <c r="B1891" s="17" t="n"/>
@@ -36525,7 +36376,7 @@
       <c r="E1892" s="20" t="n"/>
       <c r="F1892" s="20" t="n"/>
     </row>
-    <row r="1893" ht="20" customHeight="1">
+    <row r="1893" ht="45" customHeight="1">
       <c r="A1893" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -36533,7 +36384,7 @@
       </c>
       <c r="B1893" s="19" t="inlineStr">
         <is>
-          <t>Mr. Dzintars Jaunzems</t>
+          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
         </is>
       </c>
       <c r="C1893" s="20" t="n"/>
@@ -36549,7 +36400,7 @@
       </c>
       <c r="B1894" s="19" t="inlineStr">
         <is>
-          <t>njaunzdz</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="C1894" s="20" t="n"/>
@@ -36641,7 +36492,7 @@
       <c r="E1900" s="20" t="n"/>
       <c r="F1900" s="20" t="n"/>
     </row>
-    <row r="1901" ht="20" customHeight="1">
+    <row r="1901" ht="45" customHeight="1">
       <c r="A1901" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -36649,7 +36500,7 @@
       </c>
       <c r="B1901" s="19" t="inlineStr">
         <is>
-          <t>Mr. Dzintars Jaunzems</t>
+          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
         </is>
       </c>
       <c r="C1901" s="20" t="n"/>
@@ -36693,7 +36544,7 @@
       </c>
       <c r="B1904" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/njaunzdz</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14587</t>
         </is>
       </c>
       <c r="C1904" s="20" t="n"/>
@@ -36704,7 +36555,7 @@
     <row r="1906" ht="30" customHeight="1">
       <c r="A1906" s="16" t="inlineStr">
         <is>
-          <t>FICHA 128: 14587</t>
+          <t>FICHA 128: njaunzdz</t>
         </is>
       </c>
       <c r="B1906" s="17" t="n"/>
@@ -36729,7 +36580,7 @@
       <c r="E1907" s="20" t="n"/>
       <c r="F1907" s="20" t="n"/>
     </row>
-    <row r="1908" ht="45" customHeight="1">
+    <row r="1908" ht="20" customHeight="1">
       <c r="A1908" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -36737,7 +36588,7 @@
       </c>
       <c r="B1908" s="19" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
+          <t>Mr. Dzintars Jaunzems</t>
         </is>
       </c>
       <c r="C1908" s="20" t="n"/>
@@ -36753,7 +36604,7 @@
       </c>
       <c r="B1909" s="19" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>njaunzdz</t>
         </is>
       </c>
       <c r="C1909" s="20" t="n"/>
@@ -36845,7 +36696,7 @@
       <c r="E1915" s="20" t="n"/>
       <c r="F1915" s="20" t="n"/>
     </row>
-    <row r="1916" ht="45" customHeight="1">
+    <row r="1916" ht="20" customHeight="1">
       <c r="A1916" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -36853,7 +36704,7 @@
       </c>
       <c r="B1916" s="19" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy production plant combined with an innovative electricity storage to provide controllable RES-E generation. How is the GHG emissions avoidance calculated in this case?</t>
+          <t>Mr. Dzintars Jaunzems</t>
         </is>
       </c>
       <c r="C1916" s="20" t="n"/>
@@ -36897,7 +36748,7 @@
       </c>
       <c r="B1919" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/14587</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/njaunzdz</t>
         </is>
       </c>
       <c r="C1919" s="20" t="n"/>
@@ -43232,7 +43083,7 @@
     <row r="2386" ht="30" customHeight="1">
       <c r="A2386" s="16" t="inlineStr">
         <is>
-          <t>FICHA 160: 928057492</t>
+          <t>FICHA 160: 928211140</t>
         </is>
       </c>
       <c r="B2386" s="17" t="n"/>
@@ -43265,7 +43116,7 @@
       </c>
       <c r="B2388" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="C2388" s="20" t="n"/>
@@ -43281,7 +43132,7 @@
       </c>
       <c r="B2389" s="19" t="inlineStr">
         <is>
-          <t>928057492</t>
+          <t>928211140</t>
         </is>
       </c>
       <c r="C2389" s="20" t="n"/>
@@ -43381,7 +43232,7 @@
       </c>
       <c r="B2396" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="C2396" s="20" t="n"/>
@@ -43425,7 +43276,7 @@
       </c>
       <c r="B2399" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928057492</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928211140</t>
         </is>
       </c>
       <c r="C2399" s="20" t="n"/>
@@ -43436,7 +43287,7 @@
     <row r="2401" ht="30" customHeight="1">
       <c r="A2401" s="16" t="inlineStr">
         <is>
-          <t>FICHA 161: 926227393</t>
+          <t>FICHA 161: 928057492</t>
         </is>
       </c>
       <c r="B2401" s="17" t="n"/>
@@ -43469,7 +43320,7 @@
       </c>
       <c r="B2403" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="C2403" s="20" t="n"/>
@@ -43485,7 +43336,7 @@
       </c>
       <c r="B2404" s="19" t="inlineStr">
         <is>
-          <t>926227393</t>
+          <t>928057492</t>
         </is>
       </c>
       <c r="C2404" s="20" t="n"/>
@@ -43585,7 +43436,7 @@
       </c>
       <c r="B2411" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="C2411" s="20" t="n"/>
@@ -43629,7 +43480,7 @@
       </c>
       <c r="B2414" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/926227393</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928057492</t>
         </is>
       </c>
       <c r="C2414" s="20" t="n"/>
@@ -43640,7 +43491,7 @@
     <row r="2416" ht="30" customHeight="1">
       <c r="A2416" s="16" t="inlineStr">
         <is>
-          <t>FICHA 162: 928211140</t>
+          <t>FICHA 162: 926227393</t>
         </is>
       </c>
       <c r="B2416" s="17" t="n"/>
@@ -43673,7 +43524,7 @@
       </c>
       <c r="B2418" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="C2418" s="20" t="n"/>
@@ -43689,7 +43540,7 @@
       </c>
       <c r="B2419" s="19" t="inlineStr">
         <is>
-          <t>928211140</t>
+          <t>926227393</t>
         </is>
       </c>
       <c r="C2419" s="20" t="n"/>
@@ -43789,7 +43640,7 @@
       </c>
       <c r="B2426" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="C2426" s="20" t="n"/>
@@ -43833,7 +43684,7 @@
       </c>
       <c r="B2429" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928211140</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/926227393</t>
         </is>
       </c>
       <c r="C2429" s="20" t="n"/>
@@ -48340,7 +48191,7 @@
     <row r="2761" ht="30" customHeight="1">
       <c r="A2761" s="16" t="inlineStr">
         <is>
-          <t>FICHA 185: 892931076</t>
+          <t>FICHA 185: 936518123</t>
         </is>
       </c>
       <c r="B2761" s="17" t="n"/>
@@ -48373,7 +48224,7 @@
       </c>
       <c r="B2763" s="19" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="C2763" s="20" t="n"/>
@@ -48389,7 +48240,7 @@
       </c>
       <c r="B2764" s="19" t="inlineStr">
         <is>
-          <t>892931076</t>
+          <t>936518123</t>
         </is>
       </c>
       <c r="C2764" s="20" t="n"/>
@@ -48489,7 +48340,7 @@
       </c>
       <c r="B2771" s="19" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="C2771" s="20" t="n"/>
@@ -48533,7 +48384,7 @@
       </c>
       <c r="B2774" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/892931076</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/936518123</t>
         </is>
       </c>
       <c r="C2774" s="20" t="n"/>
@@ -48544,7 +48395,7 @@
     <row r="2776" ht="30" customHeight="1">
       <c r="A2776" s="16" t="inlineStr">
         <is>
-          <t>FICHA 186: 936518123</t>
+          <t>FICHA 186: 892931076</t>
         </is>
       </c>
       <c r="B2776" s="17" t="n"/>
@@ -48577,7 +48428,7 @@
       </c>
       <c r="B2778" s="19" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="C2778" s="20" t="n"/>
@@ -48593,7 +48444,7 @@
       </c>
       <c r="B2779" s="19" t="inlineStr">
         <is>
-          <t>936518123</t>
+          <t>892931076</t>
         </is>
       </c>
       <c r="C2779" s="20" t="n"/>
@@ -48693,7 +48544,7 @@
       </c>
       <c r="B2786" s="19" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="C2786" s="20" t="n"/>
@@ -48737,7 +48588,7 @@
       </c>
       <c r="B2789" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/936518123</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/892931076</t>
         </is>
       </c>
       <c r="C2789" s="20" t="n"/>
@@ -48748,7 +48599,7 @@
     <row r="2791" ht="30" customHeight="1">
       <c r="A2791" s="16" t="inlineStr">
         <is>
-          <t>FICHA 187: EU4H</t>
+          <t>FICHA 187: EUS-45445</t>
         </is>
       </c>
       <c r="B2791" s="17" t="n"/>
@@ -48765,7 +48616,7 @@
       </c>
       <c r="B2792" s="19" t="inlineStr">
         <is>
-          <t>🇪🇺 Europa</t>
+          <t>🟢 Euskadi</t>
         </is>
       </c>
       <c r="C2792" s="20" t="n"/>
@@ -48773,7 +48624,7 @@
       <c r="E2792" s="20" t="n"/>
       <c r="F2792" s="20" t="n"/>
     </row>
-    <row r="2793" ht="20" customHeight="1">
+    <row r="2793" ht="45" customHeight="1">
       <c r="A2793" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -48781,7 +48632,7 @@
       </c>
       <c r="B2793" s="19" t="inlineStr">
         <is>
-          <t>European Linkage of Initiative from Science to Action in Health</t>
+          <t>Coordinación de seguridad y salud en las obras de reparación de escudo en la fachada principal de CIPF EMILIO CAMPUZANO de Bilbao (Bizkaia</t>
         </is>
       </c>
       <c r="C2793" s="20" t="n"/>
@@ -48797,7 +48648,7 @@
       </c>
       <c r="B2794" s="19" t="inlineStr">
         <is>
-          <t>EU4H</t>
+          <t>EUS-45445</t>
         </is>
       </c>
       <c r="C2794" s="20" t="n"/>
@@ -48811,7 +48662,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B2795" s="19" t="inlineStr"/>
+      <c r="B2795" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
       <c r="C2795" s="20" t="n"/>
       <c r="D2795" s="20" t="n"/>
       <c r="E2795" s="20" t="n"/>
@@ -48825,7 +48680,7 @@
       </c>
       <c r="B2796" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="C2796" s="20" t="n"/>
@@ -48869,7 +48724,7 @@
       </c>
       <c r="B2799" s="19" t="inlineStr">
         <is>
-          <t>No disponible</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2799" s="20" t="n"/>
@@ -48883,11 +48738,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2800" s="19" t="inlineStr">
-        <is>
-          <t>EU4H-2022-PJ-3</t>
-        </is>
-      </c>
+      <c r="B2800" s="19" t="inlineStr"/>
       <c r="C2800" s="20" t="n"/>
       <c r="D2800" s="20" t="n"/>
       <c r="E2800" s="20" t="n"/>
@@ -48901,7 +48752,7 @@
       </c>
       <c r="B2801" s="19" t="inlineStr">
         <is>
-          <t>European Linkage of Initiative from Science to Action in Health</t>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
       <c r="C2801" s="20" t="n"/>
@@ -48915,7 +48766,11 @@
           <t>Tags</t>
         </is>
       </c>
-      <c r="B2802" s="19" t="inlineStr"/>
+      <c r="B2802" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
       <c r="C2802" s="20" t="n"/>
       <c r="D2802" s="20" t="n"/>
       <c r="E2802" s="20" t="n"/>
@@ -48927,9 +48782,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2803" s="19" t="inlineStr">
-        <is>
-          <t>INFO — Revisar relevancia para el Ayuntamiento de Bilbao.</t>
+      <c r="B2803" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUY ALTA — </t>
         </is>
       </c>
       <c r="C2803" s="20" t="n"/>
@@ -48945,7 +48800,7 @@
       </c>
       <c r="B2804" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EU4H</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/coordinacion-seguridad-y-salud-obras-reparacion-escudo-fachada-principal-cipf-emilio-campuzano-bilbao-bizkaia/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2804" s="20" t="n"/>
@@ -48956,7 +48811,7 @@
     <row r="2806" ht="30" customHeight="1">
       <c r="A2806" s="16" t="inlineStr">
         <is>
-          <t>FICHA 188: EUS-75332</t>
+          <t>FICHA 188: EUS-92164</t>
         </is>
       </c>
       <c r="B2806" s="17" t="n"/>
@@ -48989,7 +48844,10 @@
       </c>
       <c r="B2808" s="19" t="inlineStr">
         <is>
-          <t>Renovación de las licencias o suscripciones de software VMWare actualmente implantadas en la infraestructura tecnológica del Ayuntamiento de Eibar</t>
+          <t>Coordinación de
+seguridad y salud en las obras de desinfección y
+cierre de huecos en cancha cubierta en el IES
+IBARREKOLANDA de Bilbao (Bizkaia)</t>
         </is>
       </c>
       <c r="C2808" s="20" t="n"/>
@@ -49005,7 +48863,7 @@
       </c>
       <c r="B2809" s="19" t="inlineStr">
         <is>
-          <t>EUS-75332</t>
+          <t>EUS-92164</t>
         </is>
       </c>
       <c r="C2809" s="20" t="n"/>
@@ -49157,7 +49015,7 @@
       </c>
       <c r="B2819" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/renovacion-licencias-o-suscripciones-software-vmware-actualmente-implantadas-infraestructura-tecnologica-del-ayuntamiento-eibar/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/coordinacion-seguridad-y-salud-obras-desinfeccion-y-cierre-huecos-cancha-cubierta-ies-ibarrekolanda-bilbao-bizkaia/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2819" s="20" t="n"/>
@@ -49168,7 +49026,7 @@
     <row r="2821" ht="30" customHeight="1">
       <c r="A2821" s="16" t="inlineStr">
         <is>
-          <t>FICHA 189: EUS-52813</t>
+          <t>FICHA 189: EUS-64887</t>
         </is>
       </c>
       <c r="B2821" s="17" t="n"/>
@@ -49217,7 +49075,7 @@
       </c>
       <c r="B2824" s="19" t="inlineStr">
         <is>
-          <t>EUS-52813</t>
+          <t>EUS-64887</t>
         </is>
       </c>
       <c r="C2824" s="20" t="n"/>
@@ -49380,7 +49238,7 @@
     <row r="2836" ht="30" customHeight="1">
       <c r="A2836" s="16" t="inlineStr">
         <is>
-          <t>FICHA 190: EUS-91123</t>
+          <t>FICHA 190: EUS-78605</t>
         </is>
       </c>
       <c r="B2836" s="17" t="n"/>
@@ -49429,7 +49287,7 @@
       </c>
       <c r="B2839" s="19" t="inlineStr">
         <is>
-          <t>EUS-91123</t>
+          <t>EUS-78605</t>
         </is>
       </c>
       <c r="C2839" s="20" t="n"/>
@@ -49592,7 +49450,7 @@
     <row r="2851" ht="30" customHeight="1">
       <c r="A2851" s="16" t="inlineStr">
         <is>
-          <t>FICHA 191: EUS-55604</t>
+          <t>FICHA 191: EUS-19539</t>
         </is>
       </c>
       <c r="B2851" s="17" t="n"/>
@@ -49625,7 +49483,7 @@
       </c>
       <c r="B2853" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Redacción del proyecto básico, de ejecución y la dirección facultativa para la construcción de aproximadamente 32 viviendas de protección oficial en la parcela SZR-1 y 11 alojamientos dotacionales en </t>
+          <t>coordinación de seguridad y salud en la obra de renovación y mejora de la eficiencia energética del alumbrado público</t>
         </is>
       </c>
       <c r="C2853" s="20" t="n"/>
@@ -49641,7 +49499,7 @@
       </c>
       <c r="B2854" s="19" t="inlineStr">
         <is>
-          <t>EUS-55604</t>
+          <t>EUS-19539</t>
         </is>
       </c>
       <c r="C2854" s="20" t="n"/>
@@ -49793,7 +49651,7 @@
       </c>
       <c r="B2864" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/redaccion-del-proyecto-basico-ejecucion-y-direccion-facultativa-construccion-aproximadamente-32-viviendas-proteccion-oficial-parcela-szr-1-y-11-alojamientos-dotacionales-parcela-ead-1-portugalete-bizkaia-acorde-metodologia-trabajo-bim-teniendo-cuenta-pri/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/coordinacion-seguridad-y-salud-obra-renovacion-y-mejora-eficiencia-energetica-del-alumbrado-publico/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2864" s="20" t="n"/>
@@ -49804,7 +49662,7 @@
     <row r="2866" ht="30" customHeight="1">
       <c r="A2866" s="16" t="inlineStr">
         <is>
-          <t>FICHA 192: EUS-64978</t>
+          <t>FICHA 192: EUS-34915</t>
         </is>
       </c>
       <c r="B2866" s="17" t="n"/>
@@ -49837,7 +49695,7 @@
       </c>
       <c r="B2868" s="19" t="inlineStr">
         <is>
-          <t>Ayudas para la adquisición e implantación de sistemas de nuevas tecnologías y de seguridad en el sector del transporte público 2026.</t>
+          <t>1-alquiler camión cesta- (j9/01/2025) / seguro diario / gestión de residuos y limpieza plataforma / gasoil consumido 14</t>
         </is>
       </c>
       <c r="C2868" s="20" t="n"/>
@@ -49853,7 +49711,7 @@
       </c>
       <c r="B2869" s="19" t="inlineStr">
         <is>
-          <t>EUS-64978</t>
+          <t>EUS-34915</t>
         </is>
       </c>
       <c r="C2869" s="20" t="n"/>
@@ -49929,7 +49787,7 @@
       </c>
       <c r="B2874" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2874" s="20" t="n"/>
@@ -49987,9 +49845,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2878" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
+      <c r="B2878" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTA — </t>
         </is>
       </c>
       <c r="C2878" s="20" t="n"/>
@@ -50005,7 +49863,7 @@
       </c>
       <c r="B2879" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/nuevas-tecnologias-2026/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/1-alquiler-camion-cesta-j9-01-2025-seguro-diario-gestion-residuos-y-limpieza-plataforma-gasoil-consumido-14/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2879" s="20" t="n"/>
@@ -50016,7 +49874,7 @@
     <row r="2881" ht="30" customHeight="1">
       <c r="A2881" s="16" t="inlineStr">
         <is>
-          <t>FICHA 193: EUS-61815</t>
+          <t>FICHA 193: EUS-66515</t>
         </is>
       </c>
       <c r="B2881" s="17" t="n"/>
@@ -50049,7 +49907,7 @@
       </c>
       <c r="B2883" s="19" t="inlineStr">
         <is>
-          <t>9 FAROS DE INNOVACIÓN, 3 transiciones (digital, ecológica y sociosanitaria) y 2 líneas (de retos y plataformas) son los ejes de una nueva convocatoria del Gobierno Vasco que persigue colaboración de E</t>
+          <t>Ayudas para la adquisición e implantación de sistemas de nuevas tecnologías y de seguridad en el sector del transporte público 2026.</t>
         </is>
       </c>
       <c r="C2883" s="20" t="n"/>
@@ -50065,7 +49923,7 @@
       </c>
       <c r="B2884" s="19" t="inlineStr">
         <is>
-          <t>EUS-61815</t>
+          <t>EUS-66515</t>
         </is>
       </c>
       <c r="C2884" s="20" t="n"/>
@@ -50217,7 +50075,7 @@
       </c>
       <c r="B2894" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/berrikuntzaitsasargierron/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/nuevas-tecnologias-2026/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2894" s="20" t="n"/>
@@ -50228,7 +50086,7 @@
     <row r="2896" ht="30" customHeight="1">
       <c r="A2896" s="16" t="inlineStr">
         <is>
-          <t>FICHA 194: EUS-29689</t>
+          <t>FICHA 194: EUS-12421</t>
         </is>
       </c>
       <c r="B2896" s="17" t="n"/>
@@ -50261,7 +50119,7 @@
       </c>
       <c r="B2898" s="19" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
+          <t>9 FAROS DE INNOVACIÓN, 3 transiciones (digital, ecológica y sociosanitaria) y 2 líneas (de retos y plataformas) son los ejes de una nueva convocatoria del Gobierno Vasco que persigue colaboración de E</t>
         </is>
       </c>
       <c r="C2898" s="20" t="n"/>
@@ -50277,7 +50135,7 @@
       </c>
       <c r="B2899" s="19" t="inlineStr">
         <is>
-          <t>EUS-29689</t>
+          <t>EUS-12421</t>
         </is>
       </c>
       <c r="C2899" s="20" t="n"/>
@@ -50429,7 +50287,7 @@
       </c>
       <c r="B2909" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/bioaniztasunfundaziohirin/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/berrikuntzaitsasargierron/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2909" s="20" t="n"/>
@@ -50440,7 +50298,7 @@
     <row r="2911" ht="30" customHeight="1">
       <c r="A2911" s="16" t="inlineStr">
         <is>
-          <t>FICHA 195: EUS-96720</t>
+          <t>FICHA 195: EUS-30744</t>
         </is>
       </c>
       <c r="B2911" s="17" t="n"/>
@@ -50465,7 +50323,7 @@
       <c r="E2912" s="20" t="n"/>
       <c r="F2912" s="20" t="n"/>
     </row>
-    <row r="2913" ht="20" customHeight="1">
+    <row r="2913" ht="45" customHeight="1">
       <c r="A2913" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -50473,7 +50331,7 @@
       </c>
       <c r="B2913" s="19" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Europeo de Desarrollo Regional y la Fundación Biodiversidad, en favor de la renaturalización urbana, infraestructura verde, conectividad de espa</t>
         </is>
       </c>
       <c r="C2913" s="20" t="n"/>
@@ -50489,7 +50347,7 @@
       </c>
       <c r="B2914" s="19" t="inlineStr">
         <is>
-          <t>EUS-96720</t>
+          <t>EUS-30744</t>
         </is>
       </c>
       <c r="C2914" s="20" t="n"/>
@@ -50641,7 +50499,7 @@
       </c>
       <c r="B2924" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/comunicacion-previs-digitalizacion-2027/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/bioaniztasunfundaziohirin/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2924" s="20" t="n"/>
@@ -50652,7 +50510,7 @@
     <row r="2926" ht="30" customHeight="1">
       <c r="A2926" s="16" t="inlineStr">
         <is>
-          <t>FICHA 196: EUS-38676</t>
+          <t>FICHA 196: EUS-39957</t>
         </is>
       </c>
       <c r="B2926" s="17" t="n"/>
@@ -50685,7 +50543,7 @@
       </c>
       <c r="B2928" s="19" t="inlineStr">
         <is>
-          <t>Servicio público de transporte urbano de viajeros en autobús de Arrasate</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="C2928" s="20" t="n"/>
@@ -50701,7 +50559,7 @@
       </c>
       <c r="B2929" s="19" t="inlineStr">
         <is>
-          <t>EUS-38676</t>
+          <t>EUS-39957</t>
         </is>
       </c>
       <c r="C2929" s="20" t="n"/>
@@ -50777,7 +50635,7 @@
       </c>
       <c r="B2934" s="19" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="C2934" s="20" t="n"/>
@@ -50853,7 +50711,7 @@
       </c>
       <c r="B2939" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-publico-transporte-urbano-viajeros-autobus-arrasate/expjaso750179/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/comunicacion-previs-digitalizacion-2027/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2939" s="20" t="n"/>
@@ -50864,7 +50722,7 @@
     <row r="2941" ht="30" customHeight="1">
       <c r="A2941" s="16" t="inlineStr">
         <is>
-          <t>FICHA 197: EUS-18235</t>
+          <t>FICHA 197: EUS-35301</t>
         </is>
       </c>
       <c r="B2941" s="17" t="n"/>
@@ -50889,7 +50747,7 @@
       <c r="E2942" s="20" t="n"/>
       <c r="F2942" s="20" t="n"/>
     </row>
-    <row r="2943" ht="45" customHeight="1">
+    <row r="2943" ht="20" customHeight="1">
       <c r="A2943" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -50897,7 +50755,7 @@
       </c>
       <c r="B2943" s="19" t="inlineStr">
         <is>
-          <t>Mantenimiento de la jardinería y limpieza de los parques de Monterron y Santa Barbara de Arrasate (reservado a centros especiales de empleo de iniciativa social y empresas de inserción)</t>
+          <t>transporte autobús histórico centenario funicular</t>
         </is>
       </c>
       <c r="C2943" s="20" t="n"/>
@@ -50913,7 +50771,7 @@
       </c>
       <c r="B2944" s="19" t="inlineStr">
         <is>
-          <t>EUS-18235</t>
+          <t>EUS-35301</t>
         </is>
       </c>
       <c r="C2944" s="20" t="n"/>
@@ -51065,7 +50923,7 @@
       </c>
       <c r="B2954" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/mantenimiento-jardineria-y-limpieza-parques-monterron-y-santa-barbara-arrasate-reservado-centros-especiales-empleo-iniciativa-social-y-empresas-insercion/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/transporte-autobus-historico-centenario-funicular/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2954" s="20" t="n"/>
@@ -51076,7 +50934,7 @@
     <row r="2956" ht="30" customHeight="1">
       <c r="A2956" s="16" t="inlineStr">
         <is>
-          <t>FICHA 198: EUS-95301</t>
+          <t>FICHA 198: EUS-05161</t>
         </is>
       </c>
       <c r="B2956" s="17" t="n"/>
@@ -51109,7 +50967,7 @@
       </c>
       <c r="B2958" s="19" t="inlineStr">
         <is>
-          <t>Productos de limpieza para andretxea</t>
+          <t>suministro artículos de limpieza</t>
         </is>
       </c>
       <c r="C2958" s="20" t="n"/>
@@ -51125,7 +50983,7 @@
       </c>
       <c r="B2959" s="19" t="inlineStr">
         <is>
-          <t>EUS-95301</t>
+          <t>EUS-05161</t>
         </is>
       </c>
       <c r="C2959" s="20" t="n"/>
@@ -51277,7 +51135,7 @@
       </c>
       <c r="B2969" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/productos-limpieza-andretxea/expgeeibar22008/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-articulos-limpieza/expcm539280/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2969" s="20" t="n"/>
@@ -51288,7 +51146,7 @@
     <row r="2971" ht="30" customHeight="1">
       <c r="A2971" s="16" t="inlineStr">
         <is>
-          <t>FICHA 199: EUS-12012</t>
+          <t>FICHA 199: EUS-89367</t>
         </is>
       </c>
       <c r="B2971" s="17" t="n"/>
@@ -51321,7 +51179,7 @@
       </c>
       <c r="B2973" s="19" t="inlineStr">
         <is>
-          <t>Menaje para las viviendas municipales</t>
+          <t>diorama estación kontxa ut 980 inaguación pasante</t>
         </is>
       </c>
       <c r="C2973" s="20" t="n"/>
@@ -51337,7 +51195,7 @@
       </c>
       <c r="B2974" s="19" t="inlineStr">
         <is>
-          <t>EUS-12012</t>
+          <t>EUS-89367</t>
         </is>
       </c>
       <c r="C2974" s="20" t="n"/>
@@ -51489,7 +51347,7 @@
       </c>
       <c r="B2984" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/menaje-viviendas-municipales/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/diorama-estacion-kontxa-ut-980-inaguacion-pasante/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2984" s="20" t="n"/>
@@ -51500,7 +51358,7 @@
     <row r="2986" ht="30" customHeight="1">
       <c r="A2986" s="16" t="inlineStr">
         <is>
-          <t>FICHA 200: EUS-26392</t>
+          <t>FICHA 200: EUS-18525</t>
         </is>
       </c>
       <c r="B2986" s="17" t="n"/>
@@ -51533,7 +51391,7 @@
       </c>
       <c r="B2988" s="19" t="inlineStr">
         <is>
-          <t>Menaje de hogar para viviendas municipales</t>
+          <t>trabajos y transportes de mercancías</t>
         </is>
       </c>
       <c r="C2988" s="20" t="n"/>
@@ -51549,7 +51407,7 @@
       </c>
       <c r="B2989" s="19" t="inlineStr">
         <is>
-          <t>EUS-26392</t>
+          <t>EUS-18525</t>
         </is>
       </c>
       <c r="C2989" s="20" t="n"/>
@@ -51701,7 +51559,7 @@
       </c>
       <c r="B2999" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/menaje-hogar-viviendas-municipales/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/trabajos-y-transportes-mercancias/expcm539272/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2999" s="20" t="n"/>
@@ -51709,644 +51567,8 @@
       <c r="E2999" s="20" t="n"/>
       <c r="F2999" s="20" t="n"/>
     </row>
-    <row r="3001" ht="30" customHeight="1">
-      <c r="A3001" s="16" t="inlineStr">
-        <is>
-          <t>FICHA 201: EUS-09152</t>
-        </is>
-      </c>
-      <c r="B3001" s="17" t="n"/>
-      <c r="C3001" s="17" t="n"/>
-      <c r="D3001" s="17" t="n"/>
-      <c r="E3001" s="17" t="n"/>
-      <c r="F3001" s="17" t="n"/>
-    </row>
-    <row r="3002" ht="20" customHeight="1">
-      <c r="A3002" s="18" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B3002" s="19" t="inlineStr">
-        <is>
-          <t>🟢 Euskadi</t>
-        </is>
-      </c>
-      <c r="C3002" s="20" t="n"/>
-      <c r="D3002" s="20" t="n"/>
-      <c r="E3002" s="20" t="n"/>
-      <c r="F3002" s="20" t="n"/>
-    </row>
-    <row r="3003" ht="20" customHeight="1">
-      <c r="A3003" s="18" t="inlineStr">
-        <is>
-          <t>Titulo</t>
-        </is>
-      </c>
-      <c r="B3003" s="19" t="inlineStr">
-        <is>
-          <t>Paraguas como obsequio para el día de aitites-amamas en fiestas</t>
-        </is>
-      </c>
-      <c r="C3003" s="20" t="n"/>
-      <c r="D3003" s="20" t="n"/>
-      <c r="E3003" s="20" t="n"/>
-      <c r="F3003" s="20" t="n"/>
-    </row>
-    <row r="3004" ht="20" customHeight="1">
-      <c r="A3004" s="18" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3004" s="19" t="inlineStr">
-        <is>
-          <t>EUS-09152</t>
-        </is>
-      </c>
-      <c r="C3004" s="20" t="n"/>
-      <c r="D3004" s="20" t="n"/>
-      <c r="E3004" s="20" t="n"/>
-      <c r="F3004" s="20" t="n"/>
-    </row>
-    <row r="3005" ht="20" customHeight="1">
-      <c r="A3005" s="18" t="inlineStr">
-        <is>
-          <t>Programa</t>
-        </is>
-      </c>
-      <c r="B3005" s="19" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="C3005" s="20" t="n"/>
-      <c r="D3005" s="20" t="n"/>
-      <c r="E3005" s="20" t="n"/>
-      <c r="F3005" s="20" t="n"/>
-    </row>
-    <row r="3006" ht="20" customHeight="1">
-      <c r="A3006" s="18" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B3006" s="19" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C3006" s="20" t="n"/>
-      <c r="D3006" s="20" t="n"/>
-      <c r="E3006" s="20" t="n"/>
-      <c r="F3006" s="20" t="n"/>
-    </row>
-    <row r="3007" ht="20" customHeight="1">
-      <c r="A3007" s="18" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="B3007" s="19" t="inlineStr"/>
-      <c r="C3007" s="20" t="n"/>
-      <c r="D3007" s="20" t="n"/>
-      <c r="E3007" s="20" t="n"/>
-      <c r="F3007" s="20" t="n"/>
-    </row>
-    <row r="3008" ht="20" customHeight="1">
-      <c r="A3008" s="18" t="inlineStr">
-        <is>
-          <t>Presupuesto (EUR)</t>
-        </is>
-      </c>
-      <c r="B3008" s="19" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="C3008" s="20" t="n"/>
-      <c r="D3008" s="20" t="n"/>
-      <c r="E3008" s="20" t="n"/>
-      <c r="F3008" s="20" t="n"/>
-    </row>
-    <row r="3009" ht="20" customHeight="1">
-      <c r="A3009" s="18" t="inlineStr">
-        <is>
-          <t>Tipo de Accion</t>
-        </is>
-      </c>
-      <c r="B3009" s="19" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="C3009" s="20" t="n"/>
-      <c r="D3009" s="20" t="n"/>
-      <c r="E3009" s="20" t="n"/>
-      <c r="F3009" s="20" t="n"/>
-    </row>
-    <row r="3010" ht="20" customHeight="1">
-      <c r="A3010" s="18" t="inlineStr">
-        <is>
-          <t>Call ID</t>
-        </is>
-      </c>
-      <c r="B3010" s="19" t="inlineStr"/>
-      <c r="C3010" s="20" t="n"/>
-      <c r="D3010" s="20" t="n"/>
-      <c r="E3010" s="20" t="n"/>
-      <c r="F3010" s="20" t="n"/>
-    </row>
-    <row r="3011" ht="20" customHeight="1">
-      <c r="A3011" s="18" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="B3011" s="19" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="C3011" s="20" t="n"/>
-      <c r="D3011" s="20" t="n"/>
-      <c r="E3011" s="20" t="n"/>
-      <c r="F3011" s="20" t="n"/>
-    </row>
-    <row r="3012" ht="20" customHeight="1">
-      <c r="A3012" s="18" t="inlineStr">
-        <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="B3012" s="19" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C3012" s="20" t="n"/>
-      <c r="D3012" s="20" t="n"/>
-      <c r="E3012" s="20" t="n"/>
-      <c r="F3012" s="20" t="n"/>
-    </row>
-    <row r="3013" ht="20" customHeight="1">
-      <c r="A3013" s="18" t="inlineStr">
-        <is>
-          <t>Relevancia Bilbao</t>
-        </is>
-      </c>
-      <c r="B3013" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
-        </is>
-      </c>
-      <c r="C3013" s="20" t="n"/>
-      <c r="D3013" s="20" t="n"/>
-      <c r="E3013" s="20" t="n"/>
-      <c r="F3013" s="20" t="n"/>
-    </row>
-    <row r="3014" ht="45" customHeight="1">
-      <c r="A3014" s="18" t="inlineStr">
-        <is>
-          <t>Enlace al portal</t>
-        </is>
-      </c>
-      <c r="B3014" s="22" t="inlineStr">
-        <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/paraguas-como-obsequio-dia-aitites-amamas-fiestas/web01-tramite/es/</t>
-        </is>
-      </c>
-      <c r="C3014" s="20" t="n"/>
-      <c r="D3014" s="20" t="n"/>
-      <c r="E3014" s="20" t="n"/>
-      <c r="F3014" s="20" t="n"/>
-    </row>
-    <row r="3016" ht="30" customHeight="1">
-      <c r="A3016" s="16" t="inlineStr">
-        <is>
-          <t>FICHA 202: EUS-46833</t>
-        </is>
-      </c>
-      <c r="B3016" s="17" t="n"/>
-      <c r="C3016" s="17" t="n"/>
-      <c r="D3016" s="17" t="n"/>
-      <c r="E3016" s="17" t="n"/>
-      <c r="F3016" s="17" t="n"/>
-    </row>
-    <row r="3017" ht="20" customHeight="1">
-      <c r="A3017" s="18" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B3017" s="19" t="inlineStr">
-        <is>
-          <t>🟢 Euskadi</t>
-        </is>
-      </c>
-      <c r="C3017" s="20" t="n"/>
-      <c r="D3017" s="20" t="n"/>
-      <c r="E3017" s="20" t="n"/>
-      <c r="F3017" s="20" t="n"/>
-    </row>
-    <row r="3018" ht="20" customHeight="1">
-      <c r="A3018" s="18" t="inlineStr">
-        <is>
-          <t>Titulo</t>
-        </is>
-      </c>
-      <c r="B3018" s="19" t="inlineStr">
-        <is>
-          <t>Suministro e instalación de 27 farolas led de alumbrado solar autónomo</t>
-        </is>
-      </c>
-      <c r="C3018" s="20" t="n"/>
-      <c r="D3018" s="20" t="n"/>
-      <c r="E3018" s="20" t="n"/>
-      <c r="F3018" s="20" t="n"/>
-    </row>
-    <row r="3019" ht="20" customHeight="1">
-      <c r="A3019" s="18" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3019" s="19" t="inlineStr">
-        <is>
-          <t>EUS-46833</t>
-        </is>
-      </c>
-      <c r="C3019" s="20" t="n"/>
-      <c r="D3019" s="20" t="n"/>
-      <c r="E3019" s="20" t="n"/>
-      <c r="F3019" s="20" t="n"/>
-    </row>
-    <row r="3020" ht="20" customHeight="1">
-      <c r="A3020" s="18" t="inlineStr">
-        <is>
-          <t>Programa</t>
-        </is>
-      </c>
-      <c r="B3020" s="19" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="C3020" s="20" t="n"/>
-      <c r="D3020" s="20" t="n"/>
-      <c r="E3020" s="20" t="n"/>
-      <c r="F3020" s="20" t="n"/>
-    </row>
-    <row r="3021" ht="20" customHeight="1">
-      <c r="A3021" s="18" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B3021" s="19" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C3021" s="20" t="n"/>
-      <c r="D3021" s="20" t="n"/>
-      <c r="E3021" s="20" t="n"/>
-      <c r="F3021" s="20" t="n"/>
-    </row>
-    <row r="3022" ht="20" customHeight="1">
-      <c r="A3022" s="18" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="B3022" s="19" t="inlineStr"/>
-      <c r="C3022" s="20" t="n"/>
-      <c r="D3022" s="20" t="n"/>
-      <c r="E3022" s="20" t="n"/>
-      <c r="F3022" s="20" t="n"/>
-    </row>
-    <row r="3023" ht="20" customHeight="1">
-      <c r="A3023" s="18" t="inlineStr">
-        <is>
-          <t>Presupuesto (EUR)</t>
-        </is>
-      </c>
-      <c r="B3023" s="19" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="C3023" s="20" t="n"/>
-      <c r="D3023" s="20" t="n"/>
-      <c r="E3023" s="20" t="n"/>
-      <c r="F3023" s="20" t="n"/>
-    </row>
-    <row r="3024" ht="20" customHeight="1">
-      <c r="A3024" s="18" t="inlineStr">
-        <is>
-          <t>Tipo de Accion</t>
-        </is>
-      </c>
-      <c r="B3024" s="19" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="C3024" s="20" t="n"/>
-      <c r="D3024" s="20" t="n"/>
-      <c r="E3024" s="20" t="n"/>
-      <c r="F3024" s="20" t="n"/>
-    </row>
-    <row r="3025" ht="20" customHeight="1">
-      <c r="A3025" s="18" t="inlineStr">
-        <is>
-          <t>Call ID</t>
-        </is>
-      </c>
-      <c r="B3025" s="19" t="inlineStr"/>
-      <c r="C3025" s="20" t="n"/>
-      <c r="D3025" s="20" t="n"/>
-      <c r="E3025" s="20" t="n"/>
-      <c r="F3025" s="20" t="n"/>
-    </row>
-    <row r="3026" ht="20" customHeight="1">
-      <c r="A3026" s="18" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="B3026" s="19" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="C3026" s="20" t="n"/>
-      <c r="D3026" s="20" t="n"/>
-      <c r="E3026" s="20" t="n"/>
-      <c r="F3026" s="20" t="n"/>
-    </row>
-    <row r="3027" ht="20" customHeight="1">
-      <c r="A3027" s="18" t="inlineStr">
-        <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="B3027" s="19" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C3027" s="20" t="n"/>
-      <c r="D3027" s="20" t="n"/>
-      <c r="E3027" s="20" t="n"/>
-      <c r="F3027" s="20" t="n"/>
-    </row>
-    <row r="3028" ht="20" customHeight="1">
-      <c r="A3028" s="18" t="inlineStr">
-        <is>
-          <t>Relevancia Bilbao</t>
-        </is>
-      </c>
-      <c r="B3028" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
-        </is>
-      </c>
-      <c r="C3028" s="20" t="n"/>
-      <c r="D3028" s="20" t="n"/>
-      <c r="E3028" s="20" t="n"/>
-      <c r="F3028" s="20" t="n"/>
-    </row>
-    <row r="3029" ht="45" customHeight="1">
-      <c r="A3029" s="18" t="inlineStr">
-        <is>
-          <t>Enlace al portal</t>
-        </is>
-      </c>
-      <c r="B3029" s="22" t="inlineStr">
-        <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-e-instalacion-27-farolas-led-alumbrado-solar-autonomo/web01-tramite/es/</t>
-        </is>
-      </c>
-      <c r="C3029" s="20" t="n"/>
-      <c r="D3029" s="20" t="n"/>
-      <c r="E3029" s="20" t="n"/>
-      <c r="F3029" s="20" t="n"/>
-    </row>
-    <row r="3031" ht="30" customHeight="1">
-      <c r="A3031" s="16" t="inlineStr">
-        <is>
-          <t>FICHA 203: EUS-10725</t>
-        </is>
-      </c>
-      <c r="B3031" s="17" t="n"/>
-      <c r="C3031" s="17" t="n"/>
-      <c r="D3031" s="17" t="n"/>
-      <c r="E3031" s="17" t="n"/>
-      <c r="F3031" s="17" t="n"/>
-    </row>
-    <row r="3032" ht="20" customHeight="1">
-      <c r="A3032" s="18" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B3032" s="19" t="inlineStr">
-        <is>
-          <t>🟢 Euskadi</t>
-        </is>
-      </c>
-      <c r="C3032" s="20" t="n"/>
-      <c r="D3032" s="20" t="n"/>
-      <c r="E3032" s="20" t="n"/>
-      <c r="F3032" s="20" t="n"/>
-    </row>
-    <row r="3033" ht="45" customHeight="1">
-      <c r="A3033" s="18" t="inlineStr">
-        <is>
-          <t>Titulo</t>
-        </is>
-      </c>
-      <c r="B3033" s="19" t="inlineStr">
-        <is>
-          <t>Suministro en régimen de alquiler de 2 contenedores y 1 caseta vestuario con 2 duchas para uso de la brigada municipal de obras</t>
-        </is>
-      </c>
-      <c r="C3033" s="20" t="n"/>
-      <c r="D3033" s="20" t="n"/>
-      <c r="E3033" s="20" t="n"/>
-      <c r="F3033" s="20" t="n"/>
-    </row>
-    <row r="3034" ht="20" customHeight="1">
-      <c r="A3034" s="18" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3034" s="19" t="inlineStr">
-        <is>
-          <t>EUS-10725</t>
-        </is>
-      </c>
-      <c r="C3034" s="20" t="n"/>
-      <c r="D3034" s="20" t="n"/>
-      <c r="E3034" s="20" t="n"/>
-      <c r="F3034" s="20" t="n"/>
-    </row>
-    <row r="3035" ht="20" customHeight="1">
-      <c r="A3035" s="18" t="inlineStr">
-        <is>
-          <t>Programa</t>
-        </is>
-      </c>
-      <c r="B3035" s="19" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="C3035" s="20" t="n"/>
-      <c r="D3035" s="20" t="n"/>
-      <c r="E3035" s="20" t="n"/>
-      <c r="F3035" s="20" t="n"/>
-    </row>
-    <row r="3036" ht="20" customHeight="1">
-      <c r="A3036" s="18" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B3036" s="19" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C3036" s="20" t="n"/>
-      <c r="D3036" s="20" t="n"/>
-      <c r="E3036" s="20" t="n"/>
-      <c r="F3036" s="20" t="n"/>
-    </row>
-    <row r="3037" ht="20" customHeight="1">
-      <c r="A3037" s="18" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="B3037" s="19" t="inlineStr"/>
-      <c r="C3037" s="20" t="n"/>
-      <c r="D3037" s="20" t="n"/>
-      <c r="E3037" s="20" t="n"/>
-      <c r="F3037" s="20" t="n"/>
-    </row>
-    <row r="3038" ht="20" customHeight="1">
-      <c r="A3038" s="18" t="inlineStr">
-        <is>
-          <t>Presupuesto (EUR)</t>
-        </is>
-      </c>
-      <c r="B3038" s="19" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="C3038" s="20" t="n"/>
-      <c r="D3038" s="20" t="n"/>
-      <c r="E3038" s="20" t="n"/>
-      <c r="F3038" s="20" t="n"/>
-    </row>
-    <row r="3039" ht="20" customHeight="1">
-      <c r="A3039" s="18" t="inlineStr">
-        <is>
-          <t>Tipo de Accion</t>
-        </is>
-      </c>
-      <c r="B3039" s="19" t="inlineStr">
-        <is>
-          <t>Licitacion Euskadi</t>
-        </is>
-      </c>
-      <c r="C3039" s="20" t="n"/>
-      <c r="D3039" s="20" t="n"/>
-      <c r="E3039" s="20" t="n"/>
-      <c r="F3039" s="20" t="n"/>
-    </row>
-    <row r="3040" ht="20" customHeight="1">
-      <c r="A3040" s="18" t="inlineStr">
-        <is>
-          <t>Call ID</t>
-        </is>
-      </c>
-      <c r="B3040" s="19" t="inlineStr"/>
-      <c r="C3040" s="20" t="n"/>
-      <c r="D3040" s="20" t="n"/>
-      <c r="E3040" s="20" t="n"/>
-      <c r="F3040" s="20" t="n"/>
-    </row>
-    <row r="3041" ht="20" customHeight="1">
-      <c r="A3041" s="18" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="B3041" s="19" t="inlineStr">
-        <is>
-          <t>Gobierno Vasco / Sector Publico Euskadi</t>
-        </is>
-      </c>
-      <c r="C3041" s="20" t="n"/>
-      <c r="D3041" s="20" t="n"/>
-      <c r="E3041" s="20" t="n"/>
-      <c r="F3041" s="20" t="n"/>
-    </row>
-    <row r="3042" ht="20" customHeight="1">
-      <c r="A3042" s="18" t="inlineStr">
-        <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="B3042" s="19" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C3042" s="20" t="n"/>
-      <c r="D3042" s="20" t="n"/>
-      <c r="E3042" s="20" t="n"/>
-      <c r="F3042" s="20" t="n"/>
-    </row>
-    <row r="3043" ht="20" customHeight="1">
-      <c r="A3043" s="18" t="inlineStr">
-        <is>
-          <t>Relevancia Bilbao</t>
-        </is>
-      </c>
-      <c r="B3043" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MEDIA — </t>
-        </is>
-      </c>
-      <c r="C3043" s="20" t="n"/>
-      <c r="D3043" s="20" t="n"/>
-      <c r="E3043" s="20" t="n"/>
-      <c r="F3043" s="20" t="n"/>
-    </row>
-    <row r="3044" ht="45" customHeight="1">
-      <c r="A3044" s="18" t="inlineStr">
-        <is>
-          <t>Enlace al portal</t>
-        </is>
-      </c>
-      <c r="B3044" s="22" t="inlineStr">
-        <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/suministro-regimen-alquiler-2-contenedores-y-1-caseta-vestuario-2-duchas-uso-brigada-municipal-obras/web01-tramite/es/</t>
-        </is>
-      </c>
-      <c r="C3044" s="20" t="n"/>
-      <c r="D3044" s="20" t="n"/>
-      <c r="E3044" s="20" t="n"/>
-      <c r="F3044" s="20" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="2842">
+  <mergeCells count="2800">
     <mergeCell ref="B679:F679"/>
     <mergeCell ref="B2192:F2192"/>
     <mergeCell ref="B1765:F1765"/>
@@ -52528,7 +51750,6 @@
     <mergeCell ref="B2858:F2858"/>
     <mergeCell ref="B2103:F2103"/>
     <mergeCell ref="A976:F976"/>
-    <mergeCell ref="B3003:F3003"/>
     <mergeCell ref="B2242:F2242"/>
     <mergeCell ref="B157:F157"/>
     <mergeCell ref="B455:F455"/>
@@ -52537,7 +51758,6 @@
     <mergeCell ref="B762:F762"/>
     <mergeCell ref="B1821:F1821"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B3005:F3005"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B1973:F1973"/>
     <mergeCell ref="B1218:F1218"/>
@@ -52656,11 +51876,9 @@
     <mergeCell ref="B123:F123"/>
     <mergeCell ref="B2275:F2275"/>
     <mergeCell ref="B2573:F2573"/>
-    <mergeCell ref="B3002:F3002"/>
     <mergeCell ref="B2996:F2996"/>
     <mergeCell ref="B1184:F1184"/>
     <mergeCell ref="B2270:F2270"/>
-    <mergeCell ref="B3027:F3027"/>
     <mergeCell ref="B2699:F2699"/>
     <mergeCell ref="B297:F297"/>
     <mergeCell ref="B813:F813"/>
@@ -52670,7 +51888,6 @@
     <mergeCell ref="B902:F902"/>
     <mergeCell ref="B2724:F2724"/>
     <mergeCell ref="B1331:F1331"/>
-    <mergeCell ref="B3022:F3022"/>
     <mergeCell ref="B815:F815"/>
     <mergeCell ref="B1629:F1629"/>
     <mergeCell ref="B597:F597"/>
@@ -52775,7 +51992,6 @@
     <mergeCell ref="B1654:F1654"/>
     <mergeCell ref="B595:F595"/>
     <mergeCell ref="B1925:F1925"/>
-    <mergeCell ref="B3020:F3020"/>
     <mergeCell ref="B893:F893"/>
     <mergeCell ref="B2838:F2838"/>
     <mergeCell ref="B2083:F2083"/>
@@ -52807,9 +52023,7 @@
     <mergeCell ref="B921:F921"/>
     <mergeCell ref="B606:F606"/>
     <mergeCell ref="B2741:F2741"/>
-    <mergeCell ref="B3039:F3039"/>
     <mergeCell ref="B2007:F2007"/>
-    <mergeCell ref="B3033:F3033"/>
     <mergeCell ref="B2436:F2436"/>
     <mergeCell ref="A1276:F1276"/>
     <mergeCell ref="B2770:F2770"/>
@@ -52878,7 +52092,6 @@
     <mergeCell ref="B2073:F2073"/>
     <mergeCell ref="B2048:F2048"/>
     <mergeCell ref="B261:F261"/>
-    <mergeCell ref="A3016:F3016"/>
     <mergeCell ref="B2379:F2379"/>
     <mergeCell ref="B2193:F2193"/>
     <mergeCell ref="A616:F616"/>
@@ -53008,7 +52221,6 @@
     <mergeCell ref="A2731:F2731"/>
     <mergeCell ref="B2246:F2246"/>
     <mergeCell ref="A946:F946"/>
-    <mergeCell ref="A3031:F3031"/>
     <mergeCell ref="A631:F631"/>
     <mergeCell ref="B117:F117"/>
     <mergeCell ref="B1783:F1783"/>
@@ -53047,7 +52259,6 @@
     <mergeCell ref="B1804:F1804"/>
     <mergeCell ref="B2882:F2882"/>
     <mergeCell ref="B797:F797"/>
-    <mergeCell ref="B3013:F3013"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A2011:F2011"/>
     <mergeCell ref="B2592:F2592"/>
@@ -53057,11 +52268,9 @@
     <mergeCell ref="B2884:F2884"/>
     <mergeCell ref="B799:F799"/>
     <mergeCell ref="B2129:F2129"/>
-    <mergeCell ref="B3021:F3021"/>
     <mergeCell ref="B342:F342"/>
     <mergeCell ref="B2585:F2585"/>
     <mergeCell ref="B1526:F1526"/>
-    <mergeCell ref="B3014:F3014"/>
     <mergeCell ref="B2473:F2473"/>
     <mergeCell ref="B1099:F1099"/>
     <mergeCell ref="B2915:F2915"/>
@@ -53086,7 +52295,6 @@
     <mergeCell ref="B2155:F2155"/>
     <mergeCell ref="B1123:F1123"/>
     <mergeCell ref="B368:F368"/>
-    <mergeCell ref="B3041:F3041"/>
     <mergeCell ref="B1254:F1254"/>
     <mergeCell ref="B1430:F1430"/>
     <mergeCell ref="B1552:F1552"/>
@@ -53269,7 +52477,6 @@
     <mergeCell ref="B1304:F1304"/>
     <mergeCell ref="B1608:F1608"/>
     <mergeCell ref="B2695:F2695"/>
-    <mergeCell ref="B3037:F3037"/>
     <mergeCell ref="B1967:F1967"/>
     <mergeCell ref="B908:F908"/>
     <mergeCell ref="B883:F883"/>
@@ -53287,7 +52494,6 @@
     <mergeCell ref="B1353:F1353"/>
     <mergeCell ref="B636:F636"/>
     <mergeCell ref="B2721:F2721"/>
-    <mergeCell ref="B3019:F3019"/>
     <mergeCell ref="B296:F296"/>
     <mergeCell ref="B934:F934"/>
     <mergeCell ref="B1232:F1232"/>
@@ -53406,7 +52612,6 @@
     <mergeCell ref="B2801:F2801"/>
     <mergeCell ref="B2837:F2837"/>
     <mergeCell ref="B2720:F2720"/>
-    <mergeCell ref="B3018:F3018"/>
     <mergeCell ref="B289:F289"/>
     <mergeCell ref="B1479:F1479"/>
     <mergeCell ref="B1777:F1777"/>
@@ -53687,7 +52892,6 @@
     <mergeCell ref="A676:F676"/>
     <mergeCell ref="B137:F137"/>
     <mergeCell ref="B2283:F2283"/>
-    <mergeCell ref="B3010:F3010"/>
     <mergeCell ref="B925:F925"/>
     <mergeCell ref="B1223:F1223"/>
     <mergeCell ref="B164:F164"/>
@@ -53699,13 +52903,11 @@
     <mergeCell ref="B498:F498"/>
     <mergeCell ref="B1986:F1986"/>
     <mergeCell ref="B2599:F2599"/>
-    <mergeCell ref="B3012:F3012"/>
     <mergeCell ref="B2284:F2284"/>
     <mergeCell ref="B1225:F1225"/>
     <mergeCell ref="B1523:F1523"/>
     <mergeCell ref="B2891:F2891"/>
     <mergeCell ref="B2713:F2713"/>
-    <mergeCell ref="B3011:F3011"/>
     <mergeCell ref="B1979:F1979"/>
     <mergeCell ref="A2191:F2191"/>
     <mergeCell ref="B2286:F2286"/>
@@ -53718,7 +52920,6 @@
     <mergeCell ref="A2491:F2491"/>
     <mergeCell ref="A406:F406"/>
     <mergeCell ref="B951:F951"/>
-    <mergeCell ref="B3036:F3036"/>
     <mergeCell ref="B1249:F1249"/>
     <mergeCell ref="B524:F524"/>
     <mergeCell ref="B1854:F1854"/>
@@ -53726,7 +52927,6 @@
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B2012:F2012"/>
     <mergeCell ref="B953:F953"/>
-    <mergeCell ref="B3038:F3038"/>
     <mergeCell ref="B1251:F1251"/>
     <mergeCell ref="B1549:F1549"/>
     <mergeCell ref="B1856:F1856"/>
@@ -53810,9 +53010,7 @@
     <mergeCell ref="B1652:F1652"/>
     <mergeCell ref="B2678:F2678"/>
     <mergeCell ref="B891:F891"/>
-    <mergeCell ref="B3009:F3009"/>
     <mergeCell ref="B1191:F1191"/>
-    <mergeCell ref="B3034:F3034"/>
     <mergeCell ref="B609:F609"/>
     <mergeCell ref="B1247:F1247"/>
     <mergeCell ref="B1977:F1977"/>
@@ -53830,9 +53028,7 @@
     <mergeCell ref="B1547:F1547"/>
     <mergeCell ref="B1207:F1207"/>
     <mergeCell ref="B490:F490"/>
-    <mergeCell ref="B3035:F3035"/>
     <mergeCell ref="B1338:F1338"/>
-    <mergeCell ref="B3029:F3029"/>
     <mergeCell ref="B604:F604"/>
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="B2608:F2608"/>
@@ -53999,7 +53195,6 @@
     <mergeCell ref="B999:F999"/>
     <mergeCell ref="B1303:F1303"/>
     <mergeCell ref="B1297:F1297"/>
-    <mergeCell ref="A3001:F3001"/>
     <mergeCell ref="B2487:F2487"/>
     <mergeCell ref="B2514:F2514"/>
     <mergeCell ref="B2785:F2785"/>
@@ -54115,7 +53310,6 @@
     <mergeCell ref="B2153:F2153"/>
     <mergeCell ref="B1838:F1838"/>
     <mergeCell ref="B779:F779"/>
-    <mergeCell ref="B3028:F3028"/>
     <mergeCell ref="B2810:F2810"/>
     <mergeCell ref="B358:F358"/>
     <mergeCell ref="B2138:F2138"/>
@@ -54322,14 +53516,12 @@
     <mergeCell ref="B1204:F1204"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B3007:F3007"/>
     <mergeCell ref="B922:F922"/>
     <mergeCell ref="B167:F167"/>
     <mergeCell ref="B2290:F2290"/>
     <mergeCell ref="B1220:F1220"/>
     <mergeCell ref="B503:F503"/>
     <mergeCell ref="B2588:F2588"/>
-    <mergeCell ref="B3017:F3017"/>
     <mergeCell ref="B932:F932"/>
     <mergeCell ref="B2702:F2702"/>
     <mergeCell ref="B617:F617"/>
@@ -54433,7 +53625,6 @@
     <mergeCell ref="B1315:F1315"/>
     <mergeCell ref="B283:F283"/>
     <mergeCell ref="B2377:F2377"/>
-    <mergeCell ref="B3042:F3042"/>
     <mergeCell ref="B1649:F1649"/>
     <mergeCell ref="B590:F590"/>
     <mergeCell ref="B888:F888"/>
@@ -54457,14 +53648,12 @@
     <mergeCell ref="B512:F512"/>
     <mergeCell ref="B2734:F2734"/>
     <mergeCell ref="B2728:F2728"/>
-    <mergeCell ref="B3032:F3032"/>
     <mergeCell ref="B2000:F2000"/>
     <mergeCell ref="B303:F303"/>
     <mergeCell ref="B941:F941"/>
     <mergeCell ref="A1726:F1726"/>
     <mergeCell ref="B1239:F1239"/>
     <mergeCell ref="B484:F484"/>
-    <mergeCell ref="B3026:F3026"/>
     <mergeCell ref="B2429:F2429"/>
     <mergeCell ref="B732:F732"/>
     <mergeCell ref="B2605:F2605"/>
@@ -54590,7 +53779,6 @@
     <mergeCell ref="B1782:F1782"/>
     <mergeCell ref="B899:F899"/>
     <mergeCell ref="B752:F752"/>
-    <mergeCell ref="B3025:F3025"/>
     <mergeCell ref="B2112:F2112"/>
     <mergeCell ref="B325:F325"/>
     <mergeCell ref="B2568:F2568"/>
@@ -54738,7 +53926,6 @@
     <mergeCell ref="B2708:F2708"/>
     <mergeCell ref="B1061:F1061"/>
     <mergeCell ref="A2461:F2461"/>
-    <mergeCell ref="B3006:F3006"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B1097:F1097"/>
     <mergeCell ref="B2579:F2579"/>
@@ -54750,7 +53937,6 @@
     <mergeCell ref="B1090:F1090"/>
     <mergeCell ref="B1361:F1361"/>
     <mergeCell ref="B2122:F2122"/>
-    <mergeCell ref="B3008:F3008"/>
     <mergeCell ref="B1221:F1221"/>
     <mergeCell ref="B1397:F1397"/>
     <mergeCell ref="B1519:F1519"/>
@@ -54845,7 +54031,6 @@
     <mergeCell ref="B307:F307"/>
     <mergeCell ref="B429:F429"/>
     <mergeCell ref="B1034:F1034"/>
-    <mergeCell ref="B3004:F3004"/>
     <mergeCell ref="B2979:F2979"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B1947:F1947"/>
@@ -54882,7 +54067,6 @@
     <mergeCell ref="B144:F144"/>
     <mergeCell ref="B442:F442"/>
     <mergeCell ref="B1116:F1116"/>
-    <mergeCell ref="B3023:F3023"/>
     <mergeCell ref="B1414:F1414"/>
     <mergeCell ref="B2604:F2604"/>
     <mergeCell ref="B907:F907"/>
@@ -54897,7 +54081,6 @@
     <mergeCell ref="B318:F318"/>
     <mergeCell ref="A1741:F1741"/>
     <mergeCell ref="B1098:F1098"/>
-    <mergeCell ref="B3043:F3043"/>
     <mergeCell ref="B958:F958"/>
     <mergeCell ref="B1134:F1134"/>
     <mergeCell ref="B1256:F1256"/>
@@ -54917,7 +54100,6 @@
     <mergeCell ref="B1562:F1562"/>
     <mergeCell ref="B2317:F2317"/>
     <mergeCell ref="B1556:F1556"/>
-    <mergeCell ref="B3044:F3044"/>
     <mergeCell ref="A856:F856"/>
     <mergeCell ref="B1129:F1129"/>
     <mergeCell ref="B374:F374"/>
@@ -55017,7 +54199,6 @@
     <mergeCell ref="B197:F197"/>
     <mergeCell ref="B2104:F2104"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B3040:F3040"/>
     <mergeCell ref="B1343:F1343"/>
     <mergeCell ref="B1641:F1641"/>
     <mergeCell ref="B2315:F2315"/>
@@ -55145,7 +54326,6 @@
     <mergeCell ref="B2428:F2428"/>
     <mergeCell ref="B2726:F2726"/>
     <mergeCell ref="B1694:F1694"/>
-    <mergeCell ref="B3024:F3024"/>
     <mergeCell ref="B2878:F2878"/>
     <mergeCell ref="B2123:F2123"/>
     <mergeCell ref="B2457:F2457"/>
@@ -55391,9 +54571,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2969" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2984" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2999" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3014" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3029" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3044" r:id="rId203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55405,7 +54582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J204"/>
+  <dimension ref="A1:J201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -59527,12 +58704,12 @@
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>njaunzdz</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Mr. Dzintars Jaunzems</t>
+          <t>A project intends to build an innovative renewable energy pr</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr"/>
@@ -59559,12 +58736,12 @@
     <row r="129" ht="28" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>njaunzdz</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>A project intends to build an innovative renewable energy pr</t>
+          <t>Mr. Dzintars Jaunzems</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr"/>
@@ -60583,12 +59760,12 @@
     <row r="161" ht="28" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>928057492</t>
+          <t>928211140</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr"/>
@@ -60615,12 +59792,12 @@
     <row r="162" ht="28" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>926227393</t>
+          <t>928057492</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr"/>
@@ -60647,12 +59824,12 @@
     <row r="163" ht="28" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>928211140</t>
+          <t>926227393</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr"/>
@@ -61383,12 +60560,12 @@
     <row r="186" ht="28" customHeight="1">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>892931076</t>
+          <t>936518123</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VILA DE REI</t>
+          <t>Urban Initiative</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr"/>
@@ -61415,12 +60592,12 @@
     <row r="187" ht="28" customHeight="1">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>936518123</t>
+          <t>892931076</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>Urban Initiative</t>
+          <t>MUNICIPIO DE VILA DE REI</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr"/>
@@ -61447,24 +60624,28 @@
     <row r="188" ht="28" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>EU4H</t>
+          <t>EUS-45445</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>European Linkage of Initiative from Science to Action in Hea</t>
-        </is>
-      </c>
-      <c r="C188" s="6" t="inlineStr"/>
+          <t>Coordinación de seguridad y salud en las obras de reparación</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr"/>
       <c r="F188" s="25" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>MUY ALTA</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr"/>
@@ -61479,12 +60660,13 @@
     <row r="189" ht="28" customHeight="1">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>EUS-75332</t>
+          <t>EUS-92164</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>Renovación de las licencias o suscripciones de software VMWa</t>
+          <t>Coordinación de
+seguridad y salud en las obras de desinfecci</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
@@ -61515,7 +60697,7 @@
     <row r="190" ht="28" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>EUS-52813</t>
+          <t>EUS-64887</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
@@ -61551,7 +60733,7 @@
     <row r="191" ht="28" customHeight="1">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>EUS-91123</t>
+          <t>EUS-78605</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
@@ -61587,12 +60769,12 @@
     <row r="192" ht="28" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>EUS-55604</t>
+          <t>EUS-19539</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Redacción del proyecto básico, de ejecución y la dirección f</t>
+          <t>coordinación de seguridad y salud en la obra de renovación y</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
@@ -61623,12 +60805,12 @@
     <row r="193" ht="28" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>EUS-64978</t>
+          <t>EUS-34915</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>Ayudas para la adquisición e implantación de sistemas de nue</t>
+          <t>1-alquiler camión cesta- (j9/01/2025) / seguro diario / gest</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
@@ -61644,7 +60826,7 @@
       <c r="E193" s="6" t="inlineStr"/>
       <c r="F193" s="25" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="G193" s="6" t="inlineStr"/>
@@ -61659,12 +60841,12 @@
     <row r="194" ht="28" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>EUS-61815</t>
+          <t>EUS-66515</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 FAROS DE INNOVACIÓN, 3 transiciones (digital, ecológica y </t>
+          <t>Ayudas para la adquisición e implantación de sistemas de nue</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
@@ -61695,12 +60877,12 @@
     <row r="195" ht="28" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>EUS-29689</t>
+          <t>EUS-12421</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Euro</t>
+          <t xml:space="preserve">9 FAROS DE INNOVACIÓN, 3 transiciones (digital, ecológica y </t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -61731,12 +60913,12 @@
     <row r="196" ht="28" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>EUS-96720</t>
+          <t>EUS-30744</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Comunicación previa - Digitalización 2027</t>
+          <t>MEDIO AMBIENTE URBANO Y FEDER. Ayudas mediante el Fondo Euro</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -61767,12 +60949,12 @@
     <row r="197" ht="28" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>EUS-38676</t>
+          <t>EUS-39957</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>Servicio público de transporte urbano de viajeros en autobús</t>
+          <t>Comunicación previa - Digitalización 2027</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -61803,12 +60985,12 @@
     <row r="198" ht="28" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>EUS-18235</t>
+          <t>EUS-35301</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenimiento de la jardinería y limpieza de los parques de </t>
+          <t>transporte autobús histórico centenario funicular</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
@@ -61839,12 +61021,12 @@
     <row r="199" ht="28" customHeight="1">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>EUS-95301</t>
+          <t>EUS-05161</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>Productos de limpieza para andretxea</t>
+          <t>suministro artículos de limpieza</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
@@ -61875,12 +61057,12 @@
     <row r="200" ht="28" customHeight="1">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>EUS-12012</t>
+          <t>EUS-89367</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Menaje para las viviendas municipales</t>
+          <t>diorama estación kontxa ut 980 inaguación pasante</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
@@ -61911,12 +61093,12 @@
     <row r="201" ht="28" customHeight="1">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>EUS-26392</t>
+          <t>EUS-18525</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>Menaje de hogar para viviendas municipales</t>
+          <t>trabajos y transportes de mercancías</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -61944,116 +61126,8 @@
       <c r="I201" s="6" t="inlineStr"/>
       <c r="J201" s="6" t="inlineStr"/>
     </row>
-    <row r="202" ht="28" customHeight="1">
-      <c r="A202" s="6" t="inlineStr">
-        <is>
-          <t>EUS-09152</t>
-        </is>
-      </c>
-      <c r="B202" s="6" t="inlineStr">
-        <is>
-          <t>Paraguas como obsequio para el día de aitites-amamas en fies</t>
-        </is>
-      </c>
-      <c r="C202" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="D202" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E202" s="6" t="inlineStr"/>
-      <c r="F202" s="25" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="G202" s="6" t="inlineStr"/>
-      <c r="H202" s="6" t="inlineStr">
-        <is>
-          <t>Por revisar</t>
-        </is>
-      </c>
-      <c r="I202" s="6" t="inlineStr"/>
-      <c r="J202" s="6" t="inlineStr"/>
-    </row>
-    <row r="203" ht="28" customHeight="1">
-      <c r="A203" s="6" t="inlineStr">
-        <is>
-          <t>EUS-46833</t>
-        </is>
-      </c>
-      <c r="B203" s="6" t="inlineStr">
-        <is>
-          <t>Suministro e instalación de 27 farolas led de alumbrado sola</t>
-        </is>
-      </c>
-      <c r="C203" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="D203" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E203" s="6" t="inlineStr"/>
-      <c r="F203" s="25" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="G203" s="6" t="inlineStr"/>
-      <c r="H203" s="6" t="inlineStr">
-        <is>
-          <t>Por revisar</t>
-        </is>
-      </c>
-      <c r="I203" s="6" t="inlineStr"/>
-      <c r="J203" s="6" t="inlineStr"/>
-    </row>
-    <row r="204" ht="28" customHeight="1">
-      <c r="A204" s="6" t="inlineStr">
-        <is>
-          <t>EUS-10725</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
-        <is>
-          <t>Suministro en régimen de alquiler de 2 contenedores y 1 case</t>
-        </is>
-      </c>
-      <c r="C204" s="6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="D204" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E204" s="6" t="inlineStr"/>
-      <c r="F204" s="25" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="G204" s="6" t="inlineStr"/>
-      <c r="H204" s="6" t="inlineStr">
-        <is>
-          <t>Por revisar</t>
-        </is>
-      </c>
-      <c r="I204" s="6" t="inlineStr"/>
-      <c r="J204" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J204"/>
+  <autoFilter ref="A1:J201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/resultados_convocatorias.xlsx
+++ b/docs/resultados_convocatorias.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Recursos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$216</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$213</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M216"/>
+  <dimension ref="A1:M218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -685,7 +685,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 24/10/2026 09:55 - 210 convocatorias - 12 nuevas</t>
+          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 25/10/2026 10:15 - 212 convocatorias - 13 nuevas</t>
         </is>
       </c>
     </row>
@@ -4120,19 +4120,15 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr"/>
       <c r="E77" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4153,7 +4149,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4171,15 +4167,19 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr"/>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr"/>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr"/>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr"/>
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -4833,12 +4833,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr"/>
@@ -8734,12 +8734,12 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>877682967</t>
+          <t>UCPM</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
+          <t>RIsk WATER flooding  EXercise</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr"/>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
+          <t>RIsk WATER flooding EXercise</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>UCPM</t>
+          <t>877682967</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>RIsk WATER flooding  EXercise</t>
+          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr"/>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>RIsk WATER flooding EXercise</t>
+          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
         </is>
       </c>
       <c r="L176" s="6" t="inlineStr"/>
@@ -10104,12 +10104,13 @@
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>EUS-93732</t>
+          <t>EUS-18844</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>Ayudas a proyectos al amparo de la estrategia de desarrollo local participativo (EDLP), aprobada al grupo de acción local del sector pesquero (GALP) para el desarrollo sostenible de las zonas de pesca</t>
+          <t>Contratación del servicio de mantenimiento integral e inspección de las instalaciones térmicas en edificios e instalaciones 
+municipales del Ayuntamiento de Amorebieta-Etxano</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
@@ -10126,12 +10127,12 @@
       <c r="G205" s="6" t="inlineStr"/>
       <c r="H205" s="6" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
-        </is>
-      </c>
-      <c r="I205" s="8" t="inlineStr">
-        <is>
-          <t>ALTA</t>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I205" s="11" t="inlineStr">
+        <is>
+          <t>MUY ALTA</t>
         </is>
       </c>
       <c r="J205" s="6" t="inlineStr"/>
@@ -10159,12 +10160,12 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>EUS-28838</t>
+          <t>EUS-01951</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocatorias transversales ligadas a multitud de líneas innovadoras, que atañen a inteligencia artificial y digitalización, energía y descarbonizació</t>
+          <t>Ayudas a proyectos al amparo de la estrategia de desarrollo local participativo (EDLP), aprobada al grupo de acción local del sector pesquero (GALP) para el desarrollo sostenible de las zonas de pesca</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
@@ -10214,12 +10215,12 @@
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>EUS-72505</t>
+          <t>EUS-56052</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>Asistencia técnica para la elaboración del Plan de Movilidad Sostenible de la Diputación Foral de Álava</t>
+          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocatorias transversales ligadas a multitud de líneas innovadoras, que atañen a inteligencia artificial y digitalización, energía y descarbonizació</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
@@ -10236,7 +10237,7 @@
       <c r="G207" s="6" t="inlineStr"/>
       <c r="H207" s="6" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="I207" s="8" t="inlineStr">
@@ -10269,12 +10270,12 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>EUS-51417</t>
+          <t>EUS-50335</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>Alquiler contenedor para residuos y su tratamiento</t>
+          <t>Asistencia técnica para la elaboración del Plan de Movilidad Sostenible de la Diputación Foral de Álava</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
@@ -10324,7 +10325,7 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>EUS-76515</t>
+          <t>EUS-95257</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
@@ -10379,7 +10380,7 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>EUS-69468</t>
+          <t>EUS-13959</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
@@ -10434,7 +10435,7 @@
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>EUS-08471</t>
+          <t>EUS-94998</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
@@ -10489,7 +10490,7 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>EUS-98139</t>
+          <t>EUS-92809</t>
         </is>
       </c>
       <c r="C212" s="6" t="inlineStr">
@@ -10544,7 +10545,7 @@
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>EUS-44103</t>
+          <t>EUS-29254</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
@@ -10599,7 +10600,7 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>EUS-99252</t>
+          <t>EUS-17441</t>
         </is>
       </c>
       <c r="C214" s="6" t="inlineStr">
@@ -10635,11 +10636,7 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L214" s="15" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
+      <c r="L214" s="6" t="inlineStr"/>
       <c r="M214" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -10654,12 +10651,12 @@
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>EUS-62644</t>
+          <t>EUS-52186</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>Redacción de proyecto de ejecución para la instalación de una cubierta en Urizar</t>
+          <t>Servicio de atención y gestión integral de la vivienda Comunitaria de Laguardia</t>
         </is>
       </c>
       <c r="D215" s="6" t="inlineStr">
@@ -10709,12 +10706,12 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>EUS-01533</t>
+          <t>EUS-87459</t>
         </is>
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>Estudio de detalle cubierta</t>
+          <t>Mejora del alumbrado público Fase 3</t>
         </is>
       </c>
       <c r="D216" s="6" t="inlineStr">
@@ -10756,8 +10753,118 @@
         </is>
       </c>
     </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>EUS-84294</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>Redacción de proyecto de ejecución para la instalación de una cubierta en Urizar</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="inlineStr"/>
+      <c r="G217" s="6" t="inlineStr"/>
+      <c r="H217" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I217" s="12" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="J217" s="6" t="inlineStr"/>
+      <c r="K217" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L217" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M217" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>EUS-19207</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>Estudio de detalle cubierta</t>
+        </is>
+      </c>
+      <c r="D218" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F218" s="6" t="inlineStr"/>
+      <c r="G218" s="6" t="inlineStr"/>
+      <c r="H218" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I218" s="12" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="J218" s="6" t="inlineStr"/>
+      <c r="K218" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L218" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M218" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:M216"/>
+  <autoFilter ref="A4:M218"/>
   <mergeCells count="4">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A204:M204"/>
@@ -10975,6 +11082,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M214" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M215" r:id="rId209"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId212"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10986,7 +11095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3149"/>
+  <dimension ref="A1:F3179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25544,7 +25653,7 @@
     <row r="1066" ht="30" customHeight="1">
       <c r="A1066" s="16" t="inlineStr">
         <is>
-          <t>FICHA 72: HORIZON</t>
+          <t>FICHA 72: ERASMUS2027</t>
         </is>
       </c>
       <c r="B1066" s="17" t="n"/>
@@ -25577,7 +25686,7 @@
       </c>
       <c r="B1068" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C1068" s="20" t="n"/>
@@ -25593,7 +25702,7 @@
       </c>
       <c r="B1069" s="19" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C1069" s="20" t="n"/>
@@ -25607,11 +25716,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1070" s="19" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+      <c r="B1070" s="19" t="inlineStr"/>
       <c r="C1070" s="20" t="n"/>
       <c r="D1070" s="20" t="n"/>
       <c r="E1070" s="20" t="n"/>
@@ -25685,7 +25790,7 @@
       </c>
       <c r="B1075" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2021-CIT-02</t>
+          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
         </is>
       </c>
       <c r="C1075" s="20" t="n"/>
@@ -25701,7 +25806,7 @@
       </c>
       <c r="B1076" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C1076" s="20" t="n"/>
@@ -25745,7 +25850,7 @@
       </c>
       <c r="B1079" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
         </is>
       </c>
       <c r="C1079" s="20" t="n"/>
@@ -25756,7 +25861,7 @@
     <row r="1081" ht="30" customHeight="1">
       <c r="A1081" s="16" t="inlineStr">
         <is>
-          <t>FICHA 73: ERASMUS2027</t>
+          <t>FICHA 73: HORIZON</t>
         </is>
       </c>
       <c r="B1081" s="17" t="n"/>
@@ -25789,7 +25894,7 @@
       </c>
       <c r="B1083" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C1083" s="20" t="n"/>
@@ -25805,7 +25910,7 @@
       </c>
       <c r="B1084" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C1084" s="20" t="n"/>
@@ -25819,7 +25924,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1085" s="19" t="inlineStr"/>
+      <c r="B1085" s="19" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="C1085" s="20" t="n"/>
       <c r="D1085" s="20" t="n"/>
       <c r="E1085" s="20" t="n"/>
@@ -25893,7 +26002,7 @@
       </c>
       <c r="B1090" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
+          <t>HORIZON-MISS-2021-CIT-02</t>
         </is>
       </c>
       <c r="C1090" s="20" t="n"/>
@@ -25909,7 +26018,7 @@
       </c>
       <c r="B1091" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C1091" s="20" t="n"/>
@@ -25953,7 +26062,7 @@
       </c>
       <c r="B1094" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
         </is>
       </c>
       <c r="C1094" s="20" t="n"/>
@@ -28016,7 +28125,7 @@
     <row r="1246" ht="30" customHeight="1">
       <c r="A1246" s="16" t="inlineStr">
         <is>
-          <t>FICHA 84: 928447529</t>
+          <t>FICHA 84: 917779760</t>
         </is>
       </c>
       <c r="B1246" s="17" t="n"/>
@@ -28049,7 +28158,7 @@
       </c>
       <c r="B1248" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1248" s="20" t="n"/>
@@ -28065,7 +28174,7 @@
       </c>
       <c r="B1249" s="19" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C1249" s="20" t="n"/>
@@ -28165,7 +28274,7 @@
       </c>
       <c r="B1256" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1256" s="20" t="n"/>
@@ -28209,7 +28318,7 @@
       </c>
       <c r="B1259" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
         </is>
       </c>
       <c r="C1259" s="20" t="n"/>
@@ -28220,7 +28329,7 @@
     <row r="1261" ht="30" customHeight="1">
       <c r="A1261" s="16" t="inlineStr">
         <is>
-          <t>FICHA 85: 917671508</t>
+          <t>FICHA 85: 920115617</t>
         </is>
       </c>
       <c r="B1261" s="17" t="n"/>
@@ -28253,7 +28362,7 @@
       </c>
       <c r="B1263" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1263" s="20" t="n"/>
@@ -28269,7 +28378,7 @@
       </c>
       <c r="B1264" s="19" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C1264" s="20" t="n"/>
@@ -28369,7 +28478,7 @@
       </c>
       <c r="B1271" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1271" s="20" t="n"/>
@@ -28413,7 +28522,7 @@
       </c>
       <c r="B1274" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
         </is>
       </c>
       <c r="C1274" s="20" t="n"/>
@@ -28424,7 +28533,7 @@
     <row r="1276" ht="30" customHeight="1">
       <c r="A1276" s="16" t="inlineStr">
         <is>
-          <t>FICHA 86: 917779760</t>
+          <t>FICHA 86: 917671508</t>
         </is>
       </c>
       <c r="B1276" s="17" t="n"/>
@@ -28457,7 +28566,7 @@
       </c>
       <c r="B1278" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1278" s="20" t="n"/>
@@ -28473,7 +28582,7 @@
       </c>
       <c r="B1279" s="19" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C1279" s="20" t="n"/>
@@ -28573,7 +28682,7 @@
       </c>
       <c r="B1286" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1286" s="20" t="n"/>
@@ -28617,7 +28726,7 @@
       </c>
       <c r="B1289" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
         </is>
       </c>
       <c r="C1289" s="20" t="n"/>
@@ -28628,7 +28737,7 @@
     <row r="1291" ht="30" customHeight="1">
       <c r="A1291" s="16" t="inlineStr">
         <is>
-          <t>FICHA 87: 920115617</t>
+          <t>FICHA 87: 928447529</t>
         </is>
       </c>
       <c r="B1291" s="17" t="n"/>
@@ -28661,7 +28770,7 @@
       </c>
       <c r="B1293" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1293" s="20" t="n"/>
@@ -28677,7 +28786,7 @@
       </c>
       <c r="B1294" s="19" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C1294" s="20" t="n"/>
@@ -28777,7 +28886,7 @@
       </c>
       <c r="B1301" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1301" s="20" t="n"/>
@@ -28821,7 +28930,7 @@
       </c>
       <c r="B1304" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
         </is>
       </c>
       <c r="C1304" s="20" t="n"/>
@@ -45588,7 +45697,7 @@
     <row r="2536" ht="30" customHeight="1">
       <c r="A2536" s="16" t="inlineStr">
         <is>
-          <t>FICHA 170: 877682967</t>
+          <t>FICHA 170: UCPM</t>
         </is>
       </c>
       <c r="B2536" s="17" t="n"/>
@@ -45621,7 +45730,7 @@
       </c>
       <c r="B2538" s="19" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
+          <t>RIsk WATER flooding  EXercise</t>
         </is>
       </c>
       <c r="C2538" s="20" t="n"/>
@@ -45637,7 +45746,7 @@
       </c>
       <c r="B2539" s="19" t="inlineStr">
         <is>
-          <t>877682967</t>
+          <t>UCPM</t>
         </is>
       </c>
       <c r="C2539" s="20" t="n"/>
@@ -45723,7 +45832,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2545" s="19" t="inlineStr"/>
+      <c r="B2545" s="19" t="inlineStr">
+        <is>
+          <t>UCPM-2017-EX-AG</t>
+        </is>
+      </c>
       <c r="C2545" s="20" t="n"/>
       <c r="D2545" s="20" t="n"/>
       <c r="E2545" s="20" t="n"/>
@@ -45737,7 +45850,7 @@
       </c>
       <c r="B2546" s="19" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
+          <t>RIsk WATER flooding EXercise</t>
         </is>
       </c>
       <c r="C2546" s="20" t="n"/>
@@ -45781,7 +45894,7 @@
       </c>
       <c r="B2549" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/877682967</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/UCPM</t>
         </is>
       </c>
       <c r="C2549" s="20" t="n"/>
@@ -45792,7 +45905,7 @@
     <row r="2551" ht="30" customHeight="1">
       <c r="A2551" s="16" t="inlineStr">
         <is>
-          <t>FICHA 171: UCPM</t>
+          <t>FICHA 171: 877682967</t>
         </is>
       </c>
       <c r="B2551" s="17" t="n"/>
@@ -45825,7 +45938,7 @@
       </c>
       <c r="B2553" s="19" t="inlineStr">
         <is>
-          <t>RIsk WATER flooding  EXercise</t>
+          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
         </is>
       </c>
       <c r="C2553" s="20" t="n"/>
@@ -45841,7 +45954,7 @@
       </c>
       <c r="B2554" s="19" t="inlineStr">
         <is>
-          <t>UCPM</t>
+          <t>877682967</t>
         </is>
       </c>
       <c r="C2554" s="20" t="n"/>
@@ -45927,11 +46040,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2560" s="19" t="inlineStr">
-        <is>
-          <t>UCPM-2017-EX-AG</t>
-        </is>
-      </c>
+      <c r="B2560" s="19" t="inlineStr"/>
       <c r="C2560" s="20" t="n"/>
       <c r="D2560" s="20" t="n"/>
       <c r="E2560" s="20" t="n"/>
@@ -45945,7 +46054,7 @@
       </c>
       <c r="B2561" s="19" t="inlineStr">
         <is>
-          <t>RIsk WATER flooding EXercise</t>
+          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
         </is>
       </c>
       <c r="C2561" s="20" t="n"/>
@@ -45989,7 +46098,7 @@
       </c>
       <c r="B2564" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/UCPM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/877682967</t>
         </is>
       </c>
       <c r="C2564" s="20" t="n"/>
@@ -51520,7 +51629,7 @@
     <row r="2971" ht="30" customHeight="1">
       <c r="A2971" s="16" t="inlineStr">
         <is>
-          <t>FICHA 199: EUS-93732</t>
+          <t>FICHA 199: EUS-18844</t>
         </is>
       </c>
       <c r="B2971" s="17" t="n"/>
@@ -51553,7 +51662,8 @@
       </c>
       <c r="B2973" s="19" t="inlineStr">
         <is>
-          <t>Ayudas a proyectos al amparo de la estrategia de desarrollo local participativo (EDLP), aprobada al grupo de acción local del sector pesquero (GALP) para el desarrollo sostenible de las zonas de pesca</t>
+          <t>Contratación del servicio de mantenimiento integral e inspección de las instalaciones térmicas en edificios e instalaciones 
+municipales del Ayuntamiento de Amorebieta-Etxano</t>
         </is>
       </c>
       <c r="C2973" s="20" t="n"/>
@@ -51569,7 +51679,7 @@
       </c>
       <c r="B2974" s="19" t="inlineStr">
         <is>
-          <t>EUS-93732</t>
+          <t>EUS-18844</t>
         </is>
       </c>
       <c r="C2974" s="20" t="n"/>
@@ -51645,7 +51755,7 @@
       </c>
       <c r="B2979" s="19" t="inlineStr">
         <is>
-          <t>Ayuda/Subvencion Euskadi</t>
+          <t>Licitacion Euskadi</t>
         </is>
       </c>
       <c r="C2979" s="20" t="n"/>
@@ -51703,9 +51813,9 @@
           <t>Relevancia Bilbao</t>
         </is>
       </c>
-      <c r="B2983" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALTA — </t>
+      <c r="B2983" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUY ALTA — </t>
         </is>
       </c>
       <c r="C2983" s="20" t="n"/>
@@ -51721,7 +51831,7 @@
       </c>
       <c r="B2984" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/ayudas-al-amparo-de-la-estrategia-de-desarrollo-local-participativo-2026/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/contratacion-del-servicio-mantenimiento-integral-e-inspeccion-instalaciones-termicas-edificios-e-instalaciones-municipales-del-ayuntamiento-amorebieta-etxano/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2984" s="20" t="n"/>
@@ -51732,7 +51842,7 @@
     <row r="2986" ht="30" customHeight="1">
       <c r="A2986" s="16" t="inlineStr">
         <is>
-          <t>FICHA 200: EUS-28838</t>
+          <t>FICHA 200: EUS-01951</t>
         </is>
       </c>
       <c r="B2986" s="17" t="n"/>
@@ -51765,7 +51875,7 @@
       </c>
       <c r="B2988" s="19" t="inlineStr">
         <is>
-          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocatorias transversales ligadas a multitud de líneas innovadoras, que atañen a inteligencia artificial y digitalización, energía y descarbonizació</t>
+          <t>Ayudas a proyectos al amparo de la estrategia de desarrollo local participativo (EDLP), aprobada al grupo de acción local del sector pesquero (GALP) para el desarrollo sostenible de las zonas de pesca</t>
         </is>
       </c>
       <c r="C2988" s="20" t="n"/>
@@ -51781,7 +51891,7 @@
       </c>
       <c r="B2989" s="19" t="inlineStr">
         <is>
-          <t>EUS-28838</t>
+          <t>EUS-01951</t>
         </is>
       </c>
       <c r="C2989" s="20" t="n"/>
@@ -51933,7 +52043,7 @@
       </c>
       <c r="B2999" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/ayuda_subvencion/2026/horizonzeharkakodeialdiak/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/ayudas-al-amparo-de-la-estrategia-de-desarrollo-local-participativo-2026/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2999" s="20" t="n"/>
@@ -51944,7 +52054,7 @@
     <row r="3001" ht="30" customHeight="1">
       <c r="A3001" s="16" t="inlineStr">
         <is>
-          <t>FICHA 201: EUS-72505</t>
+          <t>FICHA 201: EUS-56052</t>
         </is>
       </c>
       <c r="B3001" s="17" t="n"/>
@@ -51977,7 +52087,7 @@
       </c>
       <c r="B3003" s="19" t="inlineStr">
         <is>
-          <t>Asistencia técnica para la elaboración del Plan de Movilidad Sostenible de la Diputación Foral de Álava</t>
+          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocatorias transversales ligadas a multitud de líneas innovadoras, que atañen a inteligencia artificial y digitalización, energía y descarbonizació</t>
         </is>
       </c>
       <c r="C3003" s="20" t="n"/>
@@ -51993,7 +52103,7 @@
       </c>
       <c r="B3004" s="19" t="inlineStr">
         <is>
-          <t>EUS-72505</t>
+          <t>EUS-56052</t>
         </is>
       </c>
       <c r="C3004" s="20" t="n"/>
@@ -52069,7 +52179,7 @@
       </c>
       <c r="B3009" s="19" t="inlineStr">
         <is>
-          <t>Licitacion Euskadi</t>
+          <t>Ayuda/Subvencion Euskadi</t>
         </is>
       </c>
       <c r="C3009" s="20" t="n"/>
@@ -52145,7 +52255,7 @@
       </c>
       <c r="B3014" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/asistencia-tecnica-elaboracion-del-plan-movilidad-sostenible-diputacion-foral-alava/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/ayuda_subvencion/2026/horizonzeharkakodeialdiak/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3014" s="20" t="n"/>
@@ -52156,7 +52266,7 @@
     <row r="3016" ht="30" customHeight="1">
       <c r="A3016" s="16" t="inlineStr">
         <is>
-          <t>FICHA 202: EUS-51417</t>
+          <t>FICHA 202: EUS-50335</t>
         </is>
       </c>
       <c r="B3016" s="17" t="n"/>
@@ -52181,7 +52291,7 @@
       <c r="E3017" s="20" t="n"/>
       <c r="F3017" s="20" t="n"/>
     </row>
-    <row r="3018" ht="20" customHeight="1">
+    <row r="3018" ht="45" customHeight="1">
       <c r="A3018" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -52189,7 +52299,7 @@
       </c>
       <c r="B3018" s="19" t="inlineStr">
         <is>
-          <t>Alquiler contenedor para residuos y su tratamiento</t>
+          <t>Asistencia técnica para la elaboración del Plan de Movilidad Sostenible de la Diputación Foral de Álava</t>
         </is>
       </c>
       <c r="C3018" s="20" t="n"/>
@@ -52205,7 +52315,7 @@
       </c>
       <c r="B3019" s="19" t="inlineStr">
         <is>
-          <t>EUS-51417</t>
+          <t>EUS-50335</t>
         </is>
       </c>
       <c r="C3019" s="20" t="n"/>
@@ -52357,7 +52467,7 @@
       </c>
       <c r="B3029" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/alquiler-contenedor-residuos-y-su-tratamiento/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/asistencia-tecnica-elaboracion-del-plan-movilidad-sostenible-diputacion-foral-alava/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3029" s="20" t="n"/>
@@ -52368,7 +52478,7 @@
     <row r="3031" ht="30" customHeight="1">
       <c r="A3031" s="16" t="inlineStr">
         <is>
-          <t>FICHA 203: EUS-76515</t>
+          <t>FICHA 203: EUS-95257</t>
         </is>
       </c>
       <c r="B3031" s="17" t="n"/>
@@ -52417,7 +52527,7 @@
       </c>
       <c r="B3034" s="19" t="inlineStr">
         <is>
-          <t>EUS-76515</t>
+          <t>EUS-95257</t>
         </is>
       </c>
       <c r="C3034" s="20" t="n"/>
@@ -52580,7 +52690,7 @@
     <row r="3046" ht="30" customHeight="1">
       <c r="A3046" s="16" t="inlineStr">
         <is>
-          <t>FICHA 204: EUS-69468</t>
+          <t>FICHA 204: EUS-13959</t>
         </is>
       </c>
       <c r="B3046" s="17" t="n"/>
@@ -52629,7 +52739,7 @@
       </c>
       <c r="B3049" s="19" t="inlineStr">
         <is>
-          <t>EUS-69468</t>
+          <t>EUS-13959</t>
         </is>
       </c>
       <c r="C3049" s="20" t="n"/>
@@ -52792,7 +52902,7 @@
     <row r="3061" ht="30" customHeight="1">
       <c r="A3061" s="16" t="inlineStr">
         <is>
-          <t>FICHA 205: EUS-08471</t>
+          <t>FICHA 205: EUS-94998</t>
         </is>
       </c>
       <c r="B3061" s="17" t="n"/>
@@ -52841,7 +52951,7 @@
       </c>
       <c r="B3064" s="19" t="inlineStr">
         <is>
-          <t>EUS-08471</t>
+          <t>EUS-94998</t>
         </is>
       </c>
       <c r="C3064" s="20" t="n"/>
@@ -53004,7 +53114,7 @@
     <row r="3076" ht="30" customHeight="1">
       <c r="A3076" s="16" t="inlineStr">
         <is>
-          <t>FICHA 206: EUS-98139</t>
+          <t>FICHA 206: EUS-92809</t>
         </is>
       </c>
       <c r="B3076" s="17" t="n"/>
@@ -53053,7 +53163,7 @@
       </c>
       <c r="B3079" s="19" t="inlineStr">
         <is>
-          <t>EUS-98139</t>
+          <t>EUS-92809</t>
         </is>
       </c>
       <c r="C3079" s="20" t="n"/>
@@ -53216,7 +53326,7 @@
     <row r="3091" ht="30" customHeight="1">
       <c r="A3091" s="16" t="inlineStr">
         <is>
-          <t>FICHA 207: EUS-44103</t>
+          <t>FICHA 207: EUS-29254</t>
         </is>
       </c>
       <c r="B3091" s="17" t="n"/>
@@ -53265,7 +53375,7 @@
       </c>
       <c r="B3094" s="19" t="inlineStr">
         <is>
-          <t>EUS-44103</t>
+          <t>EUS-29254</t>
         </is>
       </c>
       <c r="C3094" s="20" t="n"/>
@@ -53428,7 +53538,7 @@
     <row r="3106" ht="30" customHeight="1">
       <c r="A3106" s="16" t="inlineStr">
         <is>
-          <t>FICHA 208: EUS-99252</t>
+          <t>FICHA 208: EUS-17441</t>
         </is>
       </c>
       <c r="B3106" s="17" t="n"/>
@@ -53477,7 +53587,7 @@
       </c>
       <c r="B3109" s="19" t="inlineStr">
         <is>
-          <t>EUS-99252</t>
+          <t>EUS-17441</t>
         </is>
       </c>
       <c r="C3109" s="20" t="n"/>
@@ -53640,7 +53750,7 @@
     <row r="3121" ht="30" customHeight="1">
       <c r="A3121" s="16" t="inlineStr">
         <is>
-          <t>FICHA 209: EUS-62644</t>
+          <t>FICHA 209: EUS-52186</t>
         </is>
       </c>
       <c r="B3121" s="17" t="n"/>
@@ -53665,7 +53775,7 @@
       <c r="E3122" s="20" t="n"/>
       <c r="F3122" s="20" t="n"/>
     </row>
-    <row r="3123" ht="45" customHeight="1">
+    <row r="3123" ht="20" customHeight="1">
       <c r="A3123" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -53673,7 +53783,7 @@
       </c>
       <c r="B3123" s="19" t="inlineStr">
         <is>
-          <t>Redacción de proyecto de ejecución para la instalación de una cubierta en Urizar</t>
+          <t>Servicio de atención y gestión integral de la vivienda Comunitaria de Laguardia</t>
         </is>
       </c>
       <c r="C3123" s="20" t="n"/>
@@ -53689,7 +53799,7 @@
       </c>
       <c r="B3124" s="19" t="inlineStr">
         <is>
-          <t>EUS-62644</t>
+          <t>EUS-52186</t>
         </is>
       </c>
       <c r="C3124" s="20" t="n"/>
@@ -53841,7 +53951,7 @@
       </c>
       <c r="B3134" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/redaccion-proyecto-ejecucion-instalacion-cubierta-urizar/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-atencion-y-gestion-integral-vivienda-comunitaria-laguardia/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3134" s="20" t="n"/>
@@ -53852,7 +53962,7 @@
     <row r="3136" ht="30" customHeight="1">
       <c r="A3136" s="16" t="inlineStr">
         <is>
-          <t>FICHA 210: EUS-01533</t>
+          <t>FICHA 210: EUS-87459</t>
         </is>
       </c>
       <c r="B3136" s="17" t="n"/>
@@ -53885,7 +53995,7 @@
       </c>
       <c r="B3138" s="19" t="inlineStr">
         <is>
-          <t>Estudio de detalle cubierta</t>
+          <t>Mejora del alumbrado público Fase 3</t>
         </is>
       </c>
       <c r="C3138" s="20" t="n"/>
@@ -53901,7 +54011,7 @@
       </c>
       <c r="B3139" s="19" t="inlineStr">
         <is>
-          <t>EUS-01533</t>
+          <t>EUS-87459</t>
         </is>
       </c>
       <c r="C3139" s="20" t="n"/>
@@ -54053,7 +54163,7 @@
       </c>
       <c r="B3149" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/estudio-detalle-cubierta/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/mejora-del-alumbrado-publico-fase-3/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3149" s="20" t="n"/>
@@ -54061,8 +54171,432 @@
       <c r="E3149" s="20" t="n"/>
       <c r="F3149" s="20" t="n"/>
     </row>
+    <row r="3151" ht="30" customHeight="1">
+      <c r="A3151" s="16" t="inlineStr">
+        <is>
+          <t>FICHA 211: EUS-84294</t>
+        </is>
+      </c>
+      <c r="B3151" s="17" t="n"/>
+      <c r="C3151" s="17" t="n"/>
+      <c r="D3151" s="17" t="n"/>
+      <c r="E3151" s="17" t="n"/>
+      <c r="F3151" s="17" t="n"/>
+    </row>
+    <row r="3152" ht="20" customHeight="1">
+      <c r="A3152" s="18" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B3152" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+      <c r="C3152" s="20" t="n"/>
+      <c r="D3152" s="20" t="n"/>
+      <c r="E3152" s="20" t="n"/>
+      <c r="F3152" s="20" t="n"/>
+    </row>
+    <row r="3153" ht="45" customHeight="1">
+      <c r="A3153" s="18" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B3153" s="19" t="inlineStr">
+        <is>
+          <t>Redacción de proyecto de ejecución para la instalación de una cubierta en Urizar</t>
+        </is>
+      </c>
+      <c r="C3153" s="20" t="n"/>
+      <c r="D3153" s="20" t="n"/>
+      <c r="E3153" s="20" t="n"/>
+      <c r="F3153" s="20" t="n"/>
+    </row>
+    <row r="3154" ht="20" customHeight="1">
+      <c r="A3154" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3154" s="19" t="inlineStr">
+        <is>
+          <t>EUS-84294</t>
+        </is>
+      </c>
+      <c r="C3154" s="20" t="n"/>
+      <c r="D3154" s="20" t="n"/>
+      <c r="E3154" s="20" t="n"/>
+      <c r="F3154" s="20" t="n"/>
+    </row>
+    <row r="3155" ht="20" customHeight="1">
+      <c r="A3155" s="18" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B3155" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="C3155" s="20" t="n"/>
+      <c r="D3155" s="20" t="n"/>
+      <c r="E3155" s="20" t="n"/>
+      <c r="F3155" s="20" t="n"/>
+    </row>
+    <row r="3156" ht="20" customHeight="1">
+      <c r="A3156" s="18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B3156" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C3156" s="20" t="n"/>
+      <c r="D3156" s="20" t="n"/>
+      <c r="E3156" s="20" t="n"/>
+      <c r="F3156" s="20" t="n"/>
+    </row>
+    <row r="3157" ht="20" customHeight="1">
+      <c r="A3157" s="18" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B3157" s="19" t="inlineStr"/>
+      <c r="C3157" s="20" t="n"/>
+      <c r="D3157" s="20" t="n"/>
+      <c r="E3157" s="20" t="n"/>
+      <c r="F3157" s="20" t="n"/>
+    </row>
+    <row r="3158" ht="20" customHeight="1">
+      <c r="A3158" s="18" t="inlineStr">
+        <is>
+          <t>Presupuesto (EUR)</t>
+        </is>
+      </c>
+      <c r="B3158" s="19" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="C3158" s="20" t="n"/>
+      <c r="D3158" s="20" t="n"/>
+      <c r="E3158" s="20" t="n"/>
+      <c r="F3158" s="20" t="n"/>
+    </row>
+    <row r="3159" ht="20" customHeight="1">
+      <c r="A3159" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de Accion</t>
+        </is>
+      </c>
+      <c r="B3159" s="19" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="C3159" s="20" t="n"/>
+      <c r="D3159" s="20" t="n"/>
+      <c r="E3159" s="20" t="n"/>
+      <c r="F3159" s="20" t="n"/>
+    </row>
+    <row r="3160" ht="20" customHeight="1">
+      <c r="A3160" s="18" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B3160" s="19" t="inlineStr"/>
+      <c r="C3160" s="20" t="n"/>
+      <c r="D3160" s="20" t="n"/>
+      <c r="E3160" s="20" t="n"/>
+      <c r="F3160" s="20" t="n"/>
+    </row>
+    <row r="3161" ht="20" customHeight="1">
+      <c r="A3161" s="18" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="B3161" s="19" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="C3161" s="20" t="n"/>
+      <c r="D3161" s="20" t="n"/>
+      <c r="E3161" s="20" t="n"/>
+      <c r="F3161" s="20" t="n"/>
+    </row>
+    <row r="3162" ht="20" customHeight="1">
+      <c r="A3162" s="18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B3162" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="C3162" s="20" t="n"/>
+      <c r="D3162" s="20" t="n"/>
+      <c r="E3162" s="20" t="n"/>
+      <c r="F3162" s="20" t="n"/>
+    </row>
+    <row r="3163" ht="20" customHeight="1">
+      <c r="A3163" s="18" t="inlineStr">
+        <is>
+          <t>Relevancia Bilbao</t>
+        </is>
+      </c>
+      <c r="B3163" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
+        </is>
+      </c>
+      <c r="C3163" s="20" t="n"/>
+      <c r="D3163" s="20" t="n"/>
+      <c r="E3163" s="20" t="n"/>
+      <c r="F3163" s="20" t="n"/>
+    </row>
+    <row r="3164" ht="45" customHeight="1">
+      <c r="A3164" s="18" t="inlineStr">
+        <is>
+          <t>Enlace al portal</t>
+        </is>
+      </c>
+      <c r="B3164" s="22" t="inlineStr">
+        <is>
+          <t>https://www.euskadi.eus/anuncio_contratacion/redaccion-proyecto-ejecucion-instalacion-cubierta-urizar/web01-tramite/es/</t>
+        </is>
+      </c>
+      <c r="C3164" s="20" t="n"/>
+      <c r="D3164" s="20" t="n"/>
+      <c r="E3164" s="20" t="n"/>
+      <c r="F3164" s="20" t="n"/>
+    </row>
+    <row r="3166" ht="30" customHeight="1">
+      <c r="A3166" s="16" t="inlineStr">
+        <is>
+          <t>FICHA 212: EUS-19207</t>
+        </is>
+      </c>
+      <c r="B3166" s="17" t="n"/>
+      <c r="C3166" s="17" t="n"/>
+      <c r="D3166" s="17" t="n"/>
+      <c r="E3166" s="17" t="n"/>
+      <c r="F3166" s="17" t="n"/>
+    </row>
+    <row r="3167" ht="20" customHeight="1">
+      <c r="A3167" s="18" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B3167" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+      <c r="C3167" s="20" t="n"/>
+      <c r="D3167" s="20" t="n"/>
+      <c r="E3167" s="20" t="n"/>
+      <c r="F3167" s="20" t="n"/>
+    </row>
+    <row r="3168" ht="20" customHeight="1">
+      <c r="A3168" s="18" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B3168" s="19" t="inlineStr">
+        <is>
+          <t>Estudio de detalle cubierta</t>
+        </is>
+      </c>
+      <c r="C3168" s="20" t="n"/>
+      <c r="D3168" s="20" t="n"/>
+      <c r="E3168" s="20" t="n"/>
+      <c r="F3168" s="20" t="n"/>
+    </row>
+    <row r="3169" ht="20" customHeight="1">
+      <c r="A3169" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3169" s="19" t="inlineStr">
+        <is>
+          <t>EUS-19207</t>
+        </is>
+      </c>
+      <c r="C3169" s="20" t="n"/>
+      <c r="D3169" s="20" t="n"/>
+      <c r="E3169" s="20" t="n"/>
+      <c r="F3169" s="20" t="n"/>
+    </row>
+    <row r="3170" ht="20" customHeight="1">
+      <c r="A3170" s="18" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B3170" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="C3170" s="20" t="n"/>
+      <c r="D3170" s="20" t="n"/>
+      <c r="E3170" s="20" t="n"/>
+      <c r="F3170" s="20" t="n"/>
+    </row>
+    <row r="3171" ht="20" customHeight="1">
+      <c r="A3171" s="18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B3171" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C3171" s="20" t="n"/>
+      <c r="D3171" s="20" t="n"/>
+      <c r="E3171" s="20" t="n"/>
+      <c r="F3171" s="20" t="n"/>
+    </row>
+    <row r="3172" ht="20" customHeight="1">
+      <c r="A3172" s="18" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B3172" s="19" t="inlineStr"/>
+      <c r="C3172" s="20" t="n"/>
+      <c r="D3172" s="20" t="n"/>
+      <c r="E3172" s="20" t="n"/>
+      <c r="F3172" s="20" t="n"/>
+    </row>
+    <row r="3173" ht="20" customHeight="1">
+      <c r="A3173" s="18" t="inlineStr">
+        <is>
+          <t>Presupuesto (EUR)</t>
+        </is>
+      </c>
+      <c r="B3173" s="19" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="C3173" s="20" t="n"/>
+      <c r="D3173" s="20" t="n"/>
+      <c r="E3173" s="20" t="n"/>
+      <c r="F3173" s="20" t="n"/>
+    </row>
+    <row r="3174" ht="20" customHeight="1">
+      <c r="A3174" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de Accion</t>
+        </is>
+      </c>
+      <c r="B3174" s="19" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="C3174" s="20" t="n"/>
+      <c r="D3174" s="20" t="n"/>
+      <c r="E3174" s="20" t="n"/>
+      <c r="F3174" s="20" t="n"/>
+    </row>
+    <row r="3175" ht="20" customHeight="1">
+      <c r="A3175" s="18" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B3175" s="19" t="inlineStr"/>
+      <c r="C3175" s="20" t="n"/>
+      <c r="D3175" s="20" t="n"/>
+      <c r="E3175" s="20" t="n"/>
+      <c r="F3175" s="20" t="n"/>
+    </row>
+    <row r="3176" ht="20" customHeight="1">
+      <c r="A3176" s="18" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="B3176" s="19" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="C3176" s="20" t="n"/>
+      <c r="D3176" s="20" t="n"/>
+      <c r="E3176" s="20" t="n"/>
+      <c r="F3176" s="20" t="n"/>
+    </row>
+    <row r="3177" ht="20" customHeight="1">
+      <c r="A3177" s="18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B3177" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="C3177" s="20" t="n"/>
+      <c r="D3177" s="20" t="n"/>
+      <c r="E3177" s="20" t="n"/>
+      <c r="F3177" s="20" t="n"/>
+    </row>
+    <row r="3178" ht="20" customHeight="1">
+      <c r="A3178" s="18" t="inlineStr">
+        <is>
+          <t>Relevancia Bilbao</t>
+        </is>
+      </c>
+      <c r="B3178" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
+        </is>
+      </c>
+      <c r="C3178" s="20" t="n"/>
+      <c r="D3178" s="20" t="n"/>
+      <c r="E3178" s="20" t="n"/>
+      <c r="F3178" s="20" t="n"/>
+    </row>
+    <row r="3179" ht="45" customHeight="1">
+      <c r="A3179" s="18" t="inlineStr">
+        <is>
+          <t>Enlace al portal</t>
+        </is>
+      </c>
+      <c r="B3179" s="22" t="inlineStr">
+        <is>
+          <t>https://www.euskadi.eus/anuncio_contratacion/estudio-detalle-cubierta/web01-tramite/es/</t>
+        </is>
+      </c>
+      <c r="C3179" s="20" t="n"/>
+      <c r="D3179" s="20" t="n"/>
+      <c r="E3179" s="20" t="n"/>
+      <c r="F3179" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2940">
+  <mergeCells count="2968">
     <mergeCell ref="B679:F679"/>
     <mergeCell ref="B2192:F2192"/>
     <mergeCell ref="B1765:F1765"/>
@@ -54103,6 +54637,7 @@
     <mergeCell ref="B1664:F1664"/>
     <mergeCell ref="B2879:F2879"/>
     <mergeCell ref="B2539:F2539"/>
+    <mergeCell ref="B3152:F3152"/>
     <mergeCell ref="B725:F725"/>
     <mergeCell ref="B1067:F1067"/>
     <mergeCell ref="B1778:F1778"/>
@@ -54114,6 +54649,8 @@
     <mergeCell ref="B1794:F1794"/>
     <mergeCell ref="B1788:F1788"/>
     <mergeCell ref="B718:F718"/>
+    <mergeCell ref="B3179:F3179"/>
+    <mergeCell ref="B3154:F3154"/>
     <mergeCell ref="B2839:F2839"/>
     <mergeCell ref="B1025:F1025"/>
     <mergeCell ref="B1367:F1367"/>
@@ -54229,6 +54766,7 @@
     <mergeCell ref="B2863:F2863"/>
     <mergeCell ref="B778:F778"/>
     <mergeCell ref="B2108:F2108"/>
+    <mergeCell ref="B3161:F3161"/>
     <mergeCell ref="B1076:F1076"/>
     <mergeCell ref="B1586:F1586"/>
     <mergeCell ref="B2406:F2406"/>
@@ -54635,6 +55173,7 @@
     <mergeCell ref="B279:F279"/>
     <mergeCell ref="B2862:F2862"/>
     <mergeCell ref="B410:F410"/>
+    <mergeCell ref="B3160:F3160"/>
     <mergeCell ref="B733:F733"/>
     <mergeCell ref="B708:F708"/>
     <mergeCell ref="B1463:F1463"/>
@@ -54642,6 +55181,7 @@
     <mergeCell ref="B1978:F1978"/>
     <mergeCell ref="B281:F281"/>
     <mergeCell ref="B1972:F1972"/>
+    <mergeCell ref="B3162:F3162"/>
     <mergeCell ref="B2407:F2407"/>
     <mergeCell ref="B2092:F2092"/>
     <mergeCell ref="B1033:F1033"/>
@@ -54651,6 +55191,7 @@
     <mergeCell ref="B1362:F1362"/>
     <mergeCell ref="B759:F759"/>
     <mergeCell ref="B1057:F1057"/>
+    <mergeCell ref="B3178:F3178"/>
     <mergeCell ref="B1093:F1093"/>
     <mergeCell ref="B1364:F1364"/>
     <mergeCell ref="B2119:F2119"/>
@@ -54673,6 +55214,7 @@
     <mergeCell ref="B2875:F2875"/>
     <mergeCell ref="B790:F790"/>
     <mergeCell ref="B2120:F2120"/>
+    <mergeCell ref="B3173:F3173"/>
     <mergeCell ref="B1088:F1088"/>
     <mergeCell ref="B1359:F1359"/>
     <mergeCell ref="B2418:F2418"/>
@@ -54728,6 +55270,7 @@
     <mergeCell ref="B2518:F2518"/>
     <mergeCell ref="B1459:F1459"/>
     <mergeCell ref="B704:F704"/>
+    <mergeCell ref="B3156:F3156"/>
     <mergeCell ref="B1757:F1757"/>
     <mergeCell ref="B1002:F1002"/>
     <mergeCell ref="B2649:F2649"/>
@@ -54737,6 +55280,7 @@
     <mergeCell ref="B2213:F2213"/>
     <mergeCell ref="B399:F399"/>
     <mergeCell ref="B2642:F2642"/>
+    <mergeCell ref="B3158:F3158"/>
     <mergeCell ref="B2818:F2818"/>
     <mergeCell ref="B1759:F1759"/>
     <mergeCell ref="B1004:F1004"/>
@@ -54770,8 +55314,10 @@
     <mergeCell ref="B717:F717"/>
     <mergeCell ref="B2414:F2414"/>
     <mergeCell ref="B2846:F2846"/>
+    <mergeCell ref="B3169:F3169"/>
     <mergeCell ref="B298:F298"/>
     <mergeCell ref="B2118:F2118"/>
+    <mergeCell ref="B3171:F3171"/>
     <mergeCell ref="B1959:F1959"/>
     <mergeCell ref="B443:F443"/>
     <mergeCell ref="A196:F196"/>
@@ -54848,6 +55394,7 @@
     <mergeCell ref="B1272:F1272"/>
     <mergeCell ref="B1570:F1570"/>
     <mergeCell ref="B809:F809"/>
+    <mergeCell ref="A3151:F3151"/>
     <mergeCell ref="A2836:F2836"/>
     <mergeCell ref="B2542:F2542"/>
     <mergeCell ref="B1143:F1143"/>
@@ -55042,6 +55589,7 @@
     <mergeCell ref="B934:F934"/>
     <mergeCell ref="B1232:F1232"/>
     <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B3177:F3177"/>
     <mergeCell ref="B1539:F1539"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="B507:F507"/>
@@ -55145,6 +55693,7 @@
     <mergeCell ref="B714:F714"/>
     <mergeCell ref="B2537:F2537"/>
     <mergeCell ref="B890:F890"/>
+    <mergeCell ref="B3175:F3175"/>
     <mergeCell ref="B1776:F1776"/>
     <mergeCell ref="B2080:F2080"/>
     <mergeCell ref="B2074:F2074"/>
@@ -55265,6 +55814,7 @@
     <mergeCell ref="B100:F100"/>
     <mergeCell ref="B1491:F1491"/>
     <mergeCell ref="B2859:F2859"/>
+    <mergeCell ref="B3157:F3157"/>
     <mergeCell ref="B2098:F2098"/>
     <mergeCell ref="B1370:F1370"/>
     <mergeCell ref="B311:F311"/>
@@ -55280,6 +55830,7 @@
     <mergeCell ref="B698:F698"/>
     <mergeCell ref="B1791:F1791"/>
     <mergeCell ref="B1074:F1074"/>
+    <mergeCell ref="B3159:F3159"/>
     <mergeCell ref="B1372:F1372"/>
     <mergeCell ref="B1670:F1670"/>
     <mergeCell ref="B611:F611"/>
@@ -55701,6 +56252,7 @@
     <mergeCell ref="B2718:F2718"/>
     <mergeCell ref="B170:F170"/>
     <mergeCell ref="B2832:F2832"/>
+    <mergeCell ref="B3174:F3174"/>
     <mergeCell ref="B2413:F2413"/>
     <mergeCell ref="B328:F328"/>
     <mergeCell ref="B1658:F1658"/>
@@ -55710,6 +56262,7 @@
     <mergeCell ref="B933:F933"/>
     <mergeCell ref="B1992:F1992"/>
     <mergeCell ref="B172:F172"/>
+    <mergeCell ref="B3176:F3176"/>
     <mergeCell ref="B2421:F2421"/>
     <mergeCell ref="B1389:F1389"/>
     <mergeCell ref="B2719:F2719"/>
@@ -55800,12 +56353,14 @@
     <mergeCell ref="B1029:F1029"/>
     <mergeCell ref="B1900:F1900"/>
     <mergeCell ref="B3116:F3116"/>
+    <mergeCell ref="B3170:F3170"/>
     <mergeCell ref="B712:F712"/>
     <mergeCell ref="B1929:F1929"/>
     <mergeCell ref="B2200:F2200"/>
     <mergeCell ref="B413:F413"/>
     <mergeCell ref="A166:F166"/>
     <mergeCell ref="B589:F589"/>
+    <mergeCell ref="B3172:F3172"/>
     <mergeCell ref="B1597:F1597"/>
     <mergeCell ref="B2417:F2417"/>
     <mergeCell ref="B1773:F1773"/>
@@ -55837,6 +56392,7 @@
     <mergeCell ref="B2711:F2711"/>
     <mergeCell ref="B584:F584"/>
     <mergeCell ref="B2114:F2114"/>
+    <mergeCell ref="B3167:F3167"/>
     <mergeCell ref="B2412:F2412"/>
     <mergeCell ref="B715:F715"/>
     <mergeCell ref="B1013:F1013"/>
@@ -56367,6 +56923,7 @@
     <mergeCell ref="B2079:F2079"/>
     <mergeCell ref="B1324:F1324"/>
     <mergeCell ref="B2394:F2394"/>
+    <mergeCell ref="B3155:F3155"/>
     <mergeCell ref="B1360:F1360"/>
     <mergeCell ref="B599:F599"/>
     <mergeCell ref="B1789:F1789"/>
@@ -56508,6 +57065,7 @@
     <mergeCell ref="A3046:F3046"/>
     <mergeCell ref="B1160:F1160"/>
     <mergeCell ref="B2111:F2111"/>
+    <mergeCell ref="B3164:F3164"/>
     <mergeCell ref="B2409:F2409"/>
     <mergeCell ref="B1377:F1377"/>
     <mergeCell ref="B1648:F1648"/>
@@ -56767,6 +57325,7 @@
     <mergeCell ref="B576:F576"/>
     <mergeCell ref="B138:F138"/>
     <mergeCell ref="B113:F113"/>
+    <mergeCell ref="A3166:F3166"/>
     <mergeCell ref="A1081:F1081"/>
     <mergeCell ref="B2688:F2688"/>
     <mergeCell ref="B1933:F1933"/>
@@ -56901,6 +57460,7 @@
     <mergeCell ref="B251:F251"/>
     <mergeCell ref="A1651:F1651"/>
     <mergeCell ref="B2196:F2196"/>
+    <mergeCell ref="B3168:F3168"/>
     <mergeCell ref="B1769:F1769"/>
     <mergeCell ref="B1014:F1014"/>
     <mergeCell ref="B2067:F2067"/>
@@ -56918,9 +57478,11 @@
     <mergeCell ref="B1016:F1016"/>
     <mergeCell ref="B3128:F3128"/>
     <mergeCell ref="B2707:F2707"/>
+    <mergeCell ref="B3153:F3153"/>
     <mergeCell ref="B282:F282"/>
     <mergeCell ref="B920:F920"/>
     <mergeCell ref="B580:F580"/>
+    <mergeCell ref="B3163:F3163"/>
     <mergeCell ref="B711:F711"/>
     <mergeCell ref="B1009:F1009"/>
     <mergeCell ref="B2102:F2102"/>
@@ -57215,6 +57777,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3119" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3134" r:id="rId209"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3149" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3164" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3179" r:id="rId212"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57226,7 +57790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J211"/>
+  <dimension ref="A1:J213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -59580,19 +60144,15 @@
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Circular design for bio-based innovation towards climate-neu</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr"/>
       <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -59616,15 +60176,19 @@
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neu</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIE</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -59972,12 +60536,12 @@
     <row r="85" ht="28" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr"/>
@@ -60004,12 +60568,12 @@
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr"/>
@@ -60036,12 +60600,12 @@
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr"/>
@@ -60068,12 +60632,12 @@
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr"/>
@@ -62724,12 +63288,12 @@
     <row r="171" ht="28" customHeight="1">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>877682967</t>
+          <t>UCPM</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RI</t>
+          <t>RIsk WATER flooding  EXercise</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr"/>
@@ -62756,12 +63320,12 @@
     <row r="172" ht="28" customHeight="1">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>UCPM</t>
+          <t>877682967</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>RIsk WATER flooding  EXercise</t>
+          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RI</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr"/>
@@ -63652,12 +64216,12 @@
     <row r="200" ht="28" customHeight="1">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>EUS-93732</t>
+          <t>EUS-18844</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ayudas a proyectos al amparo de la estrategia de desarrollo </t>
+          <t>Contratación del servicio de mantenimiento integral e inspec</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
@@ -63673,7 +64237,7 @@
       <c r="E200" s="6" t="inlineStr"/>
       <c r="F200" s="25" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MUY ALTA</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr"/>
@@ -63688,12 +64252,12 @@
     <row r="201" ht="28" customHeight="1">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>EUS-28838</t>
+          <t>EUS-01951</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocator</t>
+          <t xml:space="preserve">Ayudas a proyectos al amparo de la estrategia de desarrollo </t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -63724,12 +64288,12 @@
     <row r="202" ht="28" customHeight="1">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>EUS-72505</t>
+          <t>EUS-56052</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Asistencia técnica para la elaboración del Plan de Movilidad</t>
+          <t>HORIZON. El gran Programa de I+D+i de la UE lanza convocator</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
@@ -63760,12 +64324,12 @@
     <row r="203" ht="28" customHeight="1">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>EUS-51417</t>
+          <t>EUS-50335</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>Alquiler contenedor para residuos y su tratamiento</t>
+          <t>Asistencia técnica para la elaboración del Plan de Movilidad</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
@@ -63796,7 +64360,7 @@
     <row r="204" ht="28" customHeight="1">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>EUS-76515</t>
+          <t>EUS-95257</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
@@ -63832,7 +64396,7 @@
     <row r="205" ht="28" customHeight="1">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>EUS-69468</t>
+          <t>EUS-13959</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
@@ -63868,7 +64432,7 @@
     <row r="206" ht="28" customHeight="1">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>EUS-08471</t>
+          <t>EUS-94998</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
@@ -63904,7 +64468,7 @@
     <row r="207" ht="28" customHeight="1">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>EUS-98139</t>
+          <t>EUS-92809</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
@@ -63940,7 +64504,7 @@
     <row r="208" ht="28" customHeight="1">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>EUS-44103</t>
+          <t>EUS-29254</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
@@ -63976,7 +64540,7 @@
     <row r="209" ht="28" customHeight="1">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>EUS-99252</t>
+          <t>EUS-17441</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
@@ -64012,12 +64576,12 @@
     <row r="210" ht="28" customHeight="1">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>EUS-62644</t>
+          <t>EUS-52186</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>Redacción de proyecto de ejecución para la instalación de un</t>
+          <t>Servicio de atención y gestión integral de la vivienda Comun</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
@@ -64048,12 +64612,12 @@
     <row r="211" ht="28" customHeight="1">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>EUS-01533</t>
+          <t>EUS-87459</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>Estudio de detalle cubierta</t>
+          <t>Mejora del alumbrado público Fase 3</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
@@ -64081,8 +64645,80 @@
       <c r="I211" s="6" t="inlineStr"/>
       <c r="J211" s="6" t="inlineStr"/>
     </row>
+    <row r="212" ht="28" customHeight="1">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>EUS-84294</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>Redacción de proyecto de ejecución para la instalación de un</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr"/>
+      <c r="F212" s="25" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr"/>
+      <c r="H212" s="6" t="inlineStr">
+        <is>
+          <t>Por revisar</t>
+        </is>
+      </c>
+      <c r="I212" s="6" t="inlineStr"/>
+      <c r="J212" s="6" t="inlineStr"/>
+    </row>
+    <row r="213" ht="28" customHeight="1">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>EUS-19207</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>Estudio de detalle cubierta</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="inlineStr"/>
+      <c r="F213" s="25" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr"/>
+      <c r="H213" s="6" t="inlineStr">
+        <is>
+          <t>Por revisar</t>
+        </is>
+      </c>
+      <c r="I213" s="6" t="inlineStr"/>
+      <c r="J213" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J211"/>
+  <autoFilter ref="A1:J213"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/resultados_convocatorias.xlsx
+++ b/docs/resultados_convocatorias.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Recursos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$218</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$M$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seguimiento'!$A$1:$J$215</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M218"/>
+  <dimension ref="A1:M220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -685,7 +685,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 25/10/2026 10:15 - 212 convocatorias - 13 nuevas</t>
+          <t>Mision Climatica - Neutralidad 2030 - Actualizado: 26/10/2026 11:40 - 214 convocatorias - 16 nuevas</t>
         </is>
       </c>
     </row>
@@ -4120,15 +4120,19 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr"/>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4149,7 +4153,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4167,19 +4171,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr"/>
       <c r="E78" s="10" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr"/>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr"/>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr"/>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr"/>
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -4833,12 +4833,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr"/>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>937468917</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr"/>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr"/>
@@ -7136,12 +7136,12 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>n002cet5</t>
+          <t>937468917</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr"/>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7183,12 +7183,12 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>n002cet5</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr"/>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K142" s="6" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a sing</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="L142" s="6" t="inlineStr"/>
@@ -7230,12 +7230,12 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr"/>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a sing</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7277,12 +7277,12 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>885233544</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="K144" s="6" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="L144" s="6" t="inlineStr"/>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>885233544</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr"/>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="K146" s="6" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="L146" s="6" t="inlineStr"/>
@@ -7418,12 +7418,12 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr"/>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we si</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr"/>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="K148" s="6" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technolog</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we si</t>
         </is>
       </c>
       <c r="L148" s="6" t="inlineStr"/>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr"/>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technolog</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr"/>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="K150" s="6" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="L150" s="6" t="inlineStr"/>
@@ -7606,12 +7606,12 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr"/>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -7653,12 +7653,12 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>956926438</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr"/>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="K152" s="6" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="L152" s="6" t="inlineStr"/>
@@ -7700,12 +7700,12 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>956926438</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr"/>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -7747,12 +7747,12 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>953677035</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr"/>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="K154" s="6" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="L154" s="6" t="inlineStr"/>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>953552487</t>
+          <t>953677035</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>95140</t>
+          <t>953552487</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr"/>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="K156" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? </t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="L156" s="6" t="inlineStr"/>
@@ -7888,12 +7888,12 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>95140</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2022-CET, topic LIFE-2022-CET-DH, what is meant by "district heating"?</t>
+          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr"/>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>Under call LIFE-2022-CET, topic LIFE-2022-CET-DH, what is meant by "district heating"?</t>
+          <t xml:space="preserve">1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? </t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -7935,12 +7935,12 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>Under call LIFE-2022-CET, topic LIFE-2022-CET-DH, what is meant by "district heating"?</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr"/>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="K158" s="6" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>Under call LIFE-2022-CET, topic LIFE-2022-CET-DH, what is meant by "district heating"?</t>
         </is>
       </c>
       <c r="L158" s="6" t="inlineStr"/>
@@ -7982,12 +7982,12 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr"/>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8029,12 +8029,12 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>876983694</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr"/>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="K160" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="L160" s="6" t="inlineStr"/>
@@ -8076,12 +8076,12 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>876983694</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infra</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8123,12 +8123,12 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>935134321</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr"/>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="K162" s="6" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infra</t>
         </is>
       </c>
       <c r="L162" s="6" t="inlineStr"/>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>883154834</t>
+          <t>935134321</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr"/>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8217,12 +8217,12 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>883154834</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="L164" s="6" t="inlineStr"/>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>950910110</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>CURA TERRAE WATER LIMITED</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr"/>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>CURA TERRAE WATER LIMITED</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8311,12 +8311,12 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>999515355</t>
+          <t>950910110</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>TRUSTEES OF PRINCETON UNIVERSITY</t>
+          <t>CURA TERRAE WATER LIMITED</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="K166" s="6" t="inlineStr">
         <is>
-          <t>TRUSTEES OF PRINCETON UNIVERSITY</t>
+          <t>CURA TERRAE WATER LIMITED</t>
         </is>
       </c>
       <c r="L166" s="6" t="inlineStr"/>
@@ -8358,12 +8358,12 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>968942119</t>
+          <t>999515355</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>INFO-LOGICA OOD</t>
+          <t>TRUSTEES OF PRINCETON UNIVERSITY</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>INFO-LOGICA OOD</t>
+          <t>TRUSTEES OF PRINCETON UNIVERSITY</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>913143063</t>
+          <t>968942119</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA BELOVO</t>
+          <t>INFO-LOGICA OOD</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr"/>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="K168" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA BELOVO</t>
+          <t>INFO-LOGICA OOD</t>
         </is>
       </c>
       <c r="L168" s="6" t="inlineStr"/>
@@ -8452,12 +8452,12 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>947753536</t>
+          <t>913143063</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA KAZANLAK</t>
+          <t>OBSHTINA BELOVO</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr"/>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA KAZANLAK</t>
+          <t>OBSHTINA BELOVO</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>928211140</t>
+          <t>947753536</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA KAZANLAK</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="K170" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA KAZANLAK</t>
         </is>
       </c>
       <c r="L170" s="6" t="inlineStr"/>
@@ -8546,12 +8546,12 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>928057492</t>
+          <t>928211140</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>926227393</t>
+          <t>928057492</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr"/>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="K172" s="6" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="L172" s="6" t="inlineStr"/>
@@ -8640,12 +8640,12 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>926227393</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>Prof. Dr. Jorge Isidoro</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr"/>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>Prof. Dr. Jorge Isidoro</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -8734,12 +8734,12 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>UCPM</t>
+          <t>877682967</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>RIsk WATER flooding  EXercise</t>
+          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr"/>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>RIsk WATER flooding EXercise</t>
+          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>877682967</t>
+          <t>UCPM</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
+          <t>RIsk WATER flooding  EXercise</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr"/>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
+          <t>RIsk WATER flooding EXercise</t>
         </is>
       </c>
       <c r="L176" s="6" t="inlineStr"/>
@@ -10104,13 +10104,12 @@
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>EUS-18844</t>
+          <t>EUS-09468</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>Contratación del servicio de mantenimiento integral e inspección de las instalaciones térmicas en edificios e instalaciones 
-municipales del Ayuntamiento de Amorebieta-Etxano</t>
+          <t>trabajos de arreglo de cortinas en edificio ayuntamiento y dendaberri</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
@@ -10160,7 +10159,7 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>EUS-01951</t>
+          <t>EUS-84836</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
@@ -10215,7 +10214,7 @@
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>EUS-56052</t>
+          <t>EUS-98098</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
@@ -10270,12 +10269,12 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>EUS-50335</t>
+          <t>EUS-28011</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>Asistencia técnica para la elaboración del Plan de Movilidad Sostenible de la Diputación Foral de Álava</t>
+          <t>modificiacion conductos climatizacion del rocodromo</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
@@ -10325,7 +10324,7 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>EUS-95257</t>
+          <t>EUS-81589</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
@@ -10380,7 +10379,7 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>EUS-13959</t>
+          <t>EUS-29388</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
@@ -10435,7 +10434,7 @@
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>EUS-94998</t>
+          <t>EUS-00993</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
@@ -10490,7 +10489,7 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>EUS-92809</t>
+          <t>EUS-89388</t>
         </is>
       </c>
       <c r="C212" s="6" t="inlineStr">
@@ -10545,7 +10544,7 @@
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>EUS-29254</t>
+          <t>EUS-81057</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
@@ -10600,7 +10599,7 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>EUS-17441</t>
+          <t>EUS-73884</t>
         </is>
       </c>
       <c r="C214" s="6" t="inlineStr">
@@ -10636,7 +10635,11 @@
           <t>Gobierno Vasco / Sector Publico Euskadi</t>
         </is>
       </c>
-      <c r="L214" s="6" t="inlineStr"/>
+      <c r="L214" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
       <c r="M214" s="9" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -10651,12 +10654,12 @@
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>EUS-52186</t>
+          <t>EUS-69744</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>Servicio de atención y gestión integral de la vivienda Comunitaria de Laguardia</t>
+          <t>trabajos de instalación eléctrica del alumbrado en zonas de juegos y frontones de la ikastola egape</t>
         </is>
       </c>
       <c r="D215" s="6" t="inlineStr">
@@ -10706,12 +10709,12 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>EUS-87459</t>
+          <t>EUS-56877</t>
         </is>
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>Mejora del alumbrado público Fase 3</t>
+          <t>trabajos de obra civil para instalar dos nuevos puntos del alumbrado en ergoien industrialdea</t>
         </is>
       </c>
       <c r="D216" s="6" t="inlineStr">
@@ -10761,12 +10764,12 @@
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>EUS-84294</t>
+          <t>EUS-30348</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>Redacción de proyecto de ejecución para la instalación de una cubierta en Urizar</t>
+          <t>trabajos de impermeabilización zona baja de los foso de los 2 ascensores en paso bajo vías apeadero del tren</t>
         </is>
       </c>
       <c r="D217" s="6" t="inlineStr">
@@ -10816,12 +10819,12 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>EUS-19207</t>
+          <t>EUS-01123</t>
         </is>
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>Estudio de detalle cubierta</t>
+          <t>trabajos realización obra civil para renovación alumbrado público en la plaza txoritagain 03</t>
         </is>
       </c>
       <c r="D218" s="6" t="inlineStr">
@@ -10863,8 +10866,118 @@
         </is>
       </c>
     </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>EUS-15185</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>10 packs de 24, agua 0,5l</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F219" s="6" t="inlineStr"/>
+      <c r="G219" s="6" t="inlineStr"/>
+      <c r="H219" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I219" s="12" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="J219" s="6" t="inlineStr"/>
+      <c r="K219" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L219" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M219" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" s="14" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t>EUS-44336</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>suministro de contenedores de120 litros ara uso en festejos</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F220" s="6" t="inlineStr"/>
+      <c r="G220" s="6" t="inlineStr"/>
+      <c r="H220" s="6" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="I220" s="12" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="J220" s="6" t="inlineStr"/>
+      <c r="K220" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="L220" s="15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="M220" s="9" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:M218"/>
+  <autoFilter ref="A4:M220"/>
   <mergeCells count="4">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A204:M204"/>
@@ -11084,6 +11197,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId211"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M219" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M220" r:id="rId214"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11095,7 +11210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3179"/>
+  <dimension ref="A1:F3209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25653,7 +25768,7 @@
     <row r="1066" ht="30" customHeight="1">
       <c r="A1066" s="16" t="inlineStr">
         <is>
-          <t>FICHA 72: ERASMUS2027</t>
+          <t>FICHA 72: HORIZON</t>
         </is>
       </c>
       <c r="B1066" s="17" t="n"/>
@@ -25686,7 +25801,7 @@
       </c>
       <c r="B1068" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C1068" s="20" t="n"/>
@@ -25702,7 +25817,7 @@
       </c>
       <c r="B1069" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS2027</t>
+          <t>HORIZON</t>
         </is>
       </c>
       <c r="C1069" s="20" t="n"/>
@@ -25716,7 +25831,11 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1070" s="19" t="inlineStr"/>
+      <c r="B1070" s="19" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
       <c r="C1070" s="20" t="n"/>
       <c r="D1070" s="20" t="n"/>
       <c r="E1070" s="20" t="n"/>
@@ -25790,7 +25909,7 @@
       </c>
       <c r="B1075" s="19" t="inlineStr">
         <is>
-          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
+          <t>HORIZON-MISS-2021-CIT-02</t>
         </is>
       </c>
       <c r="C1075" s="20" t="n"/>
@@ -25806,7 +25925,7 @@
       </c>
       <c r="B1076" s="19" t="inlineStr">
         <is>
-          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
+          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
         </is>
       </c>
       <c r="C1076" s="20" t="n"/>
@@ -25850,7 +25969,7 @@
       </c>
       <c r="B1079" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
         </is>
       </c>
       <c r="C1079" s="20" t="n"/>
@@ -25861,7 +25980,7 @@
     <row r="1081" ht="30" customHeight="1">
       <c r="A1081" s="16" t="inlineStr">
         <is>
-          <t>FICHA 73: HORIZON</t>
+          <t>FICHA 73: ERASMUS2027</t>
         </is>
       </c>
       <c r="B1081" s="17" t="n"/>
@@ -25894,7 +26013,7 @@
       </c>
       <c r="B1083" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C1083" s="20" t="n"/>
@@ -25910,7 +26029,7 @@
       </c>
       <c r="B1084" s="19" t="inlineStr">
         <is>
-          <t>HORIZON</t>
+          <t>ERASMUS2027</t>
         </is>
       </c>
       <c r="C1084" s="20" t="n"/>
@@ -25924,11 +26043,7 @@
           <t>Programa</t>
         </is>
       </c>
-      <c r="B1085" s="19" t="inlineStr">
-        <is>
-          <t>Horizon Europe</t>
-        </is>
-      </c>
+      <c r="B1085" s="19" t="inlineStr"/>
       <c r="C1085" s="20" t="n"/>
       <c r="D1085" s="20" t="n"/>
       <c r="E1085" s="20" t="n"/>
@@ -26002,7 +26117,7 @@
       </c>
       <c r="B1090" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2021-CIT-02</t>
+          <t>ERASMUS-EDU-2022-PI-ALL-INNO</t>
         </is>
       </c>
       <c r="C1090" s="20" t="n"/>
@@ -26018,7 +26133,7 @@
       </c>
       <c r="B1091" s="19" t="inlineStr">
         <is>
-          <t>SMART PUBLIC TRANSPORT INITIATIVES FOR CLIMATE-NEUTRAL CITIES IN EUROPE</t>
+          <t>Circular design for bio-based innovation towards climate-neutral cities</t>
         </is>
       </c>
       <c r="C1091" s="20" t="n"/>
@@ -26062,7 +26177,7 @@
       </c>
       <c r="B1094" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS2027</t>
         </is>
       </c>
       <c r="C1094" s="20" t="n"/>
@@ -28125,7 +28240,7 @@
     <row r="1246" ht="30" customHeight="1">
       <c r="A1246" s="16" t="inlineStr">
         <is>
-          <t>FICHA 84: 917779760</t>
+          <t>FICHA 84: 928447529</t>
         </is>
       </c>
       <c r="B1246" s="17" t="n"/>
@@ -28158,7 +28273,7 @@
       </c>
       <c r="B1248" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1248" s="20" t="n"/>
@@ -28174,7 +28289,7 @@
       </c>
       <c r="B1249" s="19" t="inlineStr">
         <is>
-          <t>917779760</t>
+          <t>928447529</t>
         </is>
       </c>
       <c r="C1249" s="20" t="n"/>
@@ -28274,7 +28389,7 @@
       </c>
       <c r="B1256" s="19" t="inlineStr">
         <is>
-          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
+          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
         </is>
       </c>
       <c r="C1256" s="20" t="n"/>
@@ -28318,7 +28433,7 @@
       </c>
       <c r="B1259" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
         </is>
       </c>
       <c r="C1259" s="20" t="n"/>
@@ -28329,7 +28444,7 @@
     <row r="1261" ht="30" customHeight="1">
       <c r="A1261" s="16" t="inlineStr">
         <is>
-          <t>FICHA 85: 920115617</t>
+          <t>FICHA 85: 917671508</t>
         </is>
       </c>
       <c r="B1261" s="17" t="n"/>
@@ -28362,7 +28477,7 @@
       </c>
       <c r="B1263" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1263" s="20" t="n"/>
@@ -28378,7 +28493,7 @@
       </c>
       <c r="B1264" s="19" t="inlineStr">
         <is>
-          <t>920115617</t>
+          <t>917671508</t>
         </is>
       </c>
       <c r="C1264" s="20" t="n"/>
@@ -28478,7 +28593,7 @@
       </c>
       <c r="B1271" s="19" t="inlineStr">
         <is>
-          <t>EUE APS</t>
+          <t>IN-DER-CITY-BUS GMBH</t>
         </is>
       </c>
       <c r="C1271" s="20" t="n"/>
@@ -28522,7 +28637,7 @@
       </c>
       <c r="B1274" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
         </is>
       </c>
       <c r="C1274" s="20" t="n"/>
@@ -28533,7 +28648,7 @@
     <row r="1276" ht="30" customHeight="1">
       <c r="A1276" s="16" t="inlineStr">
         <is>
-          <t>FICHA 86: 917671508</t>
+          <t>FICHA 86: 917779760</t>
         </is>
       </c>
       <c r="B1276" s="17" t="n"/>
@@ -28566,7 +28681,7 @@
       </c>
       <c r="B1278" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1278" s="20" t="n"/>
@@ -28582,7 +28697,7 @@
       </c>
       <c r="B1279" s="19" t="inlineStr">
         <is>
-          <t>917671508</t>
+          <t>917779760</t>
         </is>
       </c>
       <c r="C1279" s="20" t="n"/>
@@ -28682,7 +28797,7 @@
       </c>
       <c r="B1286" s="19" t="inlineStr">
         <is>
-          <t>IN-DER-CITY-BUS GMBH</t>
+          <t>MAINZER VERKEHRSGESELLSCHAFT MBH</t>
         </is>
       </c>
       <c r="C1286" s="20" t="n"/>
@@ -28726,7 +28841,7 @@
       </c>
       <c r="B1289" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917671508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/917779760</t>
         </is>
       </c>
       <c r="C1289" s="20" t="n"/>
@@ -28737,7 +28852,7 @@
     <row r="1291" ht="30" customHeight="1">
       <c r="A1291" s="16" t="inlineStr">
         <is>
-          <t>FICHA 87: 928447529</t>
+          <t>FICHA 87: 920115617</t>
         </is>
       </c>
       <c r="B1291" s="17" t="n"/>
@@ -28770,7 +28885,7 @@
       </c>
       <c r="B1293" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1293" s="20" t="n"/>
@@ -28786,7 +28901,7 @@
       </c>
       <c r="B1294" s="19" t="inlineStr">
         <is>
-          <t>928447529</t>
+          <t>920115617</t>
         </is>
       </c>
       <c r="C1294" s="20" t="n"/>
@@ -28886,7 +29001,7 @@
       </c>
       <c r="B1301" s="19" t="inlineStr">
         <is>
-          <t>SASA SPA AG SOCIETA AUTOBUS SERVIZID'AREA SPA</t>
+          <t>EUE APS</t>
         </is>
       </c>
       <c r="C1301" s="20" t="n"/>
@@ -28930,7 +29045,7 @@
       </c>
       <c r="B1304" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928447529</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/920115617</t>
         </is>
       </c>
       <c r="C1304" s="20" t="n"/>
@@ -38557,7 +38672,7 @@
     <row r="2011" ht="30" customHeight="1">
       <c r="A2011" s="16" t="inlineStr">
         <is>
-          <t>FICHA 135: 937468917</t>
+          <t>FICHA 135: NA</t>
         </is>
       </c>
       <c r="B2011" s="17" t="n"/>
@@ -38582,7 +38697,7 @@
       <c r="E2012" s="20" t="n"/>
       <c r="F2012" s="20" t="n"/>
     </row>
-    <row r="2013" ht="45" customHeight="1">
+    <row r="2013" ht="20" customHeight="1">
       <c r="A2013" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -38590,7 +38705,7 @@
       </c>
       <c r="B2013" s="19" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="C2013" s="20" t="n"/>
@@ -38606,7 +38721,7 @@
       </c>
       <c r="B2014" s="19" t="inlineStr">
         <is>
-          <t>937468917</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="C2014" s="20" t="n"/>
@@ -38698,7 +38813,7 @@
       <c r="E2020" s="20" t="n"/>
       <c r="F2020" s="20" t="n"/>
     </row>
-    <row r="2021" ht="45" customHeight="1">
+    <row r="2021" ht="20" customHeight="1">
       <c r="A2021" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -38706,7 +38821,7 @@
       </c>
       <c r="B2021" s="19" t="inlineStr">
         <is>
-          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
+          <t>MS Elena Jauregui Baldassini</t>
         </is>
       </c>
       <c r="C2021" s="20" t="n"/>
@@ -38750,7 +38865,7 @@
       </c>
       <c r="B2024" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/937468917</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NA</t>
         </is>
       </c>
       <c r="C2024" s="20" t="n"/>
@@ -38761,7 +38876,7 @@
     <row r="2026" ht="30" customHeight="1">
       <c r="A2026" s="16" t="inlineStr">
         <is>
-          <t>FICHA 136: n002cet5</t>
+          <t>FICHA 136: 937468917</t>
         </is>
       </c>
       <c r="B2026" s="17" t="n"/>
@@ -38786,7 +38901,7 @@
       <c r="E2027" s="20" t="n"/>
       <c r="F2027" s="20" t="n"/>
     </row>
-    <row r="2028" ht="20" customHeight="1">
+    <row r="2028" ht="45" customHeight="1">
       <c r="A2028" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -38794,7 +38909,7 @@
       </c>
       <c r="B2028" s="19" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="C2028" s="20" t="n"/>
@@ -38810,7 +38925,7 @@
       </c>
       <c r="B2029" s="19" t="inlineStr">
         <is>
-          <t>n002cet5</t>
+          <t>937468917</t>
         </is>
       </c>
       <c r="C2029" s="20" t="n"/>
@@ -38902,7 +39017,7 @@
       <c r="E2035" s="20" t="n"/>
       <c r="F2035" s="20" t="n"/>
     </row>
-    <row r="2036" ht="20" customHeight="1">
+    <row r="2036" ht="45" customHeight="1">
       <c r="A2036" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -38910,7 +39025,7 @@
       </c>
       <c r="B2036" s="19" t="inlineStr">
         <is>
-          <t>Mr Valerio Gori</t>
+          <t>RETE AUTOSTRADE MEDITERRANEE PER  LA LOGISTICA LE INFRASTRUTTURE ED I  TRASPORTI SOCIETA PER AZIONI</t>
         </is>
       </c>
       <c r="C2036" s="20" t="n"/>
@@ -38954,7 +39069,7 @@
       </c>
       <c r="B2039" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n002cet5</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/937468917</t>
         </is>
       </c>
       <c r="C2039" s="20" t="n"/>
@@ -38965,7 +39080,7 @@
     <row r="2041" ht="30" customHeight="1">
       <c r="A2041" s="16" t="inlineStr">
         <is>
-          <t>FICHA 137: 48508</t>
+          <t>FICHA 137: n002cet5</t>
         </is>
       </c>
       <c r="B2041" s="17" t="n"/>
@@ -38990,7 +39105,7 @@
       <c r="E2042" s="20" t="n"/>
       <c r="F2042" s="20" t="n"/>
     </row>
-    <row r="2043" ht="45" customHeight="1">
+    <row r="2043" ht="20" customHeight="1">
       <c r="A2043" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -38998,7 +39113,7 @@
       </c>
       <c r="B2043" s="19" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="C2043" s="20" t="n"/>
@@ -39014,7 +39129,7 @@
       </c>
       <c r="B2044" s="19" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>n002cet5</t>
         </is>
       </c>
       <c r="C2044" s="20" t="n"/>
@@ -39106,7 +39221,7 @@
       <c r="E2050" s="20" t="n"/>
       <c r="F2050" s="20" t="n"/>
     </row>
-    <row r="2051" ht="45" customHeight="1">
+    <row r="2051" ht="20" customHeight="1">
       <c r="A2051" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -39114,7 +39229,7 @@
       </c>
       <c r="B2051" s="19" t="inlineStr">
         <is>
-          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
+          <t>Mr Valerio Gori</t>
         </is>
       </c>
       <c r="C2051" s="20" t="n"/>
@@ -39158,7 +39273,7 @@
       </c>
       <c r="B2054" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/48508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/n002cet5</t>
         </is>
       </c>
       <c r="C2054" s="20" t="n"/>
@@ -39169,7 +39284,7 @@
     <row r="2056" ht="30" customHeight="1">
       <c r="A2056" s="16" t="inlineStr">
         <is>
-          <t>FICHA 138: 16545</t>
+          <t>FICHA 138: 48508</t>
         </is>
       </c>
       <c r="B2056" s="17" t="n"/>
@@ -39202,7 +39317,7 @@
       </c>
       <c r="B2058" s="19" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="C2058" s="20" t="n"/>
@@ -39218,7 +39333,7 @@
       </c>
       <c r="B2059" s="19" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="C2059" s="20" t="n"/>
@@ -39318,7 +39433,7 @@
       </c>
       <c r="B2066" s="19" t="inlineStr">
         <is>
-          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
+          <t>Please clarify a Shipping / Sustainability Question. Under Lot 1 the packaging and transportation is defined. Can the sample transportation boxes be of a multi-use grade (sustainability); or is a single- use box desired.</t>
         </is>
       </c>
       <c r="C2066" s="20" t="n"/>
@@ -39362,7 +39477,7 @@
       </c>
       <c r="B2069" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16545</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/48508</t>
         </is>
       </c>
       <c r="C2069" s="20" t="n"/>
@@ -39373,7 +39488,7 @@
     <row r="2071" ht="30" customHeight="1">
       <c r="A2071" s="16" t="inlineStr">
         <is>
-          <t>FICHA 139: 885233544</t>
+          <t>FICHA 139: 16545</t>
         </is>
       </c>
       <c r="B2071" s="17" t="n"/>
@@ -39398,7 +39513,7 @@
       <c r="E2072" s="20" t="n"/>
       <c r="F2072" s="20" t="n"/>
     </row>
-    <row r="2073" ht="20" customHeight="1">
+    <row r="2073" ht="45" customHeight="1">
       <c r="A2073" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -39406,7 +39521,7 @@
       </c>
       <c r="B2073" s="19" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="C2073" s="20" t="n"/>
@@ -39422,7 +39537,7 @@
       </c>
       <c r="B2074" s="19" t="inlineStr">
         <is>
-          <t>885233544</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="C2074" s="20" t="n"/>
@@ -39514,7 +39629,7 @@
       <c r="E2080" s="20" t="n"/>
       <c r="F2080" s="20" t="n"/>
     </row>
-    <row r="2081" ht="20" customHeight="1">
+    <row r="2081" ht="45" customHeight="1">
       <c r="A2081" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -39522,7 +39637,7 @@
       </c>
       <c r="B2081" s="19" t="inlineStr">
         <is>
-          <t>ECAS_n0025qv9</t>
+          <t>Under Call CEF-E-PCI-PMI, could an entity from a third country receive financial support from CEF for energy infrastructure projects?</t>
         </is>
       </c>
       <c r="C2081" s="20" t="n"/>
@@ -39566,7 +39681,7 @@
       </c>
       <c r="B2084" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/885233544</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16545</t>
         </is>
       </c>
       <c r="C2084" s="20" t="n"/>
@@ -39577,7 +39692,7 @@
     <row r="2086" ht="30" customHeight="1">
       <c r="A2086" s="16" t="inlineStr">
         <is>
-          <t>FICHA 140: 18804</t>
+          <t>FICHA 140: 885233544</t>
         </is>
       </c>
       <c r="B2086" s="17" t="n"/>
@@ -39602,7 +39717,7 @@
       <c r="E2087" s="20" t="n"/>
       <c r="F2087" s="20" t="n"/>
     </row>
-    <row r="2088" ht="45" customHeight="1">
+    <row r="2088" ht="20" customHeight="1">
       <c r="A2088" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -39610,7 +39725,7 @@
       </c>
       <c r="B2088" s="19" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="C2088" s="20" t="n"/>
@@ -39626,7 +39741,7 @@
       </c>
       <c r="B2089" s="19" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>885233544</t>
         </is>
       </c>
       <c r="C2089" s="20" t="n"/>
@@ -39718,7 +39833,7 @@
       <c r="E2095" s="20" t="n"/>
       <c r="F2095" s="20" t="n"/>
     </row>
-    <row r="2096" ht="45" customHeight="1">
+    <row r="2096" ht="20" customHeight="1">
       <c r="A2096" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -39726,7 +39841,7 @@
       </c>
       <c r="B2096" s="19" t="inlineStr">
         <is>
-          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
+          <t>ECAS_n0025qv9</t>
         </is>
       </c>
       <c r="C2096" s="20" t="n"/>
@@ -39770,7 +39885,7 @@
       </c>
       <c r="B2099" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18804</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/885233544</t>
         </is>
       </c>
       <c r="C2099" s="20" t="n"/>
@@ -39781,7 +39896,7 @@
     <row r="2101" ht="30" customHeight="1">
       <c r="A2101" s="16" t="inlineStr">
         <is>
-          <t>FICHA 141: 18749</t>
+          <t>FICHA 141: 18804</t>
         </is>
       </c>
       <c r="B2101" s="17" t="n"/>
@@ -39814,7 +39929,7 @@
       </c>
       <c r="B2103" s="19" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="C2103" s="20" t="n"/>
@@ -39830,7 +39945,7 @@
       </c>
       <c r="B2104" s="19" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="C2104" s="20" t="n"/>
@@ -39930,7 +40045,7 @@
       </c>
       <c r="B2111" s="19" t="inlineStr">
         <is>
-          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
+          <t>Under call topic DIGITAL-2021-CLOUD-AI-01-PREP-SMART-COMM, who can apply to the call?</t>
         </is>
       </c>
       <c r="C2111" s="20" t="n"/>
@@ -39974,7 +40089,7 @@
       </c>
       <c r="B2114" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18749</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18804</t>
         </is>
       </c>
       <c r="C2114" s="20" t="n"/>
@@ -39985,7 +40100,7 @@
     <row r="2116" ht="30" customHeight="1">
       <c r="A2116" s="16" t="inlineStr">
         <is>
-          <t>FICHA 142: 31728</t>
+          <t>FICHA 142: 18749</t>
         </is>
       </c>
       <c r="B2116" s="17" t="n"/>
@@ -40018,7 +40133,7 @@
       </c>
       <c r="B2118" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="C2118" s="20" t="n"/>
@@ -40034,7 +40149,7 @@
       </c>
       <c r="B2119" s="19" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="C2119" s="20" t="n"/>
@@ -40134,7 +40249,7 @@
       </c>
       <c r="B2126" s="19" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
+          <t>Are smart cities eligible under call CEF-DIG-2024-5GLSP-SMARTCOM WORKS: 5G large scale pilots – 5G and Edge for Smart Communities – Works?</t>
         </is>
       </c>
       <c r="C2126" s="20" t="n"/>
@@ -40178,7 +40293,7 @@
       </c>
       <c r="B2129" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31728</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/18749</t>
         </is>
       </c>
       <c r="C2129" s="20" t="n"/>
@@ -40189,7 +40304,7 @@
     <row r="2131" ht="30" customHeight="1">
       <c r="A2131" s="16" t="inlineStr">
         <is>
-          <t>FICHA 143: 13660</t>
+          <t>FICHA 143: 31728</t>
         </is>
       </c>
       <c r="B2131" s="17" t="n"/>
@@ -40214,7 +40329,7 @@
       <c r="E2132" s="20" t="n"/>
       <c r="F2132" s="20" t="n"/>
     </row>
-    <row r="2133" ht="20" customHeight="1">
+    <row r="2133" ht="45" customHeight="1">
       <c r="A2133" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -40222,7 +40337,7 @@
       </c>
       <c r="B2133" s="19" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="C2133" s="20" t="n"/>
@@ -40238,7 +40353,7 @@
       </c>
       <c r="B2134" s="19" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="C2134" s="20" t="n"/>
@@ -40338,7 +40453,7 @@
       </c>
       <c r="B2141" s="19" t="inlineStr">
         <is>
-          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technology in the heating and cooling sector. This is in line with the Paris Agreement and approaches a nearly zero carbon energy system.- By</t>
+          <t>HORIZON-CL5-2024-D3-01-06: The indicative budget per project (3 M€) may not be enough to include district heating for neighbouring industries. Do proposals have to make district heating or could we simulate a cascading of residual geothermal waste heat?</t>
         </is>
       </c>
       <c r="C2141" s="20" t="n"/>
@@ -40382,7 +40497,7 @@
       </c>
       <c r="B2144" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13660</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/31728</t>
         </is>
       </c>
       <c r="C2144" s="20" t="n"/>
@@ -40393,7 +40508,7 @@
     <row r="2146" ht="30" customHeight="1">
       <c r="A2146" s="16" t="inlineStr">
         <is>
-          <t>FICHA 144: 6484</t>
+          <t>FICHA 144: 13660</t>
         </is>
       </c>
       <c r="B2146" s="17" t="n"/>
@@ -40418,7 +40533,7 @@
       <c r="E2147" s="20" t="n"/>
       <c r="F2147" s="20" t="n"/>
     </row>
-    <row r="2148" ht="45" customHeight="1">
+    <row r="2148" ht="20" customHeight="1">
       <c r="A2148" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -40426,7 +40541,7 @@
       </c>
       <c r="B2148" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector</t>
         </is>
       </c>
       <c r="C2148" s="20" t="n"/>
@@ -40442,7 +40557,7 @@
       </c>
       <c r="B2149" s="19" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="C2149" s="20" t="n"/>
@@ -40542,7 +40657,7 @@
       </c>
       <c r="B2156" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
+          <t>Strategies and tools for decarbonising EU's heating and cooling sector HRE makes it evident that by 2050:- CO2 emissions can be reduced by 4.340 Mton or 86% compared to 1990 using only known technology in the heating and cooling sector. This is in line with the Paris Agreement and approaches a nearly zero carbon energy system.- By</t>
         </is>
       </c>
       <c r="C2156" s="20" t="n"/>
@@ -40586,7 +40701,7 @@
       </c>
       <c r="B2159" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/6484</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/13660</t>
         </is>
       </c>
       <c r="C2159" s="20" t="n"/>
@@ -40597,7 +40712,7 @@
     <row r="2161" ht="30" customHeight="1">
       <c r="A2161" s="16" t="inlineStr">
         <is>
-          <t>FICHA 145: 16367</t>
+          <t>FICHA 145: 6484</t>
         </is>
       </c>
       <c r="B2161" s="17" t="n"/>
@@ -40630,7 +40745,7 @@
       </c>
       <c r="B2163" s="19" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="C2163" s="20" t="n"/>
@@ -40646,7 +40761,7 @@
       </c>
       <c r="B2164" s="19" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="C2164" s="20" t="n"/>
@@ -40746,7 +40861,7 @@
       </c>
       <c r="B2171" s="19" t="inlineStr">
         <is>
-          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
+          <t>Under call H2020-EE-2016-2017, topic EE-01-2017, can a proposal deal with heat recovery in urban areas without connection to heating and cooling supply systems or district heating and cooling systems?</t>
         </is>
       </c>
       <c r="C2171" s="20" t="n"/>
@@ -40790,7 +40905,7 @@
       </c>
       <c r="B2174" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16367</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/6484</t>
         </is>
       </c>
       <c r="C2174" s="20" t="n"/>
@@ -40801,7 +40916,7 @@
     <row r="2176" ht="30" customHeight="1">
       <c r="A2176" s="16" t="inlineStr">
         <is>
-          <t>FICHA 146: 71691</t>
+          <t>FICHA 146: 16367</t>
         </is>
       </c>
       <c r="B2176" s="17" t="n"/>
@@ -40834,7 +40949,7 @@
       </c>
       <c r="B2178" s="19" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="C2178" s="20" t="n"/>
@@ -40850,7 +40965,7 @@
       </c>
       <c r="B2179" s="19" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="C2179" s="20" t="n"/>
@@ -40950,7 +41065,7 @@
       </c>
       <c r="B2186" s="19" t="inlineStr">
         <is>
-          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
+          <t>Under call HORIZON-CL5-2021-D4-01, topic HORIZON-CL5-2021-D4-01-04, does district heating qualify as an "industrial waste heat" source?</t>
         </is>
       </c>
       <c r="C2186" s="20" t="n"/>
@@ -40994,7 +41109,7 @@
       </c>
       <c r="B2189" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71691</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/16367</t>
         </is>
       </c>
       <c r="C2189" s="20" t="n"/>
@@ -41005,7 +41120,7 @@
     <row r="2191" ht="30" customHeight="1">
       <c r="A2191" s="16" t="inlineStr">
         <is>
-          <t>FICHA 147: 956926438</t>
+          <t>FICHA 147: 71691</t>
         </is>
       </c>
       <c r="B2191" s="17" t="n"/>
@@ -41030,7 +41145,7 @@
       <c r="E2192" s="20" t="n"/>
       <c r="F2192" s="20" t="n"/>
     </row>
-    <row r="2193" ht="20" customHeight="1">
+    <row r="2193" ht="45" customHeight="1">
       <c r="A2193" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -41038,7 +41153,7 @@
       </c>
       <c r="B2193" s="19" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="C2193" s="20" t="n"/>
@@ -41054,7 +41169,7 @@
       </c>
       <c r="B2194" s="19" t="inlineStr">
         <is>
-          <t>956926438</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="C2194" s="20" t="n"/>
@@ -41146,7 +41261,7 @@
       <c r="E2200" s="20" t="n"/>
       <c r="F2200" s="20" t="n"/>
     </row>
-    <row r="2201" ht="20" customHeight="1">
+    <row r="2201" ht="45" customHeight="1">
       <c r="A2201" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -41154,7 +41269,7 @@
       </c>
       <c r="B2201" s="19" t="inlineStr">
         <is>
-          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
+          <t>Which kind of network optimisation should be covered? Is thermal energy for district heating in scope?</t>
         </is>
       </c>
       <c r="C2201" s="20" t="n"/>
@@ -41198,7 +41313,7 @@
       </c>
       <c r="B2204" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/956926438</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/71691</t>
         </is>
       </c>
       <c r="C2204" s="20" t="n"/>
@@ -41209,7 +41324,7 @@
     <row r="2206" ht="30" customHeight="1">
       <c r="A2206" s="16" t="inlineStr">
         <is>
-          <t>FICHA 148: 10027</t>
+          <t>FICHA 148: 956926438</t>
         </is>
       </c>
       <c r="B2206" s="17" t="n"/>
@@ -41234,7 +41349,7 @@
       <c r="E2207" s="20" t="n"/>
       <c r="F2207" s="20" t="n"/>
     </row>
-    <row r="2208" ht="45" customHeight="1">
+    <row r="2208" ht="20" customHeight="1">
       <c r="A2208" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -41242,7 +41357,7 @@
       </c>
       <c r="B2208" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="C2208" s="20" t="n"/>
@@ -41258,7 +41373,7 @@
       </c>
       <c r="B2209" s="19" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>956926438</t>
         </is>
       </c>
       <c r="C2209" s="20" t="n"/>
@@ -41350,7 +41465,7 @@
       <c r="E2215" s="20" t="n"/>
       <c r="F2215" s="20" t="n"/>
     </row>
-    <row r="2216" ht="45" customHeight="1">
+    <row r="2216" ht="20" customHeight="1">
       <c r="A2216" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -41358,7 +41473,7 @@
       </c>
       <c r="B2216" s="19" t="inlineStr">
         <is>
-          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
+          <t>SOLAR NAHWAERME AT ENERGIECONTRACTING GMBH</t>
         </is>
       </c>
       <c r="C2216" s="20" t="n"/>
@@ -41402,7 +41517,7 @@
       </c>
       <c r="B2219" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/10027</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/956926438</t>
         </is>
       </c>
       <c r="C2219" s="20" t="n"/>
@@ -41413,7 +41528,7 @@
     <row r="2221" ht="30" customHeight="1">
       <c r="A2221" s="16" t="inlineStr">
         <is>
-          <t>FICHA 149: 953677035</t>
+          <t>FICHA 149: 10027</t>
         </is>
       </c>
       <c r="B2221" s="17" t="n"/>
@@ -41438,7 +41553,7 @@
       <c r="E2222" s="20" t="n"/>
       <c r="F2222" s="20" t="n"/>
     </row>
-    <row r="2223" ht="20" customHeight="1">
+    <row r="2223" ht="45" customHeight="1">
       <c r="A2223" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -41446,7 +41561,7 @@
       </c>
       <c r="B2223" s="19" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="C2223" s="20" t="n"/>
@@ -41462,7 +41577,7 @@
       </c>
       <c r="B2224" s="19" t="inlineStr">
         <is>
-          <t>953677035</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="C2224" s="20" t="n"/>
@@ -41554,7 +41669,7 @@
       <c r="E2230" s="20" t="n"/>
       <c r="F2230" s="20" t="n"/>
     </row>
-    <row r="2231" ht="20" customHeight="1">
+    <row r="2231" ht="45" customHeight="1">
       <c r="A2231" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -41562,7 +41677,7 @@
       </c>
       <c r="B2231" s="19" t="inlineStr">
         <is>
-          <t>INGETEK SISTEMAS SA</t>
+          <t>Under call H2020-LC-SC3-2018-2019-2020, topic LC-SC3-EC-1-2018-2019-2020, do district heating and central heating fall within the scope of the 2018 call?</t>
         </is>
       </c>
       <c r="C2231" s="20" t="n"/>
@@ -41606,7 +41721,7 @@
       </c>
       <c r="B2234" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953677035</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/10027</t>
         </is>
       </c>
       <c r="C2234" s="20" t="n"/>
@@ -41617,7 +41732,7 @@
     <row r="2236" ht="30" customHeight="1">
       <c r="A2236" s="16" t="inlineStr">
         <is>
-          <t>FICHA 150: 953552487</t>
+          <t>FICHA 150: 953677035</t>
         </is>
       </c>
       <c r="B2236" s="17" t="n"/>
@@ -41650,7 +41765,7 @@
       </c>
       <c r="B2238" s="19" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="C2238" s="20" t="n"/>
@@ -41666,7 +41781,7 @@
       </c>
       <c r="B2239" s="19" t="inlineStr">
         <is>
-          <t>953552487</t>
+          <t>953677035</t>
         </is>
       </c>
       <c r="C2239" s="20" t="n"/>
@@ -41766,7 +41881,7 @@
       </c>
       <c r="B2246" s="19" t="inlineStr">
         <is>
-          <t>AERMEC SPA</t>
+          <t>INGETEK SISTEMAS SA</t>
         </is>
       </c>
       <c r="C2246" s="20" t="n"/>
@@ -41810,7 +41925,7 @@
       </c>
       <c r="B2249" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953552487</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953677035</t>
         </is>
       </c>
       <c r="C2249" s="20" t="n"/>
@@ -41821,7 +41936,7 @@
     <row r="2251" ht="30" customHeight="1">
       <c r="A2251" s="16" t="inlineStr">
         <is>
-          <t>FICHA 151: 95140</t>
+          <t>FICHA 151: 953552487</t>
         </is>
       </c>
       <c r="B2251" s="17" t="n"/>
@@ -41846,7 +41961,7 @@
       <c r="E2252" s="20" t="n"/>
       <c r="F2252" s="20" t="n"/>
     </row>
-    <row r="2253" ht="45" customHeight="1">
+    <row r="2253" ht="20" customHeight="1">
       <c r="A2253" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -41854,7 +41969,7 @@
       </c>
       <c r="B2253" s="19" t="inlineStr">
         <is>
-          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="C2253" s="20" t="n"/>
@@ -41870,7 +41985,7 @@
       </c>
       <c r="B2254" s="19" t="inlineStr">
         <is>
-          <t>95140</t>
+          <t>953552487</t>
         </is>
       </c>
       <c r="C2254" s="20" t="n"/>
@@ -41962,7 +42077,7 @@
       <c r="E2260" s="20" t="n"/>
       <c r="F2260" s="20" t="n"/>
     </row>
-    <row r="2261" ht="45" customHeight="1">
+    <row r="2261" ht="20" customHeight="1">
       <c r="A2261" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -41970,7 +42085,7 @@
       </c>
       <c r="B2261" s="19" t="inlineStr">
         <is>
-          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
+          <t>AERMEC SPA</t>
         </is>
       </c>
       <c r="C2261" s="20" t="n"/>
@@ -42014,7 +42129,7 @@
       </c>
       <c r="B2264" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95140</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/953552487</t>
         </is>
       </c>
       <c r="C2264" s="20" t="n"/>
@@ -42025,7 +42140,7 @@
     <row r="2266" ht="30" customHeight="1">
       <c r="A2266" s="16" t="inlineStr">
         <is>
-          <t>FICHA 152: 19895</t>
+          <t>FICHA 152: 95140</t>
         </is>
       </c>
       <c r="B2266" s="17" t="n"/>
@@ -42058,7 +42173,7 @@
       </c>
       <c r="B2268" s="19" t="inlineStr">
         <is>
-          <t>Under call LIFE-2022-CET, topic LIFE-2022-CET-DH, what is meant by "district heating"?</t>
+          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
         </is>
       </c>
       <c r="C2268" s="20" t="n"/>
@@ -42074,7 +42189,7 @@
       </c>
       <c r="B2269" s="19" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>95140</t>
         </is>
       </c>
       <c r="C2269" s="20" t="n"/>
@@ -42174,7 +42289,7 @@
       </c>
       <c r="B2276" s="19" t="inlineStr">
         <is>
-          <t>Under call LIFE-2022-CET, topic LIFE-2022-CET-DH, what is meant by "district heating"?</t>
+          <t>1. Should combustible industrial residues, like syngases, residues from food processing industries, pulp and paper etc., be included in the technology inventory and substitution-potential assessment? 2. Should industrial excess heat/waste heat recovery be covered as a decarbonisation option in its own right, or only where combined with renewable h</t>
         </is>
       </c>
       <c r="C2276" s="20" t="n"/>
@@ -42218,7 +42333,7 @@
       </c>
       <c r="B2279" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19895</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/95140</t>
         </is>
       </c>
       <c r="C2279" s="20" t="n"/>
@@ -42229,7 +42344,7 @@
     <row r="2281" ht="30" customHeight="1">
       <c r="A2281" s="16" t="inlineStr">
         <is>
-          <t>FICHA 153: 934294980</t>
+          <t>FICHA 153: 19895</t>
         </is>
       </c>
       <c r="B2281" s="17" t="n"/>
@@ -42254,7 +42369,7 @@
       <c r="E2282" s="20" t="n"/>
       <c r="F2282" s="20" t="n"/>
     </row>
-    <row r="2283" ht="20" customHeight="1">
+    <row r="2283" ht="45" customHeight="1">
       <c r="A2283" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -42262,7 +42377,7 @@
       </c>
       <c r="B2283" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>Under call LIFE-2022-CET, topic LIFE-2022-CET-DH, what is meant by "district heating"?</t>
         </is>
       </c>
       <c r="C2283" s="20" t="n"/>
@@ -42278,7 +42393,7 @@
       </c>
       <c r="B2284" s="19" t="inlineStr">
         <is>
-          <t>934294980</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="C2284" s="20" t="n"/>
@@ -42370,7 +42485,7 @@
       <c r="E2290" s="20" t="n"/>
       <c r="F2290" s="20" t="n"/>
     </row>
-    <row r="2291" ht="20" customHeight="1">
+    <row r="2291" ht="45" customHeight="1">
       <c r="A2291" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -42378,7 +42493,7 @@
       </c>
       <c r="B2291" s="19" t="inlineStr">
         <is>
-          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
+          <t>Under call LIFE-2022-CET, topic LIFE-2022-CET-DH, what is meant by "district heating"?</t>
         </is>
       </c>
       <c r="C2291" s="20" t="n"/>
@@ -42422,7 +42537,7 @@
       </c>
       <c r="B2294" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/19895</t>
         </is>
       </c>
       <c r="C2294" s="20" t="n"/>
@@ -42433,7 +42548,7 @@
     <row r="2296" ht="30" customHeight="1">
       <c r="A2296" s="16" t="inlineStr">
         <is>
-          <t>FICHA 154: 925388828</t>
+          <t>FICHA 154: 934294980</t>
         </is>
       </c>
       <c r="B2296" s="17" t="n"/>
@@ -42466,7 +42581,7 @@
       </c>
       <c r="B2298" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C2298" s="20" t="n"/>
@@ -42482,7 +42597,7 @@
       </c>
       <c r="B2299" s="19" t="inlineStr">
         <is>
-          <t>925388828</t>
+          <t>934294980</t>
         </is>
       </c>
       <c r="C2299" s="20" t="n"/>
@@ -42582,7 +42697,7 @@
       </c>
       <c r="B2306" s="19" t="inlineStr">
         <is>
-          <t>THOMSON POWER EUROPE LTD</t>
+          <t>SCHIAFFINI TRAVEL SOCIETA' PER AZIONI</t>
         </is>
       </c>
       <c r="C2306" s="20" t="n"/>
@@ -42626,7 +42741,7 @@
       </c>
       <c r="B2309" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/934294980</t>
         </is>
       </c>
       <c r="C2309" s="20" t="n"/>
@@ -42637,7 +42752,7 @@
     <row r="2311" ht="30" customHeight="1">
       <c r="A2311" s="16" t="inlineStr">
         <is>
-          <t>FICHA 155: 876983694</t>
+          <t>FICHA 155: 925388828</t>
         </is>
       </c>
       <c r="B2311" s="17" t="n"/>
@@ -42670,7 +42785,7 @@
       </c>
       <c r="B2313" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C2313" s="20" t="n"/>
@@ -42686,7 +42801,7 @@
       </c>
       <c r="B2314" s="19" t="inlineStr">
         <is>
-          <t>876983694</t>
+          <t>925388828</t>
         </is>
       </c>
       <c r="C2314" s="20" t="n"/>
@@ -42786,7 +42901,7 @@
       </c>
       <c r="B2321" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
+          <t>THOMSON POWER EUROPE LTD</t>
         </is>
       </c>
       <c r="C2321" s="20" t="n"/>
@@ -42830,7 +42945,7 @@
       </c>
       <c r="B2324" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/876983694</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/925388828</t>
         </is>
       </c>
       <c r="C2324" s="20" t="n"/>
@@ -42841,7 +42956,7 @@
     <row r="2326" ht="30" customHeight="1">
       <c r="A2326" s="16" t="inlineStr">
         <is>
-          <t>FICHA 156: 17917</t>
+          <t>FICHA 156: 876983694</t>
         </is>
       </c>
       <c r="B2326" s="17" t="n"/>
@@ -42866,7 +42981,7 @@
       <c r="E2327" s="20" t="n"/>
       <c r="F2327" s="20" t="n"/>
     </row>
-    <row r="2328" ht="45" customHeight="1">
+    <row r="2328" ht="20" customHeight="1">
       <c r="A2328" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -42874,7 +42989,7 @@
       </c>
       <c r="B2328" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="C2328" s="20" t="n"/>
@@ -42890,7 +43005,7 @@
       </c>
       <c r="B2329" s="19" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>876983694</t>
         </is>
       </c>
       <c r="C2329" s="20" t="n"/>
@@ -42982,7 +43097,7 @@
       <c r="E2335" s="20" t="n"/>
       <c r="F2335" s="20" t="n"/>
     </row>
-    <row r="2336" ht="45" customHeight="1">
+    <row r="2336" ht="20" customHeight="1">
       <c r="A2336" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -42990,7 +43105,7 @@
       </c>
       <c r="B2336" s="19" t="inlineStr">
         <is>
-          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
+          <t>KARSAN OTOMOTIV SANAYII VE TICARET A.S.</t>
         </is>
       </c>
       <c r="C2336" s="20" t="n"/>
@@ -43034,7 +43149,7 @@
       </c>
       <c r="B2339" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17917</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/876983694</t>
         </is>
       </c>
       <c r="C2339" s="20" t="n"/>
@@ -43045,7 +43160,7 @@
     <row r="2341" ht="30" customHeight="1">
       <c r="A2341" s="16" t="inlineStr">
         <is>
-          <t>FICHA 157: 935134321</t>
+          <t>FICHA 157: 17917</t>
         </is>
       </c>
       <c r="B2341" s="17" t="n"/>
@@ -43070,7 +43185,7 @@
       <c r="E2342" s="20" t="n"/>
       <c r="F2342" s="20" t="n"/>
     </row>
-    <row r="2343" ht="20" customHeight="1">
+    <row r="2343" ht="45" customHeight="1">
       <c r="A2343" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -43078,7 +43193,7 @@
       </c>
       <c r="B2343" s="19" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="C2343" s="20" t="n"/>
@@ -43094,7 +43209,7 @@
       </c>
       <c r="B2344" s="19" t="inlineStr">
         <is>
-          <t>935134321</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="C2344" s="20" t="n"/>
@@ -43186,7 +43301,7 @@
       <c r="E2350" s="20" t="n"/>
       <c r="F2350" s="20" t="n"/>
     </row>
-    <row r="2351" ht="20" customHeight="1">
+    <row r="2351" ht="45" customHeight="1">
       <c r="A2351" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -43194,7 +43309,7 @@
       </c>
       <c r="B2351" s="19" t="inlineStr">
         <is>
-          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
+          <t>AFIF – Is the cost of a new medium voltage electricity lines (20kV) eligible, if necessary to increase power capacity at a public transport bus depot for supplying recharging points? Even if the infrastructure remains property of the DSO?</t>
         </is>
       </c>
       <c r="C2351" s="20" t="n"/>
@@ -43238,7 +43353,7 @@
       </c>
       <c r="B2354" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/935134321</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/17917</t>
         </is>
       </c>
       <c r="C2354" s="20" t="n"/>
@@ -43249,7 +43364,7 @@
     <row r="2356" ht="30" customHeight="1">
       <c r="A2356" s="16" t="inlineStr">
         <is>
-          <t>FICHA 158: 883154834</t>
+          <t>FICHA 158: 935134321</t>
         </is>
       </c>
       <c r="B2356" s="17" t="n"/>
@@ -43282,7 +43397,7 @@
       </c>
       <c r="B2358" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="C2358" s="20" t="n"/>
@@ -43298,7 +43413,7 @@
       </c>
       <c r="B2359" s="19" t="inlineStr">
         <is>
-          <t>883154834</t>
+          <t>935134321</t>
         </is>
       </c>
       <c r="C2359" s="20" t="n"/>
@@ -43398,7 +43513,7 @@
       </c>
       <c r="B2366" s="19" t="inlineStr">
         <is>
-          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
+          <t>RIGAS PASVALDIBAS SABIEDRIBA AR IEROBEZOTU ATBILDIBU RIGAS SATIKSME</t>
         </is>
       </c>
       <c r="C2366" s="20" t="n"/>
@@ -43442,7 +43557,7 @@
       </c>
       <c r="B2369" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/883154834</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/935134321</t>
         </is>
       </c>
       <c r="C2369" s="20" t="n"/>
@@ -43453,7 +43568,7 @@
     <row r="2371" ht="30" customHeight="1">
       <c r="A2371" s="16" t="inlineStr">
         <is>
-          <t>FICHA 159: 93508</t>
+          <t>FICHA 159: 883154834</t>
         </is>
       </c>
       <c r="B2371" s="17" t="n"/>
@@ -43478,7 +43593,7 @@
       <c r="E2372" s="20" t="n"/>
       <c r="F2372" s="20" t="n"/>
     </row>
-    <row r="2373" ht="45" customHeight="1">
+    <row r="2373" ht="20" customHeight="1">
       <c r="A2373" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -43486,7 +43601,7 @@
       </c>
       <c r="B2373" s="19" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="C2373" s="20" t="n"/>
@@ -43502,7 +43617,7 @@
       </c>
       <c r="B2374" s="19" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>883154834</t>
         </is>
       </c>
       <c r="C2374" s="20" t="n"/>
@@ -43594,7 +43709,7 @@
       <c r="E2380" s="20" t="n"/>
       <c r="F2380" s="20" t="n"/>
     </row>
-    <row r="2381" ht="45" customHeight="1">
+    <row r="2381" ht="20" customHeight="1">
       <c r="A2381" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -43602,7 +43717,7 @@
       </c>
       <c r="B2381" s="19" t="inlineStr">
         <is>
-          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
+          <t>KARSAN OTOMOTIV SANAYI TICARET A.S.</t>
         </is>
       </c>
       <c r="C2381" s="20" t="n"/>
@@ -43646,7 +43761,7 @@
       </c>
       <c r="B2384" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/93508</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/883154834</t>
         </is>
       </c>
       <c r="C2384" s="20" t="n"/>
@@ -43657,7 +43772,7 @@
     <row r="2386" ht="30" customHeight="1">
       <c r="A2386" s="16" t="inlineStr">
         <is>
-          <t>FICHA 160: 950910110</t>
+          <t>FICHA 160: 93508</t>
         </is>
       </c>
       <c r="B2386" s="17" t="n"/>
@@ -43682,7 +43797,7 @@
       <c r="E2387" s="20" t="n"/>
       <c r="F2387" s="20" t="n"/>
     </row>
-    <row r="2388" ht="20" customHeight="1">
+    <row r="2388" ht="45" customHeight="1">
       <c r="A2388" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -43690,7 +43805,7 @@
       </c>
       <c r="B2388" s="19" t="inlineStr">
         <is>
-          <t>CURA TERRAE WATER LIMITED</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="C2388" s="20" t="n"/>
@@ -43706,7 +43821,7 @@
       </c>
       <c r="B2389" s="19" t="inlineStr">
         <is>
-          <t>950910110</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="C2389" s="20" t="n"/>
@@ -43798,7 +43913,7 @@
       <c r="E2395" s="20" t="n"/>
       <c r="F2395" s="20" t="n"/>
     </row>
-    <row r="2396" ht="20" customHeight="1">
+    <row r="2396" ht="45" customHeight="1">
       <c r="A2396" s="18" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -43806,7 +43921,7 @@
       </c>
       <c r="B2396" s="19" t="inlineStr">
         <is>
-          <t>CURA TERRAE WATER LIMITED</t>
+          <t>1. Could the Contracting Authority clarify the scope of the term “environmental sector” under the technical capacity criterion and confirm whether projects related to water supply, sewerage, water and wastewater treatment, stormwater drainage, flood protection, climate resilience, water resources management, dams/reservoirs, and coastal protection</t>
         </is>
       </c>
       <c r="C2396" s="20" t="n"/>
@@ -43850,7 +43965,7 @@
       </c>
       <c r="B2399" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/950910110</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/93508</t>
         </is>
       </c>
       <c r="C2399" s="20" t="n"/>
@@ -43861,7 +43976,7 @@
     <row r="2401" ht="30" customHeight="1">
       <c r="A2401" s="16" t="inlineStr">
         <is>
-          <t>FICHA 161: 999515355</t>
+          <t>FICHA 161: 950910110</t>
         </is>
       </c>
       <c r="B2401" s="17" t="n"/>
@@ -43894,7 +44009,7 @@
       </c>
       <c r="B2403" s="19" t="inlineStr">
         <is>
-          <t>TRUSTEES OF PRINCETON UNIVERSITY</t>
+          <t>CURA TERRAE WATER LIMITED</t>
         </is>
       </c>
       <c r="C2403" s="20" t="n"/>
@@ -43910,7 +44025,7 @@
       </c>
       <c r="B2404" s="19" t="inlineStr">
         <is>
-          <t>999515355</t>
+          <t>950910110</t>
         </is>
       </c>
       <c r="C2404" s="20" t="n"/>
@@ -44010,7 +44125,7 @@
       </c>
       <c r="B2411" s="19" t="inlineStr">
         <is>
-          <t>TRUSTEES OF PRINCETON UNIVERSITY</t>
+          <t>CURA TERRAE WATER LIMITED</t>
         </is>
       </c>
       <c r="C2411" s="20" t="n"/>
@@ -44054,7 +44169,7 @@
       </c>
       <c r="B2414" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/999515355</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/950910110</t>
         </is>
       </c>
       <c r="C2414" s="20" t="n"/>
@@ -44065,7 +44180,7 @@
     <row r="2416" ht="30" customHeight="1">
       <c r="A2416" s="16" t="inlineStr">
         <is>
-          <t>FICHA 162: 968942119</t>
+          <t>FICHA 162: 999515355</t>
         </is>
       </c>
       <c r="B2416" s="17" t="n"/>
@@ -44098,7 +44213,7 @@
       </c>
       <c r="B2418" s="19" t="inlineStr">
         <is>
-          <t>INFO-LOGICA OOD</t>
+          <t>TRUSTEES OF PRINCETON UNIVERSITY</t>
         </is>
       </c>
       <c r="C2418" s="20" t="n"/>
@@ -44114,7 +44229,7 @@
       </c>
       <c r="B2419" s="19" t="inlineStr">
         <is>
-          <t>968942119</t>
+          <t>999515355</t>
         </is>
       </c>
       <c r="C2419" s="20" t="n"/>
@@ -44214,7 +44329,7 @@
       </c>
       <c r="B2426" s="19" t="inlineStr">
         <is>
-          <t>INFO-LOGICA OOD</t>
+          <t>TRUSTEES OF PRINCETON UNIVERSITY</t>
         </is>
       </c>
       <c r="C2426" s="20" t="n"/>
@@ -44258,7 +44373,7 @@
       </c>
       <c r="B2429" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/968942119</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/999515355</t>
         </is>
       </c>
       <c r="C2429" s="20" t="n"/>
@@ -44269,7 +44384,7 @@
     <row r="2431" ht="30" customHeight="1">
       <c r="A2431" s="16" t="inlineStr">
         <is>
-          <t>FICHA 163: 913143063</t>
+          <t>FICHA 163: 968942119</t>
         </is>
       </c>
       <c r="B2431" s="17" t="n"/>
@@ -44302,7 +44417,7 @@
       </c>
       <c r="B2433" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA BELOVO</t>
+          <t>INFO-LOGICA OOD</t>
         </is>
       </c>
       <c r="C2433" s="20" t="n"/>
@@ -44318,7 +44433,7 @@
       </c>
       <c r="B2434" s="19" t="inlineStr">
         <is>
-          <t>913143063</t>
+          <t>968942119</t>
         </is>
       </c>
       <c r="C2434" s="20" t="n"/>
@@ -44418,7 +44533,7 @@
       </c>
       <c r="B2441" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA BELOVO</t>
+          <t>INFO-LOGICA OOD</t>
         </is>
       </c>
       <c r="C2441" s="20" t="n"/>
@@ -44462,7 +44577,7 @@
       </c>
       <c r="B2444" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/913143063</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/968942119</t>
         </is>
       </c>
       <c r="C2444" s="20" t="n"/>
@@ -44473,7 +44588,7 @@
     <row r="2446" ht="30" customHeight="1">
       <c r="A2446" s="16" t="inlineStr">
         <is>
-          <t>FICHA 164: 947753536</t>
+          <t>FICHA 164: 913143063</t>
         </is>
       </c>
       <c r="B2446" s="17" t="n"/>
@@ -44506,7 +44621,7 @@
       </c>
       <c r="B2448" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA KAZANLAK</t>
+          <t>OBSHTINA BELOVO</t>
         </is>
       </c>
       <c r="C2448" s="20" t="n"/>
@@ -44522,7 +44637,7 @@
       </c>
       <c r="B2449" s="19" t="inlineStr">
         <is>
-          <t>947753536</t>
+          <t>913143063</t>
         </is>
       </c>
       <c r="C2449" s="20" t="n"/>
@@ -44622,7 +44737,7 @@
       </c>
       <c r="B2456" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA KAZANLAK</t>
+          <t>OBSHTINA BELOVO</t>
         </is>
       </c>
       <c r="C2456" s="20" t="n"/>
@@ -44666,7 +44781,7 @@
       </c>
       <c r="B2459" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/947753536</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/913143063</t>
         </is>
       </c>
       <c r="C2459" s="20" t="n"/>
@@ -44677,7 +44792,7 @@
     <row r="2461" ht="30" customHeight="1">
       <c r="A2461" s="16" t="inlineStr">
         <is>
-          <t>FICHA 165: 928211140</t>
+          <t>FICHA 165: 947753536</t>
         </is>
       </c>
       <c r="B2461" s="17" t="n"/>
@@ -44710,7 +44825,7 @@
       </c>
       <c r="B2463" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA KAZANLAK</t>
         </is>
       </c>
       <c r="C2463" s="20" t="n"/>
@@ -44726,7 +44841,7 @@
       </c>
       <c r="B2464" s="19" t="inlineStr">
         <is>
-          <t>928211140</t>
+          <t>947753536</t>
         </is>
       </c>
       <c r="C2464" s="20" t="n"/>
@@ -44826,7 +44941,7 @@
       </c>
       <c r="B2471" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA PARVOMAY</t>
+          <t>OBSHTINA KAZANLAK</t>
         </is>
       </c>
       <c r="C2471" s="20" t="n"/>
@@ -44870,7 +44985,7 @@
       </c>
       <c r="B2474" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928211140</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/947753536</t>
         </is>
       </c>
       <c r="C2474" s="20" t="n"/>
@@ -44881,7 +44996,7 @@
     <row r="2476" ht="30" customHeight="1">
       <c r="A2476" s="16" t="inlineStr">
         <is>
-          <t>FICHA 166: 928057492</t>
+          <t>FICHA 166: 928211140</t>
         </is>
       </c>
       <c r="B2476" s="17" t="n"/>
@@ -44914,7 +45029,7 @@
       </c>
       <c r="B2478" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="C2478" s="20" t="n"/>
@@ -44930,7 +45045,7 @@
       </c>
       <c r="B2479" s="19" t="inlineStr">
         <is>
-          <t>928057492</t>
+          <t>928211140</t>
         </is>
       </c>
       <c r="C2479" s="20" t="n"/>
@@ -45030,7 +45145,7 @@
       </c>
       <c r="B2486" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA RODOPI</t>
+          <t>OBSHTINA PARVOMAY</t>
         </is>
       </c>
       <c r="C2486" s="20" t="n"/>
@@ -45074,7 +45189,7 @@
       </c>
       <c r="B2489" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928057492</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928211140</t>
         </is>
       </c>
       <c r="C2489" s="20" t="n"/>
@@ -45085,7 +45200,7 @@
     <row r="2491" ht="30" customHeight="1">
       <c r="A2491" s="16" t="inlineStr">
         <is>
-          <t>FICHA 167: 926227393</t>
+          <t>FICHA 167: 928057492</t>
         </is>
       </c>
       <c r="B2491" s="17" t="n"/>
@@ -45118,7 +45233,7 @@
       </c>
       <c r="B2493" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="C2493" s="20" t="n"/>
@@ -45134,7 +45249,7 @@
       </c>
       <c r="B2494" s="19" t="inlineStr">
         <is>
-          <t>926227393</t>
+          <t>928057492</t>
         </is>
       </c>
       <c r="C2494" s="20" t="n"/>
@@ -45234,7 +45349,7 @@
       </c>
       <c r="B2501" s="19" t="inlineStr">
         <is>
-          <t>OBSHTINA SVILENGRAD</t>
+          <t>OBSHTINA RODOPI</t>
         </is>
       </c>
       <c r="C2501" s="20" t="n"/>
@@ -45278,7 +45393,7 @@
       </c>
       <c r="B2504" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/926227393</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/928057492</t>
         </is>
       </c>
       <c r="C2504" s="20" t="n"/>
@@ -45289,7 +45404,7 @@
     <row r="2506" ht="30" customHeight="1">
       <c r="A2506" s="16" t="inlineStr">
         <is>
-          <t>FICHA 168: NA</t>
+          <t>FICHA 168: 926227393</t>
         </is>
       </c>
       <c r="B2506" s="17" t="n"/>
@@ -45322,7 +45437,7 @@
       </c>
       <c r="B2508" s="19" t="inlineStr">
         <is>
-          <t>Prof. Dr. Jorge Isidoro</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="C2508" s="20" t="n"/>
@@ -45338,7 +45453,7 @@
       </c>
       <c r="B2509" s="19" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>926227393</t>
         </is>
       </c>
       <c r="C2509" s="20" t="n"/>
@@ -45438,7 +45553,7 @@
       </c>
       <c r="B2516" s="19" t="inlineStr">
         <is>
-          <t>Prof. Dr. Jorge Isidoro</t>
+          <t>OBSHTINA SVILENGRAD</t>
         </is>
       </c>
       <c r="C2516" s="20" t="n"/>
@@ -45482,7 +45597,7 @@
       </c>
       <c r="B2519" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/926227393</t>
         </is>
       </c>
       <c r="C2519" s="20" t="n"/>
@@ -45697,7 +45812,7 @@
     <row r="2536" ht="30" customHeight="1">
       <c r="A2536" s="16" t="inlineStr">
         <is>
-          <t>FICHA 170: UCPM</t>
+          <t>FICHA 170: 877682967</t>
         </is>
       </c>
       <c r="B2536" s="17" t="n"/>
@@ -45730,7 +45845,7 @@
       </c>
       <c r="B2538" s="19" t="inlineStr">
         <is>
-          <t>RIsk WATER flooding  EXercise</t>
+          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
         </is>
       </c>
       <c r="C2538" s="20" t="n"/>
@@ -45746,7 +45861,7 @@
       </c>
       <c r="B2539" s="19" t="inlineStr">
         <is>
-          <t>UCPM</t>
+          <t>877682967</t>
         </is>
       </c>
       <c r="C2539" s="20" t="n"/>
@@ -45832,11 +45947,7 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2545" s="19" t="inlineStr">
-        <is>
-          <t>UCPM-2017-EX-AG</t>
-        </is>
-      </c>
+      <c r="B2545" s="19" t="inlineStr"/>
       <c r="C2545" s="20" t="n"/>
       <c r="D2545" s="20" t="n"/>
       <c r="E2545" s="20" t="n"/>
@@ -45850,7 +45961,7 @@
       </c>
       <c r="B2546" s="19" t="inlineStr">
         <is>
-          <t>RIsk WATER flooding EXercise</t>
+          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
         </is>
       </c>
       <c r="C2546" s="20" t="n"/>
@@ -45894,7 +46005,7 @@
       </c>
       <c r="B2549" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/UCPM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/877682967</t>
         </is>
       </c>
       <c r="C2549" s="20" t="n"/>
@@ -45905,7 +46016,7 @@
     <row r="2551" ht="30" customHeight="1">
       <c r="A2551" s="16" t="inlineStr">
         <is>
-          <t>FICHA 171: 877682967</t>
+          <t>FICHA 171: UCPM</t>
         </is>
       </c>
       <c r="B2551" s="17" t="n"/>
@@ -45938,7 +46049,7 @@
       </c>
       <c r="B2553" s="19" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
+          <t>RIsk WATER flooding  EXercise</t>
         </is>
       </c>
       <c r="C2553" s="20" t="n"/>
@@ -45954,7 +46065,7 @@
       </c>
       <c r="B2554" s="19" t="inlineStr">
         <is>
-          <t>877682967</t>
+          <t>UCPM</t>
         </is>
       </c>
       <c r="C2554" s="20" t="n"/>
@@ -46040,7 +46151,11 @@
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B2560" s="19" t="inlineStr"/>
+      <c r="B2560" s="19" t="inlineStr">
+        <is>
+          <t>UCPM-2017-EX-AG</t>
+        </is>
+      </c>
       <c r="C2560" s="20" t="n"/>
       <c r="D2560" s="20" t="n"/>
       <c r="E2560" s="20" t="n"/>
@@ -46054,7 +46169,7 @@
       </c>
       <c r="B2561" s="19" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN CENTRO DE INVESTIGACIÓN EN GESTIÓN INTEGRAL DE RIESGOS</t>
+          <t>RIsk WATER flooding EXercise</t>
         </is>
       </c>
       <c r="C2561" s="20" t="n"/>
@@ -46098,7 +46213,7 @@
       </c>
       <c r="B2564" s="22" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/877682967</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/UCPM</t>
         </is>
       </c>
       <c r="C2564" s="20" t="n"/>
@@ -51629,7 +51744,7 @@
     <row r="2971" ht="30" customHeight="1">
       <c r="A2971" s="16" t="inlineStr">
         <is>
-          <t>FICHA 199: EUS-18844</t>
+          <t>FICHA 199: EUS-09468</t>
         </is>
       </c>
       <c r="B2971" s="17" t="n"/>
@@ -51654,7 +51769,7 @@
       <c r="E2972" s="20" t="n"/>
       <c r="F2972" s="20" t="n"/>
     </row>
-    <row r="2973" ht="45" customHeight="1">
+    <row r="2973" ht="20" customHeight="1">
       <c r="A2973" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -51662,8 +51777,7 @@
       </c>
       <c r="B2973" s="19" t="inlineStr">
         <is>
-          <t>Contratación del servicio de mantenimiento integral e inspección de las instalaciones térmicas en edificios e instalaciones 
-municipales del Ayuntamiento de Amorebieta-Etxano</t>
+          <t>trabajos de arreglo de cortinas en edificio ayuntamiento y dendaberri</t>
         </is>
       </c>
       <c r="C2973" s="20" t="n"/>
@@ -51679,7 +51793,7 @@
       </c>
       <c r="B2974" s="19" t="inlineStr">
         <is>
-          <t>EUS-18844</t>
+          <t>EUS-09468</t>
         </is>
       </c>
       <c r="C2974" s="20" t="n"/>
@@ -51831,7 +51945,7 @@
       </c>
       <c r="B2984" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/contratacion-del-servicio-mantenimiento-integral-e-inspeccion-instalaciones-termicas-edificios-e-instalaciones-municipales-del-ayuntamiento-amorebieta-etxano/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/trabajos-arreglo-cortinas-edificio-ayuntamiento-y-dendaberri/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C2984" s="20" t="n"/>
@@ -51842,7 +51956,7 @@
     <row r="2986" ht="30" customHeight="1">
       <c r="A2986" s="16" t="inlineStr">
         <is>
-          <t>FICHA 200: EUS-01951</t>
+          <t>FICHA 200: EUS-84836</t>
         </is>
       </c>
       <c r="B2986" s="17" t="n"/>
@@ -51891,7 +52005,7 @@
       </c>
       <c r="B2989" s="19" t="inlineStr">
         <is>
-          <t>EUS-01951</t>
+          <t>EUS-84836</t>
         </is>
       </c>
       <c r="C2989" s="20" t="n"/>
@@ -52054,7 +52168,7 @@
     <row r="3001" ht="30" customHeight="1">
       <c r="A3001" s="16" t="inlineStr">
         <is>
-          <t>FICHA 201: EUS-56052</t>
+          <t>FICHA 201: EUS-98098</t>
         </is>
       </c>
       <c r="B3001" s="17" t="n"/>
@@ -52103,7 +52217,7 @@
       </c>
       <c r="B3004" s="19" t="inlineStr">
         <is>
-          <t>EUS-56052</t>
+          <t>EUS-98098</t>
         </is>
       </c>
       <c r="C3004" s="20" t="n"/>
@@ -52266,7 +52380,7 @@
     <row r="3016" ht="30" customHeight="1">
       <c r="A3016" s="16" t="inlineStr">
         <is>
-          <t>FICHA 202: EUS-50335</t>
+          <t>FICHA 202: EUS-28011</t>
         </is>
       </c>
       <c r="B3016" s="17" t="n"/>
@@ -52291,7 +52405,7 @@
       <c r="E3017" s="20" t="n"/>
       <c r="F3017" s="20" t="n"/>
     </row>
-    <row r="3018" ht="45" customHeight="1">
+    <row r="3018" ht="20" customHeight="1">
       <c r="A3018" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -52299,7 +52413,7 @@
       </c>
       <c r="B3018" s="19" t="inlineStr">
         <is>
-          <t>Asistencia técnica para la elaboración del Plan de Movilidad Sostenible de la Diputación Foral de Álava</t>
+          <t>modificiacion conductos climatizacion del rocodromo</t>
         </is>
       </c>
       <c r="C3018" s="20" t="n"/>
@@ -52315,7 +52429,7 @@
       </c>
       <c r="B3019" s="19" t="inlineStr">
         <is>
-          <t>EUS-50335</t>
+          <t>EUS-28011</t>
         </is>
       </c>
       <c r="C3019" s="20" t="n"/>
@@ -52467,7 +52581,7 @@
       </c>
       <c r="B3029" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/asistencia-tecnica-elaboracion-del-plan-movilidad-sostenible-diputacion-foral-alava/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/modificiacion-conductos-climatizacion-del-rocodromo/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3029" s="20" t="n"/>
@@ -52478,7 +52592,7 @@
     <row r="3031" ht="30" customHeight="1">
       <c r="A3031" s="16" t="inlineStr">
         <is>
-          <t>FICHA 203: EUS-95257</t>
+          <t>FICHA 203: EUS-81589</t>
         </is>
       </c>
       <c r="B3031" s="17" t="n"/>
@@ -52527,7 +52641,7 @@
       </c>
       <c r="B3034" s="19" t="inlineStr">
         <is>
-          <t>EUS-95257</t>
+          <t>EUS-81589</t>
         </is>
       </c>
       <c r="C3034" s="20" t="n"/>
@@ -52690,7 +52804,7 @@
     <row r="3046" ht="30" customHeight="1">
       <c r="A3046" s="16" t="inlineStr">
         <is>
-          <t>FICHA 204: EUS-13959</t>
+          <t>FICHA 204: EUS-29388</t>
         </is>
       </c>
       <c r="B3046" s="17" t="n"/>
@@ -52739,7 +52853,7 @@
       </c>
       <c r="B3049" s="19" t="inlineStr">
         <is>
-          <t>EUS-13959</t>
+          <t>EUS-29388</t>
         </is>
       </c>
       <c r="C3049" s="20" t="n"/>
@@ -52902,7 +53016,7 @@
     <row r="3061" ht="30" customHeight="1">
       <c r="A3061" s="16" t="inlineStr">
         <is>
-          <t>FICHA 205: EUS-94998</t>
+          <t>FICHA 205: EUS-00993</t>
         </is>
       </c>
       <c r="B3061" s="17" t="n"/>
@@ -52951,7 +53065,7 @@
       </c>
       <c r="B3064" s="19" t="inlineStr">
         <is>
-          <t>EUS-94998</t>
+          <t>EUS-00993</t>
         </is>
       </c>
       <c r="C3064" s="20" t="n"/>
@@ -53114,7 +53228,7 @@
     <row r="3076" ht="30" customHeight="1">
       <c r="A3076" s="16" t="inlineStr">
         <is>
-          <t>FICHA 206: EUS-92809</t>
+          <t>FICHA 206: EUS-89388</t>
         </is>
       </c>
       <c r="B3076" s="17" t="n"/>
@@ -53163,7 +53277,7 @@
       </c>
       <c r="B3079" s="19" t="inlineStr">
         <is>
-          <t>EUS-92809</t>
+          <t>EUS-89388</t>
         </is>
       </c>
       <c r="C3079" s="20" t="n"/>
@@ -53326,7 +53440,7 @@
     <row r="3091" ht="30" customHeight="1">
       <c r="A3091" s="16" t="inlineStr">
         <is>
-          <t>FICHA 207: EUS-29254</t>
+          <t>FICHA 207: EUS-81057</t>
         </is>
       </c>
       <c r="B3091" s="17" t="n"/>
@@ -53375,7 +53489,7 @@
       </c>
       <c r="B3094" s="19" t="inlineStr">
         <is>
-          <t>EUS-29254</t>
+          <t>EUS-81057</t>
         </is>
       </c>
       <c r="C3094" s="20" t="n"/>
@@ -53538,7 +53652,7 @@
     <row r="3106" ht="30" customHeight="1">
       <c r="A3106" s="16" t="inlineStr">
         <is>
-          <t>FICHA 208: EUS-17441</t>
+          <t>FICHA 208: EUS-73884</t>
         </is>
       </c>
       <c r="B3106" s="17" t="n"/>
@@ -53587,7 +53701,7 @@
       </c>
       <c r="B3109" s="19" t="inlineStr">
         <is>
-          <t>EUS-17441</t>
+          <t>EUS-73884</t>
         </is>
       </c>
       <c r="C3109" s="20" t="n"/>
@@ -53750,7 +53864,7 @@
     <row r="3121" ht="30" customHeight="1">
       <c r="A3121" s="16" t="inlineStr">
         <is>
-          <t>FICHA 209: EUS-52186</t>
+          <t>FICHA 209: EUS-69744</t>
         </is>
       </c>
       <c r="B3121" s="17" t="n"/>
@@ -53775,7 +53889,7 @@
       <c r="E3122" s="20" t="n"/>
       <c r="F3122" s="20" t="n"/>
     </row>
-    <row r="3123" ht="20" customHeight="1">
+    <row r="3123" ht="45" customHeight="1">
       <c r="A3123" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -53783,7 +53897,7 @@
       </c>
       <c r="B3123" s="19" t="inlineStr">
         <is>
-          <t>Servicio de atención y gestión integral de la vivienda Comunitaria de Laguardia</t>
+          <t>trabajos de instalación eléctrica del alumbrado en zonas de juegos y frontones de la ikastola egape</t>
         </is>
       </c>
       <c r="C3123" s="20" t="n"/>
@@ -53799,7 +53913,7 @@
       </c>
       <c r="B3124" s="19" t="inlineStr">
         <is>
-          <t>EUS-52186</t>
+          <t>EUS-69744</t>
         </is>
       </c>
       <c r="C3124" s="20" t="n"/>
@@ -53951,7 +54065,7 @@
       </c>
       <c r="B3134" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/servicio-atencion-y-gestion-integral-vivienda-comunitaria-laguardia/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/trabajos-instalacion-electrica-del-alumbrado-zonas-juegos-y-frontones-ikastola-egape/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3134" s="20" t="n"/>
@@ -53962,7 +54076,7 @@
     <row r="3136" ht="30" customHeight="1">
       <c r="A3136" s="16" t="inlineStr">
         <is>
-          <t>FICHA 210: EUS-87459</t>
+          <t>FICHA 210: EUS-56877</t>
         </is>
       </c>
       <c r="B3136" s="17" t="n"/>
@@ -53987,7 +54101,7 @@
       <c r="E3137" s="20" t="n"/>
       <c r="F3137" s="20" t="n"/>
     </row>
-    <row r="3138" ht="20" customHeight="1">
+    <row r="3138" ht="45" customHeight="1">
       <c r="A3138" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -53995,7 +54109,7 @@
       </c>
       <c r="B3138" s="19" t="inlineStr">
         <is>
-          <t>Mejora del alumbrado público Fase 3</t>
+          <t>trabajos de obra civil para instalar dos nuevos puntos del alumbrado en ergoien industrialdea</t>
         </is>
       </c>
       <c r="C3138" s="20" t="n"/>
@@ -54011,7 +54125,7 @@
       </c>
       <c r="B3139" s="19" t="inlineStr">
         <is>
-          <t>EUS-87459</t>
+          <t>EUS-56877</t>
         </is>
       </c>
       <c r="C3139" s="20" t="n"/>
@@ -54163,7 +54277,7 @@
       </c>
       <c r="B3149" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/mejora-del-alumbrado-publico-fase-3/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/trabajos-obra-civil-instalar-dos-nuevos-puntos-del-alumbrado-ergoien-industrialdea/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3149" s="20" t="n"/>
@@ -54174,7 +54288,7 @@
     <row r="3151" ht="30" customHeight="1">
       <c r="A3151" s="16" t="inlineStr">
         <is>
-          <t>FICHA 211: EUS-84294</t>
+          <t>FICHA 211: EUS-30348</t>
         </is>
       </c>
       <c r="B3151" s="17" t="n"/>
@@ -54207,7 +54321,7 @@
       </c>
       <c r="B3153" s="19" t="inlineStr">
         <is>
-          <t>Redacción de proyecto de ejecución para la instalación de una cubierta en Urizar</t>
+          <t>trabajos de impermeabilización zona baja de los foso de los 2 ascensores en paso bajo vías apeadero del tren</t>
         </is>
       </c>
       <c r="C3153" s="20" t="n"/>
@@ -54223,7 +54337,7 @@
       </c>
       <c r="B3154" s="19" t="inlineStr">
         <is>
-          <t>EUS-84294</t>
+          <t>EUS-30348</t>
         </is>
       </c>
       <c r="C3154" s="20" t="n"/>
@@ -54375,7 +54489,7 @@
       </c>
       <c r="B3164" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/redaccion-proyecto-ejecucion-instalacion-cubierta-urizar/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/trabajos-impermeabilizacion-zona-baja-foso-2-ascensores-paso-vias-apeadero-del-tren/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3164" s="20" t="n"/>
@@ -54386,7 +54500,7 @@
     <row r="3166" ht="30" customHeight="1">
       <c r="A3166" s="16" t="inlineStr">
         <is>
-          <t>FICHA 212: EUS-19207</t>
+          <t>FICHA 212: EUS-01123</t>
         </is>
       </c>
       <c r="B3166" s="17" t="n"/>
@@ -54411,7 +54525,7 @@
       <c r="E3167" s="20" t="n"/>
       <c r="F3167" s="20" t="n"/>
     </row>
-    <row r="3168" ht="20" customHeight="1">
+    <row r="3168" ht="45" customHeight="1">
       <c r="A3168" s="18" t="inlineStr">
         <is>
           <t>Titulo</t>
@@ -54419,7 +54533,7 @@
       </c>
       <c r="B3168" s="19" t="inlineStr">
         <is>
-          <t>Estudio de detalle cubierta</t>
+          <t>trabajos realización obra civil para renovación alumbrado público en la plaza txoritagain 03</t>
         </is>
       </c>
       <c r="C3168" s="20" t="n"/>
@@ -54435,7 +54549,7 @@
       </c>
       <c r="B3169" s="19" t="inlineStr">
         <is>
-          <t>EUS-19207</t>
+          <t>EUS-01123</t>
         </is>
       </c>
       <c r="C3169" s="20" t="n"/>
@@ -54587,7 +54701,7 @@
       </c>
       <c r="B3179" s="22" t="inlineStr">
         <is>
-          <t>https://www.euskadi.eus/anuncio_contratacion/estudio-detalle-cubierta/web01-tramite/es/</t>
+          <t>https://www.euskadi.eus/anuncio_contratacion/trabajos-realizacion-obra-civil-renovacion-alumbrado-publico-plaza-txoritagain-03/web01-tramite/es/</t>
         </is>
       </c>
       <c r="C3179" s="20" t="n"/>
@@ -54595,8 +54709,432 @@
       <c r="E3179" s="20" t="n"/>
       <c r="F3179" s="20" t="n"/>
     </row>
+    <row r="3181" ht="30" customHeight="1">
+      <c r="A3181" s="16" t="inlineStr">
+        <is>
+          <t>FICHA 213: EUS-15185</t>
+        </is>
+      </c>
+      <c r="B3181" s="17" t="n"/>
+      <c r="C3181" s="17" t="n"/>
+      <c r="D3181" s="17" t="n"/>
+      <c r="E3181" s="17" t="n"/>
+      <c r="F3181" s="17" t="n"/>
+    </row>
+    <row r="3182" ht="20" customHeight="1">
+      <c r="A3182" s="18" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B3182" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+      <c r="C3182" s="20" t="n"/>
+      <c r="D3182" s="20" t="n"/>
+      <c r="E3182" s="20" t="n"/>
+      <c r="F3182" s="20" t="n"/>
+    </row>
+    <row r="3183" ht="20" customHeight="1">
+      <c r="A3183" s="18" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B3183" s="19" t="inlineStr">
+        <is>
+          <t>10 packs de 24, agua 0,5l</t>
+        </is>
+      </c>
+      <c r="C3183" s="20" t="n"/>
+      <c r="D3183" s="20" t="n"/>
+      <c r="E3183" s="20" t="n"/>
+      <c r="F3183" s="20" t="n"/>
+    </row>
+    <row r="3184" ht="20" customHeight="1">
+      <c r="A3184" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3184" s="19" t="inlineStr">
+        <is>
+          <t>EUS-15185</t>
+        </is>
+      </c>
+      <c r="C3184" s="20" t="n"/>
+      <c r="D3184" s="20" t="n"/>
+      <c r="E3184" s="20" t="n"/>
+      <c r="F3184" s="20" t="n"/>
+    </row>
+    <row r="3185" ht="20" customHeight="1">
+      <c r="A3185" s="18" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B3185" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="C3185" s="20" t="n"/>
+      <c r="D3185" s="20" t="n"/>
+      <c r="E3185" s="20" t="n"/>
+      <c r="F3185" s="20" t="n"/>
+    </row>
+    <row r="3186" ht="20" customHeight="1">
+      <c r="A3186" s="18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B3186" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C3186" s="20" t="n"/>
+      <c r="D3186" s="20" t="n"/>
+      <c r="E3186" s="20" t="n"/>
+      <c r="F3186" s="20" t="n"/>
+    </row>
+    <row r="3187" ht="20" customHeight="1">
+      <c r="A3187" s="18" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B3187" s="19" t="inlineStr"/>
+      <c r="C3187" s="20" t="n"/>
+      <c r="D3187" s="20" t="n"/>
+      <c r="E3187" s="20" t="n"/>
+      <c r="F3187" s="20" t="n"/>
+    </row>
+    <row r="3188" ht="20" customHeight="1">
+      <c r="A3188" s="18" t="inlineStr">
+        <is>
+          <t>Presupuesto (EUR)</t>
+        </is>
+      </c>
+      <c r="B3188" s="19" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="C3188" s="20" t="n"/>
+      <c r="D3188" s="20" t="n"/>
+      <c r="E3188" s="20" t="n"/>
+      <c r="F3188" s="20" t="n"/>
+    </row>
+    <row r="3189" ht="20" customHeight="1">
+      <c r="A3189" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de Accion</t>
+        </is>
+      </c>
+      <c r="B3189" s="19" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="C3189" s="20" t="n"/>
+      <c r="D3189" s="20" t="n"/>
+      <c r="E3189" s="20" t="n"/>
+      <c r="F3189" s="20" t="n"/>
+    </row>
+    <row r="3190" ht="20" customHeight="1">
+      <c r="A3190" s="18" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B3190" s="19" t="inlineStr"/>
+      <c r="C3190" s="20" t="n"/>
+      <c r="D3190" s="20" t="n"/>
+      <c r="E3190" s="20" t="n"/>
+      <c r="F3190" s="20" t="n"/>
+    </row>
+    <row r="3191" ht="20" customHeight="1">
+      <c r="A3191" s="18" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="B3191" s="19" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="C3191" s="20" t="n"/>
+      <c r="D3191" s="20" t="n"/>
+      <c r="E3191" s="20" t="n"/>
+      <c r="F3191" s="20" t="n"/>
+    </row>
+    <row r="3192" ht="20" customHeight="1">
+      <c r="A3192" s="18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B3192" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="C3192" s="20" t="n"/>
+      <c r="D3192" s="20" t="n"/>
+      <c r="E3192" s="20" t="n"/>
+      <c r="F3192" s="20" t="n"/>
+    </row>
+    <row r="3193" ht="20" customHeight="1">
+      <c r="A3193" s="18" t="inlineStr">
+        <is>
+          <t>Relevancia Bilbao</t>
+        </is>
+      </c>
+      <c r="B3193" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
+        </is>
+      </c>
+      <c r="C3193" s="20" t="n"/>
+      <c r="D3193" s="20" t="n"/>
+      <c r="E3193" s="20" t="n"/>
+      <c r="F3193" s="20" t="n"/>
+    </row>
+    <row r="3194" ht="45" customHeight="1">
+      <c r="A3194" s="18" t="inlineStr">
+        <is>
+          <t>Enlace al portal</t>
+        </is>
+      </c>
+      <c r="B3194" s="22" t="inlineStr">
+        <is>
+          <t>https://www.euskadi.eus/anuncio_contratacion/10-packs-24-agua-0-5l/web01-tramite/es/</t>
+        </is>
+      </c>
+      <c r="C3194" s="20" t="n"/>
+      <c r="D3194" s="20" t="n"/>
+      <c r="E3194" s="20" t="n"/>
+      <c r="F3194" s="20" t="n"/>
+    </row>
+    <row r="3196" ht="30" customHeight="1">
+      <c r="A3196" s="16" t="inlineStr">
+        <is>
+          <t>FICHA 214: EUS-44336</t>
+        </is>
+      </c>
+      <c r="B3196" s="17" t="n"/>
+      <c r="C3196" s="17" t="n"/>
+      <c r="D3196" s="17" t="n"/>
+      <c r="E3196" s="17" t="n"/>
+      <c r="F3196" s="17" t="n"/>
+    </row>
+    <row r="3197" ht="20" customHeight="1">
+      <c r="A3197" s="18" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B3197" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Euskadi</t>
+        </is>
+      </c>
+      <c r="C3197" s="20" t="n"/>
+      <c r="D3197" s="20" t="n"/>
+      <c r="E3197" s="20" t="n"/>
+      <c r="F3197" s="20" t="n"/>
+    </row>
+    <row r="3198" ht="20" customHeight="1">
+      <c r="A3198" s="18" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="B3198" s="19" t="inlineStr">
+        <is>
+          <t>suministro de contenedores de120 litros ara uso en festejos</t>
+        </is>
+      </c>
+      <c r="C3198" s="20" t="n"/>
+      <c r="D3198" s="20" t="n"/>
+      <c r="E3198" s="20" t="n"/>
+      <c r="F3198" s="20" t="n"/>
+    </row>
+    <row r="3199" ht="20" customHeight="1">
+      <c r="A3199" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3199" s="19" t="inlineStr">
+        <is>
+          <t>EUS-44336</t>
+        </is>
+      </c>
+      <c r="C3199" s="20" t="n"/>
+      <c r="D3199" s="20" t="n"/>
+      <c r="E3199" s="20" t="n"/>
+      <c r="F3199" s="20" t="n"/>
+    </row>
+    <row r="3200" ht="20" customHeight="1">
+      <c r="A3200" s="18" t="inlineStr">
+        <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B3200" s="19" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="C3200" s="20" t="n"/>
+      <c r="D3200" s="20" t="n"/>
+      <c r="E3200" s="20" t="n"/>
+      <c r="F3200" s="20" t="n"/>
+    </row>
+    <row r="3201" ht="20" customHeight="1">
+      <c r="A3201" s="18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B3201" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C3201" s="20" t="n"/>
+      <c r="D3201" s="20" t="n"/>
+      <c r="E3201" s="20" t="n"/>
+      <c r="F3201" s="20" t="n"/>
+    </row>
+    <row r="3202" ht="20" customHeight="1">
+      <c r="A3202" s="18" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="B3202" s="19" t="inlineStr"/>
+      <c r="C3202" s="20" t="n"/>
+      <c r="D3202" s="20" t="n"/>
+      <c r="E3202" s="20" t="n"/>
+      <c r="F3202" s="20" t="n"/>
+    </row>
+    <row r="3203" ht="20" customHeight="1">
+      <c r="A3203" s="18" t="inlineStr">
+        <is>
+          <t>Presupuesto (EUR)</t>
+        </is>
+      </c>
+      <c r="B3203" s="19" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="C3203" s="20" t="n"/>
+      <c r="D3203" s="20" t="n"/>
+      <c r="E3203" s="20" t="n"/>
+      <c r="F3203" s="20" t="n"/>
+    </row>
+    <row r="3204" ht="20" customHeight="1">
+      <c r="A3204" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de Accion</t>
+        </is>
+      </c>
+      <c r="B3204" s="19" t="inlineStr">
+        <is>
+          <t>Licitacion Euskadi</t>
+        </is>
+      </c>
+      <c r="C3204" s="20" t="n"/>
+      <c r="D3204" s="20" t="n"/>
+      <c r="E3204" s="20" t="n"/>
+      <c r="F3204" s="20" t="n"/>
+    </row>
+    <row r="3205" ht="20" customHeight="1">
+      <c r="A3205" s="18" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B3205" s="19" t="inlineStr"/>
+      <c r="C3205" s="20" t="n"/>
+      <c r="D3205" s="20" t="n"/>
+      <c r="E3205" s="20" t="n"/>
+      <c r="F3205" s="20" t="n"/>
+    </row>
+    <row r="3206" ht="20" customHeight="1">
+      <c r="A3206" s="18" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="B3206" s="19" t="inlineStr">
+        <is>
+          <t>Gobierno Vasco / Sector Publico Euskadi</t>
+        </is>
+      </c>
+      <c r="C3206" s="20" t="n"/>
+      <c r="D3206" s="20" t="n"/>
+      <c r="E3206" s="20" t="n"/>
+      <c r="F3206" s="20" t="n"/>
+    </row>
+    <row r="3207" ht="20" customHeight="1">
+      <c r="A3207" s="18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="B3207" s="19" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="C3207" s="20" t="n"/>
+      <c r="D3207" s="20" t="n"/>
+      <c r="E3207" s="20" t="n"/>
+      <c r="F3207" s="20" t="n"/>
+    </row>
+    <row r="3208" ht="20" customHeight="1">
+      <c r="A3208" s="18" t="inlineStr">
+        <is>
+          <t>Relevancia Bilbao</t>
+        </is>
+      </c>
+      <c r="B3208" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIA — </t>
+        </is>
+      </c>
+      <c r="C3208" s="20" t="n"/>
+      <c r="D3208" s="20" t="n"/>
+      <c r="E3208" s="20" t="n"/>
+      <c r="F3208" s="20" t="n"/>
+    </row>
+    <row r="3209" ht="45" customHeight="1">
+      <c r="A3209" s="18" t="inlineStr">
+        <is>
+          <t>Enlace al portal</t>
+        </is>
+      </c>
+      <